--- a/data/df_best_models.xlsx
+++ b/data/df_best_models.xlsx
@@ -261,7 +261,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="151">
   <si>
     <t>id_country</t>
   </si>
@@ -413,13 +413,13 @@
     }</t>
   </si>
   <si>
-    <t>0.10</t>
-  </si>
-  <si>
     <t>[771, 772, 773, 774]</t>
   </si>
   <si>
     <t>SVC</t>
+  </si>
+  <si>
+    <t>4.9%</t>
   </si>
   <si>
     <t>Hasta el 20/8, le tenia miedo al doble oportunidad pero ahora ya no.</t>
@@ -473,6 +473,9 @@
   </si>
   <si>
     <t>0.7</t>
+  </si>
+  <si>
+    <t>0.10</t>
   </si>
   <si>
     <t>[591, 593, 594]</t>
@@ -1291,23 +1294,23 @@
     <xf borderId="3" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="3" fillId="0" fontId="3" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="3" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="10" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="3" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2077,7 +2080,7 @@
         <v>41</v>
       </c>
       <c r="F4" s="14">
-        <v>174.0</v>
+        <v>470.0</v>
       </c>
       <c r="G4" s="15">
         <v>30.0</v>
@@ -2085,27 +2088,25 @@
       <c r="H4" s="15">
         <v>3.0</v>
       </c>
-      <c r="I4" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="J4" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="K4" s="28" t="s">
-        <v>42</v>
+      <c r="I4" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J4" s="15"/>
+      <c r="K4" s="16" t="s">
+        <v>31</v>
       </c>
       <c r="L4" s="15">
         <v>5.0</v>
       </c>
       <c r="M4" s="15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N4" s="15"/>
       <c r="O4" s="15" t="s">
         <v>38</v>
       </c>
       <c r="P4" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Q4" s="18">
         <v>35.0</v>
@@ -2127,24 +2128,24 @@
         <v>14.60463869</v>
       </c>
       <c r="W4" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="X4" s="29">
-        <v>0.0205</v>
+        <v>39</v>
+      </c>
+      <c r="X4" s="15" t="s">
+        <v>44</v>
       </c>
       <c r="Y4" s="20">
-        <v>56.36</v>
+        <v>63.09</v>
       </c>
       <c r="Z4" s="15">
         <v>112.0</v>
       </c>
       <c r="AA4" s="20">
         <f t="shared" si="1"/>
-        <v>0.5032142857</v>
+        <v>0.5633035714</v>
       </c>
       <c r="AB4" s="20">
         <f>'Data preparation'!$B$2*AA4</f>
-        <v>0.07548214286</v>
+        <v>0.08449553571</v>
       </c>
       <c r="AC4" s="21" t="s">
         <v>45</v>
@@ -2157,13 +2158,13 @@
       <c r="B5" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="28">
         <v>45419.0</v>
       </c>
       <c r="D5" s="12">
         <v>1536.0</v>
       </c>
-      <c r="E5" s="31"/>
+      <c r="E5" s="29"/>
       <c r="F5" s="14">
         <v>808.0</v>
       </c>
@@ -2193,7 +2194,7 @@
         <v>38</v>
       </c>
       <c r="P5" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Q5" s="18">
         <v>34.0</v>
@@ -2217,7 +2218,7 @@
       <c r="W5" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="X5" s="29">
+      <c r="X5" s="30">
         <v>1.39</v>
       </c>
       <c r="Y5" s="20">
@@ -2237,7 +2238,7 @@
       <c r="AC5" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="AG5" s="32"/>
+      <c r="AG5" s="31"/>
     </row>
     <row r="6" ht="41.25" customHeight="1">
       <c r="A6" s="9">
@@ -2252,7 +2253,7 @@
       <c r="D6" s="26">
         <v>1536.0</v>
       </c>
-      <c r="E6" s="33" t="s">
+      <c r="E6" s="32" t="s">
         <v>50</v>
       </c>
       <c r="F6" s="14">
@@ -2267,10 +2268,10 @@
       <c r="I6" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="J6" s="28" t="s">
+      <c r="J6" s="33" t="s">
         <v>51</v>
       </c>
-      <c r="K6" s="28"/>
+      <c r="K6" s="33"/>
       <c r="L6" s="15"/>
       <c r="M6" s="15" t="s">
         <v>52</v>
@@ -2339,7 +2340,7 @@
       <c r="D7" s="12">
         <v>1152.0</v>
       </c>
-      <c r="E7" s="31" t="s">
+      <c r="E7" s="29" t="s">
         <v>41</v>
       </c>
       <c r="F7" s="14">
@@ -2358,13 +2359,13 @@
         <v>54</v>
       </c>
       <c r="K7" s="15" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="L7" s="15">
         <v>10.0</v>
       </c>
       <c r="M7" s="15" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="N7" s="15"/>
       <c r="O7" s="15" t="s">
@@ -2395,7 +2396,7 @@
       <c r="W7" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="X7" s="29">
+      <c r="X7" s="30">
         <v>0.2515</v>
       </c>
       <c r="Y7" s="20">
@@ -2420,9 +2421,9 @@
         <v>6.0</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="C8" s="30">
+        <v>57</v>
+      </c>
+      <c r="C8" s="28">
         <v>45419.0</v>
       </c>
       <c r="D8" s="12">
@@ -2451,7 +2452,7 @@
         <v>3.0</v>
       </c>
       <c r="M8" s="15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N8" s="16"/>
       <c r="O8" s="16" t="s">
@@ -2482,7 +2483,7 @@
       <c r="W8" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="X8" s="29">
+      <c r="X8" s="30">
         <v>3.0E-4</v>
       </c>
       <c r="Y8" s="20">
@@ -2652,12 +2653,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="47" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="48" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B2" s="44">
         <v>0.15</v>
@@ -2666,19 +2667,19 @@
     </row>
     <row r="3">
       <c r="A3" s="47" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B3" s="49">
         <f>MAX('Modelos actuales'!T3:T7)</f>
         <v>18.6475</v>
       </c>
       <c r="E3" s="48" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="47" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B4" s="48">
         <v>18.0</v>
@@ -2692,7 +2693,7 @@
       <c r="A7" s="50"/>
       <c r="B7" s="50"/>
       <c r="E7" s="51" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F7" s="36">
         <f t="shared" ref="F7:F16" si="1">REPLACE(E7,FIND(".",E7),1,",")*1</f>
@@ -2701,7 +2702,7 @@
     </row>
     <row r="8">
       <c r="E8" s="52" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F8" s="36">
         <f t="shared" si="1"/>
@@ -2710,7 +2711,7 @@
     </row>
     <row r="9">
       <c r="E9" s="51" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F9" s="36">
         <f t="shared" si="1"/>
@@ -2719,7 +2720,7 @@
     </row>
     <row r="10">
       <c r="E10" s="52" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F10" s="36">
         <f t="shared" si="1"/>
@@ -2728,7 +2729,7 @@
     </row>
     <row r="11">
       <c r="E11" s="51" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F11" s="36">
         <f t="shared" si="1"/>
@@ -2737,7 +2738,7 @@
     </row>
     <row r="12">
       <c r="E12" s="52" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F12" s="36">
         <f t="shared" si="1"/>
@@ -2746,7 +2747,7 @@
     </row>
     <row r="13">
       <c r="E13" s="51" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F13" s="36">
         <f t="shared" si="1"/>
@@ -2755,7 +2756,7 @@
     </row>
     <row r="14">
       <c r="E14" s="52" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F14" s="36">
         <f t="shared" si="1"/>
@@ -2764,7 +2765,7 @@
     </row>
     <row r="15">
       <c r="E15" s="51" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F15" s="36">
         <f t="shared" si="1"/>
@@ -2773,7 +2774,7 @@
     </row>
     <row r="16">
       <c r="E16" s="52" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F16" s="36">
         <f t="shared" si="1"/>
@@ -2804,11 +2805,11 @@
       <c r="B1" s="53"/>
       <c r="C1" s="53"/>
       <c r="D1" s="54" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F1" s="55"/>
       <c r="G1" s="56" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J1" s="53"/>
       <c r="K1" s="53"/>
@@ -2816,13 +2817,13 @@
     </row>
     <row r="2">
       <c r="A2" s="57" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B2" s="57" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C2" s="57" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D2" s="58" t="s">
         <v>3</v>
@@ -2831,7 +2832,7 @@
         <v>4</v>
       </c>
       <c r="F2" s="60" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G2" s="61" t="s">
         <v>20</v>
@@ -2843,20 +2844,20 @@
         <v>19</v>
       </c>
       <c r="J2" s="57" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K2" s="57" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L2" s="57" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" ht="108.0" customHeight="1">
       <c r="A3" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="30">
+      <c r="B3" s="28">
         <v>45418.0</v>
       </c>
       <c r="C3" s="63"/>
@@ -2872,23 +2873,23 @@
         <v>17.31</v>
       </c>
       <c r="I3" s="68" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J3" s="69" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K3" s="70" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L3" s="71" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" ht="108.0" customHeight="1">
       <c r="A4" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="30">
+      <c r="B4" s="28">
         <v>45418.0</v>
       </c>
       <c r="C4" s="63"/>
@@ -2907,20 +2908,20 @@
         <v>46.72</v>
       </c>
       <c r="J4" s="69" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K4" s="70" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L4" s="74" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" ht="42.0" customHeight="1">
       <c r="A5" s="75" t="s">
         <v>46</v>
       </c>
-      <c r="B5" s="30">
+      <c r="B5" s="28">
         <v>45419.0</v>
       </c>
       <c r="C5" s="63"/>
@@ -2939,7 +2940,7 @@
         <v>16.21</v>
       </c>
       <c r="J5" s="69" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K5" s="76"/>
       <c r="L5" s="77"/>
@@ -2961,7 +2962,7 @@
       <c r="H6" s="80"/>
       <c r="I6" s="81"/>
       <c r="J6" s="69" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K6" s="76"/>
       <c r="L6" s="75" t="s">
@@ -2970,9 +2971,9 @@
     </row>
     <row r="7">
       <c r="A7" s="34" t="s">
-        <v>56</v>
-      </c>
-      <c r="B7" s="30">
+        <v>57</v>
+      </c>
+      <c r="B7" s="28">
         <v>45419.0</v>
       </c>
       <c r="C7" s="63"/>
@@ -2985,11 +2986,11 @@
       <c r="H7" s="83"/>
       <c r="I7" s="83"/>
       <c r="J7" s="69" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K7" s="76"/>
       <c r="L7" s="75" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8">
@@ -3009,7 +3010,7 @@
       <c r="H8" s="80"/>
       <c r="I8" s="81"/>
       <c r="J8" s="69" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K8" s="76"/>
       <c r="L8" s="77"/>
@@ -3022,7 +3023,7 @@
         <v>45498.0</v>
       </c>
       <c r="C9" s="84" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D9" s="82">
         <v>1152.0</v>
@@ -3041,11 +3042,11 @@
         <v>15.41</v>
       </c>
       <c r="J9" s="69" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K9" s="84"/>
       <c r="L9" s="75" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" ht="49.5" customHeight="1">
@@ -3056,7 +3057,7 @@
         <v>45498.0</v>
       </c>
       <c r="C10" s="84" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D10" s="82">
         <v>1152.0</v>
@@ -3075,7 +3076,7 @@
         <v>8.63</v>
       </c>
       <c r="J10" s="75" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K10" s="84"/>
       <c r="L10" s="75"/>
@@ -3088,16 +3089,16 @@
         <v>45502.0</v>
       </c>
       <c r="C11" s="84" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D11" s="82">
         <v>1728.0</v>
       </c>
       <c r="E11" s="85" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F11" s="86" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G11" s="37">
         <v>8.9</v>
@@ -3109,13 +3110,13 @@
         <v>5.5</v>
       </c>
       <c r="J11" s="75" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K11" s="84" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L11" s="75" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12" ht="73.5" customHeight="1">
@@ -3126,7 +3127,7 @@
         <v>45504.0</v>
       </c>
       <c r="C12" s="84" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D12" s="82">
         <v>1536.0</v>
@@ -3135,7 +3136,7 @@
         <v>50</v>
       </c>
       <c r="F12" s="86" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G12" s="37">
         <v>19.73</v>
@@ -3144,16 +3145,16 @@
         <v>47.88</v>
       </c>
       <c r="I12" s="38" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J12" s="75" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K12" s="84" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L12" s="75" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13">
@@ -3167,7 +3168,7 @@
     </row>
     <row r="14">
       <c r="A14" s="94" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D14" s="88"/>
       <c r="F14" s="89"/>
@@ -10233,7 +10234,7 @@
         <v>1</v>
       </c>
       <c r="J2" s="15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K2" s="15" t="s">
         <v>31</v>
@@ -10242,12 +10243,12 @@
         <v>5.0</v>
       </c>
       <c r="M2" s="16" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N2" s="16"/>
       <c r="O2" s="16"/>
       <c r="P2" s="34" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Q2" s="18">
         <v>18.0</v>
@@ -10270,7 +10271,7 @@
         <v>66.1176029</v>
       </c>
       <c r="W2" s="14" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="X2" s="20">
         <v>15.0684194244387</v>
@@ -10308,7 +10309,7 @@
       <c r="F3" s="14">
         <v>300.0</v>
       </c>
-      <c r="G3" s="28">
+      <c r="G3" s="33">
         <v>30.0</v>
       </c>
       <c r="H3" s="96">
@@ -10317,7 +10318,7 @@
       <c r="I3" s="16" t="b">
         <v>0</v>
       </c>
-      <c r="J3" s="28" t="s">
+      <c r="J3" s="33" t="s">
         <v>54</v>
       </c>
       <c r="K3" s="96"/>
@@ -10325,7 +10326,7 @@
         <v>10.0</v>
       </c>
       <c r="M3" s="16" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N3" s="15" t="s">
         <v>33</v>
@@ -10462,7 +10463,7 @@
         <v>0.04863669065</v>
       </c>
       <c r="AC4" s="21" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" ht="31.5" customHeight="1">
@@ -10478,7 +10479,7 @@
       <c r="D5" s="12">
         <v>1536.0</v>
       </c>
-      <c r="E5" s="31"/>
+      <c r="E5" s="29"/>
       <c r="F5" s="14">
         <v>808.0</v>
       </c>
@@ -10508,7 +10509,7 @@
         <v>38</v>
       </c>
       <c r="P5" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Q5" s="18">
         <v>34.0</v>
@@ -10552,7 +10553,7 @@
       <c r="AC5" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="AG5" s="32"/>
+      <c r="AG5" s="31"/>
     </row>
     <row r="6" ht="41.25" customHeight="1">
       <c r="A6" s="9">
@@ -10567,7 +10568,7 @@
       <c r="D6" s="12">
         <v>1152.0</v>
       </c>
-      <c r="E6" s="31" t="s">
+      <c r="E6" s="29" t="s">
         <v>41</v>
       </c>
       <c r="F6" s="14">
@@ -10586,20 +10587,20 @@
         <v>30</v>
       </c>
       <c r="K6" s="15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L6" s="15">
         <v>5.0</v>
       </c>
       <c r="M6" s="15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N6" s="16"/>
       <c r="O6" s="16" t="s">
         <v>38</v>
       </c>
       <c r="P6" s="34" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Q6" s="18">
         <v>35.0</v>
@@ -10623,7 +10624,7 @@
       <c r="W6" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="X6" s="29">
+      <c r="X6" s="30">
         <v>0.047</v>
       </c>
       <c r="Y6" s="20">
@@ -10656,7 +10657,7 @@
       <c r="D7" s="12">
         <v>1152.0</v>
       </c>
-      <c r="E7" s="31" t="s">
+      <c r="E7" s="29" t="s">
         <v>41</v>
       </c>
       <c r="F7" s="14">
@@ -10675,7 +10676,7 @@
       <c r="K7" s="16"/>
       <c r="L7" s="16"/>
       <c r="M7" s="15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N7" s="15" t="s">
         <v>33</v>
@@ -10704,9 +10705,9 @@
         <v>8.330339188</v>
       </c>
       <c r="W7" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="X7" s="29">
+        <v>106</v>
+      </c>
+      <c r="X7" s="30">
         <v>0.3172</v>
       </c>
       <c r="Y7" s="20">
@@ -10731,7 +10732,7 @@
         <v>6.0</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C8" s="22">
         <v>45419.0</v>
@@ -10760,7 +10761,7 @@
         <v>10.0</v>
       </c>
       <c r="M8" s="15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N8" s="16" t="s">
         <v>33</v>
@@ -10793,7 +10794,7 @@
       <c r="W8" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="X8" s="29">
+      <c r="X8" s="30">
         <v>-6.0E-4</v>
       </c>
       <c r="Y8" s="20">
@@ -10826,7 +10827,7 @@
       <c r="D9" s="12">
         <v>768.0</v>
       </c>
-      <c r="E9" s="31"/>
+      <c r="E9" s="29"/>
       <c r="F9" s="14">
         <v>358.0</v>
       </c>
@@ -10840,12 +10841,12 @@
         <v>0</v>
       </c>
       <c r="J9" s="15" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K9" s="15"/>
       <c r="L9" s="15"/>
       <c r="M9" s="15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N9" s="16"/>
       <c r="O9" s="15" t="s">
@@ -10877,7 +10878,7 @@
       <c r="W9" s="14">
         <v>-0.15</v>
       </c>
-      <c r="X9" s="29">
+      <c r="X9" s="30">
         <v>0.0598</v>
       </c>
       <c r="Y9" s="20">
@@ -10923,7 +10924,7 @@
       <c r="D12" s="97"/>
       <c r="E12" s="97"/>
       <c r="F12" s="97"/>
-      <c r="S12" s="32"/>
+      <c r="S12" s="31"/>
       <c r="T12" s="90"/>
       <c r="U12" s="90"/>
       <c r="AG12" s="36"/>
@@ -10948,7 +10949,7 @@
     </row>
     <row r="18">
       <c r="A18" s="101" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C18" s="97"/>
       <c r="D18" s="97"/>
@@ -11075,7 +11076,7 @@
         <v>1</v>
       </c>
       <c r="J20" s="15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K20" s="15" t="s">
         <v>31</v>
@@ -11084,12 +11085,12 @@
         <v>5.0</v>
       </c>
       <c r="M20" s="16" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N20" s="16"/>
       <c r="O20" s="16"/>
       <c r="P20" s="34" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Q20" s="18">
         <v>18.0</v>
@@ -11110,7 +11111,7 @@
         <v>17.717537506466634</v>
       </c>
       <c r="W20" s="43" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="X20" s="44">
         <v>15.0684194244387</v>
@@ -11211,7 +11212,7 @@
         <v>0.048636690647482016</v>
       </c>
       <c r="AC21" s="48" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AG21" s="36"/>
     </row>
@@ -11228,30 +11229,30 @@
       <c r="D22" s="26">
         <v>1536.0</v>
       </c>
-      <c r="E22" s="33" t="s">
+      <c r="E22" s="32" t="s">
         <v>50</v>
       </c>
       <c r="F22" s="14">
         <v>559.0</v>
       </c>
-      <c r="G22" s="28">
+      <c r="G22" s="33">
         <v>30.0</v>
       </c>
-      <c r="H22" s="28">
+      <c r="H22" s="33">
         <v>3.0</v>
       </c>
       <c r="I22" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="J22" s="28" t="s">
-        <v>113</v>
-      </c>
-      <c r="K22" s="28" t="s">
-        <v>42</v>
+      <c r="J22" s="33" t="s">
+        <v>114</v>
+      </c>
+      <c r="K22" s="33" t="s">
+        <v>55</v>
       </c>
       <c r="L22" s="15"/>
       <c r="M22" s="15" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N22" s="15" t="s">
         <v>33</v>
@@ -11279,7 +11280,7 @@
         <v>15.310398344542163</v>
       </c>
       <c r="W22" s="43" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="X22" s="44">
         <v>1.11</v>
@@ -11306,13 +11307,13 @@
       <c r="B23" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="C23" s="30">
+      <c r="C23" s="28">
         <v>45419.0</v>
       </c>
       <c r="D23" s="12">
         <v>1536.0</v>
       </c>
-      <c r="E23" s="31"/>
+      <c r="E23" s="29"/>
       <c r="F23" s="14">
         <v>808.0</v>
       </c>
@@ -11342,7 +11343,7 @@
         <v>38</v>
       </c>
       <c r="P23" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Q23" s="18">
         <v>34.0</v>
@@ -11413,23 +11414,23 @@
         <v>1</v>
       </c>
       <c r="J24" s="15" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K24" s="15" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="L24" s="15">
         <v>5.0</v>
       </c>
       <c r="M24" s="15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="N24" s="16"/>
       <c r="O24" s="15" t="s">
         <v>38</v>
       </c>
       <c r="P24" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Q24" s="18">
         <v>35.0</v>
@@ -11450,7 +11451,7 @@
         <v>11.958096223486809</v>
       </c>
       <c r="W24" s="43" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="X24" s="46">
         <v>0.047</v>
@@ -11482,7 +11483,7 @@
       <c r="D25" s="12">
         <v>1152.0</v>
       </c>
-      <c r="E25" s="31" t="s">
+      <c r="E25" s="29" t="s">
         <v>41</v>
       </c>
       <c r="F25" s="14">
@@ -11501,7 +11502,7 @@
       <c r="K25" s="16"/>
       <c r="L25" s="16"/>
       <c r="M25" s="15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N25" s="15" t="s">
         <v>33</v>
@@ -11529,7 +11530,7 @@
         <v>6.696844283497156</v>
       </c>
       <c r="W25" s="43" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="X25" s="46">
         <v>0.3172</v>
@@ -11553,9 +11554,9 @@
         <v>6.0</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="C26" s="30">
+        <v>57</v>
+      </c>
+      <c r="C26" s="28">
         <v>45419.0</v>
       </c>
       <c r="D26" s="12">
@@ -11584,7 +11585,7 @@
         <v>3.0</v>
       </c>
       <c r="M26" s="15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N26" s="16"/>
       <c r="O26" s="16" t="s">
@@ -11645,7 +11646,7 @@
     </row>
     <row r="34">
       <c r="A34" s="101" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="W34" s="42"/>
     </row>
@@ -11738,7 +11739,7 @@
         <v>17.690894981893432</v>
       </c>
       <c r="J37" s="43" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K37" s="44">
         <v>6.11</v>
@@ -11778,7 +11779,7 @@
         <v>15.888515261251941</v>
       </c>
       <c r="J38" s="43" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K38" s="46">
         <v>0.0259</v>
@@ -11852,7 +11853,7 @@
         <v>13.457061562338335</v>
       </c>
       <c r="J40" s="43" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K40" s="44">
         <v>0.83</v>
@@ -11889,7 +11890,7 @@
         <v>4.319710294878428</v>
       </c>
       <c r="J41" s="43" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K41" s="46">
         <v>0.2515</v>
@@ -12004,10 +12005,10 @@
   <sheetData>
     <row r="5">
       <c r="F5" s="104" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H5" s="105" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J5" s="55"/>
     </row>
@@ -12022,22 +12023,22 @@
         <v>2</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F6" s="106" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G6" s="107" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H6" s="108" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I6" s="109" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J6" s="110" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7">
@@ -12047,7 +12048,7 @@
       <c r="C7" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="28">
         <v>45419.0</v>
       </c>
       <c r="E7" s="17">
@@ -12057,7 +12058,7 @@
         <v>-0.16</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H7" s="113">
         <v>2304.0</v>
@@ -12087,7 +12088,7 @@
         <v>-0.34</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H8" s="116">
         <v>768.0</v>
@@ -12107,7 +12108,7 @@
       <c r="C9" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="28">
         <v>45504.0</v>
       </c>
       <c r="E9" s="17">
@@ -12117,7 +12118,7 @@
         <v>-0.23</v>
       </c>
       <c r="G9" s="17" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H9" s="117">
         <v>1536.0</v>
@@ -12137,7 +12138,7 @@
       <c r="C10" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="28">
         <v>45419.0</v>
       </c>
       <c r="E10" s="17">
@@ -12147,7 +12148,7 @@
         <v>-0.23</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H10" s="116">
         <v>1536.0</v>
@@ -12167,7 +12168,7 @@
       <c r="C11" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="28">
         <v>45498.0</v>
       </c>
       <c r="E11" s="17">
@@ -12177,7 +12178,7 @@
         <v>-0.2</v>
       </c>
       <c r="G11" s="17" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H11" s="117">
         <v>1152.0</v>
@@ -12207,7 +12208,7 @@
         <v>-0.24</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H12" s="116">
         <v>1152.0</v>
@@ -12225,9 +12226,9 @@
         <v>6.0</v>
       </c>
       <c r="C13" s="34" t="s">
-        <v>56</v>
-      </c>
-      <c r="D13" s="30">
+        <v>57</v>
+      </c>
+      <c r="D13" s="28">
         <v>45419.0</v>
       </c>
       <c r="E13" s="34">
@@ -12236,8 +12237,8 @@
       <c r="F13" s="112">
         <v>-0.33</v>
       </c>
-      <c r="G13" s="30" t="s">
-        <v>132</v>
+      <c r="G13" s="28" t="s">
+        <v>133</v>
       </c>
       <c r="H13" s="116">
         <v>2304.0</v>
@@ -12270,36 +12271,36 @@
   <sheetData>
     <row r="7">
       <c r="B7" s="101" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="48" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="119" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="120" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F10" s="48" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G10" s="48" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H10" s="48" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" s="48" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D11" s="48">
         <v>-0.15</v>
@@ -12315,22 +12316,22 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I11" s="47" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12">
       <c r="C12" s="120" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13">
       <c r="C13" s="120" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="120" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F14" s="48">
         <v>2.0</v>
@@ -12345,7 +12346,7 @@
     </row>
     <row r="15">
       <c r="C15" s="48" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D15" s="48">
         <v>-0.1</v>
@@ -12353,17 +12354,17 @@
     </row>
     <row r="16">
       <c r="C16" s="120" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="17">
       <c r="C17" s="120" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="120" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F18" s="48">
         <v>0.0</v>
@@ -12378,7 +12379,7 @@
     </row>
     <row r="19">
       <c r="C19" s="48" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D19" s="48">
         <v>-0.15</v>
@@ -12386,17 +12387,17 @@
     </row>
     <row r="20">
       <c r="C20" s="120" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="21">
       <c r="C21" s="120" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="121" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="26">
@@ -12432,7 +12433,7 @@
       <c r="C27" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="D27" s="30">
+      <c r="D27" s="28">
         <v>45419.0</v>
       </c>
       <c r="E27" s="11">
@@ -12459,7 +12460,7 @@
       <c r="C28" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="D28" s="30">
+      <c r="D28" s="28">
         <v>45467.0</v>
       </c>
       <c r="E28" s="11">
@@ -12485,7 +12486,7 @@
       <c r="C29" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="D29" s="30">
+      <c r="D29" s="28">
         <v>45504.0</v>
       </c>
       <c r="E29" s="22">
@@ -12511,7 +12512,7 @@
       <c r="C30" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D30" s="30">
+      <c r="D30" s="28">
         <v>45419.0</v>
       </c>
       <c r="E30" s="11">
@@ -12537,7 +12538,7 @@
       <c r="C31" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="D31" s="30">
+      <c r="D31" s="28">
         <v>45498.0</v>
       </c>
       <c r="E31" s="22">
@@ -12563,7 +12564,7 @@
       <c r="C32" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="D32" s="30">
+      <c r="D32" s="28">
         <v>45498.0</v>
       </c>
       <c r="E32" s="11">
@@ -12587,9 +12588,9 @@
         <v>6.0</v>
       </c>
       <c r="C33" s="34" t="s">
-        <v>56</v>
-      </c>
-      <c r="D33" s="30">
+        <v>57</v>
+      </c>
+      <c r="D33" s="28">
         <v>45419.0</v>
       </c>
       <c r="E33" s="39">

--- a/data/df_best_models.xlsx
+++ b/data/df_best_models.xlsx
@@ -2219,7 +2219,7 @@
         <v>45677.0</v>
       </c>
       <c r="D7" s="23">
-        <v>19.0</v>
+        <v>1623.0</v>
       </c>
       <c r="E7" s="23" t="s">
         <v>22</v>

--- a/data/df_best_models.xlsx
+++ b/data/df_best_models.xlsx
@@ -210,7 +210,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="263">
   <si>
     <t>id_country</t>
   </si>
@@ -644,6 +644,12 @@
     <t>4.54</t>
   </si>
   <si>
+    <t>n_iteration</t>
+  </si>
+  <si>
+    <t>roi</t>
+  </si>
+  <si>
     <t>Falta entrenarlos: 1) sin rellenar formaciones antes de construir 2) Con todos l_models y no solo logistic.</t>
   </si>
   <si>
@@ -948,9 +954,6 @@
   </si>
   <si>
     <t>roi_100</t>
-  </si>
-  <si>
-    <t>roi</t>
   </si>
   <si>
     <t>roi_por_partido</t>
@@ -2036,7 +2039,9 @@
       <c r="E4" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="24"/>
+      <c r="F4" s="24">
+        <v>56.3636363636363</v>
+      </c>
       <c r="G4" s="24">
         <v>161.57</v>
       </c>
@@ -2085,7 +2090,9 @@
       <c r="E5" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="24"/>
+      <c r="F5" s="24">
+        <v>57.7981651376146</v>
+      </c>
       <c r="G5" s="24">
         <v>147.288321859431</v>
       </c>
@@ -2186,7 +2193,9 @@
       <c r="E7" s="23" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="24"/>
+      <c r="F7" s="24">
+        <v>59.2592592592592</v>
+      </c>
       <c r="G7" s="24">
         <v>197.314387756965</v>
       </c>
@@ -2230,44 +2239,44 @@
         <v>45677.0</v>
       </c>
       <c r="D8" s="23">
-        <v>112.0</v>
+        <v>1051.0</v>
       </c>
       <c r="E8" s="23" t="s">
         <v>17</v>
       </c>
       <c r="F8" s="24">
-        <v>56.8807339449541</v>
+        <v>53.2110091743119</v>
       </c>
       <c r="G8" s="24">
-        <v>107.0</v>
+        <v>191.629402836081</v>
       </c>
       <c r="H8" s="24">
-        <f>274.34+
-1948.08+
-12.5
+        <f>301.19+
+154.98+
+109.46
 </f>
-        <v>2234.92</v>
+        <v>565.63</v>
       </c>
       <c r="I8" s="24">
         <f t="shared" si="1"/>
-        <v>20.8871028</v>
+        <v>2.95168691</v>
       </c>
       <c r="J8" s="19">
-        <v>40.0</v>
+        <v>50.0</v>
       </c>
       <c r="K8" s="19">
-        <v>70.0</v>
+        <v>15.0</v>
       </c>
       <c r="L8" s="19">
-        <v>10.0</v>
+        <v>20.0</v>
       </c>
       <c r="M8" s="19">
         <f t="shared" si="2"/>
-        <v>40</v>
+        <v>28.33333333</v>
       </c>
       <c r="N8" s="15">
         <f>M8*'Data preparation'!$C$2</f>
-        <v>12</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="9" ht="20.25" customHeight="1">
@@ -12748,7 +12757,7 @@
       </c>
       <c r="C3" s="15">
         <f>AVERAGE('Modelos actuales'!N4:N8)</f>
-        <v>12.4</v>
+        <v>11.7</v>
       </c>
       <c r="L3" s="89"/>
       <c r="P3" s="89"/>
@@ -13649,6 +13658,15 @@
       <c r="P28" s="92">
         <v>1.0</v>
       </c>
+      <c r="AA28" s="35" t="s">
+        <v>144</v>
+      </c>
+      <c r="AB28" s="35" t="s">
+        <v>145</v>
+      </c>
+      <c r="AC28" s="35" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="29">
       <c r="F29" s="29" t="s">
@@ -13670,46 +13688,144 @@
       <c r="P29" s="92">
         <v>1.0</v>
       </c>
+      <c r="AA29" s="36">
+        <v>1051.0</v>
+      </c>
+      <c r="AB29" s="35">
+        <v>207.56</v>
+      </c>
+      <c r="AC29" s="37">
+        <f t="shared" ref="AC29:AC43" si="15">VLOOKUP(AA29,$AA$48:$AB$62,2,0)</f>
+        <v>263.81</v>
+      </c>
+      <c r="AD29" s="93">
+        <f t="shared" ref="AD29:AD43" si="16">(AC29-AB29)/AB29</f>
+        <v>0.2710059742</v>
+      </c>
     </row>
     <row r="30">
       <c r="P30" s="92">
         <v>2.0</v>
       </c>
+      <c r="AA30" s="35">
+        <v>112.0</v>
+      </c>
+      <c r="AB30" s="35">
+        <v>185.35</v>
+      </c>
+      <c r="AC30" s="37">
+        <f t="shared" si="15"/>
+        <v>130.76</v>
+      </c>
+      <c r="AD30" s="93">
+        <f t="shared" si="16"/>
+        <v>-0.2945238738</v>
+      </c>
     </row>
     <row r="31">
       <c r="P31" s="92">
         <v>0.0</v>
       </c>
+      <c r="AA31" s="35">
+        <v>752.0</v>
+      </c>
+      <c r="AB31" s="35">
+        <v>121.6</v>
+      </c>
+      <c r="AC31" s="37">
+        <f t="shared" si="15"/>
+        <v>78.68</v>
+      </c>
+      <c r="AD31" s="93">
+        <f t="shared" si="16"/>
+        <v>-0.3529605263</v>
+      </c>
     </row>
     <row r="32">
       <c r="B32" s="47" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G32" s="95"/>
       <c r="P32" s="92">
         <v>1.0</v>
       </c>
+      <c r="AA32" s="36">
+        <v>1475.0</v>
+      </c>
+      <c r="AB32" s="35">
+        <v>120.82</v>
+      </c>
+      <c r="AC32" s="37">
+        <f t="shared" si="15"/>
+        <v>83.5</v>
+      </c>
+      <c r="AD32" s="93">
+        <f t="shared" si="16"/>
+        <v>-0.3088892567</v>
+      </c>
     </row>
     <row r="33">
       <c r="B33" s="101" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G33" s="102"/>
       <c r="P33" s="92">
         <v>1.0</v>
       </c>
+      <c r="AA33" s="36">
+        <v>1545.0</v>
+      </c>
+      <c r="AB33" s="35">
+        <v>111.42</v>
+      </c>
+      <c r="AC33" s="37">
+        <f t="shared" si="15"/>
+        <v>101.16</v>
+      </c>
+      <c r="AD33" s="93">
+        <f t="shared" si="16"/>
+        <v>-0.09208400646</v>
+      </c>
     </row>
     <row r="34">
       <c r="P34" s="92">
         <v>2.0</v>
       </c>
+      <c r="AA34" s="35">
+        <v>814.0</v>
+      </c>
+      <c r="AB34" s="35">
+        <v>104.32</v>
+      </c>
+      <c r="AC34" s="37">
+        <f t="shared" si="15"/>
+        <v>60.31</v>
+      </c>
+      <c r="AD34" s="93">
+        <f t="shared" si="16"/>
+        <v>-0.421875</v>
+      </c>
     </row>
     <row r="35">
       <c r="H35" s="29" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="P35" s="92">
         <v>0.0</v>
+      </c>
+      <c r="AA35" s="36">
+        <v>1426.0</v>
+      </c>
+      <c r="AB35" s="35">
+        <v>101.23</v>
+      </c>
+      <c r="AC35" s="37">
+        <f t="shared" si="15"/>
+        <v>68.02</v>
+      </c>
+      <c r="AD35" s="93">
+        <f t="shared" si="16"/>
+        <v>-0.3280648029</v>
       </c>
     </row>
     <row r="36">
@@ -13721,6 +13837,20 @@
       </c>
       <c r="P36" s="92">
         <v>1.0</v>
+      </c>
+      <c r="AA36" s="36">
+        <v>1447.0</v>
+      </c>
+      <c r="AB36" s="35">
+        <v>97.89</v>
+      </c>
+      <c r="AC36" s="37">
+        <f t="shared" si="15"/>
+        <v>138.76</v>
+      </c>
+      <c r="AD36" s="93">
+        <f t="shared" si="16"/>
+        <v>0.4175094494</v>
       </c>
     </row>
     <row r="37">
@@ -13740,6 +13870,20 @@
       <c r="P37" s="92">
         <v>0.0</v>
       </c>
+      <c r="AA37" s="35">
+        <v>136.0</v>
+      </c>
+      <c r="AB37" s="35">
+        <v>87.93</v>
+      </c>
+      <c r="AC37" s="37">
+        <f t="shared" si="15"/>
+        <v>58.8</v>
+      </c>
+      <c r="AD37" s="93">
+        <f t="shared" si="16"/>
+        <v>-0.3312862504</v>
+      </c>
     </row>
     <row r="38">
       <c r="G38" s="29" t="s">
@@ -13751,13 +13895,27 @@
       <c r="P38" s="92">
         <v>2.0</v>
       </c>
+      <c r="AA38" s="36">
+        <v>1526.0</v>
+      </c>
+      <c r="AB38" s="35">
+        <v>85.82</v>
+      </c>
+      <c r="AC38" s="37">
+        <f t="shared" si="15"/>
+        <v>53.3</v>
+      </c>
+      <c r="AD38" s="93">
+        <f t="shared" si="16"/>
+        <v>-0.3789326497</v>
+      </c>
     </row>
     <row r="39">
       <c r="C39" s="106" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D39" s="95">
-        <f t="shared" ref="D39:D221" si="15">IF(COUNTA(C39)=1,C39/1,"")</f>
+        <f t="shared" ref="D39:D221" si="17">IF(COUNTA(C39)=1,C39/1,"")</f>
         <v>0</v>
       </c>
       <c r="G39" s="29" t="s">
@@ -13769,13 +13927,27 @@
       <c r="P39" s="92">
         <v>2.0</v>
       </c>
+      <c r="AA39" s="35">
+        <v>952.0</v>
+      </c>
+      <c r="AB39" s="35">
+        <v>78.09</v>
+      </c>
+      <c r="AC39" s="37">
+        <f t="shared" si="15"/>
+        <v>73.76</v>
+      </c>
+      <c r="AD39" s="93">
+        <f t="shared" si="16"/>
+        <v>-0.05544884108</v>
+      </c>
     </row>
     <row r="40">
       <c r="C40" s="107" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D40" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="G40" s="29" t="s">
@@ -13787,83 +13959,151 @@
       <c r="P40" s="92">
         <v>0.0</v>
       </c>
+      <c r="AA40" s="36">
+        <v>1606.0</v>
+      </c>
+      <c r="AB40" s="35">
+        <v>77.21</v>
+      </c>
+      <c r="AC40" s="37">
+        <f t="shared" si="15"/>
+        <v>75.05</v>
+      </c>
+      <c r="AD40" s="93">
+        <f t="shared" si="16"/>
+        <v>-0.02797565082</v>
+      </c>
     </row>
     <row r="41">
       <c r="C41" s="107" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D41" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.36</v>
       </c>
       <c r="P41" s="92">
         <v>1.0</v>
       </c>
+      <c r="AA41" s="36">
+        <v>1164.0</v>
+      </c>
+      <c r="AB41" s="35">
+        <v>76.05</v>
+      </c>
+      <c r="AC41" s="37">
+        <f t="shared" si="15"/>
+        <v>26.27</v>
+      </c>
+      <c r="AD41" s="93">
+        <f t="shared" si="16"/>
+        <v>-0.6545693623</v>
+      </c>
     </row>
     <row r="42">
       <c r="C42" s="107" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D42" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.25</v>
       </c>
       <c r="P42" s="92">
         <v>1.0</v>
       </c>
+      <c r="AA42" s="36">
+        <v>1448.0</v>
+      </c>
+      <c r="AB42" s="35">
+        <v>71.77</v>
+      </c>
+      <c r="AC42" s="37">
+        <f t="shared" si="15"/>
+        <v>39.69</v>
+      </c>
+      <c r="AD42" s="93">
+        <f t="shared" si="16"/>
+        <v>-0.4469834193</v>
+      </c>
     </row>
     <row r="43">
       <c r="C43" s="107" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D43" s="95">
+        <f t="shared" si="17"/>
+        <v>0.68</v>
+      </c>
+      <c r="P43" s="92"/>
+      <c r="AA43" s="36">
+        <v>1614.0</v>
+      </c>
+      <c r="AB43" s="35">
+        <v>68.01</v>
+      </c>
+      <c r="AC43" s="37">
         <f t="shared" si="15"/>
-        <v>0.68</v>
-      </c>
-      <c r="P43" s="92"/>
+        <v>67.42</v>
+      </c>
+      <c r="AD43" s="93">
+        <f t="shared" si="16"/>
+        <v>-0.008675194824</v>
+      </c>
     </row>
     <row r="44">
       <c r="C44" s="107" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D44" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="P44" s="92"/>
+      <c r="AB44" s="37">
+        <f t="shared" ref="AB44:AD44" si="18">AVERAGE(AB29:AB43)</f>
+        <v>106.338</v>
+      </c>
+      <c r="AC44" s="37">
+        <f t="shared" si="18"/>
+        <v>87.95266667</v>
+      </c>
+      <c r="AD44" s="93">
+        <f t="shared" si="18"/>
+        <v>-0.2009168941</v>
+      </c>
     </row>
     <row r="45">
       <c r="C45" s="107" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D45" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>11.25</v>
       </c>
       <c r="P45" s="92"/>
     </row>
     <row r="46">
       <c r="C46" s="107" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D46" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>9.76</v>
       </c>
       <c r="G46" s="66" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H46" s="66" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="P46" s="92"/>
     </row>
     <row r="47">
       <c r="C47" s="107" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D47" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>10.4</v>
       </c>
       <c r="G47" s="71" t="s">
@@ -13873,13 +14113,19 @@
         <v>0.376453591155815</v>
       </c>
       <c r="P47" s="92"/>
+      <c r="AA47" s="35" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB47" s="35" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="48">
       <c r="C48" s="107" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D48" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>10.84</v>
       </c>
       <c r="G48" s="71" t="s">
@@ -13889,20 +14135,26 @@
         <v>0.36678739680281</v>
       </c>
       <c r="J48" s="35" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="K48" s="93">
         <f>AVERAGE(H47:H51)</f>
         <v>0.326199044</v>
       </c>
       <c r="P48" s="92"/>
+      <c r="AA48" s="35">
+        <v>136.0</v>
+      </c>
+      <c r="AB48" s="35">
+        <v>58.8</v>
+      </c>
     </row>
     <row r="49">
       <c r="C49" s="107" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D49" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>8.37</v>
       </c>
       <c r="G49" s="71" t="s">
@@ -13912,20 +14164,26 @@
         <v>0.142870351877935</v>
       </c>
       <c r="J49" s="35" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="K49" s="93">
         <f>MEDIAN(H47:H51)</f>
         <v>0.3667873968</v>
       </c>
       <c r="P49" s="92"/>
+      <c r="AA49" s="36">
+        <v>1051.0</v>
+      </c>
+      <c r="AB49" s="35">
+        <v>263.81</v>
+      </c>
     </row>
     <row r="50">
       <c r="C50" s="107" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D50" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>10.22</v>
       </c>
       <c r="G50" s="71" t="s">
@@ -13935,20 +14193,26 @@
         <v>0.497437843674554</v>
       </c>
       <c r="J50" s="35" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="K50" s="93">
         <f>PERCENTILE(H47:H51,0.25)</f>
         <v>0.2474460363</v>
       </c>
       <c r="P50" s="92"/>
+      <c r="AA50" s="35">
+        <v>112.0</v>
+      </c>
+      <c r="AB50" s="35">
+        <v>130.76</v>
+      </c>
     </row>
     <row r="51">
       <c r="C51" s="107" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D51" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>8.79</v>
       </c>
       <c r="G51" s="71" t="s">
@@ -13958,164 +14222,236 @@
         <v>0.247446036291655</v>
       </c>
       <c r="J51" s="35" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="K51" s="93">
         <f>PERCENTILE(H47:H51,0.75)</f>
         <v>0.3764535912</v>
       </c>
       <c r="P51" s="92"/>
+      <c r="AA51" s="36">
+        <v>1545.0</v>
+      </c>
+      <c r="AB51" s="35">
+        <v>101.16</v>
+      </c>
     </row>
     <row r="52">
       <c r="C52" s="107" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D52" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>5.44</v>
       </c>
       <c r="P52" s="92"/>
+      <c r="AA52" s="36">
+        <v>1447.0</v>
+      </c>
+      <c r="AB52" s="35">
+        <v>138.76</v>
+      </c>
     </row>
     <row r="53">
       <c r="C53" s="107" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D53" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>3.3</v>
       </c>
       <c r="P53" s="92"/>
+      <c r="AA53" s="36">
+        <v>1426.0</v>
+      </c>
+      <c r="AB53" s="35">
+        <v>68.02</v>
+      </c>
     </row>
     <row r="54">
       <c r="C54" s="107" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D54" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.81</v>
       </c>
       <c r="P54" s="92"/>
+      <c r="AA54" s="36">
+        <v>1475.0</v>
+      </c>
+      <c r="AB54" s="35">
+        <v>83.5</v>
+      </c>
     </row>
     <row r="55">
       <c r="C55" s="107" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D55" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>6.54</v>
       </c>
       <c r="P55" s="92"/>
+      <c r="AA55" s="36">
+        <v>1606.0</v>
+      </c>
+      <c r="AB55" s="35">
+        <v>75.05</v>
+      </c>
     </row>
     <row r="56">
       <c r="C56" s="107" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D56" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>3.77</v>
       </c>
       <c r="P56" s="92"/>
+      <c r="AA56" s="36">
+        <v>1614.0</v>
+      </c>
+      <c r="AB56" s="35">
+        <v>67.42</v>
+      </c>
     </row>
     <row r="57">
       <c r="C57" s="107" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D57" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>6.59</v>
       </c>
       <c r="P57" s="92"/>
+      <c r="AA57" s="35">
+        <v>814.0</v>
+      </c>
+      <c r="AB57" s="35">
+        <v>60.31</v>
+      </c>
     </row>
     <row r="58">
       <c r="C58" s="107" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D58" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>4.77</v>
       </c>
       <c r="G58" s="109" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="H58" s="110"/>
       <c r="P58" s="92"/>
+      <c r="AA58" s="35">
+        <v>752.0</v>
+      </c>
+      <c r="AB58" s="35">
+        <v>78.68</v>
+      </c>
     </row>
     <row r="59">
       <c r="C59" s="107" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D59" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>6.95</v>
       </c>
       <c r="G59" s="110"/>
       <c r="H59" s="111" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="P59" s="92"/>
+      <c r="AA59" s="35">
+        <v>952.0</v>
+      </c>
+      <c r="AB59" s="35">
+        <v>73.76</v>
+      </c>
     </row>
     <row r="60">
       <c r="C60" s="107" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D60" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>4.11</v>
       </c>
       <c r="G60" s="110"/>
       <c r="H60" s="111" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="P60" s="92"/>
+      <c r="AA60" s="36">
+        <v>1526.0</v>
+      </c>
+      <c r="AB60" s="35">
+        <v>53.3</v>
+      </c>
     </row>
     <row r="61">
       <c r="C61" s="107" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D61" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>3.73</v>
       </c>
       <c r="G61" s="110"/>
       <c r="H61" s="111" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="P61" s="92"/>
+      <c r="AA61" s="36">
+        <v>1448.0</v>
+      </c>
+      <c r="AB61" s="35">
+        <v>39.69</v>
+      </c>
     </row>
     <row r="62">
       <c r="C62" s="107" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D62" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>4.8</v>
       </c>
       <c r="G62" s="110"/>
       <c r="H62" s="111" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="P62" s="92"/>
+      <c r="AA62" s="36">
+        <v>1164.0</v>
+      </c>
+      <c r="AB62" s="35">
+        <v>26.27</v>
+      </c>
     </row>
     <row r="63">
       <c r="C63" s="107" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D63" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>5.1</v>
       </c>
       <c r="G63" s="110"/>
       <c r="H63" s="111" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="P63" s="92"/>
     </row>
     <row r="64">
       <c r="C64" s="107" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D64" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>5.36</v>
       </c>
       <c r="P64" s="92"/>
@@ -14125,37 +14461,37 @@
         <v>122</v>
       </c>
       <c r="D65" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>3.68</v>
       </c>
       <c r="P65" s="92"/>
     </row>
     <row r="66">
       <c r="C66" s="107" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D66" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>3.73</v>
       </c>
       <c r="P66" s="92"/>
     </row>
     <row r="67">
       <c r="C67" s="107" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D67" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>3.56</v>
       </c>
       <c r="P67" s="92"/>
     </row>
     <row r="68">
       <c r="C68" s="107" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D68" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>3.46</v>
       </c>
       <c r="P68" s="92"/>
@@ -14165,27 +14501,27 @@
         <v>102</v>
       </c>
       <c r="D69" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>3.67</v>
       </c>
       <c r="P69" s="92"/>
     </row>
     <row r="70">
       <c r="C70" s="107" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D70" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>3.59</v>
       </c>
       <c r="P70" s="92"/>
     </row>
     <row r="71">
       <c r="C71" s="107" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D71" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>3.55</v>
       </c>
       <c r="F71" s="112"/>
@@ -14193,330 +14529,330 @@
     </row>
     <row r="72">
       <c r="C72" s="107" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D72" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>2.5</v>
       </c>
       <c r="P72" s="92"/>
     </row>
     <row r="73">
       <c r="C73" s="107" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D73" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>2.73</v>
       </c>
       <c r="P73" s="92"/>
     </row>
     <row r="74">
       <c r="C74" s="107" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D74" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>2.68</v>
       </c>
       <c r="P74" s="92"/>
     </row>
     <row r="75">
       <c r="C75" s="107" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D75" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1.89</v>
       </c>
       <c r="P75" s="92"/>
     </row>
     <row r="76">
       <c r="C76" s="107" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D76" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>2.48</v>
       </c>
       <c r="P76" s="92"/>
     </row>
     <row r="77">
       <c r="C77" s="107" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D77" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>3.32</v>
       </c>
       <c r="P77" s="92"/>
     </row>
     <row r="78">
       <c r="C78" s="107" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D78" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>4.7</v>
       </c>
       <c r="P78" s="113"/>
     </row>
     <row r="79">
       <c r="C79" s="107" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D79" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>3.85</v>
       </c>
       <c r="P79" s="113"/>
     </row>
     <row r="80">
       <c r="C80" s="107" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D80" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>4.66</v>
       </c>
       <c r="P80" s="113"/>
     </row>
     <row r="81">
       <c r="C81" s="107" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D81" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.38</v>
       </c>
       <c r="P81" s="113"/>
     </row>
     <row r="82">
       <c r="C82" s="107" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D82" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>3.46</v>
       </c>
       <c r="P82" s="113"/>
     </row>
     <row r="83">
       <c r="C83" s="107" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D83" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>4.26</v>
       </c>
       <c r="P83" s="113"/>
     </row>
     <row r="84">
       <c r="C84" s="107" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D84" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>2.96</v>
       </c>
       <c r="P84" s="113"/>
     </row>
     <row r="85">
       <c r="C85" s="107" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D85" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>6.1</v>
       </c>
       <c r="P85" s="113"/>
     </row>
     <row r="86">
       <c r="C86" s="107" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D86" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>6</v>
       </c>
       <c r="P86" s="113"/>
     </row>
     <row r="87">
       <c r="C87" s="107" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D87" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>6.42</v>
       </c>
       <c r="P87" s="113"/>
     </row>
     <row r="88">
       <c r="C88" s="107" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D88" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.62</v>
       </c>
       <c r="P88" s="113"/>
     </row>
     <row r="89">
       <c r="C89" s="107" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D89" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.03</v>
       </c>
       <c r="P89" s="113"/>
     </row>
     <row r="90">
       <c r="C90" s="107" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D90" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.51</v>
       </c>
       <c r="P90" s="113"/>
     </row>
     <row r="91">
       <c r="C91" s="107" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D91" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.4</v>
       </c>
       <c r="P91" s="113"/>
     </row>
     <row r="92">
       <c r="C92" s="107" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D92" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.59</v>
       </c>
       <c r="P92" s="113"/>
     </row>
     <row r="93">
       <c r="C93" s="107" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D93" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.61</v>
       </c>
       <c r="P93" s="113"/>
     </row>
     <row r="94">
       <c r="C94" s="107" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D94" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.6</v>
       </c>
       <c r="P94" s="113"/>
     </row>
     <row r="95">
       <c r="C95" s="107" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D95" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1.05</v>
       </c>
       <c r="P95" s="113"/>
     </row>
     <row r="96">
       <c r="C96" s="107" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D96" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.04</v>
       </c>
       <c r="P96" s="113"/>
     </row>
     <row r="97">
       <c r="C97" s="107" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D97" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.18</v>
       </c>
       <c r="P97" s="113"/>
     </row>
     <row r="98">
       <c r="C98" s="107" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D98" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="P98" s="113"/>
     </row>
     <row r="99">
       <c r="C99" s="107" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D99" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="P99" s="113"/>
     </row>
     <row r="100">
       <c r="C100" s="107" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D100" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1.25</v>
       </c>
       <c r="P100" s="113"/>
     </row>
     <row r="101">
       <c r="C101" s="107" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D101" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="P101" s="113"/>
     </row>
     <row r="102">
       <c r="C102" s="107" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D102" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="P102" s="113"/>
     </row>
     <row r="103">
       <c r="C103" s="107" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D103" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1.21</v>
       </c>
       <c r="P103" s="113"/>
     </row>
     <row r="104">
       <c r="C104" s="107" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D104" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1.12</v>
       </c>
       <c r="N104" s="114"/>
@@ -14524,10 +14860,10 @@
     </row>
     <row r="105">
       <c r="C105" s="107" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D105" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>10.75</v>
       </c>
       <c r="N105" s="14"/>
@@ -14535,10 +14871,10 @@
     </row>
     <row r="106">
       <c r="C106" s="107" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D106" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>10.43</v>
       </c>
       <c r="N106" s="14"/>
@@ -14546,10 +14882,10 @@
     </row>
     <row r="107">
       <c r="C107" s="107" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D107" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>11.53</v>
       </c>
       <c r="N107" s="14"/>
@@ -14557,10 +14893,10 @@
     </row>
     <row r="108">
       <c r="C108" s="107" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D108" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>10.85</v>
       </c>
       <c r="N108" s="14"/>
@@ -14568,10 +14904,10 @@
     </row>
     <row r="109">
       <c r="C109" s="107" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D109" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>12.26</v>
       </c>
       <c r="N109" s="14"/>
@@ -14579,10 +14915,10 @@
     </row>
     <row r="110">
       <c r="C110" s="107" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D110" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>6.98</v>
       </c>
       <c r="N110" s="14"/>
@@ -14590,10 +14926,10 @@
     </row>
     <row r="111">
       <c r="C111" s="107" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D111" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>8.25</v>
       </c>
       <c r="N111" s="14"/>
@@ -14601,180 +14937,180 @@
     </row>
     <row r="112">
       <c r="C112" s="107" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D112" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>7.63</v>
       </c>
       <c r="P112" s="113"/>
     </row>
     <row r="113">
       <c r="C113" s="107" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D113" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>7.01</v>
       </c>
       <c r="P113" s="113"/>
     </row>
     <row r="114">
       <c r="C114" s="107" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D114" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>8</v>
       </c>
       <c r="P114" s="113"/>
     </row>
     <row r="115">
       <c r="C115" s="107" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D115" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>11.16</v>
       </c>
       <c r="P115" s="113"/>
     </row>
     <row r="116">
       <c r="C116" s="107" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D116" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>7.22</v>
       </c>
       <c r="P116" s="113"/>
     </row>
     <row r="117">
       <c r="C117" s="107" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D117" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>8.7</v>
       </c>
       <c r="P117" s="113"/>
     </row>
     <row r="118">
       <c r="C118" s="107" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D118" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>11.55</v>
       </c>
       <c r="P118" s="113"/>
     </row>
     <row r="119">
       <c r="C119" s="107" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D119" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>11.18</v>
       </c>
       <c r="P119" s="113"/>
     </row>
     <row r="120">
       <c r="C120" s="107" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D120" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>11.69</v>
       </c>
       <c r="P120" s="113"/>
     </row>
     <row r="121">
       <c r="C121" s="107" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D121" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>4.09</v>
       </c>
       <c r="P121" s="113"/>
     </row>
     <row r="122">
       <c r="C122" s="107" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D122" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>3.17</v>
       </c>
       <c r="P122" s="113"/>
     </row>
     <row r="123">
       <c r="C123" s="107" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D123" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>8.85</v>
       </c>
       <c r="P123" s="113"/>
     </row>
     <row r="124">
       <c r="C124" s="107" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D124" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>12.66</v>
       </c>
       <c r="P124" s="113"/>
     </row>
     <row r="125">
       <c r="C125" s="107" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D125" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>12.45</v>
       </c>
       <c r="P125" s="113"/>
     </row>
     <row r="126">
       <c r="C126" s="107" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D126" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>8.98</v>
       </c>
       <c r="P126" s="113"/>
     </row>
     <row r="127">
       <c r="C127" s="107" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D127" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>3.04</v>
       </c>
       <c r="P127" s="113"/>
     </row>
     <row r="128">
       <c r="C128" s="107" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D128" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>2.3</v>
       </c>
       <c r="P128" s="113"/>
     </row>
     <row r="129">
       <c r="C129" s="107" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D129" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>2.99</v>
       </c>
       <c r="P129" s="113"/>
@@ -14784,47 +15120,47 @@
         <v>131</v>
       </c>
       <c r="D130" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>2.8</v>
       </c>
       <c r="P130" s="113"/>
     </row>
     <row r="131">
       <c r="C131" s="107" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D131" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1.23</v>
       </c>
       <c r="P131" s="113"/>
     </row>
     <row r="132">
       <c r="C132" s="107" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D132" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1.25</v>
       </c>
       <c r="P132" s="113"/>
     </row>
     <row r="133">
       <c r="C133" s="107" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D133" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>1.25</v>
       </c>
       <c r="P133" s="113"/>
     </row>
     <row r="134">
       <c r="C134" s="107" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D134" s="95">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v>0.8</v>
       </c>
       <c r="P134" s="113"/>
@@ -14832,7 +15168,7 @@
     <row r="135">
       <c r="C135" s="107"/>
       <c r="D135" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P135" s="113"/>
@@ -14840,7 +15176,7 @@
     <row r="136">
       <c r="C136" s="107"/>
       <c r="D136" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P136" s="113"/>
@@ -14848,7 +15184,7 @@
     <row r="137">
       <c r="C137" s="107"/>
       <c r="D137" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P137" s="113"/>
@@ -14856,7 +15192,7 @@
     <row r="138">
       <c r="C138" s="107"/>
       <c r="D138" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P138" s="113"/>
@@ -14864,7 +15200,7 @@
     <row r="139">
       <c r="C139" s="107"/>
       <c r="D139" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P139" s="113"/>
@@ -14872,7 +15208,7 @@
     <row r="140">
       <c r="C140" s="107"/>
       <c r="D140" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H140" s="35">
@@ -14889,7 +15225,7 @@
     <row r="141">
       <c r="C141" s="107"/>
       <c r="D141" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H141" s="35">
@@ -14906,7 +15242,7 @@
     <row r="142">
       <c r="C142" s="107"/>
       <c r="D142" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H142" s="35">
@@ -14923,7 +15259,7 @@
     <row r="143">
       <c r="C143" s="107"/>
       <c r="D143" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H143" s="35">
@@ -14940,7 +15276,7 @@
     <row r="144">
       <c r="C144" s="107"/>
       <c r="D144" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H144" s="35">
@@ -14957,7 +15293,7 @@
     <row r="145">
       <c r="C145" s="107"/>
       <c r="D145" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H145" s="35">
@@ -14974,7 +15310,7 @@
     <row r="146">
       <c r="C146" s="107"/>
       <c r="D146" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H146" s="35">
@@ -14991,7 +15327,7 @@
     <row r="147">
       <c r="C147" s="107"/>
       <c r="D147" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H147" s="35">
@@ -15008,7 +15344,7 @@
     <row r="148">
       <c r="C148" s="107"/>
       <c r="D148" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H148" s="35">
@@ -15025,7 +15361,7 @@
     <row r="149">
       <c r="C149" s="107"/>
       <c r="D149" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H149" s="35">
@@ -15042,7 +15378,7 @@
     <row r="150">
       <c r="C150" s="107"/>
       <c r="D150" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H150" s="35">
@@ -15059,7 +15395,7 @@
     <row r="151">
       <c r="C151" s="107"/>
       <c r="D151" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H151" s="35">
@@ -15076,7 +15412,7 @@
     <row r="152">
       <c r="C152" s="107"/>
       <c r="D152" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H152" s="35">
@@ -15093,7 +15429,7 @@
     <row r="153">
       <c r="C153" s="107"/>
       <c r="D153" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H153" s="35">
@@ -15110,7 +15446,7 @@
     <row r="154">
       <c r="C154" s="107"/>
       <c r="D154" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H154" s="35">
@@ -15127,7 +15463,7 @@
     <row r="155">
       <c r="C155" s="107"/>
       <c r="D155" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H155" s="35">
@@ -15144,7 +15480,7 @@
     <row r="156">
       <c r="C156" s="107"/>
       <c r="D156" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H156" s="35">
@@ -15161,7 +15497,7 @@
     <row r="157">
       <c r="C157" s="107"/>
       <c r="D157" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H157" s="35">
@@ -15178,7 +15514,7 @@
     <row r="158">
       <c r="C158" s="107"/>
       <c r="D158" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H158" s="35">
@@ -15195,7 +15531,7 @@
     <row r="159">
       <c r="C159" s="107"/>
       <c r="D159" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H159" s="35">
@@ -15212,7 +15548,7 @@
     <row r="160">
       <c r="C160" s="107"/>
       <c r="D160" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H160" s="35">
@@ -15229,7 +15565,7 @@
     <row r="161">
       <c r="C161" s="107"/>
       <c r="D161" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H161" s="35">
@@ -15246,7 +15582,7 @@
     <row r="162">
       <c r="C162" s="107"/>
       <c r="D162" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H162" s="35">
@@ -15263,7 +15599,7 @@
     <row r="163">
       <c r="C163" s="107"/>
       <c r="D163" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H163" s="35">
@@ -15280,7 +15616,7 @@
     <row r="164">
       <c r="C164" s="107"/>
       <c r="D164" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H164" s="35">
@@ -15297,7 +15633,7 @@
     <row r="165">
       <c r="C165" s="107"/>
       <c r="D165" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H165" s="35">
@@ -15314,7 +15650,7 @@
     <row r="166">
       <c r="C166" s="107"/>
       <c r="D166" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H166" s="35">
@@ -15331,7 +15667,7 @@
     <row r="167">
       <c r="C167" s="107"/>
       <c r="D167" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H167" s="35">
@@ -15348,7 +15684,7 @@
     <row r="168">
       <c r="C168" s="107"/>
       <c r="D168" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H168" s="35">
@@ -15365,7 +15701,7 @@
     <row r="169">
       <c r="C169" s="107"/>
       <c r="D169" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H169" s="35">
@@ -15382,7 +15718,7 @@
     <row r="170">
       <c r="C170" s="107"/>
       <c r="D170" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H170" s="35">
@@ -15399,7 +15735,7 @@
     <row r="171">
       <c r="C171" s="107"/>
       <c r="D171" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H171" s="35">
@@ -15416,7 +15752,7 @@
     <row r="172">
       <c r="C172" s="107"/>
       <c r="D172" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H172" s="35">
@@ -15433,7 +15769,7 @@
     <row r="173">
       <c r="C173" s="107"/>
       <c r="D173" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H173" s="35">
@@ -15450,7 +15786,7 @@
     <row r="174">
       <c r="C174" s="107"/>
       <c r="D174" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H174" s="35">
@@ -15467,7 +15803,7 @@
     <row r="175">
       <c r="C175" s="107"/>
       <c r="D175" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H175" s="35">
@@ -15484,7 +15820,7 @@
     <row r="176">
       <c r="C176" s="107"/>
       <c r="D176" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H176" s="35">
@@ -15501,7 +15837,7 @@
     <row r="177">
       <c r="C177" s="107"/>
       <c r="D177" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H177" s="35">
@@ -15518,7 +15854,7 @@
     <row r="178">
       <c r="C178" s="107"/>
       <c r="D178" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H178" s="35">
@@ -15535,7 +15871,7 @@
     <row r="179">
       <c r="C179" s="107"/>
       <c r="D179" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H179" s="35">
@@ -15552,7 +15888,7 @@
     <row r="180">
       <c r="C180" s="107"/>
       <c r="D180" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H180" s="35">
@@ -15569,7 +15905,7 @@
     <row r="181">
       <c r="C181" s="107"/>
       <c r="D181" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H181" s="35">
@@ -15586,7 +15922,7 @@
     <row r="182">
       <c r="C182" s="107"/>
       <c r="D182" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H182" s="35">
@@ -15603,7 +15939,7 @@
     <row r="183">
       <c r="C183" s="107"/>
       <c r="D183" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H183" s="35">
@@ -15620,7 +15956,7 @@
     <row r="184">
       <c r="C184" s="107"/>
       <c r="D184" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H184" s="35">
@@ -15637,7 +15973,7 @@
     <row r="185">
       <c r="C185" s="107"/>
       <c r="D185" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H185" s="35">
@@ -15654,7 +15990,7 @@
     <row r="186">
       <c r="C186" s="107"/>
       <c r="D186" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H186" s="35">
@@ -15671,7 +16007,7 @@
     <row r="187">
       <c r="C187" s="107"/>
       <c r="D187" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H187" s="35">
@@ -15688,7 +16024,7 @@
     <row r="188">
       <c r="C188" s="107"/>
       <c r="D188" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H188" s="35">
@@ -15705,7 +16041,7 @@
     <row r="189">
       <c r="C189" s="107"/>
       <c r="D189" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H189" s="35">
@@ -15722,7 +16058,7 @@
     <row r="190">
       <c r="C190" s="107"/>
       <c r="D190" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H190" s="35">
@@ -15739,7 +16075,7 @@
     <row r="191">
       <c r="C191" s="107"/>
       <c r="D191" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H191" s="35">
@@ -15756,7 +16092,7 @@
     <row r="192">
       <c r="C192" s="107"/>
       <c r="D192" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H192" s="35">
@@ -15773,7 +16109,7 @@
     <row r="193">
       <c r="C193" s="107"/>
       <c r="D193" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H193" s="35">
@@ -15790,7 +16126,7 @@
     <row r="194">
       <c r="C194" s="107"/>
       <c r="D194" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H194" s="35">
@@ -15807,7 +16143,7 @@
     <row r="195">
       <c r="C195" s="107"/>
       <c r="D195" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H195" s="35">
@@ -15824,7 +16160,7 @@
     <row r="196">
       <c r="C196" s="107"/>
       <c r="D196" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H196" s="35">
@@ -15841,7 +16177,7 @@
     <row r="197">
       <c r="C197" s="107"/>
       <c r="D197" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H197" s="35">
@@ -15858,7 +16194,7 @@
     <row r="198">
       <c r="C198" s="107"/>
       <c r="D198" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H198" s="35">
@@ -15875,7 +16211,7 @@
     <row r="199">
       <c r="C199" s="107"/>
       <c r="D199" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H199" s="35">
@@ -15892,7 +16228,7 @@
     <row r="200">
       <c r="C200" s="107"/>
       <c r="D200" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H200" s="35">
@@ -15909,7 +16245,7 @@
     <row r="201">
       <c r="C201" s="107"/>
       <c r="D201" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H201" s="35">
@@ -15926,7 +16262,7 @@
     <row r="202">
       <c r="C202" s="107"/>
       <c r="D202" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H202" s="35">
@@ -15943,7 +16279,7 @@
     <row r="203">
       <c r="C203" s="107"/>
       <c r="D203" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H203" s="35">
@@ -15960,7 +16296,7 @@
     <row r="204">
       <c r="C204" s="107"/>
       <c r="D204" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H204" s="35">
@@ -15977,7 +16313,7 @@
     <row r="205">
       <c r="C205" s="107"/>
       <c r="D205" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H205" s="35">
@@ -15994,7 +16330,7 @@
     <row r="206">
       <c r="C206" s="107"/>
       <c r="D206" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H206" s="35">
@@ -16011,7 +16347,7 @@
     <row r="207">
       <c r="C207" s="107"/>
       <c r="D207" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H207" s="35">
@@ -16028,7 +16364,7 @@
     <row r="208">
       <c r="C208" s="107"/>
       <c r="D208" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H208" s="35">
@@ -16045,7 +16381,7 @@
     <row r="209">
       <c r="C209" s="107"/>
       <c r="D209" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H209" s="35">
@@ -16062,7 +16398,7 @@
     <row r="210">
       <c r="C210" s="107"/>
       <c r="D210" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H210" s="35">
@@ -16079,7 +16415,7 @@
     <row r="211">
       <c r="C211" s="107"/>
       <c r="D211" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H211" s="35">
@@ -16096,7 +16432,7 @@
     <row r="212">
       <c r="C212" s="107"/>
       <c r="D212" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H212" s="35">
@@ -16113,7 +16449,7 @@
     <row r="213">
       <c r="C213" s="107"/>
       <c r="D213" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H213" s="35">
@@ -16130,7 +16466,7 @@
     <row r="214">
       <c r="C214" s="107"/>
       <c r="D214" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H214" s="35">
@@ -16147,7 +16483,7 @@
     <row r="215">
       <c r="C215" s="107"/>
       <c r="D215" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H215" s="35">
@@ -16164,7 +16500,7 @@
     <row r="216">
       <c r="C216" s="107"/>
       <c r="D216" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H216" s="35">
@@ -16181,7 +16517,7 @@
     <row r="217">
       <c r="C217" s="107"/>
       <c r="D217" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H217" s="35">
@@ -16198,7 +16534,7 @@
     <row r="218">
       <c r="C218" s="107"/>
       <c r="D218" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H218" s="35">
@@ -16215,7 +16551,7 @@
     <row r="219">
       <c r="C219" s="107"/>
       <c r="D219" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H219" s="35">
@@ -16232,7 +16568,7 @@
     <row r="220">
       <c r="C220" s="107"/>
       <c r="D220" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H220" s="35">
@@ -16249,7 +16585,7 @@
     <row r="221">
       <c r="C221" s="107"/>
       <c r="D221" s="95" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="H221" s="35">
@@ -35634,6 +35970,18 @@
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF57BB8A"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD29:AD43">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="max"/>
+        <color rgb="FFE67C73"/>
         <color rgb="FFFFFFFF"/>
         <color rgb="FF57BB8A"/>
       </colorScale>
@@ -35657,14 +36005,14 @@
     <row r="1">
       <c r="A1" s="75"/>
       <c r="B1" s="117" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C1" s="118"/>
       <c r="D1" s="118"/>
       <c r="E1" s="118"/>
       <c r="F1" s="118"/>
       <c r="G1" s="119" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="H1" s="118"/>
       <c r="I1" s="118"/>
@@ -35692,19 +36040,19 @@
         <v>3</v>
       </c>
       <c r="B2" s="121" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C2" s="122" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D2" s="122" t="s">
-        <v>246</v>
+        <v>145</v>
       </c>
       <c r="E2" s="122" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F2" s="123" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G2" s="121">
         <v>1.0</v>
@@ -35716,25 +36064,25 @@
         <v>2.0</v>
       </c>
       <c r="J2" s="122" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K2" s="124" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L2" s="122" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="M2" s="125" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="N2" s="71" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O2" s="71" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P2" s="71" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q2" s="8"/>
       <c r="R2" s="8"/>
@@ -36517,7 +36865,7 @@
       <c r="E27" s="8"/>
       <c r="F27" s="8"/>
       <c r="G27" s="139" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H27" s="8"/>
       <c r="I27" s="8"/>
@@ -36578,7 +36926,7 @@
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
       <c r="D29" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E29" s="4">
         <f>J29</f>
@@ -36600,10 +36948,10 @@
       </c>
       <c r="K29" s="8"/>
       <c r="L29" s="65" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="M29" s="65" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="O29" s="4">
         <v>1.0</v>
@@ -36739,7 +37087,7 @@
       <c r="E33" s="8"/>
       <c r="F33" s="8"/>
       <c r="G33" s="90" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="J33" s="8"/>
       <c r="K33" s="8"/>
@@ -36916,7 +37264,7 @@
       <c r="D38" s="8"/>
       <c r="E38" s="8"/>
       <c r="F38" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G38" s="142">
         <f t="shared" ref="G38:I38" si="8">G30-G35</f>

--- a/data/df_best_models.xlsx
+++ b/data/df_best_models.xlsx
@@ -210,7 +210,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="225">
   <si>
     <t>id_country</t>
   </si>
@@ -659,22 +659,28 @@
     <t>Stake promedio</t>
   </si>
   <si>
+    <t>1.15</t>
+  </si>
+  <si>
     <t>0.00</t>
   </si>
   <si>
-    <t>0.36</t>
+    <t>9.75</t>
   </si>
   <si>
-    <t>0.25</t>
+    <t>9.37</t>
   </si>
   <si>
-    <t>0.68</t>
+    <t>9.80</t>
   </si>
   <si>
-    <t>11.25</t>
+    <t>7.97</t>
   </si>
   <si>
-    <t>9.76</t>
+    <t>8.90</t>
+  </si>
+  <si>
+    <t>7.33</t>
   </si>
   <si>
     <t>Country</t>
@@ -683,265 +689,145 @@
     <t>Correl ROI y Expected ROI</t>
   </si>
   <si>
-    <t>10.40</t>
+    <t>7.98</t>
   </si>
   <si>
-    <t>10.84</t>
+    <t>5.97</t>
   </si>
   <si>
     <t>mean</t>
   </si>
   <si>
-    <t>8.37</t>
+    <t>7.56</t>
   </si>
   <si>
     <t>median</t>
   </si>
   <si>
-    <t>10.22</t>
+    <t>7.76</t>
   </si>
   <si>
     <t>p25</t>
   </si>
   <si>
-    <t>8.79</t>
+    <t>5.79</t>
   </si>
   <si>
     <t>p75</t>
   </si>
   <si>
-    <t>5.44</t>
+    <t>5.65</t>
   </si>
   <si>
-    <t>3.30</t>
+    <t>6.08</t>
   </si>
   <si>
-    <t>0.81</t>
+    <t>5.75</t>
   </si>
   <si>
-    <t>6.54</t>
+    <t>5.87</t>
   </si>
   <si>
-    <t>3.77</t>
+    <t>2.08</t>
   </si>
   <si>
-    <t>6.59</t>
+    <t>2.22</t>
   </si>
   <si>
-    <t>4.77</t>
+    <t>11.10</t>
   </si>
   <si>
     <t>Gracias a las nuevas métricas de G/P sin bank en test, me di cuenta de que:</t>
   </si>
   <si>
-    <t>6.95</t>
-  </si>
-  <si>
     <t>La rentabilidad en ITA está en el visitante y no en el empate como creía.</t>
   </si>
   <si>
-    <t>4.11</t>
+    <t>9.12</t>
   </si>
   <si>
     <t>La rentabilidad en ENG y GER está en el empate tal como creía.</t>
   </si>
   <si>
-    <t>3.73</t>
-  </si>
-  <si>
     <t>En SPA esta repartido aunque Empate saca una ventaja.</t>
   </si>
   <si>
-    <t>4.80</t>
+    <t>2.26</t>
   </si>
   <si>
     <t>En FRA, depende el modelo. A veces local, a veces, empate.</t>
   </si>
   <si>
-    <t>5.10</t>
+    <t>11.57</t>
   </si>
   <si>
     <t>Si en FRA empate no rinde, no tiene sentido exigirle una buena distrib en empate… → Tiene sentido pero al parecer si importa el empate puesto que el modelo que gana se basa en empate.</t>
   </si>
   <si>
-    <t>5.36</t>
+    <t>2.10</t>
   </si>
   <si>
-    <t>3.56</t>
+    <t>2.03</t>
   </si>
   <si>
-    <t>3.46</t>
+    <t>1.25</t>
   </si>
   <si>
-    <t>3.59</t>
+    <t>1.19</t>
   </si>
   <si>
-    <t>3.55</t>
+    <t>0.01</t>
   </si>
   <si>
-    <t>2.50</t>
+    <t>0.05</t>
   </si>
   <si>
-    <t>2.73</t>
+    <t>5.01</t>
   </si>
   <si>
-    <t>2.68</t>
+    <t>5.09</t>
   </si>
   <si>
-    <t>1.89</t>
+    <t>5.00</t>
   </si>
   <si>
-    <t>2.48</t>
+    <t>11.21</t>
   </si>
   <si>
-    <t>3.32</t>
+    <t>11.06</t>
   </si>
   <si>
-    <t>4.70</t>
+    <t>12.77</t>
   </si>
   <si>
-    <t>3.85</t>
+    <t>8.80</t>
   </si>
   <si>
-    <t>4.66</t>
+    <t>9.18</t>
   </si>
   <si>
-    <t>0.38</t>
+    <t>9.74</t>
   </si>
   <si>
-    <t>4.26</t>
+    <t>5.44</t>
   </si>
   <si>
-    <t>2.96</t>
-  </si>
-  <si>
-    <t>6.10</t>
-  </si>
-  <si>
-    <t>6.00</t>
+    <t>8.59</t>
   </si>
   <si>
     <t>6.42</t>
   </si>
   <si>
-    <t>0.62</t>
+    <t>2.94</t>
   </si>
   <si>
-    <t>0.03</t>
+    <t>3.62</t>
   </si>
   <si>
-    <t>0.51</t>
+    <t>3.72</t>
   </si>
   <si>
-    <t>0.40</t>
-  </si>
-  <si>
-    <t>0.59</t>
-  </si>
-  <si>
-    <t>0.61</t>
-  </si>
-  <si>
-    <t>0.60</t>
-  </si>
-  <si>
-    <t>1.05</t>
-  </si>
-  <si>
-    <t>0.04</t>
-  </si>
-  <si>
-    <t>0.18</t>
-  </si>
-  <si>
-    <t>1.25</t>
-  </si>
-  <si>
-    <t>1.21</t>
-  </si>
-  <si>
-    <t>1.12</t>
-  </si>
-  <si>
-    <t>10.75</t>
-  </si>
-  <si>
-    <t>10.43</t>
-  </si>
-  <si>
-    <t>11.53</t>
-  </si>
-  <si>
-    <t>10.85</t>
-  </si>
-  <si>
-    <t>12.26</t>
-  </si>
-  <si>
-    <t>6.98</t>
-  </si>
-  <si>
-    <t>8.25</t>
-  </si>
-  <si>
-    <t>7.63</t>
-  </si>
-  <si>
-    <t>7.01</t>
-  </si>
-  <si>
-    <t>8.00</t>
-  </si>
-  <si>
-    <t>11.16</t>
-  </si>
-  <si>
-    <t>7.22</t>
-  </si>
-  <si>
-    <t>8.70</t>
-  </si>
-  <si>
-    <t>11.55</t>
-  </si>
-  <si>
-    <t>11.18</t>
-  </si>
-  <si>
-    <t>11.69</t>
-  </si>
-  <si>
-    <t>4.09</t>
-  </si>
-  <si>
-    <t>3.17</t>
-  </si>
-  <si>
-    <t>8.85</t>
-  </si>
-  <si>
-    <t>12.66</t>
-  </si>
-  <si>
-    <t>12.45</t>
-  </si>
-  <si>
-    <t>8.98</t>
-  </si>
-  <si>
-    <t>3.04</t>
-  </si>
-  <si>
-    <t>2.30</t>
-  </si>
-  <si>
-    <t>2.99</t>
-  </si>
-  <si>
-    <t>1.23</t>
-  </si>
-  <si>
-    <t>0.80</t>
+    <t>4.85</t>
   </si>
   <si>
     <t>RENTABILIDAD</t>
@@ -1389,10 +1275,10 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="3" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -2188,44 +2074,44 @@
         <v>45677.0</v>
       </c>
       <c r="D7" s="23">
-        <v>19.0</v>
+        <v>1623.0</v>
       </c>
       <c r="E7" s="23" t="s">
         <v>17</v>
       </c>
       <c r="F7" s="24">
-        <v>59.2592592592592</v>
+        <v>60.0</v>
       </c>
       <c r="G7" s="24">
-        <v>197.314387756965</v>
+        <v>146.88838482783</v>
       </c>
       <c r="H7" s="24">
-        <f>-0.77+
-457.18+
-3246.15
+        <f>-1.86+
+3963.24+
+625.47
 </f>
-        <v>3702.56</v>
+        <v>4586.85</v>
       </c>
       <c r="I7" s="24">
         <f t="shared" si="1"/>
-        <v>18.76477454</v>
+        <v>31.2267713</v>
       </c>
       <c r="J7" s="19">
         <v>5.0</v>
       </c>
       <c r="K7" s="19">
-        <v>25.0</v>
+        <v>70.0</v>
       </c>
       <c r="L7" s="19">
-        <v>80.0</v>
+        <v>50.0</v>
       </c>
       <c r="M7" s="19">
         <f t="shared" si="2"/>
-        <v>36.66666667</v>
+        <v>41.66666667</v>
       </c>
       <c r="N7" s="15">
         <f>M7*'Data preparation'!$C$2</f>
-        <v>11</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="8">
@@ -2239,27 +2125,27 @@
         <v>45677.0</v>
       </c>
       <c r="D8" s="23">
-        <v>1051.0</v>
+        <v>112.0</v>
       </c>
       <c r="E8" s="23" t="s">
         <v>17</v>
       </c>
       <c r="F8" s="24">
-        <v>53.2110091743119</v>
+        <v>57.2727272727272</v>
       </c>
       <c r="G8" s="24">
-        <v>191.629402836081</v>
+        <v>114.811855439534</v>
       </c>
       <c r="H8" s="24">
-        <f>301.19+
-154.98+
-109.46
+        <f>274.77+
+3714.77+
+12.5
 </f>
-        <v>565.63</v>
+        <v>4002.04</v>
       </c>
       <c r="I8" s="24">
         <f t="shared" si="1"/>
-        <v>2.95168691</v>
+        <v>34.85737588</v>
       </c>
       <c r="J8" s="19">
         <v>50.0</v>
@@ -2316,56 +2202,55 @@
     </row>
     <row r="13">
       <c r="A13" s="32"/>
-      <c r="C13" s="33"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="34"/>
-      <c r="H13" s="34"/>
-      <c r="I13" s="34"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="33"/>
+      <c r="H13" s="33"/>
+      <c r="I13" s="33"/>
     </row>
     <row r="14">
-      <c r="C14" s="33"/>
-      <c r="F14" s="34"/>
-      <c r="G14" s="34"/>
-      <c r="H14" s="34"/>
-      <c r="I14" s="34"/>
-      <c r="J14" s="34"/>
-      <c r="K14" s="34"/>
-      <c r="L14" s="34"/>
-      <c r="M14" s="34"/>
+      <c r="C14" s="34"/>
+      <c r="F14" s="33"/>
+      <c r="G14" s="33"/>
+      <c r="H14" s="33"/>
+      <c r="I14" s="33"/>
+      <c r="J14" s="33"/>
+      <c r="K14" s="33"/>
+      <c r="L14" s="33"/>
+      <c r="M14" s="33"/>
     </row>
     <row r="15">
-      <c r="C15" s="33"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="34"/>
-      <c r="H15" s="34"/>
-      <c r="I15" s="34"/>
-      <c r="J15" s="34"/>
-      <c r="K15" s="34"/>
-      <c r="L15" s="34"/>
-      <c r="M15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="F15" s="33"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="33"/>
+      <c r="I15" s="33"/>
+      <c r="J15" s="33"/>
+      <c r="K15" s="33"/>
+      <c r="L15" s="33"/>
+      <c r="M15" s="33"/>
     </row>
     <row r="16">
-      <c r="C16" s="33"/>
+      <c r="C16" s="34"/>
       <c r="H16" s="27"/>
-      <c r="I16" s="34"/>
+      <c r="I16" s="33"/>
     </row>
     <row r="17">
-      <c r="C17" s="33"/>
+      <c r="C17" s="34"/>
       <c r="G17" s="35"/>
       <c r="H17" s="27"/>
-      <c r="I17" s="34"/>
+      <c r="I17" s="33"/>
     </row>
     <row r="18">
-      <c r="C18" s="33"/>
+      <c r="C18" s="34"/>
       <c r="H18" s="27"/>
       <c r="I18" s="27"/>
     </row>
     <row r="19">
-      <c r="C19" s="33"/>
+      <c r="C19" s="34"/>
       <c r="F19" s="36"/>
       <c r="G19" s="36"/>
-      <c r="H19" s="34"/>
-      <c r="I19" s="34"/>
+      <c r="H19" s="33"/>
+      <c r="I19" s="33"/>
       <c r="J19" s="36"/>
       <c r="K19" s="36"/>
       <c r="L19" s="36"/>
@@ -2373,11 +2258,11 @@
       <c r="P19" s="36"/>
     </row>
     <row r="20">
-      <c r="C20" s="33"/>
+      <c r="C20" s="34"/>
       <c r="F20" s="36"/>
       <c r="G20" s="36"/>
-      <c r="H20" s="34"/>
-      <c r="I20" s="34"/>
+      <c r="H20" s="33"/>
+      <c r="I20" s="33"/>
       <c r="J20" s="36"/>
       <c r="K20" s="36"/>
       <c r="L20" s="36"/>
@@ -2387,8 +2272,8 @@
     <row r="21">
       <c r="F21" s="36"/>
       <c r="G21" s="36"/>
-      <c r="H21" s="34"/>
-      <c r="I21" s="34"/>
+      <c r="H21" s="33"/>
+      <c r="I21" s="33"/>
       <c r="J21" s="36"/>
       <c r="K21" s="36"/>
       <c r="L21" s="36"/>
@@ -2397,7 +2282,7 @@
     </row>
     <row r="22">
       <c r="E22" s="35"/>
-      <c r="H22" s="34"/>
+      <c r="H22" s="33"/>
       <c r="I22" s="27"/>
       <c r="J22" s="35"/>
       <c r="K22" s="35"/>
@@ -2406,7 +2291,7 @@
     </row>
     <row r="23">
       <c r="E23" s="35"/>
-      <c r="H23" s="34"/>
+      <c r="H23" s="33"/>
       <c r="I23" s="27"/>
       <c r="J23" s="35"/>
       <c r="K23" s="35"/>
@@ -2420,8 +2305,8 @@
     <row r="25">
       <c r="F25" s="36"/>
       <c r="G25" s="36"/>
-      <c r="H25" s="34"/>
-      <c r="I25" s="34"/>
+      <c r="H25" s="33"/>
+      <c r="I25" s="33"/>
       <c r="J25" s="36"/>
       <c r="K25" s="36"/>
       <c r="L25" s="36"/>
@@ -2430,8 +2315,8 @@
     <row r="26">
       <c r="F26" s="36"/>
       <c r="G26" s="36"/>
-      <c r="H26" s="34"/>
-      <c r="I26" s="34"/>
+      <c r="H26" s="33"/>
+      <c r="I26" s="33"/>
       <c r="J26" s="36"/>
       <c r="K26" s="36"/>
       <c r="L26" s="36"/>
@@ -2439,47 +2324,47 @@
     </row>
     <row r="27">
       <c r="A27" s="32"/>
-      <c r="C27" s="33"/>
-      <c r="F27" s="34"/>
-      <c r="G27" s="34"/>
-      <c r="H27" s="34"/>
-      <c r="I27" s="34"/>
+      <c r="C27" s="34"/>
+      <c r="F27" s="33"/>
+      <c r="G27" s="33"/>
+      <c r="H27" s="33"/>
+      <c r="I27" s="33"/>
     </row>
     <row r="28">
-      <c r="C28" s="33"/>
-      <c r="F28" s="34"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="34"/>
-      <c r="I28" s="34"/>
-      <c r="J28" s="34"/>
-      <c r="K28" s="34"/>
-      <c r="L28" s="34"/>
-      <c r="M28" s="34"/>
+      <c r="C28" s="34"/>
+      <c r="F28" s="33"/>
+      <c r="G28" s="33"/>
+      <c r="H28" s="33"/>
+      <c r="I28" s="33"/>
+      <c r="J28" s="33"/>
+      <c r="K28" s="33"/>
+      <c r="L28" s="33"/>
+      <c r="M28" s="33"/>
     </row>
     <row r="29">
-      <c r="C29" s="33"/>
-      <c r="F29" s="34"/>
-      <c r="G29" s="34"/>
-      <c r="H29" s="34"/>
-      <c r="I29" s="34"/>
-      <c r="J29" s="34"/>
-      <c r="K29" s="34"/>
-      <c r="L29" s="34"/>
-      <c r="M29" s="34"/>
+      <c r="C29" s="34"/>
+      <c r="F29" s="33"/>
+      <c r="G29" s="33"/>
+      <c r="H29" s="33"/>
+      <c r="I29" s="33"/>
+      <c r="J29" s="33"/>
+      <c r="K29" s="33"/>
+      <c r="L29" s="33"/>
+      <c r="M29" s="33"/>
     </row>
     <row r="30">
-      <c r="C30" s="33"/>
-      <c r="F30" s="34"/>
-      <c r="G30" s="34"/>
-      <c r="H30" s="34"/>
-      <c r="I30" s="34"/>
+      <c r="C30" s="34"/>
+      <c r="F30" s="33"/>
+      <c r="G30" s="33"/>
+      <c r="H30" s="33"/>
+      <c r="I30" s="33"/>
     </row>
     <row r="31">
-      <c r="C31" s="33"/>
-      <c r="F31" s="34"/>
-      <c r="G31" s="34"/>
-      <c r="H31" s="34"/>
-      <c r="I31" s="34"/>
+      <c r="C31" s="34"/>
+      <c r="F31" s="33"/>
+      <c r="G31" s="33"/>
+      <c r="H31" s="33"/>
+      <c r="I31" s="33"/>
     </row>
     <row r="32">
       <c r="H32" s="27"/>
@@ -8825,7 +8710,7 @@
       <c r="B2" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="33">
+      <c r="C2" s="34">
         <v>45679.0</v>
       </c>
       <c r="D2" s="35">
@@ -8837,14 +8722,14 @@
       <c r="F2" s="35">
         <v>57.9999999999999</v>
       </c>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34"/>
-      <c r="K2" s="34">
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33">
         <v>2.0</v>
       </c>
-      <c r="L2" s="34">
+      <c r="L2" s="33">
         <v>153.7</v>
       </c>
       <c r="M2" s="38">
@@ -8853,8 +8738,8 @@
       <c r="N2" s="35">
         <v>30.0</v>
       </c>
-      <c r="O2" s="34"/>
-      <c r="P2" s="34">
+      <c r="O2" s="33"/>
+      <c r="P2" s="33">
         <v>22.82244632400781</v>
       </c>
       <c r="Q2" s="37">
@@ -8868,7 +8753,7 @@
       <c r="B3" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="33">
+      <c r="C3" s="34">
         <v>45679.0</v>
       </c>
       <c r="D3" s="35">
@@ -8877,27 +8762,27 @@
       <c r="E3" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="34">
+      <c r="F3" s="33">
         <v>61.0</v>
       </c>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
-      <c r="K3" s="34">
+      <c r="G3" s="33"/>
+      <c r="H3" s="33"/>
+      <c r="I3" s="33"/>
+      <c r="J3" s="33"/>
+      <c r="K3" s="33">
         <v>7.0</v>
       </c>
-      <c r="L3" s="34">
+      <c r="L3" s="33">
         <v>174.21</v>
       </c>
-      <c r="M3" s="34">
+      <c r="M3" s="33">
         <v>1825.8099999999997</v>
       </c>
-      <c r="N3" s="34">
+      <c r="N3" s="33">
         <v>30.0</v>
       </c>
-      <c r="O3" s="34"/>
-      <c r="P3" s="34">
+      <c r="O3" s="33"/>
+      <c r="P3" s="33">
         <v>10.480512025716088</v>
       </c>
       <c r="Q3" s="37">
@@ -8911,7 +8796,7 @@
       <c r="B4" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="33">
+      <c r="C4" s="34">
         <v>45680.0</v>
       </c>
       <c r="D4" s="35">
@@ -8920,27 +8805,27 @@
       <c r="E4" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="34">
+      <c r="F4" s="33">
         <v>62.0</v>
       </c>
-      <c r="G4" s="34"/>
-      <c r="H4" s="34"/>
-      <c r="I4" s="34"/>
-      <c r="J4" s="34"/>
-      <c r="K4" s="34">
+      <c r="G4" s="33"/>
+      <c r="H4" s="33"/>
+      <c r="I4" s="33"/>
+      <c r="J4" s="33"/>
+      <c r="K4" s="33">
         <v>3.0</v>
       </c>
-      <c r="L4" s="34">
+      <c r="L4" s="33">
         <v>171.72</v>
       </c>
       <c r="M4" s="39">
         <v>5053.5599999999995</v>
       </c>
-      <c r="N4" s="34">
+      <c r="N4" s="33">
         <v>25.0</v>
       </c>
-      <c r="O4" s="34"/>
-      <c r="P4" s="34">
+      <c r="O4" s="33"/>
+      <c r="P4" s="33">
         <v>29.429070580013974</v>
       </c>
       <c r="Q4" s="37">
@@ -8986,8 +8871,8 @@
       <c r="N5" s="35">
         <v>40.0</v>
       </c>
-      <c r="O5" s="34"/>
-      <c r="P5" s="34">
+      <c r="O5" s="33"/>
+      <c r="P5" s="33">
         <f t="shared" ref="P5:P6" si="1">M5/L5</f>
         <v>8.303997896</v>
       </c>
@@ -9021,8 +8906,8 @@
       <c r="N6" s="35">
         <v>40.0</v>
       </c>
-      <c r="O6" s="34"/>
-      <c r="P6" s="34">
+      <c r="O6" s="33"/>
+      <c r="P6" s="33">
         <f t="shared" si="1"/>
         <v>20.68623291</v>
       </c>
@@ -9040,10 +8925,10 @@
       <c r="J8" s="36"/>
       <c r="K8" s="36"/>
       <c r="L8" s="36"/>
-      <c r="M8" s="34"/>
+      <c r="M8" s="33"/>
       <c r="N8" s="36"/>
-      <c r="O8" s="34"/>
-      <c r="P8" s="34"/>
+      <c r="O8" s="33"/>
+      <c r="P8" s="33"/>
     </row>
     <row r="9">
       <c r="F9" s="36"/>
@@ -9053,10 +8938,10 @@
       <c r="J9" s="36"/>
       <c r="K9" s="36"/>
       <c r="L9" s="36"/>
-      <c r="M9" s="34"/>
+      <c r="M9" s="33"/>
       <c r="N9" s="36"/>
-      <c r="O9" s="34"/>
-      <c r="P9" s="34"/>
+      <c r="O9" s="33"/>
+      <c r="P9" s="33"/>
     </row>
     <row r="10">
       <c r="F10" s="36"/>
@@ -9066,10 +8951,10 @@
       <c r="J10" s="36"/>
       <c r="K10" s="36"/>
       <c r="L10" s="36"/>
-      <c r="M10" s="34"/>
+      <c r="M10" s="33"/>
       <c r="N10" s="36"/>
-      <c r="O10" s="34"/>
-      <c r="P10" s="34"/>
+      <c r="O10" s="33"/>
+      <c r="P10" s="33"/>
     </row>
     <row r="11">
       <c r="E11" s="43" t="s">
@@ -9116,10 +9001,10 @@
       <c r="J14" s="36"/>
       <c r="K14" s="36"/>
       <c r="L14" s="36"/>
-      <c r="M14" s="34"/>
+      <c r="M14" s="33"/>
       <c r="N14" s="36"/>
-      <c r="O14" s="34"/>
-      <c r="P14" s="34"/>
+      <c r="O14" s="33"/>
+      <c r="P14" s="33"/>
     </row>
     <row r="15">
       <c r="F15" s="36"/>
@@ -9129,10 +9014,10 @@
       <c r="J15" s="36"/>
       <c r="K15" s="36"/>
       <c r="L15" s="36"/>
-      <c r="M15" s="34"/>
+      <c r="M15" s="33"/>
       <c r="N15" s="36"/>
-      <c r="O15" s="34"/>
-      <c r="P15" s="34"/>
+      <c r="O15" s="33"/>
+      <c r="P15" s="33"/>
     </row>
     <row r="16">
       <c r="A16" s="45">
@@ -9141,7 +9026,7 @@
       <c r="B16" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="33">
+      <c r="C16" s="34">
         <v>45679.0</v>
       </c>
       <c r="D16" s="47">
@@ -9153,24 +9038,24 @@
       <c r="F16" s="35">
         <v>57.5213675213675</v>
       </c>
-      <c r="G16" s="34"/>
-      <c r="H16" s="34"/>
-      <c r="I16" s="34"/>
-      <c r="J16" s="34"/>
-      <c r="K16" s="34">
+      <c r="G16" s="33"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="33"/>
+      <c r="J16" s="33"/>
+      <c r="K16" s="33">
         <v>5.99999999999999</v>
       </c>
-      <c r="L16" s="34">
+      <c r="L16" s="33">
         <v>127.72</v>
       </c>
-      <c r="M16" s="34">
+      <c r="M16" s="33">
         <v>958.71</v>
       </c>
       <c r="N16" s="35">
         <v>40.0</v>
       </c>
-      <c r="O16" s="34"/>
-      <c r="P16" s="34">
+      <c r="O16" s="33"/>
+      <c r="P16" s="33">
         <v>7.50634199812089</v>
       </c>
       <c r="Q16" s="37">
@@ -9184,7 +9069,7 @@
       <c r="B17" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="33">
+      <c r="C17" s="34">
         <v>45679.0</v>
       </c>
       <c r="D17" s="35">
@@ -9193,27 +9078,27 @@
       <c r="E17" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="F17" s="34">
+      <c r="F17" s="33">
         <v>57.7626974489822</v>
       </c>
-      <c r="G17" s="34"/>
-      <c r="H17" s="34"/>
-      <c r="I17" s="34"/>
-      <c r="J17" s="34"/>
-      <c r="K17" s="34">
+      <c r="G17" s="33"/>
+      <c r="H17" s="33"/>
+      <c r="I17" s="33"/>
+      <c r="J17" s="33"/>
+      <c r="K17" s="33">
         <v>7.0</v>
       </c>
-      <c r="L17" s="34">
+      <c r="L17" s="33">
         <v>174.21</v>
       </c>
-      <c r="M17" s="34">
+      <c r="M17" s="33">
         <v>1825.8099999999997</v>
       </c>
-      <c r="N17" s="34">
+      <c r="N17" s="33">
         <v>30.0</v>
       </c>
-      <c r="O17" s="34"/>
-      <c r="P17" s="34">
+      <c r="O17" s="33"/>
+      <c r="P17" s="33">
         <v>10.480512025716088</v>
       </c>
       <c r="Q17" s="37">
@@ -9227,7 +9112,7 @@
       <c r="B18" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="33">
+      <c r="C18" s="34">
         <v>45680.0</v>
       </c>
       <c r="D18" s="35">
@@ -9236,25 +9121,25 @@
       <c r="E18" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="F18" s="34">
+      <c r="F18" s="33">
         <v>61.8147668934429</v>
       </c>
-      <c r="G18" s="34"/>
-      <c r="H18" s="34"/>
-      <c r="I18" s="34"/>
-      <c r="J18" s="34"/>
-      <c r="K18" s="34">
+      <c r="G18" s="33"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="33"/>
+      <c r="J18" s="33"/>
+      <c r="K18" s="33">
         <v>5.0</v>
       </c>
-      <c r="L18" s="34">
+      <c r="L18" s="33">
         <v>149.66</v>
       </c>
-      <c r="M18" s="34">
+      <c r="M18" s="33">
         <v>8422.4</v>
       </c>
-      <c r="N18" s="34"/>
-      <c r="O18" s="34"/>
-      <c r="P18" s="34">
+      <c r="N18" s="33"/>
+      <c r="O18" s="33"/>
+      <c r="P18" s="33">
         <v>56.27689429373246</v>
       </c>
       <c r="Q18" s="37">
@@ -9268,7 +9153,7 @@
       <c r="B19" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="33">
+      <c r="C19" s="34">
         <v>45677.0</v>
       </c>
       <c r="D19" s="47">
@@ -9277,27 +9162,27 @@
       <c r="E19" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="F19" s="34">
+      <c r="F19" s="33">
         <v>60.7563651137594</v>
       </c>
-      <c r="G19" s="34"/>
-      <c r="H19" s="34"/>
-      <c r="I19" s="34"/>
-      <c r="J19" s="34"/>
-      <c r="K19" s="34">
+      <c r="G19" s="33"/>
+      <c r="H19" s="33"/>
+      <c r="I19" s="33"/>
+      <c r="J19" s="33"/>
+      <c r="K19" s="33">
         <v>12.0</v>
       </c>
-      <c r="L19" s="34">
+      <c r="L19" s="33">
         <v>152.96</v>
       </c>
-      <c r="M19" s="34">
+      <c r="M19" s="33">
         <v>2356.64</v>
       </c>
       <c r="N19" s="35">
         <v>60.0</v>
       </c>
-      <c r="O19" s="34"/>
-      <c r="P19" s="34">
+      <c r="O19" s="33"/>
+      <c r="P19" s="33">
         <v>15.406903765690375</v>
       </c>
       <c r="Q19" s="37">
@@ -9311,7 +9196,7 @@
       <c r="B20" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="C20" s="33">
+      <c r="C20" s="34">
         <v>45677.0</v>
       </c>
       <c r="D20" s="35">
@@ -9320,27 +9205,27 @@
       <c r="E20" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="F20" s="34">
+      <c r="F20" s="33">
         <v>56.4173196363555</v>
       </c>
-      <c r="G20" s="34"/>
-      <c r="H20" s="34"/>
-      <c r="I20" s="34"/>
-      <c r="J20" s="34"/>
-      <c r="K20" s="34">
+      <c r="G20" s="33"/>
+      <c r="H20" s="33"/>
+      <c r="I20" s="33"/>
+      <c r="J20" s="33"/>
+      <c r="K20" s="33">
         <v>6.99999999999999</v>
       </c>
-      <c r="L20" s="34">
+      <c r="L20" s="33">
         <v>101.46</v>
       </c>
-      <c r="M20" s="34">
+      <c r="M20" s="33">
         <v>795.72</v>
       </c>
       <c r="N20" s="35">
         <v>30.0</v>
       </c>
-      <c r="O20" s="34"/>
-      <c r="P20" s="34">
+      <c r="O20" s="33"/>
+      <c r="P20" s="33">
         <v>7.842696629213484</v>
       </c>
       <c r="Q20" s="37">
@@ -12757,7 +12642,7 @@
       </c>
       <c r="C3" s="15">
         <f>AVERAGE('Modelos actuales'!N4:N8)</f>
-        <v>11.7</v>
+        <v>12</v>
       </c>
       <c r="L3" s="89"/>
       <c r="P3" s="89"/>
@@ -13859,7 +13744,7 @@
       <c r="C37" s="31"/>
       <c r="D37" s="104">
         <f>AVERAGE(D39:D1775)</f>
-        <v>4.63625</v>
+        <v>5.718823529</v>
       </c>
       <c r="G37" s="29" t="s">
         <v>36</v>
@@ -13916,7 +13801,7 @@
       </c>
       <c r="D39" s="95">
         <f t="shared" ref="D39:D221" si="17">IF(COUNTA(C39)=1,C39/1,"")</f>
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="G39" s="29" t="s">
         <v>29</v>
@@ -13944,7 +13829,7 @@
     </row>
     <row r="40">
       <c r="C40" s="107" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D40" s="95">
         <f t="shared" si="17"/>
@@ -13976,11 +13861,11 @@
     </row>
     <row r="41">
       <c r="C41" s="107" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D41" s="95">
         <f t="shared" si="17"/>
-        <v>0.36</v>
+        <v>9.75</v>
       </c>
       <c r="P41" s="92">
         <v>1.0</v>
@@ -14002,11 +13887,11 @@
     </row>
     <row r="42">
       <c r="C42" s="107" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D42" s="95">
         <f t="shared" si="17"/>
-        <v>0.25</v>
+        <v>9.37</v>
       </c>
       <c r="P42" s="92">
         <v>1.0</v>
@@ -14028,11 +13913,11 @@
     </row>
     <row r="43">
       <c r="C43" s="107" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D43" s="95">
         <f t="shared" si="17"/>
-        <v>0.68</v>
+        <v>9.8</v>
       </c>
       <c r="P43" s="92"/>
       <c r="AA43" s="36">
@@ -14052,11 +13937,11 @@
     </row>
     <row r="44">
       <c r="C44" s="107" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="D44" s="95">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>7.97</v>
       </c>
       <c r="P44" s="92"/>
       <c r="AB44" s="37">
@@ -14074,37 +13959,37 @@
     </row>
     <row r="45">
       <c r="C45" s="107" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D45" s="95">
         <f t="shared" si="17"/>
-        <v>11.25</v>
+        <v>8.9</v>
       </c>
       <c r="P45" s="92"/>
     </row>
     <row r="46">
       <c r="C46" s="107" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D46" s="95">
         <f t="shared" si="17"/>
-        <v>9.76</v>
+        <v>7.33</v>
       </c>
       <c r="G46" s="66" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H46" s="66" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="P46" s="92"/>
     </row>
     <row r="47">
       <c r="C47" s="107" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D47" s="95">
         <f t="shared" si="17"/>
-        <v>10.4</v>
+        <v>7.98</v>
       </c>
       <c r="G47" s="71" t="s">
         <v>37</v>
@@ -14122,11 +14007,11 @@
     </row>
     <row r="48">
       <c r="C48" s="107" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D48" s="95">
         <f t="shared" si="17"/>
-        <v>10.84</v>
+        <v>5.97</v>
       </c>
       <c r="G48" s="71" t="s">
         <v>36</v>
@@ -14135,7 +14020,7 @@
         <v>0.36678739680281</v>
       </c>
       <c r="J48" s="35" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="K48" s="93">
         <f>AVERAGE(H47:H51)</f>
@@ -14151,11 +14036,11 @@
     </row>
     <row r="49">
       <c r="C49" s="107" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D49" s="95">
         <f t="shared" si="17"/>
-        <v>8.37</v>
+        <v>7.56</v>
       </c>
       <c r="G49" s="71" t="s">
         <v>28</v>
@@ -14164,7 +14049,7 @@
         <v>0.142870351877935</v>
       </c>
       <c r="J49" s="35" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="K49" s="93">
         <f>MEDIAN(H47:H51)</f>
@@ -14180,11 +14065,11 @@
     </row>
     <row r="50">
       <c r="C50" s="107" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D50" s="95">
         <f t="shared" si="17"/>
-        <v>10.22</v>
+        <v>7.76</v>
       </c>
       <c r="G50" s="71" t="s">
         <v>29</v>
@@ -14193,7 +14078,7 @@
         <v>0.497437843674554</v>
       </c>
       <c r="J50" s="35" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="K50" s="93">
         <f>PERCENTILE(H47:H51,0.25)</f>
@@ -14209,11 +14094,11 @@
     </row>
     <row r="51">
       <c r="C51" s="107" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D51" s="95">
         <f t="shared" si="17"/>
-        <v>8.79</v>
+        <v>5.79</v>
       </c>
       <c r="G51" s="71" t="s">
         <v>25</v>
@@ -14222,7 +14107,7 @@
         <v>0.247446036291655</v>
       </c>
       <c r="J51" s="35" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="K51" s="93">
         <f>PERCENTILE(H47:H51,0.75)</f>
@@ -14238,11 +14123,11 @@
     </row>
     <row r="52">
       <c r="C52" s="107" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D52" s="95">
         <f t="shared" si="17"/>
-        <v>5.44</v>
+        <v>5.65</v>
       </c>
       <c r="P52" s="92"/>
       <c r="AA52" s="36">
@@ -14254,11 +14139,11 @@
     </row>
     <row r="53">
       <c r="C53" s="107" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D53" s="95">
         <f t="shared" si="17"/>
-        <v>3.3</v>
+        <v>6.08</v>
       </c>
       <c r="P53" s="92"/>
       <c r="AA53" s="36">
@@ -14270,11 +14155,11 @@
     </row>
     <row r="54">
       <c r="C54" s="107" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D54" s="95">
         <f t="shared" si="17"/>
-        <v>0.81</v>
+        <v>5.75</v>
       </c>
       <c r="P54" s="92"/>
       <c r="AA54" s="36">
@@ -14286,11 +14171,11 @@
     </row>
     <row r="55">
       <c r="C55" s="107" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D55" s="95">
         <f t="shared" si="17"/>
-        <v>6.54</v>
+        <v>5.87</v>
       </c>
       <c r="P55" s="92"/>
       <c r="AA55" s="36">
@@ -14302,11 +14187,11 @@
     </row>
     <row r="56">
       <c r="C56" s="107" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D56" s="95">
         <f t="shared" si="17"/>
-        <v>3.77</v>
+        <v>2.08</v>
       </c>
       <c r="P56" s="92"/>
       <c r="AA56" s="36">
@@ -14318,11 +14203,11 @@
     </row>
     <row r="57">
       <c r="C57" s="107" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D57" s="95">
         <f t="shared" si="17"/>
-        <v>6.59</v>
+        <v>2.22</v>
       </c>
       <c r="P57" s="92"/>
       <c r="AA57" s="35">
@@ -14334,14 +14219,14 @@
     </row>
     <row r="58">
       <c r="C58" s="107" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D58" s="95">
         <f t="shared" si="17"/>
-        <v>4.77</v>
+        <v>11.1</v>
       </c>
       <c r="G58" s="109" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H58" s="110"/>
       <c r="P58" s="92"/>
@@ -14354,15 +14239,15 @@
     </row>
     <row r="59">
       <c r="C59" s="107" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="D59" s="95">
         <f t="shared" si="17"/>
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="G59" s="110"/>
       <c r="H59" s="111" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P59" s="92"/>
       <c r="AA59" s="35">
@@ -14374,15 +14259,15 @@
     </row>
     <row r="60">
       <c r="C60" s="107" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D60" s="95">
         <f t="shared" si="17"/>
-        <v>4.11</v>
+        <v>9.12</v>
       </c>
       <c r="G60" s="110"/>
       <c r="H60" s="111" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P60" s="92"/>
       <c r="AA60" s="36">
@@ -14394,11 +14279,11 @@
     </row>
     <row r="61">
       <c r="C61" s="107" t="s">
-        <v>178</v>
+        <v>152</v>
       </c>
       <c r="D61" s="95">
         <f t="shared" si="17"/>
-        <v>3.73</v>
+        <v>9.37</v>
       </c>
       <c r="G61" s="110"/>
       <c r="H61" s="111" t="s">
@@ -14418,7 +14303,7 @@
       </c>
       <c r="D62" s="95">
         <f t="shared" si="17"/>
-        <v>4.8</v>
+        <v>2.26</v>
       </c>
       <c r="G62" s="110"/>
       <c r="H62" s="111" t="s">
@@ -14438,7 +14323,7 @@
       </c>
       <c r="D63" s="95">
         <f t="shared" si="17"/>
-        <v>5.1</v>
+        <v>11.57</v>
       </c>
       <c r="G63" s="110"/>
       <c r="H63" s="111" t="s">
@@ -14452,88 +14337,88 @@
       </c>
       <c r="D64" s="95">
         <f t="shared" si="17"/>
-        <v>5.36</v>
+        <v>2.1</v>
       </c>
       <c r="P64" s="92"/>
     </row>
     <row r="65">
       <c r="C65" s="107" t="s">
-        <v>122</v>
+        <v>172</v>
       </c>
       <c r="D65" s="95">
         <f t="shared" si="17"/>
-        <v>3.68</v>
+        <v>2.08</v>
       </c>
       <c r="P65" s="92"/>
     </row>
     <row r="66">
       <c r="C66" s="107" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="D66" s="95">
         <f t="shared" si="17"/>
-        <v>3.73</v>
+        <v>2.03</v>
       </c>
       <c r="P66" s="92"/>
     </row>
     <row r="67">
       <c r="C67" s="107" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D67" s="95">
         <f t="shared" si="17"/>
-        <v>3.56</v>
+        <v>1.25</v>
       </c>
       <c r="P67" s="92"/>
     </row>
     <row r="68">
       <c r="C68" s="107" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D68" s="95">
         <f t="shared" si="17"/>
-        <v>3.46</v>
+        <v>1.19</v>
       </c>
       <c r="P68" s="92"/>
     </row>
     <row r="69">
       <c r="C69" s="107" t="s">
-        <v>102</v>
+        <v>186</v>
       </c>
       <c r="D69" s="95">
         <f t="shared" si="17"/>
-        <v>3.67</v>
+        <v>1.25</v>
       </c>
       <c r="P69" s="92"/>
     </row>
     <row r="70">
       <c r="C70" s="107" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D70" s="95">
         <f t="shared" si="17"/>
-        <v>3.59</v>
+        <v>0.01</v>
       </c>
       <c r="P70" s="92"/>
     </row>
     <row r="71">
       <c r="C71" s="107" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D71" s="95">
         <f t="shared" si="17"/>
-        <v>3.55</v>
+        <v>0.05</v>
       </c>
       <c r="F71" s="112"/>
       <c r="P71" s="92"/>
     </row>
     <row r="72">
       <c r="C72" s="107" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D72" s="95">
         <f t="shared" si="17"/>
-        <v>2.5</v>
+        <v>0.01</v>
       </c>
       <c r="P72" s="92"/>
     </row>
@@ -14543,7 +14428,7 @@
       </c>
       <c r="D73" s="95">
         <f t="shared" si="17"/>
-        <v>2.73</v>
+        <v>5.01</v>
       </c>
       <c r="P73" s="92"/>
     </row>
@@ -14553,7 +14438,7 @@
       </c>
       <c r="D74" s="95">
         <f t="shared" si="17"/>
-        <v>2.68</v>
+        <v>5.09</v>
       </c>
       <c r="P74" s="92"/>
     </row>
@@ -14563,7 +14448,7 @@
       </c>
       <c r="D75" s="95">
         <f t="shared" si="17"/>
-        <v>1.89</v>
+        <v>5</v>
       </c>
       <c r="P75" s="92"/>
     </row>
@@ -14573,7 +14458,7 @@
       </c>
       <c r="D76" s="95">
         <f t="shared" si="17"/>
-        <v>2.48</v>
+        <v>11.21</v>
       </c>
       <c r="P76" s="92"/>
     </row>
@@ -14583,7 +14468,7 @@
       </c>
       <c r="D77" s="95">
         <f t="shared" si="17"/>
-        <v>3.32</v>
+        <v>11.06</v>
       </c>
       <c r="P77" s="92"/>
     </row>
@@ -14593,7 +14478,7 @@
       </c>
       <c r="D78" s="95">
         <f t="shared" si="17"/>
-        <v>4.7</v>
+        <v>12.77</v>
       </c>
       <c r="P78" s="113"/>
     </row>
@@ -14603,7 +14488,7 @@
       </c>
       <c r="D79" s="95">
         <f t="shared" si="17"/>
-        <v>3.85</v>
+        <v>8.8</v>
       </c>
       <c r="P79" s="113"/>
     </row>
@@ -14613,7 +14498,7 @@
       </c>
       <c r="D80" s="95">
         <f t="shared" si="17"/>
-        <v>4.66</v>
+        <v>9.18</v>
       </c>
       <c r="P80" s="113"/>
     </row>
@@ -14623,27 +14508,27 @@
       </c>
       <c r="D81" s="95">
         <f t="shared" si="17"/>
-        <v>0.38</v>
+        <v>9.74</v>
       </c>
       <c r="P81" s="113"/>
     </row>
     <row r="82">
       <c r="C82" s="107" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="D82" s="95">
         <f t="shared" si="17"/>
-        <v>3.46</v>
+        <v>5.44</v>
       </c>
       <c r="P82" s="113"/>
     </row>
     <row r="83">
       <c r="C83" s="107" t="s">
-        <v>199</v>
+        <v>136</v>
       </c>
       <c r="D83" s="95">
         <f t="shared" si="17"/>
-        <v>4.26</v>
+        <v>7.85</v>
       </c>
       <c r="P83" s="113"/>
     </row>
@@ -14653,7 +14538,7 @@
       </c>
       <c r="D84" s="95">
         <f t="shared" si="17"/>
-        <v>2.96</v>
+        <v>8.59</v>
       </c>
       <c r="P84" s="113"/>
     </row>
@@ -14663,7 +14548,7 @@
       </c>
       <c r="D85" s="95">
         <f t="shared" si="17"/>
-        <v>6.1</v>
+        <v>6.42</v>
       </c>
       <c r="P85" s="113"/>
     </row>
@@ -14673,7 +14558,7 @@
       </c>
       <c r="D86" s="95">
         <f t="shared" si="17"/>
-        <v>6</v>
+        <v>2.94</v>
       </c>
       <c r="P86" s="113"/>
     </row>
@@ -14683,7 +14568,7 @@
       </c>
       <c r="D87" s="95">
         <f t="shared" si="17"/>
-        <v>6.42</v>
+        <v>3.62</v>
       </c>
       <c r="P87" s="113"/>
     </row>
@@ -14693,7 +14578,7 @@
       </c>
       <c r="D88" s="95">
         <f t="shared" si="17"/>
-        <v>0.62</v>
+        <v>3.72</v>
       </c>
       <c r="P88" s="113"/>
     </row>
@@ -14703,465 +14588,375 @@
       </c>
       <c r="D89" s="95">
         <f t="shared" si="17"/>
-        <v>0.03</v>
+        <v>4.85</v>
       </c>
       <c r="P89" s="113"/>
     </row>
     <row r="90">
-      <c r="C90" s="107" t="s">
-        <v>206</v>
-      </c>
-      <c r="D90" s="95">
+      <c r="C90" s="107"/>
+      <c r="D90" s="95" t="str">
         <f t="shared" si="17"/>
-        <v>0.51</v>
+        <v/>
       </c>
       <c r="P90" s="113"/>
     </row>
     <row r="91">
-      <c r="C91" s="107" t="s">
-        <v>207</v>
-      </c>
-      <c r="D91" s="95">
+      <c r="C91" s="107"/>
+      <c r="D91" s="95" t="str">
         <f t="shared" si="17"/>
-        <v>0.4</v>
+        <v/>
       </c>
       <c r="P91" s="113"/>
     </row>
     <row r="92">
-      <c r="C92" s="107" t="s">
-        <v>208</v>
-      </c>
-      <c r="D92" s="95">
+      <c r="C92" s="107"/>
+      <c r="D92" s="95" t="str">
         <f t="shared" si="17"/>
-        <v>0.59</v>
+        <v/>
       </c>
       <c r="P92" s="113"/>
     </row>
     <row r="93">
-      <c r="C93" s="107" t="s">
-        <v>209</v>
-      </c>
-      <c r="D93" s="95">
+      <c r="C93" s="107"/>
+      <c r="D93" s="95" t="str">
         <f t="shared" si="17"/>
-        <v>0.61</v>
+        <v/>
       </c>
       <c r="P93" s="113"/>
     </row>
     <row r="94">
-      <c r="C94" s="107" t="s">
-        <v>210</v>
-      </c>
-      <c r="D94" s="95">
+      <c r="C94" s="107"/>
+      <c r="D94" s="95" t="str">
         <f t="shared" si="17"/>
-        <v>0.6</v>
+        <v/>
       </c>
       <c r="P94" s="113"/>
     </row>
     <row r="95">
-      <c r="C95" s="107" t="s">
-        <v>211</v>
-      </c>
-      <c r="D95" s="95">
+      <c r="C95" s="107"/>
+      <c r="D95" s="95" t="str">
         <f t="shared" si="17"/>
-        <v>1.05</v>
+        <v/>
       </c>
       <c r="P95" s="113"/>
     </row>
     <row r="96">
-      <c r="C96" s="107" t="s">
-        <v>212</v>
-      </c>
-      <c r="D96" s="95">
+      <c r="C96" s="107"/>
+      <c r="D96" s="95" t="str">
         <f t="shared" si="17"/>
-        <v>0.04</v>
+        <v/>
       </c>
       <c r="P96" s="113"/>
     </row>
     <row r="97">
-      <c r="C97" s="107" t="s">
-        <v>213</v>
-      </c>
-      <c r="D97" s="95">
+      <c r="C97" s="107"/>
+      <c r="D97" s="95" t="str">
         <f t="shared" si="17"/>
-        <v>0.18</v>
+        <v/>
       </c>
       <c r="P97" s="113"/>
     </row>
     <row r="98">
-      <c r="C98" s="107" t="s">
-        <v>149</v>
-      </c>
-      <c r="D98" s="95">
+      <c r="C98" s="107"/>
+      <c r="D98" s="95" t="str">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="P98" s="113"/>
     </row>
     <row r="99">
-      <c r="C99" s="107" t="s">
-        <v>149</v>
-      </c>
-      <c r="D99" s="95">
+      <c r="C99" s="107"/>
+      <c r="D99" s="95" t="str">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="P99" s="113"/>
     </row>
     <row r="100">
-      <c r="C100" s="107" t="s">
-        <v>214</v>
-      </c>
-      <c r="D100" s="95">
+      <c r="C100" s="107"/>
+      <c r="D100" s="95" t="str">
         <f t="shared" si="17"/>
-        <v>1.25</v>
+        <v/>
       </c>
       <c r="P100" s="113"/>
     </row>
     <row r="101">
-      <c r="C101" s="107" t="s">
-        <v>149</v>
-      </c>
-      <c r="D101" s="95">
+      <c r="C101" s="107"/>
+      <c r="D101" s="95" t="str">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="P101" s="113"/>
     </row>
     <row r="102">
-      <c r="C102" s="107" t="s">
-        <v>149</v>
-      </c>
-      <c r="D102" s="95">
+      <c r="C102" s="107"/>
+      <c r="D102" s="95" t="str">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v/>
       </c>
       <c r="P102" s="113"/>
     </row>
     <row r="103">
-      <c r="C103" s="107" t="s">
-        <v>215</v>
-      </c>
-      <c r="D103" s="95">
+      <c r="C103" s="107"/>
+      <c r="D103" s="95" t="str">
         <f t="shared" si="17"/>
-        <v>1.21</v>
+        <v/>
       </c>
       <c r="P103" s="113"/>
     </row>
     <row r="104">
-      <c r="C104" s="107" t="s">
-        <v>216</v>
-      </c>
-      <c r="D104" s="95">
+      <c r="C104" s="107"/>
+      <c r="D104" s="95" t="str">
         <f t="shared" si="17"/>
-        <v>1.12</v>
+        <v/>
       </c>
       <c r="N104" s="114"/>
       <c r="P104" s="113"/>
     </row>
     <row r="105">
-      <c r="C105" s="107" t="s">
-        <v>217</v>
-      </c>
-      <c r="D105" s="95">
+      <c r="C105" s="107"/>
+      <c r="D105" s="95" t="str">
         <f t="shared" si="17"/>
-        <v>10.75</v>
+        <v/>
       </c>
       <c r="N105" s="14"/>
       <c r="P105" s="113"/>
     </row>
     <row r="106">
-      <c r="C106" s="107" t="s">
-        <v>218</v>
-      </c>
-      <c r="D106" s="95">
+      <c r="C106" s="107"/>
+      <c r="D106" s="95" t="str">
         <f t="shared" si="17"/>
-        <v>10.43</v>
+        <v/>
       </c>
       <c r="N106" s="14"/>
       <c r="P106" s="113"/>
     </row>
     <row r="107">
-      <c r="C107" s="107" t="s">
-        <v>219</v>
-      </c>
-      <c r="D107" s="95">
+      <c r="C107" s="107"/>
+      <c r="D107" s="95" t="str">
         <f t="shared" si="17"/>
-        <v>11.53</v>
+        <v/>
       </c>
       <c r="N107" s="14"/>
       <c r="P107" s="113"/>
     </row>
     <row r="108">
-      <c r="C108" s="107" t="s">
-        <v>220</v>
-      </c>
-      <c r="D108" s="95">
+      <c r="C108" s="107"/>
+      <c r="D108" s="95" t="str">
         <f t="shared" si="17"/>
-        <v>10.85</v>
+        <v/>
       </c>
       <c r="N108" s="14"/>
       <c r="P108" s="113"/>
     </row>
     <row r="109">
-      <c r="C109" s="107" t="s">
-        <v>221</v>
-      </c>
-      <c r="D109" s="95">
+      <c r="C109" s="107"/>
+      <c r="D109" s="95" t="str">
         <f t="shared" si="17"/>
-        <v>12.26</v>
+        <v/>
       </c>
       <c r="N109" s="14"/>
       <c r="P109" s="113"/>
     </row>
     <row r="110">
-      <c r="C110" s="107" t="s">
-        <v>222</v>
-      </c>
-      <c r="D110" s="95">
+      <c r="C110" s="107"/>
+      <c r="D110" s="95" t="str">
         <f t="shared" si="17"/>
-        <v>6.98</v>
+        <v/>
       </c>
       <c r="N110" s="14"/>
       <c r="P110" s="113"/>
     </row>
     <row r="111">
-      <c r="C111" s="107" t="s">
-        <v>223</v>
-      </c>
-      <c r="D111" s="95">
+      <c r="C111" s="107"/>
+      <c r="D111" s="95" t="str">
         <f t="shared" si="17"/>
-        <v>8.25</v>
+        <v/>
       </c>
       <c r="N111" s="14"/>
       <c r="P111" s="113"/>
     </row>
     <row r="112">
-      <c r="C112" s="107" t="s">
-        <v>224</v>
-      </c>
-      <c r="D112" s="95">
+      <c r="C112" s="107"/>
+      <c r="D112" s="95" t="str">
         <f t="shared" si="17"/>
-        <v>7.63</v>
+        <v/>
       </c>
       <c r="P112" s="113"/>
     </row>
     <row r="113">
-      <c r="C113" s="107" t="s">
-        <v>225</v>
-      </c>
-      <c r="D113" s="95">
+      <c r="C113" s="107"/>
+      <c r="D113" s="95" t="str">
         <f t="shared" si="17"/>
-        <v>7.01</v>
+        <v/>
       </c>
       <c r="P113" s="113"/>
     </row>
     <row r="114">
-      <c r="C114" s="107" t="s">
-        <v>226</v>
-      </c>
-      <c r="D114" s="95">
+      <c r="C114" s="107"/>
+      <c r="D114" s="95" t="str">
         <f t="shared" si="17"/>
-        <v>8</v>
+        <v/>
       </c>
       <c r="P114" s="113"/>
     </row>
     <row r="115">
-      <c r="C115" s="107" t="s">
-        <v>227</v>
-      </c>
-      <c r="D115" s="95">
+      <c r="C115" s="107"/>
+      <c r="D115" s="95" t="str">
         <f t="shared" si="17"/>
-        <v>11.16</v>
+        <v/>
       </c>
       <c r="P115" s="113"/>
     </row>
     <row r="116">
-      <c r="C116" s="107" t="s">
-        <v>228</v>
-      </c>
-      <c r="D116" s="95">
+      <c r="C116" s="107"/>
+      <c r="D116" s="95" t="str">
         <f t="shared" si="17"/>
-        <v>7.22</v>
+        <v/>
       </c>
       <c r="P116" s="113"/>
     </row>
     <row r="117">
-      <c r="C117" s="107" t="s">
-        <v>229</v>
-      </c>
-      <c r="D117" s="95">
+      <c r="C117" s="107"/>
+      <c r="D117" s="95" t="str">
         <f t="shared" si="17"/>
-        <v>8.7</v>
+        <v/>
       </c>
       <c r="P117" s="113"/>
     </row>
     <row r="118">
-      <c r="C118" s="107" t="s">
-        <v>230</v>
-      </c>
-      <c r="D118" s="95">
+      <c r="C118" s="107"/>
+      <c r="D118" s="95" t="str">
         <f t="shared" si="17"/>
-        <v>11.55</v>
+        <v/>
       </c>
       <c r="P118" s="113"/>
     </row>
     <row r="119">
-      <c r="C119" s="107" t="s">
-        <v>231</v>
-      </c>
-      <c r="D119" s="95">
+      <c r="C119" s="107"/>
+      <c r="D119" s="95" t="str">
         <f t="shared" si="17"/>
-        <v>11.18</v>
+        <v/>
       </c>
       <c r="P119" s="113"/>
     </row>
     <row r="120">
-      <c r="C120" s="107" t="s">
-        <v>232</v>
-      </c>
-      <c r="D120" s="95">
+      <c r="C120" s="107"/>
+      <c r="D120" s="95" t="str">
         <f t="shared" si="17"/>
-        <v>11.69</v>
+        <v/>
       </c>
       <c r="P120" s="113"/>
     </row>
     <row r="121">
-      <c r="C121" s="107" t="s">
-        <v>233</v>
-      </c>
-      <c r="D121" s="95">
+      <c r="C121" s="107"/>
+      <c r="D121" s="95" t="str">
         <f t="shared" si="17"/>
-        <v>4.09</v>
+        <v/>
       </c>
       <c r="P121" s="113"/>
     </row>
     <row r="122">
-      <c r="C122" s="107" t="s">
-        <v>234</v>
-      </c>
-      <c r="D122" s="95">
+      <c r="C122" s="107"/>
+      <c r="D122" s="95" t="str">
         <f t="shared" si="17"/>
-        <v>3.17</v>
+        <v/>
       </c>
       <c r="P122" s="113"/>
     </row>
     <row r="123">
-      <c r="C123" s="107" t="s">
-        <v>235</v>
-      </c>
-      <c r="D123" s="95">
+      <c r="C123" s="107"/>
+      <c r="D123" s="95" t="str">
         <f t="shared" si="17"/>
-        <v>8.85</v>
+        <v/>
       </c>
       <c r="P123" s="113"/>
     </row>
     <row r="124">
-      <c r="C124" s="107" t="s">
-        <v>236</v>
-      </c>
-      <c r="D124" s="95">
+      <c r="C124" s="107"/>
+      <c r="D124" s="95" t="str">
         <f t="shared" si="17"/>
-        <v>12.66</v>
+        <v/>
       </c>
       <c r="P124" s="113"/>
     </row>
     <row r="125">
-      <c r="C125" s="107" t="s">
-        <v>237</v>
-      </c>
-      <c r="D125" s="95">
+      <c r="C125" s="107"/>
+      <c r="D125" s="95" t="str">
         <f t="shared" si="17"/>
-        <v>12.45</v>
+        <v/>
       </c>
       <c r="P125" s="113"/>
     </row>
     <row r="126">
-      <c r="C126" s="107" t="s">
-        <v>238</v>
-      </c>
-      <c r="D126" s="95">
+      <c r="C126" s="107"/>
+      <c r="D126" s="95" t="str">
         <f t="shared" si="17"/>
-        <v>8.98</v>
+        <v/>
       </c>
       <c r="P126" s="113"/>
     </row>
     <row r="127">
-      <c r="C127" s="107" t="s">
-        <v>239</v>
-      </c>
-      <c r="D127" s="95">
+      <c r="C127" s="107"/>
+      <c r="D127" s="95" t="str">
         <f t="shared" si="17"/>
-        <v>3.04</v>
+        <v/>
       </c>
       <c r="P127" s="113"/>
     </row>
     <row r="128">
-      <c r="C128" s="107" t="s">
-        <v>240</v>
-      </c>
-      <c r="D128" s="95">
+      <c r="C128" s="107"/>
+      <c r="D128" s="95" t="str">
         <f t="shared" si="17"/>
-        <v>2.3</v>
+        <v/>
       </c>
       <c r="P128" s="113"/>
     </row>
     <row r="129">
-      <c r="C129" s="107" t="s">
-        <v>241</v>
-      </c>
-      <c r="D129" s="95">
+      <c r="C129" s="107"/>
+      <c r="D129" s="95" t="str">
         <f t="shared" si="17"/>
-        <v>2.99</v>
+        <v/>
       </c>
       <c r="P129" s="113"/>
     </row>
     <row r="130">
-      <c r="C130" s="107" t="s">
-        <v>131</v>
-      </c>
-      <c r="D130" s="95">
+      <c r="C130" s="107"/>
+      <c r="D130" s="95" t="str">
         <f t="shared" si="17"/>
-        <v>2.8</v>
+        <v/>
       </c>
       <c r="P130" s="113"/>
     </row>
     <row r="131">
-      <c r="C131" s="107" t="s">
-        <v>242</v>
-      </c>
-      <c r="D131" s="95">
+      <c r="C131" s="107"/>
+      <c r="D131" s="95" t="str">
         <f t="shared" si="17"/>
-        <v>1.23</v>
+        <v/>
       </c>
       <c r="P131" s="113"/>
     </row>
     <row r="132">
-      <c r="C132" s="107" t="s">
-        <v>214</v>
-      </c>
-      <c r="D132" s="95">
+      <c r="C132" s="107"/>
+      <c r="D132" s="95" t="str">
         <f t="shared" si="17"/>
-        <v>1.25</v>
+        <v/>
       </c>
       <c r="P132" s="113"/>
     </row>
     <row r="133">
-      <c r="C133" s="107" t="s">
-        <v>214</v>
-      </c>
-      <c r="D133" s="95">
+      <c r="C133" s="107"/>
+      <c r="D133" s="95" t="str">
         <f t="shared" si="17"/>
-        <v>1.25</v>
+        <v/>
       </c>
       <c r="P133" s="113"/>
     </row>
     <row r="134">
-      <c r="C134" s="107" t="s">
-        <v>243</v>
-      </c>
-      <c r="D134" s="95">
+      <c r="C134" s="107"/>
+      <c r="D134" s="95" t="str">
         <f t="shared" si="17"/>
-        <v>0.8</v>
+        <v/>
       </c>
       <c r="P134" s="113"/>
     </row>
@@ -36005,14 +35800,14 @@
     <row r="1">
       <c r="A1" s="75"/>
       <c r="B1" s="117" t="s">
-        <v>244</v>
+        <v>206</v>
       </c>
       <c r="C1" s="118"/>
       <c r="D1" s="118"/>
       <c r="E1" s="118"/>
       <c r="F1" s="118"/>
       <c r="G1" s="119" t="s">
-        <v>245</v>
+        <v>207</v>
       </c>
       <c r="H1" s="118"/>
       <c r="I1" s="118"/>
@@ -36040,19 +35835,19 @@
         <v>3</v>
       </c>
       <c r="B2" s="121" t="s">
-        <v>246</v>
+        <v>208</v>
       </c>
       <c r="C2" s="122" t="s">
-        <v>247</v>
+        <v>209</v>
       </c>
       <c r="D2" s="122" t="s">
         <v>145</v>
       </c>
       <c r="E2" s="122" t="s">
-        <v>248</v>
+        <v>210</v>
       </c>
       <c r="F2" s="123" t="s">
-        <v>249</v>
+        <v>211</v>
       </c>
       <c r="G2" s="121">
         <v>1.0</v>
@@ -36064,25 +35859,25 @@
         <v>2.0</v>
       </c>
       <c r="J2" s="122" t="s">
-        <v>250</v>
+        <v>212</v>
       </c>
       <c r="K2" s="124" t="s">
-        <v>251</v>
+        <v>213</v>
       </c>
       <c r="L2" s="122" t="s">
-        <v>252</v>
+        <v>214</v>
       </c>
       <c r="M2" s="125" t="s">
-        <v>253</v>
+        <v>215</v>
       </c>
       <c r="N2" s="71" t="s">
-        <v>254</v>
+        <v>216</v>
       </c>
       <c r="O2" s="71" t="s">
-        <v>255</v>
+        <v>217</v>
       </c>
       <c r="P2" s="71" t="s">
-        <v>256</v>
+        <v>218</v>
       </c>
       <c r="Q2" s="8"/>
       <c r="R2" s="8"/>
@@ -36865,7 +36660,7 @@
       <c r="E27" s="8"/>
       <c r="F27" s="8"/>
       <c r="G27" s="139" t="s">
-        <v>257</v>
+        <v>219</v>
       </c>
       <c r="H27" s="8"/>
       <c r="I27" s="8"/>
@@ -36926,7 +36721,7 @@
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
       <c r="D29" s="4" t="s">
-        <v>258</v>
+        <v>220</v>
       </c>
       <c r="E29" s="4">
         <f>J29</f>
@@ -36948,10 +36743,10 @@
       </c>
       <c r="K29" s="8"/>
       <c r="L29" s="65" t="s">
-        <v>259</v>
+        <v>221</v>
       </c>
       <c r="M29" s="65" t="s">
-        <v>260</v>
+        <v>222</v>
       </c>
       <c r="O29" s="4">
         <v>1.0</v>
@@ -37087,7 +36882,7 @@
       <c r="E33" s="8"/>
       <c r="F33" s="8"/>
       <c r="G33" s="90" t="s">
-        <v>261</v>
+        <v>223</v>
       </c>
       <c r="J33" s="8"/>
       <c r="K33" s="8"/>
@@ -37264,7 +37059,7 @@
       <c r="D38" s="8"/>
       <c r="E38" s="8"/>
       <c r="F38" s="4" t="s">
-        <v>262</v>
+        <v>224</v>
       </c>
       <c r="G38" s="142">
         <f t="shared" ref="G38:I38" si="8">G30-G35</f>

--- a/data/df_best_models.xlsx
+++ b/data/df_best_models.xlsx
@@ -38,6 +38,11 @@
     <comment authorId="0" ref="I4">
       <text>
         <t xml:space="preserve">el empate...</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="J4">
+      <text>
+        <t xml:space="preserve">crece gracias a doble oportunidad. en este caso de 0.55</t>
       </text>
     </comment>
     <comment authorId="0" ref="A1">
@@ -211,7 +216,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="225">
   <si>
     <t>id_country</t>
   </si>
@@ -660,28 +665,28 @@
     <t>Stake promedio</t>
   </si>
   <si>
-    <t>1.15</t>
+    <t>1.42</t>
   </si>
   <si>
-    <t>0.00</t>
+    <t>0.99</t>
   </si>
   <si>
-    <t>9.75</t>
+    <t>9.04</t>
   </si>
   <si>
-    <t>9.37</t>
+    <t>8.68</t>
   </si>
   <si>
-    <t>9.80</t>
-  </si>
-  <si>
-    <t>7.97</t>
-  </si>
-  <si>
-    <t>8.90</t>
+    <t>9.08</t>
   </si>
   <si>
     <t>7.33</t>
+  </si>
+  <si>
+    <t>8.24</t>
+  </si>
+  <si>
+    <t>6.55</t>
   </si>
   <si>
     <t>Country</t>
@@ -690,10 +695,10 @@
     <t>Correl ROI y Expected ROI</t>
   </si>
   <si>
-    <t>7.98</t>
+    <t>8.69</t>
   </si>
   <si>
-    <t>5.97</t>
+    <t>6.59</t>
   </si>
   <si>
     <t>mean</t>
@@ -711,22 +716,22 @@
     <t>p25</t>
   </si>
   <si>
-    <t>5.79</t>
+    <t>6.42</t>
   </si>
   <si>
     <t>p75</t>
   </si>
   <si>
-    <t>5.65</t>
+    <t>6.28</t>
   </si>
   <si>
-    <t>6.08</t>
+    <t>6.71</t>
   </si>
   <si>
-    <t>5.75</t>
+    <t>6.38</t>
   </si>
   <si>
-    <t>5.87</t>
+    <t>6.50</t>
   </si>
   <si>
     <t>2.08</t>
@@ -735,100 +740,100 @@
     <t>2.22</t>
   </si>
   <si>
-    <t>11.10</t>
+    <t>16.91</t>
   </si>
   <si>
     <t>Gracias a las nuevas métricas de G/P sin bank en test, me di cuenta de que:</t>
   </si>
   <si>
+    <t>1.37</t>
+  </si>
+  <si>
     <t>La rentabilidad en ITA está en el visitante y no en el empate como creía.</t>
   </si>
   <si>
-    <t>9.12</t>
+    <t>14.23</t>
   </si>
   <si>
     <t>La rentabilidad en ENG y GER está en el empate tal como creía.</t>
   </si>
   <si>
+    <t>10.34</t>
+  </si>
+  <si>
     <t>En SPA esta repartido aunque Empate saca una ventaja.</t>
   </si>
   <si>
-    <t>2.26</t>
+    <t>4.57</t>
   </si>
   <si>
     <t>En FRA, depende el modelo. A veces local, a veces, empate.</t>
   </si>
   <si>
-    <t>11.57</t>
-  </si>
-  <si>
     <t>Si en FRA empate no rinde, no tiene sentido exigirle una buena distrib en empate… → Tiene sentido pero al parecer si importa el empate puesto que el modelo que gana se basa en empate.</t>
   </si>
   <si>
-    <t>2.10</t>
+    <t>0.69</t>
   </si>
   <si>
-    <t>2.03</t>
+    <t>1.97</t>
   </si>
   <si>
-    <t>1.25</t>
+    <t>3.71</t>
   </si>
   <si>
-    <t>1.19</t>
+    <t>2.06</t>
   </si>
   <si>
-    <t>0.01</t>
+    <t>4.48</t>
   </si>
   <si>
-    <t>0.05</t>
+    <t>3.49</t>
   </si>
   <si>
-    <t>5.01</t>
+    <t>0.10</t>
   </si>
   <si>
-    <t>5.09</t>
+    <t>0.57</t>
   </si>
   <si>
-    <t>5.00</t>
+    <t>10.77</t>
   </si>
   <si>
-    <t>11.21</t>
+    <t>10.44</t>
   </si>
   <si>
-    <t>11.06</t>
+    <t>7.80</t>
   </si>
   <si>
-    <t>12.77</t>
+    <t>8.87</t>
   </si>
   <si>
-    <t>8.80</t>
+    <t>3.11</t>
   </si>
   <si>
-    <t>9.18</t>
+    <t>7.17</t>
   </si>
   <si>
-    <t>9.74</t>
+    <t>5.37</t>
   </si>
   <si>
-    <t>5.44</t>
+    <t>11.08</t>
   </si>
   <si>
-    <t>8.59</t>
+    <t>5.78</t>
   </si>
   <si>
-    <t>6.42</t>
+    <t>9.30</t>
   </si>
   <si>
-    <t>2.94</t>
+    <t>0.35</t>
   </si>
   <si>
-    <t>3.62</t>
+    <t>1.74</t>
   </si>
   <si>
-    <t>3.72</t>
-  </si>
-  <si>
-    <t>4.85</t>
+    <t>2.19</t>
   </si>
   <si>
     <t>RENTABILIDAD</t>
@@ -1928,35 +1933,35 @@
         <v>56.3636363636363</v>
       </c>
       <c r="G4" s="24">
-        <v>161.57</v>
+        <v>215.601161375027</v>
       </c>
       <c r="H4" s="24">
-        <f>-2.18+
-2291.53+
-384.61
+        <f>71.19+
+2310.5+
+384.17
 </f>
-        <v>2673.96</v>
+        <v>2765.86</v>
       </c>
       <c r="I4" s="24">
         <f t="shared" ref="I4:I8" si="1">H4/G4</f>
-        <v>16.54985455</v>
+        <v>12.82859509</v>
       </c>
       <c r="J4" s="19">
-        <v>5.0</v>
+        <v>25.0</v>
       </c>
       <c r="K4" s="19">
-        <v>50.0</v>
+        <v>45.0</v>
       </c>
       <c r="L4" s="19">
-        <v>40.0</v>
+        <v>45.0</v>
       </c>
       <c r="M4" s="24">
         <f t="shared" ref="M4:M8" si="2">AVERAGE(J4:L4)</f>
-        <v>31.66666667</v>
+        <v>38.33333333</v>
       </c>
       <c r="N4" s="15">
         <f>M4*'Data preparation'!$C$2</f>
-        <v>9.5</v>
+        <v>9.583333333</v>
       </c>
     </row>
     <row r="5">
@@ -1983,31 +1988,31 @@
       </c>
       <c r="H5" s="24">
         <f>866.5+
-335.27+
+327.23+
 114.67
 </f>
-        <v>1316.44</v>
+        <v>1308.4</v>
       </c>
       <c r="I5" s="24">
         <f t="shared" si="1"/>
-        <v>8.937843703</v>
+        <v>8.88325689</v>
       </c>
       <c r="J5" s="24">
         <v>70.0</v>
       </c>
       <c r="K5" s="24">
-        <v>40.0</v>
+        <v>45.0</v>
       </c>
       <c r="L5" s="24">
         <v>25.0</v>
       </c>
       <c r="M5" s="24">
         <f t="shared" si="2"/>
-        <v>45</v>
+        <v>46.66666667</v>
       </c>
       <c r="N5" s="15">
         <f>M5*'Data preparation'!$C$2</f>
-        <v>13.5</v>
+        <v>11.66666667</v>
       </c>
       <c r="P5" s="25"/>
     </row>
@@ -2022,44 +2027,44 @@
         <v>45680.0</v>
       </c>
       <c r="D6" s="23">
-        <v>507.0</v>
+        <v>1051.0</v>
       </c>
       <c r="E6" s="23" t="s">
         <v>17</v>
       </c>
       <c r="F6" s="24">
-        <v>56.8807339449541</v>
+        <v>62.3853211009174</v>
       </c>
       <c r="G6" s="24">
-        <v>236.14</v>
+        <v>239.456083423093</v>
       </c>
       <c r="H6" s="24">
-        <f>197670.24+
-315.6+
-8.71
+        <f>2054.41+
+8839.74+
+91.53
 </f>
-        <v>197994.55</v>
+        <v>10985.68</v>
       </c>
       <c r="I6" s="24">
         <f t="shared" si="1"/>
-        <v>838.4625646</v>
+        <v>45.87764004</v>
       </c>
       <c r="J6" s="24">
-        <v>135.0</v>
+        <v>70.0</v>
       </c>
       <c r="K6" s="24">
+        <v>70.0</v>
+      </c>
+      <c r="L6" s="24">
         <v>25.0</v>
-      </c>
-      <c r="L6" s="24">
-        <v>10.0</v>
       </c>
       <c r="M6" s="24">
         <f t="shared" si="2"/>
-        <v>56.66666667</v>
+        <v>55</v>
       </c>
       <c r="N6" s="15">
         <f>M6*'Data preparation'!$C$2</f>
-        <v>17</v>
+        <v>13.75</v>
       </c>
     </row>
     <row r="7">
@@ -2073,7 +2078,7 @@
         <v>45677.0</v>
       </c>
       <c r="D7" s="23">
-        <v>1623.0</v>
+        <v>19.0</v>
       </c>
       <c r="E7" s="23" t="s">
         <v>17</v>
@@ -2082,35 +2087,35 @@
         <v>60.0</v>
       </c>
       <c r="G7" s="24">
-        <v>146.88838482783</v>
+        <v>183.94673286652</v>
       </c>
       <c r="H7" s="24">
-        <f>-1.86+
-3963.24+
-625.47
+        <f>-16.55+
+335.32+
+3063.41
 </f>
-        <v>4586.85</v>
+        <v>3382.18</v>
       </c>
       <c r="I7" s="24">
         <f t="shared" si="1"/>
-        <v>31.2267713</v>
+        <v>18.38673592</v>
       </c>
       <c r="J7" s="19">
         <v>10.0</v>
       </c>
       <c r="K7" s="19">
+        <v>25.0</v>
+      </c>
+      <c r="L7" s="19">
         <v>70.0</v>
-      </c>
-      <c r="L7" s="19">
-        <v>45.0</v>
       </c>
       <c r="M7" s="19">
         <f t="shared" si="2"/>
-        <v>41.66666667</v>
+        <v>35</v>
       </c>
       <c r="N7" s="15">
         <f>M7*'Data preparation'!$C$2</f>
-        <v>12.5</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="8">
@@ -2124,7 +2129,7 @@
         <v>45677.0</v>
       </c>
       <c r="D8" s="23">
-        <v>1545.0</v>
+        <v>112.0</v>
       </c>
       <c r="E8" s="23" t="s">
         <v>17</v>
@@ -2133,18 +2138,18 @@
         <v>57.2727272727272</v>
       </c>
       <c r="G8" s="24">
-        <v>114.811855439534</v>
+        <v>121.438244474087</v>
       </c>
       <c r="H8" s="24">
-        <f>266.16+
+        <f>360.49+
 3511.03+
 12.5
 </f>
-        <v>3789.69</v>
+        <v>3884.02</v>
       </c>
       <c r="I8" s="24">
         <f t="shared" si="1"/>
-        <v>33.0078282</v>
+        <v>31.98349924</v>
       </c>
       <c r="J8" s="19">
         <v>45.0</v>
@@ -2161,7 +2166,7 @@
       </c>
       <c r="N8" s="15">
         <f>M8*'Data preparation'!$C$2</f>
-        <v>12.5</v>
+        <v>10.41666667</v>
       </c>
     </row>
     <row r="9" ht="20.25" customHeight="1">
@@ -11893,7 +11898,7 @@
       </c>
       <c r="N68" s="14">
         <f>L68*'Data preparation'!$C$2</f>
-        <v>9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="69">
@@ -11938,7 +11943,7 @@
       </c>
       <c r="N69" s="14">
         <f>L69*'Data preparation'!$C$2</f>
-        <v>9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="70">
@@ -11983,7 +11988,7 @@
       </c>
       <c r="N70" s="14">
         <f>L70*'Data preparation'!$C$2</f>
-        <v>7.5</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="71">
@@ -12027,7 +12032,7 @@
       </c>
       <c r="N71" s="14">
         <f>L71*'Data preparation'!$C$2</f>
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="72">
@@ -12071,7 +12076,7 @@
       </c>
       <c r="N72" s="14">
         <f>L72*'Data preparation'!$C$2</f>
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="76">
@@ -12225,7 +12230,7 @@
       </c>
       <c r="R80" s="15">
         <f>P80*'Data preparation'!$C$2</f>
-        <v>9.5</v>
+        <v>7.916666667</v>
       </c>
     </row>
     <row r="81">
@@ -12280,7 +12285,7 @@
       </c>
       <c r="R81" s="61">
         <f>P81*'Data preparation'!$C$2/2</f>
-        <v>9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="82">
@@ -12335,7 +12340,7 @@
       </c>
       <c r="R82" s="61">
         <f>P82*'Data preparation'!$C$2/2</f>
-        <v>8.75</v>
+        <v>7.291666667</v>
       </c>
     </row>
     <row r="83">
@@ -12390,7 +12395,7 @@
       </c>
       <c r="R83" s="15">
         <f>P83*'Data preparation'!$C$2</f>
-        <v>10</v>
+        <v>8.333333333</v>
       </c>
     </row>
     <row r="84">
@@ -12445,7 +12450,7 @@
       </c>
       <c r="R84" s="15">
         <f>P84*'Data preparation'!$C$2</f>
-        <v>15</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="94">
@@ -12622,7 +12627,7 @@
       </c>
       <c r="U99" s="15">
         <f>T99*'Data preparation'!$C$2</f>
-        <v>9.5</v>
+        <v>7.916666667</v>
       </c>
     </row>
     <row r="100">
@@ -12683,7 +12688,7 @@
       </c>
       <c r="U100" s="61">
         <f>T100*'Data preparation'!$C$2/2</f>
-        <v>9</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="101">
@@ -12744,7 +12749,7 @@
       </c>
       <c r="U101" s="61">
         <f>T101*'Data preparation'!$C$2/2</f>
-        <v>8.75</v>
+        <v>7.291666667</v>
       </c>
     </row>
     <row r="102">
@@ -12805,7 +12810,7 @@
       </c>
       <c r="U102" s="15">
         <f>T102*'Data preparation'!$C$2</f>
-        <v>13.5</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="103">
@@ -12866,7 +12871,7 @@
       </c>
       <c r="U103" s="15">
         <f>T103*'Data preparation'!$C$2</f>
-        <v>11</v>
+        <v>9.166666667</v>
       </c>
     </row>
   </sheetData>
@@ -13143,7 +13148,7 @@
         <v>84</v>
       </c>
       <c r="C2" s="19">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="L2" s="90"/>
     </row>
@@ -13154,7 +13159,7 @@
       </c>
       <c r="C3" s="15">
         <f>AVERAGE('Modelos actuales'!N4:N8)</f>
-        <v>13</v>
+        <v>10.83333333</v>
       </c>
       <c r="L3" s="90"/>
       <c r="P3" s="90"/>
@@ -14256,7 +14261,7 @@
       <c r="C37" s="34"/>
       <c r="D37" s="37">
         <f>AVERAGE(D39:D1775)</f>
-        <v>5.718823529</v>
+        <v>5.765625</v>
       </c>
       <c r="G37" s="31" t="s">
         <v>23</v>
@@ -14313,7 +14318,7 @@
       </c>
       <c r="D39" s="96">
         <f t="shared" ref="D39:D221" si="17">IF(COUNTA(C39)=1,C39/1,"")</f>
-        <v>1.15</v>
+        <v>1.42</v>
       </c>
       <c r="G39" s="31" t="s">
         <v>25</v>
@@ -14345,7 +14350,7 @@
       </c>
       <c r="D40" s="96">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="G40" s="31" t="s">
         <v>26</v>
@@ -14377,7 +14382,7 @@
       </c>
       <c r="D41" s="96">
         <f t="shared" si="17"/>
-        <v>9.75</v>
+        <v>9.04</v>
       </c>
       <c r="P41" s="93">
         <v>1.0</v>
@@ -14403,7 +14408,7 @@
       </c>
       <c r="D42" s="96">
         <f t="shared" si="17"/>
-        <v>9.37</v>
+        <v>8.68</v>
       </c>
       <c r="P42" s="93">
         <v>1.0</v>
@@ -14429,7 +14434,7 @@
       </c>
       <c r="D43" s="96">
         <f t="shared" si="17"/>
-        <v>9.8</v>
+        <v>9.08</v>
       </c>
       <c r="P43" s="93"/>
       <c r="AA43" s="36">
@@ -14453,7 +14458,7 @@
       </c>
       <c r="D44" s="96">
         <f t="shared" si="17"/>
-        <v>7.97</v>
+        <v>7.33</v>
       </c>
       <c r="P44" s="93"/>
       <c r="AB44" s="38">
@@ -14475,7 +14480,7 @@
       </c>
       <c r="D45" s="96">
         <f t="shared" si="17"/>
-        <v>8.9</v>
+        <v>8.24</v>
       </c>
       <c r="P45" s="93"/>
     </row>
@@ -14485,7 +14490,7 @@
       </c>
       <c r="D46" s="96">
         <f t="shared" si="17"/>
-        <v>7.33</v>
+        <v>6.55</v>
       </c>
       <c r="G46" s="67" t="s">
         <v>157</v>
@@ -14501,7 +14506,7 @@
       </c>
       <c r="D47" s="96">
         <f t="shared" si="17"/>
-        <v>7.98</v>
+        <v>8.69</v>
       </c>
       <c r="G47" s="72" t="s">
         <v>22</v>
@@ -14523,7 +14528,7 @@
       </c>
       <c r="D48" s="96">
         <f t="shared" si="17"/>
-        <v>5.97</v>
+        <v>6.59</v>
       </c>
       <c r="G48" s="72" t="s">
         <v>23</v>
@@ -14610,7 +14615,7 @@
       </c>
       <c r="D51" s="96">
         <f t="shared" si="17"/>
-        <v>5.79</v>
+        <v>6.42</v>
       </c>
       <c r="G51" s="72" t="s">
         <v>26</v>
@@ -14639,7 +14644,7 @@
       </c>
       <c r="D52" s="96">
         <f t="shared" si="17"/>
-        <v>5.65</v>
+        <v>6.28</v>
       </c>
       <c r="P52" s="93"/>
       <c r="AA52" s="36">
@@ -14655,7 +14660,7 @@
       </c>
       <c r="D53" s="96">
         <f t="shared" si="17"/>
-        <v>6.08</v>
+        <v>6.71</v>
       </c>
       <c r="P53" s="93"/>
       <c r="AA53" s="36">
@@ -14671,7 +14676,7 @@
       </c>
       <c r="D54" s="96">
         <f t="shared" si="17"/>
-        <v>5.75</v>
+        <v>6.38</v>
       </c>
       <c r="P54" s="93"/>
       <c r="AA54" s="36">
@@ -14687,7 +14692,7 @@
       </c>
       <c r="D55" s="96">
         <f t="shared" si="17"/>
-        <v>5.87</v>
+        <v>6.5</v>
       </c>
       <c r="P55" s="93"/>
       <c r="AA55" s="36">
@@ -14735,7 +14740,7 @@
       </c>
       <c r="D58" s="96">
         <f t="shared" si="17"/>
-        <v>11.1</v>
+        <v>16.91</v>
       </c>
       <c r="G58" s="109" t="s">
         <v>175</v>
@@ -14751,15 +14756,15 @@
     </row>
     <row r="59">
       <c r="C59" s="107" t="s">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="D59" s="96">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="G59" s="110"/>
       <c r="H59" s="111" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P59" s="93"/>
       <c r="AA59" s="32">
@@ -14771,15 +14776,15 @@
     </row>
     <row r="60">
       <c r="C60" s="107" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D60" s="96">
         <f t="shared" si="17"/>
-        <v>9.12</v>
+        <v>14.23</v>
       </c>
       <c r="G60" s="110"/>
       <c r="H60" s="111" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P60" s="93"/>
       <c r="AA60" s="36">
@@ -14791,15 +14796,15 @@
     </row>
     <row r="61">
       <c r="C61" s="107" t="s">
-        <v>152</v>
+        <v>180</v>
       </c>
       <c r="D61" s="96">
         <f t="shared" si="17"/>
-        <v>9.37</v>
+        <v>10.34</v>
       </c>
       <c r="G61" s="110"/>
       <c r="H61" s="111" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="P61" s="93"/>
       <c r="AA61" s="36">
@@ -14811,15 +14816,15 @@
     </row>
     <row r="62">
       <c r="C62" s="107" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D62" s="96">
         <f t="shared" si="17"/>
-        <v>2.26</v>
+        <v>4.57</v>
       </c>
       <c r="G62" s="110"/>
       <c r="H62" s="111" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="P62" s="93"/>
       <c r="AA62" s="36">
@@ -14831,55 +14836,55 @@
     </row>
     <row r="63">
       <c r="C63" s="107" t="s">
-        <v>182</v>
+        <v>139</v>
       </c>
       <c r="D63" s="96">
         <f t="shared" si="17"/>
-        <v>11.57</v>
+        <v>4.73</v>
       </c>
       <c r="G63" s="110"/>
       <c r="H63" s="111" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P63" s="93"/>
     </row>
     <row r="64">
       <c r="C64" s="107" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D64" s="96">
         <f t="shared" si="17"/>
-        <v>2.1</v>
+        <v>0.69</v>
       </c>
       <c r="P64" s="93"/>
     </row>
     <row r="65">
       <c r="C65" s="107" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="D65" s="96">
         <f t="shared" si="17"/>
-        <v>2.08</v>
+        <v>1.37</v>
       </c>
       <c r="P65" s="93"/>
     </row>
     <row r="66">
       <c r="C66" s="107" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D66" s="96">
         <f t="shared" si="17"/>
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
       <c r="P66" s="93"/>
     </row>
     <row r="67">
       <c r="C67" s="107" t="s">
-        <v>186</v>
+        <v>102</v>
       </c>
       <c r="D67" s="96">
         <f t="shared" si="17"/>
-        <v>1.25</v>
+        <v>3.67</v>
       </c>
       <c r="P67" s="93"/>
     </row>
@@ -14889,218 +14894,212 @@
       </c>
       <c r="D68" s="96">
         <f t="shared" si="17"/>
-        <v>1.19</v>
+        <v>3.71</v>
       </c>
       <c r="P68" s="93"/>
     </row>
     <row r="69">
       <c r="C69" s="107" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D69" s="96">
         <f t="shared" si="17"/>
-        <v>1.25</v>
+        <v>2.06</v>
       </c>
       <c r="P69" s="93"/>
     </row>
     <row r="70">
       <c r="C70" s="107" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D70" s="96">
         <f t="shared" si="17"/>
-        <v>0.01</v>
+        <v>4.48</v>
       </c>
       <c r="P70" s="93"/>
     </row>
     <row r="71">
       <c r="C71" s="107" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D71" s="96">
         <f t="shared" si="17"/>
-        <v>0.05</v>
+        <v>3.49</v>
       </c>
       <c r="F71" s="112"/>
       <c r="P71" s="93"/>
     </row>
     <row r="72">
       <c r="C72" s="107" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="D72" s="96">
         <f t="shared" si="17"/>
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="P72" s="93"/>
     </row>
     <row r="73">
       <c r="C73" s="107" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D73" s="96">
         <f t="shared" si="17"/>
-        <v>5.01</v>
+        <v>0.57</v>
       </c>
       <c r="P73" s="93"/>
     </row>
     <row r="74">
       <c r="C74" s="107" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D74" s="96">
         <f t="shared" si="17"/>
-        <v>5.09</v>
+        <v>10.77</v>
       </c>
       <c r="P74" s="93"/>
     </row>
     <row r="75">
       <c r="C75" s="107" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D75" s="96">
         <f t="shared" si="17"/>
-        <v>5</v>
+        <v>10.44</v>
       </c>
       <c r="P75" s="93"/>
     </row>
     <row r="76">
       <c r="C76" s="107" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D76" s="96">
         <f t="shared" si="17"/>
-        <v>11.21</v>
+        <v>7.8</v>
       </c>
       <c r="P76" s="93"/>
     </row>
     <row r="77">
       <c r="C77" s="107" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D77" s="96">
         <f t="shared" si="17"/>
-        <v>11.06</v>
+        <v>8.87</v>
       </c>
       <c r="P77" s="93"/>
     </row>
     <row r="78">
       <c r="C78" s="107" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D78" s="96">
         <f t="shared" si="17"/>
-        <v>12.77</v>
+        <v>3.11</v>
       </c>
       <c r="P78" s="113"/>
     </row>
     <row r="79">
       <c r="C79" s="107" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D79" s="96">
         <f t="shared" si="17"/>
-        <v>8.8</v>
+        <v>7.17</v>
       </c>
       <c r="P79" s="113"/>
     </row>
     <row r="80">
       <c r="C80" s="107" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D80" s="96">
         <f t="shared" si="17"/>
-        <v>9.18</v>
+        <v>5.37</v>
       </c>
       <c r="P80" s="113"/>
     </row>
     <row r="81">
       <c r="C81" s="107" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D81" s="96">
         <f t="shared" si="17"/>
-        <v>9.74</v>
+        <v>11.08</v>
       </c>
       <c r="P81" s="113"/>
     </row>
     <row r="82">
       <c r="C82" s="107" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D82" s="96">
         <f t="shared" si="17"/>
-        <v>5.44</v>
+        <v>5.78</v>
       </c>
       <c r="P82" s="113"/>
     </row>
     <row r="83">
       <c r="C83" s="107" t="s">
-        <v>136</v>
+        <v>202</v>
       </c>
       <c r="D83" s="96">
         <f t="shared" si="17"/>
-        <v>7.85</v>
+        <v>9.3</v>
       </c>
       <c r="P83" s="113"/>
     </row>
     <row r="84">
       <c r="C84" s="107" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="D84" s="96">
         <f t="shared" si="17"/>
-        <v>8.59</v>
+        <v>0.35</v>
       </c>
       <c r="P84" s="113"/>
     </row>
     <row r="85">
       <c r="C85" s="107" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D85" s="96">
         <f t="shared" si="17"/>
-        <v>6.42</v>
+        <v>1.74</v>
       </c>
       <c r="P85" s="113"/>
     </row>
     <row r="86">
       <c r="C86" s="107" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="D86" s="96">
         <f t="shared" si="17"/>
-        <v>2.94</v>
+        <v>2.19</v>
       </c>
       <c r="P86" s="113"/>
     </row>
     <row r="87">
-      <c r="C87" s="107" t="s">
-        <v>203</v>
-      </c>
-      <c r="D87" s="96">
+      <c r="C87" s="107"/>
+      <c r="D87" s="96" t="str">
         <f t="shared" si="17"/>
-        <v>3.62</v>
+        <v/>
       </c>
       <c r="P87" s="113"/>
     </row>
     <row r="88">
-      <c r="C88" s="107" t="s">
-        <v>204</v>
-      </c>
-      <c r="D88" s="96">
+      <c r="C88" s="107"/>
+      <c r="D88" s="96" t="str">
         <f t="shared" si="17"/>
-        <v>3.72</v>
+        <v/>
       </c>
       <c r="P88" s="113"/>
     </row>
     <row r="89">
-      <c r="C89" s="107" t="s">
-        <v>205</v>
-      </c>
-      <c r="D89" s="96">
+      <c r="C89" s="107"/>
+      <c r="D89" s="96" t="str">
         <f t="shared" si="17"/>
-        <v>4.85</v>
+        <v/>
       </c>
       <c r="P89" s="113"/>
     </row>

--- a/data/df_best_models.xlsx
+++ b/data/df_best_models.xlsx
@@ -38,31 +38,6 @@
     <comment authorId="0" ref="I4">
       <text>
         <t xml:space="preserve">el empate...</t>
-      </text>
-    </comment>
-    <comment authorId="0" ref="J4">
-      <text>
-        <t xml:space="preserve">crece gracias a doble oportunidad. en este caso de 0.45</t>
-      </text>
-    </comment>
-    <comment authorId="0" ref="L6">
-      <text>
-        <t xml:space="preserve">dp 0.45</t>
-      </text>
-    </comment>
-    <comment authorId="0" ref="J7">
-      <text>
-        <t xml:space="preserve">dp 0.55</t>
-      </text>
-    </comment>
-    <comment authorId="0" ref="J8">
-      <text>
-        <t xml:space="preserve">dp 0.45</t>
-      </text>
-    </comment>
-    <comment authorId="0" ref="L8">
-      <text>
-        <t xml:space="preserve">dp 0.7</t>
       </text>
     </comment>
     <comment authorId="0" ref="A1">
@@ -236,7 +211,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="230">
   <si>
     <t>id_country</t>
   </si>
@@ -256,12 +231,10 @@
     <t>test_accuracy</t>
   </si>
   <si>
-    <t>G/P sin bank 
-sin ea</t>
+    <t>ROI_sin_ea</t>
   </si>
   <si>
-    <t>G/P sin bank 
-con ea</t>
+    <t>ROI_con_ea</t>
   </si>
   <si>
     <t>Multiplicador ea</t>
@@ -319,6 +292,9 @@
   </si>
   <si>
     <t>SPA</t>
+  </si>
+  <si>
+    <t>Cambiaron por: 1) sacar dp? 2) Seleccionar modelo segun todo sin bank o por que?</t>
   </si>
   <si>
     <t>deberia cambiar el modelo en: ENG y en SPA</t>
@@ -693,28 +669,28 @@
     <t>Stake promedio</t>
   </si>
   <si>
-    <t>1.40</t>
+    <t>1.87</t>
   </si>
   <si>
-    <t>0.99</t>
+    <t>0.15</t>
   </si>
   <si>
-    <t>9.03</t>
+    <t>0.10</t>
   </si>
   <si>
-    <t>8.73</t>
+    <t>0.74</t>
   </si>
   <si>
-    <t>9.07</t>
+    <t>0.42</t>
   </si>
   <si>
-    <t>7.34</t>
+    <t>7.47</t>
   </si>
   <si>
-    <t>8.24</t>
+    <t>7.63</t>
   </si>
   <si>
-    <t>6.55</t>
+    <t>8.19</t>
   </si>
   <si>
     <t>Country</t>
@@ -723,10 +699,10 @@
     <t>Correl ROI y Expected ROI</t>
   </si>
   <si>
-    <t>8.66</t>
+    <t>8.59</t>
   </si>
   <si>
-    <t>6.47</t>
+    <t>6.88</t>
   </si>
   <si>
     <t>mean</t>
@@ -738,7 +714,7 @@
     <t>median</t>
   </si>
   <si>
-    <t>7.76</t>
+    <t>8.02</t>
   </si>
   <si>
     <t>p25</t>
@@ -750,13 +726,13 @@
     <t>p75</t>
   </si>
   <si>
-    <t>6.28</t>
+    <t>6.35</t>
   </si>
   <si>
-    <t>6.71</t>
+    <t>6.77</t>
   </si>
   <si>
-    <t>6.38</t>
+    <t>6.44</t>
   </si>
   <si>
     <t>6.50</t>
@@ -765,10 +741,10 @@
     <t>2.08</t>
   </si>
   <si>
-    <t>2.22</t>
+    <t>2.11</t>
   </si>
   <si>
-    <t>9.93</t>
+    <t>9.79</t>
   </si>
   <si>
     <t>Gracias a las nuevas métricas de G/P sin bank en test, me di cuenta de que:</t>
@@ -780,19 +756,19 @@
     <t>La rentabilidad en ITA está en el visitante y no en el empate como creía.</t>
   </si>
   <si>
-    <t>7.87</t>
+    <t>8.62</t>
   </si>
   <si>
     <t>La rentabilidad en ENG y GER está en el empate tal como creía.</t>
   </si>
   <si>
-    <t>8.12</t>
+    <t>8.96</t>
   </si>
   <si>
     <t>En SPA esta repartido aunque Empate saca una ventaja.</t>
   </si>
   <si>
-    <t>1.52</t>
+    <t>1.56</t>
   </si>
   <si>
     <t>En FRA, depende el modelo. A veces local, a veces, empate.</t>
@@ -804,64 +780,70 @@
     <t>Si en FRA empate no rinde, no tiene sentido exigirle una buena distrib en empate… → Tiene sentido pero al parecer si importa el empate puesto que el modelo que gana se basa en empate.</t>
   </si>
   <si>
-    <t>4.13</t>
-  </si>
-  <si>
-    <t>0.44</t>
-  </si>
-  <si>
-    <t>4.02</t>
+    <t>1.65</t>
   </si>
   <si>
     <t>2.05</t>
   </si>
   <si>
-    <t>1.55</t>
+    <t>1.90</t>
   </si>
   <si>
-    <t>0.23</t>
+    <t>5.60</t>
   </si>
   <si>
-    <t>0.28</t>
+    <t>1.00</t>
   </si>
   <si>
-    <t>4.84</t>
+    <t>1.24</t>
   </si>
   <si>
-    <t>5.00</t>
+    <t>3.38</t>
   </si>
   <si>
-    <t>10.04</t>
+    <t>6.48</t>
   </si>
   <si>
-    <t>9.79</t>
+    <t>6.96</t>
   </si>
   <si>
-    <t>11.52</t>
+    <t>3.53</t>
   </si>
   <si>
-    <t>0.50</t>
+    <t>4.04</t>
   </si>
   <si>
-    <t>7.63</t>
+    <t>5.12</t>
   </si>
   <si>
-    <t>1.35</t>
+    <t>4.35</t>
   </si>
   <si>
-    <t>7.46</t>
+    <t>1.20</t>
   </si>
   <si>
-    <t>9.85</t>
+    <t>3.69</t>
   </si>
   <si>
-    <t>1.75</t>
+    <t>0.68</t>
   </si>
   <si>
-    <t>0.64</t>
+    <t>10.90</t>
   </si>
   <si>
-    <t>1.95</t>
+    <t>1.13</t>
+  </si>
+  <si>
+    <t>2.16</t>
+  </si>
+  <si>
+    <t>1.98</t>
+  </si>
+  <si>
+    <t>1.52</t>
+  </si>
+  <si>
+    <t>2.17</t>
   </si>
   <si>
     <t>RENTABILIDAD</t>
@@ -1932,7 +1914,7 @@
       <c r="O1" s="8"/>
       <c r="P1" s="9"/>
     </row>
-    <row r="2" ht="39.0" customHeight="1">
+    <row r="2" ht="39.0" hidden="1" customHeight="1">
       <c r="A2" s="10">
         <v>6.0</v>
       </c>
@@ -1975,7 +1957,7 @@
       <c r="O2" s="19"/>
       <c r="P2" s="20"/>
     </row>
-    <row r="3">
+    <row r="3" hidden="1">
       <c r="A3" s="21">
         <v>167.0</v>
       </c>
@@ -2008,26 +1990,26 @@
         <v>45679.0</v>
       </c>
       <c r="D4" s="14">
-        <v>343.0</v>
+        <v>395.0</v>
       </c>
       <c r="E4" s="14" t="s">
         <v>15</v>
       </c>
       <c r="F4" s="15">
-        <v>55.4545454545454</v>
+        <v>56.3636363636363</v>
       </c>
       <c r="G4" s="15">
-        <v>151.075582383826</v>
+        <v>266.829530869996</v>
       </c>
       <c r="H4" s="15">
-        <v>1170.81137331263</v>
+        <v>10540.9503330339</v>
       </c>
       <c r="I4" s="16">
         <f t="shared" ref="I4:I8" si="1">H4/G4</f>
-        <v>7.749838557</v>
+        <v>39.50443678</v>
       </c>
       <c r="J4" s="17">
-        <v>45.0</v>
+        <v>10.0</v>
       </c>
       <c r="K4" s="17">
         <v>45.0</v>
@@ -2037,11 +2019,11 @@
       </c>
       <c r="M4" s="16">
         <f t="shared" ref="M4:M8" si="2">AVERAGE(J4:L4)</f>
-        <v>45</v>
+        <v>33.33333333</v>
       </c>
       <c r="N4" s="23">
         <f>M4*'Data preparation'!$C$2</f>
-        <v>11.25</v>
+        <v>8.333333333</v>
       </c>
     </row>
     <row r="5">
@@ -2064,14 +2046,14 @@
         <v>57.7981651376146</v>
       </c>
       <c r="G5" s="15">
-        <v>148.784087751072</v>
+        <v>265.483623313594</v>
       </c>
       <c r="H5" s="15">
-        <v>1017.94254308676</v>
+        <v>8764.30228233083</v>
       </c>
       <c r="I5" s="16">
         <f t="shared" si="1"/>
-        <v>6.841743351</v>
+        <v>33.01259103</v>
       </c>
       <c r="J5" s="15">
         <v>70.0</v>
@@ -2112,14 +2094,14 @@
         <v>62.3853211009174</v>
       </c>
       <c r="G6" s="15">
-        <v>223.51380979724</v>
+        <v>620.745751732881</v>
       </c>
       <c r="H6" s="29">
-        <v>1767.19401451423</v>
+        <v>235388.618048197</v>
       </c>
       <c r="I6" s="16">
         <f t="shared" si="1"/>
-        <v>7.906419814</v>
+        <v>379.2029464</v>
       </c>
       <c r="J6" s="15">
         <v>70.0</v>
@@ -2128,15 +2110,15 @@
         <v>70.0</v>
       </c>
       <c r="L6" s="15">
-        <v>25.0</v>
+        <v>10.0</v>
       </c>
       <c r="M6" s="16">
         <f t="shared" si="2"/>
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="N6" s="23">
         <f>M6*'Data preparation'!$C$2</f>
-        <v>13.75</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="7">
@@ -2150,26 +2132,26 @@
         <v>45677.0</v>
       </c>
       <c r="D7" s="14">
-        <v>1658.0</v>
+        <v>1623.0</v>
       </c>
       <c r="E7" s="14" t="s">
         <v>15</v>
       </c>
       <c r="F7" s="15">
-        <v>59.090909090909</v>
+        <v>60.0</v>
       </c>
       <c r="G7" s="15">
-        <v>138.271334532167</v>
+        <v>259.814577663094</v>
       </c>
       <c r="H7" s="15">
-        <v>1187.20111909535</v>
+        <v>26440.0274640769</v>
       </c>
       <c r="I7" s="16">
         <f t="shared" si="1"/>
-        <v>8.586024884</v>
+        <v>101.7649883</v>
       </c>
       <c r="J7" s="17">
-        <v>25.0</v>
+        <v>10.0</v>
       </c>
       <c r="K7" s="17">
         <v>70.0</v>
@@ -2179,11 +2161,11 @@
       </c>
       <c r="M7" s="24">
         <f t="shared" si="2"/>
-        <v>46.66666667</v>
+        <v>41.66666667</v>
       </c>
       <c r="N7" s="23">
         <f>M7*'Data preparation'!$C$2</f>
-        <v>11.66666667</v>
+        <v>10.41666667</v>
       </c>
     </row>
     <row r="8">
@@ -2197,40 +2179,40 @@
         <v>45677.0</v>
       </c>
       <c r="D8" s="14">
-        <v>1545.0</v>
+        <v>112.0</v>
       </c>
       <c r="E8" s="14" t="s">
         <v>15</v>
       </c>
       <c r="F8" s="15">
-        <v>54.5454545454545</v>
+        <v>57.2727272727272</v>
       </c>
       <c r="G8" s="15">
-        <v>83.1939735526323</v>
+        <v>148.175027775313</v>
       </c>
       <c r="H8" s="15">
-        <v>1139.23923226552</v>
+        <v>14775.5109669633</v>
       </c>
       <c r="I8" s="16">
         <f t="shared" si="1"/>
-        <v>13.69377112</v>
+        <v>99.7166067</v>
       </c>
       <c r="J8" s="17">
-        <v>70.0</v>
+        <v>45.0</v>
       </c>
       <c r="K8" s="17">
         <v>70.0</v>
       </c>
       <c r="L8" s="17">
-        <v>45.0</v>
+        <v>10.0</v>
       </c>
       <c r="M8" s="24">
         <f t="shared" si="2"/>
-        <v>61.66666667</v>
+        <v>41.66666667</v>
       </c>
       <c r="N8" s="23">
         <f>M8*'Data preparation'!$C$2</f>
-        <v>15.41666667</v>
+        <v>10.41666667</v>
       </c>
     </row>
     <row r="9" ht="20.25" customHeight="1">
@@ -2259,23 +2241,8 @@
       <c r="A13" s="33"/>
       <c r="F13" s="34"/>
     </row>
-    <row r="15">
-      <c r="C15" s="35"/>
-    </row>
-    <row r="16">
-      <c r="C16" s="35"/>
-    </row>
-    <row r="17">
-      <c r="C17" s="35"/>
-    </row>
-    <row r="18">
-      <c r="C18" s="35"/>
-    </row>
     <row r="19">
       <c r="C19" s="35"/>
-    </row>
-    <row r="20">
-      <c r="C20" s="35"/>
     </row>
     <row r="27">
       <c r="A27" s="33"/>
@@ -9259,6 +9226,11 @@
       <c r="E26" s="31"/>
       <c r="F26" s="31"/>
     </row>
+    <row r="30">
+      <c r="D30" s="37" t="s">
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -9540,13 +9512,13 @@
     </row>
     <row r="11">
       <c r="E11" s="49" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L11" s="37" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M11" s="44" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N11" s="50" t="s">
         <v>26</v>
@@ -9556,10 +9528,10 @@
     </row>
     <row r="12">
       <c r="E12" s="49" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L12" s="37" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M12" s="44" t="s">
         <v>24</v>
@@ -9821,12 +9793,12 @@
     </row>
     <row r="24">
       <c r="C24" s="36" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25">
       <c r="C25" s="47" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26">
@@ -9836,22 +9808,22 @@
     </row>
     <row r="27">
       <c r="C27" s="55" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28">
       <c r="C28" s="53" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30">
       <c r="C30" s="34" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="31">
       <c r="C31" s="36" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L31" s="36" t="s">
         <v>25</v>
@@ -11843,7 +11815,7 @@
     </row>
     <row r="63">
       <c r="C63" s="36" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="65">
@@ -11863,19 +11835,19 @@
         <v>4</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J65" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K65" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L65" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M65" s="65" t="s">
         <v>8</v>
@@ -12146,7 +12118,7 @@
     </row>
     <row r="76">
       <c r="C76" s="36" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="77">
@@ -12166,16 +12138,16 @@
         <v>4</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J77" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K77" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L77" s="4" t="s">
         <v>9</v>
@@ -12520,7 +12492,7 @@
     </row>
     <row r="94">
       <c r="C94" s="37" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="96">
@@ -12543,25 +12515,25 @@
         <v>5</v>
       </c>
       <c r="I96" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J96" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K96" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L96" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M96" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N96" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O96" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="P96" s="65" t="s">
         <v>8</v>
@@ -13003,146 +12975,146 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="37" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2">
       <c r="B2" s="8"/>
       <c r="C2" s="72" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E2" s="73"/>
       <c r="F2" s="74" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H2" s="73"/>
     </row>
     <row r="3">
       <c r="B3" s="75" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C3" s="76" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D3" s="75" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E3" s="77" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F3" s="75" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G3" s="75" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H3" s="75" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="78" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C4" s="79" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D4" s="80" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E4" s="81" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F4" s="82" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G4" s="82" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H4" s="80"/>
     </row>
     <row r="5">
       <c r="B5" s="78" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C5" s="83" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D5" s="84"/>
       <c r="E5" s="81" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F5" s="85" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G5" s="86" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H5" s="80"/>
     </row>
     <row r="6">
       <c r="B6" s="78" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C6" s="79" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D6" s="80" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E6" s="81" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F6" s="80" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G6" s="80"/>
       <c r="H6" s="80"/>
     </row>
     <row r="7">
       <c r="B7" s="80" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C7" s="87" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D7" s="80"/>
       <c r="E7" s="88" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F7" s="79" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G7" s="80"/>
       <c r="H7" s="80" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="89" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C8" s="90" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D8" s="91"/>
       <c r="E8" s="89" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F8" s="92" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G8" s="93" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H8" s="91"/>
     </row>
     <row r="9">
       <c r="B9" s="21" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C9" s="94" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D9" s="95"/>
       <c r="E9" s="95"/>
@@ -13152,27 +13124,27 @@
     </row>
     <row r="10">
       <c r="B10" s="21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C10" s="96"/>
       <c r="D10" s="95"/>
       <c r="E10" s="95"/>
       <c r="F10" s="96"/>
       <c r="G10" s="82" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H10" s="95"/>
     </row>
     <row r="11">
       <c r="B11" s="21" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C11" s="96"/>
       <c r="D11" s="95"/>
       <c r="E11" s="95"/>
       <c r="F11" s="96"/>
       <c r="G11" s="97" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H11" s="21"/>
     </row>
@@ -13210,7 +13182,7 @@
     <row r="2">
       <c r="A2" s="17"/>
       <c r="B2" s="74" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C2" s="17">
         <v>0.25</v>
@@ -13220,11 +13192,11 @@
     <row r="3">
       <c r="A3" s="17"/>
       <c r="B3" s="74" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C3" s="22">
         <f>AVERAGE('Modelos actuales'!N4:N8)</f>
-        <v>12.75</v>
+        <v>10.66666667</v>
       </c>
       <c r="L3" s="98"/>
       <c r="P3" s="98"/>
@@ -13238,44 +13210,44 @@
     <row r="5">
       <c r="A5" s="17"/>
       <c r="B5" s="98" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L5" s="98" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P5" s="98" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17"/>
       <c r="B6" s="37" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F6" s="37" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K6" s="36"/>
       <c r="L6" s="36" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N6" s="36" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P6" s="36" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="R6" s="36" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="V6" s="36" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AA6" s="37" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AB6" s="37" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7">
@@ -13311,7 +13283,7 @@
         <v>-0.6666666667</v>
       </c>
       <c r="AA7" s="37" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AB7" s="43">
         <f t="shared" ref="AB7:AB16" si="4">LEFT(REPLACE(AA7,1,1,""),FIND(",", AA7)-2)/1</f>
@@ -13321,14 +13293,14 @@
     <row r="8">
       <c r="A8" s="17"/>
       <c r="B8" s="103" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C8" s="104" t="str">
         <f t="shared" ref="C8:C17" si="5">REPLACE(B8,FIND(".",B8),1,",")*1</f>
         <v>#VALUE!</v>
       </c>
       <c r="F8" s="47" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G8" s="104" t="str">
         <f t="shared" ref="G8:G27" si="6">REPLACE(F8,FIND(".",F8),1,",")*1</f>
@@ -13363,7 +13335,7 @@
         <v>-0.3157894737</v>
       </c>
       <c r="AA8" s="37" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AB8" s="43">
         <f t="shared" si="4"/>
@@ -13373,14 +13345,14 @@
     <row r="9">
       <c r="A9" s="17"/>
       <c r="B9" s="103" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C9" s="104" t="str">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="F9" s="47" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G9" s="104" t="str">
         <f t="shared" si="6"/>
@@ -13394,13 +13366,13 @@
       </c>
       <c r="K9" s="17"/>
       <c r="L9" s="99" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M9" s="99" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N9" s="36" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P9" s="101">
         <v>0.0</v>
@@ -13424,7 +13396,7 @@
         <v>-0.5</v>
       </c>
       <c r="AA9" s="37" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AB9" s="43">
         <f t="shared" si="4"/>
@@ -13434,14 +13406,14 @@
     <row r="10">
       <c r="A10" s="17"/>
       <c r="B10" s="105" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C10" s="104" t="str">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="F10" s="47" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G10" s="104" t="str">
         <f t="shared" si="6"/>
@@ -13478,7 +13450,7 @@
         <v>76</v>
       </c>
       <c r="AA10" s="37" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AB10" s="43">
         <f t="shared" si="4"/>
@@ -13487,14 +13459,14 @@
     </row>
     <row r="11">
       <c r="B11" s="103" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C11" s="104" t="str">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="F11" s="47" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G11" s="104" t="str">
         <f t="shared" si="6"/>
@@ -13523,7 +13495,7 @@
         <v>0.0</v>
       </c>
       <c r="AA11" s="37" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AB11" s="43">
         <f t="shared" si="4"/>
@@ -13532,14 +13504,14 @@
     </row>
     <row r="12">
       <c r="B12" s="105" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C12" s="104" t="str">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="F12" s="47" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G12" s="104" t="str">
         <f t="shared" si="6"/>
@@ -13568,7 +13540,7 @@
         <v>2.0</v>
       </c>
       <c r="AA12" s="37" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AB12" s="43">
         <f t="shared" si="4"/>
@@ -13577,14 +13549,14 @@
     </row>
     <row r="13">
       <c r="B13" s="103" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C13" s="104" t="str">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="F13" s="47" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G13" s="104" t="str">
         <f t="shared" si="6"/>
@@ -13614,16 +13586,16 @@
       <c r="Q13" s="39"/>
       <c r="R13" s="95"/>
       <c r="S13" s="106" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="T13" s="106" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="U13" s="106" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AA13" s="37" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AB13" s="43">
         <f t="shared" si="4"/>
@@ -13632,14 +13604,14 @@
     </row>
     <row r="14">
       <c r="B14" s="103" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C14" s="104" t="str">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="F14" s="47" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G14" s="104" t="str">
         <f t="shared" si="6"/>
@@ -13679,7 +13651,7 @@
         <v>11.0</v>
       </c>
       <c r="AA14" s="37" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AB14" s="43">
         <f t="shared" si="4"/>
@@ -13688,14 +13660,14 @@
     </row>
     <row r="15">
       <c r="B15" s="103" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C15" s="104" t="str">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="F15" s="47" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G15" s="104" t="str">
         <f t="shared" si="6"/>
@@ -13735,7 +13707,7 @@
         <v>13.0</v>
       </c>
       <c r="AA15" s="37" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AB15" s="43">
         <f t="shared" si="4"/>
@@ -13744,14 +13716,14 @@
     </row>
     <row r="16">
       <c r="B16" s="103" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C16" s="104" t="str">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="F16" s="47" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G16" s="104" t="str">
         <f t="shared" si="6"/>
@@ -13791,7 +13763,7 @@
         <v>12.0</v>
       </c>
       <c r="AA16" s="37" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AB16" s="43">
         <f t="shared" si="4"/>
@@ -13800,14 +13772,14 @@
     </row>
     <row r="17">
       <c r="B17" s="103" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C17" s="104" t="str">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="F17" s="47" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G17" s="104" t="str">
         <f t="shared" si="6"/>
@@ -13835,7 +13807,7 @@
         <v>0.0</v>
       </c>
       <c r="R17" s="106" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="S17" s="107">
         <f t="shared" ref="S17:U17" si="10">SUM(S14:S16)</f>
@@ -13852,7 +13824,7 @@
     </row>
     <row r="18">
       <c r="F18" s="47" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G18" s="104" t="str">
         <f t="shared" si="6"/>
@@ -13883,14 +13855,14 @@
     </row>
     <row r="19">
       <c r="B19" s="36" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C19" s="43" t="str">
         <f>AVERAGE(C8:C17)</f>
         <v>#VALUE!</v>
       </c>
       <c r="F19" s="47" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G19" s="104" t="str">
         <f t="shared" si="6"/>
@@ -13918,7 +13890,7 @@
       <c r="T19" s="19"/>
       <c r="U19" s="19"/>
       <c r="AA19" s="37" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AB19" s="43">
         <f>AVERAGE(AB7:AB16)</f>
@@ -13927,7 +13899,7 @@
     </row>
     <row r="20">
       <c r="F20" s="47" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G20" s="104" t="str">
         <f t="shared" si="6"/>
@@ -13946,7 +13918,7 @@
     </row>
     <row r="21">
       <c r="F21" s="47" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G21" s="104" t="str">
         <f t="shared" si="6"/>
@@ -13960,19 +13932,19 @@
       </c>
       <c r="R21" s="95"/>
       <c r="S21" s="106" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="T21" s="106" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="U21" s="106" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="22">
       <c r="C22" s="104"/>
       <c r="F22" s="47" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G22" s="104" t="str">
         <f t="shared" si="6"/>
@@ -14033,7 +14005,7 @@
     </row>
     <row r="24">
       <c r="F24" s="47" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G24" s="104" t="str">
         <f t="shared" si="6"/>
@@ -14063,7 +14035,7 @@
     </row>
     <row r="25">
       <c r="F25" s="47" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G25" s="104" t="str">
         <f t="shared" si="6"/>
@@ -14076,7 +14048,7 @@
         <v>1.0</v>
       </c>
       <c r="R25" s="106" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="S25" s="107">
         <f t="shared" ref="S25:U25" si="14">SUM(S22:S24)</f>
@@ -14093,7 +14065,7 @@
     </row>
     <row r="26">
       <c r="F26" s="47" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G26" s="104" t="str">
         <f t="shared" si="6"/>
@@ -14126,18 +14098,18 @@
         <v>1.0</v>
       </c>
       <c r="AA28" s="37" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AB28" s="37" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AC28" s="37" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="29">
       <c r="F29" s="36" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G29" s="43" t="str">
         <f>AVERAGE(G8:G27)</f>
@@ -14210,7 +14182,7 @@
     </row>
     <row r="32">
       <c r="B32" s="53" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G32" s="104"/>
       <c r="P32" s="101">
@@ -14233,7 +14205,7 @@
     </row>
     <row r="33">
       <c r="B33" s="110" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G33" s="111"/>
       <c r="P33" s="101">
@@ -14275,7 +14247,7 @@
     </row>
     <row r="35">
       <c r="H35" s="36" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P35" s="101">
         <v>0.0</v>
@@ -14326,7 +14298,7 @@
       <c r="C37" s="39"/>
       <c r="D37" s="42">
         <f>AVERAGE(D39:D1775)</f>
-        <v>5.33375</v>
+        <v>4.455625</v>
       </c>
       <c r="G37" s="36" t="s">
         <v>23</v>
@@ -14379,11 +14351,11 @@
     </row>
     <row r="39">
       <c r="C39" s="114" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D39" s="104">
         <f t="shared" ref="D39:D221" si="17">IF(COUNTA(C39)=1,C39/1,"")</f>
-        <v>1.4</v>
+        <v>1.87</v>
       </c>
       <c r="G39" s="36" t="s">
         <v>25</v>
@@ -14411,11 +14383,11 @@
     </row>
     <row r="40">
       <c r="C40" s="115" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D40" s="104">
         <f t="shared" si="17"/>
-        <v>0.99</v>
+        <v>0.15</v>
       </c>
       <c r="G40" s="36" t="s">
         <v>26</v>
@@ -14443,11 +14415,11 @@
     </row>
     <row r="41">
       <c r="C41" s="115" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D41" s="104">
         <f t="shared" si="17"/>
-        <v>9.03</v>
+        <v>0.1</v>
       </c>
       <c r="P41" s="101">
         <v>1.0</v>
@@ -14469,11 +14441,11 @@
     </row>
     <row r="42">
       <c r="C42" s="115" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D42" s="104">
         <f t="shared" si="17"/>
-        <v>8.73</v>
+        <v>0.74</v>
       </c>
       <c r="P42" s="101">
         <v>1.0</v>
@@ -14495,11 +14467,11 @@
     </row>
     <row r="43">
       <c r="C43" s="115" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D43" s="104">
         <f t="shared" si="17"/>
-        <v>9.07</v>
+        <v>0.42</v>
       </c>
       <c r="P43" s="101"/>
       <c r="AA43" s="41">
@@ -14519,11 +14491,11 @@
     </row>
     <row r="44">
       <c r="C44" s="115" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D44" s="104">
         <f t="shared" si="17"/>
-        <v>7.34</v>
+        <v>7.47</v>
       </c>
       <c r="P44" s="101"/>
       <c r="AB44" s="43">
@@ -14541,37 +14513,37 @@
     </row>
     <row r="45">
       <c r="C45" s="115" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D45" s="104">
         <f t="shared" si="17"/>
-        <v>8.24</v>
+        <v>7.63</v>
       </c>
       <c r="P45" s="101"/>
     </row>
     <row r="46">
       <c r="C46" s="115" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D46" s="104">
         <f t="shared" si="17"/>
-        <v>6.55</v>
+        <v>8.19</v>
       </c>
       <c r="G46" s="75" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H46" s="75" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P46" s="101"/>
     </row>
     <row r="47">
       <c r="C47" s="115" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D47" s="104">
         <f t="shared" si="17"/>
-        <v>8.66</v>
+        <v>8.59</v>
       </c>
       <c r="G47" s="80" t="s">
         <v>22</v>
@@ -14584,16 +14556,16 @@
         <v>3</v>
       </c>
       <c r="AB47" s="37" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="48">
       <c r="C48" s="115" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D48" s="104">
         <f t="shared" si="17"/>
-        <v>6.47</v>
+        <v>6.88</v>
       </c>
       <c r="G48" s="80" t="s">
         <v>23</v>
@@ -14602,7 +14574,7 @@
         <v>0.36678739680281</v>
       </c>
       <c r="J48" s="37" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K48" s="102">
         <f>AVERAGE(H47:H51)</f>
@@ -14618,7 +14590,7 @@
     </row>
     <row r="49">
       <c r="C49" s="115" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D49" s="104">
         <f t="shared" si="17"/>
@@ -14631,7 +14603,7 @@
         <v>0.142870351877935</v>
       </c>
       <c r="J49" s="37" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K49" s="102">
         <f>MEDIAN(H47:H51)</f>
@@ -14647,11 +14619,11 @@
     </row>
     <row r="50">
       <c r="C50" s="115" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D50" s="104">
         <f t="shared" si="17"/>
-        <v>7.76</v>
+        <v>8.02</v>
       </c>
       <c r="G50" s="80" t="s">
         <v>25</v>
@@ -14660,7 +14632,7 @@
         <v>0.497437843674554</v>
       </c>
       <c r="J50" s="37" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K50" s="102">
         <f>PERCENTILE(H47:H51,0.25)</f>
@@ -14676,7 +14648,7 @@
     </row>
     <row r="51">
       <c r="C51" s="115" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D51" s="104">
         <f t="shared" si="17"/>
@@ -14689,7 +14661,7 @@
         <v>0.247446036291655</v>
       </c>
       <c r="J51" s="37" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K51" s="102">
         <f>PERCENTILE(H47:H51,0.75)</f>
@@ -14705,11 +14677,11 @@
     </row>
     <row r="52">
       <c r="C52" s="115" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D52" s="104">
         <f t="shared" si="17"/>
-        <v>6.28</v>
+        <v>6.35</v>
       </c>
       <c r="P52" s="101"/>
       <c r="AA52" s="41">
@@ -14721,11 +14693,11 @@
     </row>
     <row r="53">
       <c r="C53" s="115" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D53" s="104">
         <f t="shared" si="17"/>
-        <v>6.71</v>
+        <v>6.77</v>
       </c>
       <c r="P53" s="101"/>
       <c r="AA53" s="41">
@@ -14737,11 +14709,11 @@
     </row>
     <row r="54">
       <c r="C54" s="115" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D54" s="104">
         <f t="shared" si="17"/>
-        <v>6.38</v>
+        <v>6.44</v>
       </c>
       <c r="P54" s="101"/>
       <c r="AA54" s="41">
@@ -14753,7 +14725,7 @@
     </row>
     <row r="55">
       <c r="C55" s="115" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D55" s="104">
         <f t="shared" si="17"/>
@@ -14769,7 +14741,7 @@
     </row>
     <row r="56">
       <c r="C56" s="115" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D56" s="104">
         <f t="shared" si="17"/>
@@ -14785,11 +14757,11 @@
     </row>
     <row r="57">
       <c r="C57" s="115" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D57" s="104">
         <f t="shared" si="17"/>
-        <v>2.22</v>
+        <v>2.11</v>
       </c>
       <c r="P57" s="101"/>
       <c r="AA57" s="37">
@@ -14801,14 +14773,14 @@
     </row>
     <row r="58">
       <c r="C58" s="115" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D58" s="104">
         <f t="shared" si="17"/>
-        <v>9.93</v>
+        <v>9.79</v>
       </c>
       <c r="G58" s="117" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H58" s="118"/>
       <c r="P58" s="101"/>
@@ -14821,7 +14793,7 @@
     </row>
     <row r="59">
       <c r="C59" s="115" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D59" s="104">
         <f t="shared" si="17"/>
@@ -14829,7 +14801,7 @@
       </c>
       <c r="G59" s="118"/>
       <c r="H59" s="119" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P59" s="101"/>
       <c r="AA59" s="37">
@@ -14841,15 +14813,15 @@
     </row>
     <row r="60">
       <c r="C60" s="115" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D60" s="104">
         <f t="shared" si="17"/>
-        <v>7.87</v>
+        <v>8.62</v>
       </c>
       <c r="G60" s="118"/>
       <c r="H60" s="119" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P60" s="101"/>
       <c r="AA60" s="41">
@@ -14861,15 +14833,15 @@
     </row>
     <row r="61">
       <c r="C61" s="115" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D61" s="104">
         <f t="shared" si="17"/>
-        <v>8.12</v>
+        <v>8.96</v>
       </c>
       <c r="G61" s="118"/>
       <c r="H61" s="119" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="P61" s="101"/>
       <c r="AA61" s="41">
@@ -14881,15 +14853,15 @@
     </row>
     <row r="62">
       <c r="C62" s="115" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D62" s="104">
         <f t="shared" si="17"/>
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="G62" s="118"/>
       <c r="H62" s="119" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P62" s="101"/>
       <c r="AA62" s="41">
@@ -14901,7 +14873,7 @@
     </row>
     <row r="63">
       <c r="C63" s="115" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D63" s="104">
         <f t="shared" si="17"/>
@@ -14909,238 +14881,238 @@
       </c>
       <c r="G63" s="118"/>
       <c r="H63" s="119" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P63" s="101"/>
     </row>
     <row r="64">
       <c r="C64" s="115" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D64" s="104">
         <f t="shared" si="17"/>
-        <v>4.13</v>
+        <v>1.65</v>
       </c>
       <c r="P64" s="101"/>
     </row>
     <row r="65">
       <c r="C65" s="115" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D65" s="104">
         <f t="shared" si="17"/>
-        <v>0.44</v>
+        <v>2.05</v>
       </c>
       <c r="P65" s="101"/>
     </row>
     <row r="66">
       <c r="C66" s="115" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D66" s="104">
         <f t="shared" si="17"/>
-        <v>4.02</v>
+        <v>1.9</v>
       </c>
       <c r="P66" s="101"/>
     </row>
     <row r="67">
       <c r="C67" s="115" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D67" s="104">
         <f t="shared" si="17"/>
-        <v>2.05</v>
+        <v>5.6</v>
       </c>
       <c r="P67" s="101"/>
     </row>
     <row r="68">
       <c r="C68" s="115" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D68" s="104">
         <f t="shared" si="17"/>
-        <v>1.55</v>
+        <v>1</v>
       </c>
       <c r="P68" s="101"/>
     </row>
     <row r="69">
       <c r="C69" s="115" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D69" s="104">
         <f t="shared" si="17"/>
-        <v>0.23</v>
+        <v>1.24</v>
       </c>
       <c r="P69" s="101"/>
     </row>
     <row r="70">
       <c r="C70" s="115" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="D70" s="104">
         <f t="shared" si="17"/>
-        <v>0.44</v>
+        <v>3.38</v>
       </c>
       <c r="P70" s="101"/>
     </row>
     <row r="71">
       <c r="C71" s="115" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D71" s="104">
         <f t="shared" si="17"/>
-        <v>0.28</v>
+        <v>6.48</v>
       </c>
       <c r="F71" s="120"/>
       <c r="P71" s="101"/>
     </row>
     <row r="72">
       <c r="C72" s="115" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D72" s="104">
         <f t="shared" si="17"/>
-        <v>4.84</v>
+        <v>6.96</v>
       </c>
       <c r="P72" s="101"/>
     </row>
     <row r="73">
       <c r="C73" s="115" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D73" s="104">
         <f t="shared" si="17"/>
-        <v>5</v>
+        <v>3.53</v>
       </c>
       <c r="P73" s="101"/>
     </row>
     <row r="74">
       <c r="C74" s="115" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D74" s="104">
         <f t="shared" si="17"/>
-        <v>10.04</v>
+        <v>4.04</v>
       </c>
       <c r="P74" s="101"/>
     </row>
     <row r="75">
       <c r="C75" s="115" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D75" s="104">
         <f t="shared" si="17"/>
-        <v>9.79</v>
+        <v>5.12</v>
       </c>
       <c r="P75" s="101"/>
     </row>
     <row r="76">
       <c r="C76" s="115" t="s">
-        <v>199</v>
+        <v>171</v>
       </c>
       <c r="D76" s="104">
         <f t="shared" si="17"/>
-        <v>11.52</v>
+        <v>6.35</v>
       </c>
       <c r="P76" s="101"/>
     </row>
     <row r="77">
       <c r="C77" s="115" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D77" s="104">
         <f t="shared" si="17"/>
-        <v>0.5</v>
+        <v>4.35</v>
       </c>
       <c r="P77" s="101"/>
     </row>
     <row r="78">
       <c r="C78" s="115" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D78" s="104">
         <f t="shared" si="17"/>
-        <v>7.63</v>
+        <v>1.2</v>
       </c>
       <c r="P78" s="121"/>
     </row>
     <row r="79">
       <c r="C79" s="115" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D79" s="104">
         <f t="shared" si="17"/>
-        <v>1.35</v>
+        <v>3.69</v>
       </c>
       <c r="P79" s="121"/>
     </row>
     <row r="80">
       <c r="C80" s="115" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D80" s="104">
         <f t="shared" si="17"/>
-        <v>7.46</v>
+        <v>0.68</v>
       </c>
       <c r="P80" s="121"/>
     </row>
     <row r="81">
       <c r="C81" s="115" t="s">
-        <v>114</v>
+        <v>205</v>
       </c>
       <c r="D81" s="104">
         <f t="shared" si="17"/>
-        <v>3.83</v>
+        <v>10.9</v>
       </c>
       <c r="P81" s="121"/>
     </row>
     <row r="82">
       <c r="C82" s="115" t="s">
-        <v>125</v>
+        <v>206</v>
       </c>
       <c r="D82" s="104">
         <f t="shared" si="17"/>
-        <v>9.33</v>
+        <v>1.13</v>
       </c>
       <c r="P82" s="121"/>
     </row>
     <row r="83">
       <c r="C83" s="115" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="D83" s="104">
         <f t="shared" si="17"/>
-        <v>9.85</v>
+        <v>2.16</v>
       </c>
       <c r="P83" s="121"/>
     </row>
     <row r="84">
       <c r="C84" s="115" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="D84" s="104">
         <f t="shared" si="17"/>
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="P84" s="121"/>
     </row>
     <row r="85">
       <c r="C85" s="115" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D85" s="104">
         <f t="shared" si="17"/>
-        <v>0.64</v>
+        <v>1.52</v>
       </c>
       <c r="P85" s="121"/>
     </row>
     <row r="86">
       <c r="C86" s="115" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D86" s="104">
         <f t="shared" si="17"/>
-        <v>1.95</v>
+        <v>2.17</v>
       </c>
       <c r="P86" s="121"/>
     </row>
@@ -36376,14 +36348,14 @@
     <row r="1">
       <c r="A1" s="84"/>
       <c r="B1" s="125" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C1" s="126"/>
       <c r="D1" s="126"/>
       <c r="E1" s="126"/>
       <c r="F1" s="126"/>
       <c r="G1" s="127" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="H1" s="126"/>
       <c r="I1" s="126"/>
@@ -36411,49 +36383,49 @@
         <v>3</v>
       </c>
       <c r="B2" s="129" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C2" s="130" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D2" s="130" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E2" s="130" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F2" s="131" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="G2" s="129">
         <v>1.0</v>
       </c>
       <c r="H2" s="130" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I2" s="130">
         <v>2.0</v>
       </c>
       <c r="J2" s="130" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="K2" s="132" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="L2" s="130" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="M2" s="133" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="N2" s="80" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="O2" s="80" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="P2" s="80" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="Q2" s="8"/>
       <c r="R2" s="8"/>
@@ -37126,7 +37098,7 @@
     </row>
     <row r="24">
       <c r="A24" s="74" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B24" s="146" t="str">
         <f t="shared" ref="B24:F24" si="4">IFERROR(AVERAGE(B3:B22),"")</f>
@@ -37236,7 +37208,7 @@
       <c r="E27" s="8"/>
       <c r="F27" s="8"/>
       <c r="G27" s="147" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="H27" s="8"/>
       <c r="I27" s="8"/>
@@ -37269,7 +37241,7 @@
         <v>1.0</v>
       </c>
       <c r="H28" s="148" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I28" s="148">
         <v>2.0</v>
@@ -37297,7 +37269,7 @@
       <c r="B29" s="8"/>
       <c r="C29" s="8"/>
       <c r="D29" s="4" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="E29" s="4">
         <f>J29</f>
@@ -37319,10 +37291,10 @@
       </c>
       <c r="K29" s="8"/>
       <c r="L29" s="74" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="M29" s="74" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="O29" s="4">
         <v>1.0</v>
@@ -37458,7 +37430,7 @@
       <c r="E33" s="8"/>
       <c r="F33" s="8"/>
       <c r="G33" s="99" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="J33" s="8"/>
       <c r="K33" s="8"/>
@@ -37492,7 +37464,7 @@
         <v>1.0</v>
       </c>
       <c r="H34" s="151" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I34" s="151">
         <v>2.0</v>
@@ -37635,7 +37607,7 @@
       <c r="D38" s="8"/>
       <c r="E38" s="8"/>
       <c r="F38" s="4" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="G38" s="150">
         <f t="shared" ref="G38:I38" si="8">G30-G35</f>

--- a/data/df_best_models.xlsx
+++ b/data/df_best_models.xlsx
@@ -211,7 +211,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="274">
   <si>
     <t>id_country</t>
   </si>
@@ -2206,7 +2206,7 @@
         <v>45679.0</v>
       </c>
       <c r="D4" s="16">
-        <v>343.0</v>
+        <v>663.0</v>
       </c>
       <c r="E4" s="16" t="s">
         <v>15</v>
@@ -2251,7 +2251,7 @@
         <v>45679.0</v>
       </c>
       <c r="D5" s="16">
-        <v>724.0</v>
+        <v>1448.0</v>
       </c>
       <c r="E5" s="16" t="s">
         <v>15</v>
@@ -2299,7 +2299,7 @@
         <v>45680.0</v>
       </c>
       <c r="D6" s="16">
-        <v>1051.0</v>
+        <v>1047.0</v>
       </c>
       <c r="E6" s="16" t="s">
         <v>15</v>
@@ -2346,7 +2346,7 @@
         <v>45677.0</v>
       </c>
       <c r="D7" s="16">
-        <v>47.0</v>
+        <v>281.0</v>
       </c>
       <c r="E7" s="16" t="s">
         <v>15</v>
@@ -2391,7 +2391,7 @@
         <v>45677.0</v>
       </c>
       <c r="D8" s="16">
-        <v>1447.0</v>
+        <v>1545.0</v>
       </c>
       <c r="E8" s="16" t="s">
         <v>15</v>
@@ -12834,6 +12834,12 @@
     </row>
     <row r="11">
       <c r="A11" s="43"/>
+      <c r="E11" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="16">
+        <v>343.0</v>
+      </c>
       <c r="O11" s="46"/>
       <c r="P11" s="43"/>
       <c r="Q11" s="43"/>
@@ -12845,6 +12851,12 @@
     </row>
     <row r="12">
       <c r="A12" s="34"/>
+      <c r="E12" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="16">
+        <v>724.0</v>
+      </c>
       <c r="O12" s="37"/>
       <c r="P12" s="34"/>
       <c r="Q12" s="34"/>
@@ -12855,6 +12867,12 @@
     </row>
     <row r="13">
       <c r="A13" s="34"/>
+      <c r="E13" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" s="16">
+        <v>1051.0</v>
+      </c>
       <c r="O13" s="37"/>
       <c r="P13" s="34"/>
       <c r="Q13" s="34"/>
@@ -12865,6 +12883,12 @@
     </row>
     <row r="14">
       <c r="A14" s="34"/>
+      <c r="E14" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14" s="16">
+        <v>47.0</v>
+      </c>
       <c r="N14" s="37"/>
       <c r="O14" s="37"/>
       <c r="P14" s="34"/>
@@ -12879,8 +12903,12 @@
       <c r="B15" s="34"/>
       <c r="C15" s="34"/>
       <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="34"/>
+      <c r="E15" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="16">
+        <v>1447.0</v>
+      </c>
       <c r="G15" s="34"/>
       <c r="H15" s="34"/>
       <c r="I15" s="34"/>

--- a/data/df_best_models.xlsx
+++ b/data/df_best_models.xlsx
@@ -211,7 +211,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="428" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="279">
   <si>
     <t>id_country</t>
   </si>
@@ -412,6 +412,12 @@
   </si>
   <si>
     <t>['ROI_sb_sin_ea', 'ROI_sb_con_ea', 'roi_last_25_matches_sb_sin_ea', 'roi_last_25_matches_sb_con_ea']</t>
+  </si>
+  <si>
+    <t>Hasta el sabado incluido</t>
+  </si>
+  <si>
+    <t>En el iniicio del domingo:</t>
   </si>
   <si>
     <t>]</t>
@@ -2222,32 +2228,22 @@
         <v>15</v>
       </c>
       <c r="F4" s="17"/>
-      <c r="G4" s="18">
-        <v>1301.22317033501</v>
-      </c>
-      <c r="H4" s="19">
-        <v>10.0</v>
-      </c>
-      <c r="I4" s="19">
-        <v>45.0</v>
-      </c>
-      <c r="J4" s="19">
-        <v>25.0</v>
-      </c>
-      <c r="K4" s="22">
+      <c r="G4" s="18"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="22" t="str">
         <f t="shared" ref="K4:K8" si="1">AVERAGE(H4:J4)</f>
-        <v>26.66666667</v>
-      </c>
-      <c r="L4" s="30">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L4" s="30" t="str">
         <f>K4*'Data preparation'!$C$2</f>
-        <v>6.666666667</v>
-      </c>
-      <c r="M4" s="21">
-        <v>5564.89670858036</v>
-      </c>
-      <c r="N4" s="22">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M4" s="21"/>
+      <c r="N4" s="22" t="str">
         <f t="shared" ref="N4:N8" si="2">M4/G4</f>
-        <v>4.27666586</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="5">
@@ -2261,40 +2257,28 @@
         <v>45679.0</v>
       </c>
       <c r="D5" s="16">
-        <v>1448.0</v>
+        <v>724.0</v>
       </c>
       <c r="E5" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="17">
-        <v>57.7981651376146</v>
-      </c>
-      <c r="G5" s="18">
-        <v>823.906317742065</v>
-      </c>
-      <c r="H5" s="21">
-        <v>70.0</v>
-      </c>
-      <c r="I5" s="21">
-        <v>45.0</v>
-      </c>
-      <c r="J5" s="21">
-        <v>25.0</v>
-      </c>
-      <c r="K5" s="22">
+      <c r="F5" s="17"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="21"/>
+      <c r="I5" s="21"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="22" t="str">
         <f t="shared" si="1"/>
-        <v>46.66666667</v>
-      </c>
-      <c r="L5" s="30">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L5" s="30" t="str">
         <f>K5*'Data preparation'!$C$2</f>
-        <v>11.66666667</v>
-      </c>
-      <c r="M5" s="21">
-        <v>8764.30228233083</v>
-      </c>
-      <c r="N5" s="22">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M5" s="21"/>
+      <c r="N5" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>10.63749858</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="P5" s="34"/>
     </row>
@@ -2314,35 +2298,23 @@
       <c r="E6" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="17">
-        <v>62.3853211009174</v>
-      </c>
-      <c r="G6" s="18">
-        <v>2007.3027253796</v>
-      </c>
-      <c r="H6" s="21">
-        <v>70.0</v>
-      </c>
-      <c r="I6" s="21">
-        <v>70.0</v>
-      </c>
-      <c r="J6" s="21">
-        <v>10.0</v>
-      </c>
-      <c r="K6" s="22">
+      <c r="F6" s="17"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="21"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="21"/>
+      <c r="K6" s="22" t="str">
         <f t="shared" si="1"/>
-        <v>50</v>
-      </c>
-      <c r="L6" s="30">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L6" s="30" t="str">
         <f>K6*'Data preparation'!$C$2</f>
-        <v>12.5</v>
-      </c>
-      <c r="M6" s="35">
-        <v>235388.618048197</v>
-      </c>
-      <c r="N6" s="22">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M6" s="35"/>
+      <c r="N6" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>117.2661279</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="7">
@@ -2362,32 +2334,22 @@
         <v>15</v>
       </c>
       <c r="F7" s="17"/>
-      <c r="G7" s="18">
-        <v>759.494203200902</v>
-      </c>
-      <c r="H7" s="19">
-        <v>45.0</v>
-      </c>
-      <c r="I7" s="19">
-        <v>45.0</v>
-      </c>
-      <c r="J7" s="19">
-        <v>45.0</v>
-      </c>
-      <c r="K7" s="28">
+      <c r="G7" s="18"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="19"/>
+      <c r="K7" s="28" t="str">
         <f t="shared" si="1"/>
-        <v>45</v>
-      </c>
-      <c r="L7" s="30">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L7" s="30" t="str">
         <f>K7*'Data preparation'!$C$2</f>
-        <v>11.25</v>
-      </c>
-      <c r="M7" s="21">
-        <v>9433.02522864221</v>
-      </c>
-      <c r="N7" s="22">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M7" s="21"/>
+      <c r="N7" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>12.42014118</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="8">
@@ -2407,32 +2369,22 @@
         <v>15</v>
       </c>
       <c r="F8" s="17"/>
-      <c r="G8" s="18">
-        <v>422.057169223285</v>
-      </c>
-      <c r="H8" s="19">
-        <v>45.0</v>
-      </c>
-      <c r="I8" s="19">
-        <v>10.0</v>
-      </c>
-      <c r="J8" s="19">
-        <v>25.0</v>
-      </c>
-      <c r="K8" s="22">
+      <c r="G8" s="18"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="19"/>
+      <c r="K8" s="22" t="str">
         <f t="shared" si="1"/>
-        <v>26.66666667</v>
-      </c>
-      <c r="L8" s="30">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L8" s="30" t="str">
         <f>K8*'Data preparation'!$C$2</f>
-        <v>6.666666667</v>
-      </c>
-      <c r="M8" s="21">
-        <v>1548.87389573756</v>
-      </c>
-      <c r="N8" s="22">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M8" s="21"/>
+      <c r="N8" s="22" t="str">
         <f t="shared" si="2"/>
-        <v>3.66982013</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="9" ht="20.25" customHeight="1">
@@ -12835,6 +12787,9 @@
     </row>
     <row r="10">
       <c r="A10" s="52"/>
+      <c r="E10" s="45" t="s">
+        <v>62</v>
+      </c>
       <c r="O10" s="46"/>
       <c r="P10" s="52"/>
       <c r="Q10" s="52"/>
@@ -12963,6 +12918,9 @@
     </row>
     <row r="18">
       <c r="A18" s="46"/>
+      <c r="E18" s="45" t="s">
+        <v>63</v>
+      </c>
       <c r="O18" s="46"/>
       <c r="P18" s="46"/>
       <c r="Q18" s="46"/>
@@ -12973,6 +12931,12 @@
     </row>
     <row r="19">
       <c r="A19" s="46"/>
+      <c r="E19" s="33" t="s">
+        <v>17</v>
+      </c>
+      <c r="F19" s="16">
+        <v>663.0</v>
+      </c>
       <c r="O19" s="46"/>
       <c r="P19" s="46"/>
       <c r="Q19" s="46"/>
@@ -12981,23 +12945,47 @@
       <c r="T19" s="34"/>
     </row>
     <row r="20">
+      <c r="E20" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="F20" s="16">
+        <v>654.0</v>
+      </c>
       <c r="O20" s="46"/>
       <c r="Q20" s="34"/>
       <c r="S20" s="34"/>
       <c r="T20" s="34"/>
     </row>
     <row r="21">
+      <c r="E21" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="F21" s="16">
+        <v>1051.0</v>
+      </c>
       <c r="O21" s="46"/>
       <c r="P21" s="34"/>
       <c r="T21" s="34"/>
     </row>
     <row r="22">
+      <c r="E22" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="F22" s="16">
+        <v>622.0</v>
+      </c>
       <c r="M22" s="52"/>
       <c r="O22" s="37"/>
       <c r="P22" s="34"/>
       <c r="T22" s="34"/>
     </row>
     <row r="23">
+      <c r="E23" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" s="16">
+        <v>1545.0</v>
+      </c>
       <c r="M23" s="52"/>
       <c r="O23" s="37"/>
       <c r="T23" s="34"/>
@@ -13042,146 +13030,146 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="45" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2">
       <c r="B2" s="10"/>
       <c r="C2" s="90" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E2" s="91"/>
       <c r="F2" s="92" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H2" s="91"/>
     </row>
     <row r="3">
       <c r="B3" s="93" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C3" s="94" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D3" s="93" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E3" s="95" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F3" s="93" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G3" s="93" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H3" s="93" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="96" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C4" s="97" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D4" s="98" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E4" s="99" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F4" s="100" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G4" s="100" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H4" s="98"/>
     </row>
     <row r="5">
       <c r="B5" s="96" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C5" s="101" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D5" s="102"/>
       <c r="E5" s="99" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F5" s="103" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G5" s="104" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H5" s="98"/>
     </row>
     <row r="6">
       <c r="B6" s="96" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C6" s="97" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D6" s="98" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E6" s="99" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F6" s="98" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G6" s="98"/>
       <c r="H6" s="98"/>
     </row>
     <row r="7">
       <c r="B7" s="98" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C7" s="105" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D7" s="98"/>
       <c r="E7" s="106" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F7" s="97" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G7" s="98"/>
       <c r="H7" s="98" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="107" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C8" s="108" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D8" s="109"/>
       <c r="E8" s="107" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F8" s="110" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G8" s="111" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H8" s="109"/>
     </row>
     <row r="9">
       <c r="B9" s="25" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C9" s="112" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D9" s="82"/>
       <c r="E9" s="82"/>
@@ -13191,27 +13179,27 @@
     </row>
     <row r="10">
       <c r="B10" s="25" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C10" s="113"/>
       <c r="D10" s="82"/>
       <c r="E10" s="82"/>
       <c r="F10" s="113"/>
       <c r="G10" s="100" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H10" s="82"/>
     </row>
     <row r="11">
       <c r="B11" s="25" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C11" s="113"/>
       <c r="D11" s="82"/>
       <c r="E11" s="82"/>
       <c r="F11" s="113"/>
       <c r="G11" s="114" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H11" s="25"/>
     </row>
@@ -13249,7 +13237,7 @@
     <row r="2">
       <c r="A2" s="19"/>
       <c r="B2" s="92" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C2" s="19">
         <v>0.25</v>
@@ -13259,11 +13247,11 @@
     <row r="3">
       <c r="A3" s="19"/>
       <c r="B3" s="92" t="s">
-        <v>100</v>
-      </c>
-      <c r="C3" s="29">
+        <v>102</v>
+      </c>
+      <c r="C3" s="23" t="str">
         <f>AVERAGE('Modelos actuales'!L4:L8)</f>
-        <v>9.75</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="L3" s="115"/>
       <c r="P3" s="115"/>
@@ -13274,7 +13262,7 @@
       <c r="L4" s="115"/>
       <c r="P4" s="115"/>
       <c r="AE4" s="45" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="AF4" s="116">
         <f>CORREL(AE6:AE10000,AF6:AF10000)</f>
@@ -13284,50 +13272,50 @@
     <row r="5">
       <c r="A5" s="19"/>
       <c r="B5" s="115" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="L5" s="115" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="P5" s="115" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AE5" s="45" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AF5" s="45" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="19"/>
       <c r="B6" s="45" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F6" s="45" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="K6" s="38"/>
       <c r="L6" s="38" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="N6" s="38" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="P6" s="38" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="R6" s="38" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="V6" s="38" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AA6" s="45" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="AB6" s="45" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AE6" s="45">
         <v>519.2</v>
@@ -13369,7 +13357,7 @@
         <v>0.5454545455</v>
       </c>
       <c r="AA7" s="45" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="AB7" s="44">
         <f t="shared" ref="AB7:AB16" si="4">LEFT(REPLACE(AA7,1,1,""),FIND(",", AA7)-2)/1</f>
@@ -13385,14 +13373,14 @@
     <row r="8">
       <c r="A8" s="19"/>
       <c r="B8" s="121" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C8" s="122" t="str">
         <f t="shared" ref="C8:C17" si="5">REPLACE(B8,FIND(".",B8),1,",")*1</f>
         <v>#VALUE!</v>
       </c>
       <c r="F8" s="50" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G8" s="122" t="str">
         <f t="shared" ref="G8:G27" si="6">REPLACE(F8,FIND(".",F8),1,",")*1</f>
@@ -13427,7 +13415,7 @@
         <v>0.5263157895</v>
       </c>
       <c r="AA8" s="45" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="AB8" s="44">
         <f t="shared" si="4"/>
@@ -13443,14 +13431,14 @@
     <row r="9">
       <c r="A9" s="19"/>
       <c r="B9" s="121" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C9" s="122" t="str">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="F9" s="50" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="G9" s="122" t="str">
         <f t="shared" si="6"/>
@@ -13464,13 +13452,13 @@
       </c>
       <c r="K9" s="19"/>
       <c r="L9" s="117" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="M9" s="117" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="N9" s="38" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="P9" s="119">
         <v>1.0</v>
@@ -13494,7 +13482,7 @@
         <v>0.25</v>
       </c>
       <c r="AA9" s="45" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AB9" s="44">
         <f t="shared" si="4"/>
@@ -13510,14 +13498,14 @@
     <row r="10">
       <c r="A10" s="19"/>
       <c r="B10" s="123" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C10" s="122" t="str">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="F10" s="50" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G10" s="122" t="str">
         <f t="shared" si="6"/>
@@ -13554,7 +13542,7 @@
         <v>76</v>
       </c>
       <c r="AA10" s="45" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AB10" s="44">
         <f t="shared" si="4"/>
@@ -13569,14 +13557,14 @@
     </row>
     <row r="11">
       <c r="B11" s="121" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C11" s="122" t="str">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="F11" s="50" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G11" s="122" t="str">
         <f t="shared" si="6"/>
@@ -13605,7 +13593,7 @@
         <v>2.0</v>
       </c>
       <c r="AA11" s="45" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="AB11" s="44">
         <f t="shared" si="4"/>
@@ -13620,14 +13608,14 @@
     </row>
     <row r="12">
       <c r="B12" s="123" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C12" s="122" t="str">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="F12" s="50" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G12" s="122" t="str">
         <f t="shared" si="6"/>
@@ -13656,7 +13644,7 @@
         <v>1.0</v>
       </c>
       <c r="AA12" s="45" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="AB12" s="44">
         <f t="shared" si="4"/>
@@ -13671,14 +13659,14 @@
     </row>
     <row r="13">
       <c r="B13" s="121" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C13" s="122" t="str">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="F13" s="50" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G13" s="122" t="str">
         <f t="shared" si="6"/>
@@ -13708,16 +13696,16 @@
       <c r="Q13" s="43"/>
       <c r="R13" s="82"/>
       <c r="S13" s="87" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="T13" s="87" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="U13" s="87" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AA13" s="45" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AB13" s="44">
         <f t="shared" si="4"/>
@@ -13732,14 +13720,14 @@
     </row>
     <row r="14">
       <c r="B14" s="121" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C14" s="122" t="str">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="F14" s="50" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G14" s="122" t="str">
         <f t="shared" si="6"/>
@@ -13779,7 +13767,7 @@
         <v>11.0</v>
       </c>
       <c r="AA14" s="45" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="AB14" s="44">
         <f t="shared" si="4"/>
@@ -13794,14 +13782,14 @@
     </row>
     <row r="15">
       <c r="B15" s="121" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C15" s="122" t="str">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="F15" s="50" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G15" s="122" t="str">
         <f t="shared" si="6"/>
@@ -13841,7 +13829,7 @@
         <v>13.0</v>
       </c>
       <c r="AA15" s="45" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="AB15" s="44">
         <f t="shared" si="4"/>
@@ -13856,14 +13844,14 @@
     </row>
     <row r="16">
       <c r="B16" s="121" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C16" s="122" t="str">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="F16" s="50" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G16" s="122" t="str">
         <f t="shared" si="6"/>
@@ -13903,7 +13891,7 @@
         <v>12.0</v>
       </c>
       <c r="AA16" s="45" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AB16" s="44">
         <f t="shared" si="4"/>
@@ -13918,14 +13906,14 @@
     </row>
     <row r="17">
       <c r="B17" s="121" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C17" s="122" t="str">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="F17" s="50" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G17" s="122" t="str">
         <f t="shared" si="6"/>
@@ -13953,7 +13941,7 @@
         <v>1.0</v>
       </c>
       <c r="R17" s="87" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="S17" s="124">
         <f t="shared" ref="S17:U17" si="10">SUM(S14:S16)</f>
@@ -13976,7 +13964,7 @@
     </row>
     <row r="18">
       <c r="F18" s="50" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G18" s="122" t="str">
         <f t="shared" si="6"/>
@@ -14013,14 +14001,14 @@
     </row>
     <row r="19">
       <c r="B19" s="38" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C19" s="44" t="str">
         <f>AVERAGE(C8:C17)</f>
         <v>#VALUE!</v>
       </c>
       <c r="F19" s="50" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G19" s="122" t="str">
         <f t="shared" si="6"/>
@@ -14048,7 +14036,7 @@
       <c r="T19" s="23"/>
       <c r="U19" s="23"/>
       <c r="AA19" s="45" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AB19" s="44">
         <f>AVERAGE(AB7:AB16)</f>
@@ -14063,7 +14051,7 @@
     </row>
     <row r="20">
       <c r="F20" s="50" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G20" s="122" t="str">
         <f t="shared" si="6"/>
@@ -14088,7 +14076,7 @@
     </row>
     <row r="21">
       <c r="F21" s="50" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G21" s="122" t="str">
         <f t="shared" si="6"/>
@@ -14102,13 +14090,13 @@
       </c>
       <c r="R21" s="82"/>
       <c r="S21" s="87" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="T21" s="87" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="U21" s="87" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AE21" s="45">
         <v>146.62</v>
@@ -14120,7 +14108,7 @@
     <row r="22">
       <c r="C22" s="122"/>
       <c r="F22" s="50" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G22" s="122" t="str">
         <f t="shared" si="6"/>
@@ -14193,7 +14181,7 @@
     </row>
     <row r="24">
       <c r="F24" s="50" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G24" s="122" t="str">
         <f t="shared" si="6"/>
@@ -14229,7 +14217,7 @@
     </row>
     <row r="25">
       <c r="F25" s="50" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G25" s="122" t="str">
         <f t="shared" si="6"/>
@@ -14242,7 +14230,7 @@
         <v>1.0</v>
       </c>
       <c r="R25" s="87" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="S25" s="124">
         <f t="shared" ref="S25:U25" si="14">SUM(S22:S24)</f>
@@ -14265,7 +14253,7 @@
     </row>
     <row r="26">
       <c r="F26" s="50" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G26" s="122" t="str">
         <f t="shared" si="6"/>
@@ -14310,13 +14298,13 @@
         <v>1.0</v>
       </c>
       <c r="AA28" s="45" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="AB28" s="45" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="AC28" s="45" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="AE28" s="45">
         <v>106.73</v>
@@ -14327,7 +14315,7 @@
     </row>
     <row r="29">
       <c r="F29" s="38" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G29" s="44" t="str">
         <f>AVERAGE(G8:G27)</f>
@@ -14418,7 +14406,7 @@
     </row>
     <row r="32">
       <c r="B32" s="57" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="G32" s="122"/>
       <c r="P32" s="119">
@@ -14447,7 +14435,7 @@
     </row>
     <row r="33">
       <c r="B33" s="127" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="G33" s="128"/>
       <c r="P33" s="119">
@@ -14501,7 +14489,7 @@
     </row>
     <row r="35">
       <c r="H35" s="38" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="P35" s="119">
         <v>1.0</v>
@@ -14629,7 +14617,7 @@
     </row>
     <row r="39">
       <c r="C39" s="132" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D39" s="122">
         <f t="shared" ref="D39:D221" si="17">IF(COUNTA(C39)=1,C39/1,"")</f>
@@ -14667,7 +14655,7 @@
     </row>
     <row r="40">
       <c r="C40" s="133" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D40" s="122">
         <f t="shared" si="17"/>
@@ -14705,7 +14693,7 @@
     </row>
     <row r="41">
       <c r="C41" s="133" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D41" s="122">
         <f t="shared" si="17"/>
@@ -14737,7 +14725,7 @@
     </row>
     <row r="42">
       <c r="C42" s="133" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D42" s="122">
         <f t="shared" si="17"/>
@@ -14769,7 +14757,7 @@
     </row>
     <row r="43">
       <c r="C43" s="133" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D43" s="122">
         <f t="shared" si="17"/>
@@ -14801,7 +14789,7 @@
     </row>
     <row r="44">
       <c r="C44" s="133" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D44" s="122">
         <f t="shared" si="17"/>
@@ -14831,7 +14819,7 @@
     </row>
     <row r="45">
       <c r="C45" s="133" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D45" s="122">
         <f t="shared" si="17"/>
@@ -14849,17 +14837,17 @@
     </row>
     <row r="46">
       <c r="C46" s="133" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D46" s="122">
         <f t="shared" si="17"/>
         <v>4.55</v>
       </c>
       <c r="G46" s="93" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H46" s="93" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="P46" s="119">
         <v>0.0</v>
@@ -14873,7 +14861,7 @@
     </row>
     <row r="47">
       <c r="C47" s="133" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D47" s="122">
         <f t="shared" si="17"/>
@@ -14892,7 +14880,7 @@
         <v>3</v>
       </c>
       <c r="AB47" s="45" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="AE47" s="45">
         <v>67.98</v>
@@ -14903,7 +14891,7 @@
     </row>
     <row r="48">
       <c r="C48" s="133" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D48" s="122">
         <f t="shared" si="17"/>
@@ -14916,7 +14904,7 @@
         <v>0.36678739680281</v>
       </c>
       <c r="J48" s="45" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="K48" s="120">
         <f>AVERAGE(H47:H51)</f>
@@ -14940,7 +14928,7 @@
     </row>
     <row r="49">
       <c r="C49" s="133" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D49" s="122">
         <f t="shared" si="17"/>
@@ -14953,7 +14941,7 @@
         <v>0.142870351877935</v>
       </c>
       <c r="J49" s="45" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="K49" s="120">
         <f>MEDIAN(H47:H51)</f>
@@ -14977,7 +14965,7 @@
     </row>
     <row r="50">
       <c r="C50" s="133" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D50" s="122">
         <f t="shared" si="17"/>
@@ -14990,7 +14978,7 @@
         <v>0.497437843674554</v>
       </c>
       <c r="J50" s="45" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="K50" s="120">
         <f>PERCENTILE(H47:H51,0.25)</f>
@@ -15014,7 +15002,7 @@
     </row>
     <row r="51">
       <c r="C51" s="133" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D51" s="122">
         <f t="shared" si="17"/>
@@ -15027,7 +15015,7 @@
         <v>0.247446036291655</v>
       </c>
       <c r="J51" s="45" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="K51" s="120">
         <f>PERCENTILE(H47:H51,0.75)</f>
@@ -15051,7 +15039,7 @@
     </row>
     <row r="52">
       <c r="C52" s="133" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D52" s="122">
         <f t="shared" si="17"/>
@@ -15075,7 +15063,7 @@
     </row>
     <row r="53">
       <c r="C53" s="133" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D53" s="122">
         <f t="shared" si="17"/>
@@ -15099,7 +15087,7 @@
     </row>
     <row r="54">
       <c r="C54" s="133" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D54" s="122">
         <f t="shared" si="17"/>
@@ -15123,7 +15111,7 @@
     </row>
     <row r="55">
       <c r="C55" s="133" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D55" s="122">
         <f t="shared" si="17"/>
@@ -15147,7 +15135,7 @@
     </row>
     <row r="56">
       <c r="C56" s="133" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D56" s="122">
         <f t="shared" si="17"/>
@@ -15171,7 +15159,7 @@
     </row>
     <row r="57">
       <c r="C57" s="133" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D57" s="122">
         <f t="shared" si="17"/>
@@ -15195,14 +15183,14 @@
     </row>
     <row r="58">
       <c r="C58" s="133" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D58" s="122">
         <f t="shared" si="17"/>
         <v>7.8</v>
       </c>
       <c r="G58" s="135" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H58" s="136"/>
       <c r="P58" s="119">
@@ -15223,7 +15211,7 @@
     </row>
     <row r="59">
       <c r="C59" s="133" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D59" s="122">
         <f t="shared" si="17"/>
@@ -15231,7 +15219,7 @@
       </c>
       <c r="G59" s="136"/>
       <c r="H59" s="137" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P59" s="119">
         <v>0.0</v>
@@ -15251,7 +15239,7 @@
     </row>
     <row r="60">
       <c r="C60" s="133" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D60" s="122">
         <f t="shared" si="17"/>
@@ -15259,7 +15247,7 @@
       </c>
       <c r="G60" s="136"/>
       <c r="H60" s="137" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="P60" s="119">
         <v>2.0</v>
@@ -15279,7 +15267,7 @@
     </row>
     <row r="61">
       <c r="C61" s="133" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D61" s="122">
         <f t="shared" si="17"/>
@@ -15287,7 +15275,7 @@
       </c>
       <c r="G61" s="136"/>
       <c r="H61" s="137" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="P61" s="119">
         <v>2.0</v>
@@ -15307,7 +15295,7 @@
     </row>
     <row r="62">
       <c r="C62" s="133" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D62" s="122">
         <f t="shared" si="17"/>
@@ -15315,7 +15303,7 @@
       </c>
       <c r="G62" s="136"/>
       <c r="H62" s="137" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="P62" s="119">
         <v>1.0</v>
@@ -15335,7 +15323,7 @@
     </row>
     <row r="63">
       <c r="C63" s="133" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D63" s="122">
         <f t="shared" si="17"/>
@@ -15343,7 +15331,7 @@
       </c>
       <c r="G63" s="136"/>
       <c r="H63" s="137" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="P63" s="119">
         <v>0.0</v>
@@ -15357,7 +15345,7 @@
     </row>
     <row r="64">
       <c r="C64" s="133" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D64" s="122">
         <f t="shared" si="17"/>
@@ -15375,7 +15363,7 @@
     </row>
     <row r="65">
       <c r="C65" s="133" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D65" s="122">
         <f t="shared" si="17"/>
@@ -15393,7 +15381,7 @@
     </row>
     <row r="66">
       <c r="C66" s="133" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D66" s="122">
         <f t="shared" si="17"/>
@@ -15411,7 +15399,7 @@
     </row>
     <row r="67">
       <c r="C67" s="133" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D67" s="122">
         <f t="shared" si="17"/>
@@ -15429,7 +15417,7 @@
     </row>
     <row r="68">
       <c r="C68" s="133" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D68" s="122">
         <f t="shared" si="17"/>
@@ -15447,7 +15435,7 @@
     </row>
     <row r="69">
       <c r="C69" s="133" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D69" s="122">
         <f t="shared" si="17"/>
@@ -15465,7 +15453,7 @@
     </row>
     <row r="70">
       <c r="C70" s="133" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D70" s="122">
         <f t="shared" si="17"/>
@@ -15483,7 +15471,7 @@
     </row>
     <row r="71">
       <c r="C71" s="133" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D71" s="122">
         <f t="shared" si="17"/>
@@ -15502,7 +15490,7 @@
     </row>
     <row r="72">
       <c r="C72" s="133" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D72" s="122">
         <f t="shared" si="17"/>
@@ -15520,7 +15508,7 @@
     </row>
     <row r="73">
       <c r="C73" s="133" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D73" s="122">
         <f t="shared" si="17"/>
@@ -15538,7 +15526,7 @@
     </row>
     <row r="74">
       <c r="C74" s="133" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D74" s="122">
         <f t="shared" si="17"/>
@@ -15556,7 +15544,7 @@
     </row>
     <row r="75">
       <c r="C75" s="133" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D75" s="122">
         <f t="shared" si="17"/>
@@ -15574,7 +15562,7 @@
     </row>
     <row r="76">
       <c r="C76" s="133" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D76" s="122">
         <f t="shared" si="17"/>
@@ -15592,7 +15580,7 @@
     </row>
     <row r="77">
       <c r="C77" s="133" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D77" s="122">
         <f t="shared" si="17"/>
@@ -15610,7 +15598,7 @@
     </row>
     <row r="78">
       <c r="C78" s="133" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D78" s="122">
         <f t="shared" si="17"/>
@@ -15628,7 +15616,7 @@
     </row>
     <row r="79">
       <c r="C79" s="133" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D79" s="122">
         <f t="shared" si="17"/>
@@ -15646,7 +15634,7 @@
     </row>
     <row r="80">
       <c r="C80" s="133" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D80" s="122">
         <f t="shared" si="17"/>
@@ -15664,7 +15652,7 @@
     </row>
     <row r="81">
       <c r="C81" s="133" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D81" s="122">
         <f t="shared" si="17"/>
@@ -15682,7 +15670,7 @@
     </row>
     <row r="82">
       <c r="C82" s="133" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D82" s="122">
         <f t="shared" si="17"/>
@@ -15700,7 +15688,7 @@
     </row>
     <row r="83">
       <c r="C83" s="133" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D83" s="122">
         <f t="shared" si="17"/>
@@ -15718,7 +15706,7 @@
     </row>
     <row r="84">
       <c r="C84" s="133" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D84" s="122">
         <f t="shared" si="17"/>
@@ -15736,7 +15724,7 @@
     </row>
     <row r="85">
       <c r="C85" s="133" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D85" s="122">
         <f t="shared" si="17"/>
@@ -15754,7 +15742,7 @@
     </row>
     <row r="86">
       <c r="C86" s="133" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D86" s="122">
         <f t="shared" si="17"/>
@@ -15772,7 +15760,7 @@
     </row>
     <row r="87">
       <c r="C87" s="133" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D87" s="122">
         <f t="shared" si="17"/>
@@ -15790,7 +15778,7 @@
     </row>
     <row r="88">
       <c r="C88" s="133" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D88" s="122">
         <f t="shared" si="17"/>
@@ -15808,7 +15796,7 @@
     </row>
     <row r="89">
       <c r="C89" s="133" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D89" s="122">
         <f t="shared" si="17"/>
@@ -15826,7 +15814,7 @@
     </row>
     <row r="90">
       <c r="C90" s="133" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D90" s="122">
         <f t="shared" si="17"/>
@@ -15844,7 +15832,7 @@
     </row>
     <row r="91">
       <c r="C91" s="133" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D91" s="122">
         <f t="shared" si="17"/>
@@ -15862,7 +15850,7 @@
     </row>
     <row r="92">
       <c r="C92" s="133" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D92" s="122">
         <f t="shared" si="17"/>
@@ -15880,7 +15868,7 @@
     </row>
     <row r="93">
       <c r="C93" s="133" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D93" s="122">
         <f t="shared" si="17"/>
@@ -15898,7 +15886,7 @@
     </row>
     <row r="94">
       <c r="C94" s="133" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D94" s="122">
         <f t="shared" si="17"/>
@@ -15916,7 +15904,7 @@
     </row>
     <row r="95">
       <c r="C95" s="133" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D95" s="122">
         <f t="shared" si="17"/>
@@ -15934,7 +15922,7 @@
     </row>
     <row r="96">
       <c r="C96" s="133" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D96" s="122">
         <f t="shared" si="17"/>
@@ -15952,7 +15940,7 @@
     </row>
     <row r="97">
       <c r="C97" s="133" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D97" s="122">
         <f t="shared" si="17"/>
@@ -15970,7 +15958,7 @@
     </row>
     <row r="98">
       <c r="C98" s="133" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D98" s="122">
         <f t="shared" si="17"/>
@@ -15988,7 +15976,7 @@
     </row>
     <row r="99">
       <c r="C99" s="133" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D99" s="122">
         <f t="shared" si="17"/>
@@ -16006,7 +15994,7 @@
     </row>
     <row r="100">
       <c r="C100" s="133" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D100" s="122">
         <f t="shared" si="17"/>
@@ -16024,7 +16012,7 @@
     </row>
     <row r="101">
       <c r="C101" s="133" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="D101" s="122">
         <f t="shared" si="17"/>
@@ -16042,7 +16030,7 @@
     </row>
     <row r="102">
       <c r="C102" s="133" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D102" s="122">
         <f t="shared" si="17"/>
@@ -16060,7 +16048,7 @@
     </row>
     <row r="103">
       <c r="C103" s="133" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D103" s="122">
         <f t="shared" si="17"/>
@@ -16078,7 +16066,7 @@
     </row>
     <row r="104">
       <c r="C104" s="133" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D104" s="122">
         <f t="shared" si="17"/>
@@ -16097,7 +16085,7 @@
     </row>
     <row r="105">
       <c r="C105" s="133" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D105" s="122">
         <f t="shared" si="17"/>
@@ -16116,7 +16104,7 @@
     </row>
     <row r="106">
       <c r="C106" s="133" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D106" s="122">
         <f t="shared" si="17"/>
@@ -16135,7 +16123,7 @@
     </row>
     <row r="107">
       <c r="C107" s="133" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D107" s="122">
         <f t="shared" si="17"/>
@@ -16154,7 +16142,7 @@
     </row>
     <row r="108">
       <c r="C108" s="133" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="D108" s="122">
         <f t="shared" si="17"/>
@@ -16173,7 +16161,7 @@
     </row>
     <row r="109">
       <c r="C109" s="133" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D109" s="122">
         <f t="shared" si="17"/>
@@ -16192,7 +16180,7 @@
     </row>
     <row r="110">
       <c r="C110" s="133" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="D110" s="122">
         <f t="shared" si="17"/>
@@ -16211,7 +16199,7 @@
     </row>
     <row r="111">
       <c r="C111" s="133" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D111" s="122">
         <f t="shared" si="17"/>
@@ -16230,7 +16218,7 @@
     </row>
     <row r="112">
       <c r="C112" s="133" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D112" s="122">
         <f t="shared" si="17"/>
@@ -16248,7 +16236,7 @@
     </row>
     <row r="113">
       <c r="C113" s="133" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D113" s="122">
         <f t="shared" si="17"/>
@@ -16266,7 +16254,7 @@
     </row>
     <row r="114">
       <c r="C114" s="133" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D114" s="122">
         <f t="shared" si="17"/>
@@ -16284,7 +16272,7 @@
     </row>
     <row r="115">
       <c r="C115" s="133" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D115" s="122">
         <f t="shared" si="17"/>
@@ -16302,7 +16290,7 @@
     </row>
     <row r="116">
       <c r="C116" s="133" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D116" s="122">
         <f t="shared" si="17"/>
@@ -16320,7 +16308,7 @@
     </row>
     <row r="117">
       <c r="C117" s="133" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D117" s="122">
         <f t="shared" si="17"/>
@@ -16336,7 +16324,7 @@
     </row>
     <row r="118">
       <c r="C118" s="133" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D118" s="122">
         <f t="shared" si="17"/>
@@ -16352,7 +16340,7 @@
     </row>
     <row r="119">
       <c r="C119" s="133" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D119" s="122">
         <f t="shared" si="17"/>
@@ -16368,7 +16356,7 @@
     </row>
     <row r="120">
       <c r="C120" s="133" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D120" s="122">
         <f t="shared" si="17"/>
@@ -16384,7 +16372,7 @@
     </row>
     <row r="121">
       <c r="C121" s="133" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D121" s="122">
         <f t="shared" si="17"/>
@@ -16400,7 +16388,7 @@
     </row>
     <row r="122">
       <c r="C122" s="133" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D122" s="122">
         <f t="shared" si="17"/>
@@ -16416,7 +16404,7 @@
     </row>
     <row r="123">
       <c r="C123" s="133" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D123" s="122">
         <f t="shared" si="17"/>
@@ -16432,7 +16420,7 @@
     </row>
     <row r="124">
       <c r="C124" s="133" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D124" s="122">
         <f t="shared" si="17"/>
@@ -38884,14 +38872,14 @@
     <row r="1">
       <c r="A1" s="102"/>
       <c r="B1" s="143" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C1" s="144"/>
       <c r="D1" s="144"/>
       <c r="E1" s="144"/>
       <c r="F1" s="144"/>
       <c r="G1" s="145" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="H1" s="144"/>
       <c r="I1" s="144"/>
@@ -38919,49 +38907,49 @@
         <v>3</v>
       </c>
       <c r="B2" s="147" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C2" s="148" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D2" s="148" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E2" s="148" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F2" s="149" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="G2" s="147">
         <v>1.0</v>
       </c>
       <c r="H2" s="148" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I2" s="148">
         <v>2.0</v>
       </c>
       <c r="J2" s="148" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K2" s="150" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="L2" s="148" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="M2" s="151" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="N2" s="98" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="O2" s="98" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="P2" s="98" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q2" s="10"/>
       <c r="R2" s="10"/>
@@ -39634,7 +39622,7 @@
     </row>
     <row r="24">
       <c r="A24" s="92" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B24" s="163" t="str">
         <f t="shared" ref="B24:F24" si="4">IFERROR(AVERAGE(B3:B22),"")</f>
@@ -39744,7 +39732,7 @@
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="164" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="H27" s="10"/>
       <c r="I27" s="10"/>
@@ -39777,7 +39765,7 @@
         <v>1.0</v>
       </c>
       <c r="H28" s="165" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I28" s="165">
         <v>2.0</v>
@@ -39805,7 +39793,7 @@
       <c r="B29" s="10"/>
       <c r="C29" s="10"/>
       <c r="D29" s="6" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E29" s="6">
         <f>J29</f>
@@ -39827,10 +39815,10 @@
       </c>
       <c r="K29" s="10"/>
       <c r="L29" s="92" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="M29" s="92" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="O29" s="6">
         <v>1.0</v>
@@ -39966,7 +39954,7 @@
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
       <c r="G33" s="117" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="J33" s="10"/>
       <c r="K33" s="10"/>
@@ -40000,7 +39988,7 @@
         <v>1.0</v>
       </c>
       <c r="H34" s="168" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="I34" s="168">
         <v>2.0</v>
@@ -40143,7 +40131,7 @@
       <c r="D38" s="10"/>
       <c r="E38" s="10"/>
       <c r="F38" s="6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="G38" s="167">
         <f t="shared" ref="G38:I38" si="8">G30-G35</f>

--- a/data/df_best_models.xlsx
+++ b/data/df_best_models.xlsx
@@ -33,11 +33,6 @@
       <text>
         <t xml:space="preserve">los que mas valor tienen suelen tener un rdo mucho mas rentable que otro.
 </t>
-      </text>
-    </comment>
-    <comment authorId="0" ref="M4">
-      <text>
-        <t xml:space="preserve">el empate...</t>
       </text>
     </comment>
     <comment authorId="0" ref="A1">
@@ -211,7 +206,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="262">
   <si>
     <t>id_country</t>
   </si>
@@ -735,28 +730,25 @@
     <t>Stake promedio</t>
   </si>
   <si>
-    <t>2.33</t>
+    <t>0.00</t>
   </si>
   <si>
-    <t>0.08</t>
+    <t>2.39</t>
   </si>
   <si>
-    <t>0.86</t>
+    <t>0.37</t>
   </si>
   <si>
-    <t>0.23</t>
+    <t>6.63</t>
   </si>
   <si>
-    <t>8.96</t>
+    <t>6.25</t>
   </si>
   <si>
-    <t>9.16</t>
+    <t>2.45</t>
   </si>
   <si>
-    <t>9.83</t>
-  </si>
-  <si>
-    <t>4.55</t>
+    <t>1.66</t>
   </si>
   <si>
     <t>Country</t>
@@ -765,247 +757,199 @@
     <t>Correl ROI y Expected ROI</t>
   </si>
   <si>
-    <t>6.78</t>
+    <t>2.82</t>
   </si>
   <si>
-    <t>5.35</t>
+    <t>1.16</t>
   </si>
   <si>
     <t>mean</t>
   </si>
   <si>
-    <t>9.07</t>
+    <t>2.34</t>
   </si>
   <si>
     <t>median</t>
   </si>
   <si>
-    <t>9.62</t>
+    <t>5.55</t>
   </si>
   <si>
     <t>p25</t>
   </si>
   <si>
-    <t>6.23</t>
+    <t>6.52</t>
   </si>
   <si>
     <t>p75</t>
   </si>
   <si>
-    <t>6.67</t>
+    <t>9.11</t>
   </si>
   <si>
-    <t>7.71</t>
+    <t>8.92</t>
   </si>
   <si>
-    <t>7.62</t>
+    <t>5.46</t>
   </si>
   <si>
-    <t>8.13</t>
+    <t>2.49</t>
   </si>
   <si>
-    <t>7.73</t>
+    <t>4.97</t>
   </si>
   <si>
-    <t>7.80</t>
+    <t>4.98</t>
+  </si>
+  <si>
+    <t>4.46</t>
   </si>
   <si>
     <t>Gracias a las nuevas métricas de G/P sin bank en test, me di cuenta de que:</t>
   </si>
   <si>
-    <t>7.94</t>
+    <t>5.12</t>
   </si>
   <si>
     <t>La rentabilidad en ITA está en el visitante y no en el empate como creía.</t>
   </si>
   <si>
-    <t>8.21</t>
+    <t>4.95</t>
   </si>
   <si>
     <t>La rentabilidad en ENG y GER está en el empate tal como creía.</t>
   </si>
   <si>
-    <t>8.04</t>
+    <t>4.85</t>
   </si>
   <si>
     <t>En SPA esta repartido aunque Empate saca una ventaja.</t>
   </si>
   <si>
-    <t>7.59</t>
-  </si>
-  <si>
     <t>En FRA, depende el modelo. A veces local, a veces, empate.</t>
   </si>
   <si>
-    <t>2.60</t>
+    <t>2.00</t>
   </si>
   <si>
     <t>Si en FRA empate no rinde, no tiene sentido exigirle una buena distrib en empate… → Tiene sentido pero al parecer si importa el empate puesto que el modelo que gana se basa en empate.</t>
   </si>
   <si>
-    <t>2.54</t>
+    <t>1.40</t>
   </si>
   <si>
-    <t>4.30</t>
+    <t>2.19</t>
   </si>
   <si>
-    <t>3.91</t>
+    <t>0.49</t>
   </si>
   <si>
-    <t>11.47</t>
+    <t>0.05</t>
   </si>
   <si>
-    <t>0.00</t>
+    <t>5.85</t>
   </si>
   <si>
-    <t>10.36</t>
+    <t>6.81</t>
+  </si>
+  <si>
+    <t>5.65</t>
+  </si>
+  <si>
+    <t>6.19</t>
+  </si>
+  <si>
+    <t>1.62</t>
+  </si>
+  <si>
+    <t>6.58</t>
+  </si>
+  <si>
+    <t>6.08</t>
+  </si>
+  <si>
+    <t>1.06</t>
+  </si>
+  <si>
+    <t>1.48</t>
+  </si>
+  <si>
+    <t>1.45</t>
+  </si>
+  <si>
+    <t>1.60</t>
+  </si>
+  <si>
+    <t>1.89</t>
+  </si>
+  <si>
+    <t>1.28</t>
+  </si>
+  <si>
+    <t>2.05</t>
+  </si>
+  <si>
+    <t>1.75</t>
+  </si>
+  <si>
+    <t>1.18</t>
+  </si>
+  <si>
+    <t>1.77</t>
+  </si>
+  <si>
+    <t>1.74</t>
+  </si>
+  <si>
+    <t>1.69</t>
+  </si>
+  <si>
+    <t>1.59</t>
+  </si>
+  <si>
+    <t>1.70</t>
+  </si>
+  <si>
+    <t>1.87</t>
+  </si>
+  <si>
+    <t>1.14</t>
+  </si>
+  <si>
+    <t>1.19</t>
+  </si>
+  <si>
+    <t>1.21</t>
+  </si>
+  <si>
+    <t>4.59</t>
   </si>
   <si>
     <t>10.91</t>
   </si>
   <si>
-    <t>1.95</t>
+    <t>9.79</t>
   </si>
   <si>
-    <t>9.68</t>
+    <t>10.92</t>
   </si>
   <si>
-    <t>9.01</t>
+    <t>13.09</t>
   </si>
   <si>
-    <t>9.76</t>
+    <t>13.14</t>
   </si>
   <si>
-    <t>7.88</t>
+    <t>10.26</t>
   </si>
   <si>
-    <t>13.76</t>
+    <t>11.82</t>
   </si>
   <si>
-    <t>13.51</t>
+    <t>10.88</t>
   </si>
   <si>
-    <t>1.98</t>
-  </si>
-  <si>
-    <t>2.45</t>
-  </si>
-  <si>
-    <t>2.28</t>
-  </si>
-  <si>
-    <t>2.29</t>
-  </si>
-  <si>
-    <t>0.10</t>
-  </si>
-  <si>
-    <t>2.55</t>
-  </si>
-  <si>
-    <t>2.18</t>
-  </si>
-  <si>
-    <t>1.16</t>
-  </si>
-  <si>
-    <t>1.49</t>
-  </si>
-  <si>
-    <t>4.05</t>
-  </si>
-  <si>
-    <t>7.19</t>
-  </si>
-  <si>
-    <t>2.16</t>
-  </si>
-  <si>
-    <t>2.46</t>
-  </si>
-  <si>
-    <t>7.75</t>
-  </si>
-  <si>
-    <t>8.36</t>
-  </si>
-  <si>
-    <t>4.22</t>
-  </si>
-  <si>
-    <t>8.00</t>
-  </si>
-  <si>
-    <t>8.33</t>
-  </si>
-  <si>
-    <t>7.89</t>
-  </si>
-  <si>
-    <t>4.83</t>
-  </si>
-  <si>
-    <t>3.08</t>
-  </si>
-  <si>
-    <t>6.35</t>
-  </si>
-  <si>
-    <t>3.42</t>
-  </si>
-  <si>
-    <t>5.68</t>
-  </si>
-  <si>
-    <t>6.46</t>
-  </si>
-  <si>
-    <t>6.97</t>
-  </si>
-  <si>
-    <t>6.55</t>
-  </si>
-  <si>
-    <t>6.13</t>
-  </si>
-  <si>
-    <t>3.44</t>
-  </si>
-  <si>
-    <t>7.03</t>
-  </si>
-  <si>
-    <t>2.22</t>
-  </si>
-  <si>
-    <t>2.49</t>
-  </si>
-  <si>
-    <t>5.89</t>
-  </si>
-  <si>
-    <t>4.85</t>
-  </si>
-  <si>
-    <t>2.86</t>
-  </si>
-  <si>
-    <t>2.62</t>
-  </si>
-  <si>
-    <t>2.98</t>
-  </si>
-  <si>
-    <t>3.00</t>
-  </si>
-  <si>
-    <t>2.85</t>
-  </si>
-  <si>
-    <t>2.93</t>
-  </si>
-  <si>
-    <t>2.99</t>
+    <t>10.81</t>
   </si>
   <si>
     <t>RENTABILIDAD</t>
@@ -2144,31 +2088,32 @@
         <v>45685.0</v>
       </c>
       <c r="D2" s="14">
-        <v>40.0</v>
+        <v>616.0</v>
       </c>
       <c r="E2" s="15" t="s">
         <v>14</v>
       </c>
       <c r="F2" s="16">
-        <v>155.067930759269</v>
+        <f>5.8410821479406*100</f>
+        <v>584.1082148</v>
       </c>
       <c r="G2" s="17">
         <v>70.0</v>
       </c>
       <c r="H2" s="17">
-        <v>25.0</v>
+        <v>45.0</v>
       </c>
       <c r="I2" s="17">
-        <v>25.0</v>
+        <v>10.0</v>
       </c>
       <c r="J2" s="18"/>
       <c r="K2" s="18"/>
       <c r="L2" s="19">
-        <v>947.246174692297</v>
+        <v>31833.0939389723</v>
       </c>
       <c r="M2" s="20">
         <f>L2/F2</f>
-        <v>6.108588475</v>
+        <v>54.49862394</v>
       </c>
       <c r="N2" s="21"/>
       <c r="O2" s="22"/>
@@ -2211,7 +2156,8 @@
         <v>14</v>
       </c>
       <c r="F4" s="16">
-        <v>196.201829289439</v>
+        <f>1.95083127981317*100</f>
+        <v>195.083128</v>
       </c>
       <c r="G4" s="17">
         <v>10.0</v>
@@ -2231,11 +2177,11 @@
         <v>5</v>
       </c>
       <c r="L4" s="19">
-        <v>1933.66205998427</v>
+        <v>2031.72738744972</v>
       </c>
       <c r="M4" s="20">
         <f t="shared" ref="M4:M8" si="2">L4/F4</f>
-        <v>9.855474167</v>
+        <v>10.41467506</v>
       </c>
     </row>
     <row r="5">
@@ -2255,7 +2201,8 @@
         <v>14</v>
       </c>
       <c r="F5" s="16">
-        <v>328.964710450097</v>
+        <f>3.44623889518345*100</f>
+        <v>344.6238895</v>
       </c>
       <c r="G5" s="19">
         <v>70.0</v>
@@ -2275,11 +2222,11 @@
         <v>13.33333333</v>
       </c>
       <c r="L5" s="19">
-        <v>13260.6600418071</v>
+        <v>7144.81139954358</v>
       </c>
       <c r="M5" s="20">
         <f t="shared" si="2"/>
-        <v>40.31028138</v>
+        <v>20.73219999</v>
       </c>
       <c r="O5" s="31"/>
     </row>
@@ -2300,7 +2247,8 @@
         <v>14</v>
       </c>
       <c r="F6" s="16">
-        <v>507.622113409045</v>
+        <f>5.03501136998037*100</f>
+        <v>503.501137</v>
       </c>
       <c r="G6" s="19">
         <v>70.0</v>
@@ -2324,7 +2272,7 @@
       </c>
       <c r="M6" s="20">
         <f t="shared" si="2"/>
-        <v>144.8361095</v>
+        <v>146.0215412</v>
       </c>
     </row>
     <row r="7">
@@ -2338,13 +2286,14 @@
         <v>45677.0</v>
       </c>
       <c r="D7" s="15">
-        <v>1551.0</v>
+        <v>281.0</v>
       </c>
       <c r="E7" s="15" t="s">
         <v>14</v>
       </c>
       <c r="F7" s="16">
-        <v>272.560347757221</v>
+        <f>2.76792853614368*100</f>
+        <v>276.7928536</v>
       </c>
       <c r="G7" s="17">
         <v>10.0</v>
@@ -2353,22 +2302,22 @@
         <v>70.0</v>
       </c>
       <c r="I7" s="17">
-        <v>45.0</v>
+        <v>70.0</v>
       </c>
       <c r="J7" s="25">
         <f t="shared" si="1"/>
-        <v>41.66666667</v>
+        <v>50</v>
       </c>
       <c r="K7" s="27">
         <f>J7*'Data preparation'!$C$2</f>
-        <v>10.41666667</v>
+        <v>12.5</v>
       </c>
       <c r="L7" s="19">
-        <v>1944.23207418205</v>
+        <v>13938.355259875</v>
       </c>
       <c r="M7" s="20">
         <f t="shared" si="2"/>
-        <v>7.133216883</v>
+        <v>50.3566298</v>
       </c>
     </row>
     <row r="8">
@@ -2388,7 +2337,8 @@
         <v>14</v>
       </c>
       <c r="F8" s="16">
-        <v>331.827702137116</v>
+        <f>4.33116583093229*100</f>
+        <v>433.1165831</v>
       </c>
       <c r="G8" s="17">
         <v>45.0</v>
@@ -2397,22 +2347,22 @@
         <v>10.0</v>
       </c>
       <c r="I8" s="17">
-        <v>10.0</v>
+        <v>25.0</v>
       </c>
       <c r="J8" s="20">
         <f t="shared" si="1"/>
-        <v>21.66666667</v>
+        <v>26.66666667</v>
       </c>
       <c r="K8" s="27">
         <f>J8*'Data preparation'!$C$2</f>
-        <v>5.416666667</v>
+        <v>6.666666667</v>
       </c>
       <c r="L8" s="19">
-        <v>2994.68938021348</v>
+        <v>5748.94662953238</v>
       </c>
       <c r="M8" s="20">
         <f t="shared" si="2"/>
-        <v>9.024832348</v>
+        <v>13.27343919</v>
       </c>
     </row>
     <row r="9" ht="20.25" customHeight="1">
@@ -13277,7 +13227,7 @@
       </c>
       <c r="C3" s="26">
         <f>AVERAGE('Modelos actuales'!K4:K8)</f>
-        <v>9.333333333</v>
+        <v>10</v>
       </c>
       <c r="L3" s="112"/>
       <c r="P3" s="112"/>
@@ -14578,7 +14528,7 @@
       <c r="C37" s="40"/>
       <c r="D37" s="127">
         <f>AVERAGE(D39:D1775)</f>
-        <v>5.495813953</v>
+        <v>4.334852941</v>
       </c>
       <c r="G37" s="35" t="s">
         <v>36</v>
@@ -14647,7 +14597,7 @@
       </c>
       <c r="D39" s="119">
         <f t="shared" ref="D39:D221" si="17">IF(COUNTA(C39)=1,C39/1,"")</f>
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="G39" s="35" t="s">
         <v>28</v>
@@ -14685,7 +14635,7 @@
       </c>
       <c r="D40" s="119">
         <f t="shared" si="17"/>
-        <v>0.08</v>
+        <v>2.39</v>
       </c>
       <c r="G40" s="35" t="s">
         <v>24</v>
@@ -14723,7 +14673,7 @@
       </c>
       <c r="D41" s="119">
         <f t="shared" si="17"/>
-        <v>0.86</v>
+        <v>0.37</v>
       </c>
       <c r="P41" s="116">
         <v>0.0</v>
@@ -14751,11 +14701,11 @@
     </row>
     <row r="42">
       <c r="C42" s="130" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D42" s="119">
         <f t="shared" si="17"/>
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="P42" s="116">
         <v>2.0</v>
@@ -14783,11 +14733,11 @@
     </row>
     <row r="43">
       <c r="C43" s="130" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D43" s="119">
         <f t="shared" si="17"/>
-        <v>8.96</v>
+        <v>6.63</v>
       </c>
       <c r="P43" s="116">
         <v>1.0</v>
@@ -14815,11 +14765,11 @@
     </row>
     <row r="44">
       <c r="C44" s="130" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D44" s="119">
         <f t="shared" si="17"/>
-        <v>9.16</v>
+        <v>6.25</v>
       </c>
       <c r="P44" s="116">
         <v>2.0</v>
@@ -14845,11 +14795,11 @@
     </row>
     <row r="45">
       <c r="C45" s="130" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D45" s="119">
         <f t="shared" si="17"/>
-        <v>9.83</v>
+        <v>2.45</v>
       </c>
       <c r="P45" s="116">
         <v>1.0</v>
@@ -14863,17 +14813,17 @@
     </row>
     <row r="46">
       <c r="C46" s="130" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D46" s="119">
         <f t="shared" si="17"/>
-        <v>4.55</v>
+        <v>1.66</v>
       </c>
       <c r="G46" s="90" t="s">
+        <v>176</v>
+      </c>
+      <c r="H46" s="90" t="s">
         <v>177</v>
-      </c>
-      <c r="H46" s="90" t="s">
-        <v>178</v>
       </c>
       <c r="P46" s="116">
         <v>0.0</v>
@@ -14887,11 +14837,11 @@
     </row>
     <row r="47">
       <c r="C47" s="130" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D47" s="119">
         <f t="shared" si="17"/>
-        <v>6.78</v>
+        <v>2.82</v>
       </c>
       <c r="G47" s="95" t="s">
         <v>37</v>
@@ -14917,11 +14867,11 @@
     </row>
     <row r="48">
       <c r="C48" s="130" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D48" s="119">
         <f t="shared" si="17"/>
-        <v>5.35</v>
+        <v>1.16</v>
       </c>
       <c r="G48" s="95" t="s">
         <v>36</v>
@@ -14930,7 +14880,7 @@
         <v>0.36678739680281</v>
       </c>
       <c r="J48" s="42" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K48" s="117">
         <f>AVERAGE(H47:H51)</f>
@@ -14954,11 +14904,11 @@
     </row>
     <row r="49">
       <c r="C49" s="130" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D49" s="119">
         <f t="shared" si="17"/>
-        <v>9.07</v>
+        <v>2.34</v>
       </c>
       <c r="G49" s="95" t="s">
         <v>27</v>
@@ -14967,7 +14917,7 @@
         <v>0.142870351877935</v>
       </c>
       <c r="J49" s="42" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K49" s="117">
         <f>MEDIAN(H47:H51)</f>
@@ -14991,11 +14941,11 @@
     </row>
     <row r="50">
       <c r="C50" s="130" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D50" s="119">
         <f t="shared" si="17"/>
-        <v>9.62</v>
+        <v>5.55</v>
       </c>
       <c r="G50" s="95" t="s">
         <v>28</v>
@@ -15004,7 +14954,7 @@
         <v>0.497437843674554</v>
       </c>
       <c r="J50" s="42" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K50" s="117">
         <f>PERCENTILE(H47:H51,0.25)</f>
@@ -15028,11 +14978,11 @@
     </row>
     <row r="51">
       <c r="C51" s="130" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D51" s="119">
         <f t="shared" si="17"/>
-        <v>6.23</v>
+        <v>6.52</v>
       </c>
       <c r="G51" s="95" t="s">
         <v>24</v>
@@ -15041,7 +14991,7 @@
         <v>0.247446036291655</v>
       </c>
       <c r="J51" s="42" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="K51" s="117">
         <f>PERCENTILE(H47:H51,0.75)</f>
@@ -15065,11 +15015,11 @@
     </row>
     <row r="52">
       <c r="C52" s="130" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D52" s="119">
         <f t="shared" si="17"/>
-        <v>6.67</v>
+        <v>9.11</v>
       </c>
       <c r="P52" s="116">
         <v>0.0</v>
@@ -15089,11 +15039,11 @@
     </row>
     <row r="53">
       <c r="C53" s="130" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="D53" s="119">
         <f t="shared" si="17"/>
-        <v>8.96</v>
+        <v>8.92</v>
       </c>
       <c r="P53" s="116">
         <v>0.0</v>
@@ -15117,7 +15067,7 @@
       </c>
       <c r="D54" s="119">
         <f t="shared" si="17"/>
-        <v>7.71</v>
+        <v>5.46</v>
       </c>
       <c r="P54" s="116">
         <v>2.0</v>
@@ -15141,7 +15091,7 @@
       </c>
       <c r="D55" s="119">
         <f t="shared" si="17"/>
-        <v>7.62</v>
+        <v>2.49</v>
       </c>
       <c r="P55" s="116">
         <v>0.0</v>
@@ -15165,7 +15115,7 @@
       </c>
       <c r="D56" s="119">
         <f t="shared" si="17"/>
-        <v>8.13</v>
+        <v>4.97</v>
       </c>
       <c r="P56" s="116">
         <v>0.0</v>
@@ -15189,7 +15139,7 @@
       </c>
       <c r="D57" s="119">
         <f t="shared" si="17"/>
-        <v>7.73</v>
+        <v>4.98</v>
       </c>
       <c r="P57" s="116">
         <v>2.0</v>
@@ -15213,7 +15163,7 @@
       </c>
       <c r="D58" s="119">
         <f t="shared" si="17"/>
-        <v>7.8</v>
+        <v>4.46</v>
       </c>
       <c r="G58" s="132" t="s">
         <v>194</v>
@@ -15241,7 +15191,7 @@
       </c>
       <c r="D59" s="119">
         <f t="shared" si="17"/>
-        <v>7.94</v>
+        <v>5.12</v>
       </c>
       <c r="G59" s="133"/>
       <c r="H59" s="134" t="s">
@@ -15269,7 +15219,7 @@
       </c>
       <c r="D60" s="119">
         <f t="shared" si="17"/>
-        <v>8.21</v>
+        <v>4.95</v>
       </c>
       <c r="G60" s="133"/>
       <c r="H60" s="134" t="s">
@@ -15297,7 +15247,7 @@
       </c>
       <c r="D61" s="119">
         <f t="shared" si="17"/>
-        <v>8.04</v>
+        <v>4.85</v>
       </c>
       <c r="G61" s="133"/>
       <c r="H61" s="134" t="s">
@@ -15321,15 +15271,15 @@
     </row>
     <row r="62">
       <c r="C62" s="130" t="s">
-        <v>201</v>
+        <v>159</v>
       </c>
       <c r="D62" s="119">
         <f t="shared" si="17"/>
-        <v>7.59</v>
+        <v>4.73</v>
       </c>
       <c r="G62" s="133"/>
       <c r="H62" s="134" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P62" s="116">
         <v>1.0</v>
@@ -15349,15 +15299,15 @@
     </row>
     <row r="63">
       <c r="C63" s="130" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D63" s="119">
         <f t="shared" si="17"/>
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="G63" s="133"/>
       <c r="H63" s="134" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="P63" s="116">
         <v>0.0</v>
@@ -15371,11 +15321,11 @@
     </row>
     <row r="64">
       <c r="C64" s="130" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D64" s="119">
         <f t="shared" si="17"/>
-        <v>2.54</v>
+        <v>1.4</v>
       </c>
       <c r="P64" s="116">
         <v>1.0</v>
@@ -15389,11 +15339,11 @@
     </row>
     <row r="65">
       <c r="C65" s="130" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D65" s="119">
         <f t="shared" si="17"/>
-        <v>4.3</v>
+        <v>2.19</v>
       </c>
       <c r="P65" s="116">
         <v>2.0</v>
@@ -15407,11 +15357,11 @@
     </row>
     <row r="66">
       <c r="C66" s="130" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D66" s="119">
         <f t="shared" si="17"/>
-        <v>3.91</v>
+        <v>0.49</v>
       </c>
       <c r="P66" s="116">
         <v>0.0</v>
@@ -15425,11 +15375,11 @@
     </row>
     <row r="67">
       <c r="C67" s="130" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D67" s="119">
         <f t="shared" si="17"/>
-        <v>11.47</v>
+        <v>0.05</v>
       </c>
       <c r="P67" s="116">
         <v>0.0</v>
@@ -15443,11 +15393,11 @@
     </row>
     <row r="68">
       <c r="C68" s="130" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D68" s="119">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="P68" s="116">
         <v>1.0</v>
@@ -15461,11 +15411,11 @@
     </row>
     <row r="69">
       <c r="C69" s="130" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D69" s="119">
         <f t="shared" si="17"/>
-        <v>10.36</v>
+        <v>6.81</v>
       </c>
       <c r="P69" s="116">
         <v>2.0</v>
@@ -15479,11 +15429,11 @@
     </row>
     <row r="70">
       <c r="C70" s="130" t="s">
-        <v>211</v>
+        <v>189</v>
       </c>
       <c r="D70" s="119">
         <f t="shared" si="17"/>
-        <v>10.91</v>
+        <v>5.46</v>
       </c>
       <c r="P70" s="116">
         <v>1.0</v>
@@ -15497,11 +15447,11 @@
     </row>
     <row r="71">
       <c r="C71" s="130" t="s">
-        <v>212</v>
+        <v>159</v>
       </c>
       <c r="D71" s="119">
         <f t="shared" si="17"/>
-        <v>1.95</v>
+        <v>4.73</v>
       </c>
       <c r="F71" s="135"/>
       <c r="P71" s="116">
@@ -15516,11 +15466,11 @@
     </row>
     <row r="72">
       <c r="C72" s="130" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D72" s="119">
         <f t="shared" si="17"/>
-        <v>9.68</v>
+        <v>5.65</v>
       </c>
       <c r="P72" s="116">
         <v>0.0</v>
@@ -15534,11 +15484,11 @@
     </row>
     <row r="73">
       <c r="C73" s="130" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D73" s="119">
         <f t="shared" si="17"/>
-        <v>9.01</v>
+        <v>6.19</v>
       </c>
       <c r="P73" s="116">
         <v>1.0</v>
@@ -15552,11 +15502,11 @@
     </row>
     <row r="74">
       <c r="C74" s="130" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D74" s="119">
         <f t="shared" si="17"/>
-        <v>9.76</v>
+        <v>1.62</v>
       </c>
       <c r="P74" s="116">
         <v>0.0</v>
@@ -15570,11 +15520,11 @@
     </row>
     <row r="75">
       <c r="C75" s="130" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D75" s="119">
         <f t="shared" si="17"/>
-        <v>7.88</v>
+        <v>6.58</v>
       </c>
       <c r="P75" s="116">
         <v>1.0</v>
@@ -15588,11 +15538,11 @@
     </row>
     <row r="76">
       <c r="C76" s="130" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="D76" s="119">
         <f t="shared" si="17"/>
-        <v>13.76</v>
+        <v>6.58</v>
       </c>
       <c r="P76" s="116">
         <v>0.0</v>
@@ -15606,11 +15556,11 @@
     </row>
     <row r="77">
       <c r="C77" s="130" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="D77" s="119">
         <f t="shared" si="17"/>
-        <v>13.51</v>
+        <v>6.08</v>
       </c>
       <c r="P77" s="116">
         <v>0.0</v>
@@ -15624,11 +15574,11 @@
     </row>
     <row r="78">
       <c r="C78" s="130" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="D78" s="119">
         <f t="shared" si="17"/>
-        <v>1.98</v>
+        <v>1.06</v>
       </c>
       <c r="P78" s="116">
         <v>1.0</v>
@@ -15642,11 +15592,11 @@
     </row>
     <row r="79">
       <c r="C79" s="130" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="D79" s="119">
         <f t="shared" si="17"/>
-        <v>2.45</v>
+        <v>1.48</v>
       </c>
       <c r="P79" s="116">
         <v>2.0</v>
@@ -15660,11 +15610,11 @@
     </row>
     <row r="80">
       <c r="C80" s="130" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="D80" s="119">
         <f t="shared" si="17"/>
-        <v>2.28</v>
+        <v>1.45</v>
       </c>
       <c r="P80" s="116">
         <v>1.0</v>
@@ -15678,11 +15628,11 @@
     </row>
     <row r="81">
       <c r="C81" s="130" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="D81" s="119">
         <f t="shared" si="17"/>
-        <v>2.29</v>
+        <v>1.6</v>
       </c>
       <c r="P81" s="116">
         <v>2.0</v>
@@ -15696,11 +15646,11 @@
     </row>
     <row r="82">
       <c r="C82" s="130" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D82" s="119">
         <f t="shared" si="17"/>
-        <v>0.1</v>
+        <v>1.89</v>
       </c>
       <c r="P82" s="116">
         <v>1.0</v>
@@ -15714,11 +15664,11 @@
     </row>
     <row r="83">
       <c r="C83" s="130" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="D83" s="119">
         <f t="shared" si="17"/>
-        <v>2.55</v>
+        <v>1.28</v>
       </c>
       <c r="P83" s="116">
         <v>0.0</v>
@@ -15732,11 +15682,11 @@
     </row>
     <row r="84">
       <c r="C84" s="130" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D84" s="119">
         <f t="shared" si="17"/>
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="P84" s="116">
         <v>1.0</v>
@@ -15750,11 +15700,11 @@
     </row>
     <row r="85">
       <c r="C85" s="130" t="s">
-        <v>179</v>
+        <v>222</v>
       </c>
       <c r="D85" s="119">
         <f t="shared" si="17"/>
-        <v>6.78</v>
+        <v>1.75</v>
       </c>
       <c r="P85" s="116">
         <v>0.0</v>
@@ -15768,11 +15718,11 @@
     </row>
     <row r="86">
       <c r="C86" s="130" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="D86" s="119">
         <f t="shared" si="17"/>
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="P86" s="116">
         <v>0.0</v>
@@ -15786,11 +15736,11 @@
     </row>
     <row r="87">
       <c r="C87" s="130" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="D87" s="119">
         <f t="shared" si="17"/>
-        <v>1.49</v>
+        <v>1.06</v>
       </c>
       <c r="P87" s="116">
         <v>1.0</v>
@@ -15804,11 +15754,11 @@
     </row>
     <row r="88">
       <c r="C88" s="130" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D88" s="119">
         <f t="shared" si="17"/>
-        <v>4.05</v>
+        <v>1.77</v>
       </c>
       <c r="P88" s="116">
         <v>2.0</v>
@@ -15822,11 +15772,11 @@
     </row>
     <row r="89">
       <c r="C89" s="130" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="D89" s="119">
         <f t="shared" si="17"/>
-        <v>7.19</v>
+        <v>1.74</v>
       </c>
       <c r="P89" s="116">
         <v>2.0</v>
@@ -15840,11 +15790,11 @@
     </row>
     <row r="90">
       <c r="C90" s="130" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="D90" s="119">
         <f t="shared" si="17"/>
-        <v>2.16</v>
+        <v>1.69</v>
       </c>
       <c r="P90" s="116">
         <v>1.0</v>
@@ -15858,11 +15808,11 @@
     </row>
     <row r="91">
       <c r="C91" s="130" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="D91" s="119">
         <f t="shared" si="17"/>
-        <v>2.46</v>
+        <v>1.59</v>
       </c>
       <c r="P91" s="116">
         <v>1.0</v>
@@ -15876,11 +15826,11 @@
     </row>
     <row r="92">
       <c r="C92" s="130" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="D92" s="119">
         <f t="shared" si="17"/>
-        <v>2.29</v>
+        <v>1.7</v>
       </c>
       <c r="P92" s="116">
         <v>2.0</v>
@@ -15894,11 +15844,11 @@
     </row>
     <row r="93">
       <c r="C93" s="130" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="D93" s="119">
         <f t="shared" si="17"/>
-        <v>7.75</v>
+        <v>1.87</v>
       </c>
       <c r="P93" s="116">
         <v>0.0</v>
@@ -15912,11 +15862,11 @@
     </row>
     <row r="94">
       <c r="C94" s="130" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D94" s="119">
         <f t="shared" si="17"/>
-        <v>8.36</v>
+        <v>1.14</v>
       </c>
       <c r="P94" s="116">
         <v>0.0</v>
@@ -15930,11 +15880,11 @@
     </row>
     <row r="95">
       <c r="C95" s="130" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="D95" s="119">
         <f t="shared" si="17"/>
-        <v>4.22</v>
+        <v>1.19</v>
       </c>
       <c r="P95" s="116">
         <v>1.0</v>
@@ -15948,11 +15898,11 @@
     </row>
     <row r="96">
       <c r="C96" s="130" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D96" s="119">
         <f t="shared" si="17"/>
-        <v>8</v>
+        <v>1.21</v>
       </c>
       <c r="P96" s="116">
         <v>2.0</v>
@@ -15966,11 +15916,11 @@
     </row>
     <row r="97">
       <c r="C97" s="130" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="D97" s="119">
         <f t="shared" si="17"/>
-        <v>8.33</v>
+        <v>4.59</v>
       </c>
       <c r="P97" s="116">
         <v>0.0</v>
@@ -15984,11 +15934,11 @@
     </row>
     <row r="98">
       <c r="C98" s="130" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D98" s="119">
         <f t="shared" si="17"/>
-        <v>7.89</v>
+        <v>10.91</v>
       </c>
       <c r="P98" s="116">
         <v>2.0</v>
@@ -16002,11 +15952,11 @@
     </row>
     <row r="99">
       <c r="C99" s="130" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D99" s="119">
         <f t="shared" si="17"/>
-        <v>4.83</v>
+        <v>9.79</v>
       </c>
       <c r="P99" s="116">
         <v>2.0</v>
@@ -16020,11 +15970,11 @@
     </row>
     <row r="100">
       <c r="C100" s="130" t="s">
-        <v>190</v>
+        <v>236</v>
       </c>
       <c r="D100" s="119">
         <f t="shared" si="17"/>
-        <v>7.62</v>
+        <v>10.92</v>
       </c>
       <c r="P100" s="116">
         <v>2.0</v>
@@ -16038,11 +15988,11 @@
     </row>
     <row r="101">
       <c r="C101" s="130" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D101" s="119">
         <f t="shared" si="17"/>
-        <v>3.08</v>
+        <v>13.09</v>
       </c>
       <c r="P101" s="116">
         <v>2.0</v>
@@ -16056,11 +16006,11 @@
     </row>
     <row r="102">
       <c r="C102" s="130" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D102" s="119">
         <f t="shared" si="17"/>
-        <v>6.35</v>
+        <v>13.14</v>
       </c>
       <c r="P102" s="116">
         <v>2.0</v>
@@ -16074,11 +16024,11 @@
     </row>
     <row r="103">
       <c r="C103" s="130" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D103" s="119">
         <f t="shared" si="17"/>
-        <v>3.42</v>
+        <v>10.26</v>
       </c>
       <c r="P103" s="116">
         <v>1.0</v>
@@ -16092,11 +16042,11 @@
     </row>
     <row r="104">
       <c r="C104" s="130" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D104" s="119">
         <f t="shared" si="17"/>
-        <v>5.68</v>
+        <v>11.82</v>
       </c>
       <c r="N104" s="136"/>
       <c r="P104" s="116">
@@ -16111,11 +16061,11 @@
     </row>
     <row r="105">
       <c r="C105" s="130" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D105" s="119">
         <f t="shared" si="17"/>
-        <v>6.46</v>
+        <v>10.88</v>
       </c>
       <c r="N105" s="21"/>
       <c r="P105" s="116">
@@ -16130,11 +16080,11 @@
     </row>
     <row r="106">
       <c r="C106" s="130" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D106" s="119">
         <f t="shared" si="17"/>
-        <v>6.97</v>
+        <v>10.81</v>
       </c>
       <c r="N106" s="21"/>
       <c r="P106" s="116">
@@ -16148,12 +16098,10 @@
       </c>
     </row>
     <row r="107">
-      <c r="C107" s="130" t="s">
-        <v>240</v>
-      </c>
-      <c r="D107" s="119">
+      <c r="C107" s="130"/>
+      <c r="D107" s="119" t="str">
         <f t="shared" si="17"/>
-        <v>6.35</v>
+        <v/>
       </c>
       <c r="N107" s="21"/>
       <c r="P107" s="116">
@@ -16167,12 +16115,10 @@
       </c>
     </row>
     <row r="108">
-      <c r="C108" s="130" t="s">
-        <v>245</v>
-      </c>
-      <c r="D108" s="119">
+      <c r="C108" s="130"/>
+      <c r="D108" s="119" t="str">
         <f t="shared" si="17"/>
-        <v>6.55</v>
+        <v/>
       </c>
       <c r="N108" s="21"/>
       <c r="P108" s="116">
@@ -16186,12 +16132,10 @@
       </c>
     </row>
     <row r="109">
-      <c r="C109" s="130" t="s">
-        <v>246</v>
-      </c>
-      <c r="D109" s="119">
+      <c r="C109" s="130"/>
+      <c r="D109" s="119" t="str">
         <f t="shared" si="17"/>
-        <v>6.13</v>
+        <v/>
       </c>
       <c r="N109" s="21"/>
       <c r="P109" s="116">
@@ -16205,12 +16149,10 @@
       </c>
     </row>
     <row r="110">
-      <c r="C110" s="130" t="s">
-        <v>247</v>
-      </c>
-      <c r="D110" s="119">
+      <c r="C110" s="130"/>
+      <c r="D110" s="119" t="str">
         <f t="shared" si="17"/>
-        <v>3.44</v>
+        <v/>
       </c>
       <c r="N110" s="21"/>
       <c r="P110" s="116">
@@ -16224,12 +16166,10 @@
       </c>
     </row>
     <row r="111">
-      <c r="C111" s="130" t="s">
-        <v>248</v>
-      </c>
-      <c r="D111" s="119">
+      <c r="C111" s="130"/>
+      <c r="D111" s="119" t="str">
         <f t="shared" si="17"/>
-        <v>7.03</v>
+        <v/>
       </c>
       <c r="N111" s="21"/>
       <c r="P111" s="116">
@@ -16243,12 +16183,10 @@
       </c>
     </row>
     <row r="112">
-      <c r="C112" s="130" t="s">
-        <v>249</v>
-      </c>
-      <c r="D112" s="119">
+      <c r="C112" s="130"/>
+      <c r="D112" s="119" t="str">
         <f t="shared" si="17"/>
-        <v>2.22</v>
+        <v/>
       </c>
       <c r="P112" s="116">
         <v>1.0</v>
@@ -16261,12 +16199,10 @@
       </c>
     </row>
     <row r="113">
-      <c r="C113" s="130" t="s">
-        <v>250</v>
-      </c>
-      <c r="D113" s="119">
+      <c r="C113" s="130"/>
+      <c r="D113" s="119" t="str">
         <f t="shared" si="17"/>
-        <v>2.49</v>
+        <v/>
       </c>
       <c r="P113" s="116">
         <v>0.0</v>
@@ -16279,12 +16215,10 @@
       </c>
     </row>
     <row r="114">
-      <c r="C114" s="130" t="s">
-        <v>251</v>
-      </c>
-      <c r="D114" s="119">
+      <c r="C114" s="130"/>
+      <c r="D114" s="119" t="str">
         <f t="shared" si="17"/>
-        <v>5.89</v>
+        <v/>
       </c>
       <c r="P114" s="116">
         <v>1.0</v>
@@ -16297,12 +16231,10 @@
       </c>
     </row>
     <row r="115">
-      <c r="C115" s="130" t="s">
-        <v>252</v>
-      </c>
-      <c r="D115" s="119">
+      <c r="C115" s="130"/>
+      <c r="D115" s="119" t="str">
         <f t="shared" si="17"/>
-        <v>4.85</v>
+        <v/>
       </c>
       <c r="P115" s="116">
         <v>1.0</v>
@@ -16315,12 +16247,10 @@
       </c>
     </row>
     <row r="116">
-      <c r="C116" s="130" t="s">
-        <v>253</v>
-      </c>
-      <c r="D116" s="119">
+      <c r="C116" s="130"/>
+      <c r="D116" s="119" t="str">
         <f t="shared" si="17"/>
-        <v>2.86</v>
+        <v/>
       </c>
       <c r="P116" s="116">
         <v>1.0</v>
@@ -16333,12 +16263,10 @@
       </c>
     </row>
     <row r="117">
-      <c r="C117" s="130" t="s">
-        <v>254</v>
-      </c>
-      <c r="D117" s="119">
+      <c r="C117" s="130"/>
+      <c r="D117" s="119" t="str">
         <f t="shared" si="17"/>
-        <v>2.62</v>
+        <v/>
       </c>
       <c r="P117" s="137"/>
       <c r="AE117" s="42">
@@ -16349,12 +16277,10 @@
       </c>
     </row>
     <row r="118">
-      <c r="C118" s="130" t="s">
-        <v>255</v>
-      </c>
-      <c r="D118" s="119">
+      <c r="C118" s="130"/>
+      <c r="D118" s="119" t="str">
         <f t="shared" si="17"/>
-        <v>2.98</v>
+        <v/>
       </c>
       <c r="P118" s="137"/>
       <c r="AE118" s="42">
@@ -16365,12 +16291,10 @@
       </c>
     </row>
     <row r="119">
-      <c r="C119" s="130" t="s">
-        <v>256</v>
-      </c>
-      <c r="D119" s="119">
+      <c r="C119" s="130"/>
+      <c r="D119" s="119" t="str">
         <f t="shared" si="17"/>
-        <v>3</v>
+        <v/>
       </c>
       <c r="P119" s="137"/>
       <c r="AE119" s="42">
@@ -16381,12 +16305,10 @@
       </c>
     </row>
     <row r="120">
-      <c r="C120" s="130" t="s">
-        <v>257</v>
-      </c>
-      <c r="D120" s="119">
+      <c r="C120" s="130"/>
+      <c r="D120" s="119" t="str">
         <f t="shared" si="17"/>
-        <v>2.85</v>
+        <v/>
       </c>
       <c r="P120" s="137"/>
       <c r="AE120" s="42">
@@ -16397,12 +16319,10 @@
       </c>
     </row>
     <row r="121">
-      <c r="C121" s="130" t="s">
-        <v>256</v>
-      </c>
-      <c r="D121" s="119">
+      <c r="C121" s="130"/>
+      <c r="D121" s="119" t="str">
         <f t="shared" si="17"/>
-        <v>3</v>
+        <v/>
       </c>
       <c r="P121" s="137"/>
       <c r="AE121" s="42">
@@ -16413,12 +16333,10 @@
       </c>
     </row>
     <row r="122">
-      <c r="C122" s="130" t="s">
-        <v>258</v>
-      </c>
-      <c r="D122" s="119">
+      <c r="C122" s="130"/>
+      <c r="D122" s="119" t="str">
         <f t="shared" si="17"/>
-        <v>2.93</v>
+        <v/>
       </c>
       <c r="P122" s="137"/>
       <c r="AE122" s="42">
@@ -16429,12 +16347,10 @@
       </c>
     </row>
     <row r="123">
-      <c r="C123" s="130" t="s">
-        <v>256</v>
-      </c>
-      <c r="D123" s="119">
+      <c r="C123" s="130"/>
+      <c r="D123" s="119" t="str">
         <f t="shared" si="17"/>
-        <v>3</v>
+        <v/>
       </c>
       <c r="P123" s="137"/>
       <c r="AE123" s="42">
@@ -16445,12 +16361,10 @@
       </c>
     </row>
     <row r="124">
-      <c r="C124" s="130" t="s">
-        <v>259</v>
-      </c>
-      <c r="D124" s="119">
+      <c r="C124" s="130"/>
+      <c r="D124" s="119" t="str">
         <f t="shared" si="17"/>
-        <v>2.99</v>
+        <v/>
       </c>
       <c r="P124" s="137"/>
       <c r="AE124" s="42">
@@ -38898,14 +38812,14 @@
     <row r="1">
       <c r="A1" s="99"/>
       <c r="B1" s="140" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="C1" s="141"/>
       <c r="D1" s="141"/>
       <c r="E1" s="141"/>
       <c r="F1" s="141"/>
       <c r="G1" s="142" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
       <c r="H1" s="141"/>
       <c r="I1" s="141"/>
@@ -38933,19 +38847,19 @@
         <v>3</v>
       </c>
       <c r="B2" s="144" t="s">
-        <v>262</v>
+        <v>245</v>
       </c>
       <c r="C2" s="145" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="D2" s="145" t="s">
         <v>165</v>
       </c>
       <c r="E2" s="145" t="s">
-        <v>264</v>
+        <v>247</v>
       </c>
       <c r="F2" s="146" t="s">
-        <v>265</v>
+        <v>248</v>
       </c>
       <c r="G2" s="144">
         <v>1.0</v>
@@ -38957,25 +38871,25 @@
         <v>2.0</v>
       </c>
       <c r="J2" s="145" t="s">
-        <v>266</v>
+        <v>249</v>
       </c>
       <c r="K2" s="147" t="s">
-        <v>267</v>
+        <v>250</v>
       </c>
       <c r="L2" s="145" t="s">
-        <v>268</v>
+        <v>251</v>
       </c>
       <c r="M2" s="148" t="s">
-        <v>269</v>
+        <v>252</v>
       </c>
       <c r="N2" s="95" t="s">
-        <v>270</v>
+        <v>253</v>
       </c>
       <c r="O2" s="95" t="s">
-        <v>271</v>
+        <v>254</v>
       </c>
       <c r="P2" s="95" t="s">
-        <v>272</v>
+        <v>255</v>
       </c>
       <c r="Q2" s="9"/>
       <c r="R2" s="9"/>
@@ -39758,7 +39672,7 @@
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
       <c r="G27" s="161" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
       <c r="H27" s="9"/>
       <c r="I27" s="9"/>
@@ -39819,7 +39733,7 @@
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
       <c r="D29" s="5" t="s">
-        <v>274</v>
+        <v>257</v>
       </c>
       <c r="E29" s="5">
         <f>J29</f>
@@ -39841,10 +39755,10 @@
       </c>
       <c r="K29" s="9"/>
       <c r="L29" s="89" t="s">
-        <v>275</v>
+        <v>258</v>
       </c>
       <c r="M29" s="89" t="s">
-        <v>276</v>
+        <v>259</v>
       </c>
       <c r="O29" s="5">
         <v>1.0</v>
@@ -39980,7 +39894,7 @@
       <c r="E33" s="9"/>
       <c r="F33" s="9"/>
       <c r="G33" s="114" t="s">
-        <v>277</v>
+        <v>260</v>
       </c>
       <c r="J33" s="9"/>
       <c r="K33" s="9"/>
@@ -40157,7 +40071,7 @@
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
       <c r="F38" s="5" t="s">
-        <v>278</v>
+        <v>261</v>
       </c>
       <c r="G38" s="164">
         <f t="shared" ref="G38:I38" si="8">G30-G35</f>

--- a/data/df_best_models.xlsx
+++ b/data/df_best_models.xlsx
@@ -260,7 +260,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="309">
   <si>
     <t>id_country</t>
   </si>
@@ -329,9 +329,6 @@
   </si>
   <si>
     <t>france</t>
-  </si>
-  <si>
-    <t>L</t>
   </si>
   <si>
     <t>germany</t>
@@ -2437,26 +2434,26 @@
         <v>45693.0</v>
       </c>
       <c r="D4" s="15">
-        <v>344.0</v>
+        <v>332.0</v>
       </c>
       <c r="E4" s="15" t="s">
         <v>18</v>
       </c>
       <c r="F4" s="16">
-        <v>55.1767676767676</v>
+        <v>54.7438672438672</v>
       </c>
       <c r="G4" s="17">
-        <f>2.56753805471583*100</f>
-        <v>256.7538055</v>
+        <f>3.46734255670938*100</f>
+        <v>346.7342557</v>
       </c>
       <c r="H4" s="18">
         <v>10.0</v>
       </c>
       <c r="I4" s="18">
-        <v>45.0</v>
+        <v>25.0</v>
       </c>
       <c r="J4" s="18">
-        <v>25.0</v>
+        <v>10.0</v>
       </c>
       <c r="K4" s="18" t="s">
         <v>21</v>
@@ -2469,18 +2466,18 @@
       </c>
       <c r="N4" s="20">
         <f t="shared" ref="N4:N8" si="1">AVERAGE(H4:J4)</f>
-        <v>26.66666667</v>
+        <v>15</v>
       </c>
       <c r="O4" s="27">
         <f>N4*'Data preparation'!$C$2</f>
-        <v>6.666666667</v>
+        <v>3.75</v>
       </c>
       <c r="P4" s="16">
-        <v>5526.8335588928</v>
+        <v>2219.11264327355</v>
       </c>
       <c r="Q4" s="20">
         <f t="shared" ref="Q4:Q8" si="2">P4/G4</f>
-        <v>21.52580971</v>
+        <v>6.400038666</v>
       </c>
     </row>
     <row r="5">
@@ -2507,7 +2504,7 @@
         <v>139.3784085</v>
       </c>
       <c r="H5" s="16">
-        <v>70.0</v>
+        <v>45.0</v>
       </c>
       <c r="I5" s="16">
         <v>45.0</v>
@@ -2522,22 +2519,22 @@
         <v>21</v>
       </c>
       <c r="M5" s="16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N5" s="20">
         <f t="shared" si="1"/>
-        <v>41.66666667</v>
+        <v>33.33333333</v>
       </c>
       <c r="O5" s="27">
         <f>N5*'Data preparation'!$C$2</f>
-        <v>10.41666667</v>
+        <v>8.333333333</v>
       </c>
       <c r="P5" s="16">
-        <v>4868.12878004277</v>
+        <v>2572.90077073494</v>
       </c>
       <c r="Q5" s="20">
         <f t="shared" si="2"/>
-        <v>34.92742407</v>
+        <v>18.45982314</v>
       </c>
       <c r="S5" s="31"/>
     </row>
@@ -2546,7 +2543,7 @@
         <v>59.0</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C6" s="13">
         <v>45693.0</v>
@@ -2565,37 +2562,37 @@
         <v>601.6323262</v>
       </c>
       <c r="H6" s="16">
-        <v>70.0</v>
+        <v>45.0</v>
       </c>
       <c r="I6" s="16">
-        <v>45.0</v>
+        <v>25.0</v>
       </c>
       <c r="J6" s="16">
         <v>10.0</v>
       </c>
       <c r="K6" s="16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L6" s="16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="M6" s="16" t="s">
         <v>21</v>
       </c>
       <c r="N6" s="20">
         <f t="shared" si="1"/>
-        <v>41.66666667</v>
+        <v>26.66666667</v>
       </c>
       <c r="O6" s="27">
         <f>N6*'Data preparation'!$C$2</f>
-        <v>10.41666667</v>
+        <v>6.666666667</v>
       </c>
       <c r="P6" s="32">
-        <v>38220.1573794083</v>
+        <v>13978.9606210805</v>
       </c>
       <c r="Q6" s="20">
         <f t="shared" si="2"/>
-        <v>63.52743314</v>
+        <v>23.23505572</v>
       </c>
     </row>
     <row r="7">
@@ -2603,7 +2600,7 @@
         <v>77.0</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C7" s="13">
         <v>45693.0</v>
@@ -2631,7 +2628,7 @@
         <v>45.0</v>
       </c>
       <c r="K7" s="18" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L7" s="18" t="s">
         <v>21</v>
@@ -2639,7 +2636,7 @@
       <c r="M7" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="N7" s="25">
+      <c r="N7" s="20">
         <f t="shared" si="1"/>
         <v>31.66666667</v>
       </c>
@@ -2648,11 +2645,11 @@
         <v>7.916666667</v>
       </c>
       <c r="P7" s="16">
-        <v>2633.48953477897</v>
+        <v>2440.21825177097</v>
       </c>
       <c r="Q7" s="20">
         <f t="shared" si="2"/>
-        <v>11.35536811</v>
+        <v>10.52199986</v>
       </c>
     </row>
     <row r="8">
@@ -2660,13 +2657,13 @@
         <v>148.0</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C8" s="13">
         <v>45693.0</v>
       </c>
       <c r="D8" s="15">
-        <v>508.0</v>
+        <v>530.0</v>
       </c>
       <c r="E8" s="15" t="s">
         <v>18</v>
@@ -2741,9 +2738,6 @@
     <row r="12" ht="20.25" customHeight="1"/>
     <row r="13">
       <c r="A13" s="37"/>
-    </row>
-    <row r="19">
-      <c r="C19" s="38"/>
     </row>
     <row r="27">
       <c r="A27" s="37"/>
@@ -8978,6 +8972,16 @@
       <formula>"K"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="N4:N8">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF57BB8A"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
 </worksheet>
@@ -9095,7 +9099,7 @@
         <v>59.0</v>
       </c>
       <c r="B4" s="42" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C4" s="38">
         <v>45680.0</v>
@@ -9138,7 +9142,7 @@
         <v>77.0</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C5" s="13">
         <v>45677.0</v>
@@ -9183,7 +9187,7 @@
         <v>148.0</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C6" s="13">
         <v>45677.0</v>
@@ -9259,32 +9263,32 @@
     </row>
     <row r="11">
       <c r="E11" s="50" t="s">
+        <v>26</v>
+      </c>
+      <c r="L11" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="L11" s="42" t="s">
+      <c r="M11" s="44" t="s">
         <v>28</v>
       </c>
-      <c r="M11" s="44" t="s">
+      <c r="N11" s="51" t="s">
         <v>29</v>
-      </c>
-      <c r="N11" s="51" t="s">
-        <v>30</v>
       </c>
       <c r="O11" s="34"/>
       <c r="P11" s="34"/>
     </row>
     <row r="12">
       <c r="E12" s="50" t="s">
+        <v>30</v>
+      </c>
+      <c r="L12" s="42" t="s">
         <v>31</v>
       </c>
-      <c r="L12" s="42" t="s">
+      <c r="M12" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="M12" s="44" t="s">
+      <c r="N12" s="51" t="s">
         <v>33</v>
-      </c>
-      <c r="N12" s="51" t="s">
-        <v>34</v>
       </c>
       <c r="O12" s="34"/>
       <c r="P12" s="34"/>
@@ -9411,7 +9415,7 @@
         <v>59.0</v>
       </c>
       <c r="B18" s="42" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C18" s="38">
         <v>45680.0</v>
@@ -9452,7 +9456,7 @@
         <v>77.0</v>
       </c>
       <c r="B19" s="54" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C19" s="38">
         <v>45677.0</v>
@@ -9495,7 +9499,7 @@
         <v>148.0</v>
       </c>
       <c r="B20" s="42" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C20" s="38">
         <v>45677.0</v>
@@ -9540,49 +9544,49 @@
     </row>
     <row r="24">
       <c r="C24" s="35" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25">
       <c r="C25" s="47" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26">
       <c r="C26" s="55" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27">
       <c r="C27" s="56" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="28">
       <c r="C28" s="54" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="30">
       <c r="C30" s="57" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="31">
       <c r="C31" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="L31" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q31" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="L31" s="35" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q31" s="35" t="s">
+      <c r="Z31" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH31" s="35" t="s">
         <v>42</v>
-      </c>
-      <c r="Z31" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="AH31" s="35" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="32">
@@ -11562,7 +11566,7 @@
     </row>
     <row r="63">
       <c r="C63" s="35" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="65">
@@ -11582,19 +11586,19 @@
         <v>4</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I65" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J65" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="J65" s="4" t="s">
+      <c r="K65" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="K65" s="7" t="s">
+      <c r="L65" s="4" t="s">
         <v>47</v>
-      </c>
-      <c r="L65" s="4" t="s">
-        <v>48</v>
       </c>
       <c r="M65" s="67" t="s">
         <v>16</v>
@@ -11735,7 +11739,7 @@
         <v>59.0</v>
       </c>
       <c r="D70" s="23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E70" s="13">
         <v>45680.0</v>
@@ -11780,7 +11784,7 @@
         <v>77.0</v>
       </c>
       <c r="D71" s="23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E71" s="13">
         <v>45677.0</v>
@@ -11824,7 +11828,7 @@
         <v>148.0</v>
       </c>
       <c r="D72" s="23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E72" s="13">
         <v>45677.0</v>
@@ -11865,7 +11869,7 @@
     </row>
     <row r="76">
       <c r="C76" s="35" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="77">
@@ -11885,16 +11889,16 @@
         <v>4</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I77" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J77" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="J77" s="4" t="s">
+      <c r="K77" s="7" t="s">
         <v>46</v>
-      </c>
-      <c r="K77" s="7" t="s">
-        <v>47</v>
       </c>
       <c r="L77" s="4" t="s">
         <v>7</v>
@@ -12077,7 +12081,7 @@
         <v>59.0</v>
       </c>
       <c r="D82" s="23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E82" s="13">
         <v>45680.0</v>
@@ -12132,7 +12136,7 @@
         <v>77.0</v>
       </c>
       <c r="D83" s="23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E83" s="13">
         <v>45677.0</v>
@@ -12187,7 +12191,7 @@
         <v>148.0</v>
       </c>
       <c r="D84" s="23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E84" s="13">
         <v>45677.0</v>
@@ -12239,7 +12243,7 @@
     </row>
     <row r="94">
       <c r="C94" s="42" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="96">
@@ -12259,28 +12263,28 @@
         <v>4</v>
       </c>
       <c r="H96" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I96" s="4" t="s">
         <v>5</v>
       </c>
       <c r="J96" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K96" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="L96" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="L96" s="7" t="s">
+      <c r="M96" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="M96" s="7" t="s">
-        <v>53</v>
-      </c>
       <c r="N96" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="O96" s="7" t="s">
         <v>46</v>
-      </c>
-      <c r="O96" s="7" t="s">
-        <v>47</v>
       </c>
       <c r="P96" s="67" t="s">
         <v>16</v>
@@ -12480,7 +12484,7 @@
         <v>59.0</v>
       </c>
       <c r="D101" s="72" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E101" s="13">
         <v>45680.0</v>
@@ -12541,7 +12545,7 @@
         <v>77.0</v>
       </c>
       <c r="D102" s="72" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E102" s="13">
         <v>45677.0</v>
@@ -12602,7 +12606,7 @@
         <v>148.0</v>
       </c>
       <c r="D103" s="72" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E103" s="13">
         <v>45677.0</v>
@@ -12713,7 +12717,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="74" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B1" s="75"/>
       <c r="C1" s="75"/>
@@ -12736,54 +12740,54 @@
     <row r="2">
       <c r="A2" s="79"/>
       <c r="B2" s="80" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="80" t="s">
         <v>55</v>
       </c>
-      <c r="C2" s="80" t="s">
+      <c r="D2" s="81" t="s">
         <v>56</v>
       </c>
-      <c r="D2" s="81" t="s">
+      <c r="E2" s="81" t="s">
         <v>57</v>
       </c>
-      <c r="E2" s="81" t="s">
+      <c r="F2" s="80" t="s">
         <v>58</v>
-      </c>
-      <c r="F2" s="80" t="s">
-        <v>59</v>
       </c>
       <c r="G2" s="82" t="s">
         <v>6</v>
       </c>
       <c r="H2" s="82" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I2" s="82" t="s">
         <v>15</v>
       </c>
       <c r="J2" s="80"/>
       <c r="K2" s="80" t="s">
+        <v>60</v>
+      </c>
+      <c r="L2" s="80" t="s">
         <v>61</v>
       </c>
-      <c r="L2" s="80" t="s">
+      <c r="M2" s="83" t="s">
         <v>62</v>
       </c>
-      <c r="M2" s="83" t="s">
+      <c r="N2" s="82" t="s">
         <v>63</v>
       </c>
-      <c r="N2" s="82" t="s">
+      <c r="O2" s="82" t="s">
         <v>64</v>
       </c>
-      <c r="O2" s="82" t="s">
+      <c r="P2" s="82" t="s">
         <v>65</v>
-      </c>
-      <c r="P2" s="82" t="s">
-        <v>66</v>
       </c>
       <c r="U2" s="40"/>
       <c r="V2" s="35"/>
     </row>
     <row r="3">
       <c r="A3" s="84" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B3" s="23">
         <v>343.0</v>
@@ -12831,7 +12835,7 @@
     </row>
     <row r="4">
       <c r="A4" s="84" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B4" s="23">
         <v>1127.0</v>
@@ -12882,7 +12886,7 @@
     </row>
     <row r="5">
       <c r="A5" s="84" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B5" s="85">
         <v>1051.0</v>
@@ -12933,7 +12937,7 @@
     </row>
     <row r="6">
       <c r="A6" s="84" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B6" s="23">
         <v>622.0</v>
@@ -12981,7 +12985,7 @@
     </row>
     <row r="7">
       <c r="A7" s="84" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B7" s="23">
         <v>1447.0</v>
@@ -13041,7 +13045,7 @@
     <row r="10">
       <c r="A10" s="49"/>
       <c r="E10" s="42" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O10" s="43"/>
       <c r="P10" s="49"/>
@@ -13086,7 +13090,7 @@
     <row r="13">
       <c r="A13" s="31"/>
       <c r="E13" s="23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F13" s="15">
         <v>1051.0</v>
@@ -13102,7 +13106,7 @@
     <row r="14">
       <c r="A14" s="31"/>
       <c r="E14" s="23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F14" s="15">
         <v>47.0</v>
@@ -13122,7 +13126,7 @@
       <c r="C15" s="31"/>
       <c r="D15" s="31"/>
       <c r="E15" s="23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F15" s="15">
         <v>1447.0</v>
@@ -13172,7 +13176,7 @@
     <row r="18">
       <c r="A18" s="43"/>
       <c r="E18" s="42" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O18" s="43"/>
       <c r="P18" s="43"/>
@@ -13211,7 +13215,7 @@
     </row>
     <row r="21">
       <c r="E21" s="23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F21" s="15">
         <v>1051.0</v>
@@ -13222,7 +13226,7 @@
     </row>
     <row r="22">
       <c r="E22" s="23" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F22" s="15">
         <v>622.0</v>
@@ -13234,7 +13238,7 @@
     </row>
     <row r="23">
       <c r="E23" s="23" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F23" s="15">
         <v>1545.0</v>
@@ -13454,7 +13458,7 @@
         <v>59.0</v>
       </c>
       <c r="D37" s="72" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E37" s="13">
         <v>45680.0</v>
@@ -13499,7 +13503,7 @@
         <v>77.0</v>
       </c>
       <c r="D38" s="72" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E38" s="13">
         <v>45677.0</v>
@@ -13544,7 +13548,7 @@
         <v>148.0</v>
       </c>
       <c r="D39" s="72" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E39" s="13">
         <v>45677.0</v>
@@ -13752,13 +13756,13 @@
     </row>
     <row r="9">
       <c r="B9" s="42" t="s">
+        <v>68</v>
+      </c>
+      <c r="C9" s="42" t="s">
         <v>69</v>
       </c>
-      <c r="C9" s="42" t="s">
+      <c r="D9" s="42" t="s">
         <v>70</v>
-      </c>
-      <c r="D9" s="42" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="10">
@@ -13776,7 +13780,7 @@
         <v>-0.1658536585</v>
       </c>
       <c r="F10" s="42" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11">
@@ -13794,7 +13798,7 @@
         <v>-0.15</v>
       </c>
       <c r="F11" s="42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12">
@@ -13832,16 +13836,16 @@
     </row>
     <row r="16">
       <c r="H16" s="42" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17">
       <c r="G17" s="89"/>
       <c r="H17" s="35" t="s">
+        <v>74</v>
+      </c>
+      <c r="I17" s="35" t="s">
         <v>75</v>
-      </c>
-      <c r="I17" s="35" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -13855,13 +13859,13 @@
         <v>0.85</v>
       </c>
       <c r="G18" s="90" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H18" s="42">
         <v>332.0</v>
       </c>
       <c r="I18" s="91" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19">
@@ -13875,13 +13879,13 @@
         <v>0.81</v>
       </c>
       <c r="G19" s="90" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H19" s="42" t="s">
+        <v>77</v>
+      </c>
+      <c r="I19" s="42" t="s">
         <v>78</v>
-      </c>
-      <c r="I19" s="42" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="20">
@@ -13895,45 +13899,45 @@
         <v>0.89</v>
       </c>
       <c r="G20" s="90" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H20" s="42">
         <v>411.0</v>
       </c>
       <c r="I20" s="42" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21">
       <c r="G21" s="90" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H21" s="42" t="s">
+        <v>80</v>
+      </c>
+      <c r="I21" s="42" t="s">
         <v>81</v>
-      </c>
-      <c r="I21" s="42" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="22">
       <c r="G22" s="90" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H22" s="42" t="s">
+        <v>82</v>
+      </c>
+      <c r="I22" s="42" t="s">
         <v>83</v>
-      </c>
-      <c r="I22" s="42" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="24">
       <c r="I24" s="42" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25">
       <c r="I25" s="42" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="26">
@@ -13954,28 +13958,28 @@
     </row>
     <row r="30">
       <c r="I30" s="35" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M30" s="34"/>
       <c r="N30" s="34"/>
     </row>
     <row r="31">
       <c r="I31" s="35" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="M31" s="34"/>
       <c r="N31" s="34"/>
     </row>
     <row r="32">
       <c r="I32" s="42" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M32" s="34"/>
       <c r="N32" s="34"/>
     </row>
     <row r="33">
       <c r="I33" s="42" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M33" s="34"/>
       <c r="N33" s="34"/>
@@ -13986,7 +13990,7 @@
     </row>
     <row r="35">
       <c r="I35" s="42" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M35" s="34"/>
       <c r="N35" s="34"/>
@@ -14005,28 +14009,28 @@
     </row>
     <row r="39">
       <c r="I39" s="35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="M39" s="34"/>
       <c r="N39" s="34"/>
     </row>
     <row r="40">
       <c r="I40" s="42" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M40" s="34"/>
       <c r="N40" s="34"/>
     </row>
     <row r="41">
       <c r="I41" s="42" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M41" s="34"/>
       <c r="N41" s="34"/>
     </row>
     <row r="42">
       <c r="I42" s="57" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M42" s="34"/>
       <c r="N42" s="34"/>
@@ -14037,7 +14041,7 @@
     </row>
     <row r="44">
       <c r="I44" s="35" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -14064,146 +14068,146 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="42" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2">
       <c r="B2" s="9"/>
       <c r="C2" s="92" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E2" s="93"/>
       <c r="F2" s="94" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H2" s="93"/>
     </row>
     <row r="3">
       <c r="B3" s="95" t="s">
+        <v>99</v>
+      </c>
+      <c r="C3" s="96" t="s">
         <v>100</v>
       </c>
-      <c r="C3" s="96" t="s">
+      <c r="D3" s="95" t="s">
         <v>101</v>
       </c>
-      <c r="D3" s="95" t="s">
+      <c r="E3" s="97" t="s">
         <v>102</v>
       </c>
-      <c r="E3" s="97" t="s">
+      <c r="F3" s="95" t="s">
         <v>103</v>
       </c>
-      <c r="F3" s="95" t="s">
+      <c r="G3" s="95" t="s">
         <v>104</v>
       </c>
-      <c r="G3" s="95" t="s">
+      <c r="H3" s="95" t="s">
         <v>105</v>
-      </c>
-      <c r="H3" s="95" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="98" t="s">
+        <v>106</v>
+      </c>
+      <c r="C4" s="99" t="s">
         <v>107</v>
       </c>
-      <c r="C4" s="99" t="s">
+      <c r="D4" s="100" t="s">
         <v>108</v>
       </c>
-      <c r="D4" s="100" t="s">
+      <c r="E4" s="101" t="s">
         <v>109</v>
       </c>
-      <c r="E4" s="101" t="s">
+      <c r="F4" s="102" t="s">
         <v>110</v>
       </c>
-      <c r="F4" s="102" t="s">
+      <c r="G4" s="102" t="s">
         <v>111</v>
-      </c>
-      <c r="G4" s="102" t="s">
-        <v>112</v>
       </c>
       <c r="H4" s="100"/>
     </row>
     <row r="5">
       <c r="B5" s="98" t="s">
+        <v>112</v>
+      </c>
+      <c r="C5" s="103" t="s">
         <v>113</v>
-      </c>
-      <c r="C5" s="103" t="s">
-        <v>114</v>
       </c>
       <c r="D5" s="104"/>
       <c r="E5" s="101" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F5" s="105" t="s">
+        <v>114</v>
+      </c>
+      <c r="G5" s="106" t="s">
         <v>115</v>
-      </c>
-      <c r="G5" s="106" t="s">
-        <v>116</v>
       </c>
       <c r="H5" s="100"/>
     </row>
     <row r="6">
       <c r="B6" s="98" t="s">
+        <v>116</v>
+      </c>
+      <c r="C6" s="99" t="s">
+        <v>107</v>
+      </c>
+      <c r="D6" s="100" t="s">
         <v>117</v>
       </c>
-      <c r="C6" s="99" t="s">
-        <v>108</v>
-      </c>
-      <c r="D6" s="100" t="s">
+      <c r="E6" s="101" t="s">
+        <v>109</v>
+      </c>
+      <c r="F6" s="100" t="s">
         <v>118</v>
-      </c>
-      <c r="E6" s="101" t="s">
-        <v>110</v>
-      </c>
-      <c r="F6" s="100" t="s">
-        <v>119</v>
       </c>
       <c r="G6" s="100"/>
       <c r="H6" s="100"/>
     </row>
     <row r="7">
       <c r="B7" s="100" t="s">
+        <v>119</v>
+      </c>
+      <c r="C7" s="107" t="s">
         <v>120</v>
-      </c>
-      <c r="C7" s="107" t="s">
-        <v>121</v>
       </c>
       <c r="D7" s="100"/>
       <c r="E7" s="108" t="s">
+        <v>121</v>
+      </c>
+      <c r="F7" s="99" t="s">
         <v>122</v>
-      </c>
-      <c r="F7" s="99" t="s">
-        <v>123</v>
       </c>
       <c r="G7" s="100"/>
       <c r="H7" s="100" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="109" t="s">
+        <v>124</v>
+      </c>
+      <c r="C8" s="110" t="s">
         <v>125</v>
-      </c>
-      <c r="C8" s="110" t="s">
-        <v>126</v>
       </c>
       <c r="D8" s="111"/>
       <c r="E8" s="109" t="s">
+        <v>126</v>
+      </c>
+      <c r="F8" s="112" t="s">
         <v>127</v>
       </c>
-      <c r="F8" s="112" t="s">
+      <c r="G8" s="113" t="s">
         <v>128</v>
-      </c>
-      <c r="G8" s="113" t="s">
-        <v>129</v>
       </c>
       <c r="H8" s="111"/>
     </row>
     <row r="9">
       <c r="B9" s="23" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C9" s="114" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D9" s="79"/>
       <c r="E9" s="79"/>
@@ -14213,27 +14217,27 @@
     </row>
     <row r="10">
       <c r="B10" s="23" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C10" s="115"/>
       <c r="D10" s="79"/>
       <c r="E10" s="79"/>
       <c r="F10" s="115"/>
       <c r="G10" s="102" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H10" s="79"/>
     </row>
     <row r="11">
       <c r="B11" s="23" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C11" s="115"/>
       <c r="D11" s="79"/>
       <c r="E11" s="79"/>
       <c r="F11" s="115"/>
       <c r="G11" s="116" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H11" s="23"/>
     </row>
@@ -14271,7 +14275,7 @@
     <row r="2">
       <c r="A2" s="18"/>
       <c r="B2" s="94" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C2" s="18">
         <v>0.25</v>
@@ -14281,11 +14285,11 @@
     <row r="3">
       <c r="A3" s="18"/>
       <c r="B3" s="94" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C3" s="26">
         <f>AVERAGE('Modelos actuales'!O4:O8)</f>
-        <v>8.666666667</v>
+        <v>6.916666667</v>
       </c>
       <c r="L3" s="117"/>
       <c r="P3" s="117"/>
@@ -14296,7 +14300,7 @@
       <c r="L4" s="117"/>
       <c r="P4" s="117"/>
       <c r="AE4" s="42" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AF4" s="118">
         <f>CORREL(AE6:AE10000,AF6:AF10000)</f>
@@ -14306,50 +14310,50 @@
     <row r="5">
       <c r="A5" s="18"/>
       <c r="B5" s="117" t="s">
+        <v>136</v>
+      </c>
+      <c r="L5" s="117" t="s">
         <v>137</v>
       </c>
-      <c r="L5" s="117" t="s">
+      <c r="P5" s="117" t="s">
         <v>138</v>
       </c>
-      <c r="P5" s="117" t="s">
+      <c r="AE5" s="42" t="s">
         <v>139</v>
       </c>
-      <c r="AE5" s="42" t="s">
+      <c r="AF5" s="42" t="s">
         <v>140</v>
-      </c>
-      <c r="AF5" s="42" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="18"/>
       <c r="B6" s="42" t="s">
+        <v>141</v>
+      </c>
+      <c r="F6" s="42" t="s">
         <v>142</v>
-      </c>
-      <c r="F6" s="42" t="s">
-        <v>143</v>
       </c>
       <c r="K6" s="35"/>
       <c r="L6" s="35" t="s">
+        <v>143</v>
+      </c>
+      <c r="N6" s="35" t="s">
         <v>144</v>
       </c>
-      <c r="N6" s="35" t="s">
+      <c r="P6" s="35" t="s">
         <v>145</v>
       </c>
-      <c r="P6" s="35" t="s">
+      <c r="R6" s="35" t="s">
         <v>146</v>
       </c>
-      <c r="R6" s="35" t="s">
+      <c r="V6" s="35" t="s">
         <v>147</v>
       </c>
-      <c r="V6" s="35" t="s">
+      <c r="AA6" s="42" t="s">
         <v>148</v>
       </c>
-      <c r="AA6" s="42" t="s">
+      <c r="AB6" s="42" t="s">
         <v>149</v>
-      </c>
-      <c r="AB6" s="42" t="s">
-        <v>150</v>
       </c>
       <c r="AE6" s="42">
         <v>519.2</v>
@@ -14391,7 +14395,7 @@
         <v>0.5454545455</v>
       </c>
       <c r="AA7" s="42" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AB7" s="41">
         <f t="shared" ref="AB7:AB16" si="4">LEFT(REPLACE(AA7,1,1,""),FIND(",", AA7)-2)/1</f>
@@ -14407,14 +14411,14 @@
     <row r="8">
       <c r="A8" s="18"/>
       <c r="B8" s="122" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C8" s="123" t="str">
         <f t="shared" ref="C8:C17" si="5">REPLACE(B8,FIND(".",B8),1,",")*1</f>
         <v>#VALUE!</v>
       </c>
       <c r="F8" s="47" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G8" s="123" t="str">
         <f t="shared" ref="G8:G27" si="6">REPLACE(F8,FIND(".",F8),1,",")*1</f>
@@ -14449,7 +14453,7 @@
         <v>0.5263157895</v>
       </c>
       <c r="AA8" s="42" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AB8" s="41">
         <f t="shared" si="4"/>
@@ -14465,14 +14469,14 @@
     <row r="9">
       <c r="A9" s="18"/>
       <c r="B9" s="122" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C9" s="123" t="str">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="F9" s="47" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G9" s="123" t="str">
         <f t="shared" si="6"/>
@@ -14486,13 +14490,13 @@
       </c>
       <c r="K9" s="18"/>
       <c r="L9" s="119" t="s">
+        <v>156</v>
+      </c>
+      <c r="M9" s="119" t="s">
         <v>157</v>
       </c>
-      <c r="M9" s="119" t="s">
+      <c r="N9" s="35" t="s">
         <v>158</v>
-      </c>
-      <c r="N9" s="35" t="s">
-        <v>159</v>
       </c>
       <c r="P9" s="121">
         <v>1.0</v>
@@ -14516,7 +14520,7 @@
         <v>0.25</v>
       </c>
       <c r="AA9" s="42" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AB9" s="41">
         <f t="shared" si="4"/>
@@ -14532,14 +14536,14 @@
     <row r="10">
       <c r="A10" s="18"/>
       <c r="B10" s="124" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C10" s="123" t="str">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="F10" s="47" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G10" s="123" t="str">
         <f t="shared" si="6"/>
@@ -14576,7 +14580,7 @@
         <v>76</v>
       </c>
       <c r="AA10" s="42" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AB10" s="41">
         <f t="shared" si="4"/>
@@ -14591,14 +14595,14 @@
     </row>
     <row r="11">
       <c r="B11" s="122" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C11" s="123" t="str">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="F11" s="47" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G11" s="123" t="str">
         <f t="shared" si="6"/>
@@ -14627,7 +14631,7 @@
         <v>2.0</v>
       </c>
       <c r="AA11" s="42" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AB11" s="41">
         <f t="shared" si="4"/>
@@ -14642,14 +14646,14 @@
     </row>
     <row r="12">
       <c r="B12" s="124" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C12" s="123" t="str">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="F12" s="47" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G12" s="123" t="str">
         <f t="shared" si="6"/>
@@ -14678,7 +14682,7 @@
         <v>1.0</v>
       </c>
       <c r="AA12" s="42" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AB12" s="41">
         <f t="shared" si="4"/>
@@ -14693,14 +14697,14 @@
     </row>
     <row r="13">
       <c r="B13" s="122" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C13" s="123" t="str">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="F13" s="47" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G13" s="123" t="str">
         <f t="shared" si="6"/>
@@ -14730,16 +14734,16 @@
       <c r="Q13" s="40"/>
       <c r="R13" s="79"/>
       <c r="S13" s="84" t="s">
+        <v>170</v>
+      </c>
+      <c r="T13" s="84" t="s">
         <v>171</v>
       </c>
-      <c r="T13" s="84" t="s">
+      <c r="U13" s="84" t="s">
         <v>172</v>
       </c>
-      <c r="U13" s="84" t="s">
+      <c r="AA13" s="42" t="s">
         <v>173</v>
-      </c>
-      <c r="AA13" s="42" t="s">
-        <v>174</v>
       </c>
       <c r="AB13" s="41">
         <f t="shared" si="4"/>
@@ -14754,14 +14758,14 @@
     </row>
     <row r="14">
       <c r="B14" s="122" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C14" s="123" t="str">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="F14" s="47" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G14" s="123" t="str">
         <f t="shared" si="6"/>
@@ -14801,7 +14805,7 @@
         <v>11.0</v>
       </c>
       <c r="AA14" s="42" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AB14" s="41">
         <f t="shared" si="4"/>
@@ -14816,14 +14820,14 @@
     </row>
     <row r="15">
       <c r="B15" s="122" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C15" s="123" t="str">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="F15" s="47" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G15" s="123" t="str">
         <f t="shared" si="6"/>
@@ -14863,7 +14867,7 @@
         <v>13.0</v>
       </c>
       <c r="AA15" s="42" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AB15" s="41">
         <f t="shared" si="4"/>
@@ -14878,14 +14882,14 @@
     </row>
     <row r="16">
       <c r="B16" s="122" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C16" s="123" t="str">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="F16" s="47" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G16" s="123" t="str">
         <f t="shared" si="6"/>
@@ -14925,7 +14929,7 @@
         <v>12.0</v>
       </c>
       <c r="AA16" s="42" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AB16" s="41">
         <f t="shared" si="4"/>
@@ -14940,14 +14944,14 @@
     </row>
     <row r="17">
       <c r="B17" s="122" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C17" s="123" t="str">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="F17" s="47" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G17" s="123" t="str">
         <f t="shared" si="6"/>
@@ -14975,7 +14979,7 @@
         <v>1.0</v>
       </c>
       <c r="R17" s="84" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="S17" s="125">
         <f t="shared" ref="S17:U17" si="10">SUM(S14:S16)</f>
@@ -14998,7 +15002,7 @@
     </row>
     <row r="18">
       <c r="F18" s="47" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G18" s="123" t="str">
         <f t="shared" si="6"/>
@@ -15035,14 +15039,14 @@
     </row>
     <row r="19">
       <c r="B19" s="35" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C19" s="41" t="str">
         <f>AVERAGE(C8:C17)</f>
         <v>#VALUE!</v>
       </c>
       <c r="F19" s="47" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G19" s="123" t="str">
         <f t="shared" si="6"/>
@@ -15070,7 +15074,7 @@
       <c r="T19" s="21"/>
       <c r="U19" s="21"/>
       <c r="AA19" s="42" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AB19" s="41">
         <f>AVERAGE(AB7:AB16)</f>
@@ -15085,7 +15089,7 @@
     </row>
     <row r="20">
       <c r="F20" s="47" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G20" s="123" t="str">
         <f t="shared" si="6"/>
@@ -15110,7 +15114,7 @@
     </row>
     <row r="21">
       <c r="F21" s="47" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G21" s="123" t="str">
         <f t="shared" si="6"/>
@@ -15124,13 +15128,13 @@
       </c>
       <c r="R21" s="79"/>
       <c r="S21" s="84" t="s">
+        <v>170</v>
+      </c>
+      <c r="T21" s="84" t="s">
         <v>171</v>
       </c>
-      <c r="T21" s="84" t="s">
+      <c r="U21" s="84" t="s">
         <v>172</v>
-      </c>
-      <c r="U21" s="84" t="s">
-        <v>173</v>
       </c>
       <c r="AE21" s="42">
         <v>146.62</v>
@@ -15142,7 +15146,7 @@
     <row r="22">
       <c r="C22" s="123"/>
       <c r="F22" s="47" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G22" s="123" t="str">
         <f t="shared" si="6"/>
@@ -15215,7 +15219,7 @@
     </row>
     <row r="24">
       <c r="F24" s="47" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G24" s="123" t="str">
         <f t="shared" si="6"/>
@@ -15251,7 +15255,7 @@
     </row>
     <row r="25">
       <c r="F25" s="47" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G25" s="123" t="str">
         <f t="shared" si="6"/>
@@ -15264,7 +15268,7 @@
         <v>1.0</v>
       </c>
       <c r="R25" s="84" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="S25" s="125">
         <f t="shared" ref="S25:U25" si="14">SUM(S22:S24)</f>
@@ -15287,7 +15291,7 @@
     </row>
     <row r="26">
       <c r="F26" s="47" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G26" s="123" t="str">
         <f t="shared" si="6"/>
@@ -15332,13 +15336,13 @@
         <v>1.0</v>
       </c>
       <c r="AA28" s="42" t="s">
+        <v>196</v>
+      </c>
+      <c r="AB28" s="42" t="s">
         <v>197</v>
       </c>
-      <c r="AB28" s="42" t="s">
-        <v>198</v>
-      </c>
       <c r="AC28" s="42" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AE28" s="42">
         <v>106.73</v>
@@ -15349,7 +15353,7 @@
     </row>
     <row r="29">
       <c r="F29" s="35" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G29" s="41" t="str">
         <f>AVERAGE(G8:G27)</f>
@@ -15440,7 +15444,7 @@
     </row>
     <row r="32">
       <c r="B32" s="54" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G32" s="123"/>
       <c r="P32" s="121">
@@ -15469,7 +15473,7 @@
     </row>
     <row r="33">
       <c r="B33" s="128" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G33" s="129"/>
       <c r="P33" s="121">
@@ -15523,7 +15527,7 @@
     </row>
     <row r="35">
       <c r="H35" s="35" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="P35" s="121">
         <v>1.0</v>
@@ -15551,7 +15555,7 @@
     </row>
     <row r="36">
       <c r="G36" s="35" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H36" s="130">
         <v>4.555000000000001</v>
@@ -15589,7 +15593,7 @@
         <v>4.136590909</v>
       </c>
       <c r="G37" s="35" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H37" s="130">
         <v>7.555294117647058</v>
@@ -15620,7 +15624,7 @@
     </row>
     <row r="38">
       <c r="G38" s="35" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H38" s="132">
         <v>2.21</v>
@@ -15651,14 +15655,14 @@
     </row>
     <row r="39">
       <c r="C39" s="133" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D39" s="123">
         <f t="shared" ref="D39:D221" si="17">IF(COUNTA(C39)=1,C39/1,"")</f>
         <v>0</v>
       </c>
       <c r="G39" s="35" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H39" s="130">
         <v>9.938235294117648</v>
@@ -15689,14 +15693,14 @@
     </row>
     <row r="40">
       <c r="C40" s="134" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D40" s="123">
         <f t="shared" si="17"/>
         <v>1.89</v>
       </c>
       <c r="G40" s="35" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H40" s="130">
         <v>3.3411111111111107</v>
@@ -15727,7 +15731,7 @@
     </row>
     <row r="41">
       <c r="C41" s="134" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D41" s="123">
         <f t="shared" si="17"/>
@@ -15759,7 +15763,7 @@
     </row>
     <row r="42">
       <c r="C42" s="134" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D42" s="123">
         <f t="shared" si="17"/>
@@ -15791,7 +15795,7 @@
     </row>
     <row r="43">
       <c r="C43" s="134" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D43" s="123">
         <f t="shared" si="17"/>
@@ -15823,7 +15827,7 @@
     </row>
     <row r="44">
       <c r="C44" s="134" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D44" s="123">
         <f t="shared" si="17"/>
@@ -15853,7 +15857,7 @@
     </row>
     <row r="45">
       <c r="C45" s="134" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D45" s="123">
         <f t="shared" si="17"/>
@@ -15871,17 +15875,17 @@
     </row>
     <row r="46">
       <c r="C46" s="134" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D46" s="123">
         <f t="shared" si="17"/>
         <v>3.67</v>
       </c>
       <c r="G46" s="95" t="s">
+        <v>207</v>
+      </c>
+      <c r="H46" s="95" t="s">
         <v>208</v>
-      </c>
-      <c r="H46" s="95" t="s">
-        <v>209</v>
       </c>
       <c r="P46" s="121">
         <v>0.0</v>
@@ -15895,14 +15899,14 @@
     </row>
     <row r="47">
       <c r="C47" s="134" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D47" s="123">
         <f t="shared" si="17"/>
         <v>4.71</v>
       </c>
       <c r="G47" s="100" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H47" s="135">
         <v>0.376453591155815</v>
@@ -15914,7 +15918,7 @@
         <v>3</v>
       </c>
       <c r="AB47" s="42" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AE47" s="42">
         <v>67.98</v>
@@ -15925,20 +15929,20 @@
     </row>
     <row r="48">
       <c r="C48" s="134" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D48" s="123">
         <f t="shared" si="17"/>
         <v>3.08</v>
       </c>
       <c r="G48" s="100" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H48" s="135">
         <v>0.36678739680281</v>
       </c>
       <c r="J48" s="42" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K48" s="88">
         <f>AVERAGE(H47:H51)</f>
@@ -15962,20 +15966,20 @@
     </row>
     <row r="49">
       <c r="C49" s="134" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D49" s="123">
         <f t="shared" si="17"/>
         <v>4.19</v>
       </c>
       <c r="G49" s="100" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H49" s="135">
         <v>0.142870351877935</v>
       </c>
       <c r="J49" s="42" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K49" s="88">
         <f>MEDIAN(H47:H51)</f>
@@ -15999,20 +16003,20 @@
     </row>
     <row r="50">
       <c r="C50" s="134" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D50" s="123">
         <f t="shared" si="17"/>
         <v>4.02</v>
       </c>
       <c r="G50" s="100" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H50" s="135">
         <v>0.497437843674554</v>
       </c>
       <c r="J50" s="42" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K50" s="88">
         <f>PERCENTILE(H47:H51,0.25)</f>
@@ -16036,20 +16040,20 @@
     </row>
     <row r="51">
       <c r="C51" s="134" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D51" s="123">
         <f t="shared" si="17"/>
         <v>4.31</v>
       </c>
       <c r="G51" s="100" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H51" s="135">
         <v>0.247446036291655</v>
       </c>
       <c r="J51" s="42" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K51" s="88">
         <f>PERCENTILE(H47:H51,0.75)</f>
@@ -16073,7 +16077,7 @@
     </row>
     <row r="52">
       <c r="C52" s="134" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D52" s="123">
         <f t="shared" si="17"/>
@@ -16097,7 +16101,7 @@
     </row>
     <row r="53">
       <c r="C53" s="134" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D53" s="123">
         <f t="shared" si="17"/>
@@ -16121,7 +16125,7 @@
     </row>
     <row r="54">
       <c r="C54" s="134" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D54" s="123">
         <f t="shared" si="17"/>
@@ -16145,7 +16149,7 @@
     </row>
     <row r="55">
       <c r="C55" s="134" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D55" s="123">
         <f t="shared" si="17"/>
@@ -16169,7 +16173,7 @@
     </row>
     <row r="56">
       <c r="C56" s="134" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D56" s="123">
         <f t="shared" si="17"/>
@@ -16193,7 +16197,7 @@
     </row>
     <row r="57">
       <c r="C57" s="134" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D57" s="123">
         <f t="shared" si="17"/>
@@ -16217,14 +16221,14 @@
     </row>
     <row r="58">
       <c r="C58" s="134" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D58" s="123">
         <f t="shared" si="17"/>
         <v>3.34</v>
       </c>
       <c r="G58" s="136" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H58" s="137"/>
       <c r="P58" s="121">
@@ -16245,7 +16249,7 @@
     </row>
     <row r="59">
       <c r="C59" s="134" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D59" s="123">
         <f t="shared" si="17"/>
@@ -16253,7 +16257,7 @@
       </c>
       <c r="G59" s="137"/>
       <c r="H59" s="138" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="P59" s="121">
         <v>0.0</v>
@@ -16273,7 +16277,7 @@
     </row>
     <row r="60">
       <c r="C60" s="134" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D60" s="123">
         <f t="shared" si="17"/>
@@ -16281,7 +16285,7 @@
       </c>
       <c r="G60" s="137"/>
       <c r="H60" s="138" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="P60" s="121">
         <v>2.0</v>
@@ -16301,7 +16305,7 @@
     </row>
     <row r="61">
       <c r="C61" s="134" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D61" s="123">
         <f t="shared" si="17"/>
@@ -16309,7 +16313,7 @@
       </c>
       <c r="G61" s="137"/>
       <c r="H61" s="138" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="P61" s="121">
         <v>2.0</v>
@@ -16329,7 +16333,7 @@
     </row>
     <row r="62">
       <c r="C62" s="134" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D62" s="123">
         <f t="shared" si="17"/>
@@ -16337,7 +16341,7 @@
       </c>
       <c r="G62" s="137"/>
       <c r="H62" s="138" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="P62" s="121">
         <v>1.0</v>
@@ -16357,7 +16361,7 @@
     </row>
     <row r="63">
       <c r="C63" s="134" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D63" s="123">
         <f t="shared" si="17"/>
@@ -16365,7 +16369,7 @@
       </c>
       <c r="G63" s="137"/>
       <c r="H63" s="138" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="P63" s="121">
         <v>0.0</v>
@@ -16379,7 +16383,7 @@
     </row>
     <row r="64">
       <c r="C64" s="134" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D64" s="123">
         <f t="shared" si="17"/>
@@ -16397,7 +16401,7 @@
     </row>
     <row r="65">
       <c r="C65" s="134" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D65" s="123">
         <f t="shared" si="17"/>
@@ -16415,7 +16419,7 @@
     </row>
     <row r="66">
       <c r="C66" s="134" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D66" s="123">
         <f t="shared" si="17"/>
@@ -16433,7 +16437,7 @@
     </row>
     <row r="67">
       <c r="C67" s="134" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D67" s="123">
         <f t="shared" si="17"/>
@@ -16451,7 +16455,7 @@
     </row>
     <row r="68">
       <c r="C68" s="134" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D68" s="123">
         <f t="shared" si="17"/>
@@ -16469,7 +16473,7 @@
     </row>
     <row r="69">
       <c r="C69" s="134" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D69" s="123">
         <f t="shared" si="17"/>
@@ -16487,7 +16491,7 @@
     </row>
     <row r="70">
       <c r="C70" s="134" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D70" s="123">
         <f t="shared" si="17"/>
@@ -16505,7 +16509,7 @@
     </row>
     <row r="71">
       <c r="C71" s="134" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D71" s="123">
         <f t="shared" si="17"/>
@@ -16524,7 +16528,7 @@
     </row>
     <row r="72">
       <c r="C72" s="134" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D72" s="123">
         <f t="shared" si="17"/>
@@ -16542,7 +16546,7 @@
     </row>
     <row r="73">
       <c r="C73" s="134" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D73" s="123">
         <f t="shared" si="17"/>
@@ -16560,7 +16564,7 @@
     </row>
     <row r="74">
       <c r="C74" s="134" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D74" s="123">
         <f t="shared" si="17"/>
@@ -16578,7 +16582,7 @@
     </row>
     <row r="75">
       <c r="C75" s="134" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D75" s="123">
         <f t="shared" si="17"/>
@@ -16596,7 +16600,7 @@
     </row>
     <row r="76">
       <c r="C76" s="134" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D76" s="123">
         <f t="shared" si="17"/>
@@ -16614,7 +16618,7 @@
     </row>
     <row r="77">
       <c r="C77" s="134" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D77" s="123">
         <f t="shared" si="17"/>
@@ -16632,7 +16636,7 @@
     </row>
     <row r="78">
       <c r="C78" s="134" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D78" s="123">
         <f t="shared" si="17"/>
@@ -16650,7 +16654,7 @@
     </row>
     <row r="79">
       <c r="C79" s="134" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D79" s="123">
         <f t="shared" si="17"/>
@@ -16668,7 +16672,7 @@
     </row>
     <row r="80">
       <c r="C80" s="134" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D80" s="123">
         <f t="shared" si="17"/>
@@ -16686,7 +16690,7 @@
     </row>
     <row r="81">
       <c r="C81" s="134" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D81" s="123">
         <f t="shared" si="17"/>
@@ -16704,7 +16708,7 @@
     </row>
     <row r="82">
       <c r="C82" s="134" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D82" s="123">
         <f t="shared" si="17"/>
@@ -16722,7 +16726,7 @@
     </row>
     <row r="83">
       <c r="C83" s="134" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D83" s="123">
         <f t="shared" si="17"/>
@@ -16740,7 +16744,7 @@
     </row>
     <row r="84">
       <c r="C84" s="134" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D84" s="123">
         <f t="shared" si="17"/>
@@ -16758,7 +16762,7 @@
     </row>
     <row r="85">
       <c r="C85" s="134" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D85" s="123">
         <f t="shared" si="17"/>
@@ -16776,7 +16780,7 @@
     </row>
     <row r="86">
       <c r="C86" s="134" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D86" s="123">
         <f t="shared" si="17"/>
@@ -16794,7 +16798,7 @@
     </row>
     <row r="87">
       <c r="C87" s="134" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D87" s="123">
         <f t="shared" si="17"/>
@@ -16812,7 +16816,7 @@
     </row>
     <row r="88">
       <c r="C88" s="134" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D88" s="123">
         <f t="shared" si="17"/>
@@ -16830,7 +16834,7 @@
     </row>
     <row r="89">
       <c r="C89" s="134" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D89" s="123">
         <f t="shared" si="17"/>
@@ -16848,7 +16852,7 @@
     </row>
     <row r="90">
       <c r="C90" s="134" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D90" s="123">
         <f t="shared" si="17"/>
@@ -16866,7 +16870,7 @@
     </row>
     <row r="91">
       <c r="C91" s="134" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D91" s="123">
         <f t="shared" si="17"/>
@@ -16884,7 +16888,7 @@
     </row>
     <row r="92">
       <c r="C92" s="134" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D92" s="123">
         <f t="shared" si="17"/>
@@ -16902,7 +16906,7 @@
     </row>
     <row r="93">
       <c r="C93" s="134" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D93" s="123">
         <f t="shared" si="17"/>
@@ -16920,7 +16924,7 @@
     </row>
     <row r="94">
       <c r="C94" s="134" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D94" s="123">
         <f t="shared" si="17"/>
@@ -16938,7 +16942,7 @@
     </row>
     <row r="95">
       <c r="C95" s="134" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D95" s="123">
         <f t="shared" si="17"/>
@@ -16956,7 +16960,7 @@
     </row>
     <row r="96">
       <c r="C96" s="134" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D96" s="123">
         <f t="shared" si="17"/>
@@ -16974,7 +16978,7 @@
     </row>
     <row r="97">
       <c r="C97" s="134" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D97" s="123">
         <f t="shared" si="17"/>
@@ -16992,7 +16996,7 @@
     </row>
     <row r="98">
       <c r="C98" s="134" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D98" s="123">
         <f t="shared" si="17"/>
@@ -17010,7 +17014,7 @@
     </row>
     <row r="99">
       <c r="C99" s="134" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D99" s="123">
         <f t="shared" si="17"/>
@@ -17028,7 +17032,7 @@
     </row>
     <row r="100">
       <c r="C100" s="134" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D100" s="123">
         <f t="shared" si="17"/>
@@ -17046,7 +17050,7 @@
     </row>
     <row r="101">
       <c r="C101" s="134" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D101" s="123">
         <f t="shared" si="17"/>
@@ -17064,7 +17068,7 @@
     </row>
     <row r="102">
       <c r="C102" s="134" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D102" s="123">
         <f t="shared" si="17"/>
@@ -17082,7 +17086,7 @@
     </row>
     <row r="103">
       <c r="C103" s="134" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D103" s="123">
         <f t="shared" si="17"/>
@@ -17100,7 +17104,7 @@
     </row>
     <row r="104">
       <c r="C104" s="134" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D104" s="123">
         <f t="shared" si="17"/>
@@ -17119,7 +17123,7 @@
     </row>
     <row r="105">
       <c r="C105" s="134" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D105" s="123">
         <f t="shared" si="17"/>
@@ -17138,7 +17142,7 @@
     </row>
     <row r="106">
       <c r="C106" s="134" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D106" s="123">
         <f t="shared" si="17"/>
@@ -17157,7 +17161,7 @@
     </row>
     <row r="107">
       <c r="C107" s="134" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D107" s="123">
         <f t="shared" si="17"/>
@@ -17176,7 +17180,7 @@
     </row>
     <row r="108">
       <c r="C108" s="134" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D108" s="123">
         <f t="shared" si="17"/>
@@ -17195,7 +17199,7 @@
     </row>
     <row r="109">
       <c r="C109" s="134" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D109" s="123">
         <f t="shared" si="17"/>
@@ -17214,7 +17218,7 @@
     </row>
     <row r="110">
       <c r="C110" s="134" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D110" s="123">
         <f t="shared" si="17"/>
@@ -17233,7 +17237,7 @@
     </row>
     <row r="111">
       <c r="C111" s="134" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D111" s="123">
         <f t="shared" si="17"/>
@@ -17252,7 +17256,7 @@
     </row>
     <row r="112">
       <c r="C112" s="134" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D112" s="123">
         <f t="shared" si="17"/>
@@ -17270,7 +17274,7 @@
     </row>
     <row r="113">
       <c r="C113" s="134" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D113" s="123">
         <f t="shared" si="17"/>
@@ -17288,7 +17292,7 @@
     </row>
     <row r="114">
       <c r="C114" s="134" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D114" s="123">
         <f t="shared" si="17"/>
@@ -17306,7 +17310,7 @@
     </row>
     <row r="115">
       <c r="C115" s="134" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D115" s="123">
         <f t="shared" si="17"/>
@@ -17324,7 +17328,7 @@
     </row>
     <row r="116">
       <c r="C116" s="134" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D116" s="123">
         <f t="shared" si="17"/>
@@ -17342,7 +17346,7 @@
     </row>
     <row r="117">
       <c r="C117" s="134" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D117" s="123">
         <f t="shared" si="17"/>
@@ -17358,7 +17362,7 @@
     </row>
     <row r="118">
       <c r="C118" s="134" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D118" s="123">
         <f t="shared" si="17"/>
@@ -17374,7 +17378,7 @@
     </row>
     <row r="119">
       <c r="C119" s="134" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D119" s="123">
         <f t="shared" si="17"/>
@@ -17390,7 +17394,7 @@
     </row>
     <row r="120">
       <c r="C120" s="134" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D120" s="123">
         <f t="shared" si="17"/>
@@ -17406,7 +17410,7 @@
     </row>
     <row r="121">
       <c r="C121" s="134" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D121" s="123">
         <f t="shared" si="17"/>
@@ -17422,7 +17426,7 @@
     </row>
     <row r="122">
       <c r="C122" s="134" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D122" s="123">
         <f t="shared" si="17"/>
@@ -17438,7 +17442,7 @@
     </row>
     <row r="123">
       <c r="C123" s="134" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D123" s="123">
         <f t="shared" si="17"/>
@@ -17454,7 +17458,7 @@
     </row>
     <row r="124">
       <c r="C124" s="134" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D124" s="123">
         <f t="shared" si="17"/>
@@ -17470,7 +17474,7 @@
     </row>
     <row r="125">
       <c r="C125" s="134" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D125" s="123">
         <f t="shared" si="17"/>
@@ -17486,7 +17490,7 @@
     </row>
     <row r="126">
       <c r="C126" s="134" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D126" s="123">
         <f t="shared" si="17"/>
@@ -39910,14 +39914,14 @@
     <row r="1">
       <c r="A1" s="104"/>
       <c r="B1" s="144" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C1" s="145"/>
       <c r="D1" s="145"/>
       <c r="E1" s="145"/>
       <c r="F1" s="145"/>
       <c r="G1" s="146" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1" s="145"/>
       <c r="I1" s="145"/>
@@ -39945,49 +39949,49 @@
         <v>3</v>
       </c>
       <c r="B2" s="148" t="s">
+        <v>292</v>
+      </c>
+      <c r="C2" s="149" t="s">
         <v>293</v>
       </c>
-      <c r="C2" s="149" t="s">
+      <c r="D2" s="149" t="s">
+        <v>197</v>
+      </c>
+      <c r="E2" s="149" t="s">
         <v>294</v>
       </c>
-      <c r="D2" s="149" t="s">
-        <v>198</v>
-      </c>
-      <c r="E2" s="149" t="s">
+      <c r="F2" s="150" t="s">
         <v>295</v>
-      </c>
-      <c r="F2" s="150" t="s">
-        <v>296</v>
       </c>
       <c r="G2" s="148">
         <v>1.0</v>
       </c>
       <c r="H2" s="149" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I2" s="149">
         <v>2.0</v>
       </c>
       <c r="J2" s="149" t="s">
+        <v>296</v>
+      </c>
+      <c r="K2" s="151" t="s">
         <v>297</v>
       </c>
-      <c r="K2" s="151" t="s">
+      <c r="L2" s="149" t="s">
         <v>298</v>
       </c>
-      <c r="L2" s="149" t="s">
+      <c r="M2" s="152" t="s">
         <v>299</v>
       </c>
-      <c r="M2" s="152" t="s">
+      <c r="N2" s="100" t="s">
         <v>300</v>
       </c>
-      <c r="N2" s="100" t="s">
+      <c r="O2" s="100" t="s">
         <v>301</v>
       </c>
-      <c r="O2" s="100" t="s">
+      <c r="P2" s="100" t="s">
         <v>302</v>
-      </c>
-      <c r="P2" s="100" t="s">
-        <v>303</v>
       </c>
       <c r="Q2" s="9"/>
       <c r="R2" s="9"/>
@@ -40660,7 +40664,7 @@
     </row>
     <row r="24">
       <c r="A24" s="94" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B24" s="164" t="str">
         <f t="shared" ref="B24:F24" si="4">IFERROR(AVERAGE(B3:B22),"")</f>
@@ -40770,7 +40774,7 @@
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
       <c r="G27" s="165" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H27" s="9"/>
       <c r="I27" s="9"/>
@@ -40803,7 +40807,7 @@
         <v>1.0</v>
       </c>
       <c r="H28" s="166" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I28" s="166">
         <v>2.0</v>
@@ -40831,7 +40835,7 @@
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
       <c r="D29" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E29" s="4">
         <f>J29</f>
@@ -40853,10 +40857,10 @@
       </c>
       <c r="K29" s="9"/>
       <c r="L29" s="94" t="s">
+        <v>305</v>
+      </c>
+      <c r="M29" s="94" t="s">
         <v>306</v>
-      </c>
-      <c r="M29" s="94" t="s">
-        <v>307</v>
       </c>
       <c r="O29" s="4">
         <v>1.0</v>
@@ -40992,7 +40996,7 @@
       <c r="E33" s="9"/>
       <c r="F33" s="9"/>
       <c r="G33" s="119" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="J33" s="9"/>
       <c r="K33" s="9"/>
@@ -41026,7 +41030,7 @@
         <v>1.0</v>
       </c>
       <c r="H34" s="169" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="I34" s="169">
         <v>2.0</v>
@@ -41169,7 +41173,7 @@
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
       <c r="F38" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G38" s="168">
         <f t="shared" ref="G38:I38" si="8">G30-G35</f>

--- a/data/df_best_models.xlsx
+++ b/data/df_best_models.xlsx
@@ -260,7 +260,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="313">
   <si>
     <t>id_country</t>
   </si>
@@ -922,22 +922,28 @@
     <t>Stake promedio</t>
   </si>
   <si>
+    <t>1.87</t>
+  </si>
+  <si>
+    <t>2.17</t>
+  </si>
+  <si>
+    <t>0.14</t>
+  </si>
+  <si>
+    <t>6.52</t>
+  </si>
+  <si>
     <t>0.00</t>
   </si>
   <si>
-    <t>1.89</t>
+    <t>2.79</t>
   </si>
   <si>
-    <t>0.32</t>
+    <t>0.02</t>
   </si>
   <si>
-    <t>4.46</t>
-  </si>
-  <si>
-    <t>4.20</t>
-  </si>
-  <si>
-    <t>4.21</t>
+    <t>2.67</t>
   </si>
   <si>
     <t>Country</t>
@@ -946,247 +952,253 @@
     <t>Correl ROI y Expected ROI</t>
   </si>
   <si>
-    <t>4.71</t>
+    <t>2.49</t>
   </si>
   <si>
-    <t>3.08</t>
+    <t>2.75</t>
   </si>
   <si>
     <t>mean</t>
   </si>
   <si>
+    <t>1.83</t>
+  </si>
+  <si>
     <t>median</t>
+  </si>
+  <si>
+    <t>p25</t>
+  </si>
+  <si>
+    <t>7.09</t>
+  </si>
+  <si>
+    <t>p75</t>
+  </si>
+  <si>
+    <t>0.94</t>
+  </si>
+  <si>
+    <t>4.28</t>
+  </si>
+  <si>
+    <t>6.54</t>
+  </si>
+  <si>
+    <t>0.74</t>
+  </si>
+  <si>
+    <t>5.39</t>
+  </si>
+  <si>
+    <t>3.55</t>
+  </si>
+  <si>
+    <t>Gracias a las nuevas métricas de G/P sin bank en test, me di cuenta de que:</t>
+  </si>
+  <si>
+    <t>3.94</t>
+  </si>
+  <si>
+    <t>La rentabilidad en ITA está en el visitante y no en el empate como creía.</t>
+  </si>
+  <si>
+    <t>3.95</t>
+  </si>
+  <si>
+    <t>La rentabilidad en ENG y GER está en el empate tal como creía.</t>
+  </si>
+  <si>
+    <t>8.55</t>
+  </si>
+  <si>
+    <t>En SPA esta repartido aunque Empate saca una ventaja.</t>
+  </si>
+  <si>
+    <t>4.12</t>
+  </si>
+  <si>
+    <t>En FRA, depende el modelo. A veces local, a veces, empate.</t>
+  </si>
+  <si>
+    <t>7.78</t>
+  </si>
+  <si>
+    <t>Si en FRA empate no rinde, no tiene sentido exigirle una buena distrib en empate… → Tiene sentido pero al parecer si importa el empate puesto que el modelo que gana se basa en empate.</t>
+  </si>
+  <si>
+    <t>2.32</t>
+  </si>
+  <si>
+    <t>1.23</t>
+  </si>
+  <si>
+    <t>0.32</t>
+  </si>
+  <si>
+    <t>7.49</t>
+  </si>
+  <si>
+    <t>7.07</t>
+  </si>
+  <si>
+    <t>4.67</t>
+  </si>
+  <si>
+    <t>3.28</t>
+  </si>
+  <si>
+    <t>7.29</t>
+  </si>
+  <si>
+    <t>5.59</t>
+  </si>
+  <si>
+    <t>2.34</t>
+  </si>
+  <si>
+    <t>5.12</t>
+  </si>
+  <si>
+    <t>6.01</t>
+  </si>
+  <si>
+    <t>5.91</t>
+  </si>
+  <si>
+    <t>5.55</t>
+  </si>
+  <si>
+    <t>5.36</t>
+  </si>
+  <si>
+    <t>0.17</t>
+  </si>
+  <si>
+    <t>2.44</t>
+  </si>
+  <si>
+    <t>2.77</t>
+  </si>
+  <si>
+    <t>2.53</t>
+  </si>
+  <si>
+    <t>2.98</t>
+  </si>
+  <si>
+    <t>1.35</t>
+  </si>
+  <si>
+    <t>2.29</t>
+  </si>
+  <si>
+    <t>1.41</t>
+  </si>
+  <si>
+    <t>3.19</t>
+  </si>
+  <si>
+    <t>1.90</t>
+  </si>
+  <si>
+    <t>1.98</t>
+  </si>
+  <si>
+    <t>1.69</t>
+  </si>
+  <si>
+    <t>3.03</t>
+  </si>
+  <si>
+    <t>4.89</t>
+  </si>
+  <si>
+    <t>5.69</t>
+  </si>
+  <si>
+    <t>8.18</t>
+  </si>
+  <si>
+    <t>6.94</t>
+  </si>
+  <si>
+    <t>6.57</t>
+  </si>
+  <si>
+    <t>9.63</t>
+  </si>
+  <si>
+    <t>8.72</t>
+  </si>
+  <si>
+    <t>8.58</t>
+  </si>
+  <si>
+    <t>7.00</t>
+  </si>
+  <si>
+    <t>7.33</t>
+  </si>
+  <si>
+    <t>3.85</t>
+  </si>
+  <si>
+    <t>7.54</t>
+  </si>
+  <si>
+    <t>3.77</t>
+  </si>
+  <si>
+    <t>1.50</t>
+  </si>
+  <si>
+    <t>5.24</t>
+  </si>
+  <si>
+    <t>4.41</t>
+  </si>
+  <si>
+    <t>1.76</t>
+  </si>
+  <si>
+    <t>4.52</t>
+  </si>
+  <si>
+    <t>4.80</t>
+  </si>
+  <si>
+    <t>1.81</t>
+  </si>
+  <si>
+    <t>5.04</t>
+  </si>
+  <si>
+    <t>8.91</t>
   </si>
   <si>
     <t>4.02</t>
   </si>
   <si>
-    <t>p25</t>
-  </si>
-  <si>
-    <t>4.31</t>
-  </si>
-  <si>
-    <t>p75</t>
-  </si>
-  <si>
-    <t>6.06</t>
-  </si>
-  <si>
-    <t>1.91</t>
-  </si>
-  <si>
-    <t>3.75</t>
-  </si>
-  <si>
-    <t>3.26</t>
-  </si>
-  <si>
-    <t>3.34</t>
-  </si>
-  <si>
-    <t>Gracias a las nuevas métricas de G/P sin bank en test, me di cuenta de que:</t>
-  </si>
-  <si>
-    <t>La rentabilidad en ITA está en el visitante y no en el empate como creía.</t>
-  </si>
-  <si>
-    <t>3.41</t>
-  </si>
-  <si>
-    <t>La rentabilidad en ENG y GER está en el empate tal como creía.</t>
-  </si>
-  <si>
-    <t>3.53</t>
-  </si>
-  <si>
-    <t>En SPA esta repartido aunque Empate saca una ventaja.</t>
-  </si>
-  <si>
-    <t>En FRA, depende el modelo. A veces local, a veces, empate.</t>
-  </si>
-  <si>
-    <t>4.83</t>
-  </si>
-  <si>
-    <t>Si en FRA empate no rinde, no tiene sentido exigirle una buena distrib en empate… → Tiene sentido pero al parecer si importa el empate puesto que el modelo que gana se basa en empate.</t>
-  </si>
-  <si>
-    <t>4.38</t>
-  </si>
-  <si>
-    <t>5.13</t>
-  </si>
-  <si>
-    <t>3.76</t>
-  </si>
-  <si>
-    <t>1.45</t>
-  </si>
-  <si>
-    <t>6.14</t>
-  </si>
-  <si>
-    <t>8.07</t>
-  </si>
-  <si>
-    <t>4.79</t>
-  </si>
-  <si>
-    <t>6.66</t>
-  </si>
-  <si>
-    <t>7.81</t>
-  </si>
-  <si>
-    <t>7.09</t>
-  </si>
-  <si>
-    <t>6.99</t>
-  </si>
-  <si>
     <t>9.05</t>
   </si>
   <si>
-    <t>8.43</t>
+    <t>0.07</t>
   </si>
   <si>
-    <t>8.21</t>
+    <t>2.99</t>
   </si>
   <si>
-    <t>0.99</t>
+    <t>2.40</t>
   </si>
   <si>
-    <t>0.95</t>
+    <t>3.00</t>
   </si>
   <si>
-    <t>1.06</t>
+    <t>2.97</t>
   </si>
   <si>
-    <t>1.27</t>
-  </si>
-  <si>
-    <t>0.84</t>
-  </si>
-  <si>
-    <t>0.79</t>
-  </si>
-  <si>
-    <t>1.34</t>
-  </si>
-  <si>
-    <t>1.18</t>
-  </si>
-  <si>
-    <t>1.01</t>
-  </si>
-  <si>
-    <t>0.73</t>
-  </si>
-  <si>
-    <t>1.10</t>
-  </si>
-  <si>
-    <t>1.14</t>
-  </si>
-  <si>
-    <t>1.20</t>
-  </si>
-  <si>
-    <t>0.82</t>
-  </si>
-  <si>
-    <t>1.32</t>
-  </si>
-  <si>
-    <t>1.47</t>
-  </si>
-  <si>
-    <t>0.76</t>
-  </si>
-  <si>
-    <t>7.13</t>
-  </si>
-  <si>
-    <t>5.99</t>
-  </si>
-  <si>
-    <t>5.72</t>
-  </si>
-  <si>
-    <t>7.29</t>
-  </si>
-  <si>
-    <t>7.19</t>
-  </si>
-  <si>
-    <t>8.65</t>
-  </si>
-  <si>
-    <t>10.86</t>
-  </si>
-  <si>
-    <t>10.38</t>
-  </si>
-  <si>
-    <t>5.43</t>
-  </si>
-  <si>
-    <t>9.50</t>
-  </si>
-  <si>
-    <t>8.37</t>
-  </si>
-  <si>
-    <t>6.85</t>
-  </si>
-  <si>
-    <t>6.29</t>
-  </si>
-  <si>
-    <t>3.01</t>
-  </si>
-  <si>
-    <t>5.84</t>
-  </si>
-  <si>
-    <t>5.33</t>
-  </si>
-  <si>
-    <t>6.10</t>
-  </si>
-  <si>
-    <t>7.44</t>
-  </si>
-  <si>
-    <t>6.78</t>
-  </si>
-  <si>
-    <t>3.92</t>
-  </si>
-  <si>
-    <t>0.27</t>
-  </si>
-  <si>
-    <t>1.99</t>
-  </si>
-  <si>
-    <t>2.00</t>
-  </si>
-  <si>
-    <t>1.98</t>
-  </si>
-  <si>
-    <t>3.84</t>
-  </si>
-  <si>
-    <t>4.23</t>
-  </si>
-  <si>
-    <t>2.79</t>
-  </si>
-  <si>
-    <t>3.21</t>
+    <t>0.35</t>
   </si>
   <si>
     <t>RENTABILIDAD</t>
@@ -2434,7 +2446,7 @@
         <v>45693.0</v>
       </c>
       <c r="D4" s="15">
-        <v>332.0</v>
+        <v>344.0</v>
       </c>
       <c r="E4" s="15" t="s">
         <v>18</v>
@@ -2549,7 +2561,7 @@
         <v>45693.0</v>
       </c>
       <c r="D6" s="15">
-        <v>411.0</v>
+        <v>447.0</v>
       </c>
       <c r="E6" s="15" t="s">
         <v>18</v>
@@ -2606,7 +2618,7 @@
         <v>45693.0</v>
       </c>
       <c r="D7" s="15">
-        <v>1015.0</v>
+        <v>1271.0</v>
       </c>
       <c r="E7" s="15" t="s">
         <v>18</v>
@@ -2663,7 +2675,7 @@
         <v>45693.0</v>
       </c>
       <c r="D8" s="15">
-        <v>530.0</v>
+        <v>1212.0</v>
       </c>
       <c r="E8" s="15" t="s">
         <v>18</v>
@@ -13931,32 +13943,66 @@
       </c>
     </row>
     <row r="24">
+      <c r="B24" s="12"/>
       <c r="I24" s="42" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="25">
+      <c r="B25" s="2" t="s">
+        <v>1</v>
+      </c>
       <c r="I25" s="42" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="26">
+      <c r="B26" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" s="42">
+        <v>332.0</v>
+      </c>
       <c r="M26" s="34"/>
       <c r="N26" s="34"/>
     </row>
     <row r="27">
+      <c r="B27" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="C27" s="42">
+        <v>1288.0</v>
+      </c>
       <c r="M27" s="34"/>
       <c r="N27" s="34"/>
     </row>
     <row r="28">
+      <c r="B28" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="C28" s="42">
+        <v>411.0</v>
+      </c>
       <c r="M28" s="34"/>
       <c r="N28" s="34"/>
     </row>
     <row r="29">
+      <c r="B29" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" s="42">
+        <v>1015.0</v>
+      </c>
       <c r="M29" s="34"/>
       <c r="N29" s="34"/>
     </row>
     <row r="30">
+      <c r="B30" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="C30" s="42">
+        <v>530.0</v>
+      </c>
       <c r="I30" s="35" t="s">
         <v>86</v>
       </c>
@@ -15590,7 +15636,7 @@
       <c r="C37" s="40"/>
       <c r="D37" s="131">
         <f>AVERAGE(D39:D1775)</f>
-        <v>4.136590909</v>
+        <v>3.991363636</v>
       </c>
       <c r="G37" s="35" t="s">
         <v>41</v>
@@ -15659,7 +15705,7 @@
       </c>
       <c r="D39" s="123">
         <f t="shared" ref="D39:D221" si="17">IF(COUNTA(C39)=1,C39/1,"")</f>
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="G39" s="35" t="s">
         <v>33</v>
@@ -15697,7 +15743,7 @@
       </c>
       <c r="D40" s="123">
         <f t="shared" si="17"/>
-        <v>1.89</v>
+        <v>2.17</v>
       </c>
       <c r="G40" s="35" t="s">
         <v>29</v>
@@ -15735,7 +15781,7 @@
       </c>
       <c r="D41" s="123">
         <f t="shared" si="17"/>
-        <v>0.32</v>
+        <v>0.14</v>
       </c>
       <c r="P41" s="121">
         <v>0.0</v>
@@ -15763,11 +15809,11 @@
     </row>
     <row r="42">
       <c r="C42" s="134" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="D42" s="123">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>6.52</v>
       </c>
       <c r="P42" s="121">
         <v>2.0</v>
@@ -15795,11 +15841,11 @@
     </row>
     <row r="43">
       <c r="C43" s="134" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D43" s="123">
         <f t="shared" si="17"/>
-        <v>4.46</v>
+        <v>0</v>
       </c>
       <c r="P43" s="121">
         <v>1.0</v>
@@ -15827,11 +15873,11 @@
     </row>
     <row r="44">
       <c r="C44" s="134" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D44" s="123">
         <f t="shared" si="17"/>
-        <v>4.2</v>
+        <v>2.79</v>
       </c>
       <c r="P44" s="121">
         <v>2.0</v>
@@ -15857,11 +15903,11 @@
     </row>
     <row r="45">
       <c r="C45" s="134" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D45" s="123">
         <f t="shared" si="17"/>
-        <v>4.21</v>
+        <v>0.02</v>
       </c>
       <c r="P45" s="121">
         <v>1.0</v>
@@ -15875,17 +15921,17 @@
     </row>
     <row r="46">
       <c r="C46" s="134" t="s">
-        <v>154</v>
+        <v>208</v>
       </c>
       <c r="D46" s="123">
         <f t="shared" si="17"/>
-        <v>3.67</v>
+        <v>2.67</v>
       </c>
       <c r="G46" s="95" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H46" s="95" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="P46" s="121">
         <v>0.0</v>
@@ -15899,11 +15945,11 @@
     </row>
     <row r="47">
       <c r="C47" s="134" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D47" s="123">
         <f t="shared" si="17"/>
-        <v>4.71</v>
+        <v>2.49</v>
       </c>
       <c r="G47" s="100" t="s">
         <v>42</v>
@@ -15929,11 +15975,11 @@
     </row>
     <row r="48">
       <c r="C48" s="134" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D48" s="123">
         <f t="shared" si="17"/>
-        <v>3.08</v>
+        <v>2.75</v>
       </c>
       <c r="G48" s="100" t="s">
         <v>41</v>
@@ -15942,7 +15988,7 @@
         <v>0.36678739680281</v>
       </c>
       <c r="J48" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K48" s="88">
         <f>AVERAGE(H47:H51)</f>
@@ -15966,11 +16012,11 @@
     </row>
     <row r="49">
       <c r="C49" s="134" t="s">
-        <v>193</v>
+        <v>214</v>
       </c>
       <c r="D49" s="123">
         <f t="shared" si="17"/>
-        <v>4.19</v>
+        <v>1.83</v>
       </c>
       <c r="G49" s="100" t="s">
         <v>32</v>
@@ -15979,7 +16025,7 @@
         <v>0.142870351877935</v>
       </c>
       <c r="J49" s="42" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="K49" s="88">
         <f>MEDIAN(H47:H51)</f>
@@ -16003,11 +16049,11 @@
     </row>
     <row r="50">
       <c r="C50" s="134" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D50" s="123">
         <f t="shared" si="17"/>
-        <v>4.02</v>
+        <v>1.83</v>
       </c>
       <c r="G50" s="100" t="s">
         <v>33</v>
@@ -16016,7 +16062,7 @@
         <v>0.497437843674554</v>
       </c>
       <c r="J50" s="42" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K50" s="88">
         <f>PERCENTILE(H47:H51,0.25)</f>
@@ -16040,11 +16086,11 @@
     </row>
     <row r="51">
       <c r="C51" s="134" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D51" s="123">
         <f t="shared" si="17"/>
-        <v>4.31</v>
+        <v>7.09</v>
       </c>
       <c r="G51" s="100" t="s">
         <v>29</v>
@@ -16053,7 +16099,7 @@
         <v>0.247446036291655</v>
       </c>
       <c r="J51" s="42" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="K51" s="88">
         <f>PERCENTILE(H47:H51,0.75)</f>
@@ -16077,11 +16123,11 @@
     </row>
     <row r="52">
       <c r="C52" s="134" t="s">
-        <v>217</v>
+        <v>183</v>
       </c>
       <c r="D52" s="123">
         <f t="shared" si="17"/>
-        <v>6.06</v>
+        <v>2.8</v>
       </c>
       <c r="P52" s="121">
         <v>0.0</v>
@@ -16101,11 +16147,11 @@
     </row>
     <row r="53">
       <c r="C53" s="134" t="s">
-        <v>167</v>
+        <v>219</v>
       </c>
       <c r="D53" s="123">
         <f t="shared" si="17"/>
-        <v>5.94</v>
+        <v>0.94</v>
       </c>
       <c r="P53" s="121">
         <v>0.0</v>
@@ -16125,11 +16171,11 @@
     </row>
     <row r="54">
       <c r="C54" s="134" t="s">
-        <v>166</v>
+        <v>220</v>
       </c>
       <c r="D54" s="123">
         <f t="shared" si="17"/>
-        <v>3.65</v>
+        <v>4.28</v>
       </c>
       <c r="P54" s="121">
         <v>2.0</v>
@@ -16149,11 +16195,11 @@
     </row>
     <row r="55">
       <c r="C55" s="134" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="D55" s="123">
         <f t="shared" si="17"/>
-        <v>1.91</v>
+        <v>6.54</v>
       </c>
       <c r="P55" s="121">
         <v>0.0</v>
@@ -16173,11 +16219,11 @@
     </row>
     <row r="56">
       <c r="C56" s="134" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D56" s="123">
         <f t="shared" si="17"/>
-        <v>3.75</v>
+        <v>0.74</v>
       </c>
       <c r="P56" s="121">
         <v>0.0</v>
@@ -16197,11 +16243,11 @@
     </row>
     <row r="57">
       <c r="C57" s="134" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D57" s="123">
         <f t="shared" si="17"/>
-        <v>3.26</v>
+        <v>5.39</v>
       </c>
       <c r="P57" s="121">
         <v>2.0</v>
@@ -16221,14 +16267,14 @@
     </row>
     <row r="58">
       <c r="C58" s="134" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D58" s="123">
         <f t="shared" si="17"/>
-        <v>3.34</v>
+        <v>3.55</v>
       </c>
       <c r="G58" s="136" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="H58" s="137"/>
       <c r="P58" s="121">
@@ -16249,15 +16295,15 @@
     </row>
     <row r="59">
       <c r="C59" s="134" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="D59" s="123">
         <f t="shared" si="17"/>
-        <v>3.75</v>
+        <v>3.94</v>
       </c>
       <c r="G59" s="137"/>
       <c r="H59" s="138" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="P59" s="121">
         <v>0.0</v>
@@ -16277,15 +16323,15 @@
     </row>
     <row r="60">
       <c r="C60" s="134" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="D60" s="123">
         <f t="shared" si="17"/>
-        <v>3.41</v>
+        <v>3.95</v>
       </c>
       <c r="G60" s="137"/>
       <c r="H60" s="138" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="P60" s="121">
         <v>2.0</v>
@@ -16305,15 +16351,15 @@
     </row>
     <row r="61">
       <c r="C61" s="134" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="D61" s="123">
         <f t="shared" si="17"/>
-        <v>3.53</v>
+        <v>8.55</v>
       </c>
       <c r="G61" s="137"/>
       <c r="H61" s="138" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="P61" s="121">
         <v>2.0</v>
@@ -16333,15 +16379,15 @@
     </row>
     <row r="62">
       <c r="C62" s="134" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="D62" s="123">
         <f t="shared" si="17"/>
-        <v>3.53</v>
+        <v>4.12</v>
       </c>
       <c r="G62" s="137"/>
       <c r="H62" s="138" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="P62" s="121">
         <v>1.0</v>
@@ -16361,15 +16407,15 @@
     </row>
     <row r="63">
       <c r="C63" s="134" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="D63" s="123">
         <f t="shared" si="17"/>
-        <v>4.83</v>
+        <v>7.78</v>
       </c>
       <c r="G63" s="137"/>
       <c r="H63" s="138" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="P63" s="121">
         <v>0.0</v>
@@ -16383,11 +16429,11 @@
     </row>
     <row r="64">
       <c r="C64" s="134" t="s">
-        <v>231</v>
+        <v>208</v>
       </c>
       <c r="D64" s="123">
         <f t="shared" si="17"/>
-        <v>4.38</v>
+        <v>2.67</v>
       </c>
       <c r="P64" s="121">
         <v>1.0</v>
@@ -16401,11 +16447,11 @@
     </row>
     <row r="65">
       <c r="C65" s="134" t="s">
-        <v>232</v>
+        <v>202</v>
       </c>
       <c r="D65" s="123">
         <f t="shared" si="17"/>
-        <v>5.13</v>
+        <v>2.17</v>
       </c>
       <c r="P65" s="121">
         <v>2.0</v>
@@ -16419,11 +16465,11 @@
     </row>
     <row r="66">
       <c r="C66" s="134" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="D66" s="123">
         <f t="shared" si="17"/>
-        <v>3.76</v>
+        <v>2.32</v>
       </c>
       <c r="P66" s="121">
         <v>0.0</v>
@@ -16437,11 +16483,11 @@
     </row>
     <row r="67">
       <c r="C67" s="134" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D67" s="123">
         <f t="shared" si="17"/>
-        <v>1.45</v>
+        <v>1.23</v>
       </c>
       <c r="P67" s="121">
         <v>0.0</v>
@@ -16455,11 +16501,11 @@
     </row>
     <row r="68">
       <c r="C68" s="134" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D68" s="123">
         <f t="shared" si="17"/>
-        <v>6.14</v>
+        <v>0.32</v>
       </c>
       <c r="P68" s="121">
         <v>1.0</v>
@@ -16473,11 +16519,11 @@
     </row>
     <row r="69">
       <c r="C69" s="134" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D69" s="123">
         <f t="shared" si="17"/>
-        <v>8.07</v>
+        <v>7.49</v>
       </c>
       <c r="P69" s="121">
         <v>2.0</v>
@@ -16491,11 +16537,11 @@
     </row>
     <row r="70">
       <c r="C70" s="134" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="D70" s="123">
         <f t="shared" si="17"/>
-        <v>4.79</v>
+        <v>7.07</v>
       </c>
       <c r="P70" s="121">
         <v>1.0</v>
@@ -16509,11 +16555,11 @@
     </row>
     <row r="71">
       <c r="C71" s="134" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D71" s="123">
         <f t="shared" si="17"/>
-        <v>6.66</v>
+        <v>4.67</v>
       </c>
       <c r="F71" s="139"/>
       <c r="P71" s="121">
@@ -16528,11 +16574,11 @@
     </row>
     <row r="72">
       <c r="C72" s="134" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D72" s="123">
         <f t="shared" si="17"/>
-        <v>7.81</v>
+        <v>3.28</v>
       </c>
       <c r="P72" s="121">
         <v>0.0</v>
@@ -16546,11 +16592,11 @@
     </row>
     <row r="73">
       <c r="C73" s="134" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D73" s="123">
         <f t="shared" si="17"/>
-        <v>7.09</v>
+        <v>7.29</v>
       </c>
       <c r="P73" s="121">
         <v>1.0</v>
@@ -16564,11 +16610,11 @@
     </row>
     <row r="74">
       <c r="C74" s="134" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D74" s="123">
         <f t="shared" si="17"/>
-        <v>6.99</v>
+        <v>5.59</v>
       </c>
       <c r="P74" s="121">
         <v>0.0</v>
@@ -16582,11 +16628,11 @@
     </row>
     <row r="75">
       <c r="C75" s="134" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D75" s="123">
         <f t="shared" si="17"/>
-        <v>9.05</v>
+        <v>2.34</v>
       </c>
       <c r="P75" s="121">
         <v>1.0</v>
@@ -16600,11 +16646,11 @@
     </row>
     <row r="76">
       <c r="C76" s="134" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="D76" s="123">
         <f t="shared" si="17"/>
-        <v>8.43</v>
+        <v>5.12</v>
       </c>
       <c r="P76" s="121">
         <v>0.0</v>
@@ -16618,11 +16664,11 @@
     </row>
     <row r="77">
       <c r="C77" s="134" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D77" s="123">
         <f t="shared" si="17"/>
-        <v>8.21</v>
+        <v>6.01</v>
       </c>
       <c r="P77" s="121">
         <v>0.0</v>
@@ -16636,11 +16682,11 @@
     </row>
     <row r="78">
       <c r="C78" s="134" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="D78" s="123">
         <f t="shared" si="17"/>
-        <v>0.99</v>
+        <v>5.91</v>
       </c>
       <c r="P78" s="121">
         <v>1.0</v>
@@ -16654,11 +16700,11 @@
     </row>
     <row r="79">
       <c r="C79" s="134" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="D79" s="123">
         <f t="shared" si="17"/>
-        <v>0.95</v>
+        <v>5.55</v>
       </c>
       <c r="P79" s="121">
         <v>2.0</v>
@@ -16672,11 +16718,11 @@
     </row>
     <row r="80">
       <c r="C80" s="134" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="D80" s="123">
         <f t="shared" si="17"/>
-        <v>1.06</v>
+        <v>5.36</v>
       </c>
       <c r="P80" s="121">
         <v>1.0</v>
@@ -16690,11 +16736,11 @@
     </row>
     <row r="81">
       <c r="C81" s="134" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D81" s="123">
         <f t="shared" si="17"/>
-        <v>1.27</v>
+        <v>0.17</v>
       </c>
       <c r="P81" s="121">
         <v>2.0</v>
@@ -16708,11 +16754,11 @@
     </row>
     <row r="82">
       <c r="C82" s="134" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="D82" s="123">
         <f t="shared" si="17"/>
-        <v>0.84</v>
+        <v>2.44</v>
       </c>
       <c r="P82" s="121">
         <v>1.0</v>
@@ -16726,11 +16772,11 @@
     </row>
     <row r="83">
       <c r="C83" s="134" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D83" s="123">
         <f t="shared" si="17"/>
-        <v>0.79</v>
+        <v>2.77</v>
       </c>
       <c r="P83" s="121">
         <v>0.0</v>
@@ -16744,11 +16790,11 @@
     </row>
     <row r="84">
       <c r="C84" s="134" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D84" s="123">
         <f t="shared" si="17"/>
-        <v>1.34</v>
+        <v>2.53</v>
       </c>
       <c r="P84" s="121">
         <v>1.0</v>
@@ -16762,11 +16808,11 @@
     </row>
     <row r="85">
       <c r="C85" s="134" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D85" s="123">
         <f t="shared" si="17"/>
-        <v>1.18</v>
+        <v>2.98</v>
       </c>
       <c r="P85" s="121">
         <v>0.0</v>
@@ -16780,11 +16826,11 @@
     </row>
     <row r="86">
       <c r="C86" s="134" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D86" s="123">
         <f t="shared" si="17"/>
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="P86" s="121">
         <v>0.0</v>
@@ -16798,11 +16844,11 @@
     </row>
     <row r="87">
       <c r="C87" s="134" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D87" s="123">
         <f t="shared" si="17"/>
-        <v>0.73</v>
+        <v>2.29</v>
       </c>
       <c r="P87" s="121">
         <v>1.0</v>
@@ -16816,11 +16862,11 @@
     </row>
     <row r="88">
       <c r="C88" s="134" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="D88" s="123">
         <f t="shared" si="17"/>
-        <v>1.1</v>
+        <v>1.41</v>
       </c>
       <c r="P88" s="121">
         <v>2.0</v>
@@ -16834,11 +16880,11 @@
     </row>
     <row r="89">
       <c r="C89" s="134" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D89" s="123">
         <f t="shared" si="17"/>
-        <v>1.14</v>
+        <v>3.19</v>
       </c>
       <c r="P89" s="121">
         <v>2.0</v>
@@ -16852,11 +16898,11 @@
     </row>
     <row r="90">
       <c r="C90" s="134" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D90" s="123">
         <f t="shared" si="17"/>
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="P90" s="121">
         <v>1.0</v>
@@ -16870,11 +16916,11 @@
     </row>
     <row r="91">
       <c r="C91" s="134" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="D91" s="123">
         <f t="shared" si="17"/>
-        <v>0.82</v>
+        <v>1.98</v>
       </c>
       <c r="P91" s="121">
         <v>1.0</v>
@@ -16888,11 +16934,11 @@
     </row>
     <row r="92">
       <c r="C92" s="134" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D92" s="123">
         <f t="shared" si="17"/>
-        <v>1.32</v>
+        <v>1.69</v>
       </c>
       <c r="P92" s="121">
         <v>2.0</v>
@@ -16906,11 +16952,11 @@
     </row>
     <row r="93">
       <c r="C93" s="134" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="D93" s="123">
         <f t="shared" si="17"/>
-        <v>1.47</v>
+        <v>3.03</v>
       </c>
       <c r="P93" s="121">
         <v>0.0</v>
@@ -16924,11 +16970,11 @@
     </row>
     <row r="94">
       <c r="C94" s="134" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D94" s="123">
         <f t="shared" si="17"/>
-        <v>0.76</v>
+        <v>4.89</v>
       </c>
       <c r="P94" s="121">
         <v>0.0</v>
@@ -16942,11 +16988,11 @@
     </row>
     <row r="95">
       <c r="C95" s="134" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="D95" s="123">
         <f t="shared" si="17"/>
-        <v>0.82</v>
+        <v>5.69</v>
       </c>
       <c r="P95" s="121">
         <v>1.0</v>
@@ -16960,11 +17006,11 @@
     </row>
     <row r="96">
       <c r="C96" s="134" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D96" s="123">
         <f t="shared" si="17"/>
-        <v>7.13</v>
+        <v>8.18</v>
       </c>
       <c r="P96" s="121">
         <v>2.0</v>
@@ -16978,11 +17024,11 @@
     </row>
     <row r="97">
       <c r="C97" s="134" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="D97" s="123">
         <f t="shared" si="17"/>
-        <v>5.99</v>
+        <v>6.94</v>
       </c>
       <c r="P97" s="121">
         <v>0.0</v>
@@ -16996,11 +17042,11 @@
     </row>
     <row r="98">
       <c r="C98" s="134" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="D98" s="123">
         <f t="shared" si="17"/>
-        <v>5.72</v>
+        <v>6.57</v>
       </c>
       <c r="P98" s="121">
         <v>2.0</v>
@@ -17014,11 +17060,11 @@
     </row>
     <row r="99">
       <c r="C99" s="134" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="D99" s="123">
         <f t="shared" si="17"/>
-        <v>7.29</v>
+        <v>9.63</v>
       </c>
       <c r="P99" s="121">
         <v>2.0</v>
@@ -17032,11 +17078,11 @@
     </row>
     <row r="100">
       <c r="C100" s="134" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D100" s="123">
         <f t="shared" si="17"/>
-        <v>7.19</v>
+        <v>8.72</v>
       </c>
       <c r="P100" s="121">
         <v>2.0</v>
@@ -17050,11 +17096,11 @@
     </row>
     <row r="101">
       <c r="C101" s="134" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="D101" s="123">
         <f t="shared" si="17"/>
-        <v>8.65</v>
+        <v>8.58</v>
       </c>
       <c r="P101" s="121">
         <v>2.0</v>
@@ -17068,11 +17114,11 @@
     </row>
     <row r="102">
       <c r="C102" s="134" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="D102" s="123">
         <f t="shared" si="17"/>
-        <v>10.86</v>
+        <v>7</v>
       </c>
       <c r="P102" s="121">
         <v>2.0</v>
@@ -17086,11 +17132,11 @@
     </row>
     <row r="103">
       <c r="C103" s="134" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D103" s="123">
         <f t="shared" si="17"/>
-        <v>10.38</v>
+        <v>7.33</v>
       </c>
       <c r="P103" s="121">
         <v>1.0</v>
@@ -17104,11 +17150,11 @@
     </row>
     <row r="104">
       <c r="C104" s="134" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="D104" s="123">
         <f t="shared" si="17"/>
-        <v>5.43</v>
+        <v>3.85</v>
       </c>
       <c r="N104" s="140"/>
       <c r="P104" s="121">
@@ -17123,11 +17169,11 @@
     </row>
     <row r="105">
       <c r="C105" s="134" t="s">
-        <v>271</v>
+        <v>243</v>
       </c>
       <c r="D105" s="123">
         <f t="shared" si="17"/>
-        <v>9.5</v>
+        <v>7.29</v>
       </c>
       <c r="N105" s="21"/>
       <c r="P105" s="121">
@@ -17142,11 +17188,11 @@
     </row>
     <row r="106">
       <c r="C106" s="134" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="D106" s="123">
         <f t="shared" si="17"/>
-        <v>8.37</v>
+        <v>7.54</v>
       </c>
       <c r="N106" s="21"/>
       <c r="P106" s="121">
@@ -17161,11 +17207,11 @@
     </row>
     <row r="107">
       <c r="C107" s="134" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="D107" s="123">
         <f t="shared" si="17"/>
-        <v>6.85</v>
+        <v>3.77</v>
       </c>
       <c r="N107" s="21"/>
       <c r="P107" s="121">
@@ -17180,11 +17226,11 @@
     </row>
     <row r="108">
       <c r="C108" s="134" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="D108" s="123">
         <f t="shared" si="17"/>
-        <v>6.29</v>
+        <v>1.5</v>
       </c>
       <c r="N108" s="21"/>
       <c r="P108" s="121">
@@ -17199,11 +17245,11 @@
     </row>
     <row r="109">
       <c r="C109" s="134" t="s">
-        <v>238</v>
+        <v>278</v>
       </c>
       <c r="D109" s="123">
         <f t="shared" si="17"/>
-        <v>6.66</v>
+        <v>5.24</v>
       </c>
       <c r="N109" s="21"/>
       <c r="P109" s="121">
@@ -17218,11 +17264,11 @@
     </row>
     <row r="110">
       <c r="C110" s="134" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="D110" s="123">
         <f t="shared" si="17"/>
-        <v>3.01</v>
+        <v>4.41</v>
       </c>
       <c r="N110" s="21"/>
       <c r="P110" s="121">
@@ -17237,11 +17283,11 @@
     </row>
     <row r="111">
       <c r="C111" s="134" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="D111" s="123">
         <f t="shared" si="17"/>
-        <v>5.84</v>
+        <v>1.76</v>
       </c>
       <c r="N111" s="21"/>
       <c r="P111" s="121">
@@ -17256,11 +17302,11 @@
     </row>
     <row r="112">
       <c r="C112" s="134" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="D112" s="123">
         <f t="shared" si="17"/>
-        <v>5.33</v>
+        <v>4.52</v>
       </c>
       <c r="P112" s="121">
         <v>1.0</v>
@@ -17274,11 +17320,11 @@
     </row>
     <row r="113">
       <c r="C113" s="134" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="D113" s="123">
         <f t="shared" si="17"/>
-        <v>6.1</v>
+        <v>4.8</v>
       </c>
       <c r="P113" s="121">
         <v>0.0</v>
@@ -17292,11 +17338,11 @@
     </row>
     <row r="114">
       <c r="C114" s="134" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="D114" s="123">
         <f t="shared" si="17"/>
-        <v>7.44</v>
+        <v>1.81</v>
       </c>
       <c r="P114" s="121">
         <v>1.0</v>
@@ -17310,11 +17356,11 @@
     </row>
     <row r="115">
       <c r="C115" s="134" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="D115" s="123">
         <f t="shared" si="17"/>
-        <v>6.78</v>
+        <v>5.04</v>
       </c>
       <c r="P115" s="121">
         <v>1.0</v>
@@ -17328,11 +17374,11 @@
     </row>
     <row r="116">
       <c r="C116" s="134" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="D116" s="123">
         <f t="shared" si="17"/>
-        <v>3.92</v>
+        <v>8.91</v>
       </c>
       <c r="P116" s="121">
         <v>1.0</v>
@@ -17346,11 +17392,11 @@
     </row>
     <row r="117">
       <c r="C117" s="134" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="D117" s="123">
         <f t="shared" si="17"/>
-        <v>0.27</v>
+        <v>4.02</v>
       </c>
       <c r="P117" s="141"/>
       <c r="AE117" s="42">
@@ -17362,11 +17408,11 @@
     </row>
     <row r="118">
       <c r="C118" s="134" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="D118" s="123">
         <f t="shared" si="17"/>
-        <v>1.99</v>
+        <v>9.05</v>
       </c>
       <c r="P118" s="141"/>
       <c r="AE118" s="42">
@@ -17378,11 +17424,11 @@
     </row>
     <row r="119">
       <c r="C119" s="134" t="s">
-        <v>284</v>
+        <v>166</v>
       </c>
       <c r="D119" s="123">
         <f t="shared" si="17"/>
-        <v>2</v>
+        <v>3.65</v>
       </c>
       <c r="P119" s="141"/>
       <c r="AE119" s="42">
@@ -17394,11 +17440,11 @@
     </row>
     <row r="120">
       <c r="C120" s="134" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="D120" s="123">
         <f t="shared" si="17"/>
-        <v>1.98</v>
+        <v>0.07</v>
       </c>
       <c r="P120" s="141"/>
       <c r="AE120" s="42">
@@ -17410,11 +17456,11 @@
     </row>
     <row r="121">
       <c r="C121" s="134" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="D121" s="123">
         <f t="shared" si="17"/>
-        <v>2</v>
+        <v>2.99</v>
       </c>
       <c r="P121" s="141"/>
       <c r="AE121" s="42">
@@ -17426,11 +17472,11 @@
     </row>
     <row r="122">
       <c r="C122" s="134" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="D122" s="123">
         <f t="shared" si="17"/>
-        <v>3.84</v>
+        <v>2.4</v>
       </c>
       <c r="P122" s="141"/>
       <c r="AE122" s="42">
@@ -17442,11 +17488,11 @@
     </row>
     <row r="123">
       <c r="C123" s="134" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="D123" s="123">
         <f t="shared" si="17"/>
-        <v>4.23</v>
+        <v>3</v>
       </c>
       <c r="P123" s="141"/>
       <c r="AE123" s="42">
@@ -17458,11 +17504,11 @@
     </row>
     <row r="124">
       <c r="C124" s="134" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="D124" s="123">
         <f t="shared" si="17"/>
-        <v>2.79</v>
+        <v>2.97</v>
       </c>
       <c r="P124" s="141"/>
       <c r="AE124" s="42">
@@ -17474,11 +17520,11 @@
     </row>
     <row r="125">
       <c r="C125" s="134" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="D125" s="123">
         <f t="shared" si="17"/>
-        <v>3.21</v>
+        <v>0.35</v>
       </c>
       <c r="P125" s="141"/>
       <c r="AE125" s="42">
@@ -17490,11 +17536,11 @@
     </row>
     <row r="126">
       <c r="C126" s="134" t="s">
-        <v>206</v>
+        <v>260</v>
       </c>
       <c r="D126" s="123">
         <f t="shared" si="17"/>
-        <v>4.21</v>
+        <v>1.9</v>
       </c>
       <c r="P126" s="141"/>
       <c r="AE126" s="42">
@@ -39914,14 +39960,14 @@
     <row r="1">
       <c r="A1" s="104"/>
       <c r="B1" s="144" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="C1" s="145"/>
       <c r="D1" s="145"/>
       <c r="E1" s="145"/>
       <c r="F1" s="145"/>
       <c r="G1" s="146" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="H1" s="145"/>
       <c r="I1" s="145"/>
@@ -39949,19 +39995,19 @@
         <v>3</v>
       </c>
       <c r="B2" s="148" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C2" s="149" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="D2" s="149" t="s">
         <v>197</v>
       </c>
       <c r="E2" s="149" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="F2" s="150" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="G2" s="148">
         <v>1.0</v>
@@ -39973,25 +40019,25 @@
         <v>2.0</v>
       </c>
       <c r="J2" s="149" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="K2" s="151" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="L2" s="149" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="M2" s="152" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="N2" s="100" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="O2" s="100" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="P2" s="100" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="Q2" s="9"/>
       <c r="R2" s="9"/>
@@ -40774,7 +40820,7 @@
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
       <c r="G27" s="165" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="H27" s="9"/>
       <c r="I27" s="9"/>
@@ -40835,7 +40881,7 @@
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
       <c r="D29" s="4" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="E29" s="4">
         <f>J29</f>
@@ -40857,10 +40903,10 @@
       </c>
       <c r="K29" s="9"/>
       <c r="L29" s="94" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="M29" s="94" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="O29" s="4">
         <v>1.0</v>
@@ -40996,7 +41042,7 @@
       <c r="E33" s="9"/>
       <c r="F33" s="9"/>
       <c r="G33" s="119" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="J33" s="9"/>
       <c r="K33" s="9"/>
@@ -41173,7 +41219,7 @@
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
       <c r="F38" s="4" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="G38" s="168">
         <f t="shared" ref="G38:I38" si="8">G30-G35</f>

--- a/data/df_best_models.xlsx
+++ b/data/df_best_models.xlsx
@@ -2501,7 +2501,7 @@
         <v>45693.0</v>
       </c>
       <c r="D4" s="15">
-        <v>2240.0</v>
+        <v>145.0</v>
       </c>
       <c r="E4" s="15" t="s">
         <v>15</v>
@@ -2509,21 +2509,21 @@
       <c r="F4" s="16"/>
       <c r="G4" s="17"/>
       <c r="H4" s="18">
-        <v>25.0</v>
+        <v>5.0</v>
       </c>
       <c r="I4" s="18">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
       <c r="J4" s="18">
-        <v>45.0</v>
+        <v>15.0</v>
       </c>
       <c r="K4" s="20">
         <f t="shared" ref="K4:K8" si="1">AVERAGE(H4:J4)</f>
-        <v>26.66666667</v>
+        <v>11.66666667</v>
       </c>
       <c r="L4" s="27">
         <f>K4*'Data preparation'!$C$2</f>
-        <v>6.666666667</v>
+        <v>2.916666667</v>
       </c>
       <c r="M4" s="16"/>
       <c r="N4" s="20" t="str">
@@ -2542,7 +2542,7 @@
         <v>45693.0</v>
       </c>
       <c r="D5" s="15">
-        <v>218.0</v>
+        <v>1126.0</v>
       </c>
       <c r="E5" s="15" t="s">
         <v>15</v>
@@ -2550,21 +2550,21 @@
       <c r="F5" s="16"/>
       <c r="G5" s="17"/>
       <c r="H5" s="16">
-        <v>45.0</v>
+        <v>15.0</v>
       </c>
       <c r="I5" s="16">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
       <c r="J5" s="16">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
       <c r="K5" s="20">
         <f t="shared" si="1"/>
-        <v>21.66666667</v>
+        <v>15</v>
       </c>
       <c r="L5" s="27">
         <f>K5*'Data preparation'!$C$2</f>
-        <v>5.416666667</v>
+        <v>3.75</v>
       </c>
       <c r="M5" s="16"/>
       <c r="N5" s="20" t="str">
@@ -2584,7 +2584,7 @@
         <v>45693.0</v>
       </c>
       <c r="D6" s="15">
-        <v>447.0</v>
+        <v>1288.0</v>
       </c>
       <c r="E6" s="15" t="s">
         <v>15</v>
@@ -2592,21 +2592,21 @@
       <c r="F6" s="16"/>
       <c r="G6" s="17"/>
       <c r="H6" s="16">
-        <v>45.0</v>
+        <v>15.0</v>
       </c>
       <c r="I6" s="16">
-        <v>45.0</v>
+        <v>15.0</v>
       </c>
       <c r="J6" s="16">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
       <c r="K6" s="20">
         <f t="shared" si="1"/>
-        <v>33.33333333</v>
+        <v>15</v>
       </c>
       <c r="L6" s="27">
         <f>K6*'Data preparation'!$C$2</f>
-        <v>8.333333333</v>
+        <v>3.75</v>
       </c>
       <c r="M6" s="32"/>
       <c r="N6" s="20" t="str">
@@ -2625,7 +2625,7 @@
         <v>45693.0</v>
       </c>
       <c r="D7" s="15">
-        <v>1157.0</v>
+        <v>1091.0</v>
       </c>
       <c r="E7" s="15" t="s">
         <v>15</v>
@@ -2633,21 +2633,21 @@
       <c r="F7" s="16"/>
       <c r="G7" s="17"/>
       <c r="H7" s="18">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="I7" s="18">
-        <v>45.0</v>
+        <v>15.0</v>
       </c>
       <c r="J7" s="18">
-        <v>25.0</v>
+        <v>15.0</v>
       </c>
       <c r="K7" s="20">
         <f t="shared" si="1"/>
-        <v>26.66666667</v>
+        <v>11.66666667</v>
       </c>
       <c r="L7" s="27">
         <f>K7*'Data preparation'!$C$2</f>
-        <v>6.666666667</v>
+        <v>2.916666667</v>
       </c>
       <c r="M7" s="16"/>
       <c r="N7" s="20" t="str">
@@ -2666,23 +2666,29 @@
         <v>45693.0</v>
       </c>
       <c r="D8" s="15">
-        <v>508.0</v>
+        <v>1201.0</v>
       </c>
       <c r="E8" s="15" t="s">
         <v>15</v>
       </c>
       <c r="F8" s="16"/>
       <c r="G8" s="17"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="18"/>
-      <c r="J8" s="18"/>
-      <c r="K8" s="20" t="str">
+      <c r="H8" s="18">
+        <v>15.0</v>
+      </c>
+      <c r="I8" s="18">
+        <v>15.0</v>
+      </c>
+      <c r="J8" s="18">
+        <v>15.0</v>
+      </c>
+      <c r="K8" s="20">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L8" s="27" t="str">
+        <v>15</v>
+      </c>
+      <c r="L8" s="27">
         <f>K8*'Data preparation'!$C$2</f>
-        <v>#DIV/0!</v>
+        <v>3.75</v>
       </c>
       <c r="M8" s="16"/>
       <c r="N8" s="20" t="str">
@@ -14953,9 +14959,9 @@
       <c r="B3" s="94" t="s">
         <v>143</v>
       </c>
-      <c r="C3" s="21" t="str">
+      <c r="C3" s="26">
         <f>AVERAGE('Modelos actuales'!L4:L8)</f>
-        <v>#DIV/0!</v>
+        <v>3.416666667</v>
       </c>
       <c r="L3" s="117"/>
       <c r="P3" s="117"/>

--- a/data/df_best_models.xlsx
+++ b/data/df_best_models.xlsx
@@ -13,7 +13,7 @@
     <sheet state="visible" name="Framework" sheetId="8" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Modelos actuales'!$A$1:$M$8</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Modelos actuales'!$A$1:$N$8</definedName>
     <definedName hidden="1" localSheetId="7" name="_xlnm._FilterDatabase">Framework!$A$2:$P$22</definedName>
   </definedNames>
   <calcPr/>
@@ -31,7 +31,7 @@
         <t xml:space="preserve">Fecha de entrenamiento de modelos</t>
       </text>
     </comment>
-    <comment authorId="0" ref="M1">
+    <comment authorId="0" ref="N1">
       <text>
         <t xml:space="preserve">los que mas valor tienen suelen tener un rdo mucho mas rentable que otro.
 </t>
@@ -53,7 +53,7 @@
 	-Tiptopia Mondino</t>
       </text>
     </comment>
-    <comment authorId="0" ref="G1">
+    <comment authorId="0" ref="H1">
       <text>
         <t xml:space="preserve">Tener presente que al multiplicador de roi con estrategia hay que aplicarle el porc_m para que sea el multiplicador de roi a esperar en producción puesto que aplico la estrategia en dicho porcentaje.
 	-Tiptopia Mondino
@@ -261,7 +261,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="322">
   <si>
     <t>id_country</t>
   </si>
@@ -279,6 +279,9 @@
   </si>
   <si>
     <t>ROI_sin_ea</t>
+  </si>
+  <si>
+    <t>m</t>
   </si>
   <si>
     <t>m_home</t>
@@ -387,9 +390,6 @@
   </si>
   <si>
     <t>G/P con ea</t>
-  </si>
-  <si>
-    <t>m</t>
   </si>
   <si>
     <t>Con kelly pero seleccionando con l_metrics y eso.</t>
@@ -2369,15 +2369,16 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75" outlineLevelCol="1"/>
   <cols>
     <col customWidth="1" min="3" max="3" width="14.75"/>
     <col customWidth="1" min="5" max="5" width="15.13"/>
     <col customWidth="1" min="6" max="6" width="10.13"/>
-    <col customWidth="1" min="7" max="10" width="8.25"/>
-    <col customWidth="1" min="11" max="11" width="8.75"/>
-    <col customWidth="1" min="12" max="12" width="10.13"/>
-    <col customWidth="1" min="13" max="13" width="8.25"/>
+    <col collapsed="1" customWidth="1" min="7" max="7" width="8.25"/>
+    <col customWidth="1" hidden="1" min="8" max="11" width="8.25" outlineLevel="1"/>
+    <col customWidth="1" min="12" max="12" width="8.75"/>
+    <col customWidth="1" min="13" max="13" width="10.13"/>
+    <col customWidth="1" min="14" max="14" width="8.25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2408,27 +2409,30 @@
       <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="M1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="9"/>
-      <c r="O1" s="10"/>
+      <c r="N1" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="9"/>
+      <c r="P1" s="10"/>
     </row>
     <row r="2" ht="39.0" hidden="1" customHeight="1">
       <c r="A2" s="11">
         <v>6.0</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" s="13">
         <v>45685.0</v>
@@ -2437,39 +2441,40 @@
         <v>616.0</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F2" s="16">
         <f>5.8410821479406*100</f>
         <v>584.1082148</v>
       </c>
-      <c r="G2" s="17">
+      <c r="G2" s="17"/>
+      <c r="H2" s="17">
         <v>70.0</v>
       </c>
-      <c r="H2" s="17">
+      <c r="I2" s="17">
         <v>45.0</v>
       </c>
-      <c r="I2" s="17">
+      <c r="J2" s="17">
         <v>10.0</v>
       </c>
-      <c r="J2" s="18"/>
       <c r="K2" s="18"/>
-      <c r="L2" s="19">
+      <c r="L2" s="18"/>
+      <c r="M2" s="19">
         <v>31833.0939389723</v>
       </c>
-      <c r="M2" s="20">
-        <f>L2/F2</f>
+      <c r="N2" s="20">
+        <f>M2/F2</f>
         <v>54.49862394</v>
       </c>
-      <c r="N2" s="21"/>
-      <c r="O2" s="22"/>
+      <c r="O2" s="21"/>
+      <c r="P2" s="22"/>
     </row>
     <row r="3" hidden="1">
       <c r="A3" s="23">
         <v>167.0</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" s="13"/>
       <c r="D3" s="13"/>
@@ -2478,19 +2483,20 @@
       <c r="G3" s="21"/>
       <c r="H3" s="21"/>
       <c r="I3" s="21"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="25"/>
-      <c r="L3" s="26"/>
-      <c r="M3" s="27"/>
-      <c r="N3" s="21"/>
-      <c r="O3" s="28"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="18"/>
+      <c r="L3" s="25"/>
+      <c r="M3" s="26"/>
+      <c r="N3" s="27"/>
+      <c r="O3" s="21"/>
+      <c r="P3" s="28"/>
     </row>
     <row r="4" ht="19.5" customHeight="1">
       <c r="A4" s="29">
         <v>48.0</v>
       </c>
       <c r="B4" s="30" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" s="13">
         <v>45693.0</v>
@@ -2499,34 +2505,37 @@
         <v>145.0</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F4" s="16">
         <v>723.690613490815</v>
       </c>
       <c r="G4" s="17">
+        <v>30.0</v>
+      </c>
+      <c r="H4" s="17">
         <v>5.0</v>
       </c>
-      <c r="H4" s="17">
+      <c r="I4" s="17">
         <v>20.0</v>
       </c>
-      <c r="I4" s="17">
+      <c r="J4" s="17">
         <v>50.0</v>
       </c>
-      <c r="J4" s="20">
-        <f t="shared" ref="J4:J8" si="1">AVERAGE(G4:I4)</f>
+      <c r="K4" s="20">
+        <f t="shared" ref="K4:K8" si="1">AVERAGE(H4:J4)</f>
         <v>25</v>
       </c>
-      <c r="K4" s="27">
-        <f>J4*'Data preparation'!$C$2</f>
-        <v>12.5</v>
-      </c>
-      <c r="L4" s="19">
-        <v>37801.0</v>
-      </c>
-      <c r="M4" s="20">
-        <f t="shared" ref="M4:M8" si="2">L4/F4</f>
-        <v>52.23364694</v>
+      <c r="L4" s="27">
+        <f>G4*'Data preparation'!$C$2</f>
+        <v>15</v>
+      </c>
+      <c r="M4" s="19">
+        <v>11419.7513206325</v>
+      </c>
+      <c r="N4" s="20">
+        <f t="shared" ref="N4:N8" si="2">M4/F4</f>
+        <v>15.77988039</v>
       </c>
     </row>
     <row r="5">
@@ -2534,7 +2543,7 @@
         <v>55.0</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" s="13">
         <v>45693.0</v>
@@ -2543,43 +2552,46 @@
         <v>60.0</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" s="16">
         <v>594.689200857164</v>
       </c>
       <c r="G5" s="19">
+        <v>30.0</v>
+      </c>
+      <c r="H5" s="19">
         <v>50.0</v>
       </c>
-      <c r="H5" s="19">
+      <c r="I5" s="19">
         <v>20.0</v>
       </c>
-      <c r="I5" s="19">
+      <c r="J5" s="19">
         <v>40.0</v>
       </c>
-      <c r="J5" s="20">
+      <c r="K5" s="20">
         <f t="shared" si="1"/>
         <v>36.66666667</v>
       </c>
-      <c r="K5" s="27">
-        <f>J5*'Data preparation'!$C$2</f>
-        <v>18.33333333</v>
-      </c>
-      <c r="L5" s="19">
-        <v>3331.0</v>
-      </c>
-      <c r="M5" s="20">
+      <c r="L5" s="27">
+        <f>G5*'Data preparation'!$C$2</f>
+        <v>15</v>
+      </c>
+      <c r="M5" s="19">
+        <v>2642.6610477093</v>
+      </c>
+      <c r="N5" s="20">
         <f t="shared" si="2"/>
-        <v>5.601245147</v>
-      </c>
-      <c r="O5" s="31"/>
+        <v>4.443768348</v>
+      </c>
+      <c r="P5" s="31"/>
     </row>
     <row r="6">
       <c r="A6" s="23">
         <v>59.0</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" s="13">
         <v>45693.0</v>
@@ -2588,34 +2600,37 @@
         <v>411.0</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F6" s="16">
         <v>676.372376389644</v>
       </c>
       <c r="G6" s="19">
+        <v>30.0</v>
+      </c>
+      <c r="H6" s="19">
         <v>70.0</v>
       </c>
-      <c r="H6" s="19">
+      <c r="I6" s="19">
         <v>30.0</v>
       </c>
-      <c r="I6" s="19">
+      <c r="J6" s="19">
         <v>10.0</v>
       </c>
-      <c r="J6" s="20">
+      <c r="K6" s="20">
         <f t="shared" si="1"/>
         <v>36.66666667</v>
       </c>
-      <c r="K6" s="27">
-        <f>J6*'Data preparation'!$C$2</f>
-        <v>18.33333333</v>
-      </c>
-      <c r="L6" s="32">
-        <v>18603.0</v>
-      </c>
-      <c r="M6" s="20">
+      <c r="L6" s="27">
+        <f>G6*'Data preparation'!$C$2</f>
+        <v>15</v>
+      </c>
+      <c r="M6" s="32">
+        <v>9676.39854240164</v>
+      </c>
+      <c r="N6" s="20">
         <f t="shared" si="2"/>
-        <v>27.50408007</v>
+        <v>14.30631835</v>
       </c>
     </row>
     <row r="7">
@@ -2623,7 +2638,7 @@
         <v>77.0</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" s="13">
         <v>45693.0</v>
@@ -2632,34 +2647,37 @@
         <v>536.0</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F7" s="16">
         <v>215.543732667821</v>
       </c>
       <c r="G7" s="17">
+        <v>20.0</v>
+      </c>
+      <c r="H7" s="17">
         <v>5.0</v>
-      </c>
-      <c r="H7" s="17">
-        <v>40.0</v>
       </c>
       <c r="I7" s="17">
         <v>40.0</v>
       </c>
-      <c r="J7" s="20">
+      <c r="J7" s="17">
+        <v>40.0</v>
+      </c>
+      <c r="K7" s="20">
         <f t="shared" si="1"/>
         <v>28.33333333</v>
       </c>
-      <c r="K7" s="27">
-        <f>J7*'Data preparation'!$C$2</f>
-        <v>14.16666667</v>
-      </c>
-      <c r="L7" s="19">
-        <v>5863.0</v>
-      </c>
-      <c r="M7" s="20">
+      <c r="L7" s="27">
+        <f>G7*'Data preparation'!$C$2</f>
+        <v>10</v>
+      </c>
+      <c r="M7" s="19">
+        <v>975.121072123263</v>
+      </c>
+      <c r="N7" s="20">
         <f t="shared" si="2"/>
-        <v>27.20097647</v>
+        <v>4.524005686</v>
       </c>
     </row>
     <row r="8">
@@ -2667,7 +2685,7 @@
         <v>148.0</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" s="13">
         <v>45693.0</v>
@@ -2676,7 +2694,7 @@
         <v>508.0</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F8" s="16">
         <v>353.269181924928</v>
@@ -2688,22 +2706,25 @@
         <v>30.0</v>
       </c>
       <c r="I8" s="17">
+        <v>30.0</v>
+      </c>
+      <c r="J8" s="17">
         <v>20.0</v>
       </c>
-      <c r="J8" s="20">
+      <c r="K8" s="20">
         <f t="shared" si="1"/>
         <v>26.66666667</v>
       </c>
-      <c r="K8" s="27">
-        <f>J8*'Data preparation'!$C$2</f>
-        <v>13.33333333</v>
-      </c>
-      <c r="L8" s="19">
-        <v>4677.30960048888</v>
-      </c>
-      <c r="M8" s="20">
+      <c r="L8" s="27">
+        <f>G8*'Data preparation'!$C$2</f>
+        <v>15</v>
+      </c>
+      <c r="M8" s="19">
+        <v>4184.39471694807</v>
+      </c>
+      <c r="N8" s="20">
         <f t="shared" si="2"/>
-        <v>13.24007256</v>
+        <v>11.8447771</v>
       </c>
     </row>
     <row r="9" ht="20.25" customHeight="1">
@@ -2712,14 +2733,15 @@
       <c r="H9" s="21"/>
       <c r="I9" s="21"/>
       <c r="J9" s="21"/>
-      <c r="L9" s="26"/>
+      <c r="K9" s="21"/>
       <c r="M9" s="26"/>
-      <c r="O9" s="33"/>
+      <c r="N9" s="26"/>
+      <c r="P9" s="33"/>
     </row>
     <row r="10" ht="20.25" customHeight="1"/>
     <row r="11">
-      <c r="K11" s="34"/>
-      <c r="O11" s="34"/>
+      <c r="L11" s="34"/>
+      <c r="P11" s="34"/>
     </row>
     <row r="12" ht="20.25" customHeight="1"/>
     <row r="13">
@@ -2742,6000 +2764,6000 @@
       <c r="C31" s="36"/>
     </row>
     <row r="105">
-      <c r="K105" s="17"/>
-      <c r="L105" s="37"/>
+      <c r="L105" s="17"/>
       <c r="M105" s="37"/>
+      <c r="N105" s="37"/>
     </row>
     <row r="106">
-      <c r="K106" s="17"/>
-      <c r="L106" s="37"/>
+      <c r="L106" s="17"/>
       <c r="M106" s="37"/>
+      <c r="N106" s="37"/>
     </row>
     <row r="107">
-      <c r="K107" s="17"/>
-      <c r="L107" s="37"/>
+      <c r="L107" s="17"/>
       <c r="M107" s="37"/>
+      <c r="N107" s="37"/>
     </row>
     <row r="108">
-      <c r="K108" s="17"/>
-      <c r="L108" s="37"/>
+      <c r="L108" s="17"/>
       <c r="M108" s="37"/>
+      <c r="N108" s="37"/>
     </row>
     <row r="109">
-      <c r="K109" s="17"/>
-      <c r="L109" s="37"/>
+      <c r="L109" s="17"/>
       <c r="M109" s="37"/>
+      <c r="N109" s="37"/>
     </row>
     <row r="110">
-      <c r="K110" s="17"/>
-      <c r="L110" s="37"/>
+      <c r="L110" s="17"/>
       <c r="M110" s="37"/>
+      <c r="N110" s="37"/>
     </row>
     <row r="111">
-      <c r="K111" s="17"/>
-      <c r="L111" s="37"/>
+      <c r="L111" s="17"/>
       <c r="M111" s="37"/>
+      <c r="N111" s="37"/>
     </row>
     <row r="112">
-      <c r="K112" s="17"/>
-      <c r="L112" s="37"/>
+      <c r="L112" s="17"/>
       <c r="M112" s="37"/>
+      <c r="N112" s="37"/>
     </row>
     <row r="113">
-      <c r="K113" s="17"/>
-      <c r="L113" s="37"/>
+      <c r="L113" s="17"/>
       <c r="M113" s="37"/>
+      <c r="N113" s="37"/>
     </row>
     <row r="114">
-      <c r="K114" s="17"/>
-      <c r="L114" s="37"/>
+      <c r="L114" s="17"/>
       <c r="M114" s="37"/>
+      <c r="N114" s="37"/>
     </row>
     <row r="115">
-      <c r="K115" s="17"/>
-      <c r="L115" s="37"/>
+      <c r="L115" s="17"/>
       <c r="M115" s="37"/>
+      <c r="N115" s="37"/>
     </row>
     <row r="116">
-      <c r="K116" s="17"/>
-      <c r="L116" s="37"/>
+      <c r="L116" s="17"/>
       <c r="M116" s="37"/>
+      <c r="N116" s="37"/>
     </row>
     <row r="117">
-      <c r="K117" s="17"/>
-      <c r="L117" s="37"/>
+      <c r="L117" s="17"/>
       <c r="M117" s="37"/>
+      <c r="N117" s="37"/>
     </row>
     <row r="118">
-      <c r="K118" s="17"/>
-      <c r="L118" s="37"/>
+      <c r="L118" s="17"/>
       <c r="M118" s="37"/>
+      <c r="N118" s="37"/>
     </row>
     <row r="119">
-      <c r="K119" s="17"/>
-      <c r="L119" s="37"/>
+      <c r="L119" s="17"/>
       <c r="M119" s="37"/>
+      <c r="N119" s="37"/>
     </row>
     <row r="120">
-      <c r="K120" s="17"/>
-      <c r="L120" s="37"/>
+      <c r="L120" s="17"/>
       <c r="M120" s="37"/>
+      <c r="N120" s="37"/>
     </row>
     <row r="121">
-      <c r="K121" s="17"/>
-      <c r="L121" s="37"/>
+      <c r="L121" s="17"/>
       <c r="M121" s="37"/>
+      <c r="N121" s="37"/>
     </row>
     <row r="122">
-      <c r="K122" s="17"/>
-      <c r="L122" s="37"/>
+      <c r="L122" s="17"/>
       <c r="M122" s="37"/>
+      <c r="N122" s="37"/>
     </row>
     <row r="123">
-      <c r="K123" s="17"/>
-      <c r="L123" s="37"/>
+      <c r="L123" s="17"/>
       <c r="M123" s="37"/>
+      <c r="N123" s="37"/>
     </row>
     <row r="124">
-      <c r="K124" s="17"/>
-      <c r="L124" s="37"/>
+      <c r="L124" s="17"/>
       <c r="M124" s="37"/>
+      <c r="N124" s="37"/>
     </row>
     <row r="125">
-      <c r="K125" s="17"/>
-      <c r="L125" s="37"/>
+      <c r="L125" s="17"/>
       <c r="M125" s="37"/>
+      <c r="N125" s="37"/>
     </row>
     <row r="126">
-      <c r="K126" s="17"/>
-      <c r="L126" s="37"/>
+      <c r="L126" s="17"/>
       <c r="M126" s="37"/>
+      <c r="N126" s="37"/>
     </row>
     <row r="127">
-      <c r="K127" s="17"/>
-      <c r="L127" s="37"/>
+      <c r="L127" s="17"/>
       <c r="M127" s="37"/>
+      <c r="N127" s="37"/>
     </row>
     <row r="128">
-      <c r="K128" s="17"/>
-      <c r="L128" s="37"/>
+      <c r="L128" s="17"/>
       <c r="M128" s="37"/>
+      <c r="N128" s="37"/>
     </row>
     <row r="129">
-      <c r="K129" s="17"/>
-      <c r="L129" s="37"/>
+      <c r="L129" s="17"/>
       <c r="M129" s="37"/>
+      <c r="N129" s="37"/>
     </row>
     <row r="130">
-      <c r="K130" s="17"/>
-      <c r="L130" s="37"/>
+      <c r="L130" s="17"/>
       <c r="M130" s="37"/>
+      <c r="N130" s="37"/>
     </row>
     <row r="131">
-      <c r="K131" s="17"/>
-      <c r="L131" s="37"/>
+      <c r="L131" s="17"/>
       <c r="M131" s="37"/>
+      <c r="N131" s="37"/>
     </row>
     <row r="132">
-      <c r="K132" s="17"/>
-      <c r="L132" s="37"/>
+      <c r="L132" s="17"/>
       <c r="M132" s="37"/>
+      <c r="N132" s="37"/>
     </row>
     <row r="133">
-      <c r="L133" s="37"/>
       <c r="M133" s="37"/>
+      <c r="N133" s="37"/>
     </row>
     <row r="134">
-      <c r="L134" s="37"/>
       <c r="M134" s="37"/>
+      <c r="N134" s="37"/>
     </row>
     <row r="135">
-      <c r="L135" s="37"/>
       <c r="M135" s="37"/>
+      <c r="N135" s="37"/>
     </row>
     <row r="136">
-      <c r="L136" s="37"/>
       <c r="M136" s="37"/>
+      <c r="N136" s="37"/>
     </row>
     <row r="137">
-      <c r="L137" s="37"/>
       <c r="M137" s="37"/>
+      <c r="N137" s="37"/>
     </row>
     <row r="138">
-      <c r="L138" s="37"/>
       <c r="M138" s="37"/>
+      <c r="N138" s="37"/>
     </row>
     <row r="139">
-      <c r="L139" s="37"/>
       <c r="M139" s="37"/>
+      <c r="N139" s="37"/>
     </row>
     <row r="140">
-      <c r="L140" s="37"/>
       <c r="M140" s="37"/>
+      <c r="N140" s="37"/>
     </row>
     <row r="141">
-      <c r="L141" s="37"/>
       <c r="M141" s="37"/>
+      <c r="N141" s="37"/>
     </row>
     <row r="142">
-      <c r="L142" s="37"/>
       <c r="M142" s="37"/>
+      <c r="N142" s="37"/>
     </row>
     <row r="143">
-      <c r="L143" s="37"/>
       <c r="M143" s="37"/>
+      <c r="N143" s="37"/>
     </row>
     <row r="144">
-      <c r="L144" s="37"/>
       <c r="M144" s="37"/>
+      <c r="N144" s="37"/>
     </row>
     <row r="145">
-      <c r="L145" s="37"/>
       <c r="M145" s="37"/>
+      <c r="N145" s="37"/>
     </row>
     <row r="146">
-      <c r="L146" s="37"/>
       <c r="M146" s="37"/>
+      <c r="N146" s="37"/>
     </row>
     <row r="147">
-      <c r="L147" s="37"/>
       <c r="M147" s="37"/>
+      <c r="N147" s="37"/>
     </row>
     <row r="148">
-      <c r="L148" s="37"/>
       <c r="M148" s="37"/>
+      <c r="N148" s="37"/>
     </row>
     <row r="149">
-      <c r="L149" s="37"/>
       <c r="M149" s="37"/>
+      <c r="N149" s="37"/>
     </row>
     <row r="150">
-      <c r="L150" s="37"/>
       <c r="M150" s="37"/>
+      <c r="N150" s="37"/>
     </row>
     <row r="151">
-      <c r="L151" s="37"/>
       <c r="M151" s="37"/>
+      <c r="N151" s="37"/>
     </row>
     <row r="152">
-      <c r="L152" s="37"/>
       <c r="M152" s="37"/>
+      <c r="N152" s="37"/>
     </row>
     <row r="153">
-      <c r="L153" s="37"/>
       <c r="M153" s="37"/>
+      <c r="N153" s="37"/>
     </row>
     <row r="154">
-      <c r="L154" s="37"/>
       <c r="M154" s="37"/>
+      <c r="N154" s="37"/>
     </row>
     <row r="155">
-      <c r="L155" s="37"/>
       <c r="M155" s="37"/>
+      <c r="N155" s="37"/>
     </row>
     <row r="156">
-      <c r="L156" s="37"/>
       <c r="M156" s="37"/>
+      <c r="N156" s="37"/>
     </row>
     <row r="157">
-      <c r="L157" s="37"/>
       <c r="M157" s="37"/>
+      <c r="N157" s="37"/>
     </row>
     <row r="158">
-      <c r="L158" s="37"/>
       <c r="M158" s="37"/>
+      <c r="N158" s="37"/>
     </row>
     <row r="159">
-      <c r="L159" s="37"/>
       <c r="M159" s="37"/>
+      <c r="N159" s="37"/>
     </row>
     <row r="160">
-      <c r="L160" s="37"/>
       <c r="M160" s="37"/>
+      <c r="N160" s="37"/>
     </row>
     <row r="161">
-      <c r="L161" s="37"/>
       <c r="M161" s="37"/>
+      <c r="N161" s="37"/>
     </row>
     <row r="162">
-      <c r="L162" s="37"/>
       <c r="M162" s="37"/>
+      <c r="N162" s="37"/>
     </row>
     <row r="163">
-      <c r="L163" s="37"/>
       <c r="M163" s="37"/>
+      <c r="N163" s="37"/>
     </row>
     <row r="164">
-      <c r="L164" s="37"/>
       <c r="M164" s="37"/>
+      <c r="N164" s="37"/>
     </row>
     <row r="165">
-      <c r="L165" s="37"/>
       <c r="M165" s="37"/>
+      <c r="N165" s="37"/>
     </row>
     <row r="166">
-      <c r="L166" s="37"/>
       <c r="M166" s="37"/>
+      <c r="N166" s="37"/>
     </row>
     <row r="167">
-      <c r="L167" s="37"/>
       <c r="M167" s="37"/>
+      <c r="N167" s="37"/>
     </row>
     <row r="168">
-      <c r="L168" s="37"/>
       <c r="M168" s="37"/>
+      <c r="N168" s="37"/>
     </row>
     <row r="169">
-      <c r="L169" s="37"/>
       <c r="M169" s="37"/>
+      <c r="N169" s="37"/>
     </row>
     <row r="170">
-      <c r="L170" s="37"/>
       <c r="M170" s="37"/>
+      <c r="N170" s="37"/>
     </row>
     <row r="171">
-      <c r="L171" s="37"/>
       <c r="M171" s="37"/>
+      <c r="N171" s="37"/>
     </row>
     <row r="172">
-      <c r="L172" s="37"/>
       <c r="M172" s="37"/>
+      <c r="N172" s="37"/>
     </row>
     <row r="173">
-      <c r="L173" s="37"/>
       <c r="M173" s="37"/>
+      <c r="N173" s="37"/>
     </row>
     <row r="174">
-      <c r="L174" s="37"/>
       <c r="M174" s="37"/>
+      <c r="N174" s="37"/>
     </row>
     <row r="175">
-      <c r="L175" s="37"/>
       <c r="M175" s="37"/>
+      <c r="N175" s="37"/>
     </row>
     <row r="176">
-      <c r="L176" s="37"/>
       <c r="M176" s="37"/>
+      <c r="N176" s="37"/>
     </row>
     <row r="177">
-      <c r="L177" s="37"/>
       <c r="M177" s="37"/>
+      <c r="N177" s="37"/>
     </row>
     <row r="178">
-      <c r="L178" s="37"/>
       <c r="M178" s="37"/>
+      <c r="N178" s="37"/>
     </row>
     <row r="179">
-      <c r="L179" s="37"/>
       <c r="M179" s="37"/>
+      <c r="N179" s="37"/>
     </row>
     <row r="180">
-      <c r="L180" s="37"/>
       <c r="M180" s="37"/>
+      <c r="N180" s="37"/>
     </row>
     <row r="181">
-      <c r="L181" s="37"/>
       <c r="M181" s="37"/>
+      <c r="N181" s="37"/>
     </row>
     <row r="182">
-      <c r="L182" s="37"/>
       <c r="M182" s="37"/>
+      <c r="N182" s="37"/>
     </row>
     <row r="183">
-      <c r="L183" s="37"/>
       <c r="M183" s="37"/>
+      <c r="N183" s="37"/>
     </row>
     <row r="184">
-      <c r="L184" s="37"/>
       <c r="M184" s="37"/>
+      <c r="N184" s="37"/>
     </row>
     <row r="185">
-      <c r="L185" s="37"/>
       <c r="M185" s="37"/>
+      <c r="N185" s="37"/>
     </row>
     <row r="186">
-      <c r="L186" s="37"/>
       <c r="M186" s="37"/>
+      <c r="N186" s="37"/>
     </row>
     <row r="187">
-      <c r="L187" s="37"/>
       <c r="M187" s="37"/>
+      <c r="N187" s="37"/>
     </row>
     <row r="188">
-      <c r="L188" s="37"/>
       <c r="M188" s="37"/>
+      <c r="N188" s="37"/>
     </row>
     <row r="189">
-      <c r="L189" s="37"/>
       <c r="M189" s="37"/>
+      <c r="N189" s="37"/>
     </row>
     <row r="190">
-      <c r="L190" s="37"/>
       <c r="M190" s="37"/>
+      <c r="N190" s="37"/>
     </row>
     <row r="191">
-      <c r="L191" s="37"/>
       <c r="M191" s="37"/>
+      <c r="N191" s="37"/>
     </row>
     <row r="192">
-      <c r="L192" s="37"/>
       <c r="M192" s="37"/>
+      <c r="N192" s="37"/>
     </row>
     <row r="193">
-      <c r="L193" s="37"/>
       <c r="M193" s="37"/>
+      <c r="N193" s="37"/>
     </row>
     <row r="194">
-      <c r="L194" s="37"/>
       <c r="M194" s="37"/>
+      <c r="N194" s="37"/>
     </row>
     <row r="195">
-      <c r="L195" s="37"/>
       <c r="M195" s="37"/>
+      <c r="N195" s="37"/>
     </row>
     <row r="196">
-      <c r="L196" s="37"/>
       <c r="M196" s="37"/>
+      <c r="N196" s="37"/>
     </row>
     <row r="197">
-      <c r="L197" s="37"/>
       <c r="M197" s="37"/>
+      <c r="N197" s="37"/>
     </row>
     <row r="198">
-      <c r="L198" s="37"/>
       <c r="M198" s="37"/>
+      <c r="N198" s="37"/>
     </row>
     <row r="199">
-      <c r="L199" s="37"/>
       <c r="M199" s="37"/>
+      <c r="N199" s="37"/>
     </row>
     <row r="200">
-      <c r="L200" s="37"/>
       <c r="M200" s="37"/>
+      <c r="N200" s="37"/>
     </row>
     <row r="201">
-      <c r="L201" s="37"/>
       <c r="M201" s="37"/>
+      <c r="N201" s="37"/>
     </row>
     <row r="202">
-      <c r="L202" s="37"/>
       <c r="M202" s="37"/>
+      <c r="N202" s="37"/>
     </row>
     <row r="203">
-      <c r="L203" s="37"/>
       <c r="M203" s="37"/>
+      <c r="N203" s="37"/>
     </row>
     <row r="204">
-      <c r="L204" s="37"/>
       <c r="M204" s="37"/>
+      <c r="N204" s="37"/>
     </row>
     <row r="205">
-      <c r="L205" s="37"/>
       <c r="M205" s="37"/>
+      <c r="N205" s="37"/>
     </row>
     <row r="206">
-      <c r="L206" s="37"/>
       <c r="M206" s="37"/>
+      <c r="N206" s="37"/>
     </row>
     <row r="207">
-      <c r="L207" s="37"/>
       <c r="M207" s="37"/>
+      <c r="N207" s="37"/>
     </row>
     <row r="208">
-      <c r="L208" s="37"/>
       <c r="M208" s="37"/>
+      <c r="N208" s="37"/>
     </row>
     <row r="209">
-      <c r="L209" s="37"/>
       <c r="M209" s="37"/>
+      <c r="N209" s="37"/>
     </row>
     <row r="210">
-      <c r="L210" s="37"/>
       <c r="M210" s="37"/>
+      <c r="N210" s="37"/>
     </row>
     <row r="211">
-      <c r="L211" s="37"/>
       <c r="M211" s="37"/>
+      <c r="N211" s="37"/>
     </row>
     <row r="212">
-      <c r="L212" s="37"/>
       <c r="M212" s="37"/>
+      <c r="N212" s="37"/>
     </row>
     <row r="213">
-      <c r="L213" s="37"/>
       <c r="M213" s="37"/>
+      <c r="N213" s="37"/>
     </row>
     <row r="214">
-      <c r="L214" s="37"/>
       <c r="M214" s="37"/>
+      <c r="N214" s="37"/>
     </row>
     <row r="215">
-      <c r="L215" s="37"/>
       <c r="M215" s="37"/>
+      <c r="N215" s="37"/>
     </row>
     <row r="216">
-      <c r="L216" s="37"/>
       <c r="M216" s="37"/>
+      <c r="N216" s="37"/>
     </row>
     <row r="217">
-      <c r="L217" s="37"/>
       <c r="M217" s="37"/>
+      <c r="N217" s="37"/>
     </row>
     <row r="218">
-      <c r="L218" s="37"/>
       <c r="M218" s="37"/>
+      <c r="N218" s="37"/>
     </row>
     <row r="219">
-      <c r="L219" s="37"/>
       <c r="M219" s="37"/>
+      <c r="N219" s="37"/>
     </row>
     <row r="220">
-      <c r="L220" s="37"/>
       <c r="M220" s="37"/>
+      <c r="N220" s="37"/>
     </row>
     <row r="221">
-      <c r="L221" s="37"/>
       <c r="M221" s="37"/>
+      <c r="N221" s="37"/>
     </row>
     <row r="222">
-      <c r="L222" s="37"/>
       <c r="M222" s="37"/>
+      <c r="N222" s="37"/>
     </row>
     <row r="223">
-      <c r="L223" s="37"/>
       <c r="M223" s="37"/>
+      <c r="N223" s="37"/>
     </row>
     <row r="224">
-      <c r="L224" s="37"/>
       <c r="M224" s="37"/>
+      <c r="N224" s="37"/>
     </row>
     <row r="225">
-      <c r="L225" s="37"/>
       <c r="M225" s="37"/>
+      <c r="N225" s="37"/>
     </row>
     <row r="226">
-      <c r="L226" s="37"/>
       <c r="M226" s="37"/>
+      <c r="N226" s="37"/>
     </row>
     <row r="227">
-      <c r="L227" s="37"/>
       <c r="M227" s="37"/>
+      <c r="N227" s="37"/>
     </row>
     <row r="228">
-      <c r="L228" s="37"/>
       <c r="M228" s="37"/>
+      <c r="N228" s="37"/>
     </row>
     <row r="229">
-      <c r="L229" s="37"/>
       <c r="M229" s="37"/>
+      <c r="N229" s="37"/>
     </row>
     <row r="230">
-      <c r="L230" s="37"/>
       <c r="M230" s="37"/>
+      <c r="N230" s="37"/>
     </row>
     <row r="231">
-      <c r="L231" s="37"/>
       <c r="M231" s="37"/>
+      <c r="N231" s="37"/>
     </row>
     <row r="232">
-      <c r="L232" s="37"/>
       <c r="M232" s="37"/>
+      <c r="N232" s="37"/>
     </row>
     <row r="233">
-      <c r="L233" s="37"/>
       <c r="M233" s="37"/>
+      <c r="N233" s="37"/>
     </row>
     <row r="234">
-      <c r="L234" s="37"/>
       <c r="M234" s="37"/>
+      <c r="N234" s="37"/>
     </row>
     <row r="235">
-      <c r="L235" s="37"/>
       <c r="M235" s="37"/>
+      <c r="N235" s="37"/>
     </row>
     <row r="236">
-      <c r="L236" s="37"/>
       <c r="M236" s="37"/>
+      <c r="N236" s="37"/>
     </row>
     <row r="237">
-      <c r="L237" s="37"/>
       <c r="M237" s="37"/>
+      <c r="N237" s="37"/>
     </row>
     <row r="238">
-      <c r="L238" s="37"/>
       <c r="M238" s="37"/>
+      <c r="N238" s="37"/>
     </row>
     <row r="239">
-      <c r="L239" s="37"/>
       <c r="M239" s="37"/>
+      <c r="N239" s="37"/>
     </row>
     <row r="240">
-      <c r="L240" s="37"/>
       <c r="M240" s="37"/>
+      <c r="N240" s="37"/>
     </row>
     <row r="241">
-      <c r="L241" s="37"/>
       <c r="M241" s="37"/>
+      <c r="N241" s="37"/>
     </row>
     <row r="242">
-      <c r="L242" s="37"/>
       <c r="M242" s="37"/>
+      <c r="N242" s="37"/>
     </row>
     <row r="243">
-      <c r="L243" s="37"/>
       <c r="M243" s="37"/>
+      <c r="N243" s="37"/>
     </row>
     <row r="244">
-      <c r="L244" s="37"/>
       <c r="M244" s="37"/>
+      <c r="N244" s="37"/>
     </row>
     <row r="245">
-      <c r="L245" s="37"/>
       <c r="M245" s="37"/>
+      <c r="N245" s="37"/>
     </row>
     <row r="246">
-      <c r="L246" s="37"/>
       <c r="M246" s="37"/>
+      <c r="N246" s="37"/>
     </row>
     <row r="247">
-      <c r="L247" s="37"/>
       <c r="M247" s="37"/>
+      <c r="N247" s="37"/>
     </row>
     <row r="248">
-      <c r="L248" s="37"/>
       <c r="M248" s="37"/>
+      <c r="N248" s="37"/>
     </row>
     <row r="249">
-      <c r="L249" s="37"/>
       <c r="M249" s="37"/>
+      <c r="N249" s="37"/>
     </row>
     <row r="250">
-      <c r="L250" s="37"/>
       <c r="M250" s="37"/>
+      <c r="N250" s="37"/>
     </row>
     <row r="251">
-      <c r="L251" s="37"/>
       <c r="M251" s="37"/>
+      <c r="N251" s="37"/>
     </row>
     <row r="252">
-      <c r="L252" s="37"/>
       <c r="M252" s="37"/>
+      <c r="N252" s="37"/>
     </row>
     <row r="253">
-      <c r="L253" s="37"/>
       <c r="M253" s="37"/>
+      <c r="N253" s="37"/>
     </row>
     <row r="254">
-      <c r="L254" s="37"/>
       <c r="M254" s="37"/>
+      <c r="N254" s="37"/>
     </row>
     <row r="255">
-      <c r="L255" s="37"/>
       <c r="M255" s="37"/>
+      <c r="N255" s="37"/>
     </row>
     <row r="256">
-      <c r="L256" s="37"/>
       <c r="M256" s="37"/>
+      <c r="N256" s="37"/>
     </row>
     <row r="257">
-      <c r="L257" s="37"/>
       <c r="M257" s="37"/>
+      <c r="N257" s="37"/>
     </row>
     <row r="258">
-      <c r="L258" s="37"/>
       <c r="M258" s="37"/>
+      <c r="N258" s="37"/>
     </row>
     <row r="259">
-      <c r="L259" s="37"/>
       <c r="M259" s="37"/>
+      <c r="N259" s="37"/>
     </row>
     <row r="260">
-      <c r="L260" s="37"/>
       <c r="M260" s="37"/>
+      <c r="N260" s="37"/>
     </row>
     <row r="261">
-      <c r="L261" s="37"/>
       <c r="M261" s="37"/>
+      <c r="N261" s="37"/>
     </row>
     <row r="262">
-      <c r="L262" s="37"/>
       <c r="M262" s="37"/>
+      <c r="N262" s="37"/>
     </row>
     <row r="263">
-      <c r="L263" s="37"/>
       <c r="M263" s="37"/>
+      <c r="N263" s="37"/>
     </row>
     <row r="264">
-      <c r="L264" s="37"/>
       <c r="M264" s="37"/>
+      <c r="N264" s="37"/>
     </row>
     <row r="265">
-      <c r="L265" s="37"/>
       <c r="M265" s="37"/>
+      <c r="N265" s="37"/>
     </row>
     <row r="266">
-      <c r="L266" s="37"/>
       <c r="M266" s="37"/>
+      <c r="N266" s="37"/>
     </row>
     <row r="267">
-      <c r="L267" s="37"/>
       <c r="M267" s="37"/>
+      <c r="N267" s="37"/>
     </row>
     <row r="268">
-      <c r="L268" s="37"/>
       <c r="M268" s="37"/>
+      <c r="N268" s="37"/>
     </row>
     <row r="269">
-      <c r="L269" s="37"/>
       <c r="M269" s="37"/>
+      <c r="N269" s="37"/>
     </row>
     <row r="270">
-      <c r="L270" s="37"/>
       <c r="M270" s="37"/>
+      <c r="N270" s="37"/>
     </row>
     <row r="271">
-      <c r="L271" s="37"/>
       <c r="M271" s="37"/>
+      <c r="N271" s="37"/>
     </row>
     <row r="272">
-      <c r="L272" s="37"/>
       <c r="M272" s="37"/>
+      <c r="N272" s="37"/>
     </row>
     <row r="273">
-      <c r="L273" s="37"/>
       <c r="M273" s="37"/>
+      <c r="N273" s="37"/>
     </row>
     <row r="274">
-      <c r="L274" s="37"/>
       <c r="M274" s="37"/>
+      <c r="N274" s="37"/>
     </row>
     <row r="275">
-      <c r="L275" s="37"/>
       <c r="M275" s="37"/>
+      <c r="N275" s="37"/>
     </row>
     <row r="276">
-      <c r="L276" s="37"/>
       <c r="M276" s="37"/>
+      <c r="N276" s="37"/>
     </row>
     <row r="277">
-      <c r="L277" s="37"/>
       <c r="M277" s="37"/>
+      <c r="N277" s="37"/>
     </row>
     <row r="278">
-      <c r="L278" s="37"/>
       <c r="M278" s="37"/>
+      <c r="N278" s="37"/>
     </row>
     <row r="279">
-      <c r="L279" s="37"/>
       <c r="M279" s="37"/>
+      <c r="N279" s="37"/>
     </row>
     <row r="280">
-      <c r="L280" s="37"/>
       <c r="M280" s="37"/>
+      <c r="N280" s="37"/>
     </row>
     <row r="281">
-      <c r="L281" s="37"/>
       <c r="M281" s="37"/>
+      <c r="N281" s="37"/>
     </row>
     <row r="282">
-      <c r="L282" s="37"/>
       <c r="M282" s="37"/>
+      <c r="N282" s="37"/>
     </row>
     <row r="283">
-      <c r="L283" s="37"/>
       <c r="M283" s="37"/>
+      <c r="N283" s="37"/>
     </row>
     <row r="284">
-      <c r="L284" s="37"/>
       <c r="M284" s="37"/>
+      <c r="N284" s="37"/>
     </row>
     <row r="285">
-      <c r="L285" s="37"/>
       <c r="M285" s="37"/>
+      <c r="N285" s="37"/>
     </row>
     <row r="286">
-      <c r="L286" s="37"/>
       <c r="M286" s="37"/>
+      <c r="N286" s="37"/>
     </row>
     <row r="287">
-      <c r="L287" s="37"/>
       <c r="M287" s="37"/>
+      <c r="N287" s="37"/>
     </row>
     <row r="288">
-      <c r="L288" s="37"/>
       <c r="M288" s="37"/>
+      <c r="N288" s="37"/>
     </row>
     <row r="289">
-      <c r="L289" s="37"/>
       <c r="M289" s="37"/>
+      <c r="N289" s="37"/>
     </row>
     <row r="290">
-      <c r="L290" s="37"/>
       <c r="M290" s="37"/>
+      <c r="N290" s="37"/>
     </row>
     <row r="291">
-      <c r="L291" s="37"/>
       <c r="M291" s="37"/>
+      <c r="N291" s="37"/>
     </row>
     <row r="292">
-      <c r="L292" s="37"/>
       <c r="M292" s="37"/>
+      <c r="N292" s="37"/>
     </row>
     <row r="293">
-      <c r="L293" s="37"/>
       <c r="M293" s="37"/>
+      <c r="N293" s="37"/>
     </row>
     <row r="294">
-      <c r="L294" s="37"/>
       <c r="M294" s="37"/>
+      <c r="N294" s="37"/>
     </row>
     <row r="295">
-      <c r="L295" s="37"/>
       <c r="M295" s="37"/>
+      <c r="N295" s="37"/>
     </row>
     <row r="296">
-      <c r="L296" s="37"/>
       <c r="M296" s="37"/>
+      <c r="N296" s="37"/>
     </row>
     <row r="297">
-      <c r="L297" s="37"/>
       <c r="M297" s="37"/>
+      <c r="N297" s="37"/>
     </row>
     <row r="298">
-      <c r="L298" s="37"/>
       <c r="M298" s="37"/>
+      <c r="N298" s="37"/>
     </row>
     <row r="299">
-      <c r="L299" s="37"/>
       <c r="M299" s="37"/>
+      <c r="N299" s="37"/>
     </row>
     <row r="300">
-      <c r="L300" s="37"/>
       <c r="M300" s="37"/>
+      <c r="N300" s="37"/>
     </row>
     <row r="301">
-      <c r="L301" s="37"/>
       <c r="M301" s="37"/>
+      <c r="N301" s="37"/>
     </row>
     <row r="302">
-      <c r="L302" s="37"/>
       <c r="M302" s="37"/>
+      <c r="N302" s="37"/>
     </row>
     <row r="303">
-      <c r="L303" s="37"/>
       <c r="M303" s="37"/>
+      <c r="N303" s="37"/>
     </row>
     <row r="304">
-      <c r="L304" s="37"/>
       <c r="M304" s="37"/>
+      <c r="N304" s="37"/>
     </row>
     <row r="305">
-      <c r="L305" s="37"/>
       <c r="M305" s="37"/>
+      <c r="N305" s="37"/>
     </row>
     <row r="306">
-      <c r="L306" s="37"/>
       <c r="M306" s="37"/>
+      <c r="N306" s="37"/>
     </row>
     <row r="307">
-      <c r="L307" s="37"/>
       <c r="M307" s="37"/>
+      <c r="N307" s="37"/>
     </row>
     <row r="308">
-      <c r="L308" s="37"/>
       <c r="M308" s="37"/>
+      <c r="N308" s="37"/>
     </row>
     <row r="309">
-      <c r="L309" s="37"/>
       <c r="M309" s="37"/>
+      <c r="N309" s="37"/>
     </row>
     <row r="310">
-      <c r="L310" s="37"/>
       <c r="M310" s="37"/>
+      <c r="N310" s="37"/>
     </row>
     <row r="311">
-      <c r="L311" s="37"/>
       <c r="M311" s="37"/>
+      <c r="N311" s="37"/>
     </row>
     <row r="312">
-      <c r="L312" s="37"/>
       <c r="M312" s="37"/>
+      <c r="N312" s="37"/>
     </row>
     <row r="313">
-      <c r="L313" s="37"/>
       <c r="M313" s="37"/>
+      <c r="N313" s="37"/>
     </row>
     <row r="314">
-      <c r="L314" s="37"/>
       <c r="M314" s="37"/>
+      <c r="N314" s="37"/>
     </row>
     <row r="315">
-      <c r="L315" s="37"/>
       <c r="M315" s="37"/>
+      <c r="N315" s="37"/>
     </row>
     <row r="316">
-      <c r="L316" s="37"/>
       <c r="M316" s="37"/>
+      <c r="N316" s="37"/>
     </row>
     <row r="317">
-      <c r="L317" s="37"/>
       <c r="M317" s="37"/>
+      <c r="N317" s="37"/>
     </row>
     <row r="318">
-      <c r="L318" s="37"/>
       <c r="M318" s="37"/>
+      <c r="N318" s="37"/>
     </row>
     <row r="319">
-      <c r="L319" s="37"/>
       <c r="M319" s="37"/>
+      <c r="N319" s="37"/>
     </row>
     <row r="320">
-      <c r="L320" s="37"/>
       <c r="M320" s="37"/>
+      <c r="N320" s="37"/>
     </row>
     <row r="321">
-      <c r="L321" s="37"/>
       <c r="M321" s="37"/>
+      <c r="N321" s="37"/>
     </row>
     <row r="322">
-      <c r="L322" s="37"/>
       <c r="M322" s="37"/>
+      <c r="N322" s="37"/>
     </row>
     <row r="323">
-      <c r="L323" s="37"/>
       <c r="M323" s="37"/>
+      <c r="N323" s="37"/>
     </row>
     <row r="324">
-      <c r="L324" s="37"/>
       <c r="M324" s="37"/>
+      <c r="N324" s="37"/>
     </row>
     <row r="325">
-      <c r="L325" s="37"/>
       <c r="M325" s="37"/>
+      <c r="N325" s="37"/>
     </row>
     <row r="326">
-      <c r="L326" s="37"/>
       <c r="M326" s="37"/>
+      <c r="N326" s="37"/>
     </row>
     <row r="327">
-      <c r="L327" s="37"/>
       <c r="M327" s="37"/>
+      <c r="N327" s="37"/>
     </row>
     <row r="328">
-      <c r="L328" s="37"/>
       <c r="M328" s="37"/>
+      <c r="N328" s="37"/>
     </row>
     <row r="329">
-      <c r="L329" s="37"/>
       <c r="M329" s="37"/>
+      <c r="N329" s="37"/>
     </row>
     <row r="330">
-      <c r="L330" s="37"/>
       <c r="M330" s="37"/>
+      <c r="N330" s="37"/>
     </row>
     <row r="331">
-      <c r="L331" s="37"/>
       <c r="M331" s="37"/>
+      <c r="N331" s="37"/>
     </row>
     <row r="332">
-      <c r="L332" s="37"/>
       <c r="M332" s="37"/>
+      <c r="N332" s="37"/>
     </row>
     <row r="333">
-      <c r="L333" s="37"/>
       <c r="M333" s="37"/>
+      <c r="N333" s="37"/>
     </row>
     <row r="334">
-      <c r="L334" s="37"/>
       <c r="M334" s="37"/>
+      <c r="N334" s="37"/>
     </row>
     <row r="335">
-      <c r="L335" s="37"/>
       <c r="M335" s="37"/>
+      <c r="N335" s="37"/>
     </row>
     <row r="336">
-      <c r="L336" s="37"/>
       <c r="M336" s="37"/>
+      <c r="N336" s="37"/>
     </row>
     <row r="337">
-      <c r="L337" s="37"/>
       <c r="M337" s="37"/>
+      <c r="N337" s="37"/>
     </row>
     <row r="338">
-      <c r="L338" s="37"/>
       <c r="M338" s="37"/>
+      <c r="N338" s="37"/>
     </row>
     <row r="339">
-      <c r="L339" s="37"/>
       <c r="M339" s="37"/>
+      <c r="N339" s="37"/>
     </row>
     <row r="340">
-      <c r="L340" s="37"/>
       <c r="M340" s="37"/>
+      <c r="N340" s="37"/>
     </row>
     <row r="341">
-      <c r="L341" s="37"/>
       <c r="M341" s="37"/>
+      <c r="N341" s="37"/>
     </row>
     <row r="342">
-      <c r="L342" s="37"/>
       <c r="M342" s="37"/>
+      <c r="N342" s="37"/>
     </row>
     <row r="343">
-      <c r="L343" s="37"/>
       <c r="M343" s="37"/>
+      <c r="N343" s="37"/>
     </row>
     <row r="344">
-      <c r="L344" s="37"/>
       <c r="M344" s="37"/>
+      <c r="N344" s="37"/>
     </row>
     <row r="345">
-      <c r="L345" s="37"/>
       <c r="M345" s="37"/>
+      <c r="N345" s="37"/>
     </row>
     <row r="346">
-      <c r="L346" s="37"/>
       <c r="M346" s="37"/>
+      <c r="N346" s="37"/>
     </row>
     <row r="347">
-      <c r="L347" s="37"/>
       <c r="M347" s="37"/>
+      <c r="N347" s="37"/>
     </row>
     <row r="348">
-      <c r="L348" s="37"/>
       <c r="M348" s="37"/>
+      <c r="N348" s="37"/>
     </row>
     <row r="349">
-      <c r="L349" s="37"/>
       <c r="M349" s="37"/>
+      <c r="N349" s="37"/>
     </row>
     <row r="350">
-      <c r="L350" s="37"/>
       <c r="M350" s="37"/>
+      <c r="N350" s="37"/>
     </row>
     <row r="351">
-      <c r="L351" s="37"/>
       <c r="M351" s="37"/>
+      <c r="N351" s="37"/>
     </row>
     <row r="352">
-      <c r="L352" s="37"/>
       <c r="M352" s="37"/>
+      <c r="N352" s="37"/>
     </row>
     <row r="353">
-      <c r="L353" s="37"/>
       <c r="M353" s="37"/>
+      <c r="N353" s="37"/>
     </row>
     <row r="354">
-      <c r="L354" s="37"/>
       <c r="M354" s="37"/>
+      <c r="N354" s="37"/>
     </row>
     <row r="355">
-      <c r="L355" s="37"/>
       <c r="M355" s="37"/>
+      <c r="N355" s="37"/>
     </row>
     <row r="356">
-      <c r="L356" s="37"/>
       <c r="M356" s="37"/>
+      <c r="N356" s="37"/>
     </row>
     <row r="357">
-      <c r="L357" s="37"/>
       <c r="M357" s="37"/>
+      <c r="N357" s="37"/>
     </row>
     <row r="358">
-      <c r="L358" s="37"/>
       <c r="M358" s="37"/>
+      <c r="N358" s="37"/>
     </row>
     <row r="359">
-      <c r="L359" s="37"/>
       <c r="M359" s="37"/>
+      <c r="N359" s="37"/>
     </row>
     <row r="360">
-      <c r="L360" s="37"/>
       <c r="M360" s="37"/>
+      <c r="N360" s="37"/>
     </row>
     <row r="361">
-      <c r="L361" s="37"/>
       <c r="M361" s="37"/>
+      <c r="N361" s="37"/>
     </row>
     <row r="362">
-      <c r="L362" s="37"/>
       <c r="M362" s="37"/>
+      <c r="N362" s="37"/>
     </row>
     <row r="363">
-      <c r="L363" s="37"/>
       <c r="M363" s="37"/>
+      <c r="N363" s="37"/>
     </row>
     <row r="364">
-      <c r="L364" s="37"/>
       <c r="M364" s="37"/>
+      <c r="N364" s="37"/>
     </row>
     <row r="365">
-      <c r="L365" s="37"/>
       <c r="M365" s="37"/>
+      <c r="N365" s="37"/>
     </row>
     <row r="366">
-      <c r="L366" s="37"/>
       <c r="M366" s="37"/>
+      <c r="N366" s="37"/>
     </row>
     <row r="367">
-      <c r="L367" s="37"/>
       <c r="M367" s="37"/>
+      <c r="N367" s="37"/>
     </row>
     <row r="368">
-      <c r="L368" s="37"/>
       <c r="M368" s="37"/>
+      <c r="N368" s="37"/>
     </row>
     <row r="369">
-      <c r="L369" s="37"/>
       <c r="M369" s="37"/>
+      <c r="N369" s="37"/>
     </row>
     <row r="370">
-      <c r="L370" s="37"/>
       <c r="M370" s="37"/>
+      <c r="N370" s="37"/>
     </row>
     <row r="371">
-      <c r="L371" s="37"/>
       <c r="M371" s="37"/>
+      <c r="N371" s="37"/>
     </row>
     <row r="372">
-      <c r="L372" s="37"/>
       <c r="M372" s="37"/>
+      <c r="N372" s="37"/>
     </row>
     <row r="373">
-      <c r="L373" s="37"/>
       <c r="M373" s="37"/>
+      <c r="N373" s="37"/>
     </row>
     <row r="374">
-      <c r="L374" s="37"/>
       <c r="M374" s="37"/>
+      <c r="N374" s="37"/>
     </row>
     <row r="375">
-      <c r="L375" s="37"/>
       <c r="M375" s="37"/>
+      <c r="N375" s="37"/>
     </row>
     <row r="376">
-      <c r="L376" s="37"/>
       <c r="M376" s="37"/>
+      <c r="N376" s="37"/>
     </row>
     <row r="377">
-      <c r="L377" s="37"/>
       <c r="M377" s="37"/>
+      <c r="N377" s="37"/>
     </row>
     <row r="378">
-      <c r="L378" s="37"/>
       <c r="M378" s="37"/>
+      <c r="N378" s="37"/>
     </row>
     <row r="379">
-      <c r="L379" s="37"/>
       <c r="M379" s="37"/>
+      <c r="N379" s="37"/>
     </row>
     <row r="380">
-      <c r="L380" s="37"/>
       <c r="M380" s="37"/>
+      <c r="N380" s="37"/>
     </row>
     <row r="381">
-      <c r="L381" s="37"/>
       <c r="M381" s="37"/>
+      <c r="N381" s="37"/>
     </row>
     <row r="382">
-      <c r="L382" s="37"/>
       <c r="M382" s="37"/>
+      <c r="N382" s="37"/>
     </row>
     <row r="383">
-      <c r="L383" s="37"/>
       <c r="M383" s="37"/>
+      <c r="N383" s="37"/>
     </row>
     <row r="384">
-      <c r="L384" s="37"/>
       <c r="M384" s="37"/>
+      <c r="N384" s="37"/>
     </row>
     <row r="385">
-      <c r="L385" s="37"/>
       <c r="M385" s="37"/>
+      <c r="N385" s="37"/>
     </row>
     <row r="386">
-      <c r="L386" s="37"/>
       <c r="M386" s="37"/>
+      <c r="N386" s="37"/>
     </row>
     <row r="387">
-      <c r="L387" s="37"/>
       <c r="M387" s="37"/>
+      <c r="N387" s="37"/>
     </row>
     <row r="388">
-      <c r="L388" s="37"/>
       <c r="M388" s="37"/>
+      <c r="N388" s="37"/>
     </row>
     <row r="389">
-      <c r="L389" s="37"/>
       <c r="M389" s="37"/>
+      <c r="N389" s="37"/>
     </row>
     <row r="390">
-      <c r="L390" s="37"/>
       <c r="M390" s="37"/>
+      <c r="N390" s="37"/>
     </row>
     <row r="391">
-      <c r="L391" s="37"/>
       <c r="M391" s="37"/>
+      <c r="N391" s="37"/>
     </row>
     <row r="392">
-      <c r="L392" s="37"/>
       <c r="M392" s="37"/>
+      <c r="N392" s="37"/>
     </row>
     <row r="393">
-      <c r="L393" s="37"/>
       <c r="M393" s="37"/>
+      <c r="N393" s="37"/>
     </row>
     <row r="394">
-      <c r="L394" s="37"/>
       <c r="M394" s="37"/>
+      <c r="N394" s="37"/>
     </row>
     <row r="395">
-      <c r="L395" s="37"/>
       <c r="M395" s="37"/>
+      <c r="N395" s="37"/>
     </row>
     <row r="396">
-      <c r="L396" s="37"/>
       <c r="M396" s="37"/>
+      <c r="N396" s="37"/>
     </row>
     <row r="397">
-      <c r="L397" s="37"/>
       <c r="M397" s="37"/>
+      <c r="N397" s="37"/>
     </row>
     <row r="398">
-      <c r="L398" s="37"/>
       <c r="M398" s="37"/>
+      <c r="N398" s="37"/>
     </row>
     <row r="399">
-      <c r="L399" s="37"/>
       <c r="M399" s="37"/>
+      <c r="N399" s="37"/>
     </row>
     <row r="400">
-      <c r="L400" s="37"/>
       <c r="M400" s="37"/>
+      <c r="N400" s="37"/>
     </row>
     <row r="401">
-      <c r="L401" s="37"/>
       <c r="M401" s="37"/>
+      <c r="N401" s="37"/>
     </row>
     <row r="402">
-      <c r="L402" s="37"/>
       <c r="M402" s="37"/>
+      <c r="N402" s="37"/>
     </row>
     <row r="403">
-      <c r="L403" s="37"/>
       <c r="M403" s="37"/>
+      <c r="N403" s="37"/>
     </row>
     <row r="404">
-      <c r="L404" s="37"/>
       <c r="M404" s="37"/>
+      <c r="N404" s="37"/>
     </row>
     <row r="405">
-      <c r="L405" s="37"/>
       <c r="M405" s="37"/>
+      <c r="N405" s="37"/>
     </row>
     <row r="406">
-      <c r="L406" s="37"/>
       <c r="M406" s="37"/>
+      <c r="N406" s="37"/>
     </row>
     <row r="407">
-      <c r="L407" s="37"/>
       <c r="M407" s="37"/>
+      <c r="N407" s="37"/>
     </row>
     <row r="408">
-      <c r="L408" s="37"/>
       <c r="M408" s="37"/>
+      <c r="N408" s="37"/>
     </row>
     <row r="409">
-      <c r="L409" s="37"/>
       <c r="M409" s="37"/>
+      <c r="N409" s="37"/>
     </row>
     <row r="410">
-      <c r="L410" s="37"/>
       <c r="M410" s="37"/>
+      <c r="N410" s="37"/>
     </row>
     <row r="411">
-      <c r="L411" s="37"/>
       <c r="M411" s="37"/>
+      <c r="N411" s="37"/>
     </row>
     <row r="412">
-      <c r="L412" s="37"/>
       <c r="M412" s="37"/>
+      <c r="N412" s="37"/>
     </row>
     <row r="413">
-      <c r="L413" s="37"/>
       <c r="M413" s="37"/>
+      <c r="N413" s="37"/>
     </row>
     <row r="414">
-      <c r="L414" s="37"/>
       <c r="M414" s="37"/>
+      <c r="N414" s="37"/>
     </row>
     <row r="415">
-      <c r="L415" s="37"/>
       <c r="M415" s="37"/>
+      <c r="N415" s="37"/>
     </row>
     <row r="416">
-      <c r="L416" s="37"/>
       <c r="M416" s="37"/>
+      <c r="N416" s="37"/>
     </row>
     <row r="417">
-      <c r="L417" s="37"/>
       <c r="M417" s="37"/>
+      <c r="N417" s="37"/>
     </row>
     <row r="418">
-      <c r="L418" s="37"/>
       <c r="M418" s="37"/>
+      <c r="N418" s="37"/>
     </row>
     <row r="419">
-      <c r="L419" s="37"/>
       <c r="M419" s="37"/>
+      <c r="N419" s="37"/>
     </row>
     <row r="420">
-      <c r="L420" s="37"/>
       <c r="M420" s="37"/>
+      <c r="N420" s="37"/>
     </row>
     <row r="421">
-      <c r="L421" s="37"/>
       <c r="M421" s="37"/>
+      <c r="N421" s="37"/>
     </row>
     <row r="422">
-      <c r="L422" s="37"/>
       <c r="M422" s="37"/>
+      <c r="N422" s="37"/>
     </row>
     <row r="423">
-      <c r="L423" s="37"/>
       <c r="M423" s="37"/>
+      <c r="N423" s="37"/>
     </row>
     <row r="424">
-      <c r="L424" s="37"/>
       <c r="M424" s="37"/>
+      <c r="N424" s="37"/>
     </row>
     <row r="425">
-      <c r="L425" s="37"/>
       <c r="M425" s="37"/>
+      <c r="N425" s="37"/>
     </row>
     <row r="426">
-      <c r="L426" s="37"/>
       <c r="M426" s="37"/>
+      <c r="N426" s="37"/>
     </row>
     <row r="427">
-      <c r="L427" s="37"/>
       <c r="M427" s="37"/>
+      <c r="N427" s="37"/>
     </row>
     <row r="428">
-      <c r="L428" s="37"/>
       <c r="M428" s="37"/>
+      <c r="N428" s="37"/>
     </row>
     <row r="429">
-      <c r="L429" s="37"/>
       <c r="M429" s="37"/>
+      <c r="N429" s="37"/>
     </row>
     <row r="430">
-      <c r="L430" s="37"/>
       <c r="M430" s="37"/>
+      <c r="N430" s="37"/>
     </row>
     <row r="431">
-      <c r="L431" s="37"/>
       <c r="M431" s="37"/>
+      <c r="N431" s="37"/>
     </row>
     <row r="432">
-      <c r="L432" s="37"/>
       <c r="M432" s="37"/>
+      <c r="N432" s="37"/>
     </row>
     <row r="433">
-      <c r="L433" s="37"/>
       <c r="M433" s="37"/>
+      <c r="N433" s="37"/>
     </row>
     <row r="434">
-      <c r="L434" s="37"/>
       <c r="M434" s="37"/>
+      <c r="N434" s="37"/>
     </row>
     <row r="435">
-      <c r="L435" s="37"/>
       <c r="M435" s="37"/>
+      <c r="N435" s="37"/>
     </row>
     <row r="436">
-      <c r="L436" s="37"/>
       <c r="M436" s="37"/>
+      <c r="N436" s="37"/>
     </row>
     <row r="437">
-      <c r="L437" s="37"/>
       <c r="M437" s="37"/>
+      <c r="N437" s="37"/>
     </row>
     <row r="438">
-      <c r="L438" s="37"/>
       <c r="M438" s="37"/>
+      <c r="N438" s="37"/>
     </row>
     <row r="439">
-      <c r="L439" s="37"/>
       <c r="M439" s="37"/>
+      <c r="N439" s="37"/>
     </row>
     <row r="440">
-      <c r="L440" s="37"/>
       <c r="M440" s="37"/>
+      <c r="N440" s="37"/>
     </row>
     <row r="441">
-      <c r="L441" s="37"/>
       <c r="M441" s="37"/>
+      <c r="N441" s="37"/>
     </row>
     <row r="442">
-      <c r="L442" s="37"/>
       <c r="M442" s="37"/>
+      <c r="N442" s="37"/>
     </row>
     <row r="443">
-      <c r="L443" s="37"/>
       <c r="M443" s="37"/>
+      <c r="N443" s="37"/>
     </row>
     <row r="444">
-      <c r="L444" s="37"/>
       <c r="M444" s="37"/>
+      <c r="N444" s="37"/>
     </row>
     <row r="445">
-      <c r="L445" s="37"/>
       <c r="M445" s="37"/>
+      <c r="N445" s="37"/>
     </row>
     <row r="446">
-      <c r="L446" s="37"/>
       <c r="M446" s="37"/>
+      <c r="N446" s="37"/>
     </row>
     <row r="447">
-      <c r="L447" s="37"/>
       <c r="M447" s="37"/>
+      <c r="N447" s="37"/>
     </row>
     <row r="448">
-      <c r="L448" s="37"/>
       <c r="M448" s="37"/>
+      <c r="N448" s="37"/>
     </row>
     <row r="449">
-      <c r="L449" s="37"/>
       <c r="M449" s="37"/>
+      <c r="N449" s="37"/>
     </row>
     <row r="450">
-      <c r="L450" s="37"/>
       <c r="M450" s="37"/>
+      <c r="N450" s="37"/>
     </row>
     <row r="451">
-      <c r="L451" s="37"/>
       <c r="M451" s="37"/>
+      <c r="N451" s="37"/>
     </row>
     <row r="452">
-      <c r="L452" s="37"/>
       <c r="M452" s="37"/>
+      <c r="N452" s="37"/>
     </row>
     <row r="453">
-      <c r="L453" s="37"/>
       <c r="M453" s="37"/>
+      <c r="N453" s="37"/>
     </row>
     <row r="454">
-      <c r="L454" s="37"/>
       <c r="M454" s="37"/>
+      <c r="N454" s="37"/>
     </row>
     <row r="455">
-      <c r="L455" s="37"/>
       <c r="M455" s="37"/>
+      <c r="N455" s="37"/>
     </row>
     <row r="456">
-      <c r="L456" s="37"/>
       <c r="M456" s="37"/>
+      <c r="N456" s="37"/>
     </row>
     <row r="457">
-      <c r="L457" s="37"/>
       <c r="M457" s="37"/>
+      <c r="N457" s="37"/>
     </row>
     <row r="458">
-      <c r="L458" s="37"/>
       <c r="M458" s="37"/>
+      <c r="N458" s="37"/>
     </row>
     <row r="459">
-      <c r="L459" s="37"/>
       <c r="M459" s="37"/>
+      <c r="N459" s="37"/>
     </row>
     <row r="460">
-      <c r="L460" s="37"/>
       <c r="M460" s="37"/>
+      <c r="N460" s="37"/>
     </row>
     <row r="461">
-      <c r="L461" s="37"/>
       <c r="M461" s="37"/>
+      <c r="N461" s="37"/>
     </row>
     <row r="462">
-      <c r="L462" s="37"/>
       <c r="M462" s="37"/>
+      <c r="N462" s="37"/>
     </row>
     <row r="463">
-      <c r="L463" s="37"/>
       <c r="M463" s="37"/>
+      <c r="N463" s="37"/>
     </row>
     <row r="464">
-      <c r="L464" s="37"/>
       <c r="M464" s="37"/>
+      <c r="N464" s="37"/>
     </row>
     <row r="465">
-      <c r="L465" s="37"/>
       <c r="M465" s="37"/>
+      <c r="N465" s="37"/>
     </row>
     <row r="466">
-      <c r="L466" s="37"/>
       <c r="M466" s="37"/>
+      <c r="N466" s="37"/>
     </row>
     <row r="467">
-      <c r="L467" s="37"/>
       <c r="M467" s="37"/>
+      <c r="N467" s="37"/>
     </row>
     <row r="468">
-      <c r="L468" s="37"/>
       <c r="M468" s="37"/>
+      <c r="N468" s="37"/>
     </row>
     <row r="469">
-      <c r="L469" s="37"/>
       <c r="M469" s="37"/>
+      <c r="N469" s="37"/>
     </row>
     <row r="470">
-      <c r="L470" s="37"/>
       <c r="M470" s="37"/>
+      <c r="N470" s="37"/>
     </row>
     <row r="471">
-      <c r="L471" s="37"/>
       <c r="M471" s="37"/>
+      <c r="N471" s="37"/>
     </row>
     <row r="472">
-      <c r="L472" s="37"/>
       <c r="M472" s="37"/>
+      <c r="N472" s="37"/>
     </row>
     <row r="473">
-      <c r="L473" s="37"/>
       <c r="M473" s="37"/>
+      <c r="N473" s="37"/>
     </row>
     <row r="474">
-      <c r="L474" s="37"/>
       <c r="M474" s="37"/>
+      <c r="N474" s="37"/>
     </row>
     <row r="475">
-      <c r="L475" s="37"/>
       <c r="M475" s="37"/>
+      <c r="N475" s="37"/>
     </row>
     <row r="476">
-      <c r="L476" s="37"/>
       <c r="M476" s="37"/>
+      <c r="N476" s="37"/>
     </row>
     <row r="477">
-      <c r="L477" s="37"/>
       <c r="M477" s="37"/>
+      <c r="N477" s="37"/>
     </row>
     <row r="478">
-      <c r="L478" s="37"/>
       <c r="M478" s="37"/>
+      <c r="N478" s="37"/>
     </row>
     <row r="479">
-      <c r="L479" s="37"/>
       <c r="M479" s="37"/>
+      <c r="N479" s="37"/>
     </row>
     <row r="480">
-      <c r="L480" s="37"/>
       <c r="M480" s="37"/>
+      <c r="N480" s="37"/>
     </row>
     <row r="481">
-      <c r="L481" s="37"/>
       <c r="M481" s="37"/>
+      <c r="N481" s="37"/>
     </row>
     <row r="482">
-      <c r="L482" s="37"/>
       <c r="M482" s="37"/>
+      <c r="N482" s="37"/>
     </row>
     <row r="483">
-      <c r="L483" s="37"/>
       <c r="M483" s="37"/>
+      <c r="N483" s="37"/>
     </row>
     <row r="484">
-      <c r="L484" s="37"/>
       <c r="M484" s="37"/>
+      <c r="N484" s="37"/>
     </row>
     <row r="485">
-      <c r="L485" s="37"/>
       <c r="M485" s="37"/>
+      <c r="N485" s="37"/>
     </row>
     <row r="486">
-      <c r="L486" s="37"/>
       <c r="M486" s="37"/>
+      <c r="N486" s="37"/>
     </row>
     <row r="487">
-      <c r="L487" s="37"/>
       <c r="M487" s="37"/>
+      <c r="N487" s="37"/>
     </row>
     <row r="488">
-      <c r="L488" s="37"/>
       <c r="M488" s="37"/>
+      <c r="N488" s="37"/>
     </row>
     <row r="489">
-      <c r="L489" s="37"/>
       <c r="M489" s="37"/>
+      <c r="N489" s="37"/>
     </row>
     <row r="490">
-      <c r="L490" s="37"/>
       <c r="M490" s="37"/>
+      <c r="N490" s="37"/>
     </row>
     <row r="491">
-      <c r="L491" s="37"/>
       <c r="M491" s="37"/>
+      <c r="N491" s="37"/>
     </row>
     <row r="492">
-      <c r="L492" s="37"/>
       <c r="M492" s="37"/>
+      <c r="N492" s="37"/>
     </row>
     <row r="493">
-      <c r="L493" s="37"/>
       <c r="M493" s="37"/>
+      <c r="N493" s="37"/>
     </row>
     <row r="494">
-      <c r="L494" s="37"/>
       <c r="M494" s="37"/>
+      <c r="N494" s="37"/>
     </row>
     <row r="495">
-      <c r="L495" s="37"/>
       <c r="M495" s="37"/>
+      <c r="N495" s="37"/>
     </row>
     <row r="496">
-      <c r="L496" s="37"/>
       <c r="M496" s="37"/>
+      <c r="N496" s="37"/>
     </row>
     <row r="497">
-      <c r="L497" s="37"/>
       <c r="M497" s="37"/>
+      <c r="N497" s="37"/>
     </row>
     <row r="498">
-      <c r="L498" s="37"/>
       <c r="M498" s="37"/>
+      <c r="N498" s="37"/>
     </row>
     <row r="499">
-      <c r="L499" s="37"/>
       <c r="M499" s="37"/>
+      <c r="N499" s="37"/>
     </row>
     <row r="500">
-      <c r="L500" s="37"/>
       <c r="M500" s="37"/>
+      <c r="N500" s="37"/>
     </row>
     <row r="501">
-      <c r="L501" s="37"/>
       <c r="M501" s="37"/>
+      <c r="N501" s="37"/>
     </row>
     <row r="502">
-      <c r="L502" s="37"/>
       <c r="M502" s="37"/>
+      <c r="N502" s="37"/>
     </row>
     <row r="503">
-      <c r="L503" s="37"/>
       <c r="M503" s="37"/>
+      <c r="N503" s="37"/>
     </row>
     <row r="504">
-      <c r="L504" s="37"/>
       <c r="M504" s="37"/>
+      <c r="N504" s="37"/>
     </row>
     <row r="505">
-      <c r="L505" s="37"/>
       <c r="M505" s="37"/>
+      <c r="N505" s="37"/>
     </row>
     <row r="506">
-      <c r="L506" s="37"/>
       <c r="M506" s="37"/>
+      <c r="N506" s="37"/>
     </row>
     <row r="507">
-      <c r="L507" s="37"/>
       <c r="M507" s="37"/>
+      <c r="N507" s="37"/>
     </row>
     <row r="508">
-      <c r="L508" s="37"/>
       <c r="M508" s="37"/>
+      <c r="N508" s="37"/>
     </row>
     <row r="509">
-      <c r="L509" s="37"/>
       <c r="M509" s="37"/>
+      <c r="N509" s="37"/>
     </row>
     <row r="510">
-      <c r="L510" s="37"/>
       <c r="M510" s="37"/>
+      <c r="N510" s="37"/>
     </row>
     <row r="511">
-      <c r="L511" s="37"/>
       <c r="M511" s="37"/>
+      <c r="N511" s="37"/>
     </row>
     <row r="512">
-      <c r="L512" s="37"/>
       <c r="M512" s="37"/>
+      <c r="N512" s="37"/>
     </row>
     <row r="513">
-      <c r="L513" s="37"/>
       <c r="M513" s="37"/>
+      <c r="N513" s="37"/>
     </row>
     <row r="514">
-      <c r="L514" s="37"/>
       <c r="M514" s="37"/>
+      <c r="N514" s="37"/>
     </row>
     <row r="515">
-      <c r="L515" s="37"/>
       <c r="M515" s="37"/>
+      <c r="N515" s="37"/>
     </row>
     <row r="516">
-      <c r="L516" s="37"/>
       <c r="M516" s="37"/>
+      <c r="N516" s="37"/>
     </row>
     <row r="517">
-      <c r="L517" s="37"/>
       <c r="M517" s="37"/>
+      <c r="N517" s="37"/>
     </row>
     <row r="518">
-      <c r="L518" s="37"/>
       <c r="M518" s="37"/>
+      <c r="N518" s="37"/>
     </row>
     <row r="519">
-      <c r="L519" s="37"/>
       <c r="M519" s="37"/>
+      <c r="N519" s="37"/>
     </row>
     <row r="520">
-      <c r="L520" s="37"/>
       <c r="M520" s="37"/>
+      <c r="N520" s="37"/>
     </row>
     <row r="521">
-      <c r="L521" s="37"/>
       <c r="M521" s="37"/>
+      <c r="N521" s="37"/>
     </row>
     <row r="522">
-      <c r="L522" s="37"/>
       <c r="M522" s="37"/>
+      <c r="N522" s="37"/>
     </row>
     <row r="523">
-      <c r="L523" s="37"/>
       <c r="M523" s="37"/>
+      <c r="N523" s="37"/>
     </row>
     <row r="524">
-      <c r="L524" s="37"/>
       <c r="M524" s="37"/>
+      <c r="N524" s="37"/>
     </row>
     <row r="525">
-      <c r="L525" s="37"/>
       <c r="M525" s="37"/>
+      <c r="N525" s="37"/>
     </row>
     <row r="526">
-      <c r="L526" s="37"/>
       <c r="M526" s="37"/>
+      <c r="N526" s="37"/>
     </row>
     <row r="527">
-      <c r="L527" s="37"/>
       <c r="M527" s="37"/>
+      <c r="N527" s="37"/>
     </row>
     <row r="528">
-      <c r="L528" s="37"/>
       <c r="M528" s="37"/>
+      <c r="N528" s="37"/>
     </row>
     <row r="529">
-      <c r="L529" s="37"/>
       <c r="M529" s="37"/>
+      <c r="N529" s="37"/>
     </row>
     <row r="530">
-      <c r="L530" s="37"/>
       <c r="M530" s="37"/>
+      <c r="N530" s="37"/>
     </row>
     <row r="531">
-      <c r="L531" s="37"/>
       <c r="M531" s="37"/>
+      <c r="N531" s="37"/>
     </row>
     <row r="532">
-      <c r="L532" s="37"/>
       <c r="M532" s="37"/>
+      <c r="N532" s="37"/>
     </row>
     <row r="533">
-      <c r="L533" s="37"/>
       <c r="M533" s="37"/>
+      <c r="N533" s="37"/>
     </row>
     <row r="534">
-      <c r="L534" s="37"/>
       <c r="M534" s="37"/>
+      <c r="N534" s="37"/>
     </row>
     <row r="535">
-      <c r="L535" s="37"/>
       <c r="M535" s="37"/>
+      <c r="N535" s="37"/>
     </row>
     <row r="536">
-      <c r="L536" s="37"/>
       <c r="M536" s="37"/>
+      <c r="N536" s="37"/>
     </row>
     <row r="537">
-      <c r="L537" s="37"/>
       <c r="M537" s="37"/>
+      <c r="N537" s="37"/>
     </row>
     <row r="538">
-      <c r="L538" s="37"/>
       <c r="M538" s="37"/>
+      <c r="N538" s="37"/>
     </row>
     <row r="539">
-      <c r="L539" s="37"/>
       <c r="M539" s="37"/>
+      <c r="N539" s="37"/>
     </row>
     <row r="540">
-      <c r="L540" s="37"/>
       <c r="M540" s="37"/>
+      <c r="N540" s="37"/>
     </row>
     <row r="541">
-      <c r="L541" s="37"/>
       <c r="M541" s="37"/>
+      <c r="N541" s="37"/>
     </row>
     <row r="542">
-      <c r="L542" s="37"/>
       <c r="M542" s="37"/>
+      <c r="N542" s="37"/>
     </row>
     <row r="543">
-      <c r="L543" s="37"/>
       <c r="M543" s="37"/>
+      <c r="N543" s="37"/>
     </row>
     <row r="544">
-      <c r="L544" s="37"/>
       <c r="M544" s="37"/>
+      <c r="N544" s="37"/>
     </row>
     <row r="545">
-      <c r="L545" s="37"/>
       <c r="M545" s="37"/>
+      <c r="N545" s="37"/>
     </row>
     <row r="546">
-      <c r="L546" s="37"/>
       <c r="M546" s="37"/>
+      <c r="N546" s="37"/>
     </row>
     <row r="547">
-      <c r="L547" s="37"/>
       <c r="M547" s="37"/>
+      <c r="N547" s="37"/>
     </row>
     <row r="548">
-      <c r="L548" s="37"/>
       <c r="M548" s="37"/>
+      <c r="N548" s="37"/>
     </row>
     <row r="549">
-      <c r="L549" s="37"/>
       <c r="M549" s="37"/>
+      <c r="N549" s="37"/>
     </row>
     <row r="550">
-      <c r="L550" s="37"/>
       <c r="M550" s="37"/>
+      <c r="N550" s="37"/>
     </row>
     <row r="551">
-      <c r="L551" s="37"/>
       <c r="M551" s="37"/>
+      <c r="N551" s="37"/>
     </row>
     <row r="552">
-      <c r="L552" s="37"/>
       <c r="M552" s="37"/>
+      <c r="N552" s="37"/>
     </row>
     <row r="553">
-      <c r="L553" s="37"/>
       <c r="M553" s="37"/>
+      <c r="N553" s="37"/>
     </row>
     <row r="554">
-      <c r="L554" s="37"/>
       <c r="M554" s="37"/>
+      <c r="N554" s="37"/>
     </row>
     <row r="555">
-      <c r="L555" s="37"/>
       <c r="M555" s="37"/>
+      <c r="N555" s="37"/>
     </row>
     <row r="556">
-      <c r="L556" s="37"/>
       <c r="M556" s="37"/>
+      <c r="N556" s="37"/>
     </row>
     <row r="557">
-      <c r="L557" s="37"/>
       <c r="M557" s="37"/>
+      <c r="N557" s="37"/>
     </row>
     <row r="558">
-      <c r="L558" s="37"/>
       <c r="M558" s="37"/>
+      <c r="N558" s="37"/>
     </row>
     <row r="559">
-      <c r="L559" s="37"/>
       <c r="M559" s="37"/>
+      <c r="N559" s="37"/>
     </row>
     <row r="560">
-      <c r="L560" s="37"/>
       <c r="M560" s="37"/>
+      <c r="N560" s="37"/>
     </row>
     <row r="561">
-      <c r="L561" s="37"/>
       <c r="M561" s="37"/>
+      <c r="N561" s="37"/>
     </row>
     <row r="562">
-      <c r="L562" s="37"/>
       <c r="M562" s="37"/>
+      <c r="N562" s="37"/>
     </row>
     <row r="563">
-      <c r="L563" s="37"/>
       <c r="M563" s="37"/>
+      <c r="N563" s="37"/>
     </row>
     <row r="564">
-      <c r="L564" s="37"/>
       <c r="M564" s="37"/>
+      <c r="N564" s="37"/>
     </row>
     <row r="565">
-      <c r="L565" s="37"/>
       <c r="M565" s="37"/>
+      <c r="N565" s="37"/>
     </row>
     <row r="566">
-      <c r="L566" s="37"/>
       <c r="M566" s="37"/>
+      <c r="N566" s="37"/>
     </row>
     <row r="567">
-      <c r="L567" s="37"/>
       <c r="M567" s="37"/>
+      <c r="N567" s="37"/>
     </row>
     <row r="568">
-      <c r="L568" s="37"/>
       <c r="M568" s="37"/>
+      <c r="N568" s="37"/>
     </row>
     <row r="569">
-      <c r="L569" s="37"/>
       <c r="M569" s="37"/>
+      <c r="N569" s="37"/>
     </row>
     <row r="570">
-      <c r="L570" s="37"/>
       <c r="M570" s="37"/>
+      <c r="N570" s="37"/>
     </row>
     <row r="571">
-      <c r="L571" s="37"/>
       <c r="M571" s="37"/>
+      <c r="N571" s="37"/>
     </row>
     <row r="572">
-      <c r="L572" s="37"/>
       <c r="M572" s="37"/>
+      <c r="N572" s="37"/>
     </row>
     <row r="573">
-      <c r="L573" s="37"/>
       <c r="M573" s="37"/>
+      <c r="N573" s="37"/>
     </row>
     <row r="574">
-      <c r="L574" s="37"/>
       <c r="M574" s="37"/>
+      <c r="N574" s="37"/>
     </row>
     <row r="575">
-      <c r="L575" s="37"/>
       <c r="M575" s="37"/>
+      <c r="N575" s="37"/>
     </row>
     <row r="576">
-      <c r="L576" s="37"/>
       <c r="M576" s="37"/>
+      <c r="N576" s="37"/>
     </row>
     <row r="577">
-      <c r="L577" s="37"/>
       <c r="M577" s="37"/>
+      <c r="N577" s="37"/>
     </row>
     <row r="578">
-      <c r="L578" s="37"/>
       <c r="M578" s="37"/>
+      <c r="N578" s="37"/>
     </row>
     <row r="579">
-      <c r="L579" s="37"/>
       <c r="M579" s="37"/>
+      <c r="N579" s="37"/>
     </row>
     <row r="580">
-      <c r="L580" s="37"/>
       <c r="M580" s="37"/>
+      <c r="N580" s="37"/>
     </row>
     <row r="581">
-      <c r="L581" s="37"/>
       <c r="M581" s="37"/>
+      <c r="N581" s="37"/>
     </row>
     <row r="582">
-      <c r="L582" s="37"/>
       <c r="M582" s="37"/>
+      <c r="N582" s="37"/>
     </row>
     <row r="583">
-      <c r="L583" s="37"/>
       <c r="M583" s="37"/>
+      <c r="N583" s="37"/>
     </row>
     <row r="584">
-      <c r="L584" s="37"/>
       <c r="M584" s="37"/>
+      <c r="N584" s="37"/>
     </row>
     <row r="585">
-      <c r="L585" s="37"/>
       <c r="M585" s="37"/>
+      <c r="N585" s="37"/>
     </row>
     <row r="586">
-      <c r="L586" s="37"/>
       <c r="M586" s="37"/>
+      <c r="N586" s="37"/>
     </row>
     <row r="587">
-      <c r="L587" s="37"/>
       <c r="M587" s="37"/>
+      <c r="N587" s="37"/>
     </row>
     <row r="588">
-      <c r="L588" s="37"/>
       <c r="M588" s="37"/>
+      <c r="N588" s="37"/>
     </row>
     <row r="589">
-      <c r="L589" s="37"/>
       <c r="M589" s="37"/>
+      <c r="N589" s="37"/>
     </row>
     <row r="590">
-      <c r="L590" s="37"/>
       <c r="M590" s="37"/>
+      <c r="N590" s="37"/>
     </row>
     <row r="591">
-      <c r="L591" s="37"/>
       <c r="M591" s="37"/>
+      <c r="N591" s="37"/>
     </row>
     <row r="592">
-      <c r="L592" s="37"/>
       <c r="M592" s="37"/>
+      <c r="N592" s="37"/>
     </row>
     <row r="593">
-      <c r="L593" s="37"/>
       <c r="M593" s="37"/>
+      <c r="N593" s="37"/>
     </row>
     <row r="594">
-      <c r="L594" s="37"/>
       <c r="M594" s="37"/>
+      <c r="N594" s="37"/>
     </row>
     <row r="595">
-      <c r="L595" s="37"/>
       <c r="M595" s="37"/>
+      <c r="N595" s="37"/>
     </row>
     <row r="596">
-      <c r="L596" s="37"/>
       <c r="M596" s="37"/>
+      <c r="N596" s="37"/>
     </row>
     <row r="597">
-      <c r="L597" s="37"/>
       <c r="M597" s="37"/>
+      <c r="N597" s="37"/>
     </row>
     <row r="598">
-      <c r="L598" s="37"/>
       <c r="M598" s="37"/>
+      <c r="N598" s="37"/>
     </row>
     <row r="599">
-      <c r="L599" s="37"/>
       <c r="M599" s="37"/>
+      <c r="N599" s="37"/>
     </row>
     <row r="600">
-      <c r="L600" s="37"/>
       <c r="M600" s="37"/>
+      <c r="N600" s="37"/>
     </row>
     <row r="601">
-      <c r="L601" s="37"/>
       <c r="M601" s="37"/>
+      <c r="N601" s="37"/>
     </row>
     <row r="602">
-      <c r="L602" s="37"/>
       <c r="M602" s="37"/>
+      <c r="N602" s="37"/>
     </row>
     <row r="603">
-      <c r="L603" s="37"/>
       <c r="M603" s="37"/>
+      <c r="N603" s="37"/>
     </row>
     <row r="604">
-      <c r="L604" s="37"/>
       <c r="M604" s="37"/>
+      <c r="N604" s="37"/>
     </row>
     <row r="605">
-      <c r="L605" s="37"/>
       <c r="M605" s="37"/>
+      <c r="N605" s="37"/>
     </row>
     <row r="606">
-      <c r="L606" s="37"/>
       <c r="M606" s="37"/>
+      <c r="N606" s="37"/>
     </row>
     <row r="607">
-      <c r="L607" s="37"/>
       <c r="M607" s="37"/>
+      <c r="N607" s="37"/>
     </row>
     <row r="608">
-      <c r="L608" s="37"/>
       <c r="M608" s="37"/>
+      <c r="N608" s="37"/>
     </row>
     <row r="609">
-      <c r="L609" s="37"/>
       <c r="M609" s="37"/>
+      <c r="N609" s="37"/>
     </row>
     <row r="610">
-      <c r="L610" s="37"/>
       <c r="M610" s="37"/>
+      <c r="N610" s="37"/>
     </row>
     <row r="611">
-      <c r="L611" s="37"/>
       <c r="M611" s="37"/>
+      <c r="N611" s="37"/>
     </row>
     <row r="612">
-      <c r="L612" s="37"/>
       <c r="M612" s="37"/>
+      <c r="N612" s="37"/>
     </row>
     <row r="613">
-      <c r="L613" s="37"/>
       <c r="M613" s="37"/>
+      <c r="N613" s="37"/>
     </row>
     <row r="614">
-      <c r="L614" s="37"/>
       <c r="M614" s="37"/>
+      <c r="N614" s="37"/>
     </row>
     <row r="615">
-      <c r="L615" s="37"/>
       <c r="M615" s="37"/>
+      <c r="N615" s="37"/>
     </row>
     <row r="616">
-      <c r="L616" s="37"/>
       <c r="M616" s="37"/>
+      <c r="N616" s="37"/>
     </row>
     <row r="617">
-      <c r="L617" s="37"/>
       <c r="M617" s="37"/>
+      <c r="N617" s="37"/>
     </row>
     <row r="618">
-      <c r="L618" s="37"/>
       <c r="M618" s="37"/>
+      <c r="N618" s="37"/>
     </row>
     <row r="619">
-      <c r="L619" s="37"/>
       <c r="M619" s="37"/>
+      <c r="N619" s="37"/>
     </row>
     <row r="620">
-      <c r="L620" s="37"/>
       <c r="M620" s="37"/>
+      <c r="N620" s="37"/>
     </row>
     <row r="621">
-      <c r="L621" s="37"/>
       <c r="M621" s="37"/>
+      <c r="N621" s="37"/>
     </row>
     <row r="622">
-      <c r="L622" s="37"/>
       <c r="M622" s="37"/>
+      <c r="N622" s="37"/>
     </row>
     <row r="623">
-      <c r="L623" s="37"/>
       <c r="M623" s="37"/>
+      <c r="N623" s="37"/>
     </row>
     <row r="624">
-      <c r="L624" s="37"/>
       <c r="M624" s="37"/>
+      <c r="N624" s="37"/>
     </row>
     <row r="625">
-      <c r="L625" s="37"/>
       <c r="M625" s="37"/>
+      <c r="N625" s="37"/>
     </row>
     <row r="626">
-      <c r="L626" s="37"/>
       <c r="M626" s="37"/>
+      <c r="N626" s="37"/>
     </row>
     <row r="627">
-      <c r="L627" s="37"/>
       <c r="M627" s="37"/>
+      <c r="N627" s="37"/>
     </row>
     <row r="628">
-      <c r="L628" s="37"/>
       <c r="M628" s="37"/>
+      <c r="N628" s="37"/>
     </row>
     <row r="629">
-      <c r="L629" s="37"/>
       <c r="M629" s="37"/>
+      <c r="N629" s="37"/>
     </row>
     <row r="630">
-      <c r="L630" s="37"/>
       <c r="M630" s="37"/>
+      <c r="N630" s="37"/>
     </row>
     <row r="631">
-      <c r="L631" s="37"/>
       <c r="M631" s="37"/>
+      <c r="N631" s="37"/>
     </row>
     <row r="632">
-      <c r="L632" s="37"/>
       <c r="M632" s="37"/>
+      <c r="N632" s="37"/>
     </row>
     <row r="633">
-      <c r="L633" s="37"/>
       <c r="M633" s="37"/>
+      <c r="N633" s="37"/>
     </row>
     <row r="634">
-      <c r="L634" s="37"/>
       <c r="M634" s="37"/>
+      <c r="N634" s="37"/>
     </row>
     <row r="635">
-      <c r="L635" s="37"/>
       <c r="M635" s="37"/>
+      <c r="N635" s="37"/>
     </row>
     <row r="636">
-      <c r="L636" s="37"/>
       <c r="M636" s="37"/>
+      <c r="N636" s="37"/>
     </row>
     <row r="637">
-      <c r="L637" s="37"/>
       <c r="M637" s="37"/>
+      <c r="N637" s="37"/>
     </row>
     <row r="638">
-      <c r="L638" s="37"/>
       <c r="M638" s="37"/>
+      <c r="N638" s="37"/>
     </row>
     <row r="639">
-      <c r="L639" s="37"/>
       <c r="M639" s="37"/>
+      <c r="N639" s="37"/>
     </row>
     <row r="640">
-      <c r="L640" s="37"/>
       <c r="M640" s="37"/>
+      <c r="N640" s="37"/>
     </row>
     <row r="641">
-      <c r="L641" s="37"/>
       <c r="M641" s="37"/>
+      <c r="N641" s="37"/>
     </row>
     <row r="642">
-      <c r="L642" s="37"/>
       <c r="M642" s="37"/>
+      <c r="N642" s="37"/>
     </row>
     <row r="643">
-      <c r="L643" s="37"/>
       <c r="M643" s="37"/>
+      <c r="N643" s="37"/>
     </row>
     <row r="644">
-      <c r="L644" s="37"/>
       <c r="M644" s="37"/>
+      <c r="N644" s="37"/>
     </row>
     <row r="645">
-      <c r="L645" s="37"/>
       <c r="M645" s="37"/>
+      <c r="N645" s="37"/>
     </row>
     <row r="646">
-      <c r="L646" s="37"/>
       <c r="M646" s="37"/>
+      <c r="N646" s="37"/>
     </row>
     <row r="647">
-      <c r="L647" s="37"/>
       <c r="M647" s="37"/>
+      <c r="N647" s="37"/>
     </row>
     <row r="648">
-      <c r="L648" s="37"/>
       <c r="M648" s="37"/>
+      <c r="N648" s="37"/>
     </row>
     <row r="649">
-      <c r="L649" s="37"/>
       <c r="M649" s="37"/>
+      <c r="N649" s="37"/>
     </row>
     <row r="650">
-      <c r="L650" s="37"/>
       <c r="M650" s="37"/>
+      <c r="N650" s="37"/>
     </row>
     <row r="651">
-      <c r="L651" s="37"/>
       <c r="M651" s="37"/>
+      <c r="N651" s="37"/>
     </row>
     <row r="652">
-      <c r="L652" s="37"/>
       <c r="M652" s="37"/>
+      <c r="N652" s="37"/>
     </row>
     <row r="653">
-      <c r="L653" s="37"/>
       <c r="M653" s="37"/>
+      <c r="N653" s="37"/>
     </row>
     <row r="654">
-      <c r="L654" s="37"/>
       <c r="M654" s="37"/>
+      <c r="N654" s="37"/>
     </row>
     <row r="655">
-      <c r="L655" s="37"/>
       <c r="M655" s="37"/>
+      <c r="N655" s="37"/>
     </row>
     <row r="656">
-      <c r="L656" s="37"/>
       <c r="M656" s="37"/>
+      <c r="N656" s="37"/>
     </row>
     <row r="657">
-      <c r="L657" s="37"/>
       <c r="M657" s="37"/>
+      <c r="N657" s="37"/>
     </row>
     <row r="658">
-      <c r="L658" s="37"/>
       <c r="M658" s="37"/>
+      <c r="N658" s="37"/>
     </row>
     <row r="659">
-      <c r="L659" s="37"/>
       <c r="M659" s="37"/>
+      <c r="N659" s="37"/>
     </row>
     <row r="660">
-      <c r="L660" s="37"/>
       <c r="M660" s="37"/>
+      <c r="N660" s="37"/>
     </row>
     <row r="661">
-      <c r="L661" s="37"/>
       <c r="M661" s="37"/>
+      <c r="N661" s="37"/>
     </row>
     <row r="662">
-      <c r="L662" s="37"/>
       <c r="M662" s="37"/>
+      <c r="N662" s="37"/>
     </row>
     <row r="663">
-      <c r="L663" s="37"/>
       <c r="M663" s="37"/>
+      <c r="N663" s="37"/>
     </row>
     <row r="664">
-      <c r="L664" s="37"/>
       <c r="M664" s="37"/>
+      <c r="N664" s="37"/>
     </row>
     <row r="665">
-      <c r="L665" s="37"/>
       <c r="M665" s="37"/>
+      <c r="N665" s="37"/>
     </row>
     <row r="666">
-      <c r="L666" s="37"/>
       <c r="M666" s="37"/>
+      <c r="N666" s="37"/>
     </row>
     <row r="667">
-      <c r="L667" s="37"/>
       <c r="M667" s="37"/>
+      <c r="N667" s="37"/>
     </row>
     <row r="668">
-      <c r="L668" s="37"/>
       <c r="M668" s="37"/>
+      <c r="N668" s="37"/>
     </row>
     <row r="669">
-      <c r="L669" s="37"/>
       <c r="M669" s="37"/>
+      <c r="N669" s="37"/>
     </row>
     <row r="670">
-      <c r="L670" s="37"/>
       <c r="M670" s="37"/>
+      <c r="N670" s="37"/>
     </row>
     <row r="671">
-      <c r="L671" s="37"/>
       <c r="M671" s="37"/>
+      <c r="N671" s="37"/>
     </row>
     <row r="672">
-      <c r="L672" s="37"/>
       <c r="M672" s="37"/>
+      <c r="N672" s="37"/>
     </row>
     <row r="673">
-      <c r="L673" s="37"/>
       <c r="M673" s="37"/>
+      <c r="N673" s="37"/>
     </row>
     <row r="674">
-      <c r="L674" s="37"/>
       <c r="M674" s="37"/>
+      <c r="N674" s="37"/>
     </row>
     <row r="675">
-      <c r="L675" s="37"/>
       <c r="M675" s="37"/>
+      <c r="N675" s="37"/>
     </row>
     <row r="676">
-      <c r="L676" s="37"/>
       <c r="M676" s="37"/>
+      <c r="N676" s="37"/>
     </row>
     <row r="677">
-      <c r="L677" s="37"/>
       <c r="M677" s="37"/>
+      <c r="N677" s="37"/>
     </row>
     <row r="678">
-      <c r="L678" s="37"/>
       <c r="M678" s="37"/>
+      <c r="N678" s="37"/>
     </row>
     <row r="679">
-      <c r="L679" s="37"/>
       <c r="M679" s="37"/>
+      <c r="N679" s="37"/>
     </row>
     <row r="680">
-      <c r="L680" s="37"/>
       <c r="M680" s="37"/>
+      <c r="N680" s="37"/>
     </row>
     <row r="681">
-      <c r="L681" s="37"/>
       <c r="M681" s="37"/>
+      <c r="N681" s="37"/>
     </row>
     <row r="682">
-      <c r="L682" s="37"/>
       <c r="M682" s="37"/>
+      <c r="N682" s="37"/>
     </row>
     <row r="683">
-      <c r="L683" s="37"/>
       <c r="M683" s="37"/>
+      <c r="N683" s="37"/>
     </row>
     <row r="684">
-      <c r="L684" s="37"/>
       <c r="M684" s="37"/>
+      <c r="N684" s="37"/>
     </row>
     <row r="685">
-      <c r="L685" s="37"/>
       <c r="M685" s="37"/>
+      <c r="N685" s="37"/>
     </row>
     <row r="686">
-      <c r="L686" s="37"/>
       <c r="M686" s="37"/>
+      <c r="N686" s="37"/>
     </row>
     <row r="687">
-      <c r="L687" s="37"/>
       <c r="M687" s="37"/>
+      <c r="N687" s="37"/>
     </row>
     <row r="688">
-      <c r="L688" s="37"/>
       <c r="M688" s="37"/>
+      <c r="N688" s="37"/>
     </row>
     <row r="689">
-      <c r="L689" s="37"/>
       <c r="M689" s="37"/>
+      <c r="N689" s="37"/>
     </row>
     <row r="690">
-      <c r="L690" s="37"/>
       <c r="M690" s="37"/>
+      <c r="N690" s="37"/>
     </row>
     <row r="691">
-      <c r="L691" s="37"/>
       <c r="M691" s="37"/>
+      <c r="N691" s="37"/>
     </row>
     <row r="692">
-      <c r="L692" s="37"/>
       <c r="M692" s="37"/>
+      <c r="N692" s="37"/>
     </row>
     <row r="693">
-      <c r="L693" s="37"/>
       <c r="M693" s="37"/>
+      <c r="N693" s="37"/>
     </row>
     <row r="694">
-      <c r="L694" s="37"/>
       <c r="M694" s="37"/>
+      <c r="N694" s="37"/>
     </row>
     <row r="695">
-      <c r="L695" s="37"/>
       <c r="M695" s="37"/>
+      <c r="N695" s="37"/>
     </row>
     <row r="696">
-      <c r="L696" s="37"/>
       <c r="M696" s="37"/>
+      <c r="N696" s="37"/>
     </row>
     <row r="697">
-      <c r="L697" s="37"/>
       <c r="M697" s="37"/>
+      <c r="N697" s="37"/>
     </row>
     <row r="698">
-      <c r="L698" s="37"/>
       <c r="M698" s="37"/>
+      <c r="N698" s="37"/>
     </row>
     <row r="699">
-      <c r="L699" s="37"/>
       <c r="M699" s="37"/>
+      <c r="N699" s="37"/>
     </row>
     <row r="700">
-      <c r="L700" s="37"/>
       <c r="M700" s="37"/>
+      <c r="N700" s="37"/>
     </row>
     <row r="701">
-      <c r="L701" s="37"/>
       <c r="M701" s="37"/>
+      <c r="N701" s="37"/>
     </row>
     <row r="702">
-      <c r="L702" s="37"/>
       <c r="M702" s="37"/>
+      <c r="N702" s="37"/>
     </row>
     <row r="703">
-      <c r="L703" s="37"/>
       <c r="M703" s="37"/>
+      <c r="N703" s="37"/>
     </row>
     <row r="704">
-      <c r="L704" s="37"/>
       <c r="M704" s="37"/>
+      <c r="N704" s="37"/>
     </row>
     <row r="705">
-      <c r="L705" s="37"/>
       <c r="M705" s="37"/>
+      <c r="N705" s="37"/>
     </row>
     <row r="706">
-      <c r="L706" s="37"/>
       <c r="M706" s="37"/>
+      <c r="N706" s="37"/>
     </row>
     <row r="707">
-      <c r="L707" s="37"/>
       <c r="M707" s="37"/>
+      <c r="N707" s="37"/>
     </row>
     <row r="708">
-      <c r="L708" s="37"/>
       <c r="M708" s="37"/>
+      <c r="N708" s="37"/>
     </row>
     <row r="709">
-      <c r="L709" s="37"/>
       <c r="M709" s="37"/>
+      <c r="N709" s="37"/>
     </row>
     <row r="710">
-      <c r="L710" s="37"/>
       <c r="M710" s="37"/>
+      <c r="N710" s="37"/>
     </row>
     <row r="711">
-      <c r="L711" s="37"/>
       <c r="M711" s="37"/>
+      <c r="N711" s="37"/>
     </row>
     <row r="712">
-      <c r="L712" s="37"/>
       <c r="M712" s="37"/>
+      <c r="N712" s="37"/>
     </row>
     <row r="713">
-      <c r="L713" s="37"/>
       <c r="M713" s="37"/>
+      <c r="N713" s="37"/>
     </row>
     <row r="714">
-      <c r="L714" s="37"/>
       <c r="M714" s="37"/>
+      <c r="N714" s="37"/>
     </row>
     <row r="715">
-      <c r="L715" s="37"/>
       <c r="M715" s="37"/>
+      <c r="N715" s="37"/>
     </row>
     <row r="716">
-      <c r="L716" s="37"/>
       <c r="M716" s="37"/>
+      <c r="N716" s="37"/>
     </row>
     <row r="717">
-      <c r="L717" s="37"/>
       <c r="M717" s="37"/>
+      <c r="N717" s="37"/>
     </row>
     <row r="718">
-      <c r="L718" s="37"/>
       <c r="M718" s="37"/>
+      <c r="N718" s="37"/>
     </row>
     <row r="719">
-      <c r="L719" s="37"/>
       <c r="M719" s="37"/>
+      <c r="N719" s="37"/>
     </row>
     <row r="720">
-      <c r="L720" s="37"/>
       <c r="M720" s="37"/>
+      <c r="N720" s="37"/>
     </row>
     <row r="721">
-      <c r="L721" s="37"/>
       <c r="M721" s="37"/>
+      <c r="N721" s="37"/>
     </row>
     <row r="722">
-      <c r="L722" s="37"/>
       <c r="M722" s="37"/>
+      <c r="N722" s="37"/>
     </row>
     <row r="723">
-      <c r="L723" s="37"/>
       <c r="M723" s="37"/>
+      <c r="N723" s="37"/>
     </row>
     <row r="724">
-      <c r="L724" s="37"/>
       <c r="M724" s="37"/>
+      <c r="N724" s="37"/>
     </row>
     <row r="725">
-      <c r="L725" s="37"/>
       <c r="M725" s="37"/>
+      <c r="N725" s="37"/>
     </row>
     <row r="726">
-      <c r="L726" s="37"/>
       <c r="M726" s="37"/>
+      <c r="N726" s="37"/>
     </row>
     <row r="727">
-      <c r="L727" s="37"/>
       <c r="M727" s="37"/>
+      <c r="N727" s="37"/>
     </row>
     <row r="728">
-      <c r="L728" s="37"/>
       <c r="M728" s="37"/>
+      <c r="N728" s="37"/>
     </row>
     <row r="729">
-      <c r="L729" s="37"/>
       <c r="M729" s="37"/>
+      <c r="N729" s="37"/>
     </row>
     <row r="730">
-      <c r="L730" s="37"/>
       <c r="M730" s="37"/>
+      <c r="N730" s="37"/>
     </row>
     <row r="731">
-      <c r="L731" s="37"/>
       <c r="M731" s="37"/>
+      <c r="N731" s="37"/>
     </row>
     <row r="732">
-      <c r="L732" s="37"/>
       <c r="M732" s="37"/>
+      <c r="N732" s="37"/>
     </row>
     <row r="733">
-      <c r="L733" s="37"/>
       <c r="M733" s="37"/>
+      <c r="N733" s="37"/>
     </row>
     <row r="734">
-      <c r="L734" s="37"/>
       <c r="M734" s="37"/>
+      <c r="N734" s="37"/>
     </row>
     <row r="735">
-      <c r="L735" s="37"/>
       <c r="M735" s="37"/>
+      <c r="N735" s="37"/>
     </row>
     <row r="736">
-      <c r="L736" s="37"/>
       <c r="M736" s="37"/>
+      <c r="N736" s="37"/>
     </row>
     <row r="737">
-      <c r="L737" s="37"/>
       <c r="M737" s="37"/>
+      <c r="N737" s="37"/>
     </row>
     <row r="738">
-      <c r="L738" s="37"/>
       <c r="M738" s="37"/>
+      <c r="N738" s="37"/>
     </row>
     <row r="739">
-      <c r="L739" s="37"/>
       <c r="M739" s="37"/>
+      <c r="N739" s="37"/>
     </row>
     <row r="740">
-      <c r="L740" s="37"/>
       <c r="M740" s="37"/>
+      <c r="N740" s="37"/>
     </row>
     <row r="741">
-      <c r="L741" s="37"/>
       <c r="M741" s="37"/>
+      <c r="N741" s="37"/>
     </row>
     <row r="742">
-      <c r="L742" s="37"/>
       <c r="M742" s="37"/>
+      <c r="N742" s="37"/>
     </row>
     <row r="743">
-      <c r="L743" s="37"/>
       <c r="M743" s="37"/>
+      <c r="N743" s="37"/>
     </row>
     <row r="744">
-      <c r="L744" s="37"/>
       <c r="M744" s="37"/>
+      <c r="N744" s="37"/>
     </row>
     <row r="745">
-      <c r="L745" s="37"/>
       <c r="M745" s="37"/>
+      <c r="N745" s="37"/>
     </row>
     <row r="746">
-      <c r="L746" s="37"/>
       <c r="M746" s="37"/>
+      <c r="N746" s="37"/>
     </row>
     <row r="747">
-      <c r="L747" s="37"/>
       <c r="M747" s="37"/>
+      <c r="N747" s="37"/>
     </row>
     <row r="748">
-      <c r="L748" s="37"/>
       <c r="M748" s="37"/>
+      <c r="N748" s="37"/>
     </row>
     <row r="749">
-      <c r="L749" s="37"/>
       <c r="M749" s="37"/>
+      <c r="N749" s="37"/>
     </row>
     <row r="750">
-      <c r="L750" s="37"/>
       <c r="M750" s="37"/>
+      <c r="N750" s="37"/>
     </row>
     <row r="751">
-      <c r="L751" s="37"/>
       <c r="M751" s="37"/>
+      <c r="N751" s="37"/>
     </row>
     <row r="752">
-      <c r="L752" s="37"/>
       <c r="M752" s="37"/>
+      <c r="N752" s="37"/>
     </row>
     <row r="753">
-      <c r="L753" s="37"/>
       <c r="M753" s="37"/>
+      <c r="N753" s="37"/>
     </row>
     <row r="754">
-      <c r="L754" s="37"/>
       <c r="M754" s="37"/>
+      <c r="N754" s="37"/>
     </row>
     <row r="755">
-      <c r="L755" s="37"/>
       <c r="M755" s="37"/>
+      <c r="N755" s="37"/>
     </row>
     <row r="756">
-      <c r="L756" s="37"/>
       <c r="M756" s="37"/>
+      <c r="N756" s="37"/>
     </row>
     <row r="757">
-      <c r="L757" s="37"/>
       <c r="M757" s="37"/>
+      <c r="N757" s="37"/>
     </row>
     <row r="758">
-      <c r="L758" s="37"/>
       <c r="M758" s="37"/>
+      <c r="N758" s="37"/>
     </row>
     <row r="759">
-      <c r="L759" s="37"/>
       <c r="M759" s="37"/>
+      <c r="N759" s="37"/>
     </row>
     <row r="760">
-      <c r="L760" s="37"/>
       <c r="M760" s="37"/>
+      <c r="N760" s="37"/>
     </row>
     <row r="761">
-      <c r="L761" s="37"/>
       <c r="M761" s="37"/>
+      <c r="N761" s="37"/>
     </row>
     <row r="762">
-      <c r="L762" s="37"/>
       <c r="M762" s="37"/>
+      <c r="N762" s="37"/>
     </row>
     <row r="763">
-      <c r="L763" s="37"/>
       <c r="M763" s="37"/>
+      <c r="N763" s="37"/>
     </row>
     <row r="764">
-      <c r="L764" s="37"/>
       <c r="M764" s="37"/>
+      <c r="N764" s="37"/>
     </row>
     <row r="765">
-      <c r="L765" s="37"/>
       <c r="M765" s="37"/>
+      <c r="N765" s="37"/>
     </row>
     <row r="766">
-      <c r="L766" s="37"/>
       <c r="M766" s="37"/>
+      <c r="N766" s="37"/>
     </row>
     <row r="767">
-      <c r="L767" s="37"/>
       <c r="M767" s="37"/>
+      <c r="N767" s="37"/>
     </row>
     <row r="768">
-      <c r="L768" s="37"/>
       <c r="M768" s="37"/>
+      <c r="N768" s="37"/>
     </row>
     <row r="769">
-      <c r="L769" s="37"/>
       <c r="M769" s="37"/>
+      <c r="N769" s="37"/>
     </row>
     <row r="770">
-      <c r="L770" s="37"/>
       <c r="M770" s="37"/>
+      <c r="N770" s="37"/>
     </row>
     <row r="771">
-      <c r="L771" s="37"/>
       <c r="M771" s="37"/>
+      <c r="N771" s="37"/>
     </row>
     <row r="772">
-      <c r="L772" s="37"/>
       <c r="M772" s="37"/>
+      <c r="N772" s="37"/>
     </row>
     <row r="773">
-      <c r="L773" s="37"/>
       <c r="M773" s="37"/>
+      <c r="N773" s="37"/>
     </row>
     <row r="774">
-      <c r="L774" s="37"/>
       <c r="M774" s="37"/>
+      <c r="N774" s="37"/>
     </row>
     <row r="775">
-      <c r="L775" s="37"/>
       <c r="M775" s="37"/>
+      <c r="N775" s="37"/>
     </row>
     <row r="776">
-      <c r="L776" s="37"/>
       <c r="M776" s="37"/>
+      <c r="N776" s="37"/>
     </row>
     <row r="777">
-      <c r="L777" s="37"/>
       <c r="M777" s="37"/>
+      <c r="N777" s="37"/>
     </row>
     <row r="778">
-      <c r="L778" s="37"/>
       <c r="M778" s="37"/>
+      <c r="N778" s="37"/>
     </row>
     <row r="779">
-      <c r="L779" s="37"/>
       <c r="M779" s="37"/>
+      <c r="N779" s="37"/>
     </row>
     <row r="780">
-      <c r="L780" s="37"/>
       <c r="M780" s="37"/>
+      <c r="N780" s="37"/>
     </row>
     <row r="781">
-      <c r="L781" s="37"/>
       <c r="M781" s="37"/>
+      <c r="N781" s="37"/>
     </row>
     <row r="782">
-      <c r="L782" s="37"/>
       <c r="M782" s="37"/>
+      <c r="N782" s="37"/>
     </row>
     <row r="783">
-      <c r="L783" s="37"/>
       <c r="M783" s="37"/>
+      <c r="N783" s="37"/>
     </row>
     <row r="784">
-      <c r="L784" s="37"/>
       <c r="M784" s="37"/>
+      <c r="N784" s="37"/>
     </row>
     <row r="785">
-      <c r="L785" s="37"/>
       <c r="M785" s="37"/>
+      <c r="N785" s="37"/>
     </row>
     <row r="786">
-      <c r="L786" s="37"/>
       <c r="M786" s="37"/>
+      <c r="N786" s="37"/>
     </row>
     <row r="787">
-      <c r="L787" s="37"/>
       <c r="M787" s="37"/>
+      <c r="N787" s="37"/>
     </row>
     <row r="788">
-      <c r="L788" s="37"/>
       <c r="M788" s="37"/>
+      <c r="N788" s="37"/>
     </row>
     <row r="789">
-      <c r="L789" s="37"/>
       <c r="M789" s="37"/>
+      <c r="N789" s="37"/>
     </row>
     <row r="790">
-      <c r="L790" s="37"/>
       <c r="M790" s="37"/>
+      <c r="N790" s="37"/>
     </row>
     <row r="791">
-      <c r="L791" s="37"/>
       <c r="M791" s="37"/>
+      <c r="N791" s="37"/>
     </row>
     <row r="792">
-      <c r="L792" s="37"/>
       <c r="M792" s="37"/>
+      <c r="N792" s="37"/>
     </row>
     <row r="793">
-      <c r="L793" s="37"/>
       <c r="M793" s="37"/>
+      <c r="N793" s="37"/>
     </row>
     <row r="794">
-      <c r="L794" s="37"/>
       <c r="M794" s="37"/>
+      <c r="N794" s="37"/>
     </row>
     <row r="795">
-      <c r="L795" s="37"/>
       <c r="M795" s="37"/>
+      <c r="N795" s="37"/>
     </row>
     <row r="796">
-      <c r="L796" s="37"/>
       <c r="M796" s="37"/>
+      <c r="N796" s="37"/>
     </row>
     <row r="797">
-      <c r="L797" s="37"/>
       <c r="M797" s="37"/>
+      <c r="N797" s="37"/>
     </row>
     <row r="798">
-      <c r="L798" s="37"/>
       <c r="M798" s="37"/>
+      <c r="N798" s="37"/>
     </row>
     <row r="799">
-      <c r="L799" s="37"/>
       <c r="M799" s="37"/>
+      <c r="N799" s="37"/>
     </row>
     <row r="800">
-      <c r="L800" s="37"/>
       <c r="M800" s="37"/>
+      <c r="N800" s="37"/>
     </row>
     <row r="801">
-      <c r="L801" s="37"/>
       <c r="M801" s="37"/>
+      <c r="N801" s="37"/>
     </row>
     <row r="802">
-      <c r="L802" s="37"/>
       <c r="M802" s="37"/>
+      <c r="N802" s="37"/>
     </row>
     <row r="803">
-      <c r="L803" s="37"/>
       <c r="M803" s="37"/>
+      <c r="N803" s="37"/>
     </row>
     <row r="804">
-      <c r="L804" s="37"/>
       <c r="M804" s="37"/>
+      <c r="N804" s="37"/>
     </row>
     <row r="805">
-      <c r="L805" s="37"/>
       <c r="M805" s="37"/>
+      <c r="N805" s="37"/>
     </row>
     <row r="806">
-      <c r="L806" s="37"/>
       <c r="M806" s="37"/>
+      <c r="N806" s="37"/>
     </row>
     <row r="807">
-      <c r="L807" s="37"/>
       <c r="M807" s="37"/>
+      <c r="N807" s="37"/>
     </row>
     <row r="808">
-      <c r="L808" s="37"/>
       <c r="M808" s="37"/>
+      <c r="N808" s="37"/>
     </row>
     <row r="809">
-      <c r="L809" s="37"/>
       <c r="M809" s="37"/>
+      <c r="N809" s="37"/>
     </row>
     <row r="810">
-      <c r="L810" s="37"/>
       <c r="M810" s="37"/>
+      <c r="N810" s="37"/>
     </row>
     <row r="811">
-      <c r="L811" s="37"/>
       <c r="M811" s="37"/>
+      <c r="N811" s="37"/>
     </row>
     <row r="812">
-      <c r="L812" s="37"/>
       <c r="M812" s="37"/>
+      <c r="N812" s="37"/>
     </row>
     <row r="813">
-      <c r="L813" s="37"/>
       <c r="M813" s="37"/>
+      <c r="N813" s="37"/>
     </row>
     <row r="814">
-      <c r="L814" s="37"/>
       <c r="M814" s="37"/>
+      <c r="N814" s="37"/>
     </row>
     <row r="815">
-      <c r="L815" s="37"/>
       <c r="M815" s="37"/>
+      <c r="N815" s="37"/>
     </row>
     <row r="816">
-      <c r="L816" s="37"/>
       <c r="M816" s="37"/>
+      <c r="N816" s="37"/>
     </row>
     <row r="817">
-      <c r="L817" s="37"/>
       <c r="M817" s="37"/>
+      <c r="N817" s="37"/>
     </row>
     <row r="818">
-      <c r="L818" s="37"/>
       <c r="M818" s="37"/>
+      <c r="N818" s="37"/>
     </row>
     <row r="819">
-      <c r="L819" s="37"/>
       <c r="M819" s="37"/>
+      <c r="N819" s="37"/>
     </row>
     <row r="820">
-      <c r="L820" s="37"/>
       <c r="M820" s="37"/>
+      <c r="N820" s="37"/>
     </row>
     <row r="821">
-      <c r="L821" s="37"/>
       <c r="M821" s="37"/>
+      <c r="N821" s="37"/>
     </row>
     <row r="822">
-      <c r="L822" s="37"/>
       <c r="M822" s="37"/>
+      <c r="N822" s="37"/>
     </row>
     <row r="823">
-      <c r="L823" s="37"/>
       <c r="M823" s="37"/>
+      <c r="N823" s="37"/>
     </row>
     <row r="824">
-      <c r="L824" s="37"/>
       <c r="M824" s="37"/>
+      <c r="N824" s="37"/>
     </row>
     <row r="825">
-      <c r="L825" s="37"/>
       <c r="M825" s="37"/>
+      <c r="N825" s="37"/>
     </row>
     <row r="826">
-      <c r="L826" s="37"/>
       <c r="M826" s="37"/>
+      <c r="N826" s="37"/>
     </row>
     <row r="827">
-      <c r="L827" s="37"/>
       <c r="M827" s="37"/>
+      <c r="N827" s="37"/>
     </row>
     <row r="828">
-      <c r="L828" s="37"/>
       <c r="M828" s="37"/>
+      <c r="N828" s="37"/>
     </row>
     <row r="829">
-      <c r="L829" s="37"/>
       <c r="M829" s="37"/>
+      <c r="N829" s="37"/>
     </row>
     <row r="830">
-      <c r="L830" s="37"/>
       <c r="M830" s="37"/>
+      <c r="N830" s="37"/>
     </row>
     <row r="831">
-      <c r="L831" s="37"/>
       <c r="M831" s="37"/>
+      <c r="N831" s="37"/>
     </row>
     <row r="832">
-      <c r="L832" s="37"/>
       <c r="M832" s="37"/>
+      <c r="N832" s="37"/>
     </row>
     <row r="833">
-      <c r="L833" s="37"/>
       <c r="M833" s="37"/>
+      <c r="N833" s="37"/>
     </row>
     <row r="834">
-      <c r="L834" s="37"/>
       <c r="M834" s="37"/>
+      <c r="N834" s="37"/>
     </row>
     <row r="835">
-      <c r="L835" s="37"/>
       <c r="M835" s="37"/>
+      <c r="N835" s="37"/>
     </row>
     <row r="836">
-      <c r="L836" s="37"/>
       <c r="M836" s="37"/>
+      <c r="N836" s="37"/>
     </row>
     <row r="837">
-      <c r="L837" s="37"/>
       <c r="M837" s="37"/>
+      <c r="N837" s="37"/>
     </row>
     <row r="838">
-      <c r="L838" s="37"/>
       <c r="M838" s="37"/>
+      <c r="N838" s="37"/>
     </row>
     <row r="839">
-      <c r="L839" s="37"/>
       <c r="M839" s="37"/>
+      <c r="N839" s="37"/>
     </row>
     <row r="840">
-      <c r="L840" s="37"/>
       <c r="M840" s="37"/>
+      <c r="N840" s="37"/>
     </row>
     <row r="841">
-      <c r="L841" s="37"/>
       <c r="M841" s="37"/>
+      <c r="N841" s="37"/>
     </row>
     <row r="842">
-      <c r="L842" s="37"/>
       <c r="M842" s="37"/>
+      <c r="N842" s="37"/>
     </row>
     <row r="843">
-      <c r="L843" s="37"/>
       <c r="M843" s="37"/>
+      <c r="N843" s="37"/>
     </row>
     <row r="844">
-      <c r="L844" s="37"/>
       <c r="M844" s="37"/>
+      <c r="N844" s="37"/>
     </row>
     <row r="845">
-      <c r="L845" s="37"/>
       <c r="M845" s="37"/>
+      <c r="N845" s="37"/>
     </row>
     <row r="846">
-      <c r="L846" s="37"/>
       <c r="M846" s="37"/>
+      <c r="N846" s="37"/>
     </row>
     <row r="847">
-      <c r="L847" s="37"/>
       <c r="M847" s="37"/>
+      <c r="N847" s="37"/>
     </row>
     <row r="848">
-      <c r="L848" s="37"/>
       <c r="M848" s="37"/>
+      <c r="N848" s="37"/>
     </row>
     <row r="849">
-      <c r="L849" s="37"/>
       <c r="M849" s="37"/>
+      <c r="N849" s="37"/>
     </row>
     <row r="850">
-      <c r="L850" s="37"/>
       <c r="M850" s="37"/>
+      <c r="N850" s="37"/>
     </row>
     <row r="851">
-      <c r="L851" s="37"/>
       <c r="M851" s="37"/>
+      <c r="N851" s="37"/>
     </row>
     <row r="852">
-      <c r="L852" s="37"/>
       <c r="M852" s="37"/>
+      <c r="N852" s="37"/>
     </row>
     <row r="853">
-      <c r="L853" s="37"/>
       <c r="M853" s="37"/>
+      <c r="N853" s="37"/>
     </row>
     <row r="854">
-      <c r="L854" s="37"/>
       <c r="M854" s="37"/>
+      <c r="N854" s="37"/>
     </row>
     <row r="855">
-      <c r="L855" s="37"/>
       <c r="M855" s="37"/>
+      <c r="N855" s="37"/>
     </row>
     <row r="856">
-      <c r="L856" s="37"/>
       <c r="M856" s="37"/>
+      <c r="N856" s="37"/>
     </row>
     <row r="857">
-      <c r="L857" s="37"/>
       <c r="M857" s="37"/>
+      <c r="N857" s="37"/>
     </row>
     <row r="858">
-      <c r="L858" s="37"/>
       <c r="M858" s="37"/>
+      <c r="N858" s="37"/>
     </row>
     <row r="859">
-      <c r="L859" s="37"/>
       <c r="M859" s="37"/>
+      <c r="N859" s="37"/>
     </row>
     <row r="860">
-      <c r="L860" s="37"/>
       <c r="M860" s="37"/>
+      <c r="N860" s="37"/>
     </row>
     <row r="861">
-      <c r="L861" s="37"/>
       <c r="M861" s="37"/>
+      <c r="N861" s="37"/>
     </row>
     <row r="862">
-      <c r="L862" s="37"/>
       <c r="M862" s="37"/>
+      <c r="N862" s="37"/>
     </row>
     <row r="863">
-      <c r="L863" s="37"/>
       <c r="M863" s="37"/>
+      <c r="N863" s="37"/>
     </row>
     <row r="864">
-      <c r="L864" s="37"/>
       <c r="M864" s="37"/>
+      <c r="N864" s="37"/>
     </row>
     <row r="865">
-      <c r="L865" s="37"/>
       <c r="M865" s="37"/>
+      <c r="N865" s="37"/>
     </row>
     <row r="866">
-      <c r="L866" s="37"/>
       <c r="M866" s="37"/>
+      <c r="N866" s="37"/>
     </row>
     <row r="867">
-      <c r="L867" s="37"/>
       <c r="M867" s="37"/>
+      <c r="N867" s="37"/>
     </row>
     <row r="868">
-      <c r="L868" s="37"/>
       <c r="M868" s="37"/>
+      <c r="N868" s="37"/>
     </row>
     <row r="869">
-      <c r="L869" s="37"/>
       <c r="M869" s="37"/>
+      <c r="N869" s="37"/>
     </row>
     <row r="870">
-      <c r="L870" s="37"/>
       <c r="M870" s="37"/>
+      <c r="N870" s="37"/>
     </row>
     <row r="871">
-      <c r="L871" s="37"/>
       <c r="M871" s="37"/>
+      <c r="N871" s="37"/>
     </row>
     <row r="872">
-      <c r="L872" s="37"/>
       <c r="M872" s="37"/>
+      <c r="N872" s="37"/>
     </row>
     <row r="873">
-      <c r="L873" s="37"/>
       <c r="M873" s="37"/>
+      <c r="N873" s="37"/>
     </row>
     <row r="874">
-      <c r="L874" s="37"/>
       <c r="M874" s="37"/>
+      <c r="N874" s="37"/>
     </row>
     <row r="875">
-      <c r="L875" s="37"/>
       <c r="M875" s="37"/>
+      <c r="N875" s="37"/>
     </row>
     <row r="876">
-      <c r="L876" s="37"/>
       <c r="M876" s="37"/>
+      <c r="N876" s="37"/>
     </row>
     <row r="877">
-      <c r="L877" s="37"/>
       <c r="M877" s="37"/>
+      <c r="N877" s="37"/>
     </row>
     <row r="878">
-      <c r="L878" s="37"/>
       <c r="M878" s="37"/>
+      <c r="N878" s="37"/>
     </row>
     <row r="879">
-      <c r="L879" s="37"/>
       <c r="M879" s="37"/>
+      <c r="N879" s="37"/>
     </row>
     <row r="880">
-      <c r="L880" s="37"/>
       <c r="M880" s="37"/>
+      <c r="N880" s="37"/>
     </row>
     <row r="881">
-      <c r="L881" s="37"/>
       <c r="M881" s="37"/>
+      <c r="N881" s="37"/>
     </row>
     <row r="882">
-      <c r="L882" s="37"/>
       <c r="M882" s="37"/>
+      <c r="N882" s="37"/>
     </row>
     <row r="883">
-      <c r="L883" s="37"/>
       <c r="M883" s="37"/>
+      <c r="N883" s="37"/>
     </row>
     <row r="884">
-      <c r="L884" s="37"/>
       <c r="M884" s="37"/>
+      <c r="N884" s="37"/>
     </row>
     <row r="885">
-      <c r="L885" s="37"/>
       <c r="M885" s="37"/>
+      <c r="N885" s="37"/>
     </row>
     <row r="886">
-      <c r="L886" s="37"/>
       <c r="M886" s="37"/>
+      <c r="N886" s="37"/>
     </row>
     <row r="887">
-      <c r="L887" s="37"/>
       <c r="M887" s="37"/>
+      <c r="N887" s="37"/>
     </row>
     <row r="888">
-      <c r="L888" s="37"/>
       <c r="M888" s="37"/>
+      <c r="N888" s="37"/>
     </row>
     <row r="889">
-      <c r="L889" s="37"/>
       <c r="M889" s="37"/>
+      <c r="N889" s="37"/>
     </row>
     <row r="890">
-      <c r="L890" s="37"/>
       <c r="M890" s="37"/>
+      <c r="N890" s="37"/>
     </row>
     <row r="891">
-      <c r="L891" s="37"/>
       <c r="M891" s="37"/>
+      <c r="N891" s="37"/>
     </row>
     <row r="892">
-      <c r="L892" s="37"/>
       <c r="M892" s="37"/>
+      <c r="N892" s="37"/>
     </row>
     <row r="893">
-      <c r="L893" s="37"/>
       <c r="M893" s="37"/>
+      <c r="N893" s="37"/>
     </row>
     <row r="894">
-      <c r="L894" s="37"/>
       <c r="M894" s="37"/>
+      <c r="N894" s="37"/>
     </row>
     <row r="895">
-      <c r="L895" s="37"/>
       <c r="M895" s="37"/>
+      <c r="N895" s="37"/>
     </row>
     <row r="896">
-      <c r="L896" s="37"/>
       <c r="M896" s="37"/>
+      <c r="N896" s="37"/>
     </row>
     <row r="897">
-      <c r="L897" s="37"/>
       <c r="M897" s="37"/>
+      <c r="N897" s="37"/>
     </row>
     <row r="898">
-      <c r="L898" s="37"/>
       <c r="M898" s="37"/>
+      <c r="N898" s="37"/>
     </row>
     <row r="899">
-      <c r="L899" s="37"/>
       <c r="M899" s="37"/>
+      <c r="N899" s="37"/>
     </row>
     <row r="900">
-      <c r="L900" s="37"/>
       <c r="M900" s="37"/>
+      <c r="N900" s="37"/>
     </row>
     <row r="901">
-      <c r="L901" s="37"/>
       <c r="M901" s="37"/>
+      <c r="N901" s="37"/>
     </row>
     <row r="902">
-      <c r="L902" s="37"/>
       <c r="M902" s="37"/>
+      <c r="N902" s="37"/>
     </row>
     <row r="903">
-      <c r="L903" s="37"/>
       <c r="M903" s="37"/>
+      <c r="N903" s="37"/>
     </row>
     <row r="904">
-      <c r="L904" s="37"/>
       <c r="M904" s="37"/>
+      <c r="N904" s="37"/>
     </row>
     <row r="905">
-      <c r="L905" s="37"/>
       <c r="M905" s="37"/>
+      <c r="N905" s="37"/>
     </row>
     <row r="906">
-      <c r="L906" s="37"/>
       <c r="M906" s="37"/>
+      <c r="N906" s="37"/>
     </row>
     <row r="907">
-      <c r="L907" s="37"/>
       <c r="M907" s="37"/>
+      <c r="N907" s="37"/>
     </row>
     <row r="908">
-      <c r="L908" s="37"/>
       <c r="M908" s="37"/>
+      <c r="N908" s="37"/>
     </row>
     <row r="909">
-      <c r="L909" s="37"/>
       <c r="M909" s="37"/>
+      <c r="N909" s="37"/>
     </row>
     <row r="910">
-      <c r="L910" s="37"/>
       <c r="M910" s="37"/>
+      <c r="N910" s="37"/>
     </row>
     <row r="911">
-      <c r="L911" s="37"/>
       <c r="M911" s="37"/>
+      <c r="N911" s="37"/>
     </row>
     <row r="912">
-      <c r="L912" s="37"/>
       <c r="M912" s="37"/>
+      <c r="N912" s="37"/>
     </row>
     <row r="913">
-      <c r="L913" s="37"/>
       <c r="M913" s="37"/>
+      <c r="N913" s="37"/>
     </row>
     <row r="914">
-      <c r="L914" s="37"/>
       <c r="M914" s="37"/>
+      <c r="N914" s="37"/>
     </row>
     <row r="915">
-      <c r="L915" s="37"/>
       <c r="M915" s="37"/>
+      <c r="N915" s="37"/>
     </row>
     <row r="916">
-      <c r="L916" s="37"/>
       <c r="M916" s="37"/>
+      <c r="N916" s="37"/>
     </row>
     <row r="917">
-      <c r="L917" s="37"/>
       <c r="M917" s="37"/>
+      <c r="N917" s="37"/>
     </row>
     <row r="918">
-      <c r="L918" s="37"/>
       <c r="M918" s="37"/>
+      <c r="N918" s="37"/>
     </row>
     <row r="919">
-      <c r="L919" s="37"/>
       <c r="M919" s="37"/>
+      <c r="N919" s="37"/>
     </row>
     <row r="920">
-      <c r="L920" s="37"/>
       <c r="M920" s="37"/>
+      <c r="N920" s="37"/>
     </row>
     <row r="921">
-      <c r="L921" s="37"/>
       <c r="M921" s="37"/>
+      <c r="N921" s="37"/>
     </row>
     <row r="922">
-      <c r="L922" s="37"/>
       <c r="M922" s="37"/>
+      <c r="N922" s="37"/>
     </row>
     <row r="923">
-      <c r="L923" s="37"/>
       <c r="M923" s="37"/>
+      <c r="N923" s="37"/>
     </row>
     <row r="924">
-      <c r="L924" s="37"/>
       <c r="M924" s="37"/>
+      <c r="N924" s="37"/>
     </row>
     <row r="925">
-      <c r="L925" s="37"/>
       <c r="M925" s="37"/>
+      <c r="N925" s="37"/>
     </row>
     <row r="926">
-      <c r="L926" s="37"/>
       <c r="M926" s="37"/>
+      <c r="N926" s="37"/>
     </row>
     <row r="927">
-      <c r="L927" s="37"/>
       <c r="M927" s="37"/>
+      <c r="N927" s="37"/>
     </row>
     <row r="928">
-      <c r="L928" s="37"/>
       <c r="M928" s="37"/>
+      <c r="N928" s="37"/>
     </row>
     <row r="929">
-      <c r="L929" s="37"/>
       <c r="M929" s="37"/>
+      <c r="N929" s="37"/>
     </row>
     <row r="930">
-      <c r="L930" s="37"/>
       <c r="M930" s="37"/>
+      <c r="N930" s="37"/>
     </row>
     <row r="931">
-      <c r="L931" s="37"/>
       <c r="M931" s="37"/>
+      <c r="N931" s="37"/>
     </row>
     <row r="932">
-      <c r="L932" s="37"/>
       <c r="M932" s="37"/>
+      <c r="N932" s="37"/>
     </row>
     <row r="933">
-      <c r="L933" s="37"/>
       <c r="M933" s="37"/>
+      <c r="N933" s="37"/>
     </row>
     <row r="934">
-      <c r="L934" s="37"/>
       <c r="M934" s="37"/>
+      <c r="N934" s="37"/>
     </row>
     <row r="935">
-      <c r="L935" s="37"/>
       <c r="M935" s="37"/>
+      <c r="N935" s="37"/>
     </row>
     <row r="936">
-      <c r="L936" s="37"/>
       <c r="M936" s="37"/>
+      <c r="N936" s="37"/>
     </row>
     <row r="937">
-      <c r="L937" s="37"/>
       <c r="M937" s="37"/>
+      <c r="N937" s="37"/>
     </row>
     <row r="938">
-      <c r="L938" s="37"/>
       <c r="M938" s="37"/>
+      <c r="N938" s="37"/>
     </row>
     <row r="939">
-      <c r="L939" s="37"/>
       <c r="M939" s="37"/>
+      <c r="N939" s="37"/>
     </row>
     <row r="940">
-      <c r="L940" s="37"/>
       <c r="M940" s="37"/>
+      <c r="N940" s="37"/>
     </row>
     <row r="941">
-      <c r="L941" s="37"/>
       <c r="M941" s="37"/>
+      <c r="N941" s="37"/>
     </row>
     <row r="942">
-      <c r="L942" s="37"/>
       <c r="M942" s="37"/>
+      <c r="N942" s="37"/>
     </row>
     <row r="943">
-      <c r="L943" s="37"/>
       <c r="M943" s="37"/>
+      <c r="N943" s="37"/>
     </row>
     <row r="944">
-      <c r="L944" s="37"/>
       <c r="M944" s="37"/>
+      <c r="N944" s="37"/>
     </row>
     <row r="945">
-      <c r="L945" s="37"/>
       <c r="M945" s="37"/>
+      <c r="N945" s="37"/>
     </row>
     <row r="946">
-      <c r="L946" s="37"/>
       <c r="M946" s="37"/>
+      <c r="N946" s="37"/>
     </row>
     <row r="947">
-      <c r="L947" s="37"/>
       <c r="M947" s="37"/>
+      <c r="N947" s="37"/>
     </row>
     <row r="948">
-      <c r="L948" s="37"/>
       <c r="M948" s="37"/>
+      <c r="N948" s="37"/>
     </row>
     <row r="949">
-      <c r="L949" s="37"/>
       <c r="M949" s="37"/>
+      <c r="N949" s="37"/>
     </row>
     <row r="950">
-      <c r="L950" s="37"/>
       <c r="M950" s="37"/>
+      <c r="N950" s="37"/>
     </row>
     <row r="951">
-      <c r="L951" s="37"/>
       <c r="M951" s="37"/>
+      <c r="N951" s="37"/>
     </row>
     <row r="952">
-      <c r="L952" s="37"/>
       <c r="M952" s="37"/>
+      <c r="N952" s="37"/>
     </row>
     <row r="953">
-      <c r="L953" s="37"/>
       <c r="M953" s="37"/>
+      <c r="N953" s="37"/>
     </row>
     <row r="954">
-      <c r="L954" s="37"/>
       <c r="M954" s="37"/>
+      <c r="N954" s="37"/>
     </row>
     <row r="955">
-      <c r="L955" s="37"/>
       <c r="M955" s="37"/>
+      <c r="N955" s="37"/>
     </row>
     <row r="956">
-      <c r="L956" s="37"/>
       <c r="M956" s="37"/>
+      <c r="N956" s="37"/>
     </row>
     <row r="957">
-      <c r="L957" s="37"/>
       <c r="M957" s="37"/>
+      <c r="N957" s="37"/>
     </row>
     <row r="958">
-      <c r="L958" s="37"/>
       <c r="M958" s="37"/>
+      <c r="N958" s="37"/>
     </row>
     <row r="959">
-      <c r="L959" s="37"/>
       <c r="M959" s="37"/>
+      <c r="N959" s="37"/>
     </row>
     <row r="960">
-      <c r="L960" s="37"/>
       <c r="M960" s="37"/>
+      <c r="N960" s="37"/>
     </row>
     <row r="961">
-      <c r="L961" s="37"/>
       <c r="M961" s="37"/>
+      <c r="N961" s="37"/>
     </row>
     <row r="962">
-      <c r="L962" s="37"/>
       <c r="M962" s="37"/>
+      <c r="N962" s="37"/>
     </row>
     <row r="963">
-      <c r="L963" s="37"/>
       <c r="M963" s="37"/>
+      <c r="N963" s="37"/>
     </row>
     <row r="964">
-      <c r="L964" s="37"/>
       <c r="M964" s="37"/>
+      <c r="N964" s="37"/>
     </row>
     <row r="965">
-      <c r="L965" s="37"/>
       <c r="M965" s="37"/>
+      <c r="N965" s="37"/>
     </row>
     <row r="966">
-      <c r="L966" s="37"/>
       <c r="M966" s="37"/>
+      <c r="N966" s="37"/>
     </row>
     <row r="967">
-      <c r="L967" s="37"/>
       <c r="M967" s="37"/>
+      <c r="N967" s="37"/>
     </row>
     <row r="968">
-      <c r="L968" s="37"/>
       <c r="M968" s="37"/>
+      <c r="N968" s="37"/>
     </row>
     <row r="969">
-      <c r="L969" s="37"/>
       <c r="M969" s="37"/>
+      <c r="N969" s="37"/>
     </row>
     <row r="970">
-      <c r="L970" s="37"/>
       <c r="M970" s="37"/>
+      <c r="N970" s="37"/>
     </row>
     <row r="971">
-      <c r="L971" s="37"/>
       <c r="M971" s="37"/>
+      <c r="N971" s="37"/>
     </row>
     <row r="972">
-      <c r="L972" s="37"/>
       <c r="M972" s="37"/>
+      <c r="N972" s="37"/>
     </row>
     <row r="973">
-      <c r="L973" s="37"/>
       <c r="M973" s="37"/>
+      <c r="N973" s="37"/>
     </row>
     <row r="974">
-      <c r="L974" s="37"/>
       <c r="M974" s="37"/>
+      <c r="N974" s="37"/>
     </row>
     <row r="975">
-      <c r="L975" s="37"/>
       <c r="M975" s="37"/>
+      <c r="N975" s="37"/>
     </row>
     <row r="976">
-      <c r="L976" s="37"/>
       <c r="M976" s="37"/>
+      <c r="N976" s="37"/>
     </row>
     <row r="977">
-      <c r="L977" s="37"/>
       <c r="M977" s="37"/>
+      <c r="N977" s="37"/>
     </row>
     <row r="978">
-      <c r="L978" s="37"/>
       <c r="M978" s="37"/>
+      <c r="N978" s="37"/>
     </row>
     <row r="979">
-      <c r="L979" s="37"/>
       <c r="M979" s="37"/>
+      <c r="N979" s="37"/>
     </row>
     <row r="980">
-      <c r="L980" s="37"/>
       <c r="M980" s="37"/>
+      <c r="N980" s="37"/>
     </row>
     <row r="981">
-      <c r="L981" s="37"/>
       <c r="M981" s="37"/>
+      <c r="N981" s="37"/>
     </row>
     <row r="982">
-      <c r="L982" s="37"/>
       <c r="M982" s="37"/>
+      <c r="N982" s="37"/>
     </row>
     <row r="983">
-      <c r="L983" s="37"/>
       <c r="M983" s="37"/>
+      <c r="N983" s="37"/>
     </row>
     <row r="984">
-      <c r="L984" s="37"/>
       <c r="M984" s="37"/>
+      <c r="N984" s="37"/>
     </row>
     <row r="985">
-      <c r="L985" s="37"/>
       <c r="M985" s="37"/>
+      <c r="N985" s="37"/>
     </row>
     <row r="986">
-      <c r="L986" s="37"/>
       <c r="M986" s="37"/>
+      <c r="N986" s="37"/>
     </row>
     <row r="987">
-      <c r="L987" s="37"/>
       <c r="M987" s="37"/>
+      <c r="N987" s="37"/>
     </row>
     <row r="988">
-      <c r="L988" s="37"/>
       <c r="M988" s="37"/>
+      <c r="N988" s="37"/>
     </row>
     <row r="989">
-      <c r="L989" s="37"/>
       <c r="M989" s="37"/>
+      <c r="N989" s="37"/>
     </row>
     <row r="990">
-      <c r="L990" s="37"/>
       <c r="M990" s="37"/>
+      <c r="N990" s="37"/>
     </row>
     <row r="991">
-      <c r="L991" s="37"/>
       <c r="M991" s="37"/>
+      <c r="N991" s="37"/>
     </row>
     <row r="992">
-      <c r="L992" s="37"/>
       <c r="M992" s="37"/>
+      <c r="N992" s="37"/>
     </row>
     <row r="993">
-      <c r="L993" s="37"/>
       <c r="M993" s="37"/>
+      <c r="N993" s="37"/>
     </row>
     <row r="994">
-      <c r="L994" s="37"/>
       <c r="M994" s="37"/>
+      <c r="N994" s="37"/>
     </row>
     <row r="995">
-      <c r="L995" s="37"/>
       <c r="M995" s="37"/>
+      <c r="N995" s="37"/>
     </row>
     <row r="996">
-      <c r="L996" s="37"/>
       <c r="M996" s="37"/>
+      <c r="N996" s="37"/>
     </row>
     <row r="997">
-      <c r="L997" s="37"/>
       <c r="M997" s="37"/>
+      <c r="N997" s="37"/>
     </row>
     <row r="998">
-      <c r="L998" s="37"/>
       <c r="M998" s="37"/>
+      <c r="N998" s="37"/>
     </row>
     <row r="999">
-      <c r="L999" s="37"/>
       <c r="M999" s="37"/>
+      <c r="N999" s="37"/>
     </row>
     <row r="1000">
-      <c r="L1000" s="37"/>
       <c r="M1000" s="37"/>
+      <c r="N1000" s="37"/>
     </row>
     <row r="1001">
-      <c r="L1001" s="37"/>
       <c r="M1001" s="37"/>
+      <c r="N1001" s="37"/>
     </row>
     <row r="1002">
-      <c r="L1002" s="37"/>
       <c r="M1002" s="37"/>
+      <c r="N1002" s="37"/>
     </row>
     <row r="1003">
-      <c r="L1003" s="37"/>
       <c r="M1003" s="37"/>
+      <c r="N1003" s="37"/>
     </row>
     <row r="1004">
-      <c r="L1004" s="37"/>
       <c r="M1004" s="37"/>
+      <c r="N1004" s="37"/>
     </row>
     <row r="1005">
-      <c r="L1005" s="37"/>
       <c r="M1005" s="37"/>
+      <c r="N1005" s="37"/>
     </row>
     <row r="1006">
-      <c r="L1006" s="37"/>
       <c r="M1006" s="37"/>
+      <c r="N1006" s="37"/>
     </row>
     <row r="1007">
-      <c r="L1007" s="37"/>
       <c r="M1007" s="37"/>
+      <c r="N1007" s="37"/>
     </row>
     <row r="1008">
-      <c r="L1008" s="37"/>
       <c r="M1008" s="37"/>
+      <c r="N1008" s="37"/>
     </row>
     <row r="1009">
-      <c r="L1009" s="37"/>
       <c r="M1009" s="37"/>
+      <c r="N1009" s="37"/>
     </row>
     <row r="1010">
-      <c r="L1010" s="37"/>
       <c r="M1010" s="37"/>
+      <c r="N1010" s="37"/>
     </row>
     <row r="1011">
-      <c r="L1011" s="37"/>
       <c r="M1011" s="37"/>
+      <c r="N1011" s="37"/>
     </row>
     <row r="1012">
-      <c r="L1012" s="37"/>
       <c r="M1012" s="37"/>
+      <c r="N1012" s="37"/>
     </row>
     <row r="1013">
-      <c r="L1013" s="37"/>
       <c r="M1013" s="37"/>
+      <c r="N1013" s="37"/>
     </row>
     <row r="1014">
-      <c r="L1014" s="37"/>
       <c r="M1014" s="37"/>
+      <c r="N1014" s="37"/>
     </row>
     <row r="1015">
-      <c r="L1015" s="37"/>
       <c r="M1015" s="37"/>
+      <c r="N1015" s="37"/>
     </row>
     <row r="1016">
-      <c r="L1016" s="37"/>
       <c r="M1016" s="37"/>
+      <c r="N1016" s="37"/>
     </row>
     <row r="1017">
-      <c r="L1017" s="37"/>
       <c r="M1017" s="37"/>
+      <c r="N1017" s="37"/>
     </row>
     <row r="1018">
-      <c r="L1018" s="37"/>
       <c r="M1018" s="37"/>
+      <c r="N1018" s="37"/>
     </row>
     <row r="1019">
-      <c r="L1019" s="37"/>
       <c r="M1019" s="37"/>
+      <c r="N1019" s="37"/>
     </row>
     <row r="1020">
-      <c r="L1020" s="37"/>
       <c r="M1020" s="37"/>
+      <c r="N1020" s="37"/>
     </row>
     <row r="1021">
-      <c r="L1021" s="37"/>
       <c r="M1021" s="37"/>
+      <c r="N1021" s="37"/>
     </row>
     <row r="1022">
-      <c r="L1022" s="37"/>
       <c r="M1022" s="37"/>
+      <c r="N1022" s="37"/>
     </row>
     <row r="1023">
-      <c r="L1023" s="37"/>
       <c r="M1023" s="37"/>
+      <c r="N1023" s="37"/>
     </row>
     <row r="1024">
-      <c r="L1024" s="37"/>
       <c r="M1024" s="37"/>
+      <c r="N1024" s="37"/>
     </row>
     <row r="1025">
-      <c r="L1025" s="37"/>
       <c r="M1025" s="37"/>
+      <c r="N1025" s="37"/>
     </row>
     <row r="1026">
-      <c r="L1026" s="37"/>
       <c r="M1026" s="37"/>
+      <c r="N1026" s="37"/>
     </row>
     <row r="1027">
-      <c r="L1027" s="37"/>
       <c r="M1027" s="37"/>
+      <c r="N1027" s="37"/>
     </row>
     <row r="1028">
-      <c r="L1028" s="37"/>
       <c r="M1028" s="37"/>
+      <c r="N1028" s="37"/>
     </row>
     <row r="1029">
-      <c r="L1029" s="37"/>
       <c r="M1029" s="37"/>
+      <c r="N1029" s="37"/>
     </row>
     <row r="1030">
-      <c r="L1030" s="37"/>
       <c r="M1030" s="37"/>
+      <c r="N1030" s="37"/>
     </row>
     <row r="1031">
-      <c r="L1031" s="37"/>
       <c r="M1031" s="37"/>
+      <c r="N1031" s="37"/>
     </row>
     <row r="1032">
-      <c r="L1032" s="37"/>
       <c r="M1032" s="37"/>
+      <c r="N1032" s="37"/>
     </row>
     <row r="1033">
-      <c r="L1033" s="37"/>
       <c r="M1033" s="37"/>
+      <c r="N1033" s="37"/>
     </row>
     <row r="1034">
-      <c r="L1034" s="37"/>
       <c r="M1034" s="37"/>
+      <c r="N1034" s="37"/>
     </row>
     <row r="1035">
-      <c r="L1035" s="37"/>
       <c r="M1035" s="37"/>
+      <c r="N1035" s="37"/>
     </row>
     <row r="1036">
-      <c r="L1036" s="37"/>
       <c r="M1036" s="37"/>
+      <c r="N1036" s="37"/>
     </row>
     <row r="1037">
-      <c r="L1037" s="37"/>
       <c r="M1037" s="37"/>
+      <c r="N1037" s="37"/>
     </row>
     <row r="1038">
-      <c r="L1038" s="37"/>
       <c r="M1038" s="37"/>
+      <c r="N1038" s="37"/>
     </row>
     <row r="1039">
-      <c r="L1039" s="37"/>
       <c r="M1039" s="37"/>
+      <c r="N1039" s="37"/>
     </row>
     <row r="1040">
-      <c r="L1040" s="37"/>
       <c r="M1040" s="37"/>
+      <c r="N1040" s="37"/>
     </row>
     <row r="1041">
-      <c r="L1041" s="37"/>
       <c r="M1041" s="37"/>
+      <c r="N1041" s="37"/>
     </row>
     <row r="1042">
-      <c r="L1042" s="37"/>
       <c r="M1042" s="37"/>
+      <c r="N1042" s="37"/>
     </row>
     <row r="1043">
-      <c r="L1043" s="37"/>
       <c r="M1043" s="37"/>
+      <c r="N1043" s="37"/>
     </row>
     <row r="1044">
-      <c r="L1044" s="37"/>
       <c r="M1044" s="37"/>
+      <c r="N1044" s="37"/>
     </row>
     <row r="1045">
-      <c r="L1045" s="37"/>
       <c r="M1045" s="37"/>
+      <c r="N1045" s="37"/>
     </row>
     <row r="1046">
-      <c r="L1046" s="37"/>
       <c r="M1046" s="37"/>
+      <c r="N1046" s="37"/>
     </row>
     <row r="1047">
-      <c r="L1047" s="37"/>
       <c r="M1047" s="37"/>
+      <c r="N1047" s="37"/>
     </row>
     <row r="1048">
-      <c r="L1048" s="37"/>
       <c r="M1048" s="37"/>
+      <c r="N1048" s="37"/>
     </row>
     <row r="1049">
-      <c r="L1049" s="37"/>
       <c r="M1049" s="37"/>
+      <c r="N1049" s="37"/>
     </row>
     <row r="1050">
-      <c r="L1050" s="37"/>
       <c r="M1050" s="37"/>
+      <c r="N1050" s="37"/>
     </row>
     <row r="1051">
-      <c r="L1051" s="37"/>
       <c r="M1051" s="37"/>
+      <c r="N1051" s="37"/>
     </row>
     <row r="1052">
-      <c r="L1052" s="37"/>
       <c r="M1052" s="37"/>
+      <c r="N1052" s="37"/>
     </row>
     <row r="1053">
-      <c r="L1053" s="37"/>
       <c r="M1053" s="37"/>
+      <c r="N1053" s="37"/>
     </row>
     <row r="1054">
-      <c r="L1054" s="37"/>
       <c r="M1054" s="37"/>
+      <c r="N1054" s="37"/>
     </row>
     <row r="1055">
-      <c r="L1055" s="37"/>
       <c r="M1055" s="37"/>
+      <c r="N1055" s="37"/>
     </row>
     <row r="1056">
-      <c r="L1056" s="37"/>
       <c r="M1056" s="37"/>
+      <c r="N1056" s="37"/>
     </row>
     <row r="1057">
-      <c r="L1057" s="37"/>
       <c r="M1057" s="37"/>
+      <c r="N1057" s="37"/>
     </row>
     <row r="1058">
-      <c r="L1058" s="37"/>
       <c r="M1058" s="37"/>
+      <c r="N1058" s="37"/>
     </row>
     <row r="1059">
-      <c r="L1059" s="37"/>
       <c r="M1059" s="37"/>
+      <c r="N1059" s="37"/>
     </row>
     <row r="1060">
-      <c r="L1060" s="37"/>
       <c r="M1060" s="37"/>
+      <c r="N1060" s="37"/>
     </row>
     <row r="1061">
-      <c r="L1061" s="37"/>
       <c r="M1061" s="37"/>
+      <c r="N1061" s="37"/>
     </row>
     <row r="1062">
-      <c r="L1062" s="37"/>
       <c r="M1062" s="37"/>
+      <c r="N1062" s="37"/>
     </row>
     <row r="1063">
-      <c r="L1063" s="37"/>
       <c r="M1063" s="37"/>
+      <c r="N1063" s="37"/>
     </row>
     <row r="1064">
-      <c r="L1064" s="37"/>
       <c r="M1064" s="37"/>
+      <c r="N1064" s="37"/>
     </row>
     <row r="1065">
-      <c r="L1065" s="37"/>
       <c r="M1065" s="37"/>
+      <c r="N1065" s="37"/>
     </row>
     <row r="1066">
-      <c r="L1066" s="37"/>
       <c r="M1066" s="37"/>
+      <c r="N1066" s="37"/>
     </row>
     <row r="1067">
-      <c r="L1067" s="37"/>
       <c r="M1067" s="37"/>
+      <c r="N1067" s="37"/>
     </row>
     <row r="1068">
-      <c r="L1068" s="37"/>
       <c r="M1068" s="37"/>
+      <c r="N1068" s="37"/>
     </row>
     <row r="1069">
-      <c r="L1069" s="37"/>
       <c r="M1069" s="37"/>
+      <c r="N1069" s="37"/>
     </row>
     <row r="1070">
-      <c r="L1070" s="37"/>
       <c r="M1070" s="37"/>
+      <c r="N1070" s="37"/>
     </row>
     <row r="1071">
-      <c r="L1071" s="37"/>
       <c r="M1071" s="37"/>
+      <c r="N1071" s="37"/>
     </row>
     <row r="1072">
-      <c r="L1072" s="37"/>
       <c r="M1072" s="37"/>
+      <c r="N1072" s="37"/>
     </row>
     <row r="1073">
-      <c r="L1073" s="37"/>
       <c r="M1073" s="37"/>
+      <c r="N1073" s="37"/>
     </row>
     <row r="1074">
-      <c r="L1074" s="37"/>
       <c r="M1074" s="37"/>
+      <c r="N1074" s="37"/>
     </row>
     <row r="1075">
-      <c r="L1075" s="37"/>
       <c r="M1075" s="37"/>
+      <c r="N1075" s="37"/>
     </row>
     <row r="1076">
-      <c r="L1076" s="37"/>
       <c r="M1076" s="37"/>
+      <c r="N1076" s="37"/>
     </row>
     <row r="1077">
-      <c r="L1077" s="37"/>
       <c r="M1077" s="37"/>
+      <c r="N1077" s="37"/>
     </row>
     <row r="1078">
-      <c r="L1078" s="37"/>
       <c r="M1078" s="37"/>
+      <c r="N1078" s="37"/>
     </row>
     <row r="1079">
-      <c r="L1079" s="37"/>
       <c r="M1079" s="37"/>
+      <c r="N1079" s="37"/>
     </row>
     <row r="1080">
-      <c r="L1080" s="37"/>
       <c r="M1080" s="37"/>
+      <c r="N1080" s="37"/>
     </row>
     <row r="1081">
-      <c r="L1081" s="37"/>
       <c r="M1081" s="37"/>
+      <c r="N1081" s="37"/>
     </row>
     <row r="1082">
-      <c r="L1082" s="37"/>
       <c r="M1082" s="37"/>
+      <c r="N1082" s="37"/>
     </row>
     <row r="1083">
-      <c r="L1083" s="37"/>
       <c r="M1083" s="37"/>
+      <c r="N1083" s="37"/>
     </row>
     <row r="1084">
-      <c r="L1084" s="37"/>
       <c r="M1084" s="37"/>
+      <c r="N1084" s="37"/>
     </row>
     <row r="1085">
-      <c r="L1085" s="37"/>
       <c r="M1085" s="37"/>
+      <c r="N1085" s="37"/>
     </row>
     <row r="1086">
-      <c r="L1086" s="37"/>
       <c r="M1086" s="37"/>
+      <c r="N1086" s="37"/>
     </row>
     <row r="1087">
-      <c r="L1087" s="37"/>
       <c r="M1087" s="37"/>
+      <c r="N1087" s="37"/>
     </row>
     <row r="1088">
-      <c r="L1088" s="37"/>
       <c r="M1088" s="37"/>
+      <c r="N1088" s="37"/>
     </row>
     <row r="1089">
-      <c r="L1089" s="37"/>
       <c r="M1089" s="37"/>
+      <c r="N1089" s="37"/>
     </row>
     <row r="1090">
-      <c r="L1090" s="37"/>
       <c r="M1090" s="37"/>
+      <c r="N1090" s="37"/>
     </row>
     <row r="1091">
-      <c r="L1091" s="37"/>
       <c r="M1091" s="37"/>
+      <c r="N1091" s="37"/>
     </row>
     <row r="1092">
-      <c r="L1092" s="37"/>
       <c r="M1092" s="37"/>
+      <c r="N1092" s="37"/>
     </row>
     <row r="1093">
-      <c r="L1093" s="37"/>
       <c r="M1093" s="37"/>
+      <c r="N1093" s="37"/>
     </row>
     <row r="1094">
-      <c r="L1094" s="37"/>
       <c r="M1094" s="37"/>
+      <c r="N1094" s="37"/>
     </row>
     <row r="1095">
-      <c r="L1095" s="37"/>
       <c r="M1095" s="37"/>
+      <c r="N1095" s="37"/>
     </row>
     <row r="1096">
-      <c r="L1096" s="37"/>
       <c r="M1096" s="37"/>
+      <c r="N1096" s="37"/>
     </row>
     <row r="1097">
-      <c r="L1097" s="37"/>
       <c r="M1097" s="37"/>
+      <c r="N1097" s="37"/>
     </row>
     <row r="1098">
-      <c r="L1098" s="37"/>
       <c r="M1098" s="37"/>
+      <c r="N1098" s="37"/>
     </row>
     <row r="1099">
-      <c r="L1099" s="37"/>
       <c r="M1099" s="37"/>
+      <c r="N1099" s="37"/>
     </row>
     <row r="1100">
-      <c r="L1100" s="37"/>
       <c r="M1100" s="37"/>
+      <c r="N1100" s="37"/>
     </row>
     <row r="1101">
-      <c r="L1101" s="37"/>
       <c r="M1101" s="37"/>
+      <c r="N1101" s="37"/>
     </row>
     <row r="1102">
-      <c r="L1102" s="37"/>
       <c r="M1102" s="37"/>
+      <c r="N1102" s="37"/>
     </row>
     <row r="1103">
-      <c r="L1103" s="37"/>
       <c r="M1103" s="37"/>
+      <c r="N1103" s="37"/>
     </row>
     <row r="1104">
-      <c r="L1104" s="37"/>
       <c r="M1104" s="37"/>
+      <c r="N1104" s="37"/>
     </row>
     <row r="1105">
-      <c r="L1105" s="37"/>
       <c r="M1105" s="37"/>
+      <c r="N1105" s="37"/>
     </row>
     <row r="1106">
-      <c r="L1106" s="37"/>
       <c r="M1106" s="37"/>
+      <c r="N1106" s="37"/>
     </row>
     <row r="1107">
-      <c r="L1107" s="37"/>
       <c r="M1107" s="37"/>
+      <c r="N1107" s="37"/>
     </row>
     <row r="1108">
-      <c r="L1108" s="37"/>
       <c r="M1108" s="37"/>
+      <c r="N1108" s="37"/>
     </row>
     <row r="1109">
-      <c r="L1109" s="37"/>
       <c r="M1109" s="37"/>
+      <c r="N1109" s="37"/>
     </row>
     <row r="1110">
-      <c r="L1110" s="37"/>
       <c r="M1110" s="37"/>
+      <c r="N1110" s="37"/>
     </row>
     <row r="1111">
-      <c r="L1111" s="37"/>
       <c r="M1111" s="37"/>
+      <c r="N1111" s="37"/>
     </row>
     <row r="1112">
-      <c r="L1112" s="37"/>
       <c r="M1112" s="37"/>
+      <c r="N1112" s="37"/>
     </row>
     <row r="1113">
-      <c r="L1113" s="37"/>
       <c r="M1113" s="37"/>
+      <c r="N1113" s="37"/>
     </row>
     <row r="1114">
-      <c r="L1114" s="37"/>
       <c r="M1114" s="37"/>
+      <c r="N1114" s="37"/>
     </row>
     <row r="1115">
-      <c r="L1115" s="37"/>
       <c r="M1115" s="37"/>
+      <c r="N1115" s="37"/>
     </row>
     <row r="1116">
-      <c r="L1116" s="37"/>
       <c r="M1116" s="37"/>
+      <c r="N1116" s="37"/>
     </row>
     <row r="1117">
-      <c r="L1117" s="37"/>
       <c r="M1117" s="37"/>
+      <c r="N1117" s="37"/>
     </row>
     <row r="1118">
-      <c r="L1118" s="37"/>
       <c r="M1118" s="37"/>
+      <c r="N1118" s="37"/>
     </row>
     <row r="1119">
-      <c r="L1119" s="37"/>
       <c r="M1119" s="37"/>
+      <c r="N1119" s="37"/>
     </row>
     <row r="1120">
-      <c r="L1120" s="37"/>
       <c r="M1120" s="37"/>
+      <c r="N1120" s="37"/>
     </row>
     <row r="1121">
-      <c r="L1121" s="37"/>
       <c r="M1121" s="37"/>
+      <c r="N1121" s="37"/>
     </row>
     <row r="1122">
-      <c r="L1122" s="37"/>
       <c r="M1122" s="37"/>
+      <c r="N1122" s="37"/>
     </row>
     <row r="1123">
-      <c r="L1123" s="37"/>
       <c r="M1123" s="37"/>
+      <c r="N1123" s="37"/>
     </row>
     <row r="1124">
-      <c r="L1124" s="37"/>
       <c r="M1124" s="37"/>
+      <c r="N1124" s="37"/>
     </row>
     <row r="1125">
-      <c r="L1125" s="37"/>
       <c r="M1125" s="37"/>
+      <c r="N1125" s="37"/>
     </row>
     <row r="1126">
-      <c r="L1126" s="37"/>
       <c r="M1126" s="37"/>
+      <c r="N1126" s="37"/>
     </row>
     <row r="1127">
-      <c r="L1127" s="37"/>
       <c r="M1127" s="37"/>
+      <c r="N1127" s="37"/>
     </row>
     <row r="1128">
-      <c r="L1128" s="37"/>
       <c r="M1128" s="37"/>
+      <c r="N1128" s="37"/>
     </row>
     <row r="1129">
-      <c r="L1129" s="37"/>
       <c r="M1129" s="37"/>
+      <c r="N1129" s="37"/>
     </row>
     <row r="1130">
-      <c r="L1130" s="37"/>
       <c r="M1130" s="37"/>
+      <c r="N1130" s="37"/>
     </row>
     <row r="1131">
-      <c r="L1131" s="37"/>
       <c r="M1131" s="37"/>
+      <c r="N1131" s="37"/>
     </row>
     <row r="1132">
-      <c r="L1132" s="37"/>
       <c r="M1132" s="37"/>
+      <c r="N1132" s="37"/>
     </row>
     <row r="1133">
-      <c r="L1133" s="37"/>
       <c r="M1133" s="37"/>
+      <c r="N1133" s="37"/>
     </row>
     <row r="1134">
-      <c r="L1134" s="37"/>
       <c r="M1134" s="37"/>
+      <c r="N1134" s="37"/>
     </row>
     <row r="1135">
-      <c r="L1135" s="37"/>
       <c r="M1135" s="37"/>
+      <c r="N1135" s="37"/>
     </row>
     <row r="1136">
-      <c r="L1136" s="37"/>
       <c r="M1136" s="37"/>
+      <c r="N1136" s="37"/>
     </row>
     <row r="1137">
-      <c r="L1137" s="37"/>
       <c r="M1137" s="37"/>
+      <c r="N1137" s="37"/>
     </row>
     <row r="1138">
-      <c r="L1138" s="37"/>
       <c r="M1138" s="37"/>
+      <c r="N1138" s="37"/>
     </row>
     <row r="1139">
-      <c r="L1139" s="37"/>
       <c r="M1139" s="37"/>
+      <c r="N1139" s="37"/>
     </row>
     <row r="1140">
-      <c r="L1140" s="37"/>
       <c r="M1140" s="37"/>
+      <c r="N1140" s="37"/>
     </row>
     <row r="1141">
-      <c r="L1141" s="37"/>
       <c r="M1141" s="37"/>
+      <c r="N1141" s="37"/>
     </row>
     <row r="1142">
-      <c r="L1142" s="37"/>
       <c r="M1142" s="37"/>
+      <c r="N1142" s="37"/>
     </row>
     <row r="1143">
-      <c r="L1143" s="37"/>
       <c r="M1143" s="37"/>
+      <c r="N1143" s="37"/>
     </row>
     <row r="1144">
-      <c r="L1144" s="37"/>
       <c r="M1144" s="37"/>
+      <c r="N1144" s="37"/>
     </row>
     <row r="1145">
-      <c r="L1145" s="37"/>
       <c r="M1145" s="37"/>
+      <c r="N1145" s="37"/>
     </row>
     <row r="1146">
-      <c r="L1146" s="37"/>
       <c r="M1146" s="37"/>
+      <c r="N1146" s="37"/>
     </row>
     <row r="1147">
-      <c r="L1147" s="37"/>
       <c r="M1147" s="37"/>
+      <c r="N1147" s="37"/>
     </row>
     <row r="1148">
-      <c r="L1148" s="37"/>
       <c r="M1148" s="37"/>
+      <c r="N1148" s="37"/>
     </row>
     <row r="1149">
-      <c r="L1149" s="37"/>
       <c r="M1149" s="37"/>
+      <c r="N1149" s="37"/>
     </row>
     <row r="1150">
-      <c r="L1150" s="37"/>
       <c r="M1150" s="37"/>
+      <c r="N1150" s="37"/>
     </row>
     <row r="1151">
-      <c r="L1151" s="37"/>
       <c r="M1151" s="37"/>
+      <c r="N1151" s="37"/>
     </row>
     <row r="1152">
-      <c r="L1152" s="37"/>
       <c r="M1152" s="37"/>
+      <c r="N1152" s="37"/>
     </row>
     <row r="1153">
-      <c r="L1153" s="37"/>
       <c r="M1153" s="37"/>
+      <c r="N1153" s="37"/>
     </row>
     <row r="1154">
-      <c r="L1154" s="37"/>
       <c r="M1154" s="37"/>
+      <c r="N1154" s="37"/>
     </row>
     <row r="1155">
-      <c r="L1155" s="37"/>
       <c r="M1155" s="37"/>
+      <c r="N1155" s="37"/>
     </row>
     <row r="1156">
-      <c r="L1156" s="37"/>
       <c r="M1156" s="37"/>
+      <c r="N1156" s="37"/>
     </row>
     <row r="1157">
-      <c r="L1157" s="37"/>
       <c r="M1157" s="37"/>
+      <c r="N1157" s="37"/>
     </row>
     <row r="1158">
-      <c r="L1158" s="37"/>
       <c r="M1158" s="37"/>
+      <c r="N1158" s="37"/>
     </row>
     <row r="1159">
-      <c r="L1159" s="37"/>
       <c r="M1159" s="37"/>
+      <c r="N1159" s="37"/>
     </row>
     <row r="1160">
-      <c r="L1160" s="37"/>
       <c r="M1160" s="37"/>
+      <c r="N1160" s="37"/>
     </row>
     <row r="1161">
-      <c r="L1161" s="37"/>
       <c r="M1161" s="37"/>
+      <c r="N1161" s="37"/>
     </row>
     <row r="1162">
-      <c r="L1162" s="37"/>
       <c r="M1162" s="37"/>
+      <c r="N1162" s="37"/>
     </row>
     <row r="1163">
-      <c r="L1163" s="37"/>
       <c r="M1163" s="37"/>
+      <c r="N1163" s="37"/>
     </row>
     <row r="1164">
-      <c r="L1164" s="37"/>
       <c r="M1164" s="37"/>
+      <c r="N1164" s="37"/>
     </row>
     <row r="1165">
-      <c r="L1165" s="37"/>
       <c r="M1165" s="37"/>
+      <c r="N1165" s="37"/>
     </row>
     <row r="1166">
-      <c r="L1166" s="37"/>
       <c r="M1166" s="37"/>
+      <c r="N1166" s="37"/>
     </row>
     <row r="1167">
-      <c r="L1167" s="37"/>
       <c r="M1167" s="37"/>
+      <c r="N1167" s="37"/>
     </row>
     <row r="1168">
-      <c r="L1168" s="37"/>
       <c r="M1168" s="37"/>
+      <c r="N1168" s="37"/>
     </row>
     <row r="1169">
-      <c r="L1169" s="37"/>
       <c r="M1169" s="37"/>
+      <c r="N1169" s="37"/>
     </row>
     <row r="1170">
-      <c r="L1170" s="37"/>
       <c r="M1170" s="37"/>
+      <c r="N1170" s="37"/>
     </row>
     <row r="1171">
-      <c r="L1171" s="37"/>
       <c r="M1171" s="37"/>
+      <c r="N1171" s="37"/>
     </row>
     <row r="1172">
-      <c r="L1172" s="37"/>
       <c r="M1172" s="37"/>
+      <c r="N1172" s="37"/>
     </row>
     <row r="1173">
-      <c r="L1173" s="37"/>
       <c r="M1173" s="37"/>
+      <c r="N1173" s="37"/>
     </row>
     <row r="1174">
-      <c r="L1174" s="37"/>
       <c r="M1174" s="37"/>
+      <c r="N1174" s="37"/>
     </row>
     <row r="1175">
-      <c r="L1175" s="37"/>
       <c r="M1175" s="37"/>
+      <c r="N1175" s="37"/>
     </row>
     <row r="1176">
-      <c r="L1176" s="37"/>
       <c r="M1176" s="37"/>
+      <c r="N1176" s="37"/>
     </row>
     <row r="1177">
-      <c r="L1177" s="37"/>
       <c r="M1177" s="37"/>
+      <c r="N1177" s="37"/>
     </row>
     <row r="1178">
-      <c r="L1178" s="37"/>
       <c r="M1178" s="37"/>
+      <c r="N1178" s="37"/>
     </row>
     <row r="1179">
-      <c r="L1179" s="37"/>
       <c r="M1179" s="37"/>
+      <c r="N1179" s="37"/>
     </row>
     <row r="1180">
-      <c r="L1180" s="37"/>
       <c r="M1180" s="37"/>
+      <c r="N1180" s="37"/>
     </row>
     <row r="1181">
-      <c r="L1181" s="37"/>
       <c r="M1181" s="37"/>
+      <c r="N1181" s="37"/>
     </row>
     <row r="1182">
-      <c r="L1182" s="37"/>
       <c r="M1182" s="37"/>
+      <c r="N1182" s="37"/>
     </row>
     <row r="1183">
-      <c r="L1183" s="37"/>
       <c r="M1183" s="37"/>
+      <c r="N1183" s="37"/>
     </row>
     <row r="1184">
-      <c r="L1184" s="37"/>
       <c r="M1184" s="37"/>
+      <c r="N1184" s="37"/>
     </row>
     <row r="1185">
-      <c r="L1185" s="37"/>
       <c r="M1185" s="37"/>
+      <c r="N1185" s="37"/>
     </row>
     <row r="1186">
-      <c r="L1186" s="37"/>
       <c r="M1186" s="37"/>
+      <c r="N1186" s="37"/>
     </row>
     <row r="1187">
-      <c r="L1187" s="37"/>
       <c r="M1187" s="37"/>
+      <c r="N1187" s="37"/>
     </row>
     <row r="1188">
-      <c r="L1188" s="37"/>
       <c r="M1188" s="37"/>
+      <c r="N1188" s="37"/>
     </row>
     <row r="1189">
-      <c r="L1189" s="37"/>
       <c r="M1189" s="37"/>
+      <c r="N1189" s="37"/>
     </row>
     <row r="1190">
-      <c r="L1190" s="37"/>
       <c r="M1190" s="37"/>
+      <c r="N1190" s="37"/>
     </row>
     <row r="1191">
-      <c r="L1191" s="37"/>
       <c r="M1191" s="37"/>
+      <c r="N1191" s="37"/>
     </row>
     <row r="1192">
-      <c r="L1192" s="37"/>
       <c r="M1192" s="37"/>
+      <c r="N1192" s="37"/>
     </row>
     <row r="1193">
-      <c r="L1193" s="37"/>
       <c r="M1193" s="37"/>
+      <c r="N1193" s="37"/>
     </row>
     <row r="1194">
-      <c r="L1194" s="37"/>
       <c r="M1194" s="37"/>
+      <c r="N1194" s="37"/>
     </row>
     <row r="1195">
-      <c r="L1195" s="37"/>
       <c r="M1195" s="37"/>
+      <c r="N1195" s="37"/>
     </row>
     <row r="1196">
-      <c r="L1196" s="37"/>
       <c r="M1196" s="37"/>
+      <c r="N1196" s="37"/>
     </row>
     <row r="1197">
-      <c r="L1197" s="37"/>
       <c r="M1197" s="37"/>
+      <c r="N1197" s="37"/>
     </row>
     <row r="1198">
-      <c r="L1198" s="37"/>
       <c r="M1198" s="37"/>
+      <c r="N1198" s="37"/>
     </row>
     <row r="1199">
-      <c r="L1199" s="37"/>
       <c r="M1199" s="37"/>
+      <c r="N1199" s="37"/>
     </row>
     <row r="1200">
-      <c r="L1200" s="37"/>
       <c r="M1200" s="37"/>
+      <c r="N1200" s="37"/>
     </row>
     <row r="1201">
-      <c r="L1201" s="37"/>
       <c r="M1201" s="37"/>
+      <c r="N1201" s="37"/>
     </row>
     <row r="1202">
-      <c r="L1202" s="37"/>
       <c r="M1202" s="37"/>
+      <c r="N1202" s="37"/>
     </row>
     <row r="1203">
-      <c r="L1203" s="37"/>
       <c r="M1203" s="37"/>
+      <c r="N1203" s="37"/>
     </row>
     <row r="1204">
-      <c r="L1204" s="37"/>
       <c r="M1204" s="37"/>
+      <c r="N1204" s="37"/>
     </row>
     <row r="1205">
-      <c r="L1205" s="37"/>
       <c r="M1205" s="37"/>
+      <c r="N1205" s="37"/>
     </row>
     <row r="1206">
-      <c r="L1206" s="37"/>
       <c r="M1206" s="37"/>
+      <c r="N1206" s="37"/>
     </row>
     <row r="1207">
-      <c r="L1207" s="37"/>
       <c r="M1207" s="37"/>
+      <c r="N1207" s="37"/>
     </row>
     <row r="1208">
-      <c r="L1208" s="37"/>
       <c r="M1208" s="37"/>
+      <c r="N1208" s="37"/>
     </row>
     <row r="1209">
-      <c r="L1209" s="37"/>
       <c r="M1209" s="37"/>
+      <c r="N1209" s="37"/>
     </row>
     <row r="1210">
-      <c r="L1210" s="37"/>
       <c r="M1210" s="37"/>
+      <c r="N1210" s="37"/>
     </row>
     <row r="1211">
-      <c r="L1211" s="37"/>
       <c r="M1211" s="37"/>
+      <c r="N1211" s="37"/>
     </row>
     <row r="1212">
-      <c r="L1212" s="37"/>
       <c r="M1212" s="37"/>
+      <c r="N1212" s="37"/>
     </row>
     <row r="1213">
-      <c r="L1213" s="37"/>
       <c r="M1213" s="37"/>
+      <c r="N1213" s="37"/>
     </row>
     <row r="1214">
-      <c r="L1214" s="37"/>
       <c r="M1214" s="37"/>
+      <c r="N1214" s="37"/>
     </row>
     <row r="1215">
-      <c r="L1215" s="37"/>
       <c r="M1215" s="37"/>
+      <c r="N1215" s="37"/>
     </row>
     <row r="1216">
-      <c r="L1216" s="37"/>
       <c r="M1216" s="37"/>
+      <c r="N1216" s="37"/>
     </row>
     <row r="1217">
-      <c r="L1217" s="37"/>
       <c r="M1217" s="37"/>
+      <c r="N1217" s="37"/>
     </row>
     <row r="1218">
-      <c r="L1218" s="37"/>
       <c r="M1218" s="37"/>
+      <c r="N1218" s="37"/>
     </row>
     <row r="1219">
-      <c r="L1219" s="37"/>
       <c r="M1219" s="37"/>
+      <c r="N1219" s="37"/>
     </row>
     <row r="1220">
-      <c r="L1220" s="37"/>
       <c r="M1220" s="37"/>
+      <c r="N1220" s="37"/>
     </row>
     <row r="1221">
-      <c r="L1221" s="37"/>
       <c r="M1221" s="37"/>
+      <c r="N1221" s="37"/>
     </row>
     <row r="1222">
-      <c r="L1222" s="37"/>
       <c r="M1222" s="37"/>
+      <c r="N1222" s="37"/>
     </row>
     <row r="1223">
-      <c r="L1223" s="37"/>
       <c r="M1223" s="37"/>
+      <c r="N1223" s="37"/>
     </row>
     <row r="1224">
-      <c r="L1224" s="37"/>
       <c r="M1224" s="37"/>
+      <c r="N1224" s="37"/>
     </row>
     <row r="1225">
-      <c r="L1225" s="37"/>
       <c r="M1225" s="37"/>
+      <c r="N1225" s="37"/>
     </row>
     <row r="1226">
-      <c r="L1226" s="37"/>
       <c r="M1226" s="37"/>
+      <c r="N1226" s="37"/>
     </row>
     <row r="1227">
-      <c r="L1227" s="37"/>
       <c r="M1227" s="37"/>
+      <c r="N1227" s="37"/>
     </row>
     <row r="1228">
-      <c r="L1228" s="37"/>
       <c r="M1228" s="37"/>
+      <c r="N1228" s="37"/>
     </row>
     <row r="1229">
-      <c r="L1229" s="37"/>
       <c r="M1229" s="37"/>
+      <c r="N1229" s="37"/>
     </row>
     <row r="1230">
-      <c r="L1230" s="37"/>
       <c r="M1230" s="37"/>
+      <c r="N1230" s="37"/>
     </row>
     <row r="1231">
-      <c r="L1231" s="37"/>
       <c r="M1231" s="37"/>
+      <c r="N1231" s="37"/>
     </row>
     <row r="1232">
-      <c r="L1232" s="37"/>
       <c r="M1232" s="37"/>
+      <c r="N1232" s="37"/>
     </row>
     <row r="1233">
-      <c r="L1233" s="37"/>
       <c r="M1233" s="37"/>
+      <c r="N1233" s="37"/>
     </row>
     <row r="1234">
-      <c r="L1234" s="37"/>
       <c r="M1234" s="37"/>
+      <c r="N1234" s="37"/>
     </row>
     <row r="1235">
-      <c r="L1235" s="37"/>
       <c r="M1235" s="37"/>
+      <c r="N1235" s="37"/>
     </row>
     <row r="1236">
-      <c r="L1236" s="37"/>
       <c r="M1236" s="37"/>
+      <c r="N1236" s="37"/>
     </row>
     <row r="1237">
-      <c r="L1237" s="37"/>
       <c r="M1237" s="37"/>
+      <c r="N1237" s="37"/>
     </row>
     <row r="1238">
-      <c r="L1238" s="37"/>
       <c r="M1238" s="37"/>
+      <c r="N1238" s="37"/>
     </row>
     <row r="1239">
-      <c r="L1239" s="37"/>
       <c r="M1239" s="37"/>
+      <c r="N1239" s="37"/>
     </row>
     <row r="1240">
-      <c r="L1240" s="37"/>
       <c r="M1240" s="37"/>
+      <c r="N1240" s="37"/>
     </row>
     <row r="1241">
-      <c r="L1241" s="37"/>
       <c r="M1241" s="37"/>
+      <c r="N1241" s="37"/>
     </row>
     <row r="1242">
-      <c r="L1242" s="37"/>
       <c r="M1242" s="37"/>
+      <c r="N1242" s="37"/>
     </row>
     <row r="1243">
-      <c r="L1243" s="37"/>
       <c r="M1243" s="37"/>
+      <c r="N1243" s="37"/>
     </row>
     <row r="1244">
-      <c r="L1244" s="37"/>
       <c r="M1244" s="37"/>
+      <c r="N1244" s="37"/>
     </row>
     <row r="1245">
-      <c r="L1245" s="37"/>
       <c r="M1245" s="37"/>
+      <c r="N1245" s="37"/>
     </row>
     <row r="1246">
-      <c r="L1246" s="37"/>
       <c r="M1246" s="37"/>
+      <c r="N1246" s="37"/>
     </row>
     <row r="1247">
-      <c r="L1247" s="37"/>
       <c r="M1247" s="37"/>
+      <c r="N1247" s="37"/>
     </row>
     <row r="1248">
-      <c r="L1248" s="37"/>
       <c r="M1248" s="37"/>
+      <c r="N1248" s="37"/>
     </row>
     <row r="1249">
-      <c r="L1249" s="37"/>
       <c r="M1249" s="37"/>
+      <c r="N1249" s="37"/>
     </row>
     <row r="1250">
-      <c r="L1250" s="37"/>
       <c r="M1250" s="37"/>
+      <c r="N1250" s="37"/>
     </row>
     <row r="1251">
-      <c r="L1251" s="37"/>
       <c r="M1251" s="37"/>
+      <c r="N1251" s="37"/>
     </row>
     <row r="1252">
-      <c r="L1252" s="37"/>
       <c r="M1252" s="37"/>
+      <c r="N1252" s="37"/>
     </row>
     <row r="1253">
-      <c r="L1253" s="37"/>
       <c r="M1253" s="37"/>
+      <c r="N1253" s="37"/>
     </row>
     <row r="1254">
-      <c r="L1254" s="37"/>
       <c r="M1254" s="37"/>
+      <c r="N1254" s="37"/>
     </row>
     <row r="1255">
-      <c r="L1255" s="37"/>
       <c r="M1255" s="37"/>
+      <c r="N1255" s="37"/>
     </row>
     <row r="1256">
-      <c r="L1256" s="37"/>
       <c r="M1256" s="37"/>
+      <c r="N1256" s="37"/>
     </row>
     <row r="1257">
-      <c r="L1257" s="37"/>
       <c r="M1257" s="37"/>
+      <c r="N1257" s="37"/>
     </row>
     <row r="1258">
-      <c r="L1258" s="37"/>
       <c r="M1258" s="37"/>
+      <c r="N1258" s="37"/>
     </row>
     <row r="1259">
-      <c r="L1259" s="37"/>
       <c r="M1259" s="37"/>
+      <c r="N1259" s="37"/>
     </row>
     <row r="1260">
-      <c r="L1260" s="37"/>
       <c r="M1260" s="37"/>
+      <c r="N1260" s="37"/>
     </row>
     <row r="1261">
-      <c r="L1261" s="37"/>
       <c r="M1261" s="37"/>
+      <c r="N1261" s="37"/>
     </row>
     <row r="1262">
-      <c r="L1262" s="37"/>
       <c r="M1262" s="37"/>
+      <c r="N1262" s="37"/>
     </row>
     <row r="1263">
-      <c r="L1263" s="37"/>
       <c r="M1263" s="37"/>
+      <c r="N1263" s="37"/>
     </row>
     <row r="1264">
-      <c r="L1264" s="37"/>
       <c r="M1264" s="37"/>
+      <c r="N1264" s="37"/>
     </row>
     <row r="1265">
-      <c r="L1265" s="37"/>
       <c r="M1265" s="37"/>
+      <c r="N1265" s="37"/>
     </row>
     <row r="1266">
-      <c r="L1266" s="37"/>
       <c r="M1266" s="37"/>
+      <c r="N1266" s="37"/>
     </row>
     <row r="1267">
-      <c r="L1267" s="37"/>
       <c r="M1267" s="37"/>
+      <c r="N1267" s="37"/>
     </row>
     <row r="1268">
-      <c r="L1268" s="37"/>
       <c r="M1268" s="37"/>
+      <c r="N1268" s="37"/>
     </row>
     <row r="1269">
-      <c r="L1269" s="37"/>
       <c r="M1269" s="37"/>
+      <c r="N1269" s="37"/>
     </row>
     <row r="1270">
-      <c r="L1270" s="37"/>
       <c r="M1270" s="37"/>
+      <c r="N1270" s="37"/>
     </row>
     <row r="1271">
-      <c r="L1271" s="37"/>
       <c r="M1271" s="37"/>
+      <c r="N1271" s="37"/>
     </row>
     <row r="1272">
-      <c r="L1272" s="37"/>
       <c r="M1272" s="37"/>
+      <c r="N1272" s="37"/>
     </row>
     <row r="1273">
-      <c r="L1273" s="37"/>
       <c r="M1273" s="37"/>
+      <c r="N1273" s="37"/>
     </row>
     <row r="1274">
-      <c r="L1274" s="37"/>
       <c r="M1274" s="37"/>
+      <c r="N1274" s="37"/>
     </row>
     <row r="1275">
-      <c r="L1275" s="37"/>
       <c r="M1275" s="37"/>
+      <c r="N1275" s="37"/>
     </row>
     <row r="1276">
-      <c r="L1276" s="37"/>
       <c r="M1276" s="37"/>
+      <c r="N1276" s="37"/>
     </row>
     <row r="1277">
-      <c r="L1277" s="37"/>
       <c r="M1277" s="37"/>
+      <c r="N1277" s="37"/>
     </row>
     <row r="1278">
-      <c r="L1278" s="37"/>
       <c r="M1278" s="37"/>
+      <c r="N1278" s="37"/>
     </row>
     <row r="1279">
-      <c r="L1279" s="37"/>
       <c r="M1279" s="37"/>
+      <c r="N1279" s="37"/>
     </row>
     <row r="1280">
-      <c r="L1280" s="37"/>
       <c r="M1280" s="37"/>
+      <c r="N1280" s="37"/>
     </row>
     <row r="1281">
-      <c r="L1281" s="37"/>
       <c r="M1281" s="37"/>
+      <c r="N1281" s="37"/>
     </row>
     <row r="1282">
-      <c r="L1282" s="37"/>
       <c r="M1282" s="37"/>
+      <c r="N1282" s="37"/>
     </row>
     <row r="1283">
-      <c r="L1283" s="37"/>
       <c r="M1283" s="37"/>
+      <c r="N1283" s="37"/>
     </row>
     <row r="1284">
-      <c r="L1284" s="37"/>
       <c r="M1284" s="37"/>
+      <c r="N1284" s="37"/>
     </row>
     <row r="1285">
-      <c r="L1285" s="37"/>
       <c r="M1285" s="37"/>
+      <c r="N1285" s="37"/>
     </row>
     <row r="1286">
-      <c r="L1286" s="37"/>
       <c r="M1286" s="37"/>
+      <c r="N1286" s="37"/>
     </row>
     <row r="1287">
-      <c r="L1287" s="37"/>
       <c r="M1287" s="37"/>
+      <c r="N1287" s="37"/>
     </row>
     <row r="1288">
-      <c r="L1288" s="37"/>
       <c r="M1288" s="37"/>
+      <c r="N1288" s="37"/>
     </row>
     <row r="1289">
-      <c r="L1289" s="37"/>
       <c r="M1289" s="37"/>
+      <c r="N1289" s="37"/>
     </row>
     <row r="1290">
-      <c r="L1290" s="37"/>
       <c r="M1290" s="37"/>
+      <c r="N1290" s="37"/>
     </row>
     <row r="1291">
-      <c r="L1291" s="37"/>
       <c r="M1291" s="37"/>
+      <c r="N1291" s="37"/>
     </row>
     <row r="1292">
-      <c r="L1292" s="37"/>
       <c r="M1292" s="37"/>
+      <c r="N1292" s="37"/>
     </row>
     <row r="1293">
-      <c r="L1293" s="37"/>
       <c r="M1293" s="37"/>
+      <c r="N1293" s="37"/>
     </row>
     <row r="1294">
-      <c r="L1294" s="37"/>
       <c r="M1294" s="37"/>
+      <c r="N1294" s="37"/>
     </row>
     <row r="1295">
-      <c r="L1295" s="37"/>
       <c r="M1295" s="37"/>
+      <c r="N1295" s="37"/>
     </row>
     <row r="1296">
-      <c r="L1296" s="37"/>
       <c r="M1296" s="37"/>
+      <c r="N1296" s="37"/>
     </row>
     <row r="1297">
-      <c r="L1297" s="37"/>
       <c r="M1297" s="37"/>
+      <c r="N1297" s="37"/>
     </row>
     <row r="1298">
-      <c r="L1298" s="37"/>
       <c r="M1298" s="37"/>
+      <c r="N1298" s="37"/>
     </row>
     <row r="1299">
-      <c r="L1299" s="37"/>
       <c r="M1299" s="37"/>
+      <c r="N1299" s="37"/>
     </row>
     <row r="1300">
-      <c r="L1300" s="37"/>
       <c r="M1300" s="37"/>
+      <c r="N1300" s="37"/>
     </row>
     <row r="1301">
-      <c r="L1301" s="37"/>
       <c r="M1301" s="37"/>
+      <c r="N1301" s="37"/>
     </row>
     <row r="1302">
-      <c r="L1302" s="37"/>
       <c r="M1302" s="37"/>
+      <c r="N1302" s="37"/>
     </row>
     <row r="1303">
-      <c r="L1303" s="37"/>
       <c r="M1303" s="37"/>
+      <c r="N1303" s="37"/>
     </row>
     <row r="1304">
-      <c r="L1304" s="37"/>
       <c r="M1304" s="37"/>
+      <c r="N1304" s="37"/>
     </row>
     <row r="1305">
-      <c r="L1305" s="37"/>
       <c r="M1305" s="37"/>
+      <c r="N1305" s="37"/>
     </row>
     <row r="1306">
-      <c r="L1306" s="37"/>
       <c r="M1306" s="37"/>
+      <c r="N1306" s="37"/>
     </row>
     <row r="1307">
-      <c r="L1307" s="37"/>
       <c r="M1307" s="37"/>
+      <c r="N1307" s="37"/>
     </row>
     <row r="1308">
-      <c r="L1308" s="37"/>
       <c r="M1308" s="37"/>
+      <c r="N1308" s="37"/>
     </row>
     <row r="1309">
-      <c r="L1309" s="37"/>
       <c r="M1309" s="37"/>
+      <c r="N1309" s="37"/>
     </row>
     <row r="1310">
-      <c r="L1310" s="37"/>
       <c r="M1310" s="37"/>
+      <c r="N1310" s="37"/>
     </row>
     <row r="1311">
-      <c r="L1311" s="37"/>
       <c r="M1311" s="37"/>
+      <c r="N1311" s="37"/>
     </row>
     <row r="1312">
-      <c r="L1312" s="37"/>
       <c r="M1312" s="37"/>
+      <c r="N1312" s="37"/>
     </row>
     <row r="1313">
-      <c r="L1313" s="37"/>
       <c r="M1313" s="37"/>
+      <c r="N1313" s="37"/>
     </row>
     <row r="1314">
-      <c r="L1314" s="37"/>
       <c r="M1314" s="37"/>
+      <c r="N1314" s="37"/>
     </row>
     <row r="1315">
-      <c r="L1315" s="37"/>
       <c r="M1315" s="37"/>
+      <c r="N1315" s="37"/>
     </row>
     <row r="1316">
-      <c r="L1316" s="37"/>
       <c r="M1316" s="37"/>
+      <c r="N1316" s="37"/>
     </row>
     <row r="1317">
-      <c r="L1317" s="37"/>
       <c r="M1317" s="37"/>
+      <c r="N1317" s="37"/>
     </row>
     <row r="1318">
-      <c r="L1318" s="37"/>
       <c r="M1318" s="37"/>
+      <c r="N1318" s="37"/>
     </row>
     <row r="1319">
-      <c r="L1319" s="37"/>
       <c r="M1319" s="37"/>
+      <c r="N1319" s="37"/>
     </row>
     <row r="1320">
-      <c r="L1320" s="37"/>
       <c r="M1320" s="37"/>
+      <c r="N1320" s="37"/>
     </row>
     <row r="1321">
-      <c r="L1321" s="37"/>
       <c r="M1321" s="37"/>
+      <c r="N1321" s="37"/>
     </row>
     <row r="1322">
-      <c r="L1322" s="37"/>
       <c r="M1322" s="37"/>
+      <c r="N1322" s="37"/>
     </row>
     <row r="1323">
-      <c r="L1323" s="37"/>
       <c r="M1323" s="37"/>
+      <c r="N1323" s="37"/>
     </row>
     <row r="1324">
-      <c r="L1324" s="37"/>
       <c r="M1324" s="37"/>
+      <c r="N1324" s="37"/>
     </row>
     <row r="1325">
-      <c r="L1325" s="37"/>
       <c r="M1325" s="37"/>
+      <c r="N1325" s="37"/>
     </row>
     <row r="1326">
-      <c r="L1326" s="37"/>
       <c r="M1326" s="37"/>
+      <c r="N1326" s="37"/>
     </row>
     <row r="1327">
-      <c r="L1327" s="37"/>
       <c r="M1327" s="37"/>
+      <c r="N1327" s="37"/>
     </row>
     <row r="1328">
-      <c r="L1328" s="37"/>
       <c r="M1328" s="37"/>
+      <c r="N1328" s="37"/>
     </row>
     <row r="1329">
-      <c r="L1329" s="37"/>
       <c r="M1329" s="37"/>
+      <c r="N1329" s="37"/>
     </row>
     <row r="1330">
-      <c r="L1330" s="37"/>
       <c r="M1330" s="37"/>
+      <c r="N1330" s="37"/>
     </row>
     <row r="1331">
-      <c r="L1331" s="37"/>
       <c r="M1331" s="37"/>
+      <c r="N1331" s="37"/>
     </row>
     <row r="1332">
-      <c r="L1332" s="37"/>
       <c r="M1332" s="37"/>
+      <c r="N1332" s="37"/>
     </row>
     <row r="1333">
-      <c r="L1333" s="37"/>
       <c r="M1333" s="37"/>
+      <c r="N1333" s="37"/>
     </row>
     <row r="1334">
-      <c r="L1334" s="37"/>
       <c r="M1334" s="37"/>
+      <c r="N1334" s="37"/>
     </row>
     <row r="1335">
-      <c r="L1335" s="37"/>
       <c r="M1335" s="37"/>
+      <c r="N1335" s="37"/>
     </row>
     <row r="1336">
-      <c r="L1336" s="37"/>
       <c r="M1336" s="37"/>
+      <c r="N1336" s="37"/>
     </row>
     <row r="1337">
-      <c r="L1337" s="37"/>
       <c r="M1337" s="37"/>
+      <c r="N1337" s="37"/>
     </row>
     <row r="1338">
-      <c r="L1338" s="37"/>
       <c r="M1338" s="37"/>
+      <c r="N1338" s="37"/>
     </row>
     <row r="1339">
-      <c r="L1339" s="37"/>
       <c r="M1339" s="37"/>
+      <c r="N1339" s="37"/>
     </row>
     <row r="1340">
-      <c r="L1340" s="37"/>
       <c r="M1340" s="37"/>
+      <c r="N1340" s="37"/>
     </row>
     <row r="1341">
-      <c r="L1341" s="37"/>
       <c r="M1341" s="37"/>
+      <c r="N1341" s="37"/>
     </row>
     <row r="1342">
-      <c r="L1342" s="37"/>
       <c r="M1342" s="37"/>
+      <c r="N1342" s="37"/>
     </row>
     <row r="1343">
-      <c r="L1343" s="37"/>
       <c r="M1343" s="37"/>
+      <c r="N1343" s="37"/>
     </row>
     <row r="1344">
-      <c r="L1344" s="37"/>
       <c r="M1344" s="37"/>
+      <c r="N1344" s="37"/>
     </row>
     <row r="1345">
-      <c r="L1345" s="37"/>
       <c r="M1345" s="37"/>
+      <c r="N1345" s="37"/>
     </row>
     <row r="1346">
-      <c r="L1346" s="37"/>
       <c r="M1346" s="37"/>
+      <c r="N1346" s="37"/>
     </row>
     <row r="1347">
-      <c r="L1347" s="37"/>
       <c r="M1347" s="37"/>
+      <c r="N1347" s="37"/>
     </row>
     <row r="1348">
-      <c r="L1348" s="37"/>
       <c r="M1348" s="37"/>
+      <c r="N1348" s="37"/>
     </row>
     <row r="1349">
-      <c r="L1349" s="37"/>
       <c r="M1349" s="37"/>
+      <c r="N1349" s="37"/>
     </row>
     <row r="1350">
-      <c r="L1350" s="37"/>
       <c r="M1350" s="37"/>
+      <c r="N1350" s="37"/>
     </row>
     <row r="1351">
-      <c r="L1351" s="37"/>
       <c r="M1351" s="37"/>
+      <c r="N1351" s="37"/>
     </row>
     <row r="1352">
-      <c r="L1352" s="37"/>
       <c r="M1352" s="37"/>
+      <c r="N1352" s="37"/>
     </row>
     <row r="1353">
-      <c r="L1353" s="37"/>
       <c r="M1353" s="37"/>
+      <c r="N1353" s="37"/>
     </row>
     <row r="1354">
-      <c r="L1354" s="37"/>
       <c r="M1354" s="37"/>
+      <c r="N1354" s="37"/>
     </row>
     <row r="1355">
-      <c r="L1355" s="37"/>
       <c r="M1355" s="37"/>
+      <c r="N1355" s="37"/>
     </row>
     <row r="1356">
-      <c r="L1356" s="37"/>
       <c r="M1356" s="37"/>
+      <c r="N1356" s="37"/>
     </row>
     <row r="1357">
-      <c r="L1357" s="37"/>
       <c r="M1357" s="37"/>
+      <c r="N1357" s="37"/>
     </row>
     <row r="1358">
-      <c r="L1358" s="37"/>
       <c r="M1358" s="37"/>
+      <c r="N1358" s="37"/>
     </row>
     <row r="1359">
-      <c r="L1359" s="37"/>
       <c r="M1359" s="37"/>
+      <c r="N1359" s="37"/>
     </row>
     <row r="1360">
-      <c r="L1360" s="37"/>
       <c r="M1360" s="37"/>
+      <c r="N1360" s="37"/>
     </row>
     <row r="1361">
-      <c r="L1361" s="37"/>
       <c r="M1361" s="37"/>
+      <c r="N1361" s="37"/>
     </row>
     <row r="1362">
-      <c r="L1362" s="37"/>
       <c r="M1362" s="37"/>
+      <c r="N1362" s="37"/>
     </row>
     <row r="1363">
-      <c r="L1363" s="37"/>
       <c r="M1363" s="37"/>
+      <c r="N1363" s="37"/>
     </row>
     <row r="1364">
-      <c r="L1364" s="37"/>
       <c r="M1364" s="37"/>
+      <c r="N1364" s="37"/>
     </row>
     <row r="1365">
-      <c r="L1365" s="37"/>
       <c r="M1365" s="37"/>
+      <c r="N1365" s="37"/>
     </row>
     <row r="1366">
-      <c r="L1366" s="37"/>
       <c r="M1366" s="37"/>
+      <c r="N1366" s="37"/>
     </row>
     <row r="1367">
-      <c r="L1367" s="37"/>
       <c r="M1367" s="37"/>
+      <c r="N1367" s="37"/>
     </row>
     <row r="1368">
-      <c r="L1368" s="37"/>
       <c r="M1368" s="37"/>
+      <c r="N1368" s="37"/>
     </row>
     <row r="1369">
-      <c r="L1369" s="37"/>
       <c r="M1369" s="37"/>
+      <c r="N1369" s="37"/>
     </row>
     <row r="1370">
-      <c r="L1370" s="37"/>
       <c r="M1370" s="37"/>
+      <c r="N1370" s="37"/>
     </row>
     <row r="1371">
-      <c r="L1371" s="37"/>
       <c r="M1371" s="37"/>
+      <c r="N1371" s="37"/>
     </row>
     <row r="1372">
-      <c r="L1372" s="37"/>
       <c r="M1372" s="37"/>
+      <c r="N1372" s="37"/>
     </row>
     <row r="1373">
-      <c r="L1373" s="37"/>
       <c r="M1373" s="37"/>
+      <c r="N1373" s="37"/>
     </row>
     <row r="1374">
-      <c r="L1374" s="37"/>
       <c r="M1374" s="37"/>
+      <c r="N1374" s="37"/>
     </row>
     <row r="1375">
-      <c r="L1375" s="37"/>
       <c r="M1375" s="37"/>
+      <c r="N1375" s="37"/>
     </row>
     <row r="1376">
-      <c r="L1376" s="37"/>
       <c r="M1376" s="37"/>
+      <c r="N1376" s="37"/>
     </row>
     <row r="1377">
-      <c r="L1377" s="37"/>
       <c r="M1377" s="37"/>
+      <c r="N1377" s="37"/>
     </row>
     <row r="1378">
-      <c r="L1378" s="37"/>
       <c r="M1378" s="37"/>
+      <c r="N1378" s="37"/>
     </row>
     <row r="1379">
-      <c r="L1379" s="37"/>
       <c r="M1379" s="37"/>
+      <c r="N1379" s="37"/>
     </row>
     <row r="1380">
-      <c r="L1380" s="37"/>
       <c r="M1380" s="37"/>
+      <c r="N1380" s="37"/>
     </row>
     <row r="1381">
-      <c r="L1381" s="37"/>
       <c r="M1381" s="37"/>
+      <c r="N1381" s="37"/>
     </row>
     <row r="1382">
-      <c r="L1382" s="37"/>
       <c r="M1382" s="37"/>
+      <c r="N1382" s="37"/>
     </row>
     <row r="1383">
-      <c r="L1383" s="37"/>
       <c r="M1383" s="37"/>
+      <c r="N1383" s="37"/>
     </row>
     <row r="1384">
-      <c r="L1384" s="37"/>
       <c r="M1384" s="37"/>
+      <c r="N1384" s="37"/>
     </row>
     <row r="1385">
-      <c r="L1385" s="37"/>
       <c r="M1385" s="37"/>
+      <c r="N1385" s="37"/>
     </row>
     <row r="1386">
-      <c r="L1386" s="37"/>
       <c r="M1386" s="37"/>
+      <c r="N1386" s="37"/>
     </row>
     <row r="1387">
-      <c r="L1387" s="37"/>
       <c r="M1387" s="37"/>
+      <c r="N1387" s="37"/>
     </row>
     <row r="1388">
-      <c r="L1388" s="37"/>
       <c r="M1388" s="37"/>
+      <c r="N1388" s="37"/>
     </row>
     <row r="1389">
-      <c r="L1389" s="37"/>
       <c r="M1389" s="37"/>
+      <c r="N1389" s="37"/>
     </row>
     <row r="1390">
-      <c r="L1390" s="37"/>
       <c r="M1390" s="37"/>
+      <c r="N1390" s="37"/>
     </row>
     <row r="1391">
-      <c r="L1391" s="37"/>
       <c r="M1391" s="37"/>
+      <c r="N1391" s="37"/>
     </row>
     <row r="1392">
-      <c r="L1392" s="37"/>
       <c r="M1392" s="37"/>
+      <c r="N1392" s="37"/>
     </row>
     <row r="1393">
-      <c r="L1393" s="37"/>
       <c r="M1393" s="37"/>
+      <c r="N1393" s="37"/>
     </row>
     <row r="1394">
-      <c r="L1394" s="37"/>
       <c r="M1394" s="37"/>
+      <c r="N1394" s="37"/>
     </row>
     <row r="1395">
-      <c r="L1395" s="37"/>
       <c r="M1395" s="37"/>
+      <c r="N1395" s="37"/>
     </row>
     <row r="1396">
-      <c r="L1396" s="37"/>
       <c r="M1396" s="37"/>
+      <c r="N1396" s="37"/>
     </row>
     <row r="1397">
-      <c r="L1397" s="37"/>
       <c r="M1397" s="37"/>
+      <c r="N1397" s="37"/>
     </row>
     <row r="1398">
-      <c r="L1398" s="37"/>
       <c r="M1398" s="37"/>
+      <c r="N1398" s="37"/>
     </row>
     <row r="1399">
-      <c r="L1399" s="37"/>
       <c r="M1399" s="37"/>
+      <c r="N1399" s="37"/>
     </row>
     <row r="1400">
-      <c r="L1400" s="37"/>
       <c r="M1400" s="37"/>
+      <c r="N1400" s="37"/>
     </row>
     <row r="1401">
-      <c r="L1401" s="37"/>
       <c r="M1401" s="37"/>
+      <c r="N1401" s="37"/>
     </row>
     <row r="1402">
-      <c r="L1402" s="37"/>
       <c r="M1402" s="37"/>
+      <c r="N1402" s="37"/>
     </row>
     <row r="1403">
-      <c r="L1403" s="37"/>
       <c r="M1403" s="37"/>
+      <c r="N1403" s="37"/>
     </row>
     <row r="1404">
-      <c r="L1404" s="37"/>
       <c r="M1404" s="37"/>
+      <c r="N1404" s="37"/>
     </row>
     <row r="1405">
-      <c r="L1405" s="37"/>
       <c r="M1405" s="37"/>
+      <c r="N1405" s="37"/>
     </row>
     <row r="1406">
-      <c r="L1406" s="37"/>
       <c r="M1406" s="37"/>
+      <c r="N1406" s="37"/>
     </row>
     <row r="1407">
-      <c r="L1407" s="37"/>
       <c r="M1407" s="37"/>
+      <c r="N1407" s="37"/>
     </row>
     <row r="1408">
-      <c r="L1408" s="37"/>
       <c r="M1408" s="37"/>
+      <c r="N1408" s="37"/>
     </row>
     <row r="1409">
-      <c r="L1409" s="37"/>
       <c r="M1409" s="37"/>
+      <c r="N1409" s="37"/>
     </row>
     <row r="1410">
-      <c r="L1410" s="37"/>
       <c r="M1410" s="37"/>
+      <c r="N1410" s="37"/>
     </row>
     <row r="1411">
-      <c r="L1411" s="37"/>
       <c r="M1411" s="37"/>
+      <c r="N1411" s="37"/>
     </row>
     <row r="1412">
-      <c r="L1412" s="37"/>
       <c r="M1412" s="37"/>
+      <c r="N1412" s="37"/>
     </row>
     <row r="1413">
-      <c r="L1413" s="37"/>
       <c r="M1413" s="37"/>
+      <c r="N1413" s="37"/>
     </row>
     <row r="1414">
-      <c r="L1414" s="37"/>
       <c r="M1414" s="37"/>
+      <c r="N1414" s="37"/>
     </row>
     <row r="1415">
-      <c r="L1415" s="37"/>
       <c r="M1415" s="37"/>
+      <c r="N1415" s="37"/>
     </row>
     <row r="1416">
-      <c r="L1416" s="37"/>
       <c r="M1416" s="37"/>
+      <c r="N1416" s="37"/>
     </row>
     <row r="1417">
-      <c r="L1417" s="37"/>
       <c r="M1417" s="37"/>
+      <c r="N1417" s="37"/>
     </row>
     <row r="1418">
-      <c r="L1418" s="37"/>
       <c r="M1418" s="37"/>
+      <c r="N1418" s="37"/>
     </row>
     <row r="1419">
-      <c r="L1419" s="37"/>
       <c r="M1419" s="37"/>
+      <c r="N1419" s="37"/>
     </row>
     <row r="1420">
-      <c r="L1420" s="37"/>
       <c r="M1420" s="37"/>
+      <c r="N1420" s="37"/>
     </row>
     <row r="1421">
-      <c r="L1421" s="37"/>
       <c r="M1421" s="37"/>
+      <c r="N1421" s="37"/>
     </row>
     <row r="1422">
-      <c r="L1422" s="37"/>
       <c r="M1422" s="37"/>
+      <c r="N1422" s="37"/>
     </row>
     <row r="1423">
-      <c r="L1423" s="37"/>
       <c r="M1423" s="37"/>
+      <c r="N1423" s="37"/>
     </row>
     <row r="1424">
-      <c r="L1424" s="37"/>
       <c r="M1424" s="37"/>
+      <c r="N1424" s="37"/>
     </row>
     <row r="1425">
-      <c r="L1425" s="37"/>
       <c r="M1425" s="37"/>
+      <c r="N1425" s="37"/>
     </row>
     <row r="1426">
-      <c r="L1426" s="37"/>
       <c r="M1426" s="37"/>
+      <c r="N1426" s="37"/>
     </row>
     <row r="1427">
-      <c r="L1427" s="37"/>
       <c r="M1427" s="37"/>
+      <c r="N1427" s="37"/>
     </row>
     <row r="1428">
-      <c r="L1428" s="37"/>
       <c r="M1428" s="37"/>
+      <c r="N1428" s="37"/>
     </row>
     <row r="1429">
-      <c r="L1429" s="37"/>
       <c r="M1429" s="37"/>
+      <c r="N1429" s="37"/>
     </row>
     <row r="1430">
-      <c r="L1430" s="37"/>
       <c r="M1430" s="37"/>
+      <c r="N1430" s="37"/>
     </row>
     <row r="1431">
-      <c r="L1431" s="37"/>
       <c r="M1431" s="37"/>
+      <c r="N1431" s="37"/>
     </row>
     <row r="1432">
-      <c r="L1432" s="37"/>
       <c r="M1432" s="37"/>
+      <c r="N1432" s="37"/>
     </row>
     <row r="1433">
-      <c r="L1433" s="37"/>
       <c r="M1433" s="37"/>
+      <c r="N1433" s="37"/>
     </row>
     <row r="1434">
-      <c r="L1434" s="37"/>
       <c r="M1434" s="37"/>
+      <c r="N1434" s="37"/>
     </row>
     <row r="1435">
-      <c r="L1435" s="37"/>
       <c r="M1435" s="37"/>
+      <c r="N1435" s="37"/>
     </row>
     <row r="1436">
-      <c r="L1436" s="37"/>
       <c r="M1436" s="37"/>
+      <c r="N1436" s="37"/>
     </row>
     <row r="1437">
-      <c r="L1437" s="37"/>
       <c r="M1437" s="37"/>
+      <c r="N1437" s="37"/>
     </row>
     <row r="1438">
-      <c r="L1438" s="37"/>
       <c r="M1438" s="37"/>
+      <c r="N1438" s="37"/>
     </row>
     <row r="1439">
-      <c r="L1439" s="37"/>
       <c r="M1439" s="37"/>
+      <c r="N1439" s="37"/>
     </row>
     <row r="1440">
-      <c r="L1440" s="37"/>
       <c r="M1440" s="37"/>
+      <c r="N1440" s="37"/>
     </row>
     <row r="1441">
-      <c r="L1441" s="37"/>
       <c r="M1441" s="37"/>
+      <c r="N1441" s="37"/>
     </row>
     <row r="1442">
-      <c r="L1442" s="37"/>
       <c r="M1442" s="37"/>
+      <c r="N1442" s="37"/>
     </row>
     <row r="1443">
-      <c r="L1443" s="37"/>
       <c r="M1443" s="37"/>
+      <c r="N1443" s="37"/>
     </row>
     <row r="1444">
-      <c r="L1444" s="37"/>
       <c r="M1444" s="37"/>
+      <c r="N1444" s="37"/>
     </row>
     <row r="1445">
-      <c r="L1445" s="37"/>
       <c r="M1445" s="37"/>
+      <c r="N1445" s="37"/>
     </row>
     <row r="1446">
-      <c r="L1446" s="37"/>
       <c r="M1446" s="37"/>
+      <c r="N1446" s="37"/>
     </row>
     <row r="1447">
-      <c r="L1447" s="37"/>
       <c r="M1447" s="37"/>
+      <c r="N1447" s="37"/>
     </row>
     <row r="1448">
-      <c r="L1448" s="37"/>
       <c r="M1448" s="37"/>
+      <c r="N1448" s="37"/>
     </row>
     <row r="1449">
-      <c r="L1449" s="37"/>
       <c r="M1449" s="37"/>
+      <c r="N1449" s="37"/>
     </row>
     <row r="1450">
-      <c r="L1450" s="37"/>
       <c r="M1450" s="37"/>
+      <c r="N1450" s="37"/>
     </row>
     <row r="1451">
-      <c r="L1451" s="37"/>
       <c r="M1451" s="37"/>
+      <c r="N1451" s="37"/>
     </row>
     <row r="1452">
-      <c r="L1452" s="37"/>
       <c r="M1452" s="37"/>
+      <c r="N1452" s="37"/>
     </row>
     <row r="1453">
-      <c r="L1453" s="37"/>
       <c r="M1453" s="37"/>
+      <c r="N1453" s="37"/>
     </row>
     <row r="1454">
-      <c r="L1454" s="37"/>
       <c r="M1454" s="37"/>
+      <c r="N1454" s="37"/>
     </row>
     <row r="1455">
-      <c r="L1455" s="37"/>
       <c r="M1455" s="37"/>
+      <c r="N1455" s="37"/>
     </row>
     <row r="1456">
-      <c r="L1456" s="37"/>
       <c r="M1456" s="37"/>
+      <c r="N1456" s="37"/>
     </row>
     <row r="1457">
-      <c r="L1457" s="37"/>
       <c r="M1457" s="37"/>
+      <c r="N1457" s="37"/>
     </row>
     <row r="1458">
-      <c r="L1458" s="37"/>
       <c r="M1458" s="37"/>
+      <c r="N1458" s="37"/>
     </row>
     <row r="1459">
-      <c r="L1459" s="37"/>
       <c r="M1459" s="37"/>
+      <c r="N1459" s="37"/>
     </row>
     <row r="1460">
-      <c r="L1460" s="37"/>
       <c r="M1460" s="37"/>
+      <c r="N1460" s="37"/>
     </row>
     <row r="1461">
-      <c r="L1461" s="37"/>
       <c r="M1461" s="37"/>
+      <c r="N1461" s="37"/>
     </row>
     <row r="1462">
-      <c r="L1462" s="37"/>
       <c r="M1462" s="37"/>
+      <c r="N1462" s="37"/>
     </row>
     <row r="1463">
-      <c r="L1463" s="37"/>
       <c r="M1463" s="37"/>
+      <c r="N1463" s="37"/>
     </row>
     <row r="1464">
-      <c r="L1464" s="37"/>
       <c r="M1464" s="37"/>
+      <c r="N1464" s="37"/>
     </row>
     <row r="1465">
-      <c r="L1465" s="37"/>
       <c r="M1465" s="37"/>
+      <c r="N1465" s="37"/>
     </row>
     <row r="1466">
-      <c r="L1466" s="37"/>
       <c r="M1466" s="37"/>
+      <c r="N1466" s="37"/>
     </row>
     <row r="1467">
-      <c r="L1467" s="37"/>
       <c r="M1467" s="37"/>
+      <c r="N1467" s="37"/>
     </row>
     <row r="1468">
-      <c r="L1468" s="37"/>
       <c r="M1468" s="37"/>
+      <c r="N1468" s="37"/>
     </row>
     <row r="1469">
-      <c r="L1469" s="37"/>
       <c r="M1469" s="37"/>
+      <c r="N1469" s="37"/>
     </row>
     <row r="1470">
-      <c r="L1470" s="37"/>
       <c r="M1470" s="37"/>
+      <c r="N1470" s="37"/>
     </row>
     <row r="1471">
-      <c r="L1471" s="37"/>
       <c r="M1471" s="37"/>
+      <c r="N1471" s="37"/>
     </row>
     <row r="1472">
-      <c r="L1472" s="37"/>
       <c r="M1472" s="37"/>
+      <c r="N1472" s="37"/>
     </row>
     <row r="1473">
-      <c r="L1473" s="37"/>
       <c r="M1473" s="37"/>
+      <c r="N1473" s="37"/>
     </row>
     <row r="1474">
-      <c r="L1474" s="37"/>
       <c r="M1474" s="37"/>
+      <c r="N1474" s="37"/>
     </row>
     <row r="1475">
-      <c r="L1475" s="37"/>
       <c r="M1475" s="37"/>
+      <c r="N1475" s="37"/>
     </row>
     <row r="1476">
-      <c r="L1476" s="37"/>
       <c r="M1476" s="37"/>
+      <c r="N1476" s="37"/>
     </row>
     <row r="1477">
-      <c r="L1477" s="37"/>
       <c r="M1477" s="37"/>
+      <c r="N1477" s="37"/>
     </row>
     <row r="1478">
-      <c r="L1478" s="37"/>
       <c r="M1478" s="37"/>
+      <c r="N1478" s="37"/>
     </row>
     <row r="1479">
-      <c r="L1479" s="37"/>
       <c r="M1479" s="37"/>
+      <c r="N1479" s="37"/>
     </row>
     <row r="1480">
-      <c r="L1480" s="37"/>
       <c r="M1480" s="37"/>
+      <c r="N1480" s="37"/>
     </row>
     <row r="1481">
-      <c r="L1481" s="37"/>
       <c r="M1481" s="37"/>
+      <c r="N1481" s="37"/>
     </row>
     <row r="1482">
-      <c r="L1482" s="37"/>
       <c r="M1482" s="37"/>
+      <c r="N1482" s="37"/>
     </row>
     <row r="1483">
-      <c r="L1483" s="37"/>
       <c r="M1483" s="37"/>
+      <c r="N1483" s="37"/>
     </row>
     <row r="1484">
-      <c r="L1484" s="37"/>
       <c r="M1484" s="37"/>
+      <c r="N1484" s="37"/>
     </row>
     <row r="1485">
-      <c r="L1485" s="37"/>
       <c r="M1485" s="37"/>
+      <c r="N1485" s="37"/>
     </row>
     <row r="1486">
-      <c r="L1486" s="37"/>
       <c r="M1486" s="37"/>
+      <c r="N1486" s="37"/>
     </row>
     <row r="1487">
-      <c r="L1487" s="37"/>
       <c r="M1487" s="37"/>
+      <c r="N1487" s="37"/>
     </row>
     <row r="1488">
-      <c r="L1488" s="37"/>
       <c r="M1488" s="37"/>
+      <c r="N1488" s="37"/>
     </row>
     <row r="1489">
-      <c r="L1489" s="37"/>
       <c r="M1489" s="37"/>
+      <c r="N1489" s="37"/>
     </row>
     <row r="1490">
-      <c r="L1490" s="37"/>
       <c r="M1490" s="37"/>
+      <c r="N1490" s="37"/>
     </row>
     <row r="1491">
-      <c r="L1491" s="37"/>
       <c r="M1491" s="37"/>
+      <c r="N1491" s="37"/>
     </row>
     <row r="1492">
-      <c r="L1492" s="37"/>
       <c r="M1492" s="37"/>
+      <c r="N1492" s="37"/>
     </row>
     <row r="1493">
-      <c r="L1493" s="37"/>
       <c r="M1493" s="37"/>
+      <c r="N1493" s="37"/>
     </row>
     <row r="1494">
-      <c r="L1494" s="37"/>
       <c r="M1494" s="37"/>
+      <c r="N1494" s="37"/>
     </row>
     <row r="1495">
-      <c r="L1495" s="37"/>
       <c r="M1495" s="37"/>
+      <c r="N1495" s="37"/>
     </row>
     <row r="1496">
-      <c r="L1496" s="37"/>
       <c r="M1496" s="37"/>
+      <c r="N1496" s="37"/>
     </row>
     <row r="1497">
-      <c r="L1497" s="37"/>
       <c r="M1497" s="37"/>
+      <c r="N1497" s="37"/>
     </row>
     <row r="1498">
-      <c r="L1498" s="37"/>
       <c r="M1498" s="37"/>
+      <c r="N1498" s="37"/>
     </row>
     <row r="1499">
-      <c r="L1499" s="37"/>
       <c r="M1499" s="37"/>
+      <c r="N1499" s="37"/>
     </row>
     <row r="1500">
-      <c r="L1500" s="37"/>
       <c r="M1500" s="37"/>
+      <c r="N1500" s="37"/>
     </row>
     <row r="1501">
-      <c r="L1501" s="37"/>
       <c r="M1501" s="37"/>
+      <c r="N1501" s="37"/>
     </row>
     <row r="1502">
-      <c r="L1502" s="37"/>
       <c r="M1502" s="37"/>
+      <c r="N1502" s="37"/>
     </row>
     <row r="1503">
-      <c r="L1503" s="37"/>
       <c r="M1503" s="37"/>
+      <c r="N1503" s="37"/>
     </row>
     <row r="1504">
-      <c r="L1504" s="37"/>
       <c r="M1504" s="37"/>
+      <c r="N1504" s="37"/>
     </row>
     <row r="1505">
-      <c r="L1505" s="37"/>
       <c r="M1505" s="37"/>
+      <c r="N1505" s="37"/>
     </row>
     <row r="1506">
-      <c r="L1506" s="37"/>
       <c r="M1506" s="37"/>
+      <c r="N1506" s="37"/>
     </row>
     <row r="1507">
-      <c r="L1507" s="37"/>
       <c r="M1507" s="37"/>
+      <c r="N1507" s="37"/>
     </row>
     <row r="1508">
-      <c r="L1508" s="37"/>
       <c r="M1508" s="37"/>
+      <c r="N1508" s="37"/>
     </row>
     <row r="1509">
-      <c r="L1509" s="37"/>
       <c r="M1509" s="37"/>
+      <c r="N1509" s="37"/>
     </row>
     <row r="1510">
-      <c r="L1510" s="37"/>
       <c r="M1510" s="37"/>
+      <c r="N1510" s="37"/>
     </row>
     <row r="1511">
-      <c r="L1511" s="37"/>
       <c r="M1511" s="37"/>
+      <c r="N1511" s="37"/>
     </row>
     <row r="1512">
-      <c r="L1512" s="37"/>
       <c r="M1512" s="37"/>
+      <c r="N1512" s="37"/>
     </row>
     <row r="1513">
-      <c r="L1513" s="37"/>
       <c r="M1513" s="37"/>
+      <c r="N1513" s="37"/>
     </row>
     <row r="1514">
-      <c r="L1514" s="37"/>
       <c r="M1514" s="37"/>
+      <c r="N1514" s="37"/>
     </row>
     <row r="1515">
-      <c r="L1515" s="37"/>
       <c r="M1515" s="37"/>
+      <c r="N1515" s="37"/>
     </row>
     <row r="1516">
-      <c r="L1516" s="37"/>
       <c r="M1516" s="37"/>
+      <c r="N1516" s="37"/>
     </row>
     <row r="1517">
-      <c r="L1517" s="37"/>
       <c r="M1517" s="37"/>
+      <c r="N1517" s="37"/>
     </row>
     <row r="1518">
-      <c r="L1518" s="37"/>
       <c r="M1518" s="37"/>
+      <c r="N1518" s="37"/>
     </row>
     <row r="1519">
-      <c r="L1519" s="37"/>
       <c r="M1519" s="37"/>
+      <c r="N1519" s="37"/>
     </row>
     <row r="1520">
-      <c r="L1520" s="37"/>
       <c r="M1520" s="37"/>
+      <c r="N1520" s="37"/>
     </row>
     <row r="1521">
-      <c r="L1521" s="37"/>
       <c r="M1521" s="37"/>
+      <c r="N1521" s="37"/>
     </row>
     <row r="1522">
-      <c r="L1522" s="37"/>
       <c r="M1522" s="37"/>
+      <c r="N1522" s="37"/>
     </row>
     <row r="1523">
-      <c r="L1523" s="37"/>
       <c r="M1523" s="37"/>
+      <c r="N1523" s="37"/>
     </row>
     <row r="1524">
-      <c r="L1524" s="37"/>
       <c r="M1524" s="37"/>
+      <c r="N1524" s="37"/>
     </row>
     <row r="1525">
-      <c r="L1525" s="37"/>
       <c r="M1525" s="37"/>
+      <c r="N1525" s="37"/>
     </row>
     <row r="1526">
-      <c r="L1526" s="37"/>
       <c r="M1526" s="37"/>
+      <c r="N1526" s="37"/>
     </row>
     <row r="1527">
-      <c r="L1527" s="37"/>
       <c r="M1527" s="37"/>
+      <c r="N1527" s="37"/>
     </row>
     <row r="1528">
-      <c r="L1528" s="37"/>
       <c r="M1528" s="37"/>
+      <c r="N1528" s="37"/>
     </row>
     <row r="1529">
-      <c r="L1529" s="37"/>
       <c r="M1529" s="37"/>
+      <c r="N1529" s="37"/>
     </row>
     <row r="1530">
-      <c r="L1530" s="37"/>
       <c r="M1530" s="37"/>
+      <c r="N1530" s="37"/>
     </row>
     <row r="1531">
-      <c r="L1531" s="37"/>
       <c r="M1531" s="37"/>
+      <c r="N1531" s="37"/>
     </row>
     <row r="1532">
-      <c r="L1532" s="37"/>
       <c r="M1532" s="37"/>
+      <c r="N1532" s="37"/>
     </row>
     <row r="1533">
-      <c r="L1533" s="37"/>
       <c r="M1533" s="37"/>
+      <c r="N1533" s="37"/>
     </row>
     <row r="1534">
-      <c r="L1534" s="37"/>
       <c r="M1534" s="37"/>
+      <c r="N1534" s="37"/>
     </row>
     <row r="1535">
-      <c r="L1535" s="37"/>
       <c r="M1535" s="37"/>
+      <c r="N1535" s="37"/>
     </row>
     <row r="1536">
-      <c r="L1536" s="37"/>
       <c r="M1536" s="37"/>
+      <c r="N1536" s="37"/>
     </row>
     <row r="1537">
-      <c r="L1537" s="37"/>
       <c r="M1537" s="37"/>
+      <c r="N1537" s="37"/>
     </row>
     <row r="1538">
-      <c r="L1538" s="37"/>
       <c r="M1538" s="37"/>
+      <c r="N1538" s="37"/>
     </row>
     <row r="1539">
-      <c r="L1539" s="37"/>
       <c r="M1539" s="37"/>
+      <c r="N1539" s="37"/>
     </row>
     <row r="1540">
-      <c r="L1540" s="37"/>
       <c r="M1540" s="37"/>
+      <c r="N1540" s="37"/>
     </row>
     <row r="1541">
-      <c r="L1541" s="37"/>
       <c r="M1541" s="37"/>
+      <c r="N1541" s="37"/>
     </row>
     <row r="1542">
-      <c r="L1542" s="37"/>
       <c r="M1542" s="37"/>
+      <c r="N1542" s="37"/>
     </row>
     <row r="1543">
-      <c r="L1543" s="37"/>
       <c r="M1543" s="37"/>
+      <c r="N1543" s="37"/>
     </row>
     <row r="1544">
-      <c r="L1544" s="37"/>
       <c r="M1544" s="37"/>
+      <c r="N1544" s="37"/>
     </row>
     <row r="1545">
-      <c r="L1545" s="37"/>
       <c r="M1545" s="37"/>
+      <c r="N1545" s="37"/>
     </row>
     <row r="1546">
-      <c r="L1546" s="37"/>
       <c r="M1546" s="37"/>
+      <c r="N1546" s="37"/>
     </row>
     <row r="1547">
-      <c r="L1547" s="37"/>
       <c r="M1547" s="37"/>
+      <c r="N1547" s="37"/>
     </row>
     <row r="1548">
-      <c r="L1548" s="37"/>
       <c r="M1548" s="37"/>
+      <c r="N1548" s="37"/>
     </row>
     <row r="1549">
-      <c r="L1549" s="37"/>
       <c r="M1549" s="37"/>
+      <c r="N1549" s="37"/>
     </row>
     <row r="1550">
-      <c r="L1550" s="37"/>
       <c r="M1550" s="37"/>
+      <c r="N1550" s="37"/>
     </row>
     <row r="1551">
-      <c r="L1551" s="37"/>
       <c r="M1551" s="37"/>
+      <c r="N1551" s="37"/>
     </row>
     <row r="1552">
-      <c r="L1552" s="37"/>
       <c r="M1552" s="37"/>
+      <c r="N1552" s="37"/>
     </row>
     <row r="1553">
-      <c r="L1553" s="37"/>
       <c r="M1553" s="37"/>
+      <c r="N1553" s="37"/>
     </row>
     <row r="1554">
-      <c r="L1554" s="37"/>
       <c r="M1554" s="37"/>
+      <c r="N1554" s="37"/>
     </row>
     <row r="1555">
-      <c r="L1555" s="37"/>
       <c r="M1555" s="37"/>
+      <c r="N1555" s="37"/>
     </row>
     <row r="1556">
-      <c r="L1556" s="37"/>
       <c r="M1556" s="37"/>
+      <c r="N1556" s="37"/>
     </row>
     <row r="1557">
-      <c r="L1557" s="37"/>
       <c r="M1557" s="37"/>
+      <c r="N1557" s="37"/>
     </row>
     <row r="1558">
-      <c r="L1558" s="37"/>
       <c r="M1558" s="37"/>
+      <c r="N1558" s="37"/>
     </row>
     <row r="1559">
-      <c r="L1559" s="37"/>
       <c r="M1559" s="37"/>
+      <c r="N1559" s="37"/>
     </row>
     <row r="1560">
-      <c r="L1560" s="37"/>
       <c r="M1560" s="37"/>
+      <c r="N1560" s="37"/>
     </row>
     <row r="1561">
-      <c r="L1561" s="37"/>
       <c r="M1561" s="37"/>
+      <c r="N1561" s="37"/>
     </row>
     <row r="1562">
-      <c r="L1562" s="37"/>
       <c r="M1562" s="37"/>
+      <c r="N1562" s="37"/>
     </row>
     <row r="1563">
-      <c r="L1563" s="37"/>
       <c r="M1563" s="37"/>
+      <c r="N1563" s="37"/>
     </row>
     <row r="1564">
-      <c r="L1564" s="37"/>
       <c r="M1564" s="37"/>
+      <c r="N1564" s="37"/>
     </row>
     <row r="1565">
-      <c r="L1565" s="37"/>
       <c r="M1565" s="37"/>
+      <c r="N1565" s="37"/>
     </row>
     <row r="1566">
-      <c r="L1566" s="37"/>
       <c r="M1566" s="37"/>
+      <c r="N1566" s="37"/>
     </row>
     <row r="1567">
-      <c r="L1567" s="37"/>
       <c r="M1567" s="37"/>
+      <c r="N1567" s="37"/>
     </row>
     <row r="1568">
-      <c r="L1568" s="37"/>
       <c r="M1568" s="37"/>
+      <c r="N1568" s="37"/>
     </row>
     <row r="1569">
-      <c r="L1569" s="37"/>
       <c r="M1569" s="37"/>
+      <c r="N1569" s="37"/>
     </row>
     <row r="1570">
-      <c r="L1570" s="37"/>
       <c r="M1570" s="37"/>
+      <c r="N1570" s="37"/>
     </row>
     <row r="1571">
-      <c r="L1571" s="37"/>
       <c r="M1571" s="37"/>
+      <c r="N1571" s="37"/>
     </row>
     <row r="1572">
-      <c r="L1572" s="37"/>
       <c r="M1572" s="37"/>
+      <c r="N1572" s="37"/>
     </row>
     <row r="1573">
-      <c r="L1573" s="37"/>
       <c r="M1573" s="37"/>
+      <c r="N1573" s="37"/>
     </row>
     <row r="1574">
-      <c r="L1574" s="37"/>
       <c r="M1574" s="37"/>
+      <c r="N1574" s="37"/>
     </row>
     <row r="1575">
-      <c r="L1575" s="37"/>
       <c r="M1575" s="37"/>
+      <c r="N1575" s="37"/>
     </row>
     <row r="1576">
-      <c r="L1576" s="37"/>
       <c r="M1576" s="37"/>
+      <c r="N1576" s="37"/>
     </row>
     <row r="1577">
-      <c r="L1577" s="37"/>
       <c r="M1577" s="37"/>
+      <c r="N1577" s="37"/>
     </row>
     <row r="1578">
-      <c r="L1578" s="37"/>
       <c r="M1578" s="37"/>
+      <c r="N1578" s="37"/>
     </row>
     <row r="1579">
-      <c r="L1579" s="37"/>
       <c r="M1579" s="37"/>
+      <c r="N1579" s="37"/>
     </row>
     <row r="1580">
-      <c r="L1580" s="37"/>
       <c r="M1580" s="37"/>
+      <c r="N1580" s="37"/>
     </row>
     <row r="1581">
-      <c r="L1581" s="37"/>
       <c r="M1581" s="37"/>
+      <c r="N1581" s="37"/>
     </row>
     <row r="1582">
-      <c r="L1582" s="37"/>
       <c r="M1582" s="37"/>
+      <c r="N1582" s="37"/>
     </row>
     <row r="1583">
-      <c r="L1583" s="37"/>
       <c r="M1583" s="37"/>
+      <c r="N1583" s="37"/>
     </row>
     <row r="1584">
-      <c r="L1584" s="37"/>
       <c r="M1584" s="37"/>
+      <c r="N1584" s="37"/>
     </row>
     <row r="1585">
-      <c r="L1585" s="37"/>
       <c r="M1585" s="37"/>
+      <c r="N1585" s="37"/>
     </row>
     <row r="1586">
-      <c r="L1586" s="37"/>
       <c r="M1586" s="37"/>
+      <c r="N1586" s="37"/>
     </row>
     <row r="1587">
-      <c r="L1587" s="37"/>
       <c r="M1587" s="37"/>
+      <c r="N1587" s="37"/>
     </row>
     <row r="1588">
-      <c r="L1588" s="37"/>
       <c r="M1588" s="37"/>
+      <c r="N1588" s="37"/>
     </row>
     <row r="1589">
-      <c r="L1589" s="37"/>
       <c r="M1589" s="37"/>
+      <c r="N1589" s="37"/>
     </row>
     <row r="1590">
-      <c r="L1590" s="37"/>
       <c r="M1590" s="37"/>
+      <c r="N1590" s="37"/>
     </row>
     <row r="1591">
-      <c r="L1591" s="37"/>
       <c r="M1591" s="37"/>
+      <c r="N1591" s="37"/>
     </row>
     <row r="1592">
-      <c r="L1592" s="37"/>
       <c r="M1592" s="37"/>
+      <c r="N1592" s="37"/>
     </row>
     <row r="1593">
-      <c r="L1593" s="37"/>
       <c r="M1593" s="37"/>
+      <c r="N1593" s="37"/>
     </row>
     <row r="1594">
-      <c r="L1594" s="37"/>
       <c r="M1594" s="37"/>
+      <c r="N1594" s="37"/>
     </row>
     <row r="1595">
-      <c r="L1595" s="37"/>
       <c r="M1595" s="37"/>
+      <c r="N1595" s="37"/>
     </row>
   </sheetData>
-  <autoFilter ref="$A$1:$M$8"/>
-  <conditionalFormatting sqref="M2 M4:M8">
+  <autoFilter ref="$A$1:$N$8"/>
+  <conditionalFormatting sqref="N2 N4:N8">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -8745,7 +8767,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G4:I8">
+  <conditionalFormatting sqref="G4:J8">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -8755,7 +8777,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J4:J8">
+  <conditionalFormatting sqref="K4:K8">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -8796,7 +8818,7 @@
         <v>48.0</v>
       </c>
       <c r="B2" s="41" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" s="36">
         <v>45679.0</v>
@@ -8805,7 +8827,7 @@
         <v>395.0</v>
       </c>
       <c r="E2" s="42" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F2" s="42">
         <v>57.9999999999999</v>
@@ -8839,7 +8861,7 @@
         <v>55.0</v>
       </c>
       <c r="B3" s="41" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" s="36">
         <v>45679.0</v>
@@ -8848,7 +8870,7 @@
         <v>724.0</v>
       </c>
       <c r="E3" s="42" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" s="43">
         <v>61.0</v>
@@ -8882,7 +8904,7 @@
         <v>59.0</v>
       </c>
       <c r="B4" s="42" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" s="36">
         <v>45680.0</v>
@@ -8891,7 +8913,7 @@
         <v>1051.0</v>
       </c>
       <c r="E4" s="42" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F4" s="43">
         <v>62.0</v>
@@ -8925,7 +8947,7 @@
         <v>77.0</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" s="13">
         <v>45677.0</v>
@@ -8934,7 +8956,7 @@
         <v>931.0</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" s="42">
         <v>60.0</v>
@@ -8970,7 +8992,7 @@
         <v>148.0</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" s="13">
         <v>45677.0</v>
@@ -8979,7 +9001,7 @@
         <v>112.0</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L6" s="47">
         <v>127.26</v>
@@ -9046,32 +9068,32 @@
     </row>
     <row r="11">
       <c r="E11" s="50" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L11" s="42" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M11" s="44" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N11" s="51" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O11" s="37"/>
       <c r="P11" s="37"/>
     </row>
     <row r="12">
       <c r="E12" s="50" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L12" s="42" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M12" s="44" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N12" s="51" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O12" s="37"/>
       <c r="P12" s="37"/>
@@ -9112,7 +9134,7 @@
         <v>48.0</v>
       </c>
       <c r="B16" s="53" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C16" s="36">
         <v>45679.0</v>
@@ -9121,7 +9143,7 @@
         <v>1363.0</v>
       </c>
       <c r="E16" s="42" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F16" s="42">
         <v>57.5213675213675</v>
@@ -9155,7 +9177,7 @@
         <v>55.0</v>
       </c>
       <c r="B17" s="41" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C17" s="36">
         <v>45679.0</v>
@@ -9164,7 +9186,7 @@
         <v>724.0</v>
       </c>
       <c r="E17" s="42" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F17" s="43">
         <v>57.7626974489822</v>
@@ -9198,7 +9220,7 @@
         <v>59.0</v>
       </c>
       <c r="B18" s="42" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C18" s="36">
         <v>45680.0</v>
@@ -9207,7 +9229,7 @@
         <v>935.0</v>
       </c>
       <c r="E18" s="42" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F18" s="43">
         <v>61.8147668934429</v>
@@ -9239,7 +9261,7 @@
         <v>77.0</v>
       </c>
       <c r="B19" s="54" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C19" s="36">
         <v>45677.0</v>
@@ -9248,7 +9270,7 @@
         <v>47.0</v>
       </c>
       <c r="E19" s="42" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F19" s="43">
         <v>60.7563651137594</v>
@@ -9282,7 +9304,7 @@
         <v>148.0</v>
       </c>
       <c r="B20" s="42" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C20" s="36">
         <v>45677.0</v>
@@ -9291,7 +9313,7 @@
         <v>1475.0</v>
       </c>
       <c r="E20" s="42" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F20" s="43">
         <v>56.4173196363555</v>
@@ -9327,49 +9349,49 @@
     </row>
     <row r="24">
       <c r="C24" s="38" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25">
       <c r="C25" s="47" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26">
       <c r="C26" s="55" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27">
       <c r="C27" s="56" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28">
       <c r="C28" s="54" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30">
       <c r="C30" s="57" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31">
       <c r="C31" s="38" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L31" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q31" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="Z31" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="Q31" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z31" s="38" t="s">
-        <v>27</v>
-      </c>
       <c r="AH31" s="38" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="32">
@@ -11349,7 +11371,7 @@
     </row>
     <row r="63">
       <c r="C63" s="38" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="65">
@@ -11369,25 +11391,25 @@
         <v>4</v>
       </c>
       <c r="H65" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I65" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J65" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K65" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L65" s="5" t="s">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="M65" s="67" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N65" s="68" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="66">
@@ -11395,7 +11417,7 @@
         <v>6.0</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E66" s="69"/>
       <c r="F66" s="70"/>
@@ -11413,7 +11435,7 @@
         <v>167.0</v>
       </c>
       <c r="D67" s="23" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E67" s="13">
         <v>45570.0</v>
@@ -11433,7 +11455,7 @@
         <v>48.0</v>
       </c>
       <c r="D68" s="30" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E68" s="13">
         <v>45679.0</v>
@@ -11442,7 +11464,7 @@
         <v>395.0</v>
       </c>
       <c r="G68" s="15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H68" s="17">
         <v>57.2457163045398</v>
@@ -11477,7 +11499,7 @@
         <v>55.0</v>
       </c>
       <c r="D69" s="30" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E69" s="13">
         <v>45679.0</v>
@@ -11486,7 +11508,7 @@
         <v>724.0</v>
       </c>
       <c r="G69" s="15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H69" s="19">
         <v>57.7626974489822</v>
@@ -11522,7 +11544,7 @@
         <v>59.0</v>
       </c>
       <c r="D70" s="23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E70" s="13">
         <v>45680.0</v>
@@ -11531,7 +11553,7 @@
         <v>935.0</v>
       </c>
       <c r="G70" s="15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H70" s="19">
         <v>61.8147668934429</v>
@@ -11567,7 +11589,7 @@
         <v>77.0</v>
       </c>
       <c r="D71" s="23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E71" s="13">
         <v>45677.0</v>
@@ -11576,7 +11598,7 @@
         <v>931.0</v>
       </c>
       <c r="G71" s="15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H71" s="19">
         <v>59.8048011309572</v>
@@ -11611,7 +11633,7 @@
         <v>148.0</v>
       </c>
       <c r="D72" s="23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E72" s="13">
         <v>45677.0</v>
@@ -11620,7 +11642,7 @@
         <v>112.0</v>
       </c>
       <c r="G72" s="15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H72" s="19">
         <v>56.318574213311</v>
@@ -11672,35 +11694,35 @@
         <v>4</v>
       </c>
       <c r="H77" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I77" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J77" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K77" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L77" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M77" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N77" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O77" s="5"/>
       <c r="P77" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q77" s="67" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R77" s="68" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="78">
@@ -11708,7 +11730,7 @@
         <v>6.0</v>
       </c>
       <c r="D78" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E78" s="69"/>
       <c r="F78" s="70"/>
@@ -11730,7 +11752,7 @@
         <v>167.0</v>
       </c>
       <c r="D79" s="23" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E79" s="13">
         <v>45570.0</v>
@@ -11754,7 +11776,7 @@
         <v>48.0</v>
       </c>
       <c r="D80" s="30" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E80" s="13">
         <v>45679.0</v>
@@ -11763,7 +11785,7 @@
         <v>395.0</v>
       </c>
       <c r="G80" s="15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H80" s="17">
         <v>57.2457163045398</v>
@@ -11809,7 +11831,7 @@
         <v>55.0</v>
       </c>
       <c r="D81" s="30" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E81" s="13">
         <v>45679.0</v>
@@ -11818,7 +11840,7 @@
         <v>724.0</v>
       </c>
       <c r="G81" s="15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H81" s="19">
         <v>57.7626974489822</v>
@@ -11864,7 +11886,7 @@
         <v>59.0</v>
       </c>
       <c r="D82" s="23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E82" s="13">
         <v>45680.0</v>
@@ -11873,7 +11895,7 @@
         <v>935.0</v>
       </c>
       <c r="G82" s="15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H82" s="19">
         <v>61.8147668934429</v>
@@ -11919,7 +11941,7 @@
         <v>77.0</v>
       </c>
       <c r="D83" s="23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E83" s="13">
         <v>45677.0</v>
@@ -11928,7 +11950,7 @@
         <v>931.0</v>
       </c>
       <c r="G83" s="15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H83" s="19">
         <v>59.8048011309572</v>
@@ -11974,7 +11996,7 @@
         <v>148.0</v>
       </c>
       <c r="D84" s="23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E84" s="13">
         <v>45677.0</v>
@@ -11983,7 +12005,7 @@
         <v>112.0</v>
       </c>
       <c r="G84" s="15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H84" s="19">
         <v>56.318574213311</v>
@@ -12046,13 +12068,13 @@
         <v>4</v>
       </c>
       <c r="H96" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I96" s="5" t="s">
         <v>45</v>
       </c>
       <c r="J96" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K96" s="7" t="s">
         <v>46</v>
@@ -12064,28 +12086,28 @@
         <v>48</v>
       </c>
       <c r="N96" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O96" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="P96" s="67" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q96" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R96" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S96" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T96" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U96" s="68" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="97">
@@ -12093,7 +12115,7 @@
         <v>6.0</v>
       </c>
       <c r="D97" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E97" s="69"/>
       <c r="F97" s="70"/>
@@ -12118,7 +12140,7 @@
         <v>167.0</v>
       </c>
       <c r="D98" s="23" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E98" s="13">
         <v>45570.0</v>
@@ -12145,7 +12167,7 @@
         <v>48.0</v>
       </c>
       <c r="D99" s="30" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E99" s="13">
         <v>45679.0</v>
@@ -12154,7 +12176,7 @@
         <v>395.0</v>
       </c>
       <c r="G99" s="15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H99" s="19">
         <v>57.9999999999999</v>
@@ -12206,7 +12228,7 @@
         <v>55.0</v>
       </c>
       <c r="D100" s="73" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E100" s="13">
         <v>45679.0</v>
@@ -12215,7 +12237,7 @@
         <v>724.0</v>
       </c>
       <c r="G100" s="15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H100" s="19">
         <v>61.0</v>
@@ -12267,7 +12289,7 @@
         <v>59.0</v>
       </c>
       <c r="D101" s="72" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E101" s="13">
         <v>45680.0</v>
@@ -12276,7 +12298,7 @@
         <v>935.0</v>
       </c>
       <c r="G101" s="15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H101" s="19">
         <v>64.0</v>
@@ -12328,7 +12350,7 @@
         <v>77.0</v>
       </c>
       <c r="D102" s="72" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E102" s="13">
         <v>45677.0</v>
@@ -12337,7 +12359,7 @@
         <v>1623.0</v>
       </c>
       <c r="G102" s="15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H102" s="19">
         <v>60.0</v>
@@ -12389,7 +12411,7 @@
         <v>148.0</v>
       </c>
       <c r="D103" s="72" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E103" s="13">
         <v>45677.0</v>
@@ -12398,7 +12420,7 @@
         <v>814.0</v>
       </c>
       <c r="G103" s="15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H103" s="19">
         <v>56.0</v>
@@ -12544,7 +12566,7 @@
         <v>55</v>
       </c>
       <c r="I2" s="82" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J2" s="80"/>
       <c r="K2" s="80" t="s">
@@ -12570,7 +12592,7 @@
     </row>
     <row r="3">
       <c r="A3" s="84" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B3" s="23">
         <v>343.0</v>
@@ -12618,7 +12640,7 @@
     </row>
     <row r="4">
       <c r="A4" s="84" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B4" s="23">
         <v>1127.0</v>
@@ -12669,7 +12691,7 @@
     </row>
     <row r="5">
       <c r="A5" s="84" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5" s="85">
         <v>1051.0</v>
@@ -12720,7 +12742,7 @@
     </row>
     <row r="6">
       <c r="A6" s="84" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B6" s="23">
         <v>622.0</v>
@@ -12768,7 +12790,7 @@
     </row>
     <row r="7">
       <c r="A7" s="84" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B7" s="23">
         <v>1447.0</v>
@@ -12840,7 +12862,7 @@
     <row r="11">
       <c r="A11" s="40"/>
       <c r="E11" s="30" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F11" s="15">
         <v>343.0</v>
@@ -12857,7 +12879,7 @@
     <row r="12">
       <c r="A12" s="31"/>
       <c r="E12" s="30" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F12" s="15">
         <v>724.0</v>
@@ -12873,7 +12895,7 @@
     <row r="13">
       <c r="A13" s="31"/>
       <c r="E13" s="23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F13" s="15">
         <v>1051.0</v>
@@ -12889,7 +12911,7 @@
     <row r="14">
       <c r="A14" s="31"/>
       <c r="E14" s="23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F14" s="15">
         <v>47.0</v>
@@ -12909,7 +12931,7 @@
       <c r="C15" s="31"/>
       <c r="D15" s="31"/>
       <c r="E15" s="23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F15" s="15">
         <v>1447.0</v>
@@ -12972,7 +12994,7 @@
     <row r="19">
       <c r="A19" s="43"/>
       <c r="E19" s="30" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F19" s="15">
         <v>663.0</v>
@@ -12986,7 +13008,7 @@
     </row>
     <row r="20">
       <c r="E20" s="30" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F20" s="15">
         <v>654.0</v>
@@ -12998,7 +13020,7 @@
     </row>
     <row r="21">
       <c r="E21" s="23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F21" s="15">
         <v>1051.0</v>
@@ -13009,7 +13031,7 @@
     </row>
     <row r="22">
       <c r="E22" s="23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F22" s="15">
         <v>622.0</v>
@@ -13021,7 +13043,7 @@
     </row>
     <row r="23">
       <c r="E23" s="23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F23" s="15">
         <v>1545.0</v>
@@ -13067,25 +13089,25 @@
         <v>5</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N32" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O32" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33">
@@ -13093,7 +13115,7 @@
         <v>6.0</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E33" s="13">
         <v>45685.0</v>
@@ -13102,7 +13124,7 @@
         <v>616.0</v>
       </c>
       <c r="G33" s="15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H33" s="16">
         <f>5.8410821479406*100</f>
@@ -13132,7 +13154,7 @@
         <v>167.0</v>
       </c>
       <c r="D34" s="23" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E34" s="13"/>
       <c r="F34" s="13"/>
@@ -13151,7 +13173,7 @@
         <v>48.0</v>
       </c>
       <c r="D35" s="73" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E35" s="13">
         <v>45679.0</v>
@@ -13160,7 +13182,7 @@
         <v>343.0</v>
       </c>
       <c r="G35" s="15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H35" s="16">
         <f>1.95083127981317*100</f>
@@ -13196,7 +13218,7 @@
         <v>55.0</v>
       </c>
       <c r="D36" s="73" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E36" s="13">
         <v>45679.0</v>
@@ -13205,7 +13227,7 @@
         <v>724.0</v>
       </c>
       <c r="G36" s="15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H36" s="16">
         <f>3.44623889518345*100</f>
@@ -13241,7 +13263,7 @@
         <v>59.0</v>
       </c>
       <c r="D37" s="72" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E37" s="13">
         <v>45680.0</v>
@@ -13250,7 +13272,7 @@
         <v>1051.0</v>
       </c>
       <c r="G37" s="15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H37" s="16">
         <f>5.03501136998037*100</f>
@@ -13286,7 +13308,7 @@
         <v>77.0</v>
       </c>
       <c r="D38" s="72" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E38" s="13">
         <v>45677.0</v>
@@ -13295,7 +13317,7 @@
         <v>281.0</v>
       </c>
       <c r="G38" s="15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H38" s="16">
         <f>2.76792853614368*100</f>
@@ -13331,7 +13353,7 @@
         <v>148.0</v>
       </c>
       <c r="D39" s="72" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E39" s="13">
         <v>45677.0</v>
@@ -13340,7 +13362,7 @@
         <v>1051.0</v>
       </c>
       <c r="G39" s="15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H39" s="16">
         <f>4.33116583093229*100</f>
@@ -13642,7 +13664,7 @@
         <v>0.85</v>
       </c>
       <c r="G18" s="90" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H18" s="42">
         <v>332.0</v>
@@ -13662,7 +13684,7 @@
         <v>0.81</v>
       </c>
       <c r="G19" s="90" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H19" s="42" t="s">
         <v>73</v>
@@ -13682,7 +13704,7 @@
         <v>0.89</v>
       </c>
       <c r="G20" s="90" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H20" s="42">
         <v>411.0</v>
@@ -13693,7 +13715,7 @@
     </row>
     <row r="21">
       <c r="G21" s="90" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H21" s="42" t="s">
         <v>76</v>
@@ -13704,7 +13726,7 @@
     </row>
     <row r="22">
       <c r="G22" s="90" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H22" s="42" t="s">
         <v>78</v>
@@ -13729,7 +13751,7 @@
     </row>
     <row r="26">
       <c r="B26" s="30" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C26" s="42">
         <v>332.0</v>
@@ -13739,7 +13761,7 @@
     </row>
     <row r="27">
       <c r="B27" s="30" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C27" s="42">
         <v>1288.0</v>
@@ -13749,7 +13771,7 @@
     </row>
     <row r="28">
       <c r="B28" s="23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C28" s="42">
         <v>411.0</v>
@@ -13759,7 +13781,7 @@
     </row>
     <row r="29">
       <c r="B29" s="23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C29" s="42">
         <v>1015.0</v>
@@ -13769,7 +13791,7 @@
     </row>
     <row r="30">
       <c r="B30" s="23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C30" s="42">
         <v>530.0</v>
@@ -13894,7 +13916,7 @@
     </row>
     <row r="4">
       <c r="B4" s="42" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C4" s="38" t="s">
         <v>96</v>
@@ -14051,7 +14073,7 @@
     </row>
     <row r="20">
       <c r="B20" s="38" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C20" s="38" t="s">
         <v>93</v>
@@ -14186,7 +14208,7 @@
     </row>
     <row r="37">
       <c r="B37" s="38" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C37" s="38" t="s">
         <v>93</v>
@@ -14335,7 +14357,7 @@
     </row>
     <row r="54">
       <c r="B54" s="38" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C54" s="38" t="s">
         <v>93</v>
@@ -14514,7 +14536,7 @@
     </row>
     <row r="71">
       <c r="B71" s="38" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C71" s="38" t="s">
         <v>93</v>
@@ -14970,8 +14992,8 @@
         <v>143</v>
       </c>
       <c r="C3" s="26">
-        <f>AVERAGE('Modelos actuales'!K4:K8)</f>
-        <v>15.33333333</v>
+        <f>AVERAGE('Modelos actuales'!L4:L8)</f>
+        <v>14</v>
       </c>
       <c r="L3" s="117"/>
       <c r="P3" s="117"/>
@@ -16237,7 +16259,7 @@
     </row>
     <row r="36">
       <c r="G36" s="38" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H36" s="130">
         <v>4.555000000000001</v>
@@ -16275,7 +16297,7 @@
         <v>3.991363636</v>
       </c>
       <c r="G37" s="38" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H37" s="130">
         <v>7.555294117647058</v>
@@ -16306,7 +16328,7 @@
     </row>
     <row r="38">
       <c r="G38" s="38" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H38" s="132">
         <v>2.21</v>
@@ -16344,7 +16366,7 @@
         <v>1.87</v>
       </c>
       <c r="G39" s="38" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H39" s="130">
         <v>9.938235294117648</v>
@@ -16382,7 +16404,7 @@
         <v>2.17</v>
       </c>
       <c r="G40" s="38" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H40" s="130">
         <v>3.3411111111111107</v>
@@ -16588,7 +16610,7 @@
         <v>2.49</v>
       </c>
       <c r="G47" s="100" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H47" s="135">
         <v>0.376453591155815</v>
@@ -16618,7 +16640,7 @@
         <v>2.75</v>
       </c>
       <c r="G48" s="100" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H48" s="135">
         <v>0.36678739680281</v>
@@ -16655,7 +16677,7 @@
         <v>1.83</v>
       </c>
       <c r="G49" s="100" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H49" s="135">
         <v>0.142870351877935</v>
@@ -16692,7 +16714,7 @@
         <v>1.83</v>
       </c>
       <c r="G50" s="100" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H50" s="135">
         <v>0.497437843674554</v>
@@ -16729,7 +16751,7 @@
         <v>7.09</v>
       </c>
       <c r="G51" s="100" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H51" s="135">
         <v>0.247446036291655</v>

--- a/data/df_best_models.xlsx
+++ b/data/df_best_models.xlsx
@@ -261,7 +261,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="335">
   <si>
     <t>id_country</t>
   </si>
@@ -1002,28 +1002,28 @@
     <t>Stake promedio</t>
   </si>
   <si>
-    <t>7.93</t>
+    <t>7.58</t>
   </si>
   <si>
-    <t>12.86</t>
+    <t>10.24</t>
   </si>
   <si>
-    <t>0.16</t>
+    <t>7.47</t>
   </si>
   <si>
-    <t>12.27</t>
+    <t>8.73</t>
   </si>
   <si>
-    <t>12.03</t>
+    <t>8.64</t>
   </si>
   <si>
-    <t>9.22</t>
+    <t>8.72</t>
   </si>
   <si>
-    <t>12.77</t>
+    <t>9.64</t>
   </si>
   <si>
-    <t>12.99</t>
+    <t>10.34</t>
   </si>
   <si>
     <t>Country</t>
@@ -1032,280 +1032,289 @@
     <t>Correl ROI y Expected ROI</t>
   </si>
   <si>
-    <t>1.00</t>
+    <t>1.39</t>
   </si>
   <si>
-    <t>14.07</t>
+    <t>13.42</t>
   </si>
   <si>
     <t>mean</t>
   </si>
   <si>
-    <t>11.48</t>
+    <t>8.68</t>
   </si>
   <si>
     <t>median</t>
   </si>
   <si>
-    <t>11.07</t>
+    <t>7.54</t>
   </si>
   <si>
     <t>p25</t>
   </si>
   <si>
-    <t>13.49</t>
+    <t>11.32</t>
   </si>
   <si>
     <t>p75</t>
   </si>
   <si>
-    <t>12.70</t>
+    <t>13.68</t>
   </si>
   <si>
-    <t>12.43</t>
+    <t>9.52</t>
   </si>
   <si>
-    <t>9.82</t>
+    <t>11.07</t>
   </si>
   <si>
-    <t>9.99</t>
+    <t>5.85</t>
   </si>
   <si>
-    <t>13.31</t>
+    <t>10.66</t>
   </si>
   <si>
-    <t>13.53</t>
+    <t>11.13</t>
   </si>
   <si>
-    <t>7.38</t>
+    <t>8.77</t>
   </si>
   <si>
     <t>Gracias a las nuevas métricas de G/P sin bank en test, me di cuenta de que:</t>
   </si>
   <si>
-    <t>10.44</t>
+    <t>6.66</t>
   </si>
   <si>
     <t>La rentabilidad en ITA está en el visitante y no en el empate como creía.</t>
   </si>
   <si>
-    <t>8.92</t>
+    <t>1.06</t>
   </si>
   <si>
     <t>La rentabilidad en ENG y GER está en el empate tal como creía.</t>
   </si>
   <si>
-    <t>10.28</t>
+    <t>8.01</t>
   </si>
   <si>
     <t>En SPA esta repartido aunque Empate saca una ventaja.</t>
   </si>
   <si>
-    <t>3.75</t>
+    <t>12.51</t>
   </si>
   <si>
     <t>En FRA, depende el modelo. A veces local, a veces, empate.</t>
   </si>
   <si>
+    <t>7.35</t>
+  </si>
+  <si>
     <t>Si en FRA empate no rinde, no tiene sentido exigirle una buena distrib en empate… → Tiene sentido pero al parecer si importa el empate puesto que el modelo que gana se basa en empate.</t>
   </si>
   <si>
-    <t>10.15</t>
+    <t>7.00</t>
   </si>
   <si>
-    <t>2.04</t>
+    <t>7.32</t>
   </si>
   <si>
-    <t>11.54</t>
+    <t>12.88</t>
   </si>
   <si>
-    <t>7.35</t>
+    <t>1.34</t>
   </si>
   <si>
-    <t>11.49</t>
+    <t>9.67</t>
   </si>
   <si>
-    <t>0.12</t>
+    <t>1.47</t>
   </si>
   <si>
-    <t>3.87</t>
+    <t>13.17</t>
   </si>
   <si>
-    <t>2.25</t>
+    <t>1.23</t>
   </si>
   <si>
-    <t>1.52</t>
+    <t>8.34</t>
   </si>
   <si>
-    <t>10.50</t>
+    <t>8.06</t>
   </si>
   <si>
-    <t>11.30</t>
+    <t>6.29</t>
   </si>
   <si>
-    <t>4.37</t>
+    <t>9.97</t>
   </si>
   <si>
-    <t>11.20</t>
+    <t>1.44</t>
   </si>
   <si>
-    <t>5.74</t>
+    <t>9.59</t>
   </si>
   <si>
-    <t>4.72</t>
+    <t>12.78</t>
   </si>
   <si>
-    <t>4.46</t>
+    <t>12.76</t>
   </si>
   <si>
-    <t>2.26</t>
+    <t>9.88</t>
   </si>
   <si>
-    <t>9.41</t>
+    <t>14.80</t>
   </si>
   <si>
-    <t>12.35</t>
+    <t>13.66</t>
   </si>
   <si>
-    <t>5.57</t>
+    <t>12.90</t>
   </si>
   <si>
-    <t>11.16</t>
+    <t>1.46</t>
   </si>
   <si>
-    <t>9.69</t>
+    <t>13.01</t>
   </si>
   <si>
-    <t>11.21</t>
+    <t>1.55</t>
   </si>
   <si>
-    <t>9.32</t>
+    <t>10.88</t>
   </si>
   <si>
-    <t>12.79</t>
+    <t>9.70</t>
   </si>
   <si>
-    <t>9.83</t>
+    <t>14.30</t>
   </si>
   <si>
-    <t>10.65</t>
+    <t>7.41</t>
+  </si>
+  <si>
+    <t>10.62</t>
+  </si>
+  <si>
+    <t>6.11</t>
+  </si>
+  <si>
+    <t>8.03</t>
+  </si>
+  <si>
+    <t>8.22</t>
+  </si>
+  <si>
+    <t>8.46</t>
+  </si>
+  <si>
+    <t>7.64</t>
+  </si>
+  <si>
+    <t>8.62</t>
+  </si>
+  <si>
+    <t>9.37</t>
+  </si>
+  <si>
+    <t>4.91</t>
+  </si>
+  <si>
+    <t>10.05</t>
+  </si>
+  <si>
+    <t>7.02</t>
+  </si>
+  <si>
+    <t>1.12</t>
+  </si>
+  <si>
+    <t>8.65</t>
+  </si>
+  <si>
+    <t>8.08</t>
+  </si>
+  <si>
+    <t>8.54</t>
+  </si>
+  <si>
+    <t>6.46</t>
   </si>
   <si>
     <t>8.98</t>
   </si>
   <si>
-    <t>8.23</t>
+    <t>3.85</t>
   </si>
   <si>
-    <t>8.74</t>
+    <t>6.24</t>
   </si>
   <si>
-    <t>9.23</t>
+    <t>1.17</t>
+  </si>
+  <si>
+    <t>6.13</t>
+  </si>
+  <si>
+    <t>6.44</t>
+  </si>
+  <si>
+    <t>4.99</t>
+  </si>
+  <si>
+    <t>4.52</t>
+  </si>
+  <si>
+    <t>8.48</t>
+  </si>
+  <si>
+    <t>6.39</t>
   </si>
   <si>
     <t>9.74</t>
   </si>
   <si>
-    <t>6.85</t>
+    <t>7.70</t>
   </si>
   <si>
-    <t>5.70</t>
+    <t>0.80</t>
   </si>
   <si>
-    <t>6.47</t>
+    <t>9.57</t>
   </si>
   <si>
-    <t>3.43</t>
+    <t>0.71</t>
   </si>
   <si>
-    <t>0.15</t>
+    <t>4.34</t>
   </si>
   <si>
-    <t>9.39</t>
+    <t>8.09</t>
   </si>
   <si>
-    <t>0.53</t>
+    <t>6.41</t>
   </si>
   <si>
-    <t>6.69</t>
+    <t>8.83</t>
   </si>
   <si>
-    <t>0.18</t>
+    <t>4.75</t>
   </si>
   <si>
-    <t>6.92</t>
+    <t>5.68</t>
   </si>
   <si>
-    <t>5.60</t>
+    <t>9.04</t>
   </si>
   <si>
-    <t>0.28</t>
+    <t>6.89</t>
   </si>
   <si>
-    <t>1.24</t>
+    <t>4.98</t>
   </si>
   <si>
-    <t>9.44</t>
-  </si>
-  <si>
-    <t>3.11</t>
-  </si>
-  <si>
-    <t>12.90</t>
-  </si>
-  <si>
-    <t>0.77</t>
-  </si>
-  <si>
-    <t>8.33</t>
-  </si>
-  <si>
-    <t>13.99</t>
-  </si>
-  <si>
-    <t>1.03</t>
-  </si>
-  <si>
-    <t>13.48</t>
-  </si>
-  <si>
-    <t>13.88</t>
-  </si>
-  <si>
-    <t>8.68</t>
-  </si>
-  <si>
-    <t>12.29</t>
-  </si>
-  <si>
-    <t>5.54</t>
-  </si>
-  <si>
-    <t>8.36</t>
-  </si>
-  <si>
-    <t>13.42</t>
-  </si>
-  <si>
-    <t>10.20</t>
-  </si>
-  <si>
-    <t>4.56</t>
-  </si>
-  <si>
-    <t>11.70</t>
-  </si>
-  <si>
-    <t>14.03</t>
-  </si>
-  <si>
-    <t>8.15</t>
-  </si>
-  <si>
-    <t>8.46</t>
-  </si>
-  <si>
-    <t>5.83</t>
+    <t>7.92</t>
   </si>
   <si>
     <t>RENTABILIDAD</t>
@@ -2570,14 +2579,14 @@
         <v>15</v>
       </c>
       <c r="M4" s="19">
-        <v>3464.10585075032</v>
+        <v>4127.12732043093</v>
       </c>
       <c r="N4" s="31">
         <f t="shared" ref="N4:N8" si="2">M4/F4</f>
-        <v>4.786722097</v>
+        <v>5.702889112</v>
       </c>
       <c r="O4" s="19">
-        <v>176.463140301466</v>
+        <v>83.2034043962739</v>
       </c>
     </row>
     <row r="5">
@@ -2642,13 +2651,13 @@
         <v>45693.0</v>
       </c>
       <c r="D6" s="15">
-        <v>111.0</v>
+        <v>732.0</v>
       </c>
       <c r="E6" s="15" t="s">
         <v>16</v>
       </c>
       <c r="F6" s="16">
-        <v>391.688847010193</v>
+        <v>420.892675935302</v>
       </c>
       <c r="G6" s="19">
         <v>40.0</v>
@@ -2671,14 +2680,14 @@
         <v>20</v>
       </c>
       <c r="M6" s="33">
-        <v>2797.81722805449</v>
+        <v>3454.61988359074</v>
       </c>
       <c r="N6" s="31">
         <f t="shared" si="2"/>
-        <v>7.142958625</v>
+        <v>8.207840338</v>
       </c>
       <c r="O6" s="19">
-        <v>74.8994892871103</v>
+        <v>523.181373773246</v>
       </c>
     </row>
     <row r="7">
@@ -2692,13 +2701,13 @@
         <v>45693.0</v>
       </c>
       <c r="D7" s="15">
-        <v>374.0</v>
+        <v>1270.0</v>
       </c>
       <c r="E7" s="15" t="s">
         <v>16</v>
       </c>
       <c r="F7" s="16">
-        <v>199.188159667619</v>
+        <v>196.200539201566</v>
       </c>
       <c r="G7" s="17">
         <v>30.0</v>
@@ -2721,14 +2730,14 @@
         <v>15</v>
       </c>
       <c r="M7" s="19">
-        <v>697.254148551371</v>
+        <v>659.351291524406</v>
       </c>
       <c r="N7" s="31">
         <f t="shared" si="2"/>
-        <v>3.500479897</v>
+        <v>3.360598774</v>
       </c>
       <c r="O7" s="19">
-        <v>839.09522760747</v>
+        <v>334.198925698403</v>
       </c>
     </row>
     <row r="8">
@@ -2742,16 +2751,16 @@
         <v>45693.0</v>
       </c>
       <c r="D8" s="15">
-        <v>499.0</v>
+        <v>508.0</v>
       </c>
       <c r="E8" s="15" t="s">
         <v>16</v>
       </c>
       <c r="F8" s="16">
-        <v>195.637194025755</v>
+        <v>411.423262848422</v>
       </c>
       <c r="G8" s="17">
-        <v>20.0</v>
+        <v>30.0</v>
       </c>
       <c r="H8" s="17">
         <v>30.0</v>
@@ -2768,17 +2777,17 @@
       </c>
       <c r="L8" s="27">
         <f>G8*'Data preparation'!$C$2</f>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M8" s="19">
-        <v>337.019635200559</v>
+        <v>1466.69528214825</v>
       </c>
       <c r="N8" s="31">
         <f t="shared" si="2"/>
-        <v>1.722676697</v>
+        <v>3.564930364</v>
       </c>
       <c r="O8" s="19">
-        <v>-52.9989623627844</v>
+        <v>-86.9543871782569</v>
       </c>
     </row>
     <row r="9" ht="20.25" customHeight="1">
@@ -16539,7 +16548,7 @@
       </c>
       <c r="C3" s="26">
         <f>AVERAGE('Modelos actuales'!L4:L8)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L3" s="118"/>
       <c r="P3" s="118"/>
@@ -17840,7 +17849,7 @@
       <c r="C37" s="41"/>
       <c r="D37" s="132">
         <f>AVERAGE(D39:D1775)</f>
-        <v>8.188556701</v>
+        <v>7.867938144</v>
       </c>
       <c r="G37" s="39" t="s">
         <v>38</v>
@@ -17909,7 +17918,7 @@
       </c>
       <c r="D39" s="124">
         <f t="shared" ref="D39:D221" si="17">IF(COUNTA(C39)=1,C39/1,"")</f>
-        <v>7.93</v>
+        <v>7.58</v>
       </c>
       <c r="G39" s="39" t="s">
         <v>30</v>
@@ -17947,7 +17956,7 @@
       </c>
       <c r="D40" s="124">
         <f t="shared" si="17"/>
-        <v>12.86</v>
+        <v>10.24</v>
       </c>
       <c r="G40" s="39" t="s">
         <v>26</v>
@@ -17985,7 +17994,7 @@
       </c>
       <c r="D41" s="124">
         <f t="shared" si="17"/>
-        <v>0.16</v>
+        <v>7.47</v>
       </c>
       <c r="P41" s="122">
         <v>0.0</v>
@@ -18017,7 +18026,7 @@
       </c>
       <c r="D42" s="124">
         <f t="shared" si="17"/>
-        <v>12.27</v>
+        <v>8.73</v>
       </c>
       <c r="P42" s="122">
         <v>2.0</v>
@@ -18049,7 +18058,7 @@
       </c>
       <c r="D43" s="124">
         <f t="shared" si="17"/>
-        <v>12.03</v>
+        <v>8.64</v>
       </c>
       <c r="P43" s="122">
         <v>1.0</v>
@@ -18081,7 +18090,7 @@
       </c>
       <c r="D44" s="124">
         <f t="shared" si="17"/>
-        <v>9.22</v>
+        <v>8.72</v>
       </c>
       <c r="P44" s="122">
         <v>2.0</v>
@@ -18111,7 +18120,7 @@
       </c>
       <c r="D45" s="124">
         <f t="shared" si="17"/>
-        <v>12.77</v>
+        <v>9.64</v>
       </c>
       <c r="P45" s="122">
         <v>1.0</v>
@@ -18129,7 +18138,7 @@
       </c>
       <c r="D46" s="124">
         <f t="shared" si="17"/>
-        <v>12.99</v>
+        <v>10.34</v>
       </c>
       <c r="G46" s="96" t="s">
         <v>219</v>
@@ -18153,7 +18162,7 @@
       </c>
       <c r="D47" s="124">
         <f t="shared" si="17"/>
-        <v>1</v>
+        <v>1.39</v>
       </c>
       <c r="G47" s="101" t="s">
         <v>39</v>
@@ -18183,7 +18192,7 @@
       </c>
       <c r="D48" s="124">
         <f t="shared" si="17"/>
-        <v>14.07</v>
+        <v>13.42</v>
       </c>
       <c r="G48" s="101" t="s">
         <v>38</v>
@@ -18220,7 +18229,7 @@
       </c>
       <c r="D49" s="124">
         <f t="shared" si="17"/>
-        <v>11.48</v>
+        <v>8.68</v>
       </c>
       <c r="G49" s="101" t="s">
         <v>29</v>
@@ -18257,7 +18266,7 @@
       </c>
       <c r="D50" s="124">
         <f t="shared" si="17"/>
-        <v>11.07</v>
+        <v>7.54</v>
       </c>
       <c r="G50" s="101" t="s">
         <v>30</v>
@@ -18294,7 +18303,7 @@
       </c>
       <c r="D51" s="124">
         <f t="shared" si="17"/>
-        <v>13.49</v>
+        <v>11.32</v>
       </c>
       <c r="G51" s="101" t="s">
         <v>26</v>
@@ -18331,7 +18340,7 @@
       </c>
       <c r="D52" s="124">
         <f t="shared" si="17"/>
-        <v>12.7</v>
+        <v>13.68</v>
       </c>
       <c r="P52" s="122">
         <v>0.0</v>
@@ -18355,7 +18364,7 @@
       </c>
       <c r="D53" s="124">
         <f t="shared" si="17"/>
-        <v>12.43</v>
+        <v>9.52</v>
       </c>
       <c r="P53" s="122">
         <v>0.0</v>
@@ -18379,7 +18388,7 @@
       </c>
       <c r="D54" s="124">
         <f t="shared" si="17"/>
-        <v>9.82</v>
+        <v>11.07</v>
       </c>
       <c r="P54" s="122">
         <v>2.0</v>
@@ -18403,7 +18412,7 @@
       </c>
       <c r="D55" s="124">
         <f t="shared" si="17"/>
-        <v>9.99</v>
+        <v>5.85</v>
       </c>
       <c r="P55" s="122">
         <v>0.0</v>
@@ -18427,7 +18436,7 @@
       </c>
       <c r="D56" s="124">
         <f t="shared" si="17"/>
-        <v>13.31</v>
+        <v>10.66</v>
       </c>
       <c r="P56" s="122">
         <v>0.0</v>
@@ -18451,7 +18460,7 @@
       </c>
       <c r="D57" s="124">
         <f t="shared" si="17"/>
-        <v>13.53</v>
+        <v>11.13</v>
       </c>
       <c r="P57" s="122">
         <v>2.0</v>
@@ -18475,7 +18484,7 @@
       </c>
       <c r="D58" s="124">
         <f t="shared" si="17"/>
-        <v>7.38</v>
+        <v>8.77</v>
       </c>
       <c r="G58" s="137" t="s">
         <v>237</v>
@@ -18503,7 +18512,7 @@
       </c>
       <c r="D59" s="124">
         <f t="shared" si="17"/>
-        <v>10.44</v>
+        <v>6.66</v>
       </c>
       <c r="G59" s="138"/>
       <c r="H59" s="139" t="s">
@@ -18531,7 +18540,7 @@
       </c>
       <c r="D60" s="124">
         <f t="shared" si="17"/>
-        <v>8.92</v>
+        <v>1.06</v>
       </c>
       <c r="G60" s="138"/>
       <c r="H60" s="139" t="s">
@@ -18559,7 +18568,7 @@
       </c>
       <c r="D61" s="124">
         <f t="shared" si="17"/>
-        <v>10.28</v>
+        <v>8.01</v>
       </c>
       <c r="G61" s="138"/>
       <c r="H61" s="139" t="s">
@@ -18587,7 +18596,7 @@
       </c>
       <c r="D62" s="124">
         <f t="shared" si="17"/>
-        <v>3.75</v>
+        <v>12.51</v>
       </c>
       <c r="G62" s="138"/>
       <c r="H62" s="139" t="s">
@@ -18611,15 +18620,15 @@
     </row>
     <row r="63">
       <c r="C63" s="135" t="s">
-        <v>216</v>
+        <v>246</v>
       </c>
       <c r="D63" s="124">
         <f t="shared" si="17"/>
-        <v>9.22</v>
+        <v>7.35</v>
       </c>
       <c r="G63" s="138"/>
       <c r="H63" s="139" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P63" s="122">
         <v>0.0</v>
@@ -18633,11 +18642,11 @@
     </row>
     <row r="64">
       <c r="C64" s="135" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="D64" s="124">
         <f t="shared" si="17"/>
-        <v>10.15</v>
+        <v>6.66</v>
       </c>
       <c r="P64" s="122">
         <v>1.0</v>
@@ -18655,7 +18664,7 @@
       </c>
       <c r="D65" s="124">
         <f t="shared" si="17"/>
-        <v>2.04</v>
+        <v>7</v>
       </c>
       <c r="P65" s="122">
         <v>2.0</v>
@@ -18673,7 +18682,7 @@
       </c>
       <c r="D66" s="124">
         <f t="shared" si="17"/>
-        <v>11.54</v>
+        <v>7.32</v>
       </c>
       <c r="P66" s="122">
         <v>0.0</v>
@@ -18691,7 +18700,7 @@
       </c>
       <c r="D67" s="124">
         <f t="shared" si="17"/>
-        <v>7.35</v>
+        <v>12.88</v>
       </c>
       <c r="P67" s="122">
         <v>0.0</v>
@@ -18705,11 +18714,11 @@
     </row>
     <row r="68">
       <c r="C68" s="135" t="s">
-        <v>201</v>
+        <v>251</v>
       </c>
       <c r="D68" s="124">
         <f t="shared" si="17"/>
-        <v>4.73</v>
+        <v>1.34</v>
       </c>
       <c r="P68" s="122">
         <v>1.0</v>
@@ -18723,11 +18732,11 @@
     </row>
     <row r="69">
       <c r="C69" s="135" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D69" s="124">
         <f t="shared" si="17"/>
-        <v>11.49</v>
+        <v>9.67</v>
       </c>
       <c r="P69" s="122">
         <v>2.0</v>
@@ -18741,11 +18750,11 @@
     </row>
     <row r="70">
       <c r="C70" s="135" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D70" s="124">
         <f t="shared" si="17"/>
-        <v>0.12</v>
+        <v>1.47</v>
       </c>
       <c r="P70" s="122">
         <v>1.0</v>
@@ -18759,11 +18768,11 @@
     </row>
     <row r="71">
       <c r="C71" s="135" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D71" s="124">
         <f t="shared" si="17"/>
-        <v>3.87</v>
+        <v>13.17</v>
       </c>
       <c r="F71" s="140"/>
       <c r="P71" s="122">
@@ -18778,11 +18787,11 @@
     </row>
     <row r="72">
       <c r="C72" s="135" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D72" s="124">
         <f t="shared" si="17"/>
-        <v>2.25</v>
+        <v>1.23</v>
       </c>
       <c r="P72" s="122">
         <v>0.0</v>
@@ -18796,11 +18805,11 @@
     </row>
     <row r="73">
       <c r="C73" s="135" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D73" s="124">
         <f t="shared" si="17"/>
-        <v>1.52</v>
+        <v>8.34</v>
       </c>
       <c r="P73" s="122">
         <v>1.0</v>
@@ -18814,11 +18823,11 @@
     </row>
     <row r="74">
       <c r="C74" s="135" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D74" s="124">
         <f t="shared" si="17"/>
-        <v>10.5</v>
+        <v>8.06</v>
       </c>
       <c r="P74" s="122">
         <v>0.0</v>
@@ -18832,11 +18841,11 @@
     </row>
     <row r="75">
       <c r="C75" s="135" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D75" s="124">
         <f t="shared" si="17"/>
-        <v>11.3</v>
+        <v>6.29</v>
       </c>
       <c r="P75" s="122">
         <v>1.0</v>
@@ -18850,11 +18859,11 @@
     </row>
     <row r="76">
       <c r="C76" s="135" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D76" s="124">
         <f t="shared" si="17"/>
-        <v>4.37</v>
+        <v>9.97</v>
       </c>
       <c r="P76" s="122">
         <v>0.0</v>
@@ -18868,11 +18877,11 @@
     </row>
     <row r="77">
       <c r="C77" s="135" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" s="124">
         <f t="shared" si="17"/>
-        <v>11.2</v>
+        <v>1.44</v>
       </c>
       <c r="P77" s="122">
         <v>0.0</v>
@@ -18886,11 +18895,11 @@
     </row>
     <row r="78">
       <c r="C78" s="135" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D78" s="124">
         <f t="shared" si="17"/>
-        <v>5.74</v>
+        <v>9.59</v>
       </c>
       <c r="P78" s="122">
         <v>1.0</v>
@@ -18904,11 +18913,11 @@
     </row>
     <row r="79">
       <c r="C79" s="135" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D79" s="124">
         <f t="shared" si="17"/>
-        <v>4.72</v>
+        <v>12.78</v>
       </c>
       <c r="P79" s="122">
         <v>2.0</v>
@@ -18922,11 +18931,11 @@
     </row>
     <row r="80">
       <c r="C80" s="135" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D80" s="124">
         <f t="shared" si="17"/>
-        <v>4.46</v>
+        <v>12.76</v>
       </c>
       <c r="P80" s="122">
         <v>1.0</v>
@@ -18940,11 +18949,11 @@
     </row>
     <row r="81">
       <c r="C81" s="135" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D81" s="124">
         <f t="shared" si="17"/>
-        <v>2.26</v>
+        <v>9.88</v>
       </c>
       <c r="P81" s="122">
         <v>2.0</v>
@@ -18958,11 +18967,11 @@
     </row>
     <row r="82">
       <c r="C82" s="135" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D82" s="124">
         <f t="shared" si="17"/>
-        <v>9.41</v>
+        <v>14.8</v>
       </c>
       <c r="P82" s="122">
         <v>1.0</v>
@@ -18976,11 +18985,11 @@
     </row>
     <row r="83">
       <c r="C83" s="135" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D83" s="124">
         <f t="shared" si="17"/>
-        <v>12.35</v>
+        <v>13.66</v>
       </c>
       <c r="P83" s="122">
         <v>0.0</v>
@@ -18994,11 +19003,11 @@
     </row>
     <row r="84">
       <c r="C84" s="135" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D84" s="124">
         <f t="shared" si="17"/>
-        <v>5.57</v>
+        <v>12.9</v>
       </c>
       <c r="P84" s="122">
         <v>1.0</v>
@@ -19012,11 +19021,11 @@
     </row>
     <row r="85">
       <c r="C85" s="135" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D85" s="124">
         <f t="shared" si="17"/>
-        <v>11.16</v>
+        <v>1.46</v>
       </c>
       <c r="P85" s="122">
         <v>0.0</v>
@@ -19030,11 +19039,11 @@
     </row>
     <row r="86">
       <c r="C86" s="135" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D86" s="124">
         <f t="shared" si="17"/>
-        <v>9.69</v>
+        <v>13.01</v>
       </c>
       <c r="P86" s="122">
         <v>0.0</v>
@@ -19048,11 +19057,11 @@
     </row>
     <row r="87">
       <c r="C87" s="135" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D87" s="124">
         <f t="shared" si="17"/>
-        <v>11.21</v>
+        <v>1.55</v>
       </c>
       <c r="P87" s="122">
         <v>1.0</v>
@@ -19066,11 +19075,11 @@
     </row>
     <row r="88">
       <c r="C88" s="135" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D88" s="124">
         <f t="shared" si="17"/>
-        <v>9.32</v>
+        <v>10.88</v>
       </c>
       <c r="P88" s="122">
         <v>2.0</v>
@@ -19084,11 +19093,11 @@
     </row>
     <row r="89">
       <c r="C89" s="135" t="s">
-        <v>249</v>
+        <v>272</v>
       </c>
       <c r="D89" s="124">
         <f t="shared" si="17"/>
-        <v>11.54</v>
+        <v>9.7</v>
       </c>
       <c r="P89" s="122">
         <v>2.0</v>
@@ -19102,11 +19111,11 @@
     </row>
     <row r="90">
       <c r="C90" s="135" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D90" s="124">
         <f t="shared" si="17"/>
-        <v>12.79</v>
+        <v>14.3</v>
       </c>
       <c r="P90" s="122">
         <v>1.0</v>
@@ -19120,11 +19129,11 @@
     </row>
     <row r="91">
       <c r="C91" s="135" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D91" s="124">
         <f t="shared" si="17"/>
-        <v>9.83</v>
+        <v>7.41</v>
       </c>
       <c r="P91" s="122">
         <v>1.0</v>
@@ -19138,11 +19147,11 @@
     </row>
     <row r="92">
       <c r="C92" s="135" t="s">
-        <v>224</v>
+        <v>275</v>
       </c>
       <c r="D92" s="124">
         <f t="shared" si="17"/>
-        <v>11.48</v>
+        <v>10.62</v>
       </c>
       <c r="P92" s="122">
         <v>2.0</v>
@@ -19156,11 +19165,11 @@
     </row>
     <row r="93">
       <c r="C93" s="135" t="s">
-        <v>273</v>
+        <v>244</v>
       </c>
       <c r="D93" s="124">
         <f t="shared" si="17"/>
-        <v>10.65</v>
+        <v>12.51</v>
       </c>
       <c r="P93" s="122">
         <v>0.0</v>
@@ -19174,11 +19183,11 @@
     </row>
     <row r="94">
       <c r="C94" s="135" t="s">
-        <v>274</v>
+        <v>248</v>
       </c>
       <c r="D94" s="124">
         <f t="shared" si="17"/>
-        <v>8.98</v>
+        <v>7</v>
       </c>
       <c r="P94" s="122">
         <v>0.0</v>
@@ -19192,11 +19201,11 @@
     </row>
     <row r="95">
       <c r="C95" s="135" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D95" s="124">
         <f t="shared" si="17"/>
-        <v>8.23</v>
+        <v>6.11</v>
       </c>
       <c r="P95" s="122">
         <v>1.0</v>
@@ -19210,11 +19219,11 @@
     </row>
     <row r="96">
       <c r="C96" s="135" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D96" s="124">
         <f t="shared" si="17"/>
-        <v>8.74</v>
+        <v>8.03</v>
       </c>
       <c r="P96" s="122">
         <v>2.0</v>
@@ -19228,11 +19237,11 @@
     </row>
     <row r="97">
       <c r="C97" s="135" t="s">
-        <v>277</v>
+        <v>217</v>
       </c>
       <c r="D97" s="124">
         <f t="shared" si="17"/>
-        <v>9.23</v>
+        <v>9.64</v>
       </c>
       <c r="P97" s="122">
         <v>0.0</v>
@@ -19250,7 +19259,7 @@
       </c>
       <c r="D98" s="124">
         <f t="shared" si="17"/>
-        <v>9.74</v>
+        <v>8.22</v>
       </c>
       <c r="P98" s="122">
         <v>2.0</v>
@@ -19264,11 +19273,11 @@
     </row>
     <row r="99">
       <c r="C99" s="135" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="D99" s="124">
         <f t="shared" si="17"/>
-        <v>9.41</v>
+        <v>8.46</v>
       </c>
       <c r="P99" s="122">
         <v>2.0</v>
@@ -19282,11 +19291,11 @@
     </row>
     <row r="100">
       <c r="C100" s="135" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D100" s="124">
         <f t="shared" si="17"/>
-        <v>6.85</v>
+        <v>7.64</v>
       </c>
       <c r="P100" s="122">
         <v>2.0</v>
@@ -19300,11 +19309,11 @@
     </row>
     <row r="101">
       <c r="C101" s="135" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D101" s="124">
         <f t="shared" si="17"/>
-        <v>5.7</v>
+        <v>8.62</v>
       </c>
       <c r="P101" s="122">
         <v>2.0</v>
@@ -19318,11 +19327,11 @@
     </row>
     <row r="102">
       <c r="C102" s="135" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D102" s="124">
         <f t="shared" si="17"/>
-        <v>6.47</v>
+        <v>9.37</v>
       </c>
       <c r="P102" s="122">
         <v>2.0</v>
@@ -19336,11 +19345,11 @@
     </row>
     <row r="103">
       <c r="C103" s="135" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D103" s="124">
         <f t="shared" si="17"/>
-        <v>3.43</v>
+        <v>4.91</v>
       </c>
       <c r="P103" s="122">
         <v>1.0</v>
@@ -19354,11 +19363,11 @@
     </row>
     <row r="104">
       <c r="C104" s="135" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D104" s="124">
         <f t="shared" si="17"/>
-        <v>0.15</v>
+        <v>10.05</v>
       </c>
       <c r="N104" s="141"/>
       <c r="P104" s="122">
@@ -19373,11 +19382,11 @@
     </row>
     <row r="105">
       <c r="C105" s="135" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D105" s="124">
         <f t="shared" si="17"/>
-        <v>9.39</v>
+        <v>7.02</v>
       </c>
       <c r="N105" s="21"/>
       <c r="P105" s="122">
@@ -19392,11 +19401,11 @@
     </row>
     <row r="106">
       <c r="C106" s="135" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D106" s="124">
         <f t="shared" si="17"/>
-        <v>0.53</v>
+        <v>1.12</v>
       </c>
       <c r="N106" s="21"/>
       <c r="P106" s="122">
@@ -19411,11 +19420,11 @@
     </row>
     <row r="107">
       <c r="C107" s="135" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D107" s="124">
         <f t="shared" si="17"/>
-        <v>6.69</v>
+        <v>8.65</v>
       </c>
       <c r="N107" s="21"/>
       <c r="P107" s="122">
@@ -19430,11 +19439,11 @@
     </row>
     <row r="108">
       <c r="C108" s="135" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D108" s="124">
         <f t="shared" si="17"/>
-        <v>0.18</v>
+        <v>8.08</v>
       </c>
       <c r="N108" s="21"/>
       <c r="P108" s="122">
@@ -19449,11 +19458,11 @@
     </row>
     <row r="109">
       <c r="C109" s="135" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D109" s="124">
         <f t="shared" si="17"/>
-        <v>6.92</v>
+        <v>8.54</v>
       </c>
       <c r="N109" s="21"/>
       <c r="P109" s="122">
@@ -19468,11 +19477,11 @@
     </row>
     <row r="110">
       <c r="C110" s="135" t="s">
-        <v>213</v>
+        <v>290</v>
       </c>
       <c r="D110" s="124">
         <f t="shared" si="17"/>
-        <v>0.16</v>
+        <v>6.46</v>
       </c>
       <c r="N110" s="21"/>
       <c r="P110" s="122">
@@ -19487,11 +19496,11 @@
     </row>
     <row r="111">
       <c r="C111" s="135" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D111" s="124">
         <f t="shared" si="17"/>
-        <v>5.6</v>
+        <v>8.98</v>
       </c>
       <c r="N111" s="21"/>
       <c r="P111" s="122">
@@ -19506,11 +19515,11 @@
     </row>
     <row r="112">
       <c r="C112" s="135" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D112" s="124">
         <f t="shared" si="17"/>
-        <v>0.28</v>
+        <v>3.85</v>
       </c>
       <c r="P112" s="122">
         <v>1.0</v>
@@ -19524,11 +19533,11 @@
     </row>
     <row r="113">
       <c r="C113" s="135" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D113" s="124">
         <f t="shared" si="17"/>
-        <v>1.24</v>
+        <v>6.24</v>
       </c>
       <c r="P113" s="122">
         <v>0.0</v>
@@ -19542,11 +19551,11 @@
     </row>
     <row r="114">
       <c r="C114" s="135" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D114" s="124">
         <f t="shared" si="17"/>
-        <v>9.44</v>
+        <v>1.17</v>
       </c>
       <c r="P114" s="122">
         <v>1.0</v>
@@ -19560,11 +19569,11 @@
     </row>
     <row r="115">
       <c r="C115" s="135" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D115" s="124">
         <f t="shared" si="17"/>
-        <v>3.11</v>
+        <v>6.13</v>
       </c>
       <c r="P115" s="122">
         <v>1.0</v>
@@ -19578,11 +19587,11 @@
     </row>
     <row r="116">
       <c r="C116" s="135" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D116" s="124">
         <f t="shared" si="17"/>
-        <v>12.9</v>
+        <v>6.44</v>
       </c>
       <c r="P116" s="122">
         <v>1.0</v>
@@ -19596,11 +19605,11 @@
     </row>
     <row r="117">
       <c r="C117" s="135" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D117" s="124">
         <f t="shared" si="17"/>
-        <v>0.77</v>
+        <v>4.99</v>
       </c>
       <c r="P117" s="142"/>
       <c r="AE117" s="43">
@@ -19612,11 +19621,11 @@
     </row>
     <row r="118">
       <c r="C118" s="135" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D118" s="124">
         <f t="shared" si="17"/>
-        <v>8.33</v>
+        <v>4.52</v>
       </c>
       <c r="P118" s="142"/>
       <c r="AE118" s="43">
@@ -19628,11 +19637,11 @@
     </row>
     <row r="119">
       <c r="C119" s="135" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D119" s="124">
         <f t="shared" si="17"/>
-        <v>13.99</v>
+        <v>8.48</v>
       </c>
       <c r="P119" s="142"/>
       <c r="AE119" s="43">
@@ -19644,11 +19653,11 @@
     </row>
     <row r="120">
       <c r="C120" s="135" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D120" s="124">
         <f t="shared" si="17"/>
-        <v>1.03</v>
+        <v>6.39</v>
       </c>
       <c r="P120" s="142"/>
       <c r="AE120" s="43">
@@ -19660,11 +19669,11 @@
     </row>
     <row r="121">
       <c r="C121" s="135" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D121" s="124">
         <f t="shared" si="17"/>
-        <v>13.48</v>
+        <v>9.74</v>
       </c>
       <c r="P121" s="142"/>
       <c r="AE121" s="43">
@@ -19676,11 +19685,11 @@
     </row>
     <row r="122">
       <c r="C122" s="135" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D122" s="124">
         <f t="shared" si="17"/>
-        <v>13.88</v>
+        <v>7.7</v>
       </c>
       <c r="P122" s="142"/>
       <c r="AE122" s="43">
@@ -19692,11 +19701,11 @@
     </row>
     <row r="123">
       <c r="C123" s="135" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D123" s="124">
         <f t="shared" si="17"/>
-        <v>8.68</v>
+        <v>0.8</v>
       </c>
       <c r="P123" s="142"/>
       <c r="AE123" s="43">
@@ -19708,11 +19717,11 @@
     </row>
     <row r="124">
       <c r="C124" s="135" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D124" s="124">
         <f t="shared" si="17"/>
-        <v>12.29</v>
+        <v>9.57</v>
       </c>
       <c r="P124" s="142"/>
       <c r="AE124" s="43">
@@ -19724,11 +19733,11 @@
     </row>
     <row r="125">
       <c r="C125" s="135" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D125" s="124">
         <f t="shared" si="17"/>
-        <v>5.54</v>
+        <v>0.71</v>
       </c>
       <c r="P125" s="142"/>
       <c r="AE125" s="43">
@@ -19740,11 +19749,11 @@
     </row>
     <row r="126">
       <c r="C126" s="135" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D126" s="124">
         <f t="shared" si="17"/>
-        <v>8.36</v>
+        <v>4.34</v>
       </c>
       <c r="P126" s="142"/>
       <c r="AE126" s="43">
@@ -19756,11 +19765,11 @@
     </row>
     <row r="127">
       <c r="C127" s="135" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D127" s="124">
         <f t="shared" si="17"/>
-        <v>13.42</v>
+        <v>8.09</v>
       </c>
       <c r="P127" s="142"/>
       <c r="AE127" s="43">
@@ -19772,11 +19781,11 @@
     </row>
     <row r="128">
       <c r="C128" s="135" t="s">
-        <v>256</v>
+        <v>308</v>
       </c>
       <c r="D128" s="124">
         <f t="shared" si="17"/>
-        <v>10.5</v>
+        <v>6.41</v>
       </c>
       <c r="P128" s="142"/>
       <c r="AE128" s="43">
@@ -19788,11 +19797,11 @@
     </row>
     <row r="129">
       <c r="C129" s="135" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="D129" s="124">
         <f t="shared" si="17"/>
-        <v>10.2</v>
+        <v>8.83</v>
       </c>
       <c r="P129" s="142"/>
       <c r="AE129" s="43">
@@ -19804,11 +19813,11 @@
     </row>
     <row r="130">
       <c r="C130" s="135" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="D130" s="124">
         <f t="shared" si="17"/>
-        <v>4.56</v>
+        <v>4.75</v>
       </c>
       <c r="P130" s="142"/>
       <c r="AE130" s="43">
@@ -19820,11 +19829,11 @@
     </row>
     <row r="131">
       <c r="C131" s="135" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="D131" s="124">
         <f t="shared" si="17"/>
-        <v>11.7</v>
+        <v>5.68</v>
       </c>
       <c r="P131" s="142"/>
       <c r="AE131" s="43">
@@ -19836,11 +19845,11 @@
     </row>
     <row r="132">
       <c r="C132" s="135" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="D132" s="124">
         <f t="shared" si="17"/>
-        <v>14.03</v>
+        <v>9.04</v>
       </c>
       <c r="P132" s="142"/>
       <c r="AE132" s="43">
@@ -19852,11 +19861,11 @@
     </row>
     <row r="133">
       <c r="C133" s="135" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="D133" s="124">
         <f t="shared" si="17"/>
-        <v>8.15</v>
+        <v>6.89</v>
       </c>
       <c r="P133" s="142"/>
       <c r="AE133" s="43">
@@ -19868,11 +19877,11 @@
     </row>
     <row r="134">
       <c r="C134" s="135" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="D134" s="124">
         <f t="shared" si="17"/>
-        <v>8.46</v>
+        <v>4.98</v>
       </c>
       <c r="P134" s="142"/>
       <c r="AE134" s="43">
@@ -19884,11 +19893,11 @@
     </row>
     <row r="135">
       <c r="C135" s="135" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="D135" s="124">
         <f t="shared" si="17"/>
-        <v>5.83</v>
+        <v>7.92</v>
       </c>
       <c r="P135" s="142"/>
       <c r="AE135" s="43">
@@ -42182,14 +42191,14 @@
     <row r="1">
       <c r="A1" s="105"/>
       <c r="B1" s="145" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="C1" s="146"/>
       <c r="D1" s="146"/>
       <c r="E1" s="146"/>
       <c r="F1" s="146"/>
       <c r="G1" s="147" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="H1" s="146"/>
       <c r="I1" s="146"/>
@@ -42217,19 +42226,19 @@
         <v>3</v>
       </c>
       <c r="B2" s="149" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C2" s="150" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="D2" s="150" t="s">
         <v>207</v>
       </c>
       <c r="E2" s="150" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="F2" s="151" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="G2" s="149">
         <v>1.0</v>
@@ -42241,25 +42250,25 @@
         <v>2.0</v>
       </c>
       <c r="J2" s="150" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="K2" s="152" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="L2" s="150" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="M2" s="153" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="N2" s="101" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="O2" s="101" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="P2" s="101" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q2" s="9"/>
       <c r="R2" s="9"/>
@@ -43042,7 +43051,7 @@
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
       <c r="G27" s="166" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="H27" s="9"/>
       <c r="I27" s="9"/>
@@ -43103,7 +43112,7 @@
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
       <c r="D29" s="5" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="E29" s="5">
         <f>J29</f>
@@ -43125,10 +43134,10 @@
       </c>
       <c r="K29" s="9"/>
       <c r="L29" s="95" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="M29" s="95" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="O29" s="5">
         <v>1.0</v>
@@ -43264,7 +43273,7 @@
       <c r="E33" s="9"/>
       <c r="F33" s="9"/>
       <c r="G33" s="120" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="J33" s="9"/>
       <c r="K33" s="9"/>
@@ -43441,7 +43450,7 @@
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
       <c r="F38" s="5" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="G38" s="169">
         <f t="shared" ref="G38:I38" si="8">G30-G35</f>

--- a/data/df_best_models.xlsx
+++ b/data/df_best_models.xlsx
@@ -276,7 +276,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="253">
   <si>
     <t>id_country</t>
   </si>
@@ -1020,148 +1020,40 @@
     <t>Stake promedio</t>
   </si>
   <si>
-    <t>3.15</t>
-  </si>
-  <si>
-    <t>8.59</t>
-  </si>
-  <si>
-    <t>7.45</t>
-  </si>
-  <si>
-    <t>7.35</t>
-  </si>
-  <si>
-    <t>5.71</t>
-  </si>
-  <si>
-    <t>11.26</t>
-  </si>
-  <si>
-    <t>6.84</t>
-  </si>
-  <si>
     <t>Country</t>
   </si>
   <si>
     <t>Correl ROI y Expected ROI</t>
   </si>
   <si>
-    <t>3.43</t>
-  </si>
-  <si>
     <t>mean</t>
-  </si>
-  <si>
-    <t>12.98</t>
   </si>
   <si>
     <t>median</t>
   </si>
   <si>
-    <t>15.04</t>
-  </si>
-  <si>
     <t>p25</t>
-  </si>
-  <si>
-    <t>11.46</t>
   </si>
   <si>
     <t>p75</t>
   </si>
   <si>
-    <t>10.03</t>
-  </si>
-  <si>
-    <t>8.27</t>
-  </si>
-  <si>
-    <t>11.13</t>
-  </si>
-  <si>
-    <t>1.79</t>
-  </si>
-  <si>
-    <t>11.00</t>
-  </si>
-  <si>
-    <t>1.63</t>
-  </si>
-  <si>
     <t>Gracias a las nuevas métricas de G/P sin bank en test, me di cuenta de que:</t>
-  </si>
-  <si>
-    <t>2.84</t>
   </si>
   <si>
     <t>La rentabilidad en ITA está en el visitante y no en el empate como creía.</t>
   </si>
   <si>
-    <t>2.19</t>
-  </si>
-  <si>
     <t>La rentabilidad en ENG y GER está en el empate tal como creía.</t>
-  </si>
-  <si>
-    <t>2.21</t>
   </si>
   <si>
     <t>En SPA esta repartido aunque Empate saca una ventaja.</t>
   </si>
   <si>
-    <t>1.68</t>
-  </si>
-  <si>
     <t>En FRA, depende el modelo. A veces local, a veces, empate.</t>
   </si>
   <si>
-    <t>0.84</t>
-  </si>
-  <si>
     <t>Si en FRA empate no rinde, no tiene sentido exigirle una buena distrib en empate… → Tiene sentido pero al parecer si importa el empate puesto que el modelo que gana se basa en empate.</t>
-  </si>
-  <si>
-    <t>2.52</t>
-  </si>
-  <si>
-    <t>2.94</t>
-  </si>
-  <si>
-    <t>7.41</t>
-  </si>
-  <si>
-    <t>2.96</t>
-  </si>
-  <si>
-    <t>12.46</t>
-  </si>
-  <si>
-    <t>11.32</t>
-  </si>
-  <si>
-    <t>7.79</t>
-  </si>
-  <si>
-    <t>10.77</t>
-  </si>
-  <si>
-    <t>1.24</t>
-  </si>
-  <si>
-    <t>10.52</t>
-  </si>
-  <si>
-    <t>2.83</t>
-  </si>
-  <si>
-    <t>4.72</t>
-  </si>
-  <si>
-    <t>3.53</t>
-  </si>
-  <si>
-    <t>6.63</t>
   </si>
   <si>
     <t>RENTABILIDAD</t>
@@ -2563,7 +2455,7 @@
         <v>45693.0</v>
       </c>
       <c r="D6" s="15">
-        <v>30.0</v>
+        <v>812.0</v>
       </c>
       <c r="E6" s="15" t="s">
         <v>16</v>
@@ -2613,7 +2505,7 @@
         <v>45693.0</v>
       </c>
       <c r="D7" s="15">
-        <v>1271.0</v>
+        <v>1023.0</v>
       </c>
       <c r="E7" s="15" t="s">
         <v>16</v>
@@ -17765,9 +17657,9 @@
       <c r="A37" s="41"/>
       <c r="B37" s="41"/>
       <c r="C37" s="41"/>
-      <c r="D37" s="133">
+      <c r="D37" s="133" t="str">
         <f>AVERAGE(D39:D1775)</f>
-        <v>6.51525</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="G37" s="36" t="s">
         <v>39</v>
@@ -17831,12 +17723,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="C39" s="135" t="s">
-        <v>212</v>
-      </c>
-      <c r="D39" s="125">
+      <c r="C39" s="135"/>
+      <c r="D39" s="125" t="str">
         <f t="shared" ref="D39:D221" si="17">IF(COUNTA(C39)=1,C39/1,"")</f>
-        <v>3.15</v>
+        <v/>
       </c>
       <c r="G39" s="36" t="s">
         <v>31</v>
@@ -17869,12 +17759,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="C40" s="136" t="s">
-        <v>213</v>
-      </c>
-      <c r="D40" s="125">
+      <c r="C40" s="136"/>
+      <c r="D40" s="125" t="str">
         <f t="shared" si="17"/>
-        <v>8.59</v>
+        <v/>
       </c>
       <c r="G40" s="36" t="s">
         <v>27</v>
@@ -17907,12 +17795,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="C41" s="136" t="s">
-        <v>214</v>
-      </c>
-      <c r="D41" s="125">
+      <c r="C41" s="136"/>
+      <c r="D41" s="125" t="str">
         <f t="shared" si="17"/>
-        <v>7.45</v>
+        <v/>
       </c>
       <c r="P41" s="123">
         <v>0.0</v>
@@ -17939,12 +17825,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="C42" s="136" t="s">
-        <v>215</v>
-      </c>
-      <c r="D42" s="125">
+      <c r="C42" s="136"/>
+      <c r="D42" s="125" t="str">
         <f t="shared" si="17"/>
-        <v>7.35</v>
+        <v/>
       </c>
       <c r="P42" s="123">
         <v>2.0</v>
@@ -17971,12 +17855,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="C43" s="136" t="s">
-        <v>216</v>
-      </c>
-      <c r="D43" s="125">
+      <c r="C43" s="136"/>
+      <c r="D43" s="125" t="str">
         <f t="shared" si="17"/>
-        <v>5.71</v>
+        <v/>
       </c>
       <c r="P43" s="123">
         <v>1.0</v>
@@ -18003,12 +17885,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="C44" s="136" t="s">
-        <v>217</v>
-      </c>
-      <c r="D44" s="125">
+      <c r="C44" s="136"/>
+      <c r="D44" s="125" t="str">
         <f t="shared" si="17"/>
-        <v>11.26</v>
+        <v/>
       </c>
       <c r="P44" s="123">
         <v>2.0</v>
@@ -18033,12 +17913,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="C45" s="136" t="s">
-        <v>218</v>
-      </c>
-      <c r="D45" s="125">
+      <c r="C45" s="136"/>
+      <c r="D45" s="125" t="str">
         <f t="shared" si="17"/>
-        <v>6.84</v>
+        <v/>
       </c>
       <c r="P45" s="123">
         <v>1.0</v>
@@ -18051,18 +17929,16 @@
       </c>
     </row>
     <row r="46">
-      <c r="C46" s="136" t="s">
-        <v>218</v>
-      </c>
-      <c r="D46" s="125">
+      <c r="C46" s="136"/>
+      <c r="D46" s="125" t="str">
         <f t="shared" si="17"/>
-        <v>6.84</v>
+        <v/>
       </c>
       <c r="G46" s="97" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="H46" s="97" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="P46" s="123">
         <v>0.0</v>
@@ -18075,12 +17951,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="C47" s="136" t="s">
-        <v>215</v>
-      </c>
-      <c r="D47" s="125">
+      <c r="C47" s="136"/>
+      <c r="D47" s="125" t="str">
         <f t="shared" si="17"/>
-        <v>7.35</v>
+        <v/>
       </c>
       <c r="G47" s="102" t="s">
         <v>40</v>
@@ -18105,12 +17979,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="C48" s="136" t="s">
-        <v>221</v>
-      </c>
-      <c r="D48" s="125">
+      <c r="C48" s="136"/>
+      <c r="D48" s="125" t="str">
         <f t="shared" si="17"/>
-        <v>3.43</v>
+        <v/>
       </c>
       <c r="G48" s="102" t="s">
         <v>39</v>
@@ -18119,7 +17991,7 @@
         <v>0.36678739680281</v>
       </c>
       <c r="J48" s="43" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="K48" s="89">
         <f>AVERAGE(H47:H51)</f>
@@ -18142,12 +18014,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="C49" s="136" t="s">
-        <v>223</v>
-      </c>
-      <c r="D49" s="125">
+      <c r="C49" s="136"/>
+      <c r="D49" s="125" t="str">
         <f t="shared" si="17"/>
-        <v>12.98</v>
+        <v/>
       </c>
       <c r="G49" s="102" t="s">
         <v>30</v>
@@ -18156,7 +18026,7 @@
         <v>0.142870351877935</v>
       </c>
       <c r="J49" s="43" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="K49" s="89">
         <f>MEDIAN(H47:H51)</f>
@@ -18179,12 +18049,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="C50" s="136" t="s">
-        <v>225</v>
-      </c>
-      <c r="D50" s="125">
+      <c r="C50" s="136"/>
+      <c r="D50" s="125" t="str">
         <f t="shared" si="17"/>
-        <v>15.04</v>
+        <v/>
       </c>
       <c r="G50" s="102" t="s">
         <v>31</v>
@@ -18193,7 +18061,7 @@
         <v>0.497437843674554</v>
       </c>
       <c r="J50" s="43" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="K50" s="89">
         <f>PERCENTILE(H47:H51,0.25)</f>
@@ -18216,12 +18084,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="C51" s="136" t="s">
-        <v>227</v>
-      </c>
-      <c r="D51" s="125">
+      <c r="C51" s="136"/>
+      <c r="D51" s="125" t="str">
         <f t="shared" si="17"/>
-        <v>11.46</v>
+        <v/>
       </c>
       <c r="G51" s="102" t="s">
         <v>27</v>
@@ -18230,7 +18096,7 @@
         <v>0.247446036291655</v>
       </c>
       <c r="J51" s="43" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="K51" s="89">
         <f>PERCENTILE(H47:H51,0.75)</f>
@@ -18253,12 +18119,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="C52" s="136" t="s">
-        <v>229</v>
-      </c>
-      <c r="D52" s="125">
+      <c r="C52" s="136"/>
+      <c r="D52" s="125" t="str">
         <f t="shared" si="17"/>
-        <v>10.03</v>
+        <v/>
       </c>
       <c r="P52" s="123">
         <v>0.0</v>
@@ -18277,12 +18141,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="C53" s="136" t="s">
-        <v>230</v>
-      </c>
-      <c r="D53" s="125">
+      <c r="C53" s="136"/>
+      <c r="D53" s="125" t="str">
         <f t="shared" si="17"/>
-        <v>8.27</v>
+        <v/>
       </c>
       <c r="P53" s="123">
         <v>0.0</v>
@@ -18301,12 +18163,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="C54" s="136" t="s">
-        <v>230</v>
-      </c>
-      <c r="D54" s="125">
+      <c r="C54" s="136"/>
+      <c r="D54" s="125" t="str">
         <f t="shared" si="17"/>
-        <v>8.27</v>
+        <v/>
       </c>
       <c r="P54" s="123">
         <v>2.0</v>
@@ -18325,12 +18185,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="C55" s="136" t="s">
-        <v>231</v>
-      </c>
-      <c r="D55" s="125">
+      <c r="C55" s="136"/>
+      <c r="D55" s="125" t="str">
         <f t="shared" si="17"/>
-        <v>11.13</v>
+        <v/>
       </c>
       <c r="P55" s="123">
         <v>0.0</v>
@@ -18349,12 +18207,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="C56" s="136" t="s">
-        <v>232</v>
-      </c>
-      <c r="D56" s="125">
+      <c r="C56" s="136"/>
+      <c r="D56" s="125" t="str">
         <f t="shared" si="17"/>
-        <v>1.79</v>
+        <v/>
       </c>
       <c r="P56" s="123">
         <v>0.0</v>
@@ -18373,12 +18229,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="C57" s="136" t="s">
-        <v>233</v>
-      </c>
-      <c r="D57" s="125">
+      <c r="C57" s="136"/>
+      <c r="D57" s="125" t="str">
         <f t="shared" si="17"/>
-        <v>11</v>
+        <v/>
       </c>
       <c r="P57" s="123">
         <v>2.0</v>
@@ -18397,15 +18251,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="C58" s="136" t="s">
-        <v>234</v>
-      </c>
-      <c r="D58" s="125">
+      <c r="C58" s="136"/>
+      <c r="D58" s="125" t="str">
         <f t="shared" si="17"/>
-        <v>1.63</v>
+        <v/>
       </c>
       <c r="G58" s="138" t="s">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="H58" s="139"/>
       <c r="P58" s="123">
@@ -18425,16 +18277,14 @@
       </c>
     </row>
     <row r="59">
-      <c r="C59" s="136" t="s">
-        <v>236</v>
-      </c>
-      <c r="D59" s="125">
+      <c r="C59" s="136"/>
+      <c r="D59" s="125" t="str">
         <f t="shared" si="17"/>
-        <v>2.84</v>
+        <v/>
       </c>
       <c r="G59" s="139"/>
       <c r="H59" s="140" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="P59" s="123">
         <v>0.0</v>
@@ -18453,16 +18303,14 @@
       </c>
     </row>
     <row r="60">
-      <c r="C60" s="136" t="s">
-        <v>238</v>
-      </c>
-      <c r="D60" s="125">
+      <c r="C60" s="136"/>
+      <c r="D60" s="125" t="str">
         <f t="shared" si="17"/>
-        <v>2.19</v>
+        <v/>
       </c>
       <c r="G60" s="139"/>
       <c r="H60" s="140" t="s">
-        <v>239</v>
+        <v>220</v>
       </c>
       <c r="P60" s="123">
         <v>2.0</v>
@@ -18481,16 +18329,14 @@
       </c>
     </row>
     <row r="61">
-      <c r="C61" s="136" t="s">
-        <v>240</v>
-      </c>
-      <c r="D61" s="125">
+      <c r="C61" s="136"/>
+      <c r="D61" s="125" t="str">
         <f t="shared" si="17"/>
-        <v>2.21</v>
+        <v/>
       </c>
       <c r="G61" s="139"/>
       <c r="H61" s="140" t="s">
-        <v>241</v>
+        <v>221</v>
       </c>
       <c r="P61" s="123">
         <v>2.0</v>
@@ -18509,16 +18355,14 @@
       </c>
     </row>
     <row r="62">
-      <c r="C62" s="136" t="s">
-        <v>242</v>
-      </c>
-      <c r="D62" s="125">
+      <c r="C62" s="136"/>
+      <c r="D62" s="125" t="str">
         <f t="shared" si="17"/>
-        <v>1.68</v>
+        <v/>
       </c>
       <c r="G62" s="139"/>
       <c r="H62" s="140" t="s">
-        <v>243</v>
+        <v>222</v>
       </c>
       <c r="P62" s="123">
         <v>1.0</v>
@@ -18537,16 +18381,14 @@
       </c>
     </row>
     <row r="63">
-      <c r="C63" s="136" t="s">
-        <v>244</v>
-      </c>
-      <c r="D63" s="125">
+      <c r="C63" s="136"/>
+      <c r="D63" s="125" t="str">
         <f t="shared" si="17"/>
-        <v>0.84</v>
+        <v/>
       </c>
       <c r="G63" s="139"/>
       <c r="H63" s="140" t="s">
-        <v>245</v>
+        <v>223</v>
       </c>
       <c r="P63" s="123">
         <v>0.0</v>
@@ -18559,12 +18401,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="C64" s="136" t="s">
-        <v>246</v>
-      </c>
-      <c r="D64" s="125">
+      <c r="C64" s="136"/>
+      <c r="D64" s="125" t="str">
         <f t="shared" si="17"/>
-        <v>2.52</v>
+        <v/>
       </c>
       <c r="P64" s="123">
         <v>1.0</v>
@@ -18577,12 +18417,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="C65" s="136" t="s">
-        <v>247</v>
-      </c>
-      <c r="D65" s="125">
+      <c r="C65" s="136"/>
+      <c r="D65" s="125" t="str">
         <f t="shared" si="17"/>
-        <v>2.94</v>
+        <v/>
       </c>
       <c r="P65" s="123">
         <v>2.0</v>
@@ -18595,12 +18433,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="C66" s="136" t="s">
-        <v>248</v>
-      </c>
-      <c r="D66" s="125">
+      <c r="C66" s="136"/>
+      <c r="D66" s="125" t="str">
         <f t="shared" si="17"/>
-        <v>7.41</v>
+        <v/>
       </c>
       <c r="P66" s="123">
         <v>0.0</v>
@@ -18613,12 +18449,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="C67" s="136" t="s">
-        <v>249</v>
-      </c>
-      <c r="D67" s="125">
+      <c r="C67" s="136"/>
+      <c r="D67" s="125" t="str">
         <f t="shared" si="17"/>
-        <v>2.96</v>
+        <v/>
       </c>
       <c r="P67" s="123">
         <v>0.0</v>
@@ -18631,12 +18465,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="C68" s="136" t="s">
-        <v>250</v>
-      </c>
-      <c r="D68" s="125">
+      <c r="C68" s="136"/>
+      <c r="D68" s="125" t="str">
         <f t="shared" si="17"/>
-        <v>12.46</v>
+        <v/>
       </c>
       <c r="P68" s="123">
         <v>1.0</v>
@@ -18649,12 +18481,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="C69" s="136" t="s">
-        <v>251</v>
-      </c>
-      <c r="D69" s="125">
+      <c r="C69" s="136"/>
+      <c r="D69" s="125" t="str">
         <f t="shared" si="17"/>
-        <v>11.32</v>
+        <v/>
       </c>
       <c r="P69" s="123">
         <v>2.0</v>
@@ -18667,12 +18497,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="C70" s="136" t="s">
-        <v>252</v>
-      </c>
-      <c r="D70" s="125">
+      <c r="C70" s="136"/>
+      <c r="D70" s="125" t="str">
         <f t="shared" si="17"/>
-        <v>7.79</v>
+        <v/>
       </c>
       <c r="P70" s="123">
         <v>1.0</v>
@@ -18685,12 +18513,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="C71" s="136" t="s">
-        <v>253</v>
-      </c>
-      <c r="D71" s="125">
+      <c r="C71" s="136"/>
+      <c r="D71" s="125" t="str">
         <f t="shared" si="17"/>
-        <v>10.77</v>
+        <v/>
       </c>
       <c r="F71" s="141"/>
       <c r="P71" s="123">
@@ -18704,12 +18530,10 @@
       </c>
     </row>
     <row r="72">
-      <c r="C72" s="136" t="s">
-        <v>254</v>
-      </c>
-      <c r="D72" s="125">
+      <c r="C72" s="136"/>
+      <c r="D72" s="125" t="str">
         <f t="shared" si="17"/>
-        <v>1.24</v>
+        <v/>
       </c>
       <c r="P72" s="123">
         <v>0.0</v>
@@ -18722,12 +18546,10 @@
       </c>
     </row>
     <row r="73">
-      <c r="C73" s="136" t="s">
-        <v>255</v>
-      </c>
-      <c r="D73" s="125">
+      <c r="C73" s="136"/>
+      <c r="D73" s="125" t="str">
         <f t="shared" si="17"/>
-        <v>10.52</v>
+        <v/>
       </c>
       <c r="P73" s="123">
         <v>1.0</v>
@@ -18740,12 +18562,10 @@
       </c>
     </row>
     <row r="74">
-      <c r="C74" s="136" t="s">
-        <v>256</v>
-      </c>
-      <c r="D74" s="125">
+      <c r="C74" s="136"/>
+      <c r="D74" s="125" t="str">
         <f t="shared" si="17"/>
-        <v>2.83</v>
+        <v/>
       </c>
       <c r="P74" s="123">
         <v>0.0</v>
@@ -18758,12 +18578,10 @@
       </c>
     </row>
     <row r="75">
-      <c r="C75" s="136" t="s">
-        <v>257</v>
-      </c>
-      <c r="D75" s="125">
+      <c r="C75" s="136"/>
+      <c r="D75" s="125" t="str">
         <f t="shared" si="17"/>
-        <v>4.72</v>
+        <v/>
       </c>
       <c r="P75" s="123">
         <v>1.0</v>
@@ -18776,12 +18594,10 @@
       </c>
     </row>
     <row r="76">
-      <c r="C76" s="136" t="s">
-        <v>258</v>
-      </c>
-      <c r="D76" s="125">
+      <c r="C76" s="136"/>
+      <c r="D76" s="125" t="str">
         <f t="shared" si="17"/>
-        <v>3.53</v>
+        <v/>
       </c>
       <c r="P76" s="123">
         <v>0.0</v>
@@ -18794,12 +18610,10 @@
       </c>
     </row>
     <row r="77">
-      <c r="C77" s="136" t="s">
-        <v>188</v>
-      </c>
-      <c r="D77" s="125">
+      <c r="C77" s="136"/>
+      <c r="D77" s="125" t="str">
         <f t="shared" si="17"/>
-        <v>3.64</v>
+        <v/>
       </c>
       <c r="P77" s="123">
         <v>0.0</v>
@@ -18812,12 +18626,10 @@
       </c>
     </row>
     <row r="78">
-      <c r="C78" s="136" t="s">
-        <v>259</v>
-      </c>
-      <c r="D78" s="125">
+      <c r="C78" s="136"/>
+      <c r="D78" s="125" t="str">
         <f t="shared" si="17"/>
-        <v>6.63</v>
+        <v/>
       </c>
       <c r="P78" s="123">
         <v>1.0</v>
@@ -41995,14 +41807,14 @@
     <row r="1">
       <c r="A1" s="106"/>
       <c r="B1" s="146" t="s">
-        <v>260</v>
+        <v>224</v>
       </c>
       <c r="C1" s="147"/>
       <c r="D1" s="147"/>
       <c r="E1" s="147"/>
       <c r="F1" s="147"/>
       <c r="G1" s="148" t="s">
-        <v>261</v>
+        <v>225</v>
       </c>
       <c r="H1" s="147"/>
       <c r="I1" s="147"/>
@@ -42034,19 +41846,19 @@
         <v>3</v>
       </c>
       <c r="B2" s="150" t="s">
-        <v>262</v>
+        <v>226</v>
       </c>
       <c r="C2" s="151" t="s">
-        <v>263</v>
+        <v>227</v>
       </c>
       <c r="D2" s="151" t="s">
         <v>208</v>
       </c>
       <c r="E2" s="151" t="s">
-        <v>264</v>
+        <v>228</v>
       </c>
       <c r="F2" s="152" t="s">
-        <v>265</v>
+        <v>229</v>
       </c>
       <c r="G2" s="150">
         <v>1.0</v>
@@ -42058,30 +41870,30 @@
         <v>2.0</v>
       </c>
       <c r="J2" s="151" t="s">
-        <v>266</v>
+        <v>230</v>
       </c>
       <c r="K2" s="153" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="L2" s="151" t="s">
-        <v>268</v>
+        <v>232</v>
       </c>
       <c r="M2" s="154" t="s">
-        <v>269</v>
+        <v>233</v>
       </c>
       <c r="N2" s="102" t="s">
-        <v>270</v>
+        <v>234</v>
       </c>
       <c r="O2" s="102" t="s">
-        <v>271</v>
+        <v>235</v>
       </c>
       <c r="P2" s="102" t="s">
-        <v>272</v>
+        <v>236</v>
       </c>
       <c r="Q2" s="9"/>
       <c r="R2" s="9"/>
       <c r="S2" s="96" t="s">
-        <v>273</v>
+        <v>237</v>
       </c>
       <c r="T2" s="9"/>
       <c r="U2" s="9"/>
@@ -42167,7 +41979,7 @@
       <c r="Q4" s="9"/>
       <c r="R4" s="9"/>
       <c r="S4" s="160" t="s">
-        <v>274</v>
+        <v>238</v>
       </c>
       <c r="T4" s="161"/>
       <c r="Z4" s="36"/>
@@ -42203,7 +42015,7 @@
       <c r="P5" s="163"/>
       <c r="S5" s="161"/>
       <c r="T5" s="164" t="s">
-        <v>275</v>
+        <v>239</v>
       </c>
     </row>
     <row r="6">
@@ -42236,11 +42048,11 @@
       <c r="R6" s="9"/>
       <c r="S6" s="161"/>
       <c r="T6" s="164" t="s">
-        <v>276</v>
+        <v>240</v>
       </c>
       <c r="Z6" s="32"/>
       <c r="AD6" s="43" t="s">
-        <v>277</v>
+        <v>241</v>
       </c>
     </row>
     <row r="7">
@@ -42270,7 +42082,7 @@
       <c r="O7" s="80"/>
       <c r="P7" s="165"/>
       <c r="AD7" s="164" t="s">
-        <v>278</v>
+        <v>242</v>
       </c>
       <c r="AE7" s="161"/>
     </row>
@@ -42301,11 +42113,11 @@
       <c r="O8" s="80"/>
       <c r="P8" s="165"/>
       <c r="S8" s="164" t="s">
-        <v>279</v>
+        <v>243</v>
       </c>
       <c r="AA8" s="32"/>
       <c r="AD8" s="164" t="s">
-        <v>280</v>
+        <v>244</v>
       </c>
     </row>
     <row r="9">
@@ -42504,7 +42316,7 @@
       <c r="O15" s="80"/>
       <c r="P15" s="165"/>
       <c r="S15" s="43" t="s">
-        <v>281</v>
+        <v>245</v>
       </c>
     </row>
     <row r="16">
@@ -42617,7 +42429,7 @@
       <c r="Q19" s="9"/>
       <c r="R19" s="9"/>
       <c r="S19" s="43" t="s">
-        <v>282</v>
+        <v>246</v>
       </c>
     </row>
     <row r="20">
@@ -42873,7 +42685,7 @@
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
       <c r="G27" s="170" t="s">
-        <v>283</v>
+        <v>247</v>
       </c>
       <c r="H27" s="9"/>
       <c r="I27" s="9"/>
@@ -42942,7 +42754,7 @@
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
       <c r="D29" s="5" t="s">
-        <v>284</v>
+        <v>248</v>
       </c>
       <c r="E29" s="5">
         <f>J29</f>
@@ -42964,10 +42776,10 @@
       </c>
       <c r="K29" s="9"/>
       <c r="L29" s="96" t="s">
-        <v>285</v>
+        <v>249</v>
       </c>
       <c r="M29" s="96" t="s">
-        <v>286</v>
+        <v>250</v>
       </c>
       <c r="O29" s="5">
         <v>1.0</v>
@@ -43119,7 +42931,7 @@
       <c r="E33" s="9"/>
       <c r="F33" s="9"/>
       <c r="G33" s="121" t="s">
-        <v>287</v>
+        <v>251</v>
       </c>
       <c r="J33" s="9"/>
       <c r="K33" s="9"/>
@@ -43316,7 +43128,7 @@
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
       <c r="F38" s="5" t="s">
-        <v>288</v>
+        <v>252</v>
       </c>
       <c r="G38" s="173">
         <f t="shared" ref="G38:I38" si="8">G30-G35</f>

--- a/data/df_best_models.xlsx
+++ b/data/df_best_models.xlsx
@@ -276,7 +276,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="253">
   <si>
     <t>id_country</t>
   </si>
@@ -2404,7 +2404,7 @@
         <v>45693.0</v>
       </c>
       <c r="D5" s="15">
-        <v>518.0</v>
+        <v>1172.0</v>
       </c>
       <c r="E5" s="15" t="s">
         <v>16</v>
@@ -2455,7 +2455,7 @@
         <v>45693.0</v>
       </c>
       <c r="D6" s="15">
-        <v>812.0</v>
+        <v>411.0</v>
       </c>
       <c r="E6" s="15" t="s">
         <v>16</v>
@@ -2505,7 +2505,7 @@
         <v>45693.0</v>
       </c>
       <c r="D7" s="15">
-        <v>1023.0</v>
+        <v>1267.0</v>
       </c>
       <c r="E7" s="15" t="s">
         <v>16</v>
@@ -2555,7 +2555,7 @@
         <v>45693.0</v>
       </c>
       <c r="D8" s="15">
-        <v>1263.0</v>
+        <v>770.0</v>
       </c>
       <c r="E8" s="15" t="s">
         <v>16</v>
@@ -42597,9 +42597,15 @@
       <c r="P24" s="9"/>
       <c r="Q24" s="9"/>
       <c r="R24" s="9"/>
-      <c r="S24" s="9"/>
-      <c r="T24" s="9"/>
-      <c r="U24" s="9"/>
+      <c r="S24" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="T24" s="43">
+        <v>145.0</v>
+      </c>
+      <c r="U24" s="43">
+        <v>145.0</v>
+      </c>
       <c r="V24" s="9"/>
       <c r="W24" s="9"/>
       <c r="X24" s="9"/>
@@ -42630,9 +42636,15 @@
       <c r="P25" s="9"/>
       <c r="Q25" s="9"/>
       <c r="R25" s="9"/>
-      <c r="S25" s="9"/>
-      <c r="T25" s="9"/>
-      <c r="U25" s="9"/>
+      <c r="S25" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="T25" s="43">
+        <v>1172.0</v>
+      </c>
+      <c r="U25" s="43">
+        <v>518.0</v>
+      </c>
       <c r="V25" s="9"/>
       <c r="W25" s="9"/>
       <c r="X25" s="9"/>
@@ -42663,9 +42675,15 @@
       <c r="P26" s="9"/>
       <c r="Q26" s="9"/>
       <c r="R26" s="9"/>
-      <c r="S26" s="9"/>
-      <c r="T26" s="9"/>
-      <c r="U26" s="9"/>
+      <c r="S26" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="T26" s="43">
+        <v>411.0</v>
+      </c>
+      <c r="U26" s="43">
+        <v>812.0</v>
+      </c>
       <c r="V26" s="9"/>
       <c r="W26" s="9"/>
       <c r="X26" s="9"/>
@@ -42697,9 +42715,15 @@
       <c r="P27" s="9"/>
       <c r="Q27" s="9"/>
       <c r="R27" s="9"/>
-      <c r="S27" s="9"/>
-      <c r="T27" s="9"/>
-      <c r="U27" s="9"/>
+      <c r="S27" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="T27" s="43">
+        <v>1267.0</v>
+      </c>
+      <c r="U27" s="43">
+        <v>1023.0</v>
+      </c>
       <c r="V27" s="9"/>
       <c r="W27" s="9"/>
       <c r="X27" s="9"/>
@@ -42735,9 +42759,15 @@
       <c r="P28" s="9"/>
       <c r="Q28" s="9"/>
       <c r="R28" s="9"/>
-      <c r="S28" s="9"/>
-      <c r="T28" s="9"/>
-      <c r="U28" s="9"/>
+      <c r="S28" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="T28" s="43">
+        <v>770.0</v>
+      </c>
+      <c r="U28" s="43">
+        <v>1263.0</v>
+      </c>
       <c r="V28" s="9"/>
       <c r="W28" s="9"/>
       <c r="X28" s="9"/>

--- a/data/df_best_models.xlsx
+++ b/data/df_best_models.xlsx
@@ -274,7 +274,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="338">
   <si>
     <t>id_country</t>
   </si>
@@ -1111,28 +1111,28 @@
     <t>Stake promedio</t>
   </si>
   <si>
-    <t>3.58</t>
+    <t>4.84</t>
   </si>
   <si>
-    <t>3.79</t>
+    <t>4.18</t>
   </si>
   <si>
-    <t>4.09</t>
+    <t>4.80</t>
   </si>
   <si>
-    <t>4.96</t>
+    <t>1.64</t>
   </si>
   <si>
-    <t>3.62</t>
+    <t>1.05</t>
   </si>
   <si>
-    <t>3.72</t>
+    <t>7.12</t>
   </si>
   <si>
-    <t>4.81</t>
+    <t>10.03</t>
   </si>
   <si>
-    <t>0.55</t>
+    <t>6.64</t>
   </si>
   <si>
     <t>Country</t>
@@ -1141,151 +1141,151 @@
     <t>Correl ROI y Expected ROI</t>
   </si>
   <si>
-    <t>2.41</t>
+    <t>5.40</t>
   </si>
   <si>
-    <t>3.47</t>
+    <t>5.92</t>
   </si>
   <si>
     <t>mean</t>
   </si>
   <si>
-    <t>3.57</t>
+    <t>5.90</t>
   </si>
   <si>
     <t>median</t>
   </si>
   <si>
-    <t>5.31</t>
+    <t>10.26</t>
   </si>
   <si>
     <t>p25</t>
   </si>
   <si>
-    <t>4.03</t>
+    <t>5.99</t>
   </si>
   <si>
     <t>p75</t>
   </si>
   <si>
-    <t>4.07</t>
+    <t>9.16</t>
   </si>
   <si>
-    <t>3.27</t>
+    <t>4.86</t>
   </si>
   <si>
-    <t>0.58</t>
+    <t>6.89</t>
   </si>
   <si>
-    <t>3.38</t>
+    <t>8.85</t>
   </si>
   <si>
-    <t>3.24</t>
+    <t>8.58</t>
   </si>
   <si>
-    <t>1.57</t>
+    <t>1.18</t>
   </si>
   <si>
-    <t>5.69</t>
+    <t>5.60</t>
   </si>
   <si>
     <t>Gracias a las nuevas métricas de G/P sin bank en test, me di cuenta de que:</t>
   </si>
   <si>
-    <t>5.89</t>
+    <t>5.04</t>
   </si>
   <si>
     <t>La rentabilidad en ITA está en el visitante y no en el empate como creía.</t>
   </si>
   <si>
-    <t>5.55</t>
+    <t>10.85</t>
   </si>
   <si>
     <t>La rentabilidad en ENG y GER está en el empate tal como creía.</t>
   </si>
   <si>
-    <t>5.39</t>
+    <t>10.58</t>
   </si>
   <si>
     <t>En SPA esta repartido aunque Empate saca una ventaja.</t>
   </si>
   <si>
-    <t>6.13</t>
+    <t>8.46</t>
   </si>
   <si>
     <t>En FRA, depende el modelo. A veces local, a veces, empate.</t>
   </si>
   <si>
-    <t>4.32</t>
+    <t>5.03</t>
   </si>
   <si>
     <t>Si en FRA empate no rinde, no tiene sentido exigirle una buena distrib en empate… → Tiene sentido pero al parecer si importa el empate puesto que el modelo que gana se basa en empate.</t>
   </si>
   <si>
-    <t>0.86</t>
+    <t>7.01</t>
   </si>
   <si>
-    <t>4.25</t>
+    <t>5.14</t>
   </si>
   <si>
-    <t>4.02</t>
+    <t>5.77</t>
   </si>
   <si>
-    <t>1.67</t>
+    <t>3.45</t>
   </si>
   <si>
-    <t>2.77</t>
+    <t>6.06</t>
   </si>
   <si>
-    <t>0.38</t>
+    <t>4.64</t>
   </si>
   <si>
-    <t>3.61</t>
-  </si>
-  <si>
-    <t>3.37</t>
-  </si>
-  <si>
-    <t>2.46</t>
-  </si>
-  <si>
-    <t>3.86</t>
-  </si>
-  <si>
-    <t>2.15</t>
-  </si>
-  <si>
-    <t>2.67</t>
-  </si>
-  <si>
-    <t>5.37</t>
-  </si>
-  <si>
-    <t>3.77</t>
-  </si>
-  <si>
-    <t>6.10</t>
-  </si>
-  <si>
-    <t>7.54</t>
-  </si>
-  <si>
-    <t>5.07</t>
+    <t>4.97</t>
   </si>
   <si>
     <t>7.00</t>
   </si>
   <si>
-    <t>6.45</t>
+    <t>5.88</t>
   </si>
   <si>
-    <t>6.30</t>
+    <t>7.17</t>
   </si>
   <si>
-    <t>3.93</t>
+    <t>5.09</t>
   </si>
   <si>
-    <t>3.59</t>
+    <t>2.60</t>
+  </si>
+  <si>
+    <t>3.13</t>
+  </si>
+  <si>
+    <t>6.29</t>
+  </si>
+  <si>
+    <t>6.34</t>
+  </si>
+  <si>
+    <t>4.99</t>
+  </si>
+  <si>
+    <t>10.60</t>
+  </si>
+  <si>
+    <t>12.21</t>
+  </si>
+  <si>
+    <t>0.67</t>
+  </si>
+  <si>
+    <t>7.92</t>
+  </si>
+  <si>
+    <t>6.02</t>
+  </si>
+  <si>
+    <t>7.88</t>
   </si>
   <si>
     <t>RENTABILIDAD</t>
@@ -2669,7 +2669,7 @@
         <v>45719.0</v>
       </c>
       <c r="D4" s="15">
-        <v>2434.0</v>
+        <v>4764.0</v>
       </c>
       <c r="E4" s="15" t="s">
         <v>16</v>
@@ -2711,7 +2711,7 @@
         <v>45719.0</v>
       </c>
       <c r="D5" s="15">
-        <v>4863.0</v>
+        <v>4522.0</v>
       </c>
       <c r="E5" s="15" t="s">
         <v>16</v>
@@ -2720,7 +2720,7 @@
         <v>0.915878551187452</v>
       </c>
       <c r="G5" s="17">
-        <v>60.0</v>
+        <v>80.0</v>
       </c>
       <c r="H5" s="17"/>
       <c r="I5" s="17"/>
@@ -2728,7 +2728,7 @@
       <c r="K5" s="20"/>
       <c r="L5" s="26">
         <f>G5*'Data preparation'!$C$2</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M5" s="17">
         <v>44.2285986997841</v>
@@ -2753,7 +2753,7 @@
         <v>45720.0</v>
       </c>
       <c r="D6" s="15">
-        <v>5130.0</v>
+        <v>4486.0</v>
       </c>
       <c r="E6" s="15" t="s">
         <v>16</v>
@@ -2762,7 +2762,7 @@
         <v>1.01391936314265</v>
       </c>
       <c r="G6" s="17">
-        <v>60.0</v>
+        <v>80.0</v>
       </c>
       <c r="H6" s="17"/>
       <c r="I6" s="17"/>
@@ -2770,7 +2770,7 @@
       <c r="K6" s="20"/>
       <c r="L6" s="26">
         <f>G6*'Data preparation'!$C$2</f>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M6" s="31">
         <v>130.781744775489</v>
@@ -2795,7 +2795,7 @@
         <v>45720.0</v>
       </c>
       <c r="D7" s="15">
-        <v>4599.0</v>
+        <v>2516.0</v>
       </c>
       <c r="E7" s="15" t="s">
         <v>16</v>
@@ -2804,7 +2804,7 @@
         <v>0.707906165804836</v>
       </c>
       <c r="G7" s="17">
-        <v>40.0</v>
+        <v>20.0</v>
       </c>
       <c r="H7" s="18"/>
       <c r="I7" s="18"/>
@@ -2812,7 +2812,7 @@
       <c r="K7" s="20"/>
       <c r="L7" s="26">
         <f>G7*'Data preparation'!$C$2</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M7" s="17">
         <v>2.431963389625</v>
@@ -2837,7 +2837,7 @@
         <v>45720.0</v>
       </c>
       <c r="D8" s="15">
-        <v>5142.0</v>
+        <v>5132.0</v>
       </c>
       <c r="E8" s="15" t="s">
         <v>16</v>
@@ -2846,7 +2846,7 @@
         <v>0.853203073952881</v>
       </c>
       <c r="G8" s="17">
-        <v>80.0</v>
+        <v>60.0</v>
       </c>
       <c r="H8" s="18"/>
       <c r="I8" s="18"/>
@@ -2854,7 +2854,7 @@
       <c r="K8" s="20"/>
       <c r="L8" s="26">
         <f>G8*'Data preparation'!$C$2</f>
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="M8" s="17">
         <v>17.4200531203877</v>
@@ -19050,7 +19050,7 @@
       <c r="C37" s="43"/>
       <c r="D37" s="137">
         <f>AVERAGE(D39:D1775)</f>
-        <v>3.910208333</v>
+        <v>6.178541667</v>
       </c>
       <c r="G37" s="36" t="s">
         <v>71</v>
@@ -19119,7 +19119,7 @@
       </c>
       <c r="D39" s="129">
         <f t="shared" ref="D39:D221" si="17">IF(COUNTA(C39)=1,C39/1,"")</f>
-        <v>3.58</v>
+        <v>4.84</v>
       </c>
       <c r="G39" s="36" t="s">
         <v>63</v>
@@ -19157,7 +19157,7 @@
       </c>
       <c r="D40" s="129">
         <f t="shared" si="17"/>
-        <v>3.79</v>
+        <v>4.18</v>
       </c>
       <c r="G40" s="36" t="s">
         <v>59</v>
@@ -19195,7 +19195,7 @@
       </c>
       <c r="D41" s="129">
         <f t="shared" si="17"/>
-        <v>4.09</v>
+        <v>4.8</v>
       </c>
       <c r="P41" s="127">
         <v>0.0</v>
@@ -19227,7 +19227,7 @@
       </c>
       <c r="D42" s="129">
         <f t="shared" si="17"/>
-        <v>4.96</v>
+        <v>1.64</v>
       </c>
       <c r="P42" s="127">
         <v>2.0</v>
@@ -19259,7 +19259,7 @@
       </c>
       <c r="D43" s="129">
         <f t="shared" si="17"/>
-        <v>3.62</v>
+        <v>1.05</v>
       </c>
       <c r="P43" s="127">
         <v>1.0</v>
@@ -19291,7 +19291,7 @@
       </c>
       <c r="D44" s="129">
         <f t="shared" si="17"/>
-        <v>3.72</v>
+        <v>7.12</v>
       </c>
       <c r="P44" s="127">
         <v>2.0</v>
@@ -19321,7 +19321,7 @@
       </c>
       <c r="D45" s="129">
         <f t="shared" si="17"/>
-        <v>4.81</v>
+        <v>10.03</v>
       </c>
       <c r="P45" s="127">
         <v>1.0</v>
@@ -19339,7 +19339,7 @@
       </c>
       <c r="D46" s="129">
         <f t="shared" si="17"/>
-        <v>0.55</v>
+        <v>6.64</v>
       </c>
       <c r="G46" s="101" t="s">
         <v>251</v>
@@ -19363,7 +19363,7 @@
       </c>
       <c r="D47" s="129">
         <f t="shared" si="17"/>
-        <v>2.41</v>
+        <v>5.4</v>
       </c>
       <c r="G47" s="106" t="s">
         <v>72</v>
@@ -19393,7 +19393,7 @@
       </c>
       <c r="D48" s="129">
         <f t="shared" si="17"/>
-        <v>3.47</v>
+        <v>5.92</v>
       </c>
       <c r="G48" s="106" t="s">
         <v>71</v>
@@ -19430,7 +19430,7 @@
       </c>
       <c r="D49" s="129">
         <f t="shared" si="17"/>
-        <v>3.57</v>
+        <v>5.9</v>
       </c>
       <c r="G49" s="106" t="s">
         <v>62</v>
@@ -19467,7 +19467,7 @@
       </c>
       <c r="D50" s="129">
         <f t="shared" si="17"/>
-        <v>5.31</v>
+        <v>10.26</v>
       </c>
       <c r="G50" s="106" t="s">
         <v>63</v>
@@ -19504,7 +19504,7 @@
       </c>
       <c r="D51" s="129">
         <f t="shared" si="17"/>
-        <v>4.03</v>
+        <v>5.99</v>
       </c>
       <c r="G51" s="106" t="s">
         <v>59</v>
@@ -19541,7 +19541,7 @@
       </c>
       <c r="D52" s="129">
         <f t="shared" si="17"/>
-        <v>4.07</v>
+        <v>9.16</v>
       </c>
       <c r="P52" s="127">
         <v>0.0</v>
@@ -19565,7 +19565,7 @@
       </c>
       <c r="D53" s="129">
         <f t="shared" si="17"/>
-        <v>3.27</v>
+        <v>4.86</v>
       </c>
       <c r="P53" s="127">
         <v>0.0</v>
@@ -19589,7 +19589,7 @@
       </c>
       <c r="D54" s="129">
         <f t="shared" si="17"/>
-        <v>0.58</v>
+        <v>6.89</v>
       </c>
       <c r="P54" s="127">
         <v>2.0</v>
@@ -19613,7 +19613,7 @@
       </c>
       <c r="D55" s="129">
         <f t="shared" si="17"/>
-        <v>3.38</v>
+        <v>8.85</v>
       </c>
       <c r="P55" s="127">
         <v>0.0</v>
@@ -19637,7 +19637,7 @@
       </c>
       <c r="D56" s="129">
         <f t="shared" si="17"/>
-        <v>3.24</v>
+        <v>8.58</v>
       </c>
       <c r="P56" s="127">
         <v>0.0</v>
@@ -19661,7 +19661,7 @@
       </c>
       <c r="D57" s="129">
         <f t="shared" si="17"/>
-        <v>1.57</v>
+        <v>1.18</v>
       </c>
       <c r="P57" s="127">
         <v>2.0</v>
@@ -19685,7 +19685,7 @@
       </c>
       <c r="D58" s="129">
         <f t="shared" si="17"/>
-        <v>5.69</v>
+        <v>5.6</v>
       </c>
       <c r="G58" s="142" t="s">
         <v>269</v>
@@ -19713,7 +19713,7 @@
       </c>
       <c r="D59" s="129">
         <f t="shared" si="17"/>
-        <v>5.89</v>
+        <v>5.04</v>
       </c>
       <c r="G59" s="143"/>
       <c r="H59" s="144" t="s">
@@ -19741,7 +19741,7 @@
       </c>
       <c r="D60" s="129">
         <f t="shared" si="17"/>
-        <v>5.55</v>
+        <v>10.85</v>
       </c>
       <c r="G60" s="143"/>
       <c r="H60" s="144" t="s">
@@ -19769,7 +19769,7 @@
       </c>
       <c r="D61" s="129">
         <f t="shared" si="17"/>
-        <v>5.39</v>
+        <v>10.58</v>
       </c>
       <c r="G61" s="143"/>
       <c r="H61" s="144" t="s">
@@ -19797,7 +19797,7 @@
       </c>
       <c r="D62" s="129">
         <f t="shared" si="17"/>
-        <v>6.13</v>
+        <v>8.46</v>
       </c>
       <c r="G62" s="143"/>
       <c r="H62" s="144" t="s">
@@ -19825,7 +19825,7 @@
       </c>
       <c r="D63" s="129">
         <f t="shared" si="17"/>
-        <v>4.32</v>
+        <v>5.03</v>
       </c>
       <c r="G63" s="143"/>
       <c r="H63" s="144" t="s">
@@ -19847,7 +19847,7 @@
       </c>
       <c r="D64" s="129">
         <f t="shared" si="17"/>
-        <v>0.86</v>
+        <v>7.01</v>
       </c>
       <c r="P64" s="127">
         <v>1.0</v>
@@ -19865,7 +19865,7 @@
       </c>
       <c r="D65" s="129">
         <f t="shared" si="17"/>
-        <v>4.25</v>
+        <v>5.14</v>
       </c>
       <c r="P65" s="127">
         <v>2.0</v>
@@ -19883,7 +19883,7 @@
       </c>
       <c r="D66" s="129">
         <f t="shared" si="17"/>
-        <v>4.02</v>
+        <v>5.77</v>
       </c>
       <c r="P66" s="127">
         <v>0.0</v>
@@ -19901,7 +19901,7 @@
       </c>
       <c r="D67" s="129">
         <f t="shared" si="17"/>
-        <v>1.67</v>
+        <v>3.45</v>
       </c>
       <c r="P67" s="127">
         <v>0.0</v>
@@ -19919,7 +19919,7 @@
       </c>
       <c r="D68" s="129">
         <f t="shared" si="17"/>
-        <v>2.77</v>
+        <v>6.06</v>
       </c>
       <c r="P68" s="127">
         <v>1.0</v>
@@ -19937,7 +19937,7 @@
       </c>
       <c r="D69" s="129">
         <f t="shared" si="17"/>
-        <v>0.38</v>
+        <v>4.64</v>
       </c>
       <c r="P69" s="127">
         <v>2.0</v>
@@ -19955,7 +19955,7 @@
       </c>
       <c r="D70" s="129">
         <f t="shared" si="17"/>
-        <v>3.61</v>
+        <v>4.97</v>
       </c>
       <c r="P70" s="127">
         <v>1.0</v>
@@ -19969,11 +19969,11 @@
     </row>
     <row r="71">
       <c r="C71" s="140" t="s">
-        <v>287</v>
+        <v>264</v>
       </c>
       <c r="D71" s="129">
         <f t="shared" si="17"/>
-        <v>3.37</v>
+        <v>6.89</v>
       </c>
       <c r="F71" s="145"/>
       <c r="P71" s="127">
@@ -19988,11 +19988,11 @@
     </row>
     <row r="72">
       <c r="C72" s="140" t="s">
-        <v>203</v>
+        <v>287</v>
       </c>
       <c r="D72" s="129">
         <f t="shared" si="17"/>
-        <v>3.51</v>
+        <v>7</v>
       </c>
       <c r="P72" s="127">
         <v>0.0</v>
@@ -20010,7 +20010,7 @@
       </c>
       <c r="D73" s="129">
         <f t="shared" si="17"/>
-        <v>2.46</v>
+        <v>5.88</v>
       </c>
       <c r="P73" s="127">
         <v>1.0</v>
@@ -20028,7 +20028,7 @@
       </c>
       <c r="D74" s="129">
         <f t="shared" si="17"/>
-        <v>3.86</v>
+        <v>7.17</v>
       </c>
       <c r="P74" s="127">
         <v>0.0</v>
@@ -20046,7 +20046,7 @@
       </c>
       <c r="D75" s="129">
         <f t="shared" si="17"/>
-        <v>2.15</v>
+        <v>5.09</v>
       </c>
       <c r="P75" s="127">
         <v>1.0</v>
@@ -20064,7 +20064,7 @@
       </c>
       <c r="D76" s="129">
         <f t="shared" si="17"/>
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="P76" s="127">
         <v>0.0</v>
@@ -20082,7 +20082,7 @@
       </c>
       <c r="D77" s="129">
         <f t="shared" si="17"/>
-        <v>5.37</v>
+        <v>3.13</v>
       </c>
       <c r="P77" s="127">
         <v>0.0</v>
@@ -20100,7 +20100,7 @@
       </c>
       <c r="D78" s="129">
         <f t="shared" si="17"/>
-        <v>3.77</v>
+        <v>6.29</v>
       </c>
       <c r="P78" s="127">
         <v>1.0</v>
@@ -20118,7 +20118,7 @@
       </c>
       <c r="D79" s="129">
         <f t="shared" si="17"/>
-        <v>6.1</v>
+        <v>6.34</v>
       </c>
       <c r="P79" s="127">
         <v>2.0</v>
@@ -20136,7 +20136,7 @@
       </c>
       <c r="D80" s="129">
         <f t="shared" si="17"/>
-        <v>7.54</v>
+        <v>4.99</v>
       </c>
       <c r="P80" s="127">
         <v>1.0</v>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="D81" s="129">
         <f t="shared" si="17"/>
-        <v>5.07</v>
+        <v>10.6</v>
       </c>
       <c r="P81" s="127">
         <v>2.0</v>
@@ -20172,7 +20172,7 @@
       </c>
       <c r="D82" s="129">
         <f t="shared" si="17"/>
-        <v>7</v>
+        <v>12.21</v>
       </c>
       <c r="P82" s="127">
         <v>1.0</v>
@@ -20190,7 +20190,7 @@
       </c>
       <c r="D83" s="129">
         <f t="shared" si="17"/>
-        <v>6.45</v>
+        <v>0.67</v>
       </c>
       <c r="P83" s="127">
         <v>0.0</v>
@@ -20208,7 +20208,7 @@
       </c>
       <c r="D84" s="129">
         <f t="shared" si="17"/>
-        <v>6.3</v>
+        <v>7.92</v>
       </c>
       <c r="P84" s="127">
         <v>1.0</v>
@@ -20226,7 +20226,7 @@
       </c>
       <c r="D85" s="129">
         <f t="shared" si="17"/>
-        <v>3.93</v>
+        <v>6.02</v>
       </c>
       <c r="P85" s="127">
         <v>0.0</v>
@@ -20244,7 +20244,7 @@
       </c>
       <c r="D86" s="129">
         <f t="shared" si="17"/>
-        <v>3.59</v>
+        <v>7.88</v>
       </c>
       <c r="P86" s="127">
         <v>0.0</v>
@@ -45984,10 +45984,18 @@
       <c r="R70" s="9"/>
       <c r="S70" s="9"/>
       <c r="T70" s="9"/>
-      <c r="U70" s="9"/>
-      <c r="V70" s="9"/>
-      <c r="W70" s="9"/>
-      <c r="X70" s="9"/>
+      <c r="U70" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="V70" s="97">
+        <v>3526.0</v>
+      </c>
+      <c r="W70" s="97">
+        <v>3574.0</v>
+      </c>
+      <c r="X70" s="57">
+        <v>4764.0</v>
+      </c>
       <c r="Y70" s="9"/>
       <c r="Z70" s="9"/>
       <c r="AA70" s="9"/>
@@ -46023,10 +46031,12 @@
       <c r="R71" s="9"/>
       <c r="S71" s="9"/>
       <c r="T71" s="9"/>
-      <c r="U71" s="9"/>
-      <c r="V71" s="9"/>
-      <c r="W71" s="9"/>
-      <c r="X71" s="9"/>
+      <c r="U71" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="V71" s="57">
+        <v>4522.0</v>
+      </c>
       <c r="Y71" s="9"/>
       <c r="Z71" s="9"/>
       <c r="AA71" s="9"/>
@@ -46062,10 +46072,15 @@
       <c r="R72" s="9"/>
       <c r="S72" s="9"/>
       <c r="T72" s="9"/>
-      <c r="U72" s="9"/>
-      <c r="V72" s="9"/>
-      <c r="W72" s="9"/>
-      <c r="X72" s="9"/>
+      <c r="U72" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="V72" s="53">
+        <v>5130.0</v>
+      </c>
+      <c r="W72" s="57">
+        <v>4486.0</v>
+      </c>
       <c r="Y72" s="9"/>
       <c r="Z72" s="9"/>
       <c r="AA72" s="9"/>
@@ -46101,10 +46116,15 @@
       <c r="R73" s="9"/>
       <c r="S73" s="9"/>
       <c r="T73" s="9"/>
-      <c r="U73" s="9"/>
-      <c r="V73" s="9"/>
-      <c r="W73" s="9"/>
-      <c r="X73" s="9"/>
+      <c r="U73" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="V73" s="57">
+        <v>2516.0</v>
+      </c>
+      <c r="W73" s="37">
+        <v>2114.0</v>
+      </c>
       <c r="Y73" s="9"/>
       <c r="Z73" s="9"/>
       <c r="AA73" s="9"/>
@@ -46140,10 +46160,15 @@
       <c r="R74" s="9"/>
       <c r="S74" s="9"/>
       <c r="T74" s="9"/>
-      <c r="U74" s="9"/>
-      <c r="V74" s="9"/>
-      <c r="W74" s="9"/>
-      <c r="X74" s="9"/>
+      <c r="U74" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="V74" s="97">
+        <v>5142.0</v>
+      </c>
+      <c r="W74" s="57">
+        <v>5132.0</v>
+      </c>
       <c r="Y74" s="9"/>
       <c r="Z74" s="9"/>
       <c r="AA74" s="9"/>

--- a/data/df_best_models.xlsx
+++ b/data/df_best_models.xlsx
@@ -274,7 +274,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="337">
   <si>
     <t>id_country</t>
   </si>
@@ -1111,28 +1111,28 @@
     <t>Stake promedio</t>
   </si>
   <si>
-    <t>4.84</t>
+    <t>5.98</t>
   </si>
   <si>
-    <t>4.18</t>
+    <t>5.82</t>
   </si>
   <si>
-    <t>4.80</t>
+    <t>4.89</t>
   </si>
   <si>
-    <t>1.64</t>
+    <t>6.59</t>
   </si>
   <si>
-    <t>1.05</t>
+    <t>8.42</t>
   </si>
   <si>
-    <t>7.12</t>
+    <t>5.34</t>
   </si>
   <si>
-    <t>10.03</t>
+    <t>7.38</t>
   </si>
   <si>
-    <t>6.64</t>
+    <t>7.95</t>
   </si>
   <si>
     <t>Country</t>
@@ -1141,151 +1141,148 @@
     <t>Correl ROI y Expected ROI</t>
   </si>
   <si>
-    <t>5.40</t>
+    <t>6.06</t>
   </si>
   <si>
-    <t>5.92</t>
+    <t>0.81</t>
   </si>
   <si>
     <t>mean</t>
   </si>
   <si>
-    <t>5.90</t>
+    <t>6.46</t>
   </si>
   <si>
     <t>median</t>
   </si>
   <si>
-    <t>10.26</t>
+    <t>10.16</t>
   </si>
   <si>
     <t>p25</t>
   </si>
   <si>
-    <t>5.99</t>
+    <t>5.08</t>
   </si>
   <si>
     <t>p75</t>
   </si>
   <si>
-    <t>9.16</t>
+    <t>6.77</t>
   </si>
   <si>
-    <t>4.86</t>
+    <t>1.08</t>
   </si>
   <si>
-    <t>6.89</t>
+    <t>8.41</t>
   </si>
   <si>
-    <t>8.85</t>
+    <t>6.84</t>
   </si>
   <si>
-    <t>8.58</t>
+    <t>5.65</t>
   </si>
   <si>
-    <t>1.18</t>
-  </si>
-  <si>
-    <t>5.60</t>
+    <t>7.16</t>
   </si>
   <si>
     <t>Gracias a las nuevas métricas de G/P sin bank en test, me di cuenta de que:</t>
   </si>
   <si>
-    <t>5.04</t>
+    <t>12.24</t>
   </si>
   <si>
     <t>La rentabilidad en ITA está en el visitante y no en el empate como creía.</t>
   </si>
   <si>
-    <t>10.85</t>
+    <t>11.12</t>
   </si>
   <si>
     <t>La rentabilidad en ENG y GER está en el empate tal como creía.</t>
   </si>
   <si>
-    <t>10.58</t>
+    <t>12.96</t>
   </si>
   <si>
     <t>En SPA esta repartido aunque Empate saca una ventaja.</t>
   </si>
   <si>
-    <t>8.46</t>
+    <t>11.90</t>
   </si>
   <si>
     <t>En FRA, depende el modelo. A veces local, a veces, empate.</t>
   </si>
   <si>
-    <t>5.03</t>
+    <t>7.74</t>
   </si>
   <si>
     <t>Si en FRA empate no rinde, no tiene sentido exigirle una buena distrib en empate… → Tiene sentido pero al parecer si importa el empate puesto que el modelo que gana se basa en empate.</t>
   </si>
   <si>
-    <t>7.01</t>
+    <t>7.76</t>
   </si>
   <si>
-    <t>5.14</t>
+    <t>0.73</t>
   </si>
   <si>
-    <t>5.77</t>
+    <t>7.55</t>
   </si>
   <si>
-    <t>3.45</t>
+    <t>2.64</t>
   </si>
   <si>
-    <t>6.06</t>
+    <t>1.99</t>
   </si>
   <si>
-    <t>4.64</t>
+    <t>1.67</t>
   </si>
   <si>
-    <t>4.97</t>
+    <t>2.61</t>
   </si>
   <si>
-    <t>7.00</t>
+    <t>0.18</t>
   </si>
   <si>
-    <t>5.88</t>
+    <t>3.46</t>
   </si>
   <si>
-    <t>7.17</t>
+    <t>3.84</t>
   </si>
   <si>
-    <t>5.09</t>
+    <t>2.89</t>
   </si>
   <si>
-    <t>2.60</t>
+    <t>2.34</t>
   </si>
   <si>
-    <t>3.13</t>
+    <t>1.36</t>
   </si>
   <si>
-    <t>6.29</t>
+    <t>4.88</t>
   </si>
   <si>
-    <t>6.34</t>
+    <t>2.42</t>
   </si>
   <si>
-    <t>4.99</t>
+    <t>0.53</t>
   </si>
   <si>
-    <t>10.60</t>
+    <t>7.18</t>
   </si>
   <si>
-    <t>12.21</t>
+    <t>6.82</t>
   </si>
   <si>
-    <t>0.67</t>
+    <t>3.14</t>
   </si>
   <si>
-    <t>7.92</t>
+    <t>0.43</t>
   </si>
   <si>
-    <t>6.02</t>
+    <t>4.34</t>
   </si>
   <si>
-    <t>7.88</t>
+    <t>5.16</t>
   </si>
   <si>
     <t>RENTABILIDAD</t>
@@ -2795,7 +2792,7 @@
         <v>45720.0</v>
       </c>
       <c r="D7" s="15">
-        <v>2516.0</v>
+        <v>2114.0</v>
       </c>
       <c r="E7" s="15" t="s">
         <v>16</v>
@@ -2804,7 +2801,7 @@
         <v>0.707906165804836</v>
       </c>
       <c r="G7" s="17">
-        <v>20.0</v>
+        <v>40.0</v>
       </c>
       <c r="H7" s="18"/>
       <c r="I7" s="18"/>
@@ -2812,7 +2809,7 @@
       <c r="K7" s="20"/>
       <c r="L7" s="26">
         <f>G7*'Data preparation'!$C$2</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M7" s="17">
         <v>2.431963389625</v>
@@ -17749,7 +17746,7 @@
       </c>
       <c r="C3" s="25">
         <f>AVERAGE('Modelos actuales'!L4:L8)</f>
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="L3" s="123"/>
       <c r="P3" s="123"/>
@@ -19050,7 +19047,7 @@
       <c r="C37" s="43"/>
       <c r="D37" s="137">
         <f>AVERAGE(D39:D1775)</f>
-        <v>6.178541667</v>
+        <v>5.356041667</v>
       </c>
       <c r="G37" s="36" t="s">
         <v>71</v>
@@ -19119,7 +19116,7 @@
       </c>
       <c r="D39" s="129">
         <f t="shared" ref="D39:D221" si="17">IF(COUNTA(C39)=1,C39/1,"")</f>
-        <v>4.84</v>
+        <v>5.98</v>
       </c>
       <c r="G39" s="36" t="s">
         <v>63</v>
@@ -19157,7 +19154,7 @@
       </c>
       <c r="D40" s="129">
         <f t="shared" si="17"/>
-        <v>4.18</v>
+        <v>5.82</v>
       </c>
       <c r="G40" s="36" t="s">
         <v>59</v>
@@ -19195,7 +19192,7 @@
       </c>
       <c r="D41" s="129">
         <f t="shared" si="17"/>
-        <v>4.8</v>
+        <v>4.89</v>
       </c>
       <c r="P41" s="127">
         <v>0.0</v>
@@ -19227,7 +19224,7 @@
       </c>
       <c r="D42" s="129">
         <f t="shared" si="17"/>
-        <v>1.64</v>
+        <v>6.59</v>
       </c>
       <c r="P42" s="127">
         <v>2.0</v>
@@ -19259,7 +19256,7 @@
       </c>
       <c r="D43" s="129">
         <f t="shared" si="17"/>
-        <v>1.05</v>
+        <v>8.42</v>
       </c>
       <c r="P43" s="127">
         <v>1.0</v>
@@ -19291,7 +19288,7 @@
       </c>
       <c r="D44" s="129">
         <f t="shared" si="17"/>
-        <v>7.12</v>
+        <v>5.34</v>
       </c>
       <c r="P44" s="127">
         <v>2.0</v>
@@ -19321,7 +19318,7 @@
       </c>
       <c r="D45" s="129">
         <f t="shared" si="17"/>
-        <v>10.03</v>
+        <v>7.38</v>
       </c>
       <c r="P45" s="127">
         <v>1.0</v>
@@ -19339,7 +19336,7 @@
       </c>
       <c r="D46" s="129">
         <f t="shared" si="17"/>
-        <v>6.64</v>
+        <v>7.95</v>
       </c>
       <c r="G46" s="101" t="s">
         <v>251</v>
@@ -19363,7 +19360,7 @@
       </c>
       <c r="D47" s="129">
         <f t="shared" si="17"/>
-        <v>5.4</v>
+        <v>6.06</v>
       </c>
       <c r="G47" s="106" t="s">
         <v>72</v>
@@ -19393,7 +19390,7 @@
       </c>
       <c r="D48" s="129">
         <f t="shared" si="17"/>
-        <v>5.92</v>
+        <v>0.81</v>
       </c>
       <c r="G48" s="106" t="s">
         <v>71</v>
@@ -19430,7 +19427,7 @@
       </c>
       <c r="D49" s="129">
         <f t="shared" si="17"/>
-        <v>5.9</v>
+        <v>6.46</v>
       </c>
       <c r="G49" s="106" t="s">
         <v>62</v>
@@ -19467,7 +19464,7 @@
       </c>
       <c r="D50" s="129">
         <f t="shared" si="17"/>
-        <v>10.26</v>
+        <v>10.16</v>
       </c>
       <c r="G50" s="106" t="s">
         <v>63</v>
@@ -19504,7 +19501,7 @@
       </c>
       <c r="D51" s="129">
         <f t="shared" si="17"/>
-        <v>5.99</v>
+        <v>5.08</v>
       </c>
       <c r="G51" s="106" t="s">
         <v>59</v>
@@ -19541,7 +19538,7 @@
       </c>
       <c r="D52" s="129">
         <f t="shared" si="17"/>
-        <v>9.16</v>
+        <v>6.77</v>
       </c>
       <c r="P52" s="127">
         <v>0.0</v>
@@ -19561,11 +19558,11 @@
     </row>
     <row r="53">
       <c r="C53" s="140" t="s">
-        <v>263</v>
+        <v>244</v>
       </c>
       <c r="D53" s="129">
         <f t="shared" si="17"/>
-        <v>4.86</v>
+        <v>5.82</v>
       </c>
       <c r="P53" s="127">
         <v>0.0</v>
@@ -19585,11 +19582,11 @@
     </row>
     <row r="54">
       <c r="C54" s="140" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D54" s="129">
         <f t="shared" si="17"/>
-        <v>6.89</v>
+        <v>1.08</v>
       </c>
       <c r="P54" s="127">
         <v>2.0</v>
@@ -19609,11 +19606,11 @@
     </row>
     <row r="55">
       <c r="C55" s="140" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D55" s="129">
         <f t="shared" si="17"/>
-        <v>8.85</v>
+        <v>8.41</v>
       </c>
       <c r="P55" s="127">
         <v>0.0</v>
@@ -19633,11 +19630,11 @@
     </row>
     <row r="56">
       <c r="C56" s="140" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D56" s="129">
         <f t="shared" si="17"/>
-        <v>8.58</v>
+        <v>6.84</v>
       </c>
       <c r="P56" s="127">
         <v>0.0</v>
@@ -19657,11 +19654,11 @@
     </row>
     <row r="57">
       <c r="C57" s="140" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D57" s="129">
         <f t="shared" si="17"/>
-        <v>1.18</v>
+        <v>5.65</v>
       </c>
       <c r="P57" s="127">
         <v>2.0</v>
@@ -19681,14 +19678,14 @@
     </row>
     <row r="58">
       <c r="C58" s="140" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D58" s="129">
         <f t="shared" si="17"/>
-        <v>5.6</v>
+        <v>7.16</v>
       </c>
       <c r="G58" s="142" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H58" s="143"/>
       <c r="P58" s="127">
@@ -19709,15 +19706,15 @@
     </row>
     <row r="59">
       <c r="C59" s="140" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D59" s="129">
         <f t="shared" si="17"/>
-        <v>5.04</v>
+        <v>12.24</v>
       </c>
       <c r="G59" s="143"/>
       <c r="H59" s="144" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P59" s="127">
         <v>0.0</v>
@@ -19737,15 +19734,15 @@
     </row>
     <row r="60">
       <c r="C60" s="140" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D60" s="129">
         <f t="shared" si="17"/>
-        <v>10.85</v>
+        <v>11.12</v>
       </c>
       <c r="G60" s="143"/>
       <c r="H60" s="144" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="P60" s="127">
         <v>2.0</v>
@@ -19765,15 +19762,15 @@
     </row>
     <row r="61">
       <c r="C61" s="140" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D61" s="129">
         <f t="shared" si="17"/>
-        <v>10.58</v>
+        <v>12.96</v>
       </c>
       <c r="G61" s="143"/>
       <c r="H61" s="144" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P61" s="127">
         <v>2.0</v>
@@ -19793,15 +19790,15 @@
     </row>
     <row r="62">
       <c r="C62" s="140" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D62" s="129">
         <f t="shared" si="17"/>
-        <v>8.46</v>
+        <v>11.9</v>
       </c>
       <c r="G62" s="143"/>
       <c r="H62" s="144" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="P62" s="127">
         <v>1.0</v>
@@ -19821,15 +19818,15 @@
     </row>
     <row r="63">
       <c r="C63" s="140" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D63" s="129">
         <f t="shared" si="17"/>
-        <v>5.03</v>
+        <v>7.74</v>
       </c>
       <c r="G63" s="143"/>
       <c r="H63" s="144" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="P63" s="127">
         <v>0.0</v>
@@ -19843,11 +19840,11 @@
     </row>
     <row r="64">
       <c r="C64" s="140" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D64" s="129">
         <f t="shared" si="17"/>
-        <v>7.01</v>
+        <v>7.76</v>
       </c>
       <c r="P64" s="127">
         <v>1.0</v>
@@ -19861,11 +19858,11 @@
     </row>
     <row r="65">
       <c r="C65" s="140" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D65" s="129">
         <f t="shared" si="17"/>
-        <v>5.14</v>
+        <v>0.73</v>
       </c>
       <c r="P65" s="127">
         <v>2.0</v>
@@ -19879,11 +19876,11 @@
     </row>
     <row r="66">
       <c r="C66" s="140" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D66" s="129">
         <f t="shared" si="17"/>
-        <v>5.77</v>
+        <v>7.55</v>
       </c>
       <c r="P66" s="127">
         <v>0.0</v>
@@ -19897,11 +19894,11 @@
     </row>
     <row r="67">
       <c r="C67" s="140" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D67" s="129">
         <f t="shared" si="17"/>
-        <v>3.45</v>
+        <v>2.64</v>
       </c>
       <c r="P67" s="127">
         <v>0.0</v>
@@ -19915,11 +19912,11 @@
     </row>
     <row r="68">
       <c r="C68" s="140" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D68" s="129">
         <f t="shared" si="17"/>
-        <v>6.06</v>
+        <v>1.99</v>
       </c>
       <c r="P68" s="127">
         <v>1.0</v>
@@ -19933,11 +19930,11 @@
     </row>
     <row r="69">
       <c r="C69" s="140" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D69" s="129">
         <f t="shared" si="17"/>
-        <v>4.64</v>
+        <v>1.67</v>
       </c>
       <c r="P69" s="127">
         <v>2.0</v>
@@ -19951,11 +19948,11 @@
     </row>
     <row r="70">
       <c r="C70" s="140" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D70" s="129">
         <f t="shared" si="17"/>
-        <v>4.97</v>
+        <v>2.61</v>
       </c>
       <c r="P70" s="127">
         <v>1.0</v>
@@ -19969,11 +19966,11 @@
     </row>
     <row r="71">
       <c r="C71" s="140" t="s">
-        <v>264</v>
+        <v>286</v>
       </c>
       <c r="D71" s="129">
         <f t="shared" si="17"/>
-        <v>6.89</v>
+        <v>0.18</v>
       </c>
       <c r="F71" s="145"/>
       <c r="P71" s="127">
@@ -19992,7 +19989,7 @@
       </c>
       <c r="D72" s="129">
         <f t="shared" si="17"/>
-        <v>7</v>
+        <v>3.46</v>
       </c>
       <c r="P72" s="127">
         <v>0.0</v>
@@ -20010,7 +20007,7 @@
       </c>
       <c r="D73" s="129">
         <f t="shared" si="17"/>
-        <v>5.88</v>
+        <v>3.84</v>
       </c>
       <c r="P73" s="127">
         <v>1.0</v>
@@ -20028,7 +20025,7 @@
       </c>
       <c r="D74" s="129">
         <f t="shared" si="17"/>
-        <v>7.17</v>
+        <v>2.89</v>
       </c>
       <c r="P74" s="127">
         <v>0.0</v>
@@ -20046,7 +20043,7 @@
       </c>
       <c r="D75" s="129">
         <f t="shared" si="17"/>
-        <v>5.09</v>
+        <v>2.34</v>
       </c>
       <c r="P75" s="127">
         <v>1.0</v>
@@ -20064,7 +20061,7 @@
       </c>
       <c r="D76" s="129">
         <f t="shared" si="17"/>
-        <v>2.6</v>
+        <v>1.36</v>
       </c>
       <c r="P76" s="127">
         <v>0.0</v>
@@ -20078,11 +20075,11 @@
     </row>
     <row r="77">
       <c r="C77" s="140" t="s">
-        <v>292</v>
+        <v>238</v>
       </c>
       <c r="D77" s="129">
         <f t="shared" si="17"/>
-        <v>3.13</v>
+        <v>4.54</v>
       </c>
       <c r="P77" s="127">
         <v>0.0</v>
@@ -20096,11 +20093,11 @@
     </row>
     <row r="78">
       <c r="C78" s="140" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D78" s="129">
         <f t="shared" si="17"/>
-        <v>6.29</v>
+        <v>4.88</v>
       </c>
       <c r="P78" s="127">
         <v>1.0</v>
@@ -20114,11 +20111,11 @@
     </row>
     <row r="79">
       <c r="C79" s="140" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D79" s="129">
         <f t="shared" si="17"/>
-        <v>6.34</v>
+        <v>2.42</v>
       </c>
       <c r="P79" s="127">
         <v>2.0</v>
@@ -20132,11 +20129,11 @@
     </row>
     <row r="80">
       <c r="C80" s="140" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D80" s="129">
         <f t="shared" si="17"/>
-        <v>4.99</v>
+        <v>0.53</v>
       </c>
       <c r="P80" s="127">
         <v>1.0</v>
@@ -20150,11 +20147,11 @@
     </row>
     <row r="81">
       <c r="C81" s="140" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D81" s="129">
         <f t="shared" si="17"/>
-        <v>10.6</v>
+        <v>7.18</v>
       </c>
       <c r="P81" s="127">
         <v>2.0</v>
@@ -20168,11 +20165,11 @@
     </row>
     <row r="82">
       <c r="C82" s="140" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D82" s="129">
         <f t="shared" si="17"/>
-        <v>12.21</v>
+        <v>6.82</v>
       </c>
       <c r="P82" s="127">
         <v>1.0</v>
@@ -20186,11 +20183,11 @@
     </row>
     <row r="83">
       <c r="C83" s="140" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D83" s="129">
         <f t="shared" si="17"/>
-        <v>0.67</v>
+        <v>3.14</v>
       </c>
       <c r="P83" s="127">
         <v>0.0</v>
@@ -20204,11 +20201,11 @@
     </row>
     <row r="84">
       <c r="C84" s="140" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D84" s="129">
         <f t="shared" si="17"/>
-        <v>7.92</v>
+        <v>0.43</v>
       </c>
       <c r="P84" s="127">
         <v>1.0</v>
@@ -20222,11 +20219,11 @@
     </row>
     <row r="85">
       <c r="C85" s="140" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D85" s="129">
         <f t="shared" si="17"/>
-        <v>6.02</v>
+        <v>4.34</v>
       </c>
       <c r="P85" s="127">
         <v>0.0</v>
@@ -20240,11 +20237,11 @@
     </row>
     <row r="86">
       <c r="C86" s="140" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D86" s="129">
         <f t="shared" si="17"/>
-        <v>7.88</v>
+        <v>5.16</v>
       </c>
       <c r="P86" s="127">
         <v>0.0</v>
@@ -43294,14 +43291,14 @@
     <row r="1">
       <c r="A1" s="110"/>
       <c r="B1" s="150" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C1" s="151"/>
       <c r="D1" s="151"/>
       <c r="E1" s="151"/>
       <c r="F1" s="151"/>
       <c r="G1" s="152" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1" s="151"/>
       <c r="I1" s="151"/>
@@ -43335,19 +43332,19 @@
         <v>3</v>
       </c>
       <c r="B2" s="154" t="s">
+        <v>303</v>
+      </c>
+      <c r="C2" s="155" t="s">
         <v>304</v>
-      </c>
-      <c r="C2" s="155" t="s">
-        <v>305</v>
       </c>
       <c r="D2" s="155" t="s">
         <v>43</v>
       </c>
       <c r="E2" s="155" t="s">
+        <v>305</v>
+      </c>
+      <c r="F2" s="156" t="s">
         <v>306</v>
-      </c>
-      <c r="F2" s="156" t="s">
-        <v>307</v>
       </c>
       <c r="G2" s="154">
         <v>1.0</v>
@@ -43359,30 +43356,30 @@
         <v>2.0</v>
       </c>
       <c r="J2" s="155" t="s">
+        <v>307</v>
+      </c>
+      <c r="K2" s="157" t="s">
         <v>308</v>
       </c>
-      <c r="K2" s="157" t="s">
+      <c r="L2" s="155" t="s">
         <v>309</v>
       </c>
-      <c r="L2" s="155" t="s">
+      <c r="M2" s="158" t="s">
         <v>310</v>
       </c>
-      <c r="M2" s="158" t="s">
+      <c r="N2" s="106" t="s">
         <v>311</v>
       </c>
-      <c r="N2" s="106" t="s">
+      <c r="O2" s="106" t="s">
         <v>312</v>
       </c>
-      <c r="O2" s="106" t="s">
+      <c r="P2" s="106" t="s">
         <v>313</v>
-      </c>
-      <c r="P2" s="106" t="s">
-        <v>314</v>
       </c>
       <c r="Q2" s="9"/>
       <c r="R2" s="9"/>
       <c r="S2" s="100" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="T2" s="9"/>
       <c r="U2" s="9"/>
@@ -43472,7 +43469,7 @@
       <c r="Q4" s="9"/>
       <c r="R4" s="9"/>
       <c r="S4" s="164" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="T4" s="165"/>
       <c r="Z4" s="36"/>
@@ -43508,7 +43505,7 @@
       <c r="P5" s="167"/>
       <c r="S5" s="165"/>
       <c r="T5" s="168" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="6">
@@ -43541,11 +43538,11 @@
       <c r="R6" s="9"/>
       <c r="S6" s="165"/>
       <c r="T6" s="168" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="Z6" s="42"/>
       <c r="AD6" s="37" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="7">
@@ -43575,7 +43572,7 @@
       <c r="O7" s="84"/>
       <c r="P7" s="169"/>
       <c r="AD7" s="168" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="AE7" s="165"/>
       <c r="AF7" s="165"/>
@@ -43608,11 +43605,11 @@
       <c r="O8" s="84"/>
       <c r="P8" s="169"/>
       <c r="S8" s="168" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AA8" s="42"/>
       <c r="AD8" s="168" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="9">
@@ -43811,7 +43808,7 @@
       <c r="O15" s="84"/>
       <c r="P15" s="169"/>
       <c r="S15" s="37" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="16">
@@ -43924,7 +43921,7 @@
       <c r="Q19" s="9"/>
       <c r="R19" s="9"/>
       <c r="S19" s="37" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="20">
@@ -44208,7 +44205,7 @@
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
       <c r="G27" s="174" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H27" s="9"/>
       <c r="I27" s="9"/>
@@ -44293,7 +44290,7 @@
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
       <c r="D29" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E29" s="5">
         <f>J29</f>
@@ -44315,10 +44312,10 @@
       </c>
       <c r="K29" s="9"/>
       <c r="L29" s="100" t="s">
+        <v>326</v>
+      </c>
+      <c r="M29" s="100" t="s">
         <v>327</v>
-      </c>
-      <c r="M29" s="100" t="s">
-        <v>328</v>
       </c>
       <c r="O29" s="5">
         <v>1.0</v>
@@ -44418,7 +44415,7 @@
       </c>
       <c r="R31" s="9"/>
       <c r="S31" s="100" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="T31" s="9"/>
       <c r="U31" s="9"/>
@@ -44480,7 +44477,7 @@
       <c r="E33" s="9"/>
       <c r="F33" s="9"/>
       <c r="G33" s="125" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J33" s="9"/>
       <c r="K33" s="9"/>
@@ -44494,10 +44491,10 @@
       <c r="P33" s="9"/>
       <c r="R33" s="9"/>
       <c r="T33" s="45" t="s">
+        <v>330</v>
+      </c>
+      <c r="W33" s="37" t="s">
         <v>331</v>
-      </c>
-      <c r="W33" s="37" t="s">
-        <v>332</v>
       </c>
       <c r="AA33" s="36"/>
       <c r="AD33" s="9"/>
@@ -44540,7 +44537,7 @@
         <v>1626.0</v>
       </c>
       <c r="U34" s="97" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="W34" s="37">
         <v>5193.0</v>
@@ -44585,7 +44582,7 @@
         <v>4176.0</v>
       </c>
       <c r="U35" s="97" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="W35" s="37">
         <v>4863.0</v>
@@ -44683,7 +44680,7 @@
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
       <c r="F38" s="5" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G38" s="177">
         <f t="shared" ref="G38:I38" si="8">G30-G35</f>
@@ -44885,7 +44882,7 @@
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
       <c r="T45" s="168" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AD45" s="9"/>
       <c r="AE45" s="9"/>
@@ -45681,10 +45678,10 @@
       <c r="R62" s="9"/>
       <c r="S62" s="9"/>
       <c r="U62" s="37" t="s">
+        <v>335</v>
+      </c>
+      <c r="V62" s="37" t="s">
         <v>336</v>
-      </c>
-      <c r="V62" s="37" t="s">
-        <v>337</v>
       </c>
       <c r="AC62" s="9"/>
       <c r="AD62" s="9"/>

--- a/data/df_best_models.xlsx
+++ b/data/df_best_models.xlsx
@@ -2795,7 +2795,7 @@
         <v>45720.0</v>
       </c>
       <c r="D7" s="29">
-        <v>4599.0</v>
+        <v>2114.0</v>
       </c>
       <c r="E7" s="15" t="s">
         <v>15</v>

--- a/data/df_best_models.xlsx
+++ b/data/df_best_models.xlsx
@@ -2754,18 +2754,18 @@
         <v>10.0</v>
       </c>
       <c r="I4" s="18">
-        <v>80.0</v>
+        <v>60.0</v>
       </c>
       <c r="J4" s="18">
-        <v>100.0</v>
+        <v>40.0</v>
       </c>
       <c r="K4" s="20">
         <f t="shared" ref="K4:K8" si="1">AVERAGE(H4:J4)</f>
-        <v>63.33333333</v>
+        <v>36.66666667</v>
       </c>
       <c r="L4" s="26">
         <f>K4*'Data preparation'!$C$2</f>
-        <v>9.5</v>
+        <v>5.5</v>
       </c>
       <c r="M4" s="17"/>
       <c r="N4" s="31" t="str">
@@ -2785,7 +2785,7 @@
         <v>45719.0</v>
       </c>
       <c r="D5" s="29">
-        <v>3960.0</v>
+        <v>1940.0</v>
       </c>
       <c r="E5" s="15" t="s">
         <v>15</v>
@@ -2793,21 +2793,21 @@
       <c r="F5" s="30"/>
       <c r="G5" s="17"/>
       <c r="H5" s="17">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
       <c r="I5" s="17">
-        <v>100.0</v>
+        <v>120.0</v>
       </c>
       <c r="J5" s="17">
         <v>100.0</v>
       </c>
       <c r="K5" s="20">
         <f t="shared" si="1"/>
-        <v>68.33333333</v>
+        <v>80</v>
       </c>
       <c r="L5" s="26">
         <f>K5*'Data preparation'!$C$2</f>
-        <v>10.25</v>
+        <v>12</v>
       </c>
       <c r="M5" s="17"/>
       <c r="N5" s="31" t="str">
@@ -2827,7 +2827,7 @@
         <v>45720.0</v>
       </c>
       <c r="D6" s="29">
-        <v>1412.0</v>
+        <v>3993.0</v>
       </c>
       <c r="E6" s="15" t="s">
         <v>15</v>
@@ -2835,21 +2835,21 @@
       <c r="F6" s="30"/>
       <c r="G6" s="17"/>
       <c r="H6" s="17">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="I6" s="17">
+        <v>120.0</v>
+      </c>
+      <c r="J6" s="17">
         <v>80.0</v>
-      </c>
-      <c r="J6" s="17">
-        <v>100.0</v>
       </c>
       <c r="K6" s="20">
         <f t="shared" si="1"/>
-        <v>61.66666667</v>
+        <v>70</v>
       </c>
       <c r="L6" s="26">
         <f>K6*'Data preparation'!$C$2</f>
-        <v>9.25</v>
+        <v>10.5</v>
       </c>
       <c r="M6" s="32"/>
       <c r="N6" s="31" t="str">
@@ -2877,21 +2877,21 @@
       <c r="F7" s="30"/>
       <c r="G7" s="17"/>
       <c r="H7" s="18">
-        <v>10.0</v>
+        <v>120.0</v>
       </c>
       <c r="I7" s="18">
         <v>80.0</v>
       </c>
       <c r="J7" s="18">
-        <v>10.0</v>
+        <v>40.0</v>
       </c>
       <c r="K7" s="20">
         <f t="shared" si="1"/>
-        <v>33.33333333</v>
+        <v>80</v>
       </c>
       <c r="L7" s="26">
         <f>K7*'Data preparation'!$C$2</f>
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="M7" s="17"/>
       <c r="N7" s="31" t="str">
@@ -2919,21 +2919,21 @@
       <c r="F8" s="30"/>
       <c r="G8" s="17"/>
       <c r="H8" s="18">
-        <v>10.0</v>
+        <v>120.0</v>
       </c>
       <c r="I8" s="18">
         <v>120.0</v>
       </c>
       <c r="J8" s="18">
-        <v>10.0</v>
+        <v>40.0</v>
       </c>
       <c r="K8" s="20">
         <f t="shared" si="1"/>
-        <v>46.66666667</v>
+        <v>93.33333333</v>
       </c>
       <c r="L8" s="26">
         <f>K8*'Data preparation'!$C$2</f>
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="M8" s="17"/>
       <c r="N8" s="31" t="str">
@@ -15207,7 +15207,7 @@
       </c>
       <c r="C3" s="25">
         <f>AVERAGE('Modelos actuales'!L4:L8)</f>
-        <v>8.2</v>
+        <v>10.8</v>
       </c>
       <c r="L3" s="97"/>
       <c r="P3" s="97"/>

--- a/data/df_best_models.xlsx
+++ b/data/df_best_models.xlsx
@@ -268,7 +268,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="341">
   <si>
     <t>id_country</t>
   </si>
@@ -1042,25 +1042,31 @@
     <t>3.32</t>
   </si>
   <si>
-    <t>4.13</t>
+    <t>7.32</t>
   </si>
   <si>
-    <t>5.38</t>
+    <t>6.99</t>
   </si>
   <si>
-    <t>7.54</t>
+    <t>0.87</t>
   </si>
   <si>
-    <t>6.69</t>
+    <t>7.21</t>
   </si>
   <si>
-    <t>0.89</t>
+    <t>13.31</t>
   </si>
   <si>
-    <t>0.93</t>
+    <t>13.63</t>
   </si>
   <si>
-    <t>0.90</t>
+    <t>10.44</t>
+  </si>
+  <si>
+    <t>0.15</t>
+  </si>
+  <si>
+    <t>1.28</t>
   </si>
   <si>
     <t>RENTABILIDAD</t>
@@ -2800,7 +2806,7 @@
         <v>45720.0</v>
       </c>
       <c r="D7" s="29">
-        <v>1444.0</v>
+        <v>2114.0</v>
       </c>
       <c r="E7" s="15" t="s">
         <v>15</v>
@@ -2808,7 +2814,7 @@
       <c r="F7" s="30"/>
       <c r="G7" s="17"/>
       <c r="H7" s="18">
-        <v>40.0</v>
+        <v>120.0</v>
       </c>
       <c r="I7" s="18">
         <v>80.0</v>
@@ -2818,11 +2824,11 @@
       </c>
       <c r="K7" s="20">
         <f t="shared" si="1"/>
-        <v>53.33333333</v>
+        <v>80</v>
       </c>
       <c r="L7" s="26">
         <f>K7*'Data preparation'!$C$2</f>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M7" s="17"/>
       <c r="N7" s="31" t="str">
@@ -2842,7 +2848,7 @@
         <v>45720.0</v>
       </c>
       <c r="D8" s="29">
-        <v>3461.0</v>
+        <v>870.0</v>
       </c>
       <c r="E8" s="15" t="s">
         <v>15</v>
@@ -2850,7 +2856,7 @@
       <c r="F8" s="30"/>
       <c r="G8" s="17"/>
       <c r="H8" s="18">
-        <v>60.0</v>
+        <v>120.0</v>
       </c>
       <c r="I8" s="18">
         <v>120.0</v>
@@ -2860,11 +2866,11 @@
       </c>
       <c r="K8" s="20">
         <f t="shared" si="1"/>
-        <v>63.33333333</v>
+        <v>83.33333333</v>
       </c>
       <c r="L8" s="26">
         <f>K8*'Data preparation'!$C$2</f>
-        <v>9.5</v>
+        <v>12.5</v>
       </c>
       <c r="M8" s="17"/>
       <c r="N8" s="31" t="str">
@@ -15118,7 +15124,7 @@
       </c>
       <c r="C3" s="25">
         <f>AVERAGE('Modelos actuales'!L4:L8)</f>
-        <v>9.5</v>
+        <v>10.9</v>
       </c>
       <c r="L3" s="97"/>
       <c r="P3" s="97"/>
@@ -16419,7 +16425,7 @@
       <c r="C37" s="43"/>
       <c r="D37" s="112">
         <f>AVERAGE(D39:D1775)</f>
-        <v>5.199130435</v>
+        <v>5.647826087</v>
       </c>
       <c r="G37" s="38" t="s">
         <v>37</v>
@@ -17415,7 +17421,7 @@
       </c>
       <c r="D75" s="103">
         <f t="shared" si="17"/>
-        <v>4.13</v>
+        <v>7.32</v>
       </c>
       <c r="P75" s="101">
         <v>1.0</v>
@@ -17433,7 +17439,7 @@
       </c>
       <c r="D76" s="103">
         <f t="shared" si="17"/>
-        <v>5.38</v>
+        <v>6.99</v>
       </c>
       <c r="P76" s="101">
         <v>0.0</v>
@@ -17451,7 +17457,7 @@
       </c>
       <c r="D77" s="103">
         <f t="shared" si="17"/>
-        <v>7.54</v>
+        <v>0.87</v>
       </c>
       <c r="P77" s="101">
         <v>0.0</v>
@@ -17465,11 +17471,11 @@
     </row>
     <row r="78">
       <c r="C78" s="115" t="s">
-        <v>161</v>
+        <v>225</v>
       </c>
       <c r="D78" s="103">
         <f t="shared" si="17"/>
-        <v>7.85</v>
+        <v>7.21</v>
       </c>
       <c r="P78" s="101">
         <v>1.0</v>
@@ -17483,11 +17489,11 @@
     </row>
     <row r="79">
       <c r="C79" s="115" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="D79" s="103">
         <f t="shared" si="17"/>
-        <v>6.21</v>
+        <v>13.31</v>
       </c>
       <c r="P79" s="101">
         <v>2.0</v>
@@ -17501,11 +17507,11 @@
     </row>
     <row r="80">
       <c r="C80" s="115" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D80" s="103">
         <f t="shared" si="17"/>
-        <v>6.69</v>
+        <v>13.63</v>
       </c>
       <c r="P80" s="101">
         <v>1.0</v>
@@ -17519,11 +17525,11 @@
     </row>
     <row r="81">
       <c r="C81" s="115" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D81" s="103">
         <f t="shared" si="17"/>
-        <v>0.89</v>
+        <v>10.44</v>
       </c>
       <c r="P81" s="101">
         <v>2.0</v>
@@ -17537,11 +17543,11 @@
     </row>
     <row r="82">
       <c r="C82" s="115" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="D82" s="103">
         <f t="shared" si="17"/>
-        <v>0.89</v>
+        <v>0.15</v>
       </c>
       <c r="P82" s="101">
         <v>1.0</v>
@@ -17555,11 +17561,11 @@
     </row>
     <row r="83">
       <c r="C83" s="115" t="s">
-        <v>227</v>
+        <v>187</v>
       </c>
       <c r="D83" s="103">
         <f t="shared" si="17"/>
-        <v>0.93</v>
+        <v>0.85</v>
       </c>
       <c r="P83" s="101">
         <v>0.0</v>
@@ -17573,11 +17579,11 @@
     </row>
     <row r="84">
       <c r="C84" s="115" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D84" s="103">
         <f t="shared" si="17"/>
-        <v>0.9</v>
+        <v>1.28</v>
       </c>
       <c r="P84" s="101">
         <v>1.0</v>
@@ -40659,14 +40665,14 @@
     <row r="1">
       <c r="A1" s="127"/>
       <c r="B1" s="128" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C1" s="129"/>
       <c r="D1" s="129"/>
       <c r="E1" s="129"/>
       <c r="F1" s="129"/>
       <c r="G1" s="130" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="H1" s="129"/>
       <c r="I1" s="129"/>
@@ -40700,19 +40706,19 @@
         <v>3</v>
       </c>
       <c r="B2" s="132" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C2" s="133" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D2" s="133" t="s">
         <v>170</v>
       </c>
       <c r="E2" s="133" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F2" s="134" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="G2" s="132">
         <v>1.0</v>
@@ -40724,30 +40730,30 @@
         <v>2.0</v>
       </c>
       <c r="J2" s="133" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="K2" s="135" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="L2" s="133" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="M2" s="136" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="N2" s="117" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="O2" s="117" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="P2" s="117" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q2" s="9"/>
       <c r="R2" s="9"/>
       <c r="S2" s="96" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="T2" s="9"/>
       <c r="U2" s="9"/>
@@ -40837,7 +40843,7 @@
       <c r="Q4" s="9"/>
       <c r="R4" s="9"/>
       <c r="S4" s="142" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="T4" s="143"/>
       <c r="Z4" s="38"/>
@@ -40873,7 +40879,7 @@
       <c r="P5" s="145"/>
       <c r="S5" s="143"/>
       <c r="T5" s="146" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="6">
@@ -40906,11 +40912,11 @@
       <c r="R6" s="9"/>
       <c r="S6" s="143"/>
       <c r="T6" s="146" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Z6" s="89"/>
       <c r="AD6" s="39" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="7">
@@ -40940,7 +40946,7 @@
       <c r="O7" s="80"/>
       <c r="P7" s="148"/>
       <c r="AD7" s="146" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AE7" s="143"/>
       <c r="AF7" s="143"/>
@@ -40973,11 +40979,11 @@
       <c r="O8" s="80"/>
       <c r="P8" s="148"/>
       <c r="S8" s="146" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AA8" s="89"/>
       <c r="AD8" s="146" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="9">
@@ -41176,7 +41182,7 @@
       <c r="O15" s="80"/>
       <c r="P15" s="148"/>
       <c r="S15" s="39" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="16">
@@ -41289,7 +41295,7 @@
       <c r="Q19" s="9"/>
       <c r="R19" s="9"/>
       <c r="S19" s="39" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="20">
@@ -41573,7 +41579,7 @@
       <c r="E27" s="9"/>
       <c r="F27" s="9"/>
       <c r="G27" s="153" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="H27" s="9"/>
       <c r="I27" s="9"/>
@@ -41658,7 +41664,7 @@
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
       <c r="D29" s="5" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E29" s="5">
         <f>J29</f>
@@ -41680,10 +41686,10 @@
       </c>
       <c r="K29" s="9"/>
       <c r="L29" s="96" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="M29" s="96" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="O29" s="5">
         <v>1.0</v>
@@ -41783,7 +41789,7 @@
       </c>
       <c r="R31" s="9"/>
       <c r="S31" s="96" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="T31" s="9"/>
       <c r="U31" s="9"/>
@@ -41845,7 +41851,7 @@
       <c r="E33" s="9"/>
       <c r="F33" s="9"/>
       <c r="G33" s="99" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="J33" s="9"/>
       <c r="K33" s="9"/>
@@ -41859,10 +41865,10 @@
       <c r="P33" s="9"/>
       <c r="R33" s="9"/>
       <c r="T33" s="58" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="W33" s="39" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AA33" s="38"/>
       <c r="AD33" s="9"/>
@@ -41905,7 +41911,7 @@
         <v>1626.0</v>
       </c>
       <c r="U34" s="94" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="W34" s="39">
         <v>5193.0</v>
@@ -41950,7 +41956,7 @@
         <v>4176.0</v>
       </c>
       <c r="U35" s="94" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="W35" s="39">
         <v>4863.0</v>
@@ -42048,7 +42054,7 @@
       <c r="D38" s="9"/>
       <c r="E38" s="9"/>
       <c r="F38" s="5" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="G38" s="156">
         <f t="shared" ref="G38:I38" si="8">G30-G35</f>
@@ -42250,7 +42256,7 @@
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
       <c r="T45" s="146" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AD45" s="9"/>
       <c r="AE45" s="9"/>
@@ -42414,7 +42420,7 @@
         <v>13</v>
       </c>
       <c r="AG49" s="7" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="50">
@@ -42579,7 +42585,7 @@
         <v>13.03594852814783</v>
       </c>
       <c r="AG52" s="7" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="53">
@@ -42640,7 +42646,7 @@
         <v>6.291840048860032</v>
       </c>
       <c r="AG53" s="7" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="54">
@@ -42701,7 +42707,7 @@
         <v>2.7243520649411117</v>
       </c>
       <c r="AG54" s="7" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="55">
@@ -42762,7 +42768,7 @@
         <v>2.1429979739456915</v>
       </c>
       <c r="AG55" s="7" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="56">
@@ -42823,7 +42829,7 @@
         <v>3.98032040346951</v>
       </c>
       <c r="AG56" s="7" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="57">
@@ -43046,10 +43052,10 @@
       <c r="R62" s="9"/>
       <c r="S62" s="9"/>
       <c r="U62" s="39" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="V62" s="39" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AC62" s="9"/>
       <c r="AD62" s="9"/>
@@ -43091,7 +43097,7 @@
         <v>2165.0</v>
       </c>
       <c r="W63" s="39" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AC63" s="9"/>
       <c r="AD63" s="9"/>
@@ -76449,146 +76455,146 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="39" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="2">
       <c r="B2" s="9"/>
       <c r="C2" s="166" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E2" s="167"/>
       <c r="F2" s="96" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="H2" s="167"/>
     </row>
     <row r="3">
       <c r="B3" s="116" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C3" s="168" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D3" s="116" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E3" s="169" t="s">
         <v>96</v>
       </c>
       <c r="F3" s="116" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="G3" s="116" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="H3" s="116" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="170" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C4" s="171" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D4" s="117" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E4" s="172" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F4" s="173" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="G4" s="173" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H4" s="117"/>
     </row>
     <row r="5">
       <c r="B5" s="170" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C5" s="174" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D5" s="127"/>
       <c r="E5" s="172" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F5" s="175" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="G5" s="176" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="H5" s="117"/>
     </row>
     <row r="6">
       <c r="B6" s="170" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C6" s="171" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D6" s="117" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E6" s="172" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F6" s="117" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="G6" s="117"/>
       <c r="H6" s="117"/>
     </row>
     <row r="7">
       <c r="B7" s="117" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C7" s="177" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D7" s="117"/>
       <c r="E7" s="178" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="F7" s="171" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="G7" s="117"/>
       <c r="H7" s="117" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="179" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C8" s="180" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D8" s="181"/>
       <c r="E8" s="179" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F8" s="182" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="G8" s="183" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="H8" s="181"/>
     </row>
     <row r="9">
       <c r="B9" s="22" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C9" s="184" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D9" s="80"/>
       <c r="E9" s="80"/>
@@ -76598,27 +76604,27 @@
     </row>
     <row r="10">
       <c r="B10" s="22" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C10" s="147"/>
       <c r="D10" s="80"/>
       <c r="E10" s="80"/>
       <c r="F10" s="147"/>
       <c r="G10" s="173" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H10" s="80"/>
     </row>
     <row r="11">
       <c r="B11" s="22" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C11" s="147"/>
       <c r="D11" s="80"/>
       <c r="E11" s="80"/>
       <c r="F11" s="147"/>
       <c r="G11" s="185" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="H11" s="22"/>
     </row>
@@ -76641,7 +76647,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="38" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="L1" s="10"/>
     </row>
@@ -76650,16 +76656,16 @@
     </row>
     <row r="3">
       <c r="A3" s="39" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L3" s="10"/>
     </row>
     <row r="4">
       <c r="B4" s="39" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="G4" s="39" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="L4" s="10"/>
     </row>
@@ -76765,62 +76771,62 @@
     </row>
     <row r="11">
       <c r="A11" s="186" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="38" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="39" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="186" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="38" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="39" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F19" s="89"/>
     </row>
     <row r="20">
       <c r="B20" s="38" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C20" s="43"/>
       <c r="D20" s="43"/>
       <c r="E20" s="43"/>
       <c r="F20" s="43"/>
       <c r="G20" s="38" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="H20" s="38" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="I20" s="38" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="J20" s="38" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K20" s="38" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="38" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="G21" s="44">
         <v>2.575</v>
@@ -76828,27 +76834,27 @@
     </row>
     <row r="23">
       <c r="K23" s="38" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="39" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="H24" s="39" t="s">
         <v>170</v>
       </c>
       <c r="I24" s="39" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K24" s="39" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L24" s="39" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="M24" s="39" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="25">
@@ -76867,7 +76873,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K25" s="39" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="26">
@@ -76878,7 +76884,7 @@
         <v>1.19</v>
       </c>
       <c r="K26" s="39" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="27">
@@ -76889,7 +76895,7 @@
         <v>2.19</v>
       </c>
       <c r="K27" s="39" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="28">
@@ -76900,7 +76906,7 @@
         <v>0.05</v>
       </c>
       <c r="K28" s="39" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="29">
@@ -76919,7 +76925,7 @@
         <v>6.42</v>
       </c>
       <c r="K30" s="58" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="31">
@@ -77064,7 +77070,7 @@
         <v>0.61</v>
       </c>
       <c r="K41" s="38" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="42">
@@ -77075,13 +77081,13 @@
         <v>0.69</v>
       </c>
       <c r="K42" s="39" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="L42" s="39" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="M42" s="39" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="43">
@@ -77213,7 +77219,7 @@
         <v>0.0</v>
       </c>
       <c r="K51" s="39" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="52">
@@ -77241,17 +77247,17 @@
       </c>
       <c r="K54" s="80"/>
       <c r="L54" s="187" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="M54" s="188"/>
       <c r="N54" s="85" t="s">
         <v>6</v>
       </c>
       <c r="O54" s="85" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="P54" s="85" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="R54" s="18" t="s">
         <v>106</v>
@@ -77333,7 +77339,7 @@
         <v>5.86</v>
       </c>
       <c r="R57" s="39" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="S57" s="44">
         <f>SUM(P55:P74)</f>
@@ -77348,7 +77354,7 @@
         <v>0.0</v>
       </c>
       <c r="K58" s="22" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="L58" s="189">
         <v>0.57</v>
@@ -77362,7 +77368,7 @@
         <v>0.855</v>
       </c>
       <c r="P58" s="22" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="59">
@@ -77409,7 +77415,7 @@
         <v>0.96</v>
       </c>
       <c r="P60" s="22" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="61">
@@ -77420,7 +77426,7 @@
         <v>0.02</v>
       </c>
       <c r="K61" s="22" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L61" s="22">
         <v>0.42</v>
@@ -77492,7 +77498,7 @@
         <v>0.0</v>
       </c>
       <c r="K64" s="22" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="L64" s="22">
         <v>0.42</v>
@@ -77636,7 +77642,7 @@
         <v>0.0</v>
       </c>
       <c r="K70" s="22" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="L70" s="22">
         <v>0.66</v>

--- a/data/df_best_models.xlsx
+++ b/data/df_best_models.xlsx
@@ -268,7 +268,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="342">
   <si>
     <t>id_country</t>
   </si>
@@ -898,28 +898,28 @@
     <t>Stake promedio</t>
   </si>
   <si>
-    <t>1.68</t>
+    <t>9.08</t>
   </si>
   <si>
-    <t>10.08</t>
+    <t>0.59</t>
   </si>
   <si>
-    <t>5.20</t>
+    <t>3.90</t>
   </si>
   <si>
-    <t>9.86</t>
+    <t>7.66</t>
   </si>
   <si>
-    <t>6.71</t>
+    <t>6.37</t>
   </si>
   <si>
-    <t>9.30</t>
+    <t>5.53</t>
   </si>
   <si>
-    <t>9.47</t>
+    <t>7.41</t>
   </si>
   <si>
-    <t>9.16</t>
+    <t>7.80</t>
   </si>
   <si>
     <t>Country</t>
@@ -928,139 +928,142 @@
     <t>Correl ROI y Expected ROI</t>
   </si>
   <si>
-    <t>0.53</t>
+    <t>1.30</t>
   </si>
   <si>
-    <t>0.74</t>
+    <t>1.70</t>
   </si>
   <si>
     <t>mean</t>
   </si>
   <si>
-    <t>0.85</t>
+    <t>2.00</t>
   </si>
   <si>
     <t>median</t>
   </si>
   <si>
-    <t>0.22</t>
+    <t>3.75</t>
   </si>
   <si>
     <t>p25</t>
   </si>
   <si>
-    <t>1.26</t>
+    <t>0.19</t>
   </si>
   <si>
     <t>p75</t>
   </si>
   <si>
-    <t>0.64</t>
+    <t>5.82</t>
   </si>
   <si>
-    <t>7.33</t>
+    <t>3.00</t>
   </si>
   <si>
-    <t>7.61</t>
+    <t>6.17</t>
   </si>
   <si>
-    <t>5.07</t>
+    <t>1.03</t>
   </si>
   <si>
-    <t>7.64</t>
+    <t>5.46</t>
   </si>
   <si>
-    <t>8.25</t>
+    <t>5.43</t>
+  </si>
+  <si>
+    <t>5.89</t>
   </si>
   <si>
     <t>Gracias a las nuevas métricas de G/P sin bank en test, me di cuenta de que:</t>
   </si>
   <si>
-    <t>7.97</t>
+    <t>5.69</t>
   </si>
   <si>
     <t>La rentabilidad en ITA está en el visitante y no en el empate como creía.</t>
   </si>
   <si>
-    <t>8.17</t>
+    <t>5.83</t>
   </si>
   <si>
     <t>La rentabilidad en ENG y GER está en el empate tal como creía.</t>
   </si>
   <si>
-    <t>1.55</t>
+    <t>1.11</t>
   </si>
   <si>
     <t>En SPA esta repartido aunque Empate saca una ventaja.</t>
   </si>
   <si>
-    <t>9.32</t>
+    <t>6.65</t>
   </si>
   <si>
     <t>En FRA, depende el modelo. A veces local, a veces, empate.</t>
   </si>
   <si>
-    <t>4.95</t>
+    <t>2.55</t>
   </si>
   <si>
     <t>Si en FRA empate no rinde, no tiene sentido exigirle una buena distrib en empate… → Tiene sentido pero al parecer si importa el empate puesto que el modelo que gana se basa en empate.</t>
   </si>
   <si>
-    <t>11.15</t>
+    <t>7.96</t>
   </si>
   <si>
-    <t>4.97</t>
+    <t>7.09</t>
   </si>
   <si>
-    <t>5.61</t>
+    <t>8.34</t>
   </si>
   <si>
-    <t>5.84</t>
+    <t>6.15</t>
   </si>
   <si>
-    <t>4.30</t>
+    <t>7.72</t>
   </si>
   <si>
-    <t>5.41</t>
+    <t>6.61</t>
   </si>
   <si>
-    <t>9.26</t>
+    <t>7.11</t>
   </si>
   <si>
-    <t>9.95</t>
+    <t>4.75</t>
   </si>
   <si>
-    <t>6.64</t>
+    <t>3.91</t>
   </si>
   <si>
-    <t>4.36</t>
+    <t>6.22</t>
   </si>
   <si>
-    <t>2.73</t>
+    <t>7.88</t>
   </si>
   <si>
-    <t>4.35</t>
+    <t>6.04</t>
   </si>
   <si>
-    <t>4.23</t>
+    <t>6.96</t>
   </si>
   <si>
-    <t>4.87</t>
+    <t>7.30</t>
   </si>
   <si>
-    <t>5.11</t>
+    <t>9.45</t>
   </si>
   <si>
-    <t>13.23</t>
+    <t>9.23</t>
   </si>
   <si>
-    <t>12.92</t>
+    <t>0.97</t>
   </si>
   <si>
-    <t>0.68</t>
+    <t>6.06</t>
   </si>
   <si>
-    <t>3.12</t>
+    <t>4.45</t>
   </si>
   <si>
     <t>RENTABILIDAD</t>
@@ -2700,17 +2703,17 @@
         <v>45719.0</v>
       </c>
       <c r="D5" s="13">
-        <v>3960.0</v>
+        <v>3024.0</v>
       </c>
       <c r="E5" s="13" t="s">
         <v>13</v>
       </c>
       <c r="F5" s="14"/>
       <c r="G5" s="15">
+        <v>120.0</v>
+      </c>
+      <c r="H5" s="15">
         <v>80.0</v>
-      </c>
-      <c r="H5" s="15">
-        <v>120.0</v>
       </c>
       <c r="I5" s="15">
         <v>120.0</v>
@@ -2827,21 +2830,21 @@
       </c>
       <c r="F8" s="14"/>
       <c r="G8" s="15">
-        <v>130.0</v>
+        <v>120.0</v>
       </c>
       <c r="H8" s="15">
-        <v>130.0</v>
+        <v>120.0</v>
       </c>
       <c r="I8" s="15">
-        <v>70.0</v>
+        <v>80.0</v>
       </c>
       <c r="J8" s="17">
         <f t="shared" si="1"/>
-        <v>110</v>
+        <v>106.6666667</v>
       </c>
       <c r="K8" s="24">
         <f>J8*'Data preparation'!$C$2</f>
-        <v>11</v>
+        <v>10.66666667</v>
       </c>
       <c r="L8" s="25" t="str">
         <f t="shared" si="2"/>
@@ -13521,7 +13524,7 @@
       </c>
       <c r="C3" s="96">
         <f>AVERAGE('Modelos actuales'!K4:K8)</f>
-        <v>10.2</v>
+        <v>10.13333333</v>
       </c>
       <c r="L3" s="95"/>
       <c r="P3" s="95"/>
@@ -14822,7 +14825,7 @@
       <c r="C37" s="36"/>
       <c r="D37" s="111">
         <f>AVERAGE(D39:D1775)</f>
-        <v>5.863043478</v>
+        <v>5.438913043</v>
       </c>
       <c r="G37" s="34" t="s">
         <v>35</v>
@@ -14891,7 +14894,7 @@
       </c>
       <c r="D39" s="102">
         <f t="shared" ref="D39:D221" si="17">IF(COUNTA(C39)=1,C39/1,"")</f>
-        <v>1.68</v>
+        <v>9.08</v>
       </c>
       <c r="G39" s="34" t="s">
         <v>27</v>
@@ -14929,7 +14932,7 @@
       </c>
       <c r="D40" s="102">
         <f t="shared" si="17"/>
-        <v>10.08</v>
+        <v>0.59</v>
       </c>
       <c r="G40" s="34" t="s">
         <v>23</v>
@@ -14967,7 +14970,7 @@
       </c>
       <c r="D41" s="102">
         <f t="shared" si="17"/>
-        <v>5.2</v>
+        <v>3.9</v>
       </c>
       <c r="P41" s="100">
         <v>0.0</v>
@@ -14999,7 +15002,7 @@
       </c>
       <c r="D42" s="102">
         <f t="shared" si="17"/>
-        <v>9.86</v>
+        <v>7.66</v>
       </c>
       <c r="P42" s="100">
         <v>2.0</v>
@@ -15031,7 +15034,7 @@
       </c>
       <c r="D43" s="102">
         <f t="shared" si="17"/>
-        <v>6.71</v>
+        <v>6.37</v>
       </c>
       <c r="P43" s="100">
         <v>1.0</v>
@@ -15063,7 +15066,7 @@
       </c>
       <c r="D44" s="102">
         <f t="shared" si="17"/>
-        <v>9.3</v>
+        <v>5.53</v>
       </c>
       <c r="P44" s="100">
         <v>2.0</v>
@@ -15093,7 +15096,7 @@
       </c>
       <c r="D45" s="102">
         <f t="shared" si="17"/>
-        <v>9.47</v>
+        <v>7.41</v>
       </c>
       <c r="P45" s="100">
         <v>1.0</v>
@@ -15111,7 +15114,7 @@
       </c>
       <c r="D46" s="102">
         <f t="shared" si="17"/>
-        <v>9.16</v>
+        <v>7.8</v>
       </c>
       <c r="G46" s="115" t="s">
         <v>182</v>
@@ -15135,7 +15138,7 @@
       </c>
       <c r="D47" s="102">
         <f t="shared" si="17"/>
-        <v>0.53</v>
+        <v>1.3</v>
       </c>
       <c r="G47" s="116" t="s">
         <v>36</v>
@@ -15165,7 +15168,7 @@
       </c>
       <c r="D48" s="102">
         <f t="shared" si="17"/>
-        <v>0.74</v>
+        <v>1.7</v>
       </c>
       <c r="G48" s="116" t="s">
         <v>35</v>
@@ -15202,7 +15205,7 @@
       </c>
       <c r="D49" s="102">
         <f t="shared" si="17"/>
-        <v>0.85</v>
+        <v>2</v>
       </c>
       <c r="G49" s="116" t="s">
         <v>26</v>
@@ -15239,7 +15242,7 @@
       </c>
       <c r="D50" s="102">
         <f t="shared" si="17"/>
-        <v>0.22</v>
+        <v>3.75</v>
       </c>
       <c r="G50" s="116" t="s">
         <v>27</v>
@@ -15276,7 +15279,7 @@
       </c>
       <c r="D51" s="102">
         <f t="shared" si="17"/>
-        <v>1.26</v>
+        <v>0.19</v>
       </c>
       <c r="G51" s="116" t="s">
         <v>23</v>
@@ -15313,7 +15316,7 @@
       </c>
       <c r="D52" s="102">
         <f t="shared" si="17"/>
-        <v>0.64</v>
+        <v>5.82</v>
       </c>
       <c r="P52" s="100">
         <v>0.0</v>
@@ -15337,7 +15340,7 @@
       </c>
       <c r="D53" s="102">
         <f t="shared" si="17"/>
-        <v>7.33</v>
+        <v>3</v>
       </c>
       <c r="P53" s="100">
         <v>0.0</v>
@@ -15361,7 +15364,7 @@
       </c>
       <c r="D54" s="102">
         <f t="shared" si="17"/>
-        <v>7.61</v>
+        <v>6.17</v>
       </c>
       <c r="P54" s="100">
         <v>2.0</v>
@@ -15385,7 +15388,7 @@
       </c>
       <c r="D55" s="102">
         <f t="shared" si="17"/>
-        <v>5.07</v>
+        <v>1.03</v>
       </c>
       <c r="P55" s="100">
         <v>0.0</v>
@@ -15409,7 +15412,7 @@
       </c>
       <c r="D56" s="102">
         <f t="shared" si="17"/>
-        <v>7.64</v>
+        <v>5.46</v>
       </c>
       <c r="P56" s="100">
         <v>0.0</v>
@@ -15429,11 +15432,11 @@
     </row>
     <row r="57">
       <c r="C57" s="114" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D57" s="102">
         <f t="shared" si="17"/>
-        <v>7.61</v>
+        <v>5.43</v>
       </c>
       <c r="P57" s="100">
         <v>2.0</v>
@@ -15453,14 +15456,14 @@
     </row>
     <row r="58">
       <c r="C58" s="114" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D58" s="102">
         <f t="shared" si="17"/>
-        <v>8.25</v>
+        <v>5.89</v>
       </c>
       <c r="G58" s="118" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H58" s="119"/>
       <c r="P58" s="100">
@@ -15481,15 +15484,15 @@
     </row>
     <row r="59">
       <c r="C59" s="114" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D59" s="102">
         <f t="shared" si="17"/>
-        <v>7.97</v>
+        <v>5.69</v>
       </c>
       <c r="G59" s="119"/>
       <c r="H59" s="120" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P59" s="100">
         <v>0.0</v>
@@ -15509,15 +15512,15 @@
     </row>
     <row r="60">
       <c r="C60" s="114" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D60" s="102">
         <f t="shared" si="17"/>
-        <v>8.17</v>
+        <v>5.83</v>
       </c>
       <c r="G60" s="119"/>
       <c r="H60" s="120" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="P60" s="100">
         <v>2.0</v>
@@ -15537,15 +15540,15 @@
     </row>
     <row r="61">
       <c r="C61" s="114" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D61" s="102">
         <f t="shared" si="17"/>
-        <v>1.55</v>
+        <v>1.11</v>
       </c>
       <c r="G61" s="119"/>
       <c r="H61" s="120" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P61" s="100">
         <v>2.0</v>
@@ -15565,15 +15568,15 @@
     </row>
     <row r="62">
       <c r="C62" s="114" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D62" s="102">
         <f t="shared" si="17"/>
-        <v>9.32</v>
+        <v>6.65</v>
       </c>
       <c r="G62" s="119"/>
       <c r="H62" s="120" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P62" s="100">
         <v>1.0</v>
@@ -15593,15 +15596,15 @@
     </row>
     <row r="63">
       <c r="C63" s="114" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D63" s="102">
         <f t="shared" si="17"/>
-        <v>4.95</v>
+        <v>2.55</v>
       </c>
       <c r="G63" s="119"/>
       <c r="H63" s="120" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P63" s="100">
         <v>0.0</v>
@@ -15615,11 +15618,11 @@
     </row>
     <row r="64">
       <c r="C64" s="114" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D64" s="102">
         <f t="shared" si="17"/>
-        <v>11.15</v>
+        <v>7.96</v>
       </c>
       <c r="P64" s="100">
         <v>1.0</v>
@@ -15633,11 +15636,11 @@
     </row>
     <row r="65">
       <c r="C65" s="114" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D65" s="102">
         <f t="shared" si="17"/>
-        <v>4.97</v>
+        <v>7.09</v>
       </c>
       <c r="P65" s="100">
         <v>2.0</v>
@@ -15651,11 +15654,11 @@
     </row>
     <row r="66">
       <c r="C66" s="114" t="s">
-        <v>212</v>
+        <v>159</v>
       </c>
       <c r="D66" s="102">
         <f t="shared" si="17"/>
-        <v>5.61</v>
+        <v>7.91</v>
       </c>
       <c r="P66" s="100">
         <v>0.0</v>
@@ -15673,7 +15676,7 @@
       </c>
       <c r="D67" s="102">
         <f t="shared" si="17"/>
-        <v>5.84</v>
+        <v>8.34</v>
       </c>
       <c r="P67" s="100">
         <v>0.0</v>
@@ -15691,7 +15694,7 @@
       </c>
       <c r="D68" s="102">
         <f t="shared" si="17"/>
-        <v>4.3</v>
+        <v>6.15</v>
       </c>
       <c r="P68" s="100">
         <v>1.0</v>
@@ -15709,7 +15712,7 @@
       </c>
       <c r="D69" s="102">
         <f t="shared" si="17"/>
-        <v>5.41</v>
+        <v>7.72</v>
       </c>
       <c r="P69" s="100">
         <v>2.0</v>
@@ -15727,7 +15730,7 @@
       </c>
       <c r="D70" s="102">
         <f t="shared" si="17"/>
-        <v>9.26</v>
+        <v>6.61</v>
       </c>
       <c r="P70" s="100">
         <v>1.0</v>
@@ -15745,7 +15748,7 @@
       </c>
       <c r="D71" s="102">
         <f t="shared" si="17"/>
-        <v>9.95</v>
+        <v>7.11</v>
       </c>
       <c r="F71" s="121"/>
       <c r="P71" s="100">
@@ -15764,7 +15767,7 @@
       </c>
       <c r="D72" s="102">
         <f t="shared" si="17"/>
-        <v>6.64</v>
+        <v>4.75</v>
       </c>
       <c r="P72" s="100">
         <v>0.0</v>
@@ -15778,11 +15781,11 @@
     </row>
     <row r="73">
       <c r="C73" s="114" t="s">
-        <v>219</v>
+        <v>195</v>
       </c>
       <c r="D73" s="102">
         <f t="shared" si="17"/>
-        <v>4.36</v>
+        <v>6.17</v>
       </c>
       <c r="P73" s="100">
         <v>1.0</v>
@@ -15796,11 +15799,11 @@
     </row>
     <row r="74">
       <c r="C74" s="114" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D74" s="102">
         <f t="shared" si="17"/>
-        <v>2.73</v>
+        <v>3.91</v>
       </c>
       <c r="P74" s="100">
         <v>0.0</v>
@@ -15814,11 +15817,11 @@
     </row>
     <row r="75">
       <c r="C75" s="114" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D75" s="102">
         <f t="shared" si="17"/>
-        <v>4.35</v>
+        <v>6.22</v>
       </c>
       <c r="P75" s="100">
         <v>1.0</v>
@@ -15832,11 +15835,11 @@
     </row>
     <row r="76">
       <c r="C76" s="114" t="s">
-        <v>165</v>
+        <v>221</v>
       </c>
       <c r="D76" s="102">
         <f t="shared" si="17"/>
-        <v>5.56</v>
+        <v>7.88</v>
       </c>
       <c r="P76" s="100">
         <v>0.0</v>
@@ -15854,7 +15857,7 @@
       </c>
       <c r="D77" s="102">
         <f t="shared" si="17"/>
-        <v>4.23</v>
+        <v>6.04</v>
       </c>
       <c r="P77" s="100">
         <v>0.0</v>
@@ -15872,7 +15875,7 @@
       </c>
       <c r="D78" s="102">
         <f t="shared" si="17"/>
-        <v>4.87</v>
+        <v>6.96</v>
       </c>
       <c r="P78" s="100">
         <v>1.0</v>
@@ -15890,7 +15893,7 @@
       </c>
       <c r="D79" s="102">
         <f t="shared" si="17"/>
-        <v>5.11</v>
+        <v>7.3</v>
       </c>
       <c r="P79" s="100">
         <v>2.0</v>
@@ -15908,7 +15911,7 @@
       </c>
       <c r="D80" s="102">
         <f t="shared" si="17"/>
-        <v>13.23</v>
+        <v>9.45</v>
       </c>
       <c r="P80" s="100">
         <v>1.0</v>
@@ -15926,7 +15929,7 @@
       </c>
       <c r="D81" s="102">
         <f t="shared" si="17"/>
-        <v>12.92</v>
+        <v>9.23</v>
       </c>
       <c r="P81" s="100">
         <v>2.0</v>
@@ -15944,7 +15947,7 @@
       </c>
       <c r="D82" s="102">
         <f t="shared" si="17"/>
-        <v>0.68</v>
+        <v>0.97</v>
       </c>
       <c r="P82" s="100">
         <v>1.0</v>
@@ -15958,11 +15961,11 @@
     </row>
     <row r="83">
       <c r="C83" s="114" t="s">
-        <v>163</v>
+        <v>228</v>
       </c>
       <c r="D83" s="102">
         <f t="shared" si="17"/>
-        <v>4.24</v>
+        <v>6.06</v>
       </c>
       <c r="P83" s="100">
         <v>0.0</v>
@@ -15976,11 +15979,11 @@
     </row>
     <row r="84">
       <c r="C84" s="114" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D84" s="102">
         <f t="shared" si="17"/>
-        <v>3.12</v>
+        <v>4.45</v>
       </c>
       <c r="P84" s="100">
         <v>1.0</v>
@@ -39062,14 +39065,14 @@
     <row r="1">
       <c r="A1" s="126"/>
       <c r="B1" s="127" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C1" s="128"/>
       <c r="D1" s="128"/>
       <c r="E1" s="128"/>
       <c r="F1" s="128"/>
       <c r="G1" s="129" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H1" s="128"/>
       <c r="I1" s="128"/>
@@ -39103,19 +39106,19 @@
         <v>3</v>
       </c>
       <c r="B2" s="131" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C2" s="132" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D2" s="132" t="s">
         <v>170</v>
       </c>
       <c r="E2" s="132" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F2" s="133" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G2" s="131">
         <v>1.0</v>
@@ -39127,30 +39130,30 @@
         <v>2.0</v>
       </c>
       <c r="J2" s="132" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K2" s="134" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L2" s="132" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M2" s="135" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N2" s="116" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O2" s="116" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P2" s="116" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q2" s="7"/>
       <c r="R2" s="7"/>
       <c r="S2" s="94" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="T2" s="7"/>
       <c r="U2" s="7"/>
@@ -39240,7 +39243,7 @@
       <c r="Q4" s="7"/>
       <c r="R4" s="7"/>
       <c r="S4" s="141" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="T4" s="142"/>
       <c r="Z4" s="34"/>
@@ -39276,7 +39279,7 @@
       <c r="P5" s="144"/>
       <c r="S5" s="142"/>
       <c r="T5" s="145" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="6">
@@ -39309,11 +39312,11 @@
       <c r="R6" s="7"/>
       <c r="S6" s="142"/>
       <c r="T6" s="145" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Z6" s="83"/>
       <c r="AD6" s="31" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="7">
@@ -39343,7 +39346,7 @@
       <c r="O7" s="74"/>
       <c r="P7" s="147"/>
       <c r="AD7" s="145" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AE7" s="142"/>
       <c r="AF7" s="142"/>
@@ -39376,11 +39379,11 @@
       <c r="O8" s="74"/>
       <c r="P8" s="147"/>
       <c r="S8" s="145" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AA8" s="83"/>
       <c r="AD8" s="145" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="9">
@@ -39579,7 +39582,7 @@
       <c r="O15" s="74"/>
       <c r="P15" s="147"/>
       <c r="S15" s="31" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="16">
@@ -39692,7 +39695,7 @@
       <c r="Q19" s="7"/>
       <c r="R19" s="7"/>
       <c r="S19" s="31" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="20">
@@ -39976,7 +39979,7 @@
       <c r="E27" s="7"/>
       <c r="F27" s="7"/>
       <c r="G27" s="152" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H27" s="7"/>
       <c r="I27" s="7"/>
@@ -40061,7 +40064,7 @@
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
       <c r="D29" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E29" s="4">
         <f>J29</f>
@@ -40083,10 +40086,10 @@
       </c>
       <c r="K29" s="7"/>
       <c r="L29" s="94" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M29" s="94" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O29" s="4">
         <v>1.0</v>
@@ -40186,7 +40189,7 @@
       </c>
       <c r="R31" s="7"/>
       <c r="S31" s="94" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="T31" s="7"/>
       <c r="U31" s="7"/>
@@ -40248,7 +40251,7 @@
       <c r="E33" s="7"/>
       <c r="F33" s="7"/>
       <c r="G33" s="98" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J33" s="7"/>
       <c r="K33" s="7"/>
@@ -40262,10 +40265,10 @@
       <c r="P33" s="7"/>
       <c r="R33" s="7"/>
       <c r="T33" s="51" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="W33" s="31" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AA33" s="34"/>
       <c r="AD33" s="7"/>
@@ -40308,7 +40311,7 @@
         <v>1626.0</v>
       </c>
       <c r="U34" s="92" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="W34" s="31">
         <v>5193.0</v>
@@ -40353,7 +40356,7 @@
         <v>4176.0</v>
       </c>
       <c r="U35" s="92" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="W35" s="31">
         <v>4863.0</v>
@@ -40451,7 +40454,7 @@
       <c r="D38" s="7"/>
       <c r="E38" s="7"/>
       <c r="F38" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G38" s="155">
         <f t="shared" ref="G38:I38" si="8">G30-G35</f>
@@ -40653,7 +40656,7 @@
       <c r="Q45" s="7"/>
       <c r="R45" s="7"/>
       <c r="T45" s="145" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AD45" s="7"/>
       <c r="AE45" s="7"/>
@@ -40817,7 +40820,7 @@
         <v>11</v>
       </c>
       <c r="AG49" s="61" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="50">
@@ -40982,7 +40985,7 @@
         <v>13.03594852814783</v>
       </c>
       <c r="AG52" s="61" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="53">
@@ -41043,7 +41046,7 @@
         <v>6.291840048860032</v>
       </c>
       <c r="AG53" s="61" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="54">
@@ -41104,7 +41107,7 @@
         <v>2.7243520649411117</v>
       </c>
       <c r="AG54" s="61" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="55">
@@ -41165,7 +41168,7 @@
         <v>2.1429979739456915</v>
       </c>
       <c r="AG55" s="61" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="56">
@@ -41226,7 +41229,7 @@
         <v>3.98032040346951</v>
       </c>
       <c r="AG56" s="61" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="57">
@@ -41449,10 +41452,10 @@
       <c r="R62" s="7"/>
       <c r="S62" s="7"/>
       <c r="U62" s="31" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="V62" s="31" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AC62" s="7"/>
       <c r="AD62" s="7"/>
@@ -41494,7 +41497,7 @@
         <v>2165.0</v>
       </c>
       <c r="W63" s="31" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AC63" s="7"/>
       <c r="AD63" s="7"/>
@@ -42128,7 +42131,7 @@
       <c r="R79" s="7"/>
       <c r="S79" s="7"/>
       <c r="T79" s="94" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="U79" s="7"/>
       <c r="V79" s="7"/>
@@ -42169,7 +42172,7 @@
       <c r="R80" s="7"/>
       <c r="S80" s="7"/>
       <c r="T80" s="31" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="U80" s="18"/>
       <c r="V80" s="18"/>
@@ -74930,146 +74933,146 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="31" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="2">
       <c r="B2" s="7"/>
       <c r="C2" s="165" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E2" s="166"/>
       <c r="F2" s="94" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H2" s="166"/>
     </row>
     <row r="3">
       <c r="B3" s="115" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C3" s="167" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D3" s="115" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E3" s="168" t="s">
         <v>96</v>
       </c>
       <c r="F3" s="115" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G3" s="115" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H3" s="115" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="169" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C4" s="170" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D4" s="116" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E4" s="171" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F4" s="172" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G4" s="172" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H4" s="116"/>
     </row>
     <row r="5">
       <c r="B5" s="169" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C5" s="173" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D5" s="126"/>
       <c r="E5" s="171" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F5" s="174" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G5" s="175" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H5" s="116"/>
     </row>
     <row r="6">
       <c r="B6" s="169" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C6" s="170" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D6" s="116" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E6" s="171" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F6" s="116" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G6" s="116"/>
       <c r="H6" s="116"/>
     </row>
     <row r="7">
       <c r="B7" s="116" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C7" s="176" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D7" s="116"/>
       <c r="E7" s="177" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F7" s="170" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G7" s="116"/>
       <c r="H7" s="116" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="178" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C8" s="179" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D8" s="180"/>
       <c r="E8" s="178" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F8" s="181" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="G8" s="182" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H8" s="180"/>
     </row>
     <row r="9">
       <c r="B9" s="19" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C9" s="183" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D9" s="74"/>
       <c r="E9" s="74"/>
@@ -75079,27 +75082,27 @@
     </row>
     <row r="10">
       <c r="B10" s="19" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C10" s="146"/>
       <c r="D10" s="74"/>
       <c r="E10" s="74"/>
       <c r="F10" s="146"/>
       <c r="G10" s="172" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H10" s="74"/>
     </row>
     <row r="11">
       <c r="B11" s="19" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C11" s="146"/>
       <c r="D11" s="74"/>
       <c r="E11" s="74"/>
       <c r="F11" s="146"/>
       <c r="G11" s="184" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H11" s="19"/>
     </row>
@@ -75122,7 +75125,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="34" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L1" s="8"/>
     </row>
@@ -75131,16 +75134,16 @@
     </row>
     <row r="3">
       <c r="A3" s="31" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="L3" s="8"/>
     </row>
     <row r="4">
       <c r="B4" s="31" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G4" s="31" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L4" s="8"/>
     </row>
@@ -75246,62 +75249,62 @@
     </row>
     <row r="11">
       <c r="A11" s="185" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="34" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="31" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="185" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="34" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="31" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F19" s="83"/>
     </row>
     <row r="20">
       <c r="B20" s="34" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C20" s="36"/>
       <c r="D20" s="36"/>
       <c r="E20" s="36"/>
       <c r="F20" s="36"/>
       <c r="G20" s="34" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H20" s="34" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="I20" s="34" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="J20" s="34" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K20" s="34" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="34" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G21" s="37">
         <v>2.575</v>
@@ -75309,27 +75312,27 @@
     </row>
     <row r="23">
       <c r="K23" s="34" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="31" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H24" s="31" t="s">
         <v>170</v>
       </c>
       <c r="I24" s="31" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K24" s="31" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L24" s="31" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M24" s="31" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="25">
@@ -75348,7 +75351,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K25" s="31" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="26">
@@ -75359,7 +75362,7 @@
         <v>1.19</v>
       </c>
       <c r="K26" s="31" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="27">
@@ -75370,7 +75373,7 @@
         <v>2.19</v>
       </c>
       <c r="K27" s="31" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="28">
@@ -75381,7 +75384,7 @@
         <v>0.05</v>
       </c>
       <c r="K28" s="31" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="29">
@@ -75400,7 +75403,7 @@
         <v>6.42</v>
       </c>
       <c r="K30" s="51" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="31">
@@ -75545,7 +75548,7 @@
         <v>0.61</v>
       </c>
       <c r="K41" s="34" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="42">
@@ -75556,13 +75559,13 @@
         <v>0.69</v>
       </c>
       <c r="K42" s="31" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L42" s="31" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M42" s="31" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="43">
@@ -75694,7 +75697,7 @@
         <v>0.0</v>
       </c>
       <c r="K51" s="31" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="52">
@@ -75722,17 +75725,17 @@
       </c>
       <c r="K54" s="74"/>
       <c r="L54" s="186" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M54" s="187"/>
       <c r="N54" s="79" t="s">
         <v>5</v>
       </c>
       <c r="O54" s="79" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="P54" s="79" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="R54" s="15" t="s">
         <v>106</v>
@@ -75814,7 +75817,7 @@
         <v>5.86</v>
       </c>
       <c r="R57" s="31" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="S57" s="37">
         <f>SUM(P55:P74)</f>
@@ -75829,7 +75832,7 @@
         <v>0.0</v>
       </c>
       <c r="K58" s="19" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="L58" s="188">
         <v>0.57</v>
@@ -75843,7 +75846,7 @@
         <v>0.855</v>
       </c>
       <c r="P58" s="19" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="59">
@@ -75890,7 +75893,7 @@
         <v>0.96</v>
       </c>
       <c r="P60" s="19" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="61">
@@ -75901,7 +75904,7 @@
         <v>0.02</v>
       </c>
       <c r="K61" s="19" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L61" s="19">
         <v>0.42</v>
@@ -75973,7 +75976,7 @@
         <v>0.0</v>
       </c>
       <c r="K64" s="19" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L64" s="19">
         <v>0.42</v>
@@ -76117,7 +76120,7 @@
         <v>0.0</v>
       </c>
       <c r="K70" s="19" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="L70" s="19">
         <v>0.66</v>

--- a/data/df_best_models.xlsx
+++ b/data/df_best_models.xlsx
@@ -268,7 +268,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="342">
   <si>
     <t>id_country</t>
   </si>
@@ -901,28 +901,28 @@
     <t>Stake promedio</t>
   </si>
   <si>
-    <t>9.08</t>
+    <t>4.68</t>
   </si>
   <si>
-    <t>0.59</t>
+    <t>7.35</t>
   </si>
   <si>
-    <t>3.90</t>
+    <t>7.26</t>
   </si>
   <si>
-    <t>7.66</t>
+    <t>6.11</t>
   </si>
   <si>
-    <t>6.37</t>
+    <t>5.31</t>
   </si>
   <si>
-    <t>5.53</t>
+    <t>0.48</t>
   </si>
   <si>
-    <t>7.41</t>
+    <t>7.12</t>
   </si>
   <si>
-    <t>7.80</t>
+    <t>7.48</t>
   </si>
   <si>
     <t>Country</t>
@@ -931,142 +931,139 @@
     <t>Correl ROI y Expected ROI</t>
   </si>
   <si>
-    <t>1.30</t>
+    <t>1.94</t>
   </si>
   <si>
-    <t>1.70</t>
+    <t>6.31</t>
   </si>
   <si>
     <t>mean</t>
   </si>
   <si>
-    <t>2.00</t>
+    <t>3.71</t>
   </si>
   <si>
     <t>median</t>
   </si>
   <si>
-    <t>3.75</t>
-  </si>
-  <si>
     <t>p25</t>
   </si>
   <si>
-    <t>0.19</t>
+    <t>2.20</t>
   </si>
   <si>
     <t>p75</t>
   </si>
   <si>
-    <t>5.82</t>
+    <t>2.61</t>
   </si>
   <si>
-    <t>3.00</t>
+    <t>5.29</t>
   </si>
   <si>
-    <t>6.17</t>
+    <t>6.07</t>
   </si>
   <si>
-    <t>1.03</t>
+    <t>3.15</t>
   </si>
   <si>
-    <t>5.46</t>
+    <t>1.33</t>
   </si>
   <si>
-    <t>5.43</t>
+    <t>7.98</t>
   </si>
   <si>
-    <t>5.89</t>
+    <t>6.55</t>
   </si>
   <si>
     <t>Gracias a las nuevas métricas de G/P sin bank en test, me di cuenta de que:</t>
   </si>
   <si>
-    <t>5.69</t>
+    <t>3.05</t>
   </si>
   <si>
     <t>La rentabilidad en ITA está en el visitante y no en el empate como creía.</t>
   </si>
   <si>
-    <t>5.83</t>
+    <t>6.52</t>
   </si>
   <si>
     <t>La rentabilidad en ENG y GER está en el empate tal como creía.</t>
   </si>
   <si>
-    <t>1.11</t>
+    <t>7.07</t>
   </si>
   <si>
     <t>En SPA esta repartido aunque Empate saca una ventaja.</t>
   </si>
   <si>
-    <t>6.65</t>
+    <t>6.83</t>
   </si>
   <si>
     <t>En FRA, depende el modelo. A veces local, a veces, empate.</t>
   </si>
   <si>
-    <t>2.55</t>
+    <t>7.00</t>
   </si>
   <si>
     <t>Si en FRA empate no rinde, no tiene sentido exigirle una buena distrib en empate… → Tiene sentido pero al parecer si importa el empate puesto que el modelo que gana se basa en empate.</t>
   </si>
   <si>
-    <t>7.96</t>
+    <t>9.55</t>
   </si>
   <si>
-    <t>7.09</t>
+    <t>7.94</t>
   </si>
   <si>
-    <t>8.34</t>
+    <t>5.68</t>
   </si>
   <si>
-    <t>6.15</t>
+    <t>6.33</t>
   </si>
   <si>
-    <t>7.72</t>
+    <t>6.67</t>
   </si>
   <si>
-    <t>6.61</t>
+    <t>8.53</t>
   </si>
   <si>
-    <t>7.11</t>
+    <t>7.41</t>
   </si>
   <si>
-    <t>4.75</t>
+    <t>4.69</t>
   </si>
   <si>
-    <t>3.91</t>
+    <t>5.70</t>
   </si>
   <si>
-    <t>6.22</t>
+    <t>4.97</t>
   </si>
   <si>
-    <t>7.88</t>
+    <t>7.56</t>
   </si>
   <si>
-    <t>6.04</t>
+    <t>6.30</t>
   </si>
   <si>
-    <t>6.96</t>
+    <t>1.16</t>
   </si>
   <si>
-    <t>7.30</t>
+    <t>7.38</t>
   </si>
   <si>
-    <t>9.45</t>
+    <t>7.28</t>
   </si>
   <si>
-    <t>9.23</t>
+    <t>4.83</t>
   </si>
   <si>
-    <t>0.97</t>
+    <t>5.57</t>
   </si>
   <si>
-    <t>6.06</t>
+    <t>5.84</t>
   </si>
   <si>
-    <t>4.45</t>
+    <t>5.34</t>
   </si>
   <si>
     <t>RENTABILIDAD</t>
@@ -2747,7 +2744,7 @@
         <v>13</v>
       </c>
       <c r="F6" s="14">
-        <v>120.0</v>
+        <v>140.0</v>
       </c>
       <c r="G6" s="15"/>
       <c r="H6" s="15"/>
@@ -2758,7 +2755,7 @@
       </c>
       <c r="K6" s="24">
         <f>F6*'Data preparation'!$C$2</f>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L6" s="25" t="str">
         <f t="shared" si="2"/>
@@ -2783,7 +2780,7 @@
         <v>13</v>
       </c>
       <c r="F7" s="14">
-        <v>80.0</v>
+        <v>60.0</v>
       </c>
       <c r="G7" s="15"/>
       <c r="H7" s="15"/>
@@ -2794,7 +2791,7 @@
       </c>
       <c r="K7" s="24">
         <f>F7*'Data preparation'!$C$2</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L7" s="25" t="str">
         <f t="shared" si="2"/>
@@ -7497,6 +7494,16 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="J4:J8">
     <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF57BB8A"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F4:F8">
+    <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -14811,7 +14818,7 @@
       <c r="C37" s="36"/>
       <c r="D37" s="111">
         <f>AVERAGE(D39:D1775)</f>
-        <v>5.438913043</v>
+        <v>5.637826087</v>
       </c>
       <c r="G37" s="34" t="s">
         <v>36</v>
@@ -14880,7 +14887,7 @@
       </c>
       <c r="D39" s="102">
         <f t="shared" ref="D39:D221" si="17">IF(COUNTA(C39)=1,C39/1,"")</f>
-        <v>9.08</v>
+        <v>4.68</v>
       </c>
       <c r="G39" s="34" t="s">
         <v>28</v>
@@ -14918,7 +14925,7 @@
       </c>
       <c r="D40" s="102">
         <f t="shared" si="17"/>
-        <v>0.59</v>
+        <v>7.35</v>
       </c>
       <c r="G40" s="34" t="s">
         <v>24</v>
@@ -14956,7 +14963,7 @@
       </c>
       <c r="D41" s="102">
         <f t="shared" si="17"/>
-        <v>3.9</v>
+        <v>7.26</v>
       </c>
       <c r="P41" s="100">
         <v>0.0</v>
@@ -14988,7 +14995,7 @@
       </c>
       <c r="D42" s="102">
         <f t="shared" si="17"/>
-        <v>7.66</v>
+        <v>6.11</v>
       </c>
       <c r="P42" s="100">
         <v>2.0</v>
@@ -15020,7 +15027,7 @@
       </c>
       <c r="D43" s="102">
         <f t="shared" si="17"/>
-        <v>6.37</v>
+        <v>5.31</v>
       </c>
       <c r="P43" s="100">
         <v>1.0</v>
@@ -15052,7 +15059,7 @@
       </c>
       <c r="D44" s="102">
         <f t="shared" si="17"/>
-        <v>5.53</v>
+        <v>0.48</v>
       </c>
       <c r="P44" s="100">
         <v>2.0</v>
@@ -15082,7 +15089,7 @@
       </c>
       <c r="D45" s="102">
         <f t="shared" si="17"/>
-        <v>7.41</v>
+        <v>7.12</v>
       </c>
       <c r="P45" s="100">
         <v>1.0</v>
@@ -15100,7 +15107,7 @@
       </c>
       <c r="D46" s="102">
         <f t="shared" si="17"/>
-        <v>7.8</v>
+        <v>7.48</v>
       </c>
       <c r="G46" s="115" t="s">
         <v>183</v>
@@ -15124,7 +15131,7 @@
       </c>
       <c r="D47" s="102">
         <f t="shared" si="17"/>
-        <v>1.3</v>
+        <v>1.94</v>
       </c>
       <c r="G47" s="116" t="s">
         <v>37</v>
@@ -15154,7 +15161,7 @@
       </c>
       <c r="D48" s="102">
         <f t="shared" si="17"/>
-        <v>1.7</v>
+        <v>6.31</v>
       </c>
       <c r="G48" s="116" t="s">
         <v>36</v>
@@ -15191,7 +15198,7 @@
       </c>
       <c r="D49" s="102">
         <f t="shared" si="17"/>
-        <v>2</v>
+        <v>3.71</v>
       </c>
       <c r="G49" s="116" t="s">
         <v>27</v>
@@ -15224,11 +15231,11 @@
     </row>
     <row r="50">
       <c r="C50" s="114" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="D50" s="102">
         <f t="shared" si="17"/>
-        <v>3.75</v>
+        <v>6.11</v>
       </c>
       <c r="G50" s="116" t="s">
         <v>28</v>
@@ -15237,7 +15244,7 @@
         <v>0.497437843674554</v>
       </c>
       <c r="J50" s="26" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="K50" s="89">
         <f>PERCENTILE(H47:H51,0.25)</f>
@@ -15261,11 +15268,11 @@
     </row>
     <row r="51">
       <c r="C51" s="114" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D51" s="102">
         <f t="shared" si="17"/>
-        <v>0.19</v>
+        <v>2.2</v>
       </c>
       <c r="G51" s="116" t="s">
         <v>24</v>
@@ -15274,7 +15281,7 @@
         <v>0.247446036291655</v>
       </c>
       <c r="J51" s="26" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="K51" s="89">
         <f>PERCENTILE(H47:H51,0.75)</f>
@@ -15298,11 +15305,11 @@
     </row>
     <row r="52">
       <c r="C52" s="114" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D52" s="102">
         <f t="shared" si="17"/>
-        <v>5.82</v>
+        <v>2.61</v>
       </c>
       <c r="P52" s="100">
         <v>0.0</v>
@@ -15322,11 +15329,11 @@
     </row>
     <row r="53">
       <c r="C53" s="114" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D53" s="102">
         <f t="shared" si="17"/>
-        <v>3</v>
+        <v>5.29</v>
       </c>
       <c r="P53" s="100">
         <v>0.0</v>
@@ -15346,11 +15353,11 @@
     </row>
     <row r="54">
       <c r="C54" s="114" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D54" s="102">
         <f t="shared" si="17"/>
-        <v>6.17</v>
+        <v>6.07</v>
       </c>
       <c r="P54" s="100">
         <v>2.0</v>
@@ -15370,11 +15377,11 @@
     </row>
     <row r="55">
       <c r="C55" s="114" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D55" s="102">
         <f t="shared" si="17"/>
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="P55" s="100">
         <v>0.0</v>
@@ -15394,11 +15401,11 @@
     </row>
     <row r="56">
       <c r="C56" s="114" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D56" s="102">
         <f t="shared" si="17"/>
-        <v>5.46</v>
+        <v>1.33</v>
       </c>
       <c r="P56" s="100">
         <v>0.0</v>
@@ -15418,11 +15425,11 @@
     </row>
     <row r="57">
       <c r="C57" s="114" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D57" s="102">
         <f t="shared" si="17"/>
-        <v>5.43</v>
+        <v>7.98</v>
       </c>
       <c r="P57" s="100">
         <v>2.0</v>
@@ -15442,14 +15449,14 @@
     </row>
     <row r="58">
       <c r="C58" s="114" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D58" s="102">
         <f t="shared" si="17"/>
-        <v>5.89</v>
+        <v>6.55</v>
       </c>
       <c r="G58" s="118" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H58" s="119"/>
       <c r="P58" s="100">
@@ -15470,15 +15477,15 @@
     </row>
     <row r="59">
       <c r="C59" s="114" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D59" s="102">
         <f t="shared" si="17"/>
-        <v>5.69</v>
+        <v>3.05</v>
       </c>
       <c r="G59" s="119"/>
       <c r="H59" s="120" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="P59" s="100">
         <v>0.0</v>
@@ -15498,15 +15505,15 @@
     </row>
     <row r="60">
       <c r="C60" s="114" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D60" s="102">
         <f t="shared" si="17"/>
-        <v>5.83</v>
+        <v>6.52</v>
       </c>
       <c r="G60" s="119"/>
       <c r="H60" s="120" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="P60" s="100">
         <v>2.0</v>
@@ -15526,15 +15533,15 @@
     </row>
     <row r="61">
       <c r="C61" s="114" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D61" s="102">
         <f t="shared" si="17"/>
-        <v>1.11</v>
+        <v>7.07</v>
       </c>
       <c r="G61" s="119"/>
       <c r="H61" s="120" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P61" s="100">
         <v>2.0</v>
@@ -15554,15 +15561,15 @@
     </row>
     <row r="62">
       <c r="C62" s="114" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D62" s="102">
         <f t="shared" si="17"/>
-        <v>6.65</v>
+        <v>6.83</v>
       </c>
       <c r="G62" s="119"/>
       <c r="H62" s="120" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P62" s="100">
         <v>1.0</v>
@@ -15582,15 +15589,15 @@
     </row>
     <row r="63">
       <c r="C63" s="114" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D63" s="102">
         <f t="shared" si="17"/>
-        <v>2.55</v>
+        <v>7</v>
       </c>
       <c r="G63" s="119"/>
       <c r="H63" s="120" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P63" s="100">
         <v>0.0</v>
@@ -15604,11 +15611,11 @@
     </row>
     <row r="64">
       <c r="C64" s="114" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D64" s="102">
         <f t="shared" si="17"/>
-        <v>7.96</v>
+        <v>9.55</v>
       </c>
       <c r="P64" s="100">
         <v>1.0</v>
@@ -15622,11 +15629,11 @@
     </row>
     <row r="65">
       <c r="C65" s="114" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D65" s="102">
         <f t="shared" si="17"/>
-        <v>7.09</v>
+        <v>7.94</v>
       </c>
       <c r="P65" s="100">
         <v>2.0</v>
@@ -15640,11 +15647,11 @@
     </row>
     <row r="66">
       <c r="C66" s="114" t="s">
-        <v>160</v>
+        <v>213</v>
       </c>
       <c r="D66" s="102">
         <f t="shared" si="17"/>
-        <v>7.91</v>
+        <v>5.68</v>
       </c>
       <c r="P66" s="100">
         <v>0.0</v>
@@ -15662,7 +15669,7 @@
       </c>
       <c r="D67" s="102">
         <f t="shared" si="17"/>
-        <v>8.34</v>
+        <v>6.33</v>
       </c>
       <c r="P67" s="100">
         <v>0.0</v>
@@ -15680,7 +15687,7 @@
       </c>
       <c r="D68" s="102">
         <f t="shared" si="17"/>
-        <v>6.15</v>
+        <v>6.67</v>
       </c>
       <c r="P68" s="100">
         <v>1.0</v>
@@ -15698,7 +15705,7 @@
       </c>
       <c r="D69" s="102">
         <f t="shared" si="17"/>
-        <v>7.72</v>
+        <v>8.53</v>
       </c>
       <c r="P69" s="100">
         <v>2.0</v>
@@ -15716,7 +15723,7 @@
       </c>
       <c r="D70" s="102">
         <f t="shared" si="17"/>
-        <v>6.61</v>
+        <v>7.41</v>
       </c>
       <c r="P70" s="100">
         <v>1.0</v>
@@ -15734,7 +15741,7 @@
       </c>
       <c r="D71" s="102">
         <f t="shared" si="17"/>
-        <v>7.11</v>
+        <v>4.69</v>
       </c>
       <c r="F71" s="121"/>
       <c r="P71" s="100">
@@ -15753,7 +15760,7 @@
       </c>
       <c r="D72" s="102">
         <f t="shared" si="17"/>
-        <v>4.75</v>
+        <v>5.7</v>
       </c>
       <c r="P72" s="100">
         <v>0.0</v>
@@ -15767,11 +15774,11 @@
     </row>
     <row r="73">
       <c r="C73" s="114" t="s">
-        <v>196</v>
+        <v>129</v>
       </c>
       <c r="D73" s="102">
         <f t="shared" si="17"/>
-        <v>6.17</v>
+        <v>4.92</v>
       </c>
       <c r="P73" s="100">
         <v>1.0</v>
@@ -15785,11 +15792,11 @@
     </row>
     <row r="74">
       <c r="C74" s="114" t="s">
-        <v>220</v>
+        <v>143</v>
       </c>
       <c r="D74" s="102">
         <f t="shared" si="17"/>
-        <v>3.91</v>
+        <v>6.18</v>
       </c>
       <c r="P74" s="100">
         <v>0.0</v>
@@ -15803,11 +15810,11 @@
     </row>
     <row r="75">
       <c r="C75" s="114" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D75" s="102">
         <f t="shared" si="17"/>
-        <v>6.22</v>
+        <v>4.97</v>
       </c>
       <c r="P75" s="100">
         <v>1.0</v>
@@ -15821,11 +15828,11 @@
     </row>
     <row r="76">
       <c r="C76" s="114" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D76" s="102">
         <f t="shared" si="17"/>
-        <v>7.88</v>
+        <v>7.56</v>
       </c>
       <c r="P76" s="100">
         <v>0.0</v>
@@ -15839,11 +15846,11 @@
     </row>
     <row r="77">
       <c r="C77" s="114" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D77" s="102">
         <f t="shared" si="17"/>
-        <v>6.04</v>
+        <v>6.3</v>
       </c>
       <c r="P77" s="100">
         <v>0.0</v>
@@ -15857,11 +15864,11 @@
     </row>
     <row r="78">
       <c r="C78" s="114" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D78" s="102">
         <f t="shared" si="17"/>
-        <v>6.96</v>
+        <v>1.16</v>
       </c>
       <c r="P78" s="100">
         <v>1.0</v>
@@ -15875,11 +15882,11 @@
     </row>
     <row r="79">
       <c r="C79" s="114" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D79" s="102">
         <f t="shared" si="17"/>
-        <v>7.3</v>
+        <v>7.38</v>
       </c>
       <c r="P79" s="100">
         <v>2.0</v>
@@ -15893,11 +15900,11 @@
     </row>
     <row r="80">
       <c r="C80" s="114" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D80" s="102">
         <f t="shared" si="17"/>
-        <v>9.45</v>
+        <v>7.28</v>
       </c>
       <c r="P80" s="100">
         <v>1.0</v>
@@ -15911,11 +15918,11 @@
     </row>
     <row r="81">
       <c r="C81" s="114" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D81" s="102">
         <f t="shared" si="17"/>
-        <v>9.23</v>
+        <v>4.83</v>
       </c>
       <c r="P81" s="100">
         <v>2.0</v>
@@ -15929,11 +15936,11 @@
     </row>
     <row r="82">
       <c r="C82" s="114" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D82" s="102">
         <f t="shared" si="17"/>
-        <v>0.97</v>
+        <v>5.57</v>
       </c>
       <c r="P82" s="100">
         <v>1.0</v>
@@ -15947,11 +15954,11 @@
     </row>
     <row r="83">
       <c r="C83" s="114" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D83" s="102">
         <f t="shared" si="17"/>
-        <v>6.06</v>
+        <v>5.84</v>
       </c>
       <c r="P83" s="100">
         <v>0.0</v>
@@ -15965,11 +15972,11 @@
     </row>
     <row r="84">
       <c r="C84" s="114" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D84" s="102">
         <f t="shared" si="17"/>
-        <v>4.45</v>
+        <v>5.34</v>
       </c>
       <c r="P84" s="100">
         <v>1.0</v>
@@ -39051,14 +39058,14 @@
     <row r="1">
       <c r="A1" s="126"/>
       <c r="B1" s="127" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C1" s="128"/>
       <c r="D1" s="128"/>
       <c r="E1" s="128"/>
       <c r="F1" s="128"/>
       <c r="G1" s="129" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H1" s="128"/>
       <c r="I1" s="128"/>
@@ -39092,19 +39099,19 @@
         <v>3</v>
       </c>
       <c r="B2" s="131" t="s">
+        <v>232</v>
+      </c>
+      <c r="C2" s="132" t="s">
         <v>233</v>
-      </c>
-      <c r="C2" s="132" t="s">
-        <v>234</v>
       </c>
       <c r="D2" s="132" t="s">
         <v>171</v>
       </c>
       <c r="E2" s="132" t="s">
+        <v>234</v>
+      </c>
+      <c r="F2" s="133" t="s">
         <v>235</v>
-      </c>
-      <c r="F2" s="133" t="s">
-        <v>236</v>
       </c>
       <c r="G2" s="131">
         <v>1.0</v>
@@ -39116,30 +39123,30 @@
         <v>2.0</v>
       </c>
       <c r="J2" s="132" t="s">
+        <v>236</v>
+      </c>
+      <c r="K2" s="134" t="s">
         <v>237</v>
       </c>
-      <c r="K2" s="134" t="s">
+      <c r="L2" s="132" t="s">
         <v>238</v>
       </c>
-      <c r="L2" s="132" t="s">
+      <c r="M2" s="135" t="s">
         <v>239</v>
       </c>
-      <c r="M2" s="135" t="s">
+      <c r="N2" s="116" t="s">
         <v>240</v>
       </c>
-      <c r="N2" s="116" t="s">
+      <c r="O2" s="116" t="s">
         <v>241</v>
       </c>
-      <c r="O2" s="116" t="s">
+      <c r="P2" s="116" t="s">
         <v>242</v>
-      </c>
-      <c r="P2" s="116" t="s">
-        <v>243</v>
       </c>
       <c r="Q2" s="7"/>
       <c r="R2" s="7"/>
       <c r="S2" s="94" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="T2" s="7"/>
       <c r="U2" s="7"/>
@@ -39229,7 +39236,7 @@
       <c r="Q4" s="7"/>
       <c r="R4" s="7"/>
       <c r="S4" s="141" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="T4" s="142"/>
       <c r="Z4" s="34"/>
@@ -39265,7 +39272,7 @@
       <c r="P5" s="144"/>
       <c r="S5" s="142"/>
       <c r="T5" s="145" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="6">
@@ -39298,11 +39305,11 @@
       <c r="R6" s="7"/>
       <c r="S6" s="142"/>
       <c r="T6" s="145" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="Z6" s="83"/>
       <c r="AD6" s="26" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="7">
@@ -39332,7 +39339,7 @@
       <c r="O7" s="74"/>
       <c r="P7" s="147"/>
       <c r="AD7" s="145" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AE7" s="142"/>
       <c r="AF7" s="142"/>
@@ -39365,11 +39372,11 @@
       <c r="O8" s="74"/>
       <c r="P8" s="147"/>
       <c r="S8" s="145" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AA8" s="83"/>
       <c r="AD8" s="145" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="9">
@@ -39568,7 +39575,7 @@
       <c r="O15" s="74"/>
       <c r="P15" s="147"/>
       <c r="S15" s="26" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="16">
@@ -39681,7 +39688,7 @@
       <c r="Q19" s="7"/>
       <c r="R19" s="7"/>
       <c r="S19" s="26" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="20">
@@ -39965,7 +39972,7 @@
       <c r="E27" s="7"/>
       <c r="F27" s="7"/>
       <c r="G27" s="152" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H27" s="7"/>
       <c r="I27" s="7"/>
@@ -40050,7 +40057,7 @@
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
       <c r="D29" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E29" s="4">
         <f>J29</f>
@@ -40072,10 +40079,10 @@
       </c>
       <c r="K29" s="7"/>
       <c r="L29" s="94" t="s">
+        <v>255</v>
+      </c>
+      <c r="M29" s="94" t="s">
         <v>256</v>
-      </c>
-      <c r="M29" s="94" t="s">
-        <v>257</v>
       </c>
       <c r="O29" s="4">
         <v>1.0</v>
@@ -40175,7 +40182,7 @@
       </c>
       <c r="R31" s="7"/>
       <c r="S31" s="94" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="T31" s="7"/>
       <c r="U31" s="7"/>
@@ -40237,7 +40244,7 @@
       <c r="E33" s="7"/>
       <c r="F33" s="7"/>
       <c r="G33" s="98" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J33" s="7"/>
       <c r="K33" s="7"/>
@@ -40251,10 +40258,10 @@
       <c r="P33" s="7"/>
       <c r="R33" s="7"/>
       <c r="T33" s="51" t="s">
+        <v>259</v>
+      </c>
+      <c r="W33" s="26" t="s">
         <v>260</v>
-      </c>
-      <c r="W33" s="26" t="s">
-        <v>261</v>
       </c>
       <c r="AA33" s="34"/>
       <c r="AD33" s="7"/>
@@ -40297,7 +40304,7 @@
         <v>1626.0</v>
       </c>
       <c r="U34" s="92" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="W34" s="26">
         <v>5193.0</v>
@@ -40342,7 +40349,7 @@
         <v>4176.0</v>
       </c>
       <c r="U35" s="92" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="W35" s="26">
         <v>4863.0</v>
@@ -40440,7 +40447,7 @@
       <c r="D38" s="7"/>
       <c r="E38" s="7"/>
       <c r="F38" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G38" s="155">
         <f t="shared" ref="G38:I38" si="8">G30-G35</f>
@@ -40642,7 +40649,7 @@
       <c r="Q45" s="7"/>
       <c r="R45" s="7"/>
       <c r="T45" s="145" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AD45" s="7"/>
       <c r="AE45" s="7"/>
@@ -40806,7 +40813,7 @@
         <v>11</v>
       </c>
       <c r="AG49" s="61" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="50">
@@ -40971,7 +40978,7 @@
         <v>13.03594852814783</v>
       </c>
       <c r="AG52" s="61" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="53">
@@ -41032,7 +41039,7 @@
         <v>6.291840048860032</v>
       </c>
       <c r="AG53" s="61" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="54">
@@ -41093,7 +41100,7 @@
         <v>2.7243520649411117</v>
       </c>
       <c r="AG54" s="61" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="55">
@@ -41154,7 +41161,7 @@
         <v>2.1429979739456915</v>
       </c>
       <c r="AG55" s="61" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="56">
@@ -41215,7 +41222,7 @@
         <v>3.98032040346951</v>
       </c>
       <c r="AG56" s="61" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="57">
@@ -41438,10 +41445,10 @@
       <c r="R62" s="7"/>
       <c r="S62" s="7"/>
       <c r="U62" s="26" t="s">
+        <v>266</v>
+      </c>
+      <c r="V62" s="26" t="s">
         <v>267</v>
-      </c>
-      <c r="V62" s="26" t="s">
-        <v>268</v>
       </c>
       <c r="AC62" s="7"/>
       <c r="AD62" s="7"/>
@@ -41483,7 +41490,7 @@
         <v>2165.0</v>
       </c>
       <c r="W63" s="26" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AC63" s="7"/>
       <c r="AD63" s="7"/>
@@ -42117,7 +42124,7 @@
       <c r="R79" s="7"/>
       <c r="S79" s="7"/>
       <c r="T79" s="94" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="U79" s="7"/>
       <c r="V79" s="7"/>
@@ -42158,7 +42165,7 @@
       <c r="R80" s="7"/>
       <c r="S80" s="7"/>
       <c r="T80" s="26" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="U80" s="18"/>
       <c r="V80" s="18"/>
@@ -74919,146 +74926,146 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="26" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="2">
       <c r="B2" s="7"/>
       <c r="C2" s="165" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E2" s="166"/>
       <c r="F2" s="94" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H2" s="166"/>
     </row>
     <row r="3">
       <c r="B3" s="115" t="s">
+        <v>274</v>
+      </c>
+      <c r="C3" s="167" t="s">
         <v>275</v>
       </c>
-      <c r="C3" s="167" t="s">
+      <c r="D3" s="115" t="s">
         <v>276</v>
-      </c>
-      <c r="D3" s="115" t="s">
-        <v>277</v>
       </c>
       <c r="E3" s="168" t="s">
         <v>97</v>
       </c>
       <c r="F3" s="115" t="s">
+        <v>277</v>
+      </c>
+      <c r="G3" s="115" t="s">
         <v>278</v>
       </c>
-      <c r="G3" s="115" t="s">
+      <c r="H3" s="115" t="s">
         <v>279</v>
-      </c>
-      <c r="H3" s="115" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="169" t="s">
+        <v>280</v>
+      </c>
+      <c r="C4" s="170" t="s">
         <v>281</v>
       </c>
-      <c r="C4" s="170" t="s">
+      <c r="D4" s="116" t="s">
         <v>282</v>
       </c>
-      <c r="D4" s="116" t="s">
+      <c r="E4" s="171" t="s">
         <v>283</v>
       </c>
-      <c r="E4" s="171" t="s">
+      <c r="F4" s="172" t="s">
         <v>284</v>
       </c>
-      <c r="F4" s="172" t="s">
+      <c r="G4" s="172" t="s">
         <v>285</v>
-      </c>
-      <c r="G4" s="172" t="s">
-        <v>286</v>
       </c>
       <c r="H4" s="116"/>
     </row>
     <row r="5">
       <c r="B5" s="169" t="s">
+        <v>286</v>
+      </c>
+      <c r="C5" s="173" t="s">
         <v>287</v>
-      </c>
-      <c r="C5" s="173" t="s">
-        <v>288</v>
       </c>
       <c r="D5" s="126"/>
       <c r="E5" s="171" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F5" s="174" t="s">
+        <v>288</v>
+      </c>
+      <c r="G5" s="175" t="s">
         <v>289</v>
-      </c>
-      <c r="G5" s="175" t="s">
-        <v>290</v>
       </c>
       <c r="H5" s="116"/>
     </row>
     <row r="6">
       <c r="B6" s="169" t="s">
+        <v>290</v>
+      </c>
+      <c r="C6" s="170" t="s">
+        <v>281</v>
+      </c>
+      <c r="D6" s="116" t="s">
         <v>291</v>
       </c>
-      <c r="C6" s="170" t="s">
-        <v>282</v>
-      </c>
-      <c r="D6" s="116" t="s">
-        <v>292</v>
-      </c>
       <c r="E6" s="171" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F6" s="116" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G6" s="116"/>
       <c r="H6" s="116"/>
     </row>
     <row r="7">
       <c r="B7" s="116" t="s">
+        <v>292</v>
+      </c>
+      <c r="C7" s="176" t="s">
         <v>293</v>
-      </c>
-      <c r="C7" s="176" t="s">
-        <v>294</v>
       </c>
       <c r="D7" s="116"/>
       <c r="E7" s="177" t="s">
+        <v>294</v>
+      </c>
+      <c r="F7" s="170" t="s">
         <v>295</v>
-      </c>
-      <c r="F7" s="170" t="s">
-        <v>296</v>
       </c>
       <c r="G7" s="116"/>
       <c r="H7" s="116" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="178" t="s">
+        <v>297</v>
+      </c>
+      <c r="C8" s="179" t="s">
         <v>298</v>
-      </c>
-      <c r="C8" s="179" t="s">
-        <v>299</v>
       </c>
       <c r="D8" s="180"/>
       <c r="E8" s="178" t="s">
+        <v>299</v>
+      </c>
+      <c r="F8" s="181" t="s">
         <v>300</v>
       </c>
-      <c r="F8" s="181" t="s">
+      <c r="G8" s="182" t="s">
         <v>301</v>
-      </c>
-      <c r="G8" s="182" t="s">
-        <v>302</v>
       </c>
       <c r="H8" s="180"/>
     </row>
     <row r="9">
       <c r="B9" s="19" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C9" s="183" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D9" s="74"/>
       <c r="E9" s="74"/>
@@ -75068,27 +75075,27 @@
     </row>
     <row r="10">
       <c r="B10" s="19" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C10" s="146"/>
       <c r="D10" s="74"/>
       <c r="E10" s="74"/>
       <c r="F10" s="146"/>
       <c r="G10" s="172" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H10" s="74"/>
     </row>
     <row r="11">
       <c r="B11" s="19" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C11" s="146"/>
       <c r="D11" s="74"/>
       <c r="E11" s="74"/>
       <c r="F11" s="146"/>
       <c r="G11" s="184" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H11" s="19"/>
     </row>
@@ -75111,7 +75118,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="34" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="L1" s="8"/>
     </row>
@@ -75120,16 +75127,16 @@
     </row>
     <row r="3">
       <c r="A3" s="26" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="L3" s="8"/>
     </row>
     <row r="4">
       <c r="B4" s="26" t="s">
+        <v>308</v>
+      </c>
+      <c r="G4" s="26" t="s">
         <v>309</v>
-      </c>
-      <c r="G4" s="26" t="s">
-        <v>310</v>
       </c>
       <c r="L4" s="8"/>
     </row>
@@ -75235,62 +75242,62 @@
     </row>
     <row r="11">
       <c r="A11" s="185" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="34" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="26" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="185" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="34" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="26" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F19" s="83"/>
     </row>
     <row r="20">
       <c r="B20" s="34" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C20" s="36"/>
       <c r="D20" s="36"/>
       <c r="E20" s="36"/>
       <c r="F20" s="36"/>
       <c r="G20" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="H20" s="34" t="s">
         <v>318</v>
       </c>
-      <c r="H20" s="34" t="s">
+      <c r="I20" s="34" t="s">
         <v>319</v>
       </c>
-      <c r="I20" s="34" t="s">
+      <c r="J20" s="34" t="s">
         <v>320</v>
       </c>
-      <c r="J20" s="34" t="s">
+      <c r="K20" s="34" t="s">
         <v>321</v>
-      </c>
-      <c r="K20" s="34" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="34" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G21" s="37">
         <v>2.575</v>
@@ -75298,27 +75305,27 @@
     </row>
     <row r="23">
       <c r="K23" s="34" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="26" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H24" s="26" t="s">
         <v>171</v>
       </c>
       <c r="I24" s="26" t="s">
+        <v>325</v>
+      </c>
+      <c r="K24" s="26" t="s">
         <v>326</v>
       </c>
-      <c r="K24" s="26" t="s">
+      <c r="L24" s="26" t="s">
         <v>327</v>
       </c>
-      <c r="L24" s="26" t="s">
+      <c r="M24" s="26" t="s">
         <v>328</v>
-      </c>
-      <c r="M24" s="26" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="25">
@@ -75337,7 +75344,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K25" s="26" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="26">
@@ -75348,7 +75355,7 @@
         <v>1.19</v>
       </c>
       <c r="K26" s="26" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="27">
@@ -75359,7 +75366,7 @@
         <v>2.19</v>
       </c>
       <c r="K27" s="26" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="28">
@@ -75370,7 +75377,7 @@
         <v>0.05</v>
       </c>
       <c r="K28" s="26" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="29">
@@ -75389,7 +75396,7 @@
         <v>6.42</v>
       </c>
       <c r="K30" s="51" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="31">
@@ -75534,7 +75541,7 @@
         <v>0.61</v>
       </c>
       <c r="K41" s="34" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="42">
@@ -75545,13 +75552,13 @@
         <v>0.69</v>
       </c>
       <c r="K42" s="26" t="s">
+        <v>326</v>
+      </c>
+      <c r="L42" s="26" t="s">
         <v>327</v>
       </c>
-      <c r="L42" s="26" t="s">
+      <c r="M42" s="26" t="s">
         <v>328</v>
-      </c>
-      <c r="M42" s="26" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="43">
@@ -75683,7 +75690,7 @@
         <v>0.0</v>
       </c>
       <c r="K51" s="26" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="52">
@@ -75711,17 +75718,17 @@
       </c>
       <c r="K54" s="74"/>
       <c r="L54" s="186" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="M54" s="187"/>
       <c r="N54" s="79" t="s">
         <v>5</v>
       </c>
       <c r="O54" s="79" t="s">
+        <v>337</v>
+      </c>
+      <c r="P54" s="79" t="s">
         <v>338</v>
-      </c>
-      <c r="P54" s="79" t="s">
-        <v>339</v>
       </c>
       <c r="R54" s="15" t="s">
         <v>107</v>
@@ -75803,7 +75810,7 @@
         <v>5.86</v>
       </c>
       <c r="R57" s="26" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="S57" s="37">
         <f>SUM(P55:P74)</f>
@@ -75818,7 +75825,7 @@
         <v>0.0</v>
       </c>
       <c r="K58" s="19" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="L58" s="188">
         <v>0.57</v>
@@ -75832,7 +75839,7 @@
         <v>0.855</v>
       </c>
       <c r="P58" s="19" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="59">
@@ -75879,7 +75886,7 @@
         <v>0.96</v>
       </c>
       <c r="P60" s="19" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="61">
@@ -75890,7 +75897,7 @@
         <v>0.02</v>
       </c>
       <c r="K61" s="19" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="L61" s="19">
         <v>0.42</v>
@@ -75962,7 +75969,7 @@
         <v>0.0</v>
       </c>
       <c r="K64" s="19" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="L64" s="19">
         <v>0.42</v>
@@ -76106,7 +76113,7 @@
         <v>0.0</v>
       </c>
       <c r="K70" s="19" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="L70" s="19">
         <v>0.66</v>

--- a/data/df_best_models.xlsx
+++ b/data/df_best_models.xlsx
@@ -36,6 +36,16 @@
       <text>
         <t xml:space="preserve">los que mas valor tienen suelen tener un rdo mucho mas rentable que otro.
 </t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="H6">
+      <text>
+        <t xml:space="preserve">lo fuerzo a 65 puesto que sino es 200 dado que acertó todos los partidos</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="G7">
+      <text>
+        <t xml:space="preserve">era 110, lo baje a 25</t>
       </text>
     </comment>
     <comment authorId="0" ref="A1">
@@ -2551,8 +2561,8 @@
   <cols>
     <col customWidth="1" min="3" max="3" width="14.75"/>
     <col customWidth="1" min="5" max="5" width="15.13"/>
-    <col collapsed="1" customWidth="1" min="6" max="6" width="10.13"/>
-    <col customWidth="1" hidden="1" min="7" max="10" width="8.25" outlineLevel="1"/>
+    <col customWidth="1" min="6" max="6" width="10.13"/>
+    <col customWidth="1" min="7" max="10" width="8.25" outlineLevel="1"/>
     <col customWidth="1" min="11" max="11" width="8.75"/>
     <col customWidth="1" min="12" max="12" width="8.25"/>
   </cols>
@@ -2663,24 +2673,28 @@
         <v>45719.0</v>
       </c>
       <c r="D4" s="13">
-        <v>3836.0</v>
+        <v>5414.0</v>
       </c>
       <c r="E4" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="14">
-        <v>80.0</v>
-      </c>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="17" t="str">
+      <c r="F4" s="14"/>
+      <c r="G4" s="15">
+        <v>10.0</v>
+      </c>
+      <c r="H4" s="15">
+        <v>65.0</v>
+      </c>
+      <c r="I4" s="15">
+        <v>50.0</v>
+      </c>
+      <c r="J4" s="17">
         <f t="shared" ref="J4:J8" si="1">IFERROR(AVERAGE(G4:I4),"")</f>
-        <v/>
+        <v>41.66666667</v>
       </c>
       <c r="K4" s="24">
         <f>F4*'Data preparation'!$C$2</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L4" s="25" t="str">
         <f t="shared" ref="L4:L8" si="2">IFERROR(#REF!/#REF!)</f>
@@ -2707,19 +2721,23 @@
       <c r="E5" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="14">
-        <v>100.0</v>
-      </c>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="17" t="str">
+      <c r="F5" s="14"/>
+      <c r="G5" s="15">
+        <v>65.0</v>
+      </c>
+      <c r="H5" s="15">
+        <v>50.0</v>
+      </c>
+      <c r="I5" s="15">
+        <v>110.0</v>
+      </c>
+      <c r="J5" s="17">
         <f t="shared" si="1"/>
-        <v/>
+        <v>75</v>
       </c>
       <c r="K5" s="24">
         <f>F5*'Data preparation'!$C$2</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L5" s="25" t="str">
         <f t="shared" si="2"/>
@@ -2738,24 +2756,28 @@
         <v>45720.0</v>
       </c>
       <c r="D6" s="13">
-        <v>3032.0</v>
+        <v>3993.0</v>
       </c>
       <c r="E6" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="14">
-        <v>140.0</v>
-      </c>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
-      <c r="J6" s="17" t="str">
+      <c r="F6" s="14"/>
+      <c r="G6" s="15">
+        <v>10.0</v>
+      </c>
+      <c r="H6" s="15">
+        <v>65.0</v>
+      </c>
+      <c r="I6" s="15">
+        <v>65.0</v>
+      </c>
+      <c r="J6" s="17">
         <f t="shared" si="1"/>
-        <v/>
+        <v>46.66666667</v>
       </c>
       <c r="K6" s="24">
         <f>F6*'Data preparation'!$C$2</f>
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L6" s="25" t="str">
         <f t="shared" si="2"/>
@@ -2779,19 +2801,23 @@
       <c r="E7" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="14">
-        <v>60.0</v>
-      </c>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
-      <c r="J7" s="17" t="str">
+      <c r="F7" s="14"/>
+      <c r="G7" s="15">
+        <v>25.0</v>
+      </c>
+      <c r="H7" s="15">
+        <v>65.0</v>
+      </c>
+      <c r="I7" s="15">
+        <v>25.0</v>
+      </c>
+      <c r="J7" s="17">
         <f t="shared" si="1"/>
-        <v/>
+        <v>38.33333333</v>
       </c>
       <c r="K7" s="24">
         <f>F7*'Data preparation'!$C$2</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L7" s="25" t="str">
         <f t="shared" si="2"/>
@@ -2810,24 +2836,28 @@
         <v>45720.0</v>
       </c>
       <c r="D8" s="13">
-        <v>870.0</v>
+        <v>3490.0</v>
       </c>
       <c r="E8" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="14"/>
+      <c r="G8" s="15">
         <v>80.0</v>
       </c>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
-      <c r="J8" s="17" t="str">
+      <c r="H8" s="15">
+        <v>95.0</v>
+      </c>
+      <c r="I8" s="15">
+        <v>35.0</v>
+      </c>
+      <c r="J8" s="17">
         <f t="shared" si="1"/>
-        <v/>
+        <v>70</v>
       </c>
       <c r="K8" s="24">
         <f>F8*'Data preparation'!$C$2</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L8" s="25" t="str">
         <f t="shared" si="2"/>
@@ -13517,7 +13547,7 @@
       </c>
       <c r="C3" s="96">
         <f>AVERAGE('Modelos actuales'!K4:K8)</f>
-        <v>9.2</v>
+        <v>0</v>
       </c>
       <c r="L3" s="95"/>
       <c r="P3" s="95"/>

--- a/data/df_best_models.xlsx
+++ b/data/df_best_models.xlsx
@@ -278,7 +278,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="340">
   <si>
     <t>id_country</t>
   </si>
@@ -911,28 +911,28 @@
     <t>Stake promedio</t>
   </si>
   <si>
-    <t>4.68</t>
+    <t>1.84</t>
   </si>
   <si>
-    <t>7.35</t>
+    <t>12.60</t>
   </si>
   <si>
-    <t>7.26</t>
+    <t>9.34</t>
   </si>
   <si>
-    <t>6.11</t>
+    <t>7.90</t>
   </si>
   <si>
-    <t>5.31</t>
+    <t>9.16</t>
   </si>
   <si>
-    <t>0.48</t>
+    <t>5.26</t>
   </si>
   <si>
-    <t>7.12</t>
+    <t>9.20</t>
   </si>
   <si>
-    <t>7.48</t>
+    <t>8.80</t>
   </si>
   <si>
     <t>Country</t>
@@ -941,139 +941,133 @@
     <t>Correl ROI y Expected ROI</t>
   </si>
   <si>
-    <t>1.94</t>
+    <t>1.92</t>
   </si>
   <si>
-    <t>6.31</t>
+    <t>0.50</t>
   </si>
   <si>
     <t>mean</t>
   </si>
   <si>
-    <t>3.71</t>
+    <t>2.20</t>
   </si>
   <si>
     <t>median</t>
   </si>
   <si>
+    <t>4.03</t>
+  </si>
+  <si>
     <t>p25</t>
   </si>
   <si>
-    <t>2.20</t>
+    <t>3.70</t>
   </si>
   <si>
     <t>p75</t>
   </si>
   <si>
-    <t>2.61</t>
+    <t>3.87</t>
   </si>
   <si>
-    <t>5.29</t>
+    <t>9.58</t>
   </si>
   <si>
-    <t>6.07</t>
+    <t>5.15</t>
   </si>
   <si>
-    <t>3.15</t>
+    <t>1.22</t>
   </si>
   <si>
-    <t>1.33</t>
+    <t>6.58</t>
   </si>
   <si>
-    <t>7.98</t>
+    <t>7.32</t>
   </si>
   <si>
-    <t>6.55</t>
+    <t>6.49</t>
   </si>
   <si>
     <t>Gracias a las nuevas métricas de G/P sin bank en test, me di cuenta de que:</t>
   </si>
   <si>
-    <t>3.05</t>
+    <t>6.44</t>
   </si>
   <si>
     <t>La rentabilidad en ITA está en el visitante y no en el empate como creía.</t>
   </si>
   <si>
-    <t>6.52</t>
+    <t>6.43</t>
   </si>
   <si>
     <t>La rentabilidad en ENG y GER está en el empate tal como creía.</t>
   </si>
   <si>
-    <t>7.07</t>
+    <t>7.37</t>
   </si>
   <si>
     <t>En SPA esta repartido aunque Empate saca una ventaja.</t>
   </si>
   <si>
-    <t>6.83</t>
+    <t>9.18</t>
   </si>
   <si>
     <t>En FRA, depende el modelo. A veces local, a veces, empate.</t>
   </si>
   <si>
-    <t>7.00</t>
+    <t>2.59</t>
   </si>
   <si>
     <t>Si en FRA empate no rinde, no tiene sentido exigirle una buena distrib en empate… → Tiene sentido pero al parecer si importa el empate puesto que el modelo que gana se basa en empate.</t>
   </si>
   <si>
-    <t>9.55</t>
+    <t>2.57</t>
   </si>
   <si>
-    <t>7.94</t>
+    <t>2.72</t>
   </si>
   <si>
-    <t>5.68</t>
+    <t>0.39</t>
   </si>
   <si>
-    <t>6.33</t>
+    <t>2.56</t>
   </si>
   <si>
-    <t>6.67</t>
+    <t>9.40</t>
   </si>
   <si>
-    <t>8.53</t>
+    <t>6.29</t>
   </si>
   <si>
-    <t>7.41</t>
+    <t>3.49</t>
   </si>
   <si>
-    <t>4.69</t>
+    <t>2.38</t>
   </si>
   <si>
-    <t>5.70</t>
+    <t>3.76</t>
   </si>
   <si>
-    <t>4.97</t>
+    <t>3.47</t>
   </si>
   <si>
-    <t>7.56</t>
+    <t>7.27</t>
   </si>
   <si>
-    <t>6.30</t>
+    <t>4.60</t>
   </si>
   <si>
-    <t>1.16</t>
+    <t>3.93</t>
   </si>
   <si>
-    <t>7.38</t>
+    <t>5.86</t>
   </si>
   <si>
-    <t>7.28</t>
+    <t>1.60</t>
   </si>
   <si>
-    <t>4.83</t>
-  </si>
-  <si>
-    <t>5.57</t>
-  </si>
-  <si>
-    <t>5.84</t>
-  </si>
-  <si>
-    <t>5.34</t>
+    <t>0.22</t>
   </si>
   <si>
     <t>RENTABILIDAD</t>
@@ -2673,7 +2667,7 @@
         <v>45719.0</v>
       </c>
       <c r="D4" s="13">
-        <v>5414.0</v>
+        <v>6297.0</v>
       </c>
       <c r="E4" s="13" t="s">
         <v>13</v>
@@ -2796,24 +2790,24 @@
         <v>45720.0</v>
       </c>
       <c r="D7" s="13">
-        <v>2114.0</v>
+        <v>2273.0</v>
       </c>
       <c r="E7" s="13" t="s">
         <v>13</v>
       </c>
       <c r="F7" s="14"/>
       <c r="G7" s="15">
-        <v>25.0</v>
+        <v>80.0</v>
       </c>
       <c r="H7" s="15">
-        <v>65.0</v>
+        <v>110.0</v>
       </c>
       <c r="I7" s="15">
-        <v>25.0</v>
+        <v>10.0</v>
       </c>
       <c r="J7" s="17">
         <f t="shared" si="1"/>
-        <v>38.33333333</v>
+        <v>66.66666667</v>
       </c>
       <c r="K7" s="24">
         <f>F7*'Data preparation'!$C$2</f>
@@ -14848,7 +14842,7 @@
       <c r="C37" s="36"/>
       <c r="D37" s="111">
         <f>AVERAGE(D39:D1775)</f>
-        <v>5.637826087</v>
+        <v>5.067380952</v>
       </c>
       <c r="G37" s="34" t="s">
         <v>36</v>
@@ -14917,7 +14911,7 @@
       </c>
       <c r="D39" s="102">
         <f t="shared" ref="D39:D221" si="17">IF(COUNTA(C39)=1,C39/1,"")</f>
-        <v>4.68</v>
+        <v>1.84</v>
       </c>
       <c r="G39" s="34" t="s">
         <v>28</v>
@@ -14955,7 +14949,7 @@
       </c>
       <c r="D40" s="102">
         <f t="shared" si="17"/>
-        <v>7.35</v>
+        <v>12.6</v>
       </c>
       <c r="G40" s="34" t="s">
         <v>24</v>
@@ -14993,7 +14987,7 @@
       </c>
       <c r="D41" s="102">
         <f t="shared" si="17"/>
-        <v>7.26</v>
+        <v>9.34</v>
       </c>
       <c r="P41" s="100">
         <v>0.0</v>
@@ -15025,7 +15019,7 @@
       </c>
       <c r="D42" s="102">
         <f t="shared" si="17"/>
-        <v>6.11</v>
+        <v>7.9</v>
       </c>
       <c r="P42" s="100">
         <v>2.0</v>
@@ -15057,7 +15051,7 @@
       </c>
       <c r="D43" s="102">
         <f t="shared" si="17"/>
-        <v>5.31</v>
+        <v>9.16</v>
       </c>
       <c r="P43" s="100">
         <v>1.0</v>
@@ -15089,7 +15083,7 @@
       </c>
       <c r="D44" s="102">
         <f t="shared" si="17"/>
-        <v>0.48</v>
+        <v>5.26</v>
       </c>
       <c r="P44" s="100">
         <v>2.0</v>
@@ -15119,7 +15113,7 @@
       </c>
       <c r="D45" s="102">
         <f t="shared" si="17"/>
-        <v>7.12</v>
+        <v>9.2</v>
       </c>
       <c r="P45" s="100">
         <v>1.0</v>
@@ -15137,7 +15131,7 @@
       </c>
       <c r="D46" s="102">
         <f t="shared" si="17"/>
-        <v>7.48</v>
+        <v>8.8</v>
       </c>
       <c r="G46" s="115" t="s">
         <v>183</v>
@@ -15161,7 +15155,7 @@
       </c>
       <c r="D47" s="102">
         <f t="shared" si="17"/>
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="G47" s="116" t="s">
         <v>37</v>
@@ -15191,7 +15185,7 @@
       </c>
       <c r="D48" s="102">
         <f t="shared" si="17"/>
-        <v>6.31</v>
+        <v>0.5</v>
       </c>
       <c r="G48" s="116" t="s">
         <v>36</v>
@@ -15228,7 +15222,7 @@
       </c>
       <c r="D49" s="102">
         <f t="shared" si="17"/>
-        <v>3.71</v>
+        <v>2.2</v>
       </c>
       <c r="G49" s="116" t="s">
         <v>27</v>
@@ -15261,11 +15255,11 @@
     </row>
     <row r="50">
       <c r="C50" s="114" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="D50" s="102">
         <f t="shared" si="17"/>
-        <v>6.11</v>
+        <v>4.03</v>
       </c>
       <c r="G50" s="116" t="s">
         <v>28</v>
@@ -15274,7 +15268,7 @@
         <v>0.497437843674554</v>
       </c>
       <c r="J50" s="26" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K50" s="89">
         <f>PERCENTILE(H47:H51,0.25)</f>
@@ -15298,11 +15292,11 @@
     </row>
     <row r="51">
       <c r="C51" s="114" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D51" s="102">
         <f t="shared" si="17"/>
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="G51" s="116" t="s">
         <v>24</v>
@@ -15311,7 +15305,7 @@
         <v>0.247446036291655</v>
       </c>
       <c r="J51" s="26" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K51" s="89">
         <f>PERCENTILE(H47:H51,0.75)</f>
@@ -15335,11 +15329,11 @@
     </row>
     <row r="52">
       <c r="C52" s="114" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D52" s="102">
         <f t="shared" si="17"/>
-        <v>2.61</v>
+        <v>3.87</v>
       </c>
       <c r="P52" s="100">
         <v>0.0</v>
@@ -15359,11 +15353,11 @@
     </row>
     <row r="53">
       <c r="C53" s="114" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D53" s="102">
         <f t="shared" si="17"/>
-        <v>5.29</v>
+        <v>9.58</v>
       </c>
       <c r="P53" s="100">
         <v>0.0</v>
@@ -15383,11 +15377,11 @@
     </row>
     <row r="54">
       <c r="C54" s="114" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D54" s="102">
         <f t="shared" si="17"/>
-        <v>6.07</v>
+        <v>5.15</v>
       </c>
       <c r="P54" s="100">
         <v>2.0</v>
@@ -15407,11 +15401,11 @@
     </row>
     <row r="55">
       <c r="C55" s="114" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D55" s="102">
         <f t="shared" si="17"/>
-        <v>3.15</v>
+        <v>1.22</v>
       </c>
       <c r="P55" s="100">
         <v>0.0</v>
@@ -15431,11 +15425,11 @@
     </row>
     <row r="56">
       <c r="C56" s="114" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D56" s="102">
         <f t="shared" si="17"/>
-        <v>1.33</v>
+        <v>6.58</v>
       </c>
       <c r="P56" s="100">
         <v>0.0</v>
@@ -15455,11 +15449,11 @@
     </row>
     <row r="57">
       <c r="C57" s="114" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D57" s="102">
         <f t="shared" si="17"/>
-        <v>7.98</v>
+        <v>7.32</v>
       </c>
       <c r="P57" s="100">
         <v>2.0</v>
@@ -15479,14 +15473,14 @@
     </row>
     <row r="58">
       <c r="C58" s="114" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D58" s="102">
         <f t="shared" si="17"/>
-        <v>6.55</v>
+        <v>6.49</v>
       </c>
       <c r="G58" s="118" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H58" s="119"/>
       <c r="P58" s="100">
@@ -15507,15 +15501,15 @@
     </row>
     <row r="59">
       <c r="C59" s="114" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D59" s="102">
         <f t="shared" si="17"/>
-        <v>3.05</v>
+        <v>6.44</v>
       </c>
       <c r="G59" s="119"/>
       <c r="H59" s="120" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P59" s="100">
         <v>0.0</v>
@@ -15535,15 +15529,15 @@
     </row>
     <row r="60">
       <c r="C60" s="114" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D60" s="102">
         <f t="shared" si="17"/>
-        <v>6.52</v>
+        <v>6.43</v>
       </c>
       <c r="G60" s="119"/>
       <c r="H60" s="120" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P60" s="100">
         <v>2.0</v>
@@ -15563,15 +15557,15 @@
     </row>
     <row r="61">
       <c r="C61" s="114" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D61" s="102">
         <f t="shared" si="17"/>
-        <v>7.07</v>
+        <v>7.37</v>
       </c>
       <c r="G61" s="119"/>
       <c r="H61" s="120" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P61" s="100">
         <v>2.0</v>
@@ -15591,15 +15585,15 @@
     </row>
     <row r="62">
       <c r="C62" s="114" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D62" s="102">
         <f t="shared" si="17"/>
-        <v>6.83</v>
+        <v>9.18</v>
       </c>
       <c r="G62" s="119"/>
       <c r="H62" s="120" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P62" s="100">
         <v>1.0</v>
@@ -15619,15 +15613,15 @@
     </row>
     <row r="63">
       <c r="C63" s="114" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D63" s="102">
         <f t="shared" si="17"/>
-        <v>7</v>
+        <v>2.59</v>
       </c>
       <c r="G63" s="119"/>
       <c r="H63" s="120" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P63" s="100">
         <v>0.0</v>
@@ -15641,11 +15635,11 @@
     </row>
     <row r="64">
       <c r="C64" s="114" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D64" s="102">
         <f t="shared" si="17"/>
-        <v>9.55</v>
+        <v>2.57</v>
       </c>
       <c r="P64" s="100">
         <v>1.0</v>
@@ -15659,11 +15653,11 @@
     </row>
     <row r="65">
       <c r="C65" s="114" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D65" s="102">
         <f t="shared" si="17"/>
-        <v>7.94</v>
+        <v>2.72</v>
       </c>
       <c r="P65" s="100">
         <v>2.0</v>
@@ -15677,11 +15671,11 @@
     </row>
     <row r="66">
       <c r="C66" s="114" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D66" s="102">
         <f t="shared" si="17"/>
-        <v>5.68</v>
+        <v>0.39</v>
       </c>
       <c r="P66" s="100">
         <v>0.0</v>
@@ -15695,11 +15689,11 @@
     </row>
     <row r="67">
       <c r="C67" s="114" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D67" s="102">
         <f t="shared" si="17"/>
-        <v>6.33</v>
+        <v>2.56</v>
       </c>
       <c r="P67" s="100">
         <v>0.0</v>
@@ -15713,11 +15707,11 @@
     </row>
     <row r="68">
       <c r="C68" s="114" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D68" s="102">
         <f t="shared" si="17"/>
-        <v>6.67</v>
+        <v>9.4</v>
       </c>
       <c r="P68" s="100">
         <v>1.0</v>
@@ -15731,11 +15725,11 @@
     </row>
     <row r="69">
       <c r="C69" s="114" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D69" s="102">
         <f t="shared" si="17"/>
-        <v>8.53</v>
+        <v>6.29</v>
       </c>
       <c r="P69" s="100">
         <v>2.0</v>
@@ -15749,11 +15743,11 @@
     </row>
     <row r="70">
       <c r="C70" s="114" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D70" s="102">
         <f t="shared" si="17"/>
-        <v>7.41</v>
+        <v>3.49</v>
       </c>
       <c r="P70" s="100">
         <v>1.0</v>
@@ -15767,11 +15761,11 @@
     </row>
     <row r="71">
       <c r="C71" s="114" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D71" s="102">
         <f t="shared" si="17"/>
-        <v>4.69</v>
+        <v>2.38</v>
       </c>
       <c r="F71" s="121"/>
       <c r="P71" s="100">
@@ -15786,11 +15780,11 @@
     </row>
     <row r="72">
       <c r="C72" s="114" t="s">
-        <v>219</v>
+        <v>140</v>
       </c>
       <c r="D72" s="102">
         <f t="shared" si="17"/>
-        <v>5.7</v>
+        <v>3.65</v>
       </c>
       <c r="P72" s="100">
         <v>0.0</v>
@@ -15804,11 +15798,11 @@
     </row>
     <row r="73">
       <c r="C73" s="114" t="s">
-        <v>129</v>
+        <v>220</v>
       </c>
       <c r="D73" s="102">
         <f t="shared" si="17"/>
-        <v>4.92</v>
+        <v>3.76</v>
       </c>
       <c r="P73" s="100">
         <v>1.0</v>
@@ -15822,11 +15816,11 @@
     </row>
     <row r="74">
       <c r="C74" s="114" t="s">
-        <v>143</v>
+        <v>221</v>
       </c>
       <c r="D74" s="102">
         <f t="shared" si="17"/>
-        <v>6.18</v>
+        <v>3.47</v>
       </c>
       <c r="P74" s="100">
         <v>0.0</v>
@@ -15840,11 +15834,11 @@
     </row>
     <row r="75">
       <c r="C75" s="114" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D75" s="102">
         <f t="shared" si="17"/>
-        <v>4.97</v>
+        <v>7.27</v>
       </c>
       <c r="P75" s="100">
         <v>1.0</v>
@@ -15858,11 +15852,11 @@
     </row>
     <row r="76">
       <c r="C76" s="114" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D76" s="102">
         <f t="shared" si="17"/>
-        <v>7.56</v>
+        <v>4.6</v>
       </c>
       <c r="P76" s="100">
         <v>0.0</v>
@@ -15876,11 +15870,11 @@
     </row>
     <row r="77">
       <c r="C77" s="114" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D77" s="102">
         <f t="shared" si="17"/>
-        <v>6.3</v>
+        <v>3.93</v>
       </c>
       <c r="P77" s="100">
         <v>0.0</v>
@@ -15894,11 +15888,11 @@
     </row>
     <row r="78">
       <c r="C78" s="114" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D78" s="102">
         <f t="shared" si="17"/>
-        <v>1.16</v>
+        <v>5.86</v>
       </c>
       <c r="P78" s="100">
         <v>1.0</v>
@@ -15912,11 +15906,11 @@
     </row>
     <row r="79">
       <c r="C79" s="114" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D79" s="102">
         <f t="shared" si="17"/>
-        <v>7.38</v>
+        <v>1.6</v>
       </c>
       <c r="P79" s="100">
         <v>2.0</v>
@@ -15930,11 +15924,11 @@
     </row>
     <row r="80">
       <c r="C80" s="114" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D80" s="102">
         <f t="shared" si="17"/>
-        <v>7.28</v>
+        <v>0.22</v>
       </c>
       <c r="P80" s="100">
         <v>1.0</v>
@@ -15947,12 +15941,10 @@
       </c>
     </row>
     <row r="81">
-      <c r="C81" s="114" t="s">
-        <v>226</v>
-      </c>
-      <c r="D81" s="102">
+      <c r="C81" s="114"/>
+      <c r="D81" s="102" t="str">
         <f t="shared" si="17"/>
-        <v>4.83</v>
+        <v/>
       </c>
       <c r="P81" s="100">
         <v>2.0</v>
@@ -15965,12 +15957,10 @@
       </c>
     </row>
     <row r="82">
-      <c r="C82" s="114" t="s">
-        <v>227</v>
-      </c>
-      <c r="D82" s="102">
+      <c r="C82" s="114"/>
+      <c r="D82" s="102" t="str">
         <f t="shared" si="17"/>
-        <v>5.57</v>
+        <v/>
       </c>
       <c r="P82" s="100">
         <v>1.0</v>
@@ -15983,12 +15973,10 @@
       </c>
     </row>
     <row r="83">
-      <c r="C83" s="114" t="s">
-        <v>228</v>
-      </c>
-      <c r="D83" s="102">
+      <c r="C83" s="114"/>
+      <c r="D83" s="102" t="str">
         <f t="shared" si="17"/>
-        <v>5.84</v>
+        <v/>
       </c>
       <c r="P83" s="100">
         <v>0.0</v>
@@ -16001,12 +15989,10 @@
       </c>
     </row>
     <row r="84">
-      <c r="C84" s="114" t="s">
-        <v>229</v>
-      </c>
-      <c r="D84" s="102">
+      <c r="C84" s="114"/>
+      <c r="D84" s="102" t="str">
         <f t="shared" si="17"/>
-        <v>5.34</v>
+        <v/>
       </c>
       <c r="P84" s="100">
         <v>1.0</v>
@@ -39088,14 +39074,14 @@
     <row r="1">
       <c r="A1" s="126"/>
       <c r="B1" s="127" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C1" s="128"/>
       <c r="D1" s="128"/>
       <c r="E1" s="128"/>
       <c r="F1" s="128"/>
       <c r="G1" s="129" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="H1" s="128"/>
       <c r="I1" s="128"/>
@@ -39129,19 +39115,19 @@
         <v>3</v>
       </c>
       <c r="B2" s="131" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C2" s="132" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D2" s="132" t="s">
         <v>171</v>
       </c>
       <c r="E2" s="132" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F2" s="133" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G2" s="131">
         <v>1.0</v>
@@ -39153,30 +39139,30 @@
         <v>2.0</v>
       </c>
       <c r="J2" s="132" t="s">
+        <v>234</v>
+      </c>
+      <c r="K2" s="134" t="s">
+        <v>235</v>
+      </c>
+      <c r="L2" s="132" t="s">
         <v>236</v>
       </c>
-      <c r="K2" s="134" t="s">
+      <c r="M2" s="135" t="s">
         <v>237</v>
       </c>
-      <c r="L2" s="132" t="s">
+      <c r="N2" s="116" t="s">
         <v>238</v>
       </c>
-      <c r="M2" s="135" t="s">
+      <c r="O2" s="116" t="s">
         <v>239</v>
       </c>
-      <c r="N2" s="116" t="s">
+      <c r="P2" s="116" t="s">
         <v>240</v>
-      </c>
-      <c r="O2" s="116" t="s">
-        <v>241</v>
-      </c>
-      <c r="P2" s="116" t="s">
-        <v>242</v>
       </c>
       <c r="Q2" s="7"/>
       <c r="R2" s="7"/>
       <c r="S2" s="94" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="T2" s="7"/>
       <c r="U2" s="7"/>
@@ -39266,7 +39252,7 @@
       <c r="Q4" s="7"/>
       <c r="R4" s="7"/>
       <c r="S4" s="141" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="T4" s="142"/>
       <c r="Z4" s="34"/>
@@ -39302,7 +39288,7 @@
       <c r="P5" s="144"/>
       <c r="S5" s="142"/>
       <c r="T5" s="145" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="6">
@@ -39335,11 +39321,11 @@
       <c r="R6" s="7"/>
       <c r="S6" s="142"/>
       <c r="T6" s="145" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="Z6" s="83"/>
       <c r="AD6" s="26" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7">
@@ -39369,7 +39355,7 @@
       <c r="O7" s="74"/>
       <c r="P7" s="147"/>
       <c r="AD7" s="145" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="AE7" s="142"/>
       <c r="AF7" s="142"/>
@@ -39402,11 +39388,11 @@
       <c r="O8" s="74"/>
       <c r="P8" s="147"/>
       <c r="S8" s="145" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AA8" s="83"/>
       <c r="AD8" s="145" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="9">
@@ -39605,7 +39591,7 @@
       <c r="O15" s="74"/>
       <c r="P15" s="147"/>
       <c r="S15" s="26" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="16">
@@ -39718,7 +39704,7 @@
       <c r="Q19" s="7"/>
       <c r="R19" s="7"/>
       <c r="S19" s="26" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="20">
@@ -40002,7 +39988,7 @@
       <c r="E27" s="7"/>
       <c r="F27" s="7"/>
       <c r="G27" s="152" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="H27" s="7"/>
       <c r="I27" s="7"/>
@@ -40087,7 +40073,7 @@
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
       <c r="D29" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E29" s="4">
         <f>J29</f>
@@ -40109,10 +40095,10 @@
       </c>
       <c r="K29" s="7"/>
       <c r="L29" s="94" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="M29" s="94" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="O29" s="4">
         <v>1.0</v>
@@ -40212,7 +40198,7 @@
       </c>
       <c r="R31" s="7"/>
       <c r="S31" s="94" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="T31" s="7"/>
       <c r="U31" s="7"/>
@@ -40274,7 +40260,7 @@
       <c r="E33" s="7"/>
       <c r="F33" s="7"/>
       <c r="G33" s="98" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="J33" s="7"/>
       <c r="K33" s="7"/>
@@ -40288,10 +40274,10 @@
       <c r="P33" s="7"/>
       <c r="R33" s="7"/>
       <c r="T33" s="51" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="W33" s="26" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="AA33" s="34"/>
       <c r="AD33" s="7"/>
@@ -40334,7 +40320,7 @@
         <v>1626.0</v>
       </c>
       <c r="U34" s="92" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="W34" s="26">
         <v>5193.0</v>
@@ -40379,7 +40365,7 @@
         <v>4176.0</v>
       </c>
       <c r="U35" s="92" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="W35" s="26">
         <v>4863.0</v>
@@ -40477,7 +40463,7 @@
       <c r="D38" s="7"/>
       <c r="E38" s="7"/>
       <c r="F38" s="4" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G38" s="155">
         <f t="shared" ref="G38:I38" si="8">G30-G35</f>
@@ -40679,7 +40665,7 @@
       <c r="Q45" s="7"/>
       <c r="R45" s="7"/>
       <c r="T45" s="145" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AD45" s="7"/>
       <c r="AE45" s="7"/>
@@ -40843,7 +40829,7 @@
         <v>11</v>
       </c>
       <c r="AG49" s="61" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="50">
@@ -41008,7 +40994,7 @@
         <v>13.03594852814783</v>
       </c>
       <c r="AG52" s="61" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="53">
@@ -41069,7 +41055,7 @@
         <v>6.291840048860032</v>
       </c>
       <c r="AG53" s="61" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="54">
@@ -41130,7 +41116,7 @@
         <v>2.7243520649411117</v>
       </c>
       <c r="AG54" s="61" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="55">
@@ -41191,7 +41177,7 @@
         <v>2.1429979739456915</v>
       </c>
       <c r="AG55" s="61" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="56">
@@ -41252,7 +41238,7 @@
         <v>3.98032040346951</v>
       </c>
       <c r="AG56" s="61" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="57">
@@ -41475,10 +41461,10 @@
       <c r="R62" s="7"/>
       <c r="S62" s="7"/>
       <c r="U62" s="26" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="V62" s="26" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="AC62" s="7"/>
       <c r="AD62" s="7"/>
@@ -41520,7 +41506,7 @@
         <v>2165.0</v>
       </c>
       <c r="W63" s="26" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="AC63" s="7"/>
       <c r="AD63" s="7"/>
@@ -42154,7 +42140,7 @@
       <c r="R79" s="7"/>
       <c r="S79" s="7"/>
       <c r="T79" s="94" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="U79" s="7"/>
       <c r="V79" s="7"/>
@@ -42195,7 +42181,7 @@
       <c r="R80" s="7"/>
       <c r="S80" s="7"/>
       <c r="T80" s="26" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="U80" s="18"/>
       <c r="V80" s="18"/>
@@ -74956,146 +74942,146 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="26" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="2">
       <c r="B2" s="7"/>
       <c r="C2" s="165" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E2" s="166"/>
       <c r="F2" s="94" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="H2" s="166"/>
     </row>
     <row r="3">
       <c r="B3" s="115" t="s">
+        <v>272</v>
+      </c>
+      <c r="C3" s="167" t="s">
+        <v>273</v>
+      </c>
+      <c r="D3" s="115" t="s">
         <v>274</v>
-      </c>
-      <c r="C3" s="167" t="s">
-        <v>275</v>
-      </c>
-      <c r="D3" s="115" t="s">
-        <v>276</v>
       </c>
       <c r="E3" s="168" t="s">
         <v>97</v>
       </c>
       <c r="F3" s="115" t="s">
+        <v>275</v>
+      </c>
+      <c r="G3" s="115" t="s">
+        <v>276</v>
+      </c>
+      <c r="H3" s="115" t="s">
         <v>277</v>
-      </c>
-      <c r="G3" s="115" t="s">
-        <v>278</v>
-      </c>
-      <c r="H3" s="115" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="169" t="s">
+        <v>278</v>
+      </c>
+      <c r="C4" s="170" t="s">
+        <v>279</v>
+      </c>
+      <c r="D4" s="116" t="s">
         <v>280</v>
       </c>
-      <c r="C4" s="170" t="s">
+      <c r="E4" s="171" t="s">
         <v>281</v>
       </c>
-      <c r="D4" s="116" t="s">
+      <c r="F4" s="172" t="s">
         <v>282</v>
       </c>
-      <c r="E4" s="171" t="s">
+      <c r="G4" s="172" t="s">
         <v>283</v>
-      </c>
-      <c r="F4" s="172" t="s">
-        <v>284</v>
-      </c>
-      <c r="G4" s="172" t="s">
-        <v>285</v>
       </c>
       <c r="H4" s="116"/>
     </row>
     <row r="5">
       <c r="B5" s="169" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C5" s="173" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D5" s="126"/>
       <c r="E5" s="171" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F5" s="174" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="G5" s="175" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="H5" s="116"/>
     </row>
     <row r="6">
       <c r="B6" s="169" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C6" s="170" t="s">
+        <v>279</v>
+      </c>
+      <c r="D6" s="116" t="s">
+        <v>289</v>
+      </c>
+      <c r="E6" s="171" t="s">
         <v>281</v>
       </c>
-      <c r="D6" s="116" t="s">
-        <v>291</v>
-      </c>
-      <c r="E6" s="171" t="s">
-        <v>283</v>
-      </c>
       <c r="F6" s="116" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="G6" s="116"/>
       <c r="H6" s="116"/>
     </row>
     <row r="7">
       <c r="B7" s="116" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C7" s="176" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D7" s="116"/>
       <c r="E7" s="177" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="F7" s="170" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="G7" s="116"/>
       <c r="H7" s="116" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="178" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C8" s="179" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D8" s="180"/>
       <c r="E8" s="178" t="s">
+        <v>297</v>
+      </c>
+      <c r="F8" s="181" t="s">
+        <v>298</v>
+      </c>
+      <c r="G8" s="182" t="s">
         <v>299</v>
-      </c>
-      <c r="F8" s="181" t="s">
-        <v>300</v>
-      </c>
-      <c r="G8" s="182" t="s">
-        <v>301</v>
       </c>
       <c r="H8" s="180"/>
     </row>
     <row r="9">
       <c r="B9" s="19" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C9" s="183" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D9" s="74"/>
       <c r="E9" s="74"/>
@@ -75105,27 +75091,27 @@
     </row>
     <row r="10">
       <c r="B10" s="19" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C10" s="146"/>
       <c r="D10" s="74"/>
       <c r="E10" s="74"/>
       <c r="F10" s="146"/>
       <c r="G10" s="172" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H10" s="74"/>
     </row>
     <row r="11">
       <c r="B11" s="19" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C11" s="146"/>
       <c r="D11" s="74"/>
       <c r="E11" s="74"/>
       <c r="F11" s="146"/>
       <c r="G11" s="184" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="H11" s="19"/>
     </row>
@@ -75148,7 +75134,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="34" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="L1" s="8"/>
     </row>
@@ -75157,16 +75143,16 @@
     </row>
     <row r="3">
       <c r="A3" s="26" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="L3" s="8"/>
     </row>
     <row r="4">
       <c r="B4" s="26" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="G4" s="26" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="L4" s="8"/>
     </row>
@@ -75272,62 +75258,62 @@
     </row>
     <row r="11">
       <c r="A11" s="185" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="34" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="26" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="185" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="34" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="26" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="F19" s="83"/>
     </row>
     <row r="20">
       <c r="B20" s="34" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C20" s="36"/>
       <c r="D20" s="36"/>
       <c r="E20" s="36"/>
       <c r="F20" s="36"/>
       <c r="G20" s="34" t="s">
+        <v>315</v>
+      </c>
+      <c r="H20" s="34" t="s">
+        <v>316</v>
+      </c>
+      <c r="I20" s="34" t="s">
         <v>317</v>
       </c>
-      <c r="H20" s="34" t="s">
+      <c r="J20" s="34" t="s">
         <v>318</v>
       </c>
-      <c r="I20" s="34" t="s">
+      <c r="K20" s="34" t="s">
         <v>319</v>
-      </c>
-      <c r="J20" s="34" t="s">
-        <v>320</v>
-      </c>
-      <c r="K20" s="34" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="34" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="G21" s="37">
         <v>2.575</v>
@@ -75335,27 +75321,27 @@
     </row>
     <row r="23">
       <c r="K23" s="34" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="26" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="H24" s="26" t="s">
         <v>171</v>
       </c>
       <c r="I24" s="26" t="s">
+        <v>323</v>
+      </c>
+      <c r="K24" s="26" t="s">
+        <v>324</v>
+      </c>
+      <c r="L24" s="26" t="s">
         <v>325</v>
       </c>
-      <c r="K24" s="26" t="s">
+      <c r="M24" s="26" t="s">
         <v>326</v>
-      </c>
-      <c r="L24" s="26" t="s">
-        <v>327</v>
-      </c>
-      <c r="M24" s="26" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="25">
@@ -75374,7 +75360,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="K25" s="26" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="26">
@@ -75385,7 +75371,7 @@
         <v>1.19</v>
       </c>
       <c r="K26" s="26" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="27">
@@ -75396,7 +75382,7 @@
         <v>2.19</v>
       </c>
       <c r="K27" s="26" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="28">
@@ -75407,7 +75393,7 @@
         <v>0.05</v>
       </c>
       <c r="K28" s="26" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="29">
@@ -75426,7 +75412,7 @@
         <v>6.42</v>
       </c>
       <c r="K30" s="51" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="31">
@@ -75571,7 +75557,7 @@
         <v>0.61</v>
       </c>
       <c r="K41" s="34" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="42">
@@ -75582,13 +75568,13 @@
         <v>0.69</v>
       </c>
       <c r="K42" s="26" t="s">
+        <v>324</v>
+      </c>
+      <c r="L42" s="26" t="s">
+        <v>325</v>
+      </c>
+      <c r="M42" s="26" t="s">
         <v>326</v>
-      </c>
-      <c r="L42" s="26" t="s">
-        <v>327</v>
-      </c>
-      <c r="M42" s="26" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="43">
@@ -75720,7 +75706,7 @@
         <v>0.0</v>
       </c>
       <c r="K51" s="26" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="52">
@@ -75748,17 +75734,17 @@
       </c>
       <c r="K54" s="74"/>
       <c r="L54" s="186" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="M54" s="187"/>
       <c r="N54" s="79" t="s">
         <v>5</v>
       </c>
       <c r="O54" s="79" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="P54" s="79" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="R54" s="15" t="s">
         <v>107</v>
@@ -75840,7 +75826,7 @@
         <v>5.86</v>
       </c>
       <c r="R57" s="26" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="S57" s="37">
         <f>SUM(P55:P74)</f>
@@ -75855,7 +75841,7 @@
         <v>0.0</v>
       </c>
       <c r="K58" s="19" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="L58" s="188">
         <v>0.57</v>
@@ -75869,7 +75855,7 @@
         <v>0.855</v>
       </c>
       <c r="P58" s="19" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="59">
@@ -75916,7 +75902,7 @@
         <v>0.96</v>
       </c>
       <c r="P60" s="19" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="61">
@@ -75927,7 +75913,7 @@
         <v>0.02</v>
       </c>
       <c r="K61" s="19" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="L61" s="19">
         <v>0.42</v>
@@ -75999,7 +75985,7 @@
         <v>0.0</v>
       </c>
       <c r="K64" s="19" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="L64" s="19">
         <v>0.42</v>
@@ -76143,7 +76129,7 @@
         <v>0.0</v>
       </c>
       <c r="K70" s="19" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="L70" s="19">
         <v>0.66</v>

--- a/data/df_best_models.xlsx
+++ b/data/df_best_models.xlsx
@@ -38,9 +38,9 @@
 </t>
       </text>
     </comment>
-    <comment authorId="0" ref="H6">
+    <comment authorId="0" ref="H5">
       <text>
-        <t xml:space="preserve">lo fuerzo a 65 puesto que sino es 200 dado que acertó todos los partidos</t>
+        <t xml:space="preserve">200</t>
       </text>
     </comment>
     <comment authorId="0" ref="G7">
@@ -2667,7 +2667,7 @@
         <v>45719.0</v>
       </c>
       <c r="D4" s="13">
-        <v>6297.0</v>
+        <v>5414.0</v>
       </c>
       <c r="E4" s="13" t="s">
         <v>13</v>
@@ -2710,24 +2710,24 @@
         <v>45719.0</v>
       </c>
       <c r="D5" s="13">
-        <v>3024.0</v>
+        <v>5081.0</v>
       </c>
       <c r="E5" s="13" t="s">
         <v>13</v>
       </c>
       <c r="F5" s="14"/>
       <c r="G5" s="15">
-        <v>65.0</v>
+        <v>15.0</v>
       </c>
       <c r="H5" s="15">
-        <v>50.0</v>
+        <v>80.0</v>
       </c>
       <c r="I5" s="15">
-        <v>110.0</v>
+        <v>80.0</v>
       </c>
       <c r="J5" s="17">
         <f t="shared" si="1"/>
-        <v>75</v>
+        <v>58.33333333</v>
       </c>
       <c r="K5" s="24">
         <f>F5*'Data preparation'!$C$2</f>
@@ -2750,7 +2750,7 @@
         <v>45720.0</v>
       </c>
       <c r="D6" s="13">
-        <v>3993.0</v>
+        <v>4964.0</v>
       </c>
       <c r="E6" s="13" t="s">
         <v>13</v>
@@ -2763,11 +2763,11 @@
         <v>65.0</v>
       </c>
       <c r="I6" s="15">
-        <v>65.0</v>
+        <v>110.0</v>
       </c>
       <c r="J6" s="17">
         <f t="shared" si="1"/>
-        <v>46.66666667</v>
+        <v>61.66666667</v>
       </c>
       <c r="K6" s="24">
         <f>F6*'Data preparation'!$C$2</f>
@@ -2790,24 +2790,24 @@
         <v>45720.0</v>
       </c>
       <c r="D7" s="13">
-        <v>2273.0</v>
+        <v>2114.0</v>
       </c>
       <c r="E7" s="13" t="s">
         <v>13</v>
       </c>
       <c r="F7" s="14"/>
       <c r="G7" s="15">
-        <v>80.0</v>
+        <v>40.0</v>
       </c>
       <c r="H7" s="15">
-        <v>110.0</v>
+        <v>65.0</v>
       </c>
       <c r="I7" s="15">
-        <v>10.0</v>
+        <v>25.0</v>
       </c>
       <c r="J7" s="17">
         <f t="shared" si="1"/>
-        <v>66.66666667</v>
+        <v>43.33333333</v>
       </c>
       <c r="K7" s="24">
         <f>F7*'Data preparation'!$C$2</f>

--- a/data/df_best_models.xlsx
+++ b/data/df_best_models.xlsx
@@ -2667,7 +2667,7 @@
         <v>45719.0</v>
       </c>
       <c r="D4" s="13">
-        <v>5414.0</v>
+        <v>4754.0</v>
       </c>
       <c r="E4" s="13" t="s">
         <v>13</v>
@@ -2677,14 +2677,14 @@
         <v>10.0</v>
       </c>
       <c r="H4" s="15">
-        <v>65.0</v>
+        <v>140.0</v>
       </c>
       <c r="I4" s="15">
-        <v>50.0</v>
+        <v>95.0</v>
       </c>
       <c r="J4" s="17">
         <f t="shared" ref="J4:J8" si="1">IFERROR(AVERAGE(G4:I4),"")</f>
-        <v>41.66666667</v>
+        <v>81.66666667</v>
       </c>
       <c r="K4" s="24">
         <f>F4*'Data preparation'!$C$2</f>
@@ -2710,24 +2710,24 @@
         <v>45719.0</v>
       </c>
       <c r="D5" s="13">
-        <v>5081.0</v>
+        <v>3960.0</v>
       </c>
       <c r="E5" s="13" t="s">
         <v>13</v>
       </c>
       <c r="F5" s="14"/>
       <c r="G5" s="15">
-        <v>15.0</v>
+        <v>110.0</v>
       </c>
       <c r="H5" s="15">
-        <v>80.0</v>
+        <v>200.0</v>
       </c>
       <c r="I5" s="15">
-        <v>80.0</v>
+        <v>140.0</v>
       </c>
       <c r="J5" s="17">
         <f t="shared" si="1"/>
-        <v>58.33333333</v>
+        <v>150</v>
       </c>
       <c r="K5" s="24">
         <f>F5*'Data preparation'!$C$2</f>
@@ -2750,7 +2750,7 @@
         <v>45720.0</v>
       </c>
       <c r="D6" s="13">
-        <v>4964.0</v>
+        <v>4944.0</v>
       </c>
       <c r="E6" s="13" t="s">
         <v>13</v>
@@ -2760,14 +2760,14 @@
         <v>10.0</v>
       </c>
       <c r="H6" s="15">
-        <v>65.0</v>
+        <v>110.0</v>
       </c>
       <c r="I6" s="15">
-        <v>110.0</v>
+        <v>140.0</v>
       </c>
       <c r="J6" s="17">
         <f t="shared" si="1"/>
-        <v>61.66666667</v>
+        <v>86.66666667</v>
       </c>
       <c r="K6" s="24">
         <f>F6*'Data preparation'!$C$2</f>
@@ -2790,24 +2790,24 @@
         <v>45720.0</v>
       </c>
       <c r="D7" s="13">
-        <v>2114.0</v>
+        <v>2406.0</v>
       </c>
       <c r="E7" s="13" t="s">
         <v>13</v>
       </c>
       <c r="F7" s="14"/>
       <c r="G7" s="15">
-        <v>40.0</v>
+        <v>80.0</v>
       </c>
       <c r="H7" s="15">
-        <v>65.0</v>
+        <v>50.0</v>
       </c>
       <c r="I7" s="15">
-        <v>25.0</v>
+        <v>10.0</v>
       </c>
       <c r="J7" s="17">
         <f t="shared" si="1"/>
-        <v>43.33333333</v>
+        <v>46.66666667</v>
       </c>
       <c r="K7" s="24">
         <f>F7*'Data preparation'!$C$2</f>
@@ -2830,7 +2830,7 @@
         <v>45720.0</v>
       </c>
       <c r="D8" s="13">
-        <v>3490.0</v>
+        <v>2232.0</v>
       </c>
       <c r="E8" s="13" t="s">
         <v>13</v>
@@ -2840,14 +2840,14 @@
         <v>80.0</v>
       </c>
       <c r="H8" s="15">
-        <v>95.0</v>
+        <v>170.0</v>
       </c>
       <c r="I8" s="15">
-        <v>35.0</v>
+        <v>50.0</v>
       </c>
       <c r="J8" s="17">
         <f t="shared" si="1"/>
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="K8" s="24">
         <f>F8*'Data preparation'!$C$2</f>

--- a/data/df_best_models.xlsx
+++ b/data/df_best_models.xlsx
@@ -911,28 +911,28 @@
     <t>Stake promedio</t>
   </si>
   <si>
-    <t>1.84</t>
+    <t>0.06</t>
   </si>
   <si>
-    <t>12.60</t>
+    <t>0.38</t>
   </si>
   <si>
-    <t>9.34</t>
+    <t>0.26</t>
   </si>
   <si>
-    <t>7.90</t>
+    <t>5.17</t>
   </si>
   <si>
-    <t>9.16</t>
+    <t>4.25</t>
   </si>
   <si>
-    <t>5.26</t>
+    <t>4.13</t>
   </si>
   <si>
-    <t>9.20</t>
+    <t>4.80</t>
   </si>
   <si>
-    <t>8.80</t>
+    <t>5.57</t>
   </si>
   <si>
     <t>Country</t>
@@ -941,133 +941,133 @@
     <t>Correl ROI y Expected ROI</t>
   </si>
   <si>
-    <t>1.92</t>
+    <t>1.71</t>
   </si>
   <si>
-    <t>0.50</t>
+    <t>2.23</t>
   </si>
   <si>
     <t>mean</t>
   </si>
   <si>
-    <t>2.20</t>
+    <t>4.14</t>
   </si>
   <si>
     <t>median</t>
   </si>
   <si>
-    <t>4.03</t>
+    <t>1.03</t>
   </si>
   <si>
     <t>p25</t>
   </si>
   <si>
-    <t>3.70</t>
+    <t>6.23</t>
   </si>
   <si>
     <t>p75</t>
   </si>
   <si>
-    <t>3.87</t>
+    <t>1.05</t>
   </si>
   <si>
-    <t>9.58</t>
+    <t>0.99</t>
   </si>
   <si>
-    <t>5.15</t>
+    <t>0.07</t>
   </si>
   <si>
-    <t>1.22</t>
+    <t>0.55</t>
   </si>
   <si>
-    <t>6.58</t>
+    <t>5.65</t>
   </si>
   <si>
-    <t>7.32</t>
-  </si>
-  <si>
-    <t>6.49</t>
+    <t>5.60</t>
   </si>
   <si>
     <t>Gracias a las nuevas métricas de G/P sin bank en test, me di cuenta de que:</t>
   </si>
   <si>
-    <t>6.44</t>
+    <t>5.74</t>
   </si>
   <si>
     <t>La rentabilidad en ITA está en el visitante y no en el empate como creía.</t>
   </si>
   <si>
-    <t>6.43</t>
+    <t>5.66</t>
   </si>
   <si>
     <t>La rentabilidad en ENG y GER está en el empate tal como creía.</t>
   </si>
   <si>
-    <t>7.37</t>
+    <t>5.16</t>
   </si>
   <si>
     <t>En SPA esta repartido aunque Empate saca una ventaja.</t>
   </si>
   <si>
-    <t>9.18</t>
+    <t>9.57</t>
   </si>
   <si>
     <t>En FRA, depende el modelo. A veces local, a veces, empate.</t>
   </si>
   <si>
-    <t>2.59</t>
+    <t>3.41</t>
   </si>
   <si>
     <t>Si en FRA empate no rinde, no tiene sentido exigirle una buena distrib en empate… → Tiene sentido pero al parecer si importa el empate puesto que el modelo que gana se basa en empate.</t>
   </si>
   <si>
-    <t>2.57</t>
+    <t>5.99</t>
+  </si>
+  <si>
+    <t>4.88</t>
+  </si>
+  <si>
+    <t>1.27</t>
+  </si>
+  <si>
+    <t>2.92</t>
+  </si>
+  <si>
+    <t>3.13</t>
+  </si>
+  <si>
+    <t>2.22</t>
+  </si>
+  <si>
+    <t>0.90</t>
+  </si>
+  <si>
+    <t>0.54</t>
+  </si>
+  <si>
+    <t>2.83</t>
+  </si>
+  <si>
+    <t>0.39</t>
+  </si>
+  <si>
+    <t>3.85</t>
+  </si>
+  <si>
+    <t>7.31</t>
+  </si>
+  <si>
+    <t>7.60</t>
+  </si>
+  <si>
+    <t>6.51</t>
+  </si>
+  <si>
+    <t>2.50</t>
   </si>
   <si>
     <t>2.72</t>
   </si>
   <si>
-    <t>0.39</t>
-  </si>
-  <si>
-    <t>2.56</t>
-  </si>
-  <si>
-    <t>9.40</t>
-  </si>
-  <si>
-    <t>6.29</t>
-  </si>
-  <si>
-    <t>3.49</t>
-  </si>
-  <si>
-    <t>2.38</t>
-  </si>
-  <si>
-    <t>3.76</t>
-  </si>
-  <si>
-    <t>3.47</t>
-  </si>
-  <si>
-    <t>7.27</t>
-  </si>
-  <si>
-    <t>4.60</t>
-  </si>
-  <si>
-    <t>3.93</t>
-  </si>
-  <si>
-    <t>5.86</t>
-  </si>
-  <si>
-    <t>1.60</t>
-  </si>
-  <si>
-    <t>0.22</t>
+    <t>2.62</t>
   </si>
   <si>
     <t>RENTABILIDAD</t>
@@ -2710,24 +2710,24 @@
         <v>45719.0</v>
       </c>
       <c r="D5" s="13">
-        <v>3960.0</v>
+        <v>1940.0</v>
       </c>
       <c r="E5" s="13" t="s">
         <v>13</v>
       </c>
       <c r="F5" s="14"/>
       <c r="G5" s="15">
-        <v>110.0</v>
+        <v>10.0</v>
       </c>
       <c r="H5" s="15">
         <v>200.0</v>
       </c>
       <c r="I5" s="15">
-        <v>140.0</v>
+        <v>110.0</v>
       </c>
       <c r="J5" s="17">
         <f t="shared" si="1"/>
-        <v>150</v>
+        <v>106.6666667</v>
       </c>
       <c r="K5" s="24">
         <f>F5*'Data preparation'!$C$2</f>
@@ -14842,7 +14842,7 @@
       <c r="C37" s="36"/>
       <c r="D37" s="111">
         <f>AVERAGE(D39:D1775)</f>
-        <v>5.067380952</v>
+        <v>3.436428571</v>
       </c>
       <c r="G37" s="34" t="s">
         <v>36</v>
@@ -14911,7 +14911,7 @@
       </c>
       <c r="D39" s="102">
         <f t="shared" ref="D39:D221" si="17">IF(COUNTA(C39)=1,C39/1,"")</f>
-        <v>1.84</v>
+        <v>0.06</v>
       </c>
       <c r="G39" s="34" t="s">
         <v>28</v>
@@ -14949,7 +14949,7 @@
       </c>
       <c r="D40" s="102">
         <f t="shared" si="17"/>
-        <v>12.6</v>
+        <v>0.38</v>
       </c>
       <c r="G40" s="34" t="s">
         <v>24</v>
@@ -14987,7 +14987,7 @@
       </c>
       <c r="D41" s="102">
         <f t="shared" si="17"/>
-        <v>9.34</v>
+        <v>0.26</v>
       </c>
       <c r="P41" s="100">
         <v>0.0</v>
@@ -15019,7 +15019,7 @@
       </c>
       <c r="D42" s="102">
         <f t="shared" si="17"/>
-        <v>7.9</v>
+        <v>5.17</v>
       </c>
       <c r="P42" s="100">
         <v>2.0</v>
@@ -15051,7 +15051,7 @@
       </c>
       <c r="D43" s="102">
         <f t="shared" si="17"/>
-        <v>9.16</v>
+        <v>4.25</v>
       </c>
       <c r="P43" s="100">
         <v>1.0</v>
@@ -15083,7 +15083,7 @@
       </c>
       <c r="D44" s="102">
         <f t="shared" si="17"/>
-        <v>5.26</v>
+        <v>4.13</v>
       </c>
       <c r="P44" s="100">
         <v>2.0</v>
@@ -15113,7 +15113,7 @@
       </c>
       <c r="D45" s="102">
         <f t="shared" si="17"/>
-        <v>9.2</v>
+        <v>4.8</v>
       </c>
       <c r="P45" s="100">
         <v>1.0</v>
@@ -15131,7 +15131,7 @@
       </c>
       <c r="D46" s="102">
         <f t="shared" si="17"/>
-        <v>8.8</v>
+        <v>5.57</v>
       </c>
       <c r="G46" s="115" t="s">
         <v>183</v>
@@ -15155,7 +15155,7 @@
       </c>
       <c r="D47" s="102">
         <f t="shared" si="17"/>
-        <v>1.92</v>
+        <v>1.71</v>
       </c>
       <c r="G47" s="116" t="s">
         <v>37</v>
@@ -15185,7 +15185,7 @@
       </c>
       <c r="D48" s="102">
         <f t="shared" si="17"/>
-        <v>0.5</v>
+        <v>2.23</v>
       </c>
       <c r="G48" s="116" t="s">
         <v>36</v>
@@ -15222,7 +15222,7 @@
       </c>
       <c r="D49" s="102">
         <f t="shared" si="17"/>
-        <v>2.2</v>
+        <v>4.14</v>
       </c>
       <c r="G49" s="116" t="s">
         <v>27</v>
@@ -15259,7 +15259,7 @@
       </c>
       <c r="D50" s="102">
         <f t="shared" si="17"/>
-        <v>4.03</v>
+        <v>1.03</v>
       </c>
       <c r="G50" s="116" t="s">
         <v>28</v>
@@ -15296,7 +15296,7 @@
       </c>
       <c r="D51" s="102">
         <f t="shared" si="17"/>
-        <v>3.7</v>
+        <v>6.23</v>
       </c>
       <c r="G51" s="116" t="s">
         <v>24</v>
@@ -15329,11 +15329,11 @@
     </row>
     <row r="52">
       <c r="C52" s="114" t="s">
-        <v>194</v>
+        <v>137</v>
       </c>
       <c r="D52" s="102">
         <f t="shared" si="17"/>
-        <v>3.87</v>
+        <v>2.74</v>
       </c>
       <c r="P52" s="100">
         <v>0.0</v>
@@ -15353,11 +15353,11 @@
     </row>
     <row r="53">
       <c r="C53" s="114" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D53" s="102">
         <f t="shared" si="17"/>
-        <v>9.58</v>
+        <v>1.05</v>
       </c>
       <c r="P53" s="100">
         <v>0.0</v>
@@ -15377,11 +15377,11 @@
     </row>
     <row r="54">
       <c r="C54" s="114" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D54" s="102">
         <f t="shared" si="17"/>
-        <v>5.15</v>
+        <v>0.99</v>
       </c>
       <c r="P54" s="100">
         <v>2.0</v>
@@ -15401,11 +15401,11 @@
     </row>
     <row r="55">
       <c r="C55" s="114" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D55" s="102">
         <f t="shared" si="17"/>
-        <v>1.22</v>
+        <v>0.07</v>
       </c>
       <c r="P55" s="100">
         <v>0.0</v>
@@ -15425,11 +15425,11 @@
     </row>
     <row r="56">
       <c r="C56" s="114" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D56" s="102">
         <f t="shared" si="17"/>
-        <v>6.58</v>
+        <v>0.55</v>
       </c>
       <c r="P56" s="100">
         <v>0.0</v>
@@ -15449,11 +15449,11 @@
     </row>
     <row r="57">
       <c r="C57" s="114" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D57" s="102">
         <f t="shared" si="17"/>
-        <v>7.32</v>
+        <v>5.65</v>
       </c>
       <c r="P57" s="100">
         <v>2.0</v>
@@ -15473,14 +15473,14 @@
     </row>
     <row r="58">
       <c r="C58" s="114" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D58" s="102">
         <f t="shared" si="17"/>
-        <v>6.49</v>
+        <v>5.6</v>
       </c>
       <c r="G58" s="118" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H58" s="119"/>
       <c r="P58" s="100">
@@ -15501,15 +15501,15 @@
     </row>
     <row r="59">
       <c r="C59" s="114" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D59" s="102">
         <f t="shared" si="17"/>
-        <v>6.44</v>
+        <v>5.74</v>
       </c>
       <c r="G59" s="119"/>
       <c r="H59" s="120" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="P59" s="100">
         <v>0.0</v>
@@ -15529,15 +15529,15 @@
     </row>
     <row r="60">
       <c r="C60" s="114" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D60" s="102">
         <f t="shared" si="17"/>
-        <v>6.43</v>
+        <v>5.66</v>
       </c>
       <c r="G60" s="119"/>
       <c r="H60" s="120" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="P60" s="100">
         <v>2.0</v>
@@ -15557,15 +15557,15 @@
     </row>
     <row r="61">
       <c r="C61" s="114" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D61" s="102">
         <f t="shared" si="17"/>
-        <v>7.37</v>
+        <v>5.16</v>
       </c>
       <c r="G61" s="119"/>
       <c r="H61" s="120" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="P61" s="100">
         <v>2.0</v>
@@ -15585,15 +15585,15 @@
     </row>
     <row r="62">
       <c r="C62" s="114" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D62" s="102">
         <f t="shared" si="17"/>
-        <v>9.18</v>
+        <v>9.57</v>
       </c>
       <c r="G62" s="119"/>
       <c r="H62" s="120" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="P62" s="100">
         <v>1.0</v>
@@ -15613,15 +15613,15 @@
     </row>
     <row r="63">
       <c r="C63" s="114" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D63" s="102">
         <f t="shared" si="17"/>
-        <v>2.59</v>
+        <v>3.41</v>
       </c>
       <c r="G63" s="119"/>
       <c r="H63" s="120" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P63" s="100">
         <v>0.0</v>
@@ -15635,11 +15635,11 @@
     </row>
     <row r="64">
       <c r="C64" s="114" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D64" s="102">
         <f t="shared" si="17"/>
-        <v>2.57</v>
+        <v>5.99</v>
       </c>
       <c r="P64" s="100">
         <v>1.0</v>
@@ -15653,11 +15653,11 @@
     </row>
     <row r="65">
       <c r="C65" s="114" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D65" s="102">
         <f t="shared" si="17"/>
-        <v>2.72</v>
+        <v>4.88</v>
       </c>
       <c r="P65" s="100">
         <v>2.0</v>
@@ -15671,11 +15671,11 @@
     </row>
     <row r="66">
       <c r="C66" s="114" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D66" s="102">
         <f t="shared" si="17"/>
-        <v>0.39</v>
+        <v>1.27</v>
       </c>
       <c r="P66" s="100">
         <v>0.0</v>
@@ -15689,11 +15689,11 @@
     </row>
     <row r="67">
       <c r="C67" s="114" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D67" s="102">
         <f t="shared" si="17"/>
-        <v>2.56</v>
+        <v>2.92</v>
       </c>
       <c r="P67" s="100">
         <v>0.0</v>
@@ -15707,11 +15707,11 @@
     </row>
     <row r="68">
       <c r="C68" s="114" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D68" s="102">
         <f t="shared" si="17"/>
-        <v>9.4</v>
+        <v>3.13</v>
       </c>
       <c r="P68" s="100">
         <v>1.0</v>
@@ -15725,11 +15725,11 @@
     </row>
     <row r="69">
       <c r="C69" s="114" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D69" s="102">
         <f t="shared" si="17"/>
-        <v>6.29</v>
+        <v>2.22</v>
       </c>
       <c r="P69" s="100">
         <v>2.0</v>
@@ -15743,11 +15743,11 @@
     </row>
     <row r="70">
       <c r="C70" s="114" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D70" s="102">
         <f t="shared" si="17"/>
-        <v>3.49</v>
+        <v>0.9</v>
       </c>
       <c r="P70" s="100">
         <v>1.0</v>
@@ -15761,11 +15761,11 @@
     </row>
     <row r="71">
       <c r="C71" s="114" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D71" s="102">
         <f t="shared" si="17"/>
-        <v>2.38</v>
+        <v>0.54</v>
       </c>
       <c r="F71" s="121"/>
       <c r="P71" s="100">
@@ -15780,11 +15780,11 @@
     </row>
     <row r="72">
       <c r="C72" s="114" t="s">
-        <v>140</v>
+        <v>219</v>
       </c>
       <c r="D72" s="102">
         <f t="shared" si="17"/>
-        <v>3.65</v>
+        <v>2.83</v>
       </c>
       <c r="P72" s="100">
         <v>0.0</v>
@@ -15802,7 +15802,7 @@
       </c>
       <c r="D73" s="102">
         <f t="shared" si="17"/>
-        <v>3.76</v>
+        <v>0.39</v>
       </c>
       <c r="P73" s="100">
         <v>1.0</v>
@@ -15820,7 +15820,7 @@
       </c>
       <c r="D74" s="102">
         <f t="shared" si="17"/>
-        <v>3.47</v>
+        <v>3.85</v>
       </c>
       <c r="P74" s="100">
         <v>0.0</v>
@@ -15838,7 +15838,7 @@
       </c>
       <c r="D75" s="102">
         <f t="shared" si="17"/>
-        <v>7.27</v>
+        <v>7.31</v>
       </c>
       <c r="P75" s="100">
         <v>1.0</v>
@@ -15856,7 +15856,7 @@
       </c>
       <c r="D76" s="102">
         <f t="shared" si="17"/>
-        <v>4.6</v>
+        <v>7.6</v>
       </c>
       <c r="P76" s="100">
         <v>0.0</v>
@@ -15874,7 +15874,7 @@
       </c>
       <c r="D77" s="102">
         <f t="shared" si="17"/>
-        <v>3.93</v>
+        <v>6.51</v>
       </c>
       <c r="P77" s="100">
         <v>0.0</v>
@@ -15892,7 +15892,7 @@
       </c>
       <c r="D78" s="102">
         <f t="shared" si="17"/>
-        <v>5.86</v>
+        <v>2.5</v>
       </c>
       <c r="P78" s="100">
         <v>1.0</v>
@@ -15910,7 +15910,7 @@
       </c>
       <c r="D79" s="102">
         <f t="shared" si="17"/>
-        <v>1.6</v>
+        <v>2.72</v>
       </c>
       <c r="P79" s="100">
         <v>2.0</v>
@@ -15928,7 +15928,7 @@
       </c>
       <c r="D80" s="102">
         <f t="shared" si="17"/>
-        <v>0.22</v>
+        <v>2.62</v>
       </c>
       <c r="P80" s="100">
         <v>1.0</v>

--- a/data/df_best_models.xlsx
+++ b/data/df_best_models.xlsx
@@ -2639,7 +2639,7 @@
         <v>45739.0</v>
       </c>
       <c r="D4" s="13">
-        <v>1071.0</v>
+        <v>1145.0</v>
       </c>
       <c r="E4" s="13" t="s">
         <v>9</v>
@@ -2668,7 +2668,7 @@
         <v>45739.0</v>
       </c>
       <c r="D5" s="13">
-        <v>918.0</v>
+        <v>1083.0</v>
       </c>
       <c r="E5" s="13" t="s">
         <v>9</v>
@@ -2697,7 +2697,7 @@
         <v>45739.0</v>
       </c>
       <c r="D6" s="13">
-        <v>385.0</v>
+        <v>457.0</v>
       </c>
       <c r="E6" s="13" t="s">
         <v>9</v>
@@ -2726,7 +2726,7 @@
         <v>45739.0</v>
       </c>
       <c r="D7" s="13">
-        <v>955.0</v>
+        <v>907.0</v>
       </c>
       <c r="E7" s="13" t="s">
         <v>9</v>
@@ -2754,7 +2754,7 @@
         <v>45740.0</v>
       </c>
       <c r="D8" s="13">
-        <v>1135.0</v>
+        <v>649.0</v>
       </c>
       <c r="E8" s="13" t="s">
         <v>9</v>

--- a/data/df_best_models.xlsx
+++ b/data/df_best_models.xlsx
@@ -360,7 +360,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="433">
   <si>
     <t>id_country</t>
   </si>
@@ -585,10 +585,13 @@
     <t>metricas de test aceptables</t>
   </si>
   <si>
-    <t>gran roi en test y mayor roi en assess</t>
+    <t>gran roi en test y mayor roi en assess PERO mal error y las probas de prod no me gustan</t>
   </si>
   <si>
     <t>alto roi en assess + roi aceptable en test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gran roi en test y no tan buen assess </t>
   </si>
   <si>
     <t>roi bajo</t>
@@ -1162,28 +1165,28 @@
     <t>Stake promedio</t>
   </si>
   <si>
-    <t>1.52</t>
+    <t>2.17</t>
   </si>
   <si>
-    <t>0.33</t>
+    <t>1.66</t>
   </si>
   <si>
-    <t>1.43</t>
+    <t>1.96</t>
   </si>
   <si>
-    <t>0.28</t>
+    <t>1.28</t>
   </si>
   <si>
-    <t>0.92</t>
+    <t>2.78</t>
   </si>
   <si>
-    <t>1.65</t>
+    <t>2.26</t>
   </si>
   <si>
-    <t>2.05</t>
+    <t>2.45</t>
   </si>
   <si>
-    <t>1.93</t>
+    <t>1.78</t>
   </si>
   <si>
     <t>Country</t>
@@ -1192,253 +1195,253 @@
     <t>Correl ROI y Expected ROI</t>
   </si>
   <si>
-    <t>1.60</t>
+    <t>3.74</t>
   </si>
   <si>
     <t>mean</t>
   </si>
   <si>
-    <t>0.77</t>
+    <t>4.00</t>
   </si>
   <si>
     <t>median</t>
   </si>
   <si>
-    <t>6.54</t>
+    <t>3.73</t>
   </si>
   <si>
     <t>p25</t>
   </si>
   <si>
-    <t>5.57</t>
+    <t>4.30</t>
   </si>
   <si>
     <t>p75</t>
   </si>
   <si>
-    <t>4.51</t>
+    <t>5.93</t>
   </si>
   <si>
-    <t>0.84</t>
+    <t>3.66</t>
   </si>
   <si>
-    <t>0.82</t>
+    <t>4.11</t>
   </si>
   <si>
-    <t>5.71</t>
+    <t>5.40</t>
   </si>
   <si>
-    <t>6.89</t>
+    <t>5.97</t>
+  </si>
+  <si>
+    <t>4.34</t>
+  </si>
+  <si>
+    <t>1.81</t>
+  </si>
+  <si>
+    <t>Gracias a las nuevas métricas de G/P sin bank en test, me di cuenta de que:</t>
+  </si>
+  <si>
+    <t>2.99</t>
+  </si>
+  <si>
+    <t>La rentabilidad en ITA está en el visitante y no en el empate como creía.</t>
+  </si>
+  <si>
+    <t>4.84</t>
+  </si>
+  <si>
+    <t>La rentabilidad en ENG y GER está en el empate tal como creía.</t>
+  </si>
+  <si>
+    <t>1.40</t>
+  </si>
+  <si>
+    <t>En SPA esta repartido aunque Empate saca una ventaja.</t>
+  </si>
+  <si>
+    <t>3.34</t>
+  </si>
+  <si>
+    <t>En FRA, depende el modelo. A veces local, a veces, empate.</t>
+  </si>
+  <si>
+    <t>2.79</t>
+  </si>
+  <si>
+    <t>Si en FRA empate no rinde, no tiene sentido exigirle una buena distrib en empate… → Tiene sentido pero al parecer si importa el empate puesto que el modelo que gana se basa en empate.</t>
+  </si>
+  <si>
+    <t>5.39</t>
+  </si>
+  <si>
+    <t>7.99</t>
+  </si>
+  <si>
+    <t>7.76</t>
+  </si>
+  <si>
+    <t>5.24</t>
+  </si>
+  <si>
+    <t>7.66</t>
+  </si>
+  <si>
+    <t>5.19</t>
+  </si>
+  <si>
+    <t>3.76</t>
+  </si>
+  <si>
+    <t>4.44</t>
+  </si>
+  <si>
+    <t>4.86</t>
+  </si>
+  <si>
+    <t>3.33</t>
+  </si>
+  <si>
+    <t>4.29</t>
+  </si>
+  <si>
+    <t>4.57</t>
+  </si>
+  <si>
+    <t>4.61</t>
+  </si>
+  <si>
+    <t>3.16</t>
+  </si>
+  <si>
+    <t>1.90</t>
+  </si>
+  <si>
+    <t>2.73</t>
+  </si>
+  <si>
+    <t>3.44</t>
+  </si>
+  <si>
+    <t>1.24</t>
+  </si>
+  <si>
+    <t>2.33</t>
+  </si>
+  <si>
+    <t>2.32</t>
+  </si>
+  <si>
+    <t>2.57</t>
+  </si>
+  <si>
+    <t>2.46</t>
+  </si>
+  <si>
+    <t>7.39</t>
+  </si>
+  <si>
+    <t>6.49</t>
+  </si>
+  <si>
+    <t>10.63</t>
+  </si>
+  <si>
+    <t>7.30</t>
+  </si>
+  <si>
+    <t>6.60</t>
+  </si>
+  <si>
+    <t>1.74</t>
+  </si>
+  <si>
+    <t>1.94</t>
+  </si>
+  <si>
+    <t>1.65</t>
+  </si>
+  <si>
+    <t>3.32</t>
+  </si>
+  <si>
+    <t>1.62</t>
+  </si>
+  <si>
+    <t>1.91</t>
+  </si>
+  <si>
+    <t>1.76</t>
+  </si>
+  <si>
+    <t>1.89</t>
+  </si>
+  <si>
+    <t>1.69</t>
+  </si>
+  <si>
+    <t>6.59</t>
+  </si>
+  <si>
+    <t>3.23</t>
+  </si>
+  <si>
+    <t>2.66</t>
+  </si>
+  <si>
+    <t>0.33</t>
+  </si>
+  <si>
+    <t>1.99</t>
+  </si>
+  <si>
+    <t>2.01</t>
+  </si>
+  <si>
+    <t>3.56</t>
+  </si>
+  <si>
+    <t>1.97</t>
+  </si>
+  <si>
+    <t>2.93</t>
   </si>
   <si>
     <t>3.95</t>
   </si>
   <si>
-    <t>1.63</t>
+    <t>3.27</t>
   </si>
   <si>
-    <t>Gracias a las nuevas métricas de G/P sin bank en test, me di cuenta de que:</t>
+    <t>0.36</t>
   </si>
   <si>
-    <t>2.69</t>
+    <t>0.37</t>
   </si>
   <si>
-    <t>La rentabilidad en ITA está en el visitante y no en el empate como creía.</t>
+    <t>2.07</t>
   </si>
   <si>
-    <t>4.35</t>
+    <t>2.37</t>
   </si>
   <si>
-    <t>La rentabilidad en ENG y GER está en el empate tal como creía.</t>
+    <t>3.17</t>
   </si>
   <si>
-    <t>1.26</t>
+    <t>3.47</t>
   </si>
   <si>
-    <t>En SPA esta repartido aunque Empate saca una ventaja.</t>
+    <t>5.77</t>
   </si>
   <si>
-    <t>5.01</t>
+    <t>5.87</t>
   </si>
   <si>
-    <t>En FRA, depende el modelo. A veces local, a veces, empate.</t>
-  </si>
-  <si>
-    <t>4.18</t>
-  </si>
-  <si>
-    <t>Si en FRA empate no rinde, no tiene sentido exigirle una buena distrib en empate… → Tiene sentido pero al parecer si importa el empate puesto que el modelo que gana se basa en empate.</t>
-  </si>
-  <si>
-    <t>8.08</t>
-  </si>
-  <si>
-    <t>11.99</t>
-  </si>
-  <si>
-    <t>11.64</t>
-  </si>
-  <si>
-    <t>7.86</t>
-  </si>
-  <si>
-    <t>11.50</t>
-  </si>
-  <si>
-    <t>7.78</t>
-  </si>
-  <si>
-    <t>5.65</t>
-  </si>
-  <si>
-    <t>6.67</t>
-  </si>
-  <si>
-    <t>7.30</t>
-  </si>
-  <si>
-    <t>5.00</t>
-  </si>
-  <si>
-    <t>6.44</t>
-  </si>
-  <si>
-    <t>4.11</t>
-  </si>
-  <si>
-    <t>4.15</t>
-  </si>
-  <si>
-    <t>2.52</t>
-  </si>
-  <si>
-    <t>2.84</t>
-  </si>
-  <si>
-    <t>1.71</t>
-  </si>
-  <si>
-    <t>2.46</t>
-  </si>
-  <si>
-    <t>3.90</t>
-  </si>
-  <si>
-    <t>3.10</t>
-  </si>
-  <si>
-    <t>1.11</t>
-  </si>
-  <si>
-    <t>2.10</t>
-  </si>
-  <si>
-    <t>3.48</t>
-  </si>
-  <si>
-    <t>3.86</t>
-  </si>
-  <si>
-    <t>6.65</t>
-  </si>
-  <si>
-    <t>5.84</t>
-  </si>
-  <si>
-    <t>9.57</t>
-  </si>
-  <si>
-    <t>6.57</t>
-  </si>
-  <si>
-    <t>0.52</t>
-  </si>
-  <si>
-    <t>2.91</t>
-  </si>
-  <si>
-    <t>2.48</t>
-  </si>
-  <si>
-    <t>4.98</t>
-  </si>
-  <si>
-    <t>0.49</t>
-  </si>
-  <si>
-    <t>3.26</t>
-  </si>
-  <si>
-    <t>2.87</t>
-  </si>
-  <si>
-    <t>0.57</t>
-  </si>
-  <si>
-    <t>2.53</t>
-  </si>
-  <si>
-    <t>5.93</t>
-  </si>
-  <si>
-    <t>4.84</t>
-  </si>
-  <si>
-    <t>3.99</t>
-  </si>
-  <si>
-    <t>2.99</t>
-  </si>
-  <si>
-    <t>3.01</t>
-  </si>
-  <si>
-    <t>5.35</t>
-  </si>
-  <si>
-    <t>2.95</t>
-  </si>
-  <si>
-    <t>3.07</t>
-  </si>
-  <si>
-    <t>2.64</t>
-  </si>
-  <si>
-    <t>3.56</t>
-  </si>
-  <si>
-    <t>2.93</t>
+    <t>5.49</t>
   </si>
   <si>
     <t>2.24</t>
-  </si>
-  <si>
-    <t>0.32</t>
-  </si>
-  <si>
-    <t>1.86</t>
-  </si>
-  <si>
-    <t>2.13</t>
-  </si>
-  <si>
-    <t>2.85</t>
-  </si>
-  <si>
-    <t>5.20</t>
-  </si>
-  <si>
-    <t>5.28</t>
-  </si>
-  <si>
-    <t>4.94</t>
-  </si>
-  <si>
-    <t>1.96</t>
-  </si>
-  <si>
-    <t>2.23</t>
   </si>
   <si>
     <t>RENTABILIDAD</t>
@@ -3108,23 +3111,23 @@
         <v>45739.0</v>
       </c>
       <c r="D5" s="11">
-        <v>1134.0</v>
+        <v>1129.0</v>
       </c>
       <c r="E5" s="11" t="s">
         <v>10</v>
       </c>
       <c r="F5" s="17">
+        <v>40.0</v>
+      </c>
+      <c r="G5" s="17">
         <v>25.0</v>
-      </c>
-      <c r="G5" s="17">
-        <v>35.0</v>
       </c>
       <c r="H5" s="17">
         <v>45.0</v>
       </c>
       <c r="I5" s="12">
         <f t="shared" si="1"/>
-        <v>35</v>
+        <v>36.66666667</v>
       </c>
     </row>
     <row r="6">
@@ -8279,7 +8282,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="48" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L1" s="6"/>
     </row>
@@ -8288,16 +8291,16 @@
     </row>
     <row r="3">
       <c r="A3" s="38" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="L3" s="6"/>
     </row>
     <row r="4">
       <c r="B4" s="38" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="G4" s="38" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L4" s="6"/>
     </row>
@@ -8403,62 +8406,62 @@
     </row>
     <row r="11">
       <c r="A11" s="203" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="48" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="38" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="203" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="48" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="38" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F19" s="98"/>
     </row>
     <row r="20">
       <c r="B20" s="48" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C20" s="50"/>
       <c r="D20" s="50"/>
       <c r="E20" s="50"/>
       <c r="F20" s="50"/>
       <c r="G20" s="48" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H20" s="48" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="I20" s="48" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="J20" s="48" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="K20" s="48" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="48" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="G21" s="52">
         <v>2.575</v>
@@ -8466,27 +8469,27 @@
     </row>
     <row r="23">
       <c r="K23" s="48" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="38" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H24" s="38" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="I24" s="38" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="K24" s="38" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L24" s="38" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M24" s="38" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="25">
@@ -8505,7 +8508,7 @@
         <v>#REF!</v>
       </c>
       <c r="K25" s="38" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="26">
@@ -8516,7 +8519,7 @@
         <v>1.19</v>
       </c>
       <c r="K26" s="38" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="27">
@@ -8527,7 +8530,7 @@
         <v>2.19</v>
       </c>
       <c r="K27" s="38" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="28">
@@ -8538,7 +8541,7 @@
         <v>0.05</v>
       </c>
       <c r="K28" s="38" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="29">
@@ -8557,7 +8560,7 @@
         <v>6.42</v>
       </c>
       <c r="K30" s="68" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="31">
@@ -8574,7 +8577,7 @@
         <v>3</v>
       </c>
       <c r="M31" s="38" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="32">
@@ -8702,7 +8705,7 @@
         <v>0.61</v>
       </c>
       <c r="K41" s="48" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="42">
@@ -8713,13 +8716,13 @@
         <v>0.69</v>
       </c>
       <c r="K42" s="38" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="L42" s="38" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M42" s="38" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="43">
@@ -8851,7 +8854,7 @@
         <v>0.0</v>
       </c>
       <c r="K51" s="38" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="52">
@@ -8879,20 +8882,20 @@
       </c>
       <c r="K54" s="90"/>
       <c r="L54" s="204" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M54" s="205"/>
       <c r="N54" s="95" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O54" s="95" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="P54" s="95" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="R54" s="17" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="S54" s="98">
         <v>0.15</v>
@@ -8906,7 +8909,7 @@
         <v>-0.12</v>
       </c>
       <c r="K55" s="14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L55" s="206">
         <v>0.76</v>
@@ -8971,7 +8974,7 @@
         <v>5.86</v>
       </c>
       <c r="R57" s="38" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="S57" s="52">
         <f>SUM(P55:P74)</f>
@@ -8986,7 +8989,7 @@
         <v>0.0</v>
       </c>
       <c r="K58" s="14" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L58" s="206">
         <v>0.57</v>
@@ -9000,7 +9003,7 @@
         <v>0.855</v>
       </c>
       <c r="P58" s="14" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="59">
@@ -9047,7 +9050,7 @@
         <v>0.96</v>
       </c>
       <c r="P60" s="14" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="61">
@@ -9058,7 +9061,7 @@
         <v>0.02</v>
       </c>
       <c r="K61" s="14" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L61" s="14">
         <v>0.42</v>
@@ -9130,7 +9133,7 @@
         <v>0.0</v>
       </c>
       <c r="K64" s="14" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L64" s="14">
         <v>0.42</v>
@@ -9274,7 +9277,7 @@
         <v>0.0</v>
       </c>
       <c r="K70" s="14" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L70" s="14">
         <v>0.66</v>
@@ -13145,11 +13148,17 @@
       <c r="A33" s="41"/>
       <c r="C33" s="41"/>
       <c r="D33" s="41"/>
+      <c r="J33" s="38">
+        <v>1129.0</v>
+      </c>
+      <c r="K33" s="38" t="s">
+        <v>72</v>
+      </c>
       <c r="R33" s="38">
         <v>544.0</v>
       </c>
       <c r="S33" s="38" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="34">
@@ -13161,10 +13170,10 @@
     <row r="35">
       <c r="A35" s="41"/>
       <c r="C35" s="48" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D35" s="38" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="36">
@@ -13279,14 +13288,14 @@
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="AC2:AG2"/>
+    <mergeCell ref="AI2:AL2"/>
     <mergeCell ref="AM2:AQ2"/>
-    <mergeCell ref="AI2:AL2"/>
-    <mergeCell ref="U2:X2"/>
-    <mergeCell ref="R2:T2"/>
-    <mergeCell ref="J2:L2"/>
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="E2:H2"/>
+    <mergeCell ref="J2:L2"/>
     <mergeCell ref="M2:P2"/>
+    <mergeCell ref="R2:T2"/>
+    <mergeCell ref="U2:X2"/>
     <mergeCell ref="Z2:AB2"/>
   </mergeCells>
   <conditionalFormatting sqref="B6:H6">
@@ -13620,13 +13629,13 @@
     </row>
     <row r="11">
       <c r="E11" s="62" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L11" s="38" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M11" s="55" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="N11" s="40" t="s">
         <v>21</v>
@@ -13636,10 +13645,10 @@
     </row>
     <row r="12">
       <c r="E12" s="62" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="L12" s="38" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M12" s="55" t="s">
         <v>19</v>
@@ -13901,37 +13910,37 @@
     </row>
     <row r="24">
       <c r="C24" s="48" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25">
       <c r="C25" s="58" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26">
       <c r="C26" s="66" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27">
       <c r="C27" s="67" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="28">
       <c r="C28" s="65" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="30">
       <c r="C30" s="68" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="31">
       <c r="C31" s="48" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L31" s="48" t="s">
         <v>20</v>
@@ -15923,7 +15932,7 @@
     </row>
     <row r="63">
       <c r="C63" s="48" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="65">
@@ -15943,25 +15952,25 @@
         <v>4</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J65" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K65" s="30" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L65" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M65" s="78" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N65" s="79" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="66">
@@ -16226,7 +16235,7 @@
     </row>
     <row r="76">
       <c r="C76" s="48" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="77">
@@ -16246,16 +16255,16 @@
         <v>4</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J77" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K77" s="30" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L77" s="4" t="s">
         <v>5</v>
@@ -16271,10 +16280,10 @@
         <v>8</v>
       </c>
       <c r="Q77" s="78" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R77" s="79" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="78">
@@ -16600,7 +16609,7 @@
     </row>
     <row r="94">
       <c r="C94" s="38" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="96">
@@ -16620,31 +16629,31 @@
         <v>4</v>
       </c>
       <c r="H96" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="I96" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="J96" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="I96" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="J96" s="4" t="s">
-        <v>81</v>
-      </c>
       <c r="K96" s="30" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L96" s="30" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M96" s="30" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N96" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O96" s="30" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P96" s="78" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q96" s="4" t="s">
         <v>5</v>
@@ -16659,7 +16668,7 @@
         <v>8</v>
       </c>
       <c r="U96" s="79" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="97">
@@ -17074,7 +17083,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="85" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B1" s="86"/>
       <c r="C1" s="86"/>
@@ -17097,47 +17106,47 @@
     <row r="2">
       <c r="A2" s="90"/>
       <c r="B2" s="91" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C2" s="91" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D2" s="92" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E2" s="92" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F2" s="91" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G2" s="93" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H2" s="93" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I2" s="93" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J2" s="91"/>
       <c r="K2" s="91" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L2" s="91" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M2" s="94" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N2" s="93" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O2" s="93" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P2" s="93" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="U2" s="50"/>
       <c r="V2" s="48"/>
@@ -17402,7 +17411,7 @@
     <row r="10">
       <c r="A10" s="61"/>
       <c r="E10" s="38" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O10" s="54"/>
       <c r="P10" s="61"/>
@@ -17533,7 +17542,7 @@
     <row r="18">
       <c r="A18" s="54"/>
       <c r="E18" s="38" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O18" s="54"/>
       <c r="P18" s="54"/>
@@ -17638,7 +17647,7 @@
         <v>4</v>
       </c>
       <c r="H32" s="99" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I32" s="4" t="s">
         <v>5</v>
@@ -17653,13 +17662,13 @@
         <v>8</v>
       </c>
       <c r="M32" s="100" t="s">
+        <v>94</v>
+      </c>
+      <c r="N32" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="O32" s="101" t="s">
         <v>93</v>
-      </c>
-      <c r="N32" s="30" t="s">
-        <v>108</v>
-      </c>
-      <c r="O32" s="101" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="33">
@@ -18113,13 +18122,13 @@
     </row>
     <row r="9">
       <c r="B9" s="38" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C9" s="38" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D9" s="38" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10">
@@ -18137,7 +18146,7 @@
         <v>-0.1658536585</v>
       </c>
       <c r="F10" s="38" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11">
@@ -18155,7 +18164,7 @@
         <v>-0.15</v>
       </c>
       <c r="F11" s="38" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12">
@@ -18193,16 +18202,16 @@
     </row>
     <row r="16">
       <c r="H16" s="38" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17">
       <c r="G17" s="111"/>
       <c r="H17" s="48" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I17" s="48" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="18">
@@ -18222,7 +18231,7 @@
         <v>332.0</v>
       </c>
       <c r="I18" s="42" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19">
@@ -18239,10 +18248,10 @@
         <v>18</v>
       </c>
       <c r="H19" s="38" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I19" s="38" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20">
@@ -18262,7 +18271,7 @@
         <v>411.0</v>
       </c>
       <c r="I20" s="38" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="21">
@@ -18270,10 +18279,10 @@
         <v>20</v>
       </c>
       <c r="H21" s="38" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I21" s="38" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="22">
@@ -18281,16 +18290,16 @@
         <v>21</v>
       </c>
       <c r="H22" s="38" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I22" s="38" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="8"/>
       <c r="I24" s="38" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25">
@@ -18298,7 +18307,7 @@
         <v>1</v>
       </c>
       <c r="I25" s="38" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="26">
@@ -18349,28 +18358,28 @@
         <v>530.0</v>
       </c>
       <c r="I30" s="48" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M30" s="60"/>
       <c r="N30" s="60"/>
     </row>
     <row r="31">
       <c r="I31" s="48" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M31" s="60"/>
       <c r="N31" s="60"/>
     </row>
     <row r="32">
       <c r="I32" s="38" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M32" s="60"/>
       <c r="N32" s="60"/>
     </row>
     <row r="33">
       <c r="I33" s="38" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="M33" s="60"/>
       <c r="N33" s="60"/>
@@ -18381,7 +18390,7 @@
     </row>
     <row r="35">
       <c r="I35" s="38" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M35" s="60"/>
       <c r="N35" s="60"/>
@@ -18400,28 +18409,28 @@
     </row>
     <row r="39">
       <c r="I39" s="48" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M39" s="60"/>
       <c r="N39" s="60"/>
     </row>
     <row r="40">
       <c r="I40" s="38" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M40" s="60"/>
       <c r="N40" s="60"/>
     </row>
     <row r="41">
       <c r="I41" s="38" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M41" s="60"/>
       <c r="N41" s="60"/>
     </row>
     <row r="42">
       <c r="I42" s="68" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="M42" s="60"/>
       <c r="N42" s="60"/>
@@ -18432,7 +18441,7 @@
     </row>
     <row r="44">
       <c r="I44" s="48" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -18450,18 +18459,18 @@
   <sheetData>
     <row r="1">
       <c r="B1" s="38" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3">
       <c r="C3" s="38" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D3" s="38" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H3" s="38" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K3" s="60"/>
       <c r="L3" s="60"/>
@@ -18471,13 +18480,13 @@
         <v>17</v>
       </c>
       <c r="C4" s="48" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D4" s="48" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H4" s="38" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I4" s="113"/>
       <c r="J4" s="113"/>
@@ -18486,7 +18495,7 @@
     </row>
     <row r="5">
       <c r="B5" s="48" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C5" s="50">
         <f t="shared" ref="C5:D5" si="1">SUM(C6:C18)</f>
@@ -18501,7 +18510,7 @@
         <v>0.4077999152</v>
       </c>
       <c r="F5" s="38" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6">
@@ -18520,7 +18529,7 @@
         <v>3.06</v>
       </c>
       <c r="H7" s="38" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8">
@@ -18539,7 +18548,7 @@
         <v>2.3</v>
       </c>
       <c r="H9" s="38" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10">
@@ -18558,7 +18567,7 @@
         <v>4.18</v>
       </c>
       <c r="H11" s="38" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12">
@@ -18577,7 +18586,7 @@
         <v>2.35</v>
       </c>
       <c r="H13" s="38" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14">
@@ -18604,7 +18613,7 @@
         <v>1.37</v>
       </c>
       <c r="H16" s="38" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="17">
@@ -18628,15 +18637,15 @@
         <v>18</v>
       </c>
       <c r="C20" s="48" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D20" s="48" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="48" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C21" s="50">
         <f t="shared" ref="C21:D21" si="2">sum(C22:C34)</f>
@@ -18651,7 +18660,7 @@
         <v>0.4012276786</v>
       </c>
       <c r="F21" s="38" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="22">
@@ -18763,15 +18772,15 @@
         <v>19</v>
       </c>
       <c r="C37" s="48" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D37" s="48" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="48" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C38" s="50">
         <f t="shared" ref="C38:D38" si="3">sum(C39:C51)</f>
@@ -18786,7 +18795,7 @@
         <v>0.03155866056</v>
       </c>
       <c r="F38" s="38" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="39">
@@ -18912,17 +18921,17 @@
         <v>20</v>
       </c>
       <c r="C54" s="48" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D54" s="48" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K54" s="60"/>
       <c r="L54" s="60"/>
     </row>
     <row r="55">
       <c r="B55" s="48" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C55" s="50">
         <f>sum(C56:C69)</f>
@@ -18937,7 +18946,7 @@
         <v>0.005738332058</v>
       </c>
       <c r="F55" s="38" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="K55" s="60"/>
       <c r="L55" s="60"/>
@@ -19091,17 +19100,17 @@
         <v>21</v>
       </c>
       <c r="C71" s="48" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D71" s="48" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="K71" s="60"/>
       <c r="L71" s="60"/>
     </row>
     <row r="72">
       <c r="B72" s="48" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C72" s="50">
         <f>sum(C73:C86)</f>
@@ -19116,7 +19125,7 @@
         <v>0.3919949174</v>
       </c>
       <c r="F72" s="38" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K72" s="60"/>
       <c r="L72" s="60"/>
@@ -19330,7 +19339,7 @@
     <row r="2">
       <c r="A2" s="17"/>
       <c r="B2" s="114" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C2" s="17">
         <v>0.1</v>
@@ -19340,7 +19349,7 @@
     <row r="3">
       <c r="A3" s="17"/>
       <c r="B3" s="114" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C3" s="13" t="str">
         <f>AVERAGE(#REF!)</f>
@@ -19355,7 +19364,7 @@
       <c r="L4" s="20"/>
       <c r="P4" s="20"/>
       <c r="AE4" s="38" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AF4" s="115">
         <f>CORREL(AE6:AE10000,AF6:AF10000)</f>
@@ -19365,50 +19374,50 @@
     <row r="5">
       <c r="A5" s="17"/>
       <c r="B5" s="20" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L5" s="20" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P5" s="20" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AE5" s="38" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AF5" s="38" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="17"/>
       <c r="B6" s="38" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F6" s="38" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K6" s="48"/>
       <c r="L6" s="48" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N6" s="48" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P6" s="48" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="R6" s="48" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="V6" s="48" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AA6" s="38" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AB6" s="38" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AE6" s="38">
         <v>519.2</v>
@@ -19450,7 +19459,7 @@
         <v>0.5454545455</v>
       </c>
       <c r="AA7" s="38" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AB7" s="52">
         <f t="shared" ref="AB7:AB16" si="4">LEFT(REPLACE(AA7,1,1,""),FIND(",", AA7)-2)/1</f>
@@ -19466,14 +19475,14 @@
     <row r="8">
       <c r="A8" s="17"/>
       <c r="B8" s="119" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C8" s="120" t="str">
         <f t="shared" ref="C8:C17" si="5">REPLACE(B8,FIND(".",B8),1,",")*1</f>
         <v>#VALUE!</v>
       </c>
       <c r="F8" s="58" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G8" s="120" t="str">
         <f t="shared" ref="G8:G27" si="6">REPLACE(F8,FIND(".",F8),1,",")*1</f>
@@ -19508,7 +19517,7 @@
         <v>0.5263157895</v>
       </c>
       <c r="AA8" s="38" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AB8" s="52">
         <f t="shared" si="4"/>
@@ -19524,14 +19533,14 @@
     <row r="9">
       <c r="A9" s="17"/>
       <c r="B9" s="119" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C9" s="120" t="str">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="F9" s="58" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G9" s="120" t="str">
         <f t="shared" si="6"/>
@@ -19545,13 +19554,13 @@
       </c>
       <c r="K9" s="17"/>
       <c r="L9" s="116" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M9" s="116" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N9" s="48" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P9" s="118">
         <v>1.0</v>
@@ -19575,7 +19584,7 @@
         <v>0.25</v>
       </c>
       <c r="AA9" s="38" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AB9" s="52">
         <f t="shared" si="4"/>
@@ -19591,14 +19600,14 @@
     <row r="10">
       <c r="A10" s="17"/>
       <c r="B10" s="121" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C10" s="120" t="str">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="F10" s="58" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G10" s="120" t="str">
         <f t="shared" si="6"/>
@@ -19635,7 +19644,7 @@
         <v>76</v>
       </c>
       <c r="AA10" s="38" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AB10" s="52">
         <f t="shared" si="4"/>
@@ -19650,14 +19659,14 @@
     </row>
     <row r="11">
       <c r="B11" s="119" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C11" s="120" t="str">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="F11" s="58" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G11" s="120" t="str">
         <f t="shared" si="6"/>
@@ -19686,7 +19695,7 @@
         <v>2.0</v>
       </c>
       <c r="AA11" s="38" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AB11" s="52">
         <f t="shared" si="4"/>
@@ -19701,14 +19710,14 @@
     </row>
     <row r="12">
       <c r="B12" s="121" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C12" s="120" t="str">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="F12" s="58" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G12" s="120" t="str">
         <f t="shared" si="6"/>
@@ -19737,7 +19746,7 @@
         <v>1.0</v>
       </c>
       <c r="AA12" s="38" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AB12" s="52">
         <f t="shared" si="4"/>
@@ -19752,14 +19761,14 @@
     </row>
     <row r="13">
       <c r="B13" s="119" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C13" s="120" t="str">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="F13" s="58" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G13" s="120" t="str">
         <f t="shared" si="6"/>
@@ -19789,16 +19798,16 @@
       <c r="Q13" s="50"/>
       <c r="R13" s="90"/>
       <c r="S13" s="95" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="T13" s="95" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="U13" s="95" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AA13" s="38" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AB13" s="52">
         <f t="shared" si="4"/>
@@ -19813,14 +19822,14 @@
     </row>
     <row r="14">
       <c r="B14" s="119" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C14" s="120" t="str">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="F14" s="58" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G14" s="120" t="str">
         <f t="shared" si="6"/>
@@ -19860,7 +19869,7 @@
         <v>11.0</v>
       </c>
       <c r="AA14" s="38" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AB14" s="52">
         <f t="shared" si="4"/>
@@ -19875,14 +19884,14 @@
     </row>
     <row r="15">
       <c r="B15" s="119" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C15" s="120" t="str">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="F15" s="58" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G15" s="120" t="str">
         <f t="shared" si="6"/>
@@ -19922,7 +19931,7 @@
         <v>13.0</v>
       </c>
       <c r="AA15" s="38" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AB15" s="52">
         <f t="shared" si="4"/>
@@ -19937,14 +19946,14 @@
     </row>
     <row r="16">
       <c r="B16" s="119" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C16" s="120" t="str">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="F16" s="58" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G16" s="120" t="str">
         <f t="shared" si="6"/>
@@ -19984,7 +19993,7 @@
         <v>12.0</v>
       </c>
       <c r="AA16" s="38" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AB16" s="52">
         <f t="shared" si="4"/>
@@ -19999,14 +20008,14 @@
     </row>
     <row r="17">
       <c r="B17" s="119" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C17" s="120" t="str">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="F17" s="58" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G17" s="120" t="str">
         <f t="shared" si="6"/>
@@ -20034,7 +20043,7 @@
         <v>1.0</v>
       </c>
       <c r="R17" s="95" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="S17" s="123">
         <f t="shared" ref="S17:U17" si="10">SUM(S14:S16)</f>
@@ -20057,7 +20066,7 @@
     </row>
     <row r="18">
       <c r="F18" s="58" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G18" s="120" t="str">
         <f t="shared" si="6"/>
@@ -20094,14 +20103,14 @@
     </row>
     <row r="19">
       <c r="B19" s="48" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C19" s="52" t="str">
         <f>AVERAGE(C8:C17)</f>
         <v>#VALUE!</v>
       </c>
       <c r="F19" s="58" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G19" s="120" t="str">
         <f t="shared" si="6"/>
@@ -20129,7 +20138,7 @@
       <c r="T19" s="13"/>
       <c r="U19" s="13"/>
       <c r="AA19" s="38" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AB19" s="52">
         <f>AVERAGE(AB7:AB16)</f>
@@ -20144,7 +20153,7 @@
     </row>
     <row r="20">
       <c r="F20" s="58" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G20" s="120" t="str">
         <f t="shared" si="6"/>
@@ -20169,7 +20178,7 @@
     </row>
     <row r="21">
       <c r="F21" s="58" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G21" s="120" t="str">
         <f t="shared" si="6"/>
@@ -20183,13 +20192,13 @@
       </c>
       <c r="R21" s="90"/>
       <c r="S21" s="95" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="T21" s="95" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="U21" s="95" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AE21" s="38">
         <v>146.62</v>
@@ -20201,7 +20210,7 @@
     <row r="22">
       <c r="C22" s="120"/>
       <c r="F22" s="58" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G22" s="120" t="str">
         <f t="shared" si="6"/>
@@ -20274,7 +20283,7 @@
     </row>
     <row r="24">
       <c r="F24" s="58" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G24" s="120" t="str">
         <f t="shared" si="6"/>
@@ -20310,7 +20319,7 @@
     </row>
     <row r="25">
       <c r="F25" s="58" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G25" s="120" t="str">
         <f t="shared" si="6"/>
@@ -20323,7 +20332,7 @@
         <v>1.0</v>
       </c>
       <c r="R25" s="95" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="S25" s="123">
         <f t="shared" ref="S25:U25" si="14">SUM(S22:S24)</f>
@@ -20346,7 +20355,7 @@
     </row>
     <row r="26">
       <c r="F26" s="58" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G26" s="120" t="str">
         <f t="shared" si="6"/>
@@ -20391,13 +20400,13 @@
         <v>1.0</v>
       </c>
       <c r="AA28" s="38" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AB28" s="38" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AC28" s="38" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AE28" s="38">
         <v>106.73</v>
@@ -20408,7 +20417,7 @@
     </row>
     <row r="29">
       <c r="F29" s="48" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G29" s="52" t="str">
         <f>AVERAGE(G8:G27)</f>
@@ -20499,7 +20508,7 @@
     </row>
     <row r="32">
       <c r="B32" s="65" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G32" s="120"/>
       <c r="P32" s="118">
@@ -20528,7 +20537,7 @@
     </row>
     <row r="33">
       <c r="B33" s="126" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G33" s="127"/>
       <c r="P33" s="118">
@@ -20582,7 +20591,7 @@
     </row>
     <row r="35">
       <c r="H35" s="48" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P35" s="118">
         <v>1.0</v>
@@ -20645,7 +20654,7 @@
       <c r="C37" s="50"/>
       <c r="D37" s="129">
         <f>AVERAGE(D39:D1775)</f>
-        <v>3.662637363</v>
+        <v>3.436923077</v>
       </c>
       <c r="G37" s="48" t="s">
         <v>18</v>
@@ -20710,11 +20719,11 @@
     </row>
     <row r="39">
       <c r="C39" s="131" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D39" s="120">
         <f t="shared" ref="D39:D221" si="17">IF(COUNTA(C39)=1,C39/1,"")</f>
-        <v>1.52</v>
+        <v>2.17</v>
       </c>
       <c r="G39" s="48" t="s">
         <v>20</v>
@@ -20748,11 +20757,11 @@
     </row>
     <row r="40">
       <c r="C40" s="132" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D40" s="120">
         <f t="shared" si="17"/>
-        <v>0.33</v>
+        <v>1.66</v>
       </c>
       <c r="G40" s="48" t="s">
         <v>21</v>
@@ -20786,11 +20795,11 @@
     </row>
     <row r="41">
       <c r="C41" s="132" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D41" s="120">
         <f t="shared" si="17"/>
-        <v>1.43</v>
+        <v>1.96</v>
       </c>
       <c r="P41" s="118">
         <v>0.0</v>
@@ -20818,11 +20827,11 @@
     </row>
     <row r="42">
       <c r="C42" s="132" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D42" s="120">
         <f t="shared" si="17"/>
-        <v>0.28</v>
+        <v>1.28</v>
       </c>
       <c r="P42" s="118">
         <v>2.0</v>
@@ -20850,11 +20859,11 @@
     </row>
     <row r="43">
       <c r="C43" s="132" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D43" s="120">
         <f t="shared" si="17"/>
-        <v>0.92</v>
+        <v>2.78</v>
       </c>
       <c r="P43" s="118">
         <v>1.0</v>
@@ -20882,11 +20891,11 @@
     </row>
     <row r="44">
       <c r="C44" s="132" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D44" s="120">
         <f t="shared" si="17"/>
-        <v>1.65</v>
+        <v>2.26</v>
       </c>
       <c r="P44" s="118">
         <v>2.0</v>
@@ -20912,11 +20921,11 @@
     </row>
     <row r="45">
       <c r="C45" s="132" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D45" s="120">
         <f t="shared" si="17"/>
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="P45" s="118">
         <v>1.0</v>
@@ -20930,17 +20939,17 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="C46" s="132" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D46" s="120">
         <f t="shared" si="17"/>
-        <v>1.93</v>
+        <v>1.78</v>
       </c>
       <c r="G46" s="133" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H46" s="133" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P46" s="118">
         <v>0.0</v>
@@ -20954,11 +20963,11 @@
     </row>
     <row r="47">
       <c r="C47" s="132" t="s">
-        <v>237</v>
+        <v>204</v>
       </c>
       <c r="D47" s="120">
         <f t="shared" si="17"/>
-        <v>1.6</v>
+        <v>3.64</v>
       </c>
       <c r="G47" s="134" t="s">
         <v>17</v>
@@ -20973,7 +20982,7 @@
         <v>3</v>
       </c>
       <c r="AB47" s="38" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AE47" s="38">
         <v>67.98</v>
@@ -20984,11 +20993,11 @@
     </row>
     <row r="48">
       <c r="C48" s="132" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="D48" s="120">
         <f t="shared" si="17"/>
-        <v>1.65</v>
+        <v>3.74</v>
       </c>
       <c r="G48" s="134" t="s">
         <v>18</v>
@@ -20997,7 +21006,7 @@
         <v>0.36678739680281</v>
       </c>
       <c r="J48" s="38" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K48" s="110">
         <f>AVERAGE(H47:H51)</f>
@@ -21021,11 +21030,11 @@
     </row>
     <row r="49">
       <c r="C49" s="132" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D49" s="120">
         <f t="shared" si="17"/>
-        <v>0.77</v>
+        <v>4</v>
       </c>
       <c r="G49" s="134" t="s">
         <v>19</v>
@@ -21034,7 +21043,7 @@
         <v>0.142870351877935</v>
       </c>
       <c r="J49" s="38" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K49" s="110">
         <f>MEDIAN(H47:H51)</f>
@@ -21058,11 +21067,11 @@
     </row>
     <row r="50">
       <c r="C50" s="132" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D50" s="120">
         <f t="shared" si="17"/>
-        <v>6.54</v>
+        <v>3.73</v>
       </c>
       <c r="G50" s="134" t="s">
         <v>20</v>
@@ -21071,7 +21080,7 @@
         <v>0.497437843674554</v>
       </c>
       <c r="J50" s="38" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K50" s="110">
         <f>PERCENTILE(H47:H51,0.25)</f>
@@ -21095,11 +21104,11 @@
     </row>
     <row r="51">
       <c r="C51" s="132" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D51" s="120">
         <f t="shared" si="17"/>
-        <v>5.57</v>
+        <v>4.3</v>
       </c>
       <c r="G51" s="134" t="s">
         <v>21</v>
@@ -21108,7 +21117,7 @@
         <v>0.247446036291655</v>
       </c>
       <c r="J51" s="38" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K51" s="110">
         <f>PERCENTILE(H47:H51,0.75)</f>
@@ -21132,11 +21141,11 @@
     </row>
     <row r="52">
       <c r="C52" s="132" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D52" s="120">
         <f t="shared" si="17"/>
-        <v>4.51</v>
+        <v>5.93</v>
       </c>
       <c r="P52" s="118">
         <v>0.0</v>
@@ -21156,11 +21165,11 @@
     </row>
     <row r="53">
       <c r="C53" s="132" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D53" s="120">
         <f t="shared" si="17"/>
-        <v>0.84</v>
+        <v>3.66</v>
       </c>
       <c r="P53" s="118">
         <v>0.0</v>
@@ -21180,11 +21189,11 @@
     </row>
     <row r="54">
       <c r="C54" s="132" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D54" s="120">
         <f t="shared" si="17"/>
-        <v>0.82</v>
+        <v>4.11</v>
       </c>
       <c r="P54" s="118">
         <v>2.0</v>
@@ -21204,11 +21213,11 @@
     </row>
     <row r="55">
       <c r="C55" s="132" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D55" s="120">
         <f t="shared" si="17"/>
-        <v>5.71</v>
+        <v>5.4</v>
       </c>
       <c r="P55" s="118">
         <v>0.0</v>
@@ -21228,11 +21237,11 @@
     </row>
     <row r="56">
       <c r="C56" s="132" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D56" s="120">
         <f t="shared" si="17"/>
-        <v>6.89</v>
+        <v>5.97</v>
       </c>
       <c r="P56" s="118">
         <v>0.0</v>
@@ -21252,11 +21261,11 @@
     </row>
     <row r="57">
       <c r="C57" s="132" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D57" s="120">
         <f t="shared" si="17"/>
-        <v>3.95</v>
+        <v>4.34</v>
       </c>
       <c r="P57" s="118">
         <v>2.0</v>
@@ -21276,14 +21285,14 @@
     </row>
     <row r="58">
       <c r="C58" s="132" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D58" s="120">
         <f t="shared" si="17"/>
-        <v>1.63</v>
+        <v>1.81</v>
       </c>
       <c r="G58" s="136" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H58" s="137"/>
       <c r="P58" s="118">
@@ -21304,15 +21313,15 @@
     </row>
     <row r="59">
       <c r="C59" s="132" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D59" s="120">
         <f t="shared" si="17"/>
-        <v>2.69</v>
+        <v>2.99</v>
       </c>
       <c r="G59" s="137"/>
       <c r="H59" s="138" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="P59" s="118">
         <v>0.0</v>
@@ -21332,15 +21341,15 @@
     </row>
     <row r="60">
       <c r="C60" s="132" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D60" s="120">
         <f t="shared" si="17"/>
-        <v>4.35</v>
+        <v>4.84</v>
       </c>
       <c r="G60" s="137"/>
       <c r="H60" s="138" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P60" s="118">
         <v>2.0</v>
@@ -21360,15 +21369,15 @@
     </row>
     <row r="61">
       <c r="C61" s="132" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D61" s="120">
         <f t="shared" si="17"/>
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="G61" s="137"/>
       <c r="H61" s="138" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P61" s="118">
         <v>2.0</v>
@@ -21388,15 +21397,15 @@
     </row>
     <row r="62">
       <c r="C62" s="132" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D62" s="120">
         <f t="shared" si="17"/>
-        <v>5.01</v>
+        <v>3.34</v>
       </c>
       <c r="G62" s="137"/>
       <c r="H62" s="138" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="P62" s="118">
         <v>1.0</v>
@@ -21416,15 +21425,15 @@
     </row>
     <row r="63">
       <c r="C63" s="132" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D63" s="120">
         <f t="shared" si="17"/>
-        <v>4.18</v>
+        <v>2.79</v>
       </c>
       <c r="G63" s="137"/>
       <c r="H63" s="138" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P63" s="118">
         <v>0.0</v>
@@ -21438,11 +21447,11 @@
     </row>
     <row r="64">
       <c r="C64" s="132" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D64" s="120">
         <f t="shared" si="17"/>
-        <v>8.08</v>
+        <v>5.39</v>
       </c>
       <c r="P64" s="118">
         <v>1.0</v>
@@ -21456,11 +21465,11 @@
     </row>
     <row r="65">
       <c r="C65" s="132" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D65" s="120">
         <f t="shared" si="17"/>
-        <v>11.99</v>
+        <v>7.99</v>
       </c>
       <c r="P65" s="118">
         <v>2.0</v>
@@ -21474,11 +21483,11 @@
     </row>
     <row r="66">
       <c r="C66" s="132" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D66" s="120">
         <f t="shared" si="17"/>
-        <v>11.64</v>
+        <v>7.76</v>
       </c>
       <c r="P66" s="118">
         <v>0.0</v>
@@ -21492,11 +21501,11 @@
     </row>
     <row r="67">
       <c r="C67" s="132" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D67" s="120">
         <f t="shared" si="17"/>
-        <v>7.86</v>
+        <v>5.24</v>
       </c>
       <c r="P67" s="118">
         <v>0.0</v>
@@ -21510,11 +21519,11 @@
     </row>
     <row r="68">
       <c r="C68" s="132" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D68" s="120">
         <f t="shared" si="17"/>
-        <v>11.5</v>
+        <v>7.66</v>
       </c>
       <c r="P68" s="118">
         <v>1.0</v>
@@ -21528,11 +21537,11 @@
     </row>
     <row r="69">
       <c r="C69" s="132" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D69" s="120">
         <f t="shared" si="17"/>
-        <v>7.78</v>
+        <v>5.19</v>
       </c>
       <c r="P69" s="118">
         <v>2.0</v>
@@ -21546,11 +21555,11 @@
     </row>
     <row r="70">
       <c r="C70" s="132" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D70" s="120">
         <f t="shared" si="17"/>
-        <v>5.65</v>
+        <v>3.76</v>
       </c>
       <c r="P70" s="118">
         <v>1.0</v>
@@ -21564,11 +21573,11 @@
     </row>
     <row r="71">
       <c r="C71" s="132" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D71" s="120">
         <f t="shared" si="17"/>
-        <v>6.67</v>
+        <v>4.44</v>
       </c>
       <c r="F71" s="139"/>
       <c r="P71" s="118">
@@ -21583,11 +21592,11 @@
     </row>
     <row r="72">
       <c r="C72" s="132" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D72" s="120">
         <f t="shared" si="17"/>
-        <v>7.3</v>
+        <v>4.86</v>
       </c>
       <c r="P72" s="118">
         <v>0.0</v>
@@ -21601,11 +21610,11 @@
     </row>
     <row r="73">
       <c r="C73" s="132" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D73" s="120">
         <f t="shared" si="17"/>
-        <v>5</v>
+        <v>3.33</v>
       </c>
       <c r="P73" s="118">
         <v>1.0</v>
@@ -21619,11 +21628,11 @@
     </row>
     <row r="74">
       <c r="C74" s="132" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D74" s="120">
         <f t="shared" si="17"/>
-        <v>6.44</v>
+        <v>4.29</v>
       </c>
       <c r="P74" s="118">
         <v>0.0</v>
@@ -21637,11 +21646,11 @@
     </row>
     <row r="75">
       <c r="C75" s="132" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D75" s="120">
         <f t="shared" si="17"/>
-        <v>4.11</v>
+        <v>4.57</v>
       </c>
       <c r="P75" s="118">
         <v>1.0</v>
@@ -21655,11 +21664,11 @@
     </row>
     <row r="76">
       <c r="C76" s="132" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D76" s="120">
         <f t="shared" si="17"/>
-        <v>4.15</v>
+        <v>4.61</v>
       </c>
       <c r="P76" s="118">
         <v>0.0</v>
@@ -21673,11 +21682,11 @@
     </row>
     <row r="77">
       <c r="C77" s="132" t="s">
-        <v>276</v>
+        <v>210</v>
       </c>
       <c r="D77" s="120">
         <f t="shared" si="17"/>
-        <v>2.52</v>
+        <v>2.8</v>
       </c>
       <c r="P77" s="118">
         <v>0.0</v>
@@ -21695,7 +21704,7 @@
       </c>
       <c r="D78" s="120">
         <f t="shared" si="17"/>
-        <v>2.84</v>
+        <v>3.16</v>
       </c>
       <c r="P78" s="118">
         <v>1.0</v>
@@ -21713,7 +21722,7 @@
       </c>
       <c r="D79" s="120">
         <f t="shared" si="17"/>
-        <v>1.71</v>
+        <v>1.9</v>
       </c>
       <c r="P79" s="118">
         <v>2.0</v>
@@ -21731,7 +21740,7 @@
       </c>
       <c r="D80" s="120">
         <f t="shared" si="17"/>
-        <v>2.46</v>
+        <v>2.73</v>
       </c>
       <c r="P80" s="118">
         <v>1.0</v>
@@ -21745,11 +21754,11 @@
     </row>
     <row r="81">
       <c r="C81" s="132" t="s">
-        <v>280</v>
+        <v>251</v>
       </c>
       <c r="D81" s="120">
         <f t="shared" si="17"/>
-        <v>3.9</v>
+        <v>4.34</v>
       </c>
       <c r="P81" s="118">
         <v>2.0</v>
@@ -21763,11 +21772,11 @@
     </row>
     <row r="82">
       <c r="C82" s="132" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D82" s="120">
         <f t="shared" si="17"/>
-        <v>3.1</v>
+        <v>3.44</v>
       </c>
       <c r="P82" s="118">
         <v>1.0</v>
@@ -21781,11 +21790,11 @@
     </row>
     <row r="83">
       <c r="C83" s="132" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D83" s="120">
         <f t="shared" si="17"/>
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="P83" s="118">
         <v>0.0</v>
@@ -21799,11 +21808,11 @@
     </row>
     <row r="84">
       <c r="C84" s="132" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D84" s="120">
         <f t="shared" si="17"/>
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="P84" s="118">
         <v>1.0</v>
@@ -21817,11 +21826,11 @@
     </row>
     <row r="85">
       <c r="C85" s="132" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D85" s="120">
         <f t="shared" si="17"/>
-        <v>3.48</v>
+        <v>2.32</v>
       </c>
       <c r="P85" s="118">
         <v>0.0</v>
@@ -21835,11 +21844,11 @@
     </row>
     <row r="86">
       <c r="C86" s="132" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D86" s="120">
         <f t="shared" si="17"/>
-        <v>3.86</v>
+        <v>2.57</v>
       </c>
       <c r="P86" s="118">
         <v>0.0</v>
@@ -21853,11 +21862,11 @@
     </row>
     <row r="87">
       <c r="C87" s="132" t="s">
-        <v>200</v>
+        <v>285</v>
       </c>
       <c r="D87" s="120">
         <f t="shared" si="17"/>
-        <v>3.68</v>
+        <v>2.46</v>
       </c>
       <c r="P87" s="118">
         <v>1.0</v>
@@ -21875,7 +21884,7 @@
       </c>
       <c r="D88" s="120">
         <f t="shared" si="17"/>
-        <v>6.65</v>
+        <v>7.39</v>
       </c>
       <c r="P88" s="118">
         <v>2.0</v>
@@ -21893,7 +21902,7 @@
       </c>
       <c r="D89" s="120">
         <f t="shared" si="17"/>
-        <v>5.84</v>
+        <v>6.49</v>
       </c>
       <c r="P89" s="118">
         <v>2.0</v>
@@ -21911,7 +21920,7 @@
       </c>
       <c r="D90" s="120">
         <f t="shared" si="17"/>
-        <v>9.57</v>
+        <v>10.63</v>
       </c>
       <c r="P90" s="118">
         <v>1.0</v>
@@ -21929,7 +21938,7 @@
       </c>
       <c r="D91" s="120">
         <f t="shared" si="17"/>
-        <v>6.57</v>
+        <v>7.3</v>
       </c>
       <c r="P91" s="118">
         <v>1.0</v>
@@ -21943,11 +21952,11 @@
     </row>
     <row r="92">
       <c r="C92" s="132" t="s">
-        <v>193</v>
+        <v>290</v>
       </c>
       <c r="D92" s="120">
         <f t="shared" si="17"/>
-        <v>5.94</v>
+        <v>6.6</v>
       </c>
       <c r="P92" s="118">
         <v>2.0</v>
@@ -21961,11 +21970,11 @@
     </row>
     <row r="93">
       <c r="C93" s="132" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D93" s="120">
         <f t="shared" si="17"/>
-        <v>0.52</v>
+        <v>1.74</v>
       </c>
       <c r="P93" s="118">
         <v>0.0</v>
@@ -21979,11 +21988,11 @@
     </row>
     <row r="94">
       <c r="C94" s="132" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D94" s="120">
         <f t="shared" si="17"/>
-        <v>2.91</v>
+        <v>1.94</v>
       </c>
       <c r="P94" s="118">
         <v>0.0</v>
@@ -21997,11 +22006,11 @@
     </row>
     <row r="95">
       <c r="C95" s="132" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D95" s="120">
         <f t="shared" si="17"/>
-        <v>2.48</v>
+        <v>1.65</v>
       </c>
       <c r="P95" s="118">
         <v>1.0</v>
@@ -22015,11 +22024,11 @@
     </row>
     <row r="96">
       <c r="C96" s="132" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D96" s="120">
         <f t="shared" si="17"/>
-        <v>4.98</v>
+        <v>3.32</v>
       </c>
       <c r="P96" s="118">
         <v>2.0</v>
@@ -22033,11 +22042,11 @@
     </row>
     <row r="97">
       <c r="C97" s="132" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D97" s="120">
         <f t="shared" si="17"/>
-        <v>0.49</v>
+        <v>1.62</v>
       </c>
       <c r="P97" s="118">
         <v>0.0</v>
@@ -22051,11 +22060,11 @@
     </row>
     <row r="98">
       <c r="C98" s="132" t="s">
-        <v>295</v>
+        <v>228</v>
       </c>
       <c r="D98" s="120">
         <f t="shared" si="17"/>
-        <v>3.26</v>
+        <v>2.17</v>
       </c>
       <c r="P98" s="118">
         <v>2.0</v>
@@ -22073,7 +22082,7 @@
       </c>
       <c r="D99" s="120">
         <f t="shared" si="17"/>
-        <v>2.87</v>
+        <v>1.91</v>
       </c>
       <c r="P99" s="118">
         <v>2.0</v>
@@ -22087,11 +22096,11 @@
     </row>
     <row r="100">
       <c r="C100" s="132" t="s">
-        <v>220</v>
+        <v>297</v>
       </c>
       <c r="D100" s="120">
         <f t="shared" si="17"/>
-        <v>2.63</v>
+        <v>1.76</v>
       </c>
       <c r="P100" s="118">
         <v>2.0</v>
@@ -22105,11 +22114,11 @@
     </row>
     <row r="101">
       <c r="C101" s="132" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D101" s="120">
         <f t="shared" si="17"/>
-        <v>0.57</v>
+        <v>1.89</v>
       </c>
       <c r="P101" s="118">
         <v>2.0</v>
@@ -22123,11 +22132,11 @@
     </row>
     <row r="102">
       <c r="C102" s="132" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D102" s="120">
         <f t="shared" si="17"/>
-        <v>2.53</v>
+        <v>1.69</v>
       </c>
       <c r="P102" s="118">
         <v>2.0</v>
@@ -22141,11 +22150,11 @@
     </row>
     <row r="103">
       <c r="C103" s="132" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D103" s="120">
         <f t="shared" si="17"/>
-        <v>5.93</v>
+        <v>6.59</v>
       </c>
       <c r="P103" s="118">
         <v>1.0</v>
@@ -22159,11 +22168,11 @@
     </row>
     <row r="104">
       <c r="C104" s="132" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D104" s="120">
         <f t="shared" si="17"/>
-        <v>4.84</v>
+        <v>3.23</v>
       </c>
       <c r="N104" s="140"/>
       <c r="P104" s="118">
@@ -22178,11 +22187,11 @@
     </row>
     <row r="105">
       <c r="C105" s="132" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D105" s="120">
         <f t="shared" si="17"/>
-        <v>3.99</v>
+        <v>2.66</v>
       </c>
       <c r="N105" s="13"/>
       <c r="P105" s="118">
@@ -22197,11 +22206,11 @@
     </row>
     <row r="106">
       <c r="C106" s="132" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="D106" s="120">
         <f t="shared" si="17"/>
-        <v>0.49</v>
+        <v>0.33</v>
       </c>
       <c r="N106" s="13"/>
       <c r="P106" s="118">
@@ -22216,11 +22225,11 @@
     </row>
     <row r="107">
       <c r="C107" s="132" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D107" s="120">
         <f t="shared" si="17"/>
-        <v>2.99</v>
+        <v>1.99</v>
       </c>
       <c r="N107" s="13"/>
       <c r="P107" s="118">
@@ -22235,11 +22244,11 @@
     </row>
     <row r="108">
       <c r="C108" s="132" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D108" s="120">
         <f t="shared" si="17"/>
-        <v>3.01</v>
+        <v>2.01</v>
       </c>
       <c r="N108" s="13"/>
       <c r="P108" s="118">
@@ -22254,11 +22263,11 @@
     </row>
     <row r="109">
       <c r="C109" s="132" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D109" s="120">
         <f t="shared" si="17"/>
-        <v>5.35</v>
+        <v>3.56</v>
       </c>
       <c r="N109" s="13"/>
       <c r="P109" s="118">
@@ -22273,11 +22282,11 @@
     </row>
     <row r="110">
       <c r="C110" s="132" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D110" s="120">
         <f t="shared" si="17"/>
-        <v>2.95</v>
+        <v>1.97</v>
       </c>
       <c r="N110" s="13"/>
       <c r="P110" s="118">
@@ -22292,11 +22301,11 @@
     </row>
     <row r="111">
       <c r="C111" s="132" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D111" s="120">
         <f t="shared" si="17"/>
-        <v>3.07</v>
+        <v>2.93</v>
       </c>
       <c r="N111" s="13"/>
       <c r="P111" s="118">
@@ -22311,11 +22320,11 @@
     </row>
     <row r="112">
       <c r="C112" s="132" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D112" s="120">
         <f t="shared" si="17"/>
-        <v>2.64</v>
+        <v>3.95</v>
       </c>
       <c r="P112" s="118">
         <v>1.0</v>
@@ -22329,11 +22338,11 @@
     </row>
     <row r="113">
       <c r="C113" s="132" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="D113" s="120">
         <f t="shared" si="17"/>
-        <v>3.56</v>
+        <v>3.27</v>
       </c>
       <c r="P113" s="118">
         <v>0.0</v>
@@ -22347,11 +22356,11 @@
     </row>
     <row r="114">
       <c r="C114" s="132" t="s">
-        <v>309</v>
+        <v>207</v>
       </c>
       <c r="D114" s="120">
         <f t="shared" si="17"/>
-        <v>2.93</v>
+        <v>2.71</v>
       </c>
       <c r="P114" s="118">
         <v>1.0</v>
@@ -22365,11 +22374,11 @@
     </row>
     <row r="115">
       <c r="C115" s="132" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D115" s="120">
         <f t="shared" si="17"/>
-        <v>2.24</v>
+        <v>0.36</v>
       </c>
       <c r="P115" s="118">
         <v>1.0</v>
@@ -22383,11 +22392,11 @@
     </row>
     <row r="116">
       <c r="C116" s="132" t="s">
-        <v>228</v>
+        <v>312</v>
       </c>
       <c r="D116" s="120">
         <f t="shared" si="17"/>
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="P116" s="118">
         <v>1.0</v>
@@ -22401,11 +22410,11 @@
     </row>
     <row r="117">
       <c r="C117" s="132" t="s">
-        <v>228</v>
+        <v>311</v>
       </c>
       <c r="D117" s="120">
         <f t="shared" si="17"/>
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="P117" s="141"/>
       <c r="AE117" s="38">
@@ -22417,11 +22426,11 @@
     </row>
     <row r="118">
       <c r="C118" s="132" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D118" s="120">
         <f t="shared" si="17"/>
-        <v>0.32</v>
+        <v>2.07</v>
       </c>
       <c r="P118" s="141"/>
       <c r="AE118" s="38">
@@ -22433,11 +22442,11 @@
     </row>
     <row r="119">
       <c r="C119" s="132" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D119" s="120">
         <f t="shared" si="17"/>
-        <v>1.86</v>
+        <v>2.37</v>
       </c>
       <c r="P119" s="141"/>
       <c r="AE119" s="38">
@@ -22449,11 +22458,11 @@
     </row>
     <row r="120">
       <c r="C120" s="132" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D120" s="120">
         <f t="shared" si="17"/>
-        <v>2.13</v>
+        <v>3.17</v>
       </c>
       <c r="P120" s="141"/>
       <c r="AE120" s="38">
@@ -22465,11 +22474,11 @@
     </row>
     <row r="121">
       <c r="C121" s="132" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D121" s="120">
         <f t="shared" si="17"/>
-        <v>2.85</v>
+        <v>2.07</v>
       </c>
       <c r="P121" s="141"/>
       <c r="AE121" s="38">
@@ -22481,11 +22490,11 @@
     </row>
     <row r="122">
       <c r="C122" s="132" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="D122" s="120">
         <f t="shared" si="17"/>
-        <v>1.86</v>
+        <v>3.47</v>
       </c>
       <c r="P122" s="141"/>
       <c r="AE122" s="38">
@@ -22497,11 +22506,11 @@
     </row>
     <row r="123">
       <c r="C123" s="132" t="s">
-        <v>281</v>
+        <v>317</v>
       </c>
       <c r="D123" s="120">
         <f t="shared" si="17"/>
-        <v>3.1</v>
+        <v>5.77</v>
       </c>
       <c r="P123" s="141"/>
       <c r="AE123" s="38">
@@ -22513,11 +22522,11 @@
     </row>
     <row r="124">
       <c r="C124" s="132" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="D124" s="120">
         <f t="shared" si="17"/>
-        <v>5.2</v>
+        <v>5.87</v>
       </c>
       <c r="P124" s="141"/>
       <c r="AE124" s="38">
@@ -22529,11 +22538,11 @@
     </row>
     <row r="125">
       <c r="C125" s="132" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="D125" s="120">
         <f t="shared" si="17"/>
-        <v>5.28</v>
+        <v>5.49</v>
       </c>
       <c r="P125" s="141"/>
       <c r="AE125" s="38">
@@ -22545,11 +22554,11 @@
     </row>
     <row r="126">
       <c r="C126" s="132" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="D126" s="120">
         <f t="shared" si="17"/>
-        <v>4.94</v>
+        <v>2.24</v>
       </c>
       <c r="P126" s="141"/>
       <c r="AE126" s="38">
@@ -22561,11 +22570,11 @@
     </row>
     <row r="127">
       <c r="C127" s="132" t="s">
-        <v>318</v>
+        <v>282</v>
       </c>
       <c r="D127" s="120">
         <f t="shared" si="17"/>
-        <v>1.96</v>
+        <v>2.33</v>
       </c>
       <c r="P127" s="141"/>
       <c r="AE127" s="38">
@@ -22577,11 +22586,11 @@
     </row>
     <row r="128">
       <c r="C128" s="132" t="s">
-        <v>283</v>
+        <v>234</v>
       </c>
       <c r="D128" s="120">
         <f t="shared" si="17"/>
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="P128" s="141"/>
       <c r="AE128" s="38">
@@ -22593,11 +22602,11 @@
     </row>
     <row r="129">
       <c r="C129" s="132" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="D129" s="120">
         <f t="shared" si="17"/>
-        <v>2.23</v>
+        <v>0.36</v>
       </c>
       <c r="P129" s="141"/>
       <c r="AE129" s="38">
@@ -44975,14 +44984,14 @@
     <row r="1">
       <c r="A1" s="144"/>
       <c r="B1" s="145" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C1" s="146"/>
       <c r="D1" s="146"/>
       <c r="E1" s="146"/>
       <c r="F1" s="146"/>
       <c r="G1" s="147" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H1" s="146"/>
       <c r="I1" s="146"/>
@@ -45016,54 +45025,54 @@
         <v>3</v>
       </c>
       <c r="B2" s="149" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C2" s="150" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D2" s="150" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E2" s="150" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F2" s="151" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G2" s="149">
         <v>1.0</v>
       </c>
       <c r="H2" s="150" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I2" s="150">
         <v>2.0</v>
       </c>
       <c r="J2" s="150" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K2" s="152" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="L2" s="150" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M2" s="153" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N2" s="134" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="O2" s="134" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="P2" s="134" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q2" s="5"/>
       <c r="R2" s="5"/>
       <c r="S2" s="114" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="T2" s="5"/>
       <c r="U2" s="5"/>
@@ -45153,7 +45162,7 @@
       <c r="Q4" s="5"/>
       <c r="R4" s="5"/>
       <c r="S4" s="159" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="T4" s="160"/>
       <c r="Z4" s="48"/>
@@ -45189,7 +45198,7 @@
       <c r="P5" s="162"/>
       <c r="S5" s="160"/>
       <c r="T5" s="163" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="6">
@@ -45222,11 +45231,11 @@
       <c r="R6" s="5"/>
       <c r="S6" s="160"/>
       <c r="T6" s="163" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Z6" s="98"/>
       <c r="AD6" s="38" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="7">
@@ -45256,7 +45265,7 @@
       <c r="O7" s="90"/>
       <c r="P7" s="165"/>
       <c r="AD7" s="163" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AE7" s="160"/>
       <c r="AF7" s="160"/>
@@ -45289,11 +45298,11 @@
       <c r="O8" s="90"/>
       <c r="P8" s="165"/>
       <c r="S8" s="163" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AA8" s="98"/>
       <c r="AD8" s="163" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="9">
@@ -45492,7 +45501,7 @@
       <c r="O15" s="90"/>
       <c r="P15" s="165"/>
       <c r="S15" s="38" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="16">
@@ -45605,7 +45614,7 @@
       <c r="Q19" s="5"/>
       <c r="R19" s="5"/>
       <c r="S19" s="38" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="20">
@@ -45743,7 +45752,7 @@
     </row>
     <row r="24">
       <c r="A24" s="114" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B24" s="169" t="str">
         <f t="shared" ref="B24:F24" si="4">IFERROR(AVERAGE(B3:B22),"")</f>
@@ -45889,7 +45898,7 @@
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
       <c r="G27" s="170" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H27" s="5"/>
       <c r="I27" s="5"/>
@@ -45934,7 +45943,7 @@
         <v>1.0</v>
       </c>
       <c r="H28" s="171" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I28" s="171">
         <v>2.0</v>
@@ -45974,7 +45983,7 @@
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
       <c r="D29" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E29" s="4">
         <f>J29</f>
@@ -45996,10 +46005,10 @@
       </c>
       <c r="K29" s="5"/>
       <c r="L29" s="114" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M29" s="114" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O29" s="4">
         <v>1.0</v>
@@ -46099,7 +46108,7 @@
       </c>
       <c r="R31" s="5"/>
       <c r="S31" s="114" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="T31" s="5"/>
       <c r="U31" s="5"/>
@@ -46161,7 +46170,7 @@
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
       <c r="G33" s="116" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="J33" s="5"/>
       <c r="K33" s="5"/>
@@ -46175,10 +46184,10 @@
       <c r="P33" s="5"/>
       <c r="R33" s="5"/>
       <c r="T33" s="68" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="W33" s="38" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AA33" s="48"/>
       <c r="AD33" s="5"/>
@@ -46197,7 +46206,7 @@
         <v>1.0</v>
       </c>
       <c r="H34" s="174" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I34" s="174">
         <v>2.0</v>
@@ -46221,7 +46230,7 @@
         <v>1626.0</v>
       </c>
       <c r="U34" s="42" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="W34" s="38">
         <v>5193.0</v>
@@ -46266,7 +46275,7 @@
         <v>4176.0</v>
       </c>
       <c r="U35" s="42" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="W35" s="38">
         <v>4863.0</v>
@@ -46364,7 +46373,7 @@
       <c r="D38" s="5"/>
       <c r="E38" s="5"/>
       <c r="F38" s="4" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="G38" s="173">
         <f t="shared" ref="G38:I38" si="8">G30-G35</f>
@@ -46566,7 +46575,7 @@
       <c r="Q45" s="5"/>
       <c r="R45" s="5"/>
       <c r="T45" s="163" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AD45" s="5"/>
       <c r="AE45" s="5"/>
@@ -46703,10 +46712,10 @@
         <v>4</v>
       </c>
       <c r="X49" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Y49" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Z49" s="4" t="s">
         <v>5</v>
@@ -46721,16 +46730,16 @@
         <v>8</v>
       </c>
       <c r="AD49" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="AE49" s="30" t="s">
+        <v>109</v>
+      </c>
+      <c r="AF49" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="AE49" s="30" t="s">
-        <v>108</v>
-      </c>
-      <c r="AF49" s="30" t="s">
-        <v>92</v>
-      </c>
       <c r="AG49" s="30" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="50">
@@ -46895,7 +46904,7 @@
         <v>13.03594852814783</v>
       </c>
       <c r="AG52" s="30" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="53">
@@ -46956,7 +46965,7 @@
         <v>6.291840048860032</v>
       </c>
       <c r="AG53" s="30" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="54">
@@ -47017,7 +47026,7 @@
         <v>2.7243520649411117</v>
       </c>
       <c r="AG54" s="30" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="55">
@@ -47078,7 +47087,7 @@
         <v>2.1429979739456915</v>
       </c>
       <c r="AG55" s="30" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="56">
@@ -47139,7 +47148,7 @@
         <v>3.98032040346951</v>
       </c>
       <c r="AG56" s="30" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="57">
@@ -47362,10 +47371,10 @@
       <c r="R62" s="5"/>
       <c r="S62" s="5"/>
       <c r="U62" s="38" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="V62" s="38" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AC62" s="5"/>
       <c r="AD62" s="5"/>
@@ -47407,7 +47416,7 @@
         <v>2165.0</v>
       </c>
       <c r="W63" s="38" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AC63" s="5"/>
       <c r="AD63" s="5"/>
@@ -48041,7 +48050,7 @@
       <c r="R79" s="5"/>
       <c r="S79" s="5"/>
       <c r="T79" s="114" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="U79" s="5"/>
       <c r="V79" s="5"/>
@@ -48082,7 +48091,7 @@
       <c r="R80" s="5"/>
       <c r="S80" s="5"/>
       <c r="T80" s="38" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="U80" s="13"/>
       <c r="V80" s="13"/>
@@ -80843,146 +80852,146 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="38" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="2">
       <c r="B2" s="5"/>
       <c r="C2" s="182" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E2" s="183"/>
       <c r="F2" s="114" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H2" s="183"/>
     </row>
     <row r="3">
       <c r="B3" s="133" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C3" s="184" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D3" s="133" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E3" s="185" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F3" s="133" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="G3" s="133" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H3" s="133" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="186" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C4" s="187" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D4" s="134" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E4" s="188" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F4" s="189" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="G4" s="189" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H4" s="134"/>
     </row>
     <row r="5">
       <c r="B5" s="186" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C5" s="190" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D5" s="144"/>
       <c r="E5" s="188" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F5" s="191" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="G5" s="192" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H5" s="134"/>
     </row>
     <row r="6">
       <c r="B6" s="186" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C6" s="187" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D6" s="134" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E6" s="188" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F6" s="134" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G6" s="134"/>
       <c r="H6" s="134"/>
     </row>
     <row r="7">
       <c r="B7" s="134" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C7" s="193" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D7" s="134"/>
       <c r="E7" s="194" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F7" s="187" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="G7" s="134"/>
       <c r="H7" s="134" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="195" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C8" s="196" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D8" s="197"/>
       <c r="E8" s="195" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F8" s="198" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="G8" s="199" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H8" s="197"/>
     </row>
     <row r="9">
       <c r="B9" s="14" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C9" s="200" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="D9" s="90"/>
       <c r="E9" s="90"/>
@@ -80992,27 +81001,27 @@
     </row>
     <row r="10">
       <c r="B10" s="14" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C10" s="164"/>
       <c r="D10" s="90"/>
       <c r="E10" s="90"/>
       <c r="F10" s="164"/>
       <c r="G10" s="189" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H10" s="90"/>
     </row>
     <row r="11">
       <c r="B11" s="14" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C11" s="164"/>
       <c r="D11" s="90"/>
       <c r="E11" s="90"/>
       <c r="F11" s="164"/>
       <c r="G11" s="201" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H11" s="14"/>
     </row>

--- a/data/df_best_models.xlsx
+++ b/data/df_best_models.xlsx
@@ -516,7 +516,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="869" uniqueCount="445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="886" uniqueCount="461">
   <si>
     <t>id_country</t>
   </si>
@@ -1537,25 +1537,25 @@
     <t>1.39</t>
   </si>
   <si>
-    <t>0.30</t>
+    <t>1.50</t>
   </si>
   <si>
-    <t>3.88</t>
+    <t>0.46</t>
   </si>
   <si>
-    <t>2.68</t>
+    <t>0.84</t>
   </si>
   <si>
-    <t>10.34</t>
+    <t>2.83</t>
   </si>
   <si>
-    <t>3.34</t>
+    <t>1.52</t>
   </si>
   <si>
-    <t>2.81</t>
+    <t>1.94</t>
   </si>
   <si>
-    <t>0.33</t>
+    <t>1.91</t>
   </si>
   <si>
     <t>Country</t>
@@ -1564,34 +1564,97 @@
     <t>Correl ROI y Expected ROI</t>
   </si>
   <si>
-    <t>6.28</t>
+    <t>0.24</t>
   </si>
   <si>
-    <t>2.37</t>
+    <t>0.54</t>
   </si>
   <si>
     <t>mean</t>
   </si>
   <si>
-    <t>4.07</t>
+    <t>3.88</t>
   </si>
   <si>
     <t>median</t>
   </si>
   <si>
-    <t>5.16</t>
+    <t>4.22</t>
   </si>
   <si>
     <t>p25</t>
   </si>
   <si>
-    <t>0.39</t>
+    <t>4.62</t>
   </si>
   <si>
     <t>p75</t>
   </si>
   <si>
+    <t>5.77</t>
+  </si>
+  <si>
+    <t>3.56</t>
+  </si>
+  <si>
     <t>3.78</t>
+  </si>
+  <si>
+    <t>5.26</t>
+  </si>
+  <si>
+    <t>5.86</t>
+  </si>
+  <si>
+    <t>4.45</t>
+  </si>
+  <si>
+    <t>6.81</t>
+  </si>
+  <si>
+    <t>Gracias a las nuevas métricas de G/P sin bank en test, me di cuenta de que:</t>
+  </si>
+  <si>
+    <t>1.35</t>
+  </si>
+  <si>
+    <t>La rentabilidad en ITA está en el visitante y no en el empate como creía.</t>
+  </si>
+  <si>
+    <t>1.69</t>
+  </si>
+  <si>
+    <t>La rentabilidad en ENG y GER está en el empate tal como creía.</t>
+  </si>
+  <si>
+    <t>0.86</t>
+  </si>
+  <si>
+    <t>En SPA esta repartido aunque Empate saca una ventaja.</t>
+  </si>
+  <si>
+    <t>1.24</t>
+  </si>
+  <si>
+    <t>En FRA, depende el modelo. A veces local, a veces, empate.</t>
+  </si>
+  <si>
+    <t>2.38</t>
+  </si>
+  <si>
+    <t>Si en FRA empate no rinde, no tiene sentido exigirle una buena distrib en empate… → Tiene sentido pero al parecer si importa el empate puesto que el modelo que gana se basa en empate.</t>
+  </si>
+  <si>
+    <t>1.73</t>
+  </si>
+  <si>
+    <t>3.92</t>
+  </si>
+  <si>
+    <t>4.91</t>
+  </si>
+  <si>
+    <t>1.96</t>
   </si>
   <si>
     <t>2.94</t>
@@ -1612,31 +1675,16 @@
     <t>7.02</t>
   </si>
   <si>
-    <t>Gracias a las nuevas métricas de G/P sin bank en test, me di cuenta de que:</t>
-  </si>
-  <si>
     <t>9.13</t>
-  </si>
-  <si>
-    <t>La rentabilidad en ITA está en el visitante y no en el empate como creía.</t>
   </si>
   <si>
     <t>3.00</t>
   </si>
   <si>
-    <t>La rentabilidad en ENG y GER está en el empate tal como creía.</t>
-  </si>
-  <si>
-    <t>En SPA esta repartido aunque Empate saca una ventaja.</t>
-  </si>
-  <si>
     <t>1.90</t>
   </si>
   <si>
-    <t>En FRA, depende el modelo. A veces local, a veces, empate.</t>
-  </si>
-  <si>
-    <t>Si en FRA empate no rinde, no tiene sentido exigirle una buena distrib en empate… → Tiene sentido pero al parecer si importa el empate puesto que el modelo que gana se basa en empate.</t>
+    <t>0.39</t>
   </si>
   <si>
     <t>5.85</t>
@@ -1645,7 +1693,7 @@
     <t>5.70</t>
   </si>
   <si>
-    <t>0.63</t>
+    <t>3.14</t>
   </si>
   <si>
     <t>5.67</t>
@@ -1654,28 +1702,28 @@
     <t>3.55</t>
   </si>
   <si>
-    <t>3.11</t>
+    <t>2.42</t>
   </si>
   <si>
-    <t>3.05</t>
+    <t>2.64</t>
   </si>
   <si>
-    <t>5.86</t>
+    <t>3.50</t>
   </si>
   <si>
-    <t>0.37</t>
+    <t>1.99</t>
   </si>
   <si>
-    <t>2.57</t>
+    <t>2.27</t>
   </si>
   <si>
-    <t>2.28</t>
+    <t>2.55</t>
   </si>
   <si>
-    <t>2.02</t>
+    <t>1.81</t>
   </si>
   <si>
-    <t>2.22</t>
+    <t>2.16</t>
   </si>
   <si>
     <t>RENTABILIDAD</t>
@@ -3528,7 +3576,7 @@
         <v>45739.0</v>
       </c>
       <c r="D4" s="14">
-        <v>1071.0</v>
+        <v>458.0</v>
       </c>
       <c r="E4" s="14" t="s">
         <v>17</v>
@@ -3537,14 +3585,14 @@
         <v>5.0</v>
       </c>
       <c r="G4" s="24">
-        <v>9.74</v>
+        <v>12.8</v>
       </c>
       <c r="H4" s="24">
-        <v>9.74</v>
+        <v>10.79</v>
       </c>
       <c r="I4" s="24">
         <f t="shared" ref="I4:I8" si="1">AVERAGE(F4:H4)</f>
-        <v>8.16</v>
+        <v>9.53</v>
       </c>
       <c r="J4" s="25">
         <v>5.0</v>
@@ -8759,7 +8807,7 @@
     </row>
   </sheetData>
   <autoFilter ref="$A$1:$P$8"/>
-  <conditionalFormatting sqref="F4:I8">
+  <conditionalFormatting sqref="F4:H8">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -8802,146 +8850,146 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="76" t="s">
-        <v>378</v>
+        <v>394</v>
       </c>
     </row>
     <row r="2">
       <c r="B2" s="17"/>
       <c r="C2" s="5" t="s">
-        <v>379</v>
+        <v>395</v>
       </c>
       <c r="E2" s="235"/>
       <c r="F2" s="6" t="s">
-        <v>380</v>
+        <v>396</v>
       </c>
       <c r="H2" s="235"/>
     </row>
     <row r="3">
       <c r="B3" s="186" t="s">
-        <v>381</v>
+        <v>397</v>
       </c>
       <c r="C3" s="236" t="s">
-        <v>382</v>
+        <v>398</v>
       </c>
       <c r="D3" s="186" t="s">
-        <v>383</v>
+        <v>399</v>
       </c>
       <c r="E3" s="237" t="s">
         <v>212</v>
       </c>
       <c r="F3" s="186" t="s">
-        <v>384</v>
+        <v>400</v>
       </c>
       <c r="G3" s="186" t="s">
-        <v>385</v>
+        <v>401</v>
       </c>
       <c r="H3" s="186" t="s">
-        <v>386</v>
+        <v>402</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="238" t="s">
-        <v>387</v>
+        <v>403</v>
       </c>
       <c r="C4" s="239" t="s">
-        <v>388</v>
+        <v>404</v>
       </c>
       <c r="D4" s="187" t="s">
-        <v>389</v>
+        <v>405</v>
       </c>
       <c r="E4" s="240" t="s">
-        <v>390</v>
+        <v>406</v>
       </c>
       <c r="F4" s="241" t="s">
-        <v>391</v>
+        <v>407</v>
       </c>
       <c r="G4" s="241" t="s">
-        <v>392</v>
+        <v>408</v>
       </c>
       <c r="H4" s="187"/>
     </row>
     <row r="5">
       <c r="B5" s="238" t="s">
-        <v>393</v>
+        <v>409</v>
       </c>
       <c r="C5" s="242" t="s">
-        <v>394</v>
+        <v>410</v>
       </c>
       <c r="D5" s="197"/>
       <c r="E5" s="240" t="s">
-        <v>390</v>
+        <v>406</v>
       </c>
       <c r="F5" s="243" t="s">
-        <v>395</v>
+        <v>411</v>
       </c>
       <c r="G5" s="244" t="s">
-        <v>396</v>
+        <v>412</v>
       </c>
       <c r="H5" s="187"/>
     </row>
     <row r="6">
       <c r="B6" s="238" t="s">
-        <v>397</v>
+        <v>413</v>
       </c>
       <c r="C6" s="239" t="s">
-        <v>388</v>
+        <v>404</v>
       </c>
       <c r="D6" s="187" t="s">
-        <v>398</v>
+        <v>414</v>
       </c>
       <c r="E6" s="240" t="s">
-        <v>390</v>
+        <v>406</v>
       </c>
       <c r="F6" s="187" t="s">
-        <v>375</v>
+        <v>391</v>
       </c>
       <c r="G6" s="187"/>
       <c r="H6" s="187"/>
     </row>
     <row r="7">
       <c r="B7" s="187" t="s">
-        <v>399</v>
+        <v>415</v>
       </c>
       <c r="C7" s="245" t="s">
-        <v>400</v>
+        <v>416</v>
       </c>
       <c r="D7" s="187"/>
       <c r="E7" s="246" t="s">
-        <v>401</v>
+        <v>417</v>
       </c>
       <c r="F7" s="239" t="s">
-        <v>402</v>
+        <v>418</v>
       </c>
       <c r="G7" s="187"/>
       <c r="H7" s="187" t="s">
-        <v>403</v>
+        <v>419</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="247" t="s">
-        <v>404</v>
+        <v>420</v>
       </c>
       <c r="C8" s="248" t="s">
-        <v>405</v>
+        <v>421</v>
       </c>
       <c r="D8" s="249"/>
       <c r="E8" s="247" t="s">
-        <v>406</v>
+        <v>422</v>
       </c>
       <c r="F8" s="250" t="s">
-        <v>407</v>
+        <v>423</v>
       </c>
       <c r="G8" s="251" t="s">
-        <v>408</v>
+        <v>424</v>
       </c>
       <c r="H8" s="249"/>
     </row>
     <row r="9">
       <c r="B9" s="20" t="s">
-        <v>409</v>
+        <v>425</v>
       </c>
       <c r="C9" s="252" t="s">
-        <v>405</v>
+        <v>421</v>
       </c>
       <c r="D9" s="143"/>
       <c r="E9" s="143"/>
@@ -8951,27 +8999,27 @@
     </row>
     <row r="10">
       <c r="B10" s="20" t="s">
-        <v>410</v>
+        <v>426</v>
       </c>
       <c r="C10" s="217"/>
       <c r="D10" s="143"/>
       <c r="E10" s="143"/>
       <c r="F10" s="217"/>
       <c r="G10" s="241" t="s">
-        <v>392</v>
+        <v>408</v>
       </c>
       <c r="H10" s="143"/>
     </row>
     <row r="11">
       <c r="B11" s="20" t="s">
-        <v>411</v>
+        <v>427</v>
       </c>
       <c r="C11" s="217"/>
       <c r="D11" s="143"/>
       <c r="E11" s="143"/>
       <c r="F11" s="217"/>
       <c r="G11" s="253" t="s">
-        <v>412</v>
+        <v>428</v>
       </c>
       <c r="H11" s="20"/>
     </row>
@@ -8994,7 +9042,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="90" t="s">
-        <v>413</v>
+        <v>429</v>
       </c>
       <c r="L1" s="32"/>
     </row>
@@ -9003,16 +9051,16 @@
     </row>
     <row r="3">
       <c r="A3" s="76" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
       <c r="L3" s="32"/>
     </row>
     <row r="4">
       <c r="B4" s="76" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
       <c r="G4" s="76" t="s">
-        <v>416</v>
+        <v>432</v>
       </c>
       <c r="L4" s="32"/>
     </row>
@@ -9118,45 +9166,45 @@
     </row>
     <row r="11">
       <c r="A11" s="254" t="s">
-        <v>417</v>
+        <v>433</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="90" t="s">
-        <v>418</v>
+        <v>434</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="76" t="s">
-        <v>419</v>
+        <v>435</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="254" t="s">
-        <v>420</v>
+        <v>436</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="90" t="s">
-        <v>421</v>
+        <v>437</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="76" t="s">
-        <v>422</v>
+        <v>438</v>
       </c>
       <c r="F19" s="151"/>
     </row>
     <row r="20">
       <c r="B20" s="90" t="s">
-        <v>423</v>
+        <v>439</v>
       </c>
       <c r="C20" s="105"/>
       <c r="D20" s="105"/>
       <c r="E20" s="105"/>
       <c r="F20" s="105"/>
       <c r="G20" s="90" t="s">
-        <v>424</v>
+        <v>440</v>
       </c>
       <c r="H20" s="90" t="s">
         <v>65</v>
@@ -9173,7 +9221,7 @@
     </row>
     <row r="21">
       <c r="B21" s="90" t="s">
-        <v>425</v>
+        <v>441</v>
       </c>
       <c r="G21" s="107">
         <v>2.575</v>
@@ -9181,27 +9229,27 @@
     </row>
     <row r="23">
       <c r="K23" s="90" t="s">
-        <v>426</v>
+        <v>442</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="76" t="s">
-        <v>427</v>
+        <v>443</v>
       </c>
       <c r="H24" s="76" t="s">
         <v>43</v>
       </c>
       <c r="I24" s="76" t="s">
-        <v>428</v>
+        <v>444</v>
       </c>
       <c r="K24" s="76" t="s">
-        <v>429</v>
+        <v>445</v>
       </c>
       <c r="L24" s="76" t="s">
-        <v>430</v>
+        <v>446</v>
       </c>
       <c r="M24" s="76" t="s">
-        <v>431</v>
+        <v>447</v>
       </c>
     </row>
     <row r="25">
@@ -9220,7 +9268,7 @@
         <v>#REF!</v>
       </c>
       <c r="K25" s="76" t="s">
-        <v>432</v>
+        <v>448</v>
       </c>
     </row>
     <row r="26">
@@ -9231,7 +9279,7 @@
         <v>1.19</v>
       </c>
       <c r="K26" s="76" t="s">
-        <v>433</v>
+        <v>449</v>
       </c>
     </row>
     <row r="27">
@@ -9242,7 +9290,7 @@
         <v>2.19</v>
       </c>
       <c r="K27" s="76" t="s">
-        <v>434</v>
+        <v>450</v>
       </c>
     </row>
     <row r="28">
@@ -9253,7 +9301,7 @@
         <v>0.05</v>
       </c>
       <c r="K28" s="76" t="s">
-        <v>435</v>
+        <v>451</v>
       </c>
     </row>
     <row r="29">
@@ -9272,7 +9320,7 @@
         <v>6.42</v>
       </c>
       <c r="K30" s="93" t="s">
-        <v>436</v>
+        <v>452</v>
       </c>
     </row>
     <row r="31">
@@ -9417,7 +9465,7 @@
         <v>0.61</v>
       </c>
       <c r="K41" s="90" t="s">
-        <v>437</v>
+        <v>453</v>
       </c>
     </row>
     <row r="42">
@@ -9428,13 +9476,13 @@
         <v>0.69</v>
       </c>
       <c r="K42" s="76" t="s">
-        <v>429</v>
+        <v>445</v>
       </c>
       <c r="L42" s="76" t="s">
-        <v>430</v>
+        <v>446</v>
       </c>
       <c r="M42" s="76" t="s">
-        <v>431</v>
+        <v>447</v>
       </c>
     </row>
     <row r="43">
@@ -9566,7 +9614,7 @@
         <v>0.0</v>
       </c>
       <c r="K51" s="76" t="s">
-        <v>438</v>
+        <v>454</v>
       </c>
     </row>
     <row r="52">
@@ -9594,17 +9642,17 @@
       </c>
       <c r="K54" s="143"/>
       <c r="L54" s="255" t="s">
-        <v>439</v>
+        <v>455</v>
       </c>
       <c r="M54" s="256"/>
       <c r="N54" s="148" t="s">
         <v>155</v>
       </c>
       <c r="O54" s="148" t="s">
-        <v>440</v>
+        <v>456</v>
       </c>
       <c r="P54" s="148" t="s">
-        <v>441</v>
+        <v>457</v>
       </c>
       <c r="R54" s="79" t="s">
         <v>222</v>
@@ -9686,7 +9734,7 @@
         <v>5.86</v>
       </c>
       <c r="R57" s="76" t="s">
-        <v>442</v>
+        <v>458</v>
       </c>
       <c r="S57" s="107">
         <f>SUM(P55:P74)</f>
@@ -9715,7 +9763,7 @@
         <v>0.855</v>
       </c>
       <c r="P58" s="20" t="s">
-        <v>443</v>
+        <v>459</v>
       </c>
     </row>
     <row r="59">
@@ -9762,7 +9810,7 @@
         <v>0.96</v>
       </c>
       <c r="P60" s="20" t="s">
-        <v>444</v>
+        <v>460</v>
       </c>
     </row>
     <row r="61">
@@ -24468,7 +24516,7 @@
       <c r="C37" s="105"/>
       <c r="D37" s="181">
         <f>AVERAGE(D39:D1775)</f>
-        <v>3.356097561</v>
+        <v>3.140689655</v>
       </c>
       <c r="G37" s="90" t="s">
         <v>34</v>
@@ -24575,7 +24623,7 @@
       </c>
       <c r="D40" s="172">
         <f t="shared" si="17"/>
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="G40" s="90" t="s">
         <v>38</v>
@@ -24613,7 +24661,7 @@
       </c>
       <c r="D41" s="172">
         <f t="shared" si="17"/>
-        <v>3.88</v>
+        <v>0.46</v>
       </c>
       <c r="P41" s="170">
         <v>0.0</v>
@@ -24645,7 +24693,7 @@
       </c>
       <c r="D42" s="172">
         <f t="shared" si="17"/>
-        <v>2.68</v>
+        <v>0.84</v>
       </c>
       <c r="P42" s="170">
         <v>2.0</v>
@@ -24677,7 +24725,7 @@
       </c>
       <c r="D43" s="172">
         <f t="shared" si="17"/>
-        <v>10.34</v>
+        <v>2.83</v>
       </c>
       <c r="P43" s="170">
         <v>1.0</v>
@@ -24709,7 +24757,7 @@
       </c>
       <c r="D44" s="172">
         <f t="shared" si="17"/>
-        <v>3.34</v>
+        <v>1.52</v>
       </c>
       <c r="P44" s="170">
         <v>2.0</v>
@@ -24739,7 +24787,7 @@
       </c>
       <c r="D45" s="172">
         <f t="shared" si="17"/>
-        <v>2.81</v>
+        <v>1.94</v>
       </c>
       <c r="P45" s="170">
         <v>1.0</v>
@@ -24757,7 +24805,7 @@
       </c>
       <c r="D46" s="172">
         <f t="shared" si="17"/>
-        <v>0.33</v>
+        <v>1.91</v>
       </c>
       <c r="G46" s="186" t="s">
         <v>297</v>
@@ -24781,7 +24829,7 @@
       </c>
       <c r="D47" s="172">
         <f t="shared" si="17"/>
-        <v>6.28</v>
+        <v>0.24</v>
       </c>
       <c r="G47" s="187" t="s">
         <v>33</v>
@@ -24811,7 +24859,7 @@
       </c>
       <c r="D48" s="172">
         <f t="shared" si="17"/>
-        <v>2.37</v>
+        <v>0.54</v>
       </c>
       <c r="G48" s="187" t="s">
         <v>34</v>
@@ -24848,7 +24896,7 @@
       </c>
       <c r="D49" s="172">
         <f t="shared" si="17"/>
-        <v>4.07</v>
+        <v>3.88</v>
       </c>
       <c r="G49" s="187" t="s">
         <v>36</v>
@@ -24885,7 +24933,7 @@
       </c>
       <c r="D50" s="172">
         <f t="shared" si="17"/>
-        <v>5.16</v>
+        <v>4.22</v>
       </c>
       <c r="G50" s="187" t="s">
         <v>37</v>
@@ -24922,7 +24970,7 @@
       </c>
       <c r="D51" s="172">
         <f t="shared" si="17"/>
-        <v>0.39</v>
+        <v>4.62</v>
       </c>
       <c r="G51" s="187" t="s">
         <v>38</v>
@@ -24959,7 +25007,7 @@
       </c>
       <c r="D52" s="172">
         <f t="shared" si="17"/>
-        <v>3.78</v>
+        <v>5.77</v>
       </c>
       <c r="P52" s="170">
         <v>0.0</v>
@@ -24983,7 +25031,7 @@
       </c>
       <c r="D53" s="172">
         <f t="shared" si="17"/>
-        <v>2.94</v>
+        <v>3.56</v>
       </c>
       <c r="P53" s="170">
         <v>0.0</v>
@@ -25007,7 +25055,7 @@
       </c>
       <c r="D54" s="172">
         <f t="shared" si="17"/>
-        <v>2.59</v>
+        <v>3.78</v>
       </c>
       <c r="P54" s="170">
         <v>2.0</v>
@@ -25031,7 +25079,7 @@
       </c>
       <c r="D55" s="172">
         <f t="shared" si="17"/>
-        <v>2.18</v>
+        <v>5.26</v>
       </c>
       <c r="P55" s="170">
         <v>0.0</v>
@@ -25055,7 +25103,7 @@
       </c>
       <c r="D56" s="172">
         <f t="shared" si="17"/>
-        <v>2.03</v>
+        <v>5.86</v>
       </c>
       <c r="P56" s="170">
         <v>0.0</v>
@@ -25079,7 +25127,7 @@
       </c>
       <c r="D57" s="172">
         <f t="shared" si="17"/>
-        <v>3.85</v>
+        <v>4.45</v>
       </c>
       <c r="P57" s="170">
         <v>2.0</v>
@@ -25103,7 +25151,7 @@
       </c>
       <c r="D58" s="172">
         <f t="shared" si="17"/>
-        <v>7.02</v>
+        <v>6.81</v>
       </c>
       <c r="G58" s="189" t="s">
         <v>315</v>
@@ -25131,7 +25179,7 @@
       </c>
       <c r="D59" s="172">
         <f t="shared" si="17"/>
-        <v>9.13</v>
+        <v>1.35</v>
       </c>
       <c r="G59" s="190"/>
       <c r="H59" s="191" t="s">
@@ -25159,7 +25207,7 @@
       </c>
       <c r="D60" s="172">
         <f t="shared" si="17"/>
-        <v>3</v>
+        <v>1.69</v>
       </c>
       <c r="G60" s="190"/>
       <c r="H60" s="191" t="s">
@@ -25183,15 +25231,15 @@
     </row>
     <row r="61">
       <c r="C61" s="185" t="s">
-        <v>269</v>
+        <v>320</v>
       </c>
       <c r="D61" s="172">
         <f t="shared" si="17"/>
-        <v>2.71</v>
+        <v>0.86</v>
       </c>
       <c r="G61" s="190"/>
       <c r="H61" s="191" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P61" s="170">
         <v>2.0</v>
@@ -25211,15 +25259,15 @@
     </row>
     <row r="62">
       <c r="C62" s="185" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D62" s="172">
         <f t="shared" si="17"/>
-        <v>1.9</v>
+        <v>1.24</v>
       </c>
       <c r="G62" s="190"/>
       <c r="H62" s="191" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="P62" s="170">
         <v>1.0</v>
@@ -25239,15 +25287,15 @@
     </row>
     <row r="63">
       <c r="C63" s="185" t="s">
-        <v>306</v>
+        <v>324</v>
       </c>
       <c r="D63" s="172">
         <f t="shared" si="17"/>
-        <v>0.39</v>
+        <v>2.38</v>
       </c>
       <c r="G63" s="190"/>
       <c r="H63" s="191" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="P63" s="170">
         <v>0.0</v>
@@ -25261,11 +25309,11 @@
     </row>
     <row r="64">
       <c r="C64" s="185" t="s">
-        <v>241</v>
+        <v>326</v>
       </c>
       <c r="D64" s="172">
         <f t="shared" si="17"/>
-        <v>5.8</v>
+        <v>1.73</v>
       </c>
       <c r="P64" s="170">
         <v>1.0</v>
@@ -25279,11 +25327,11 @@
     </row>
     <row r="65">
       <c r="C65" s="185" t="s">
-        <v>324</v>
+        <v>253</v>
       </c>
       <c r="D65" s="172">
         <f t="shared" si="17"/>
-        <v>5.85</v>
+        <v>3.83</v>
       </c>
       <c r="P65" s="170">
         <v>2.0</v>
@@ -25297,11 +25345,11 @@
     </row>
     <row r="66">
       <c r="C66" s="185" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D66" s="172">
         <f t="shared" si="17"/>
-        <v>5.7</v>
+        <v>3.92</v>
       </c>
       <c r="P66" s="170">
         <v>0.0</v>
@@ -25315,11 +25363,11 @@
     </row>
     <row r="67">
       <c r="C67" s="185" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D67" s="172">
         <f t="shared" si="17"/>
-        <v>0.63</v>
+        <v>4.91</v>
       </c>
       <c r="P67" s="170">
         <v>0.0</v>
@@ -25333,11 +25381,11 @@
     </row>
     <row r="68">
       <c r="C68" s="185" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D68" s="172">
         <f t="shared" si="17"/>
-        <v>5.67</v>
+        <v>1.96</v>
       </c>
       <c r="P68" s="170">
         <v>1.0</v>
@@ -25351,11 +25399,11 @@
     </row>
     <row r="69">
       <c r="C69" s="185" t="s">
-        <v>328</v>
+        <v>310</v>
       </c>
       <c r="D69" s="172">
         <f t="shared" si="17"/>
-        <v>3.55</v>
+        <v>3.78</v>
       </c>
       <c r="P69" s="170">
         <v>2.0</v>
@@ -25369,11 +25417,11 @@
     </row>
     <row r="70">
       <c r="C70" s="185" t="s">
-        <v>312</v>
+        <v>330</v>
       </c>
       <c r="D70" s="172">
         <f t="shared" si="17"/>
-        <v>2.03</v>
+        <v>2.94</v>
       </c>
       <c r="P70" s="170">
         <v>1.0</v>
@@ -25387,11 +25435,11 @@
     </row>
     <row r="71">
       <c r="C71" s="185" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D71" s="172">
         <f t="shared" si="17"/>
-        <v>3.11</v>
+        <v>2.59</v>
       </c>
       <c r="F71" s="192"/>
       <c r="P71" s="170">
@@ -25406,11 +25454,11 @@
     </row>
     <row r="72">
       <c r="C72" s="185" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D72" s="172">
         <f t="shared" si="17"/>
-        <v>3.05</v>
+        <v>2.18</v>
       </c>
       <c r="P72" s="170">
         <v>0.0</v>
@@ -25424,11 +25472,11 @@
     </row>
     <row r="73">
       <c r="C73" s="185" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D73" s="172">
         <f t="shared" si="17"/>
-        <v>5.86</v>
+        <v>2.03</v>
       </c>
       <c r="P73" s="170">
         <v>1.0</v>
@@ -25442,11 +25490,11 @@
     </row>
     <row r="74">
       <c r="C74" s="185" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D74" s="172">
         <f t="shared" si="17"/>
-        <v>0.37</v>
+        <v>3.85</v>
       </c>
       <c r="P74" s="170">
         <v>0.0</v>
@@ -25460,11 +25508,11 @@
     </row>
     <row r="75">
       <c r="C75" s="185" t="s">
-        <v>312</v>
+        <v>335</v>
       </c>
       <c r="D75" s="172">
         <f t="shared" si="17"/>
-        <v>2.03</v>
+        <v>7.02</v>
       </c>
       <c r="P75" s="170">
         <v>1.0</v>
@@ -25478,11 +25526,11 @@
     </row>
     <row r="76">
       <c r="C76" s="185" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="D76" s="172">
         <f t="shared" si="17"/>
-        <v>2.57</v>
+        <v>9.13</v>
       </c>
       <c r="P76" s="170">
         <v>0.0</v>
@@ -25496,11 +25544,11 @@
     </row>
     <row r="77">
       <c r="C77" s="185" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="D77" s="172">
         <f t="shared" si="17"/>
-        <v>2.28</v>
+        <v>3</v>
       </c>
       <c r="P77" s="170">
         <v>0.0</v>
@@ -25514,11 +25562,11 @@
     </row>
     <row r="78">
       <c r="C78" s="185" t="s">
-        <v>335</v>
+        <v>269</v>
       </c>
       <c r="D78" s="172">
         <f t="shared" si="17"/>
-        <v>2.02</v>
+        <v>2.71</v>
       </c>
       <c r="P78" s="170">
         <v>1.0</v>
@@ -25532,11 +25580,11 @@
     </row>
     <row r="79">
       <c r="C79" s="185" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D79" s="172">
         <f t="shared" si="17"/>
-        <v>2.22</v>
+        <v>1.9</v>
       </c>
       <c r="P79" s="170">
         <v>2.0</v>
@@ -25549,10 +25597,12 @@
       </c>
     </row>
     <row r="80">
-      <c r="C80" s="185"/>
-      <c r="D80" s="172" t="str">
+      <c r="C80" s="185" t="s">
+        <v>339</v>
+      </c>
+      <c r="D80" s="172">
         <f t="shared" si="17"/>
-        <v/>
+        <v>0.39</v>
       </c>
       <c r="P80" s="170">
         <v>1.0</v>
@@ -25565,10 +25615,12 @@
       </c>
     </row>
     <row r="81">
-      <c r="C81" s="185"/>
-      <c r="D81" s="172" t="str">
+      <c r="C81" s="185" t="s">
+        <v>241</v>
+      </c>
+      <c r="D81" s="172">
         <f t="shared" si="17"/>
-        <v/>
+        <v>5.8</v>
       </c>
       <c r="P81" s="170">
         <v>2.0</v>
@@ -25581,10 +25633,12 @@
       </c>
     </row>
     <row r="82">
-      <c r="C82" s="185"/>
-      <c r="D82" s="172" t="str">
+      <c r="C82" s="185" t="s">
+        <v>340</v>
+      </c>
+      <c r="D82" s="172">
         <f t="shared" si="17"/>
-        <v/>
+        <v>5.85</v>
       </c>
       <c r="P82" s="170">
         <v>1.0</v>
@@ -25597,10 +25651,12 @@
       </c>
     </row>
     <row r="83">
-      <c r="C83" s="185"/>
-      <c r="D83" s="172" t="str">
+      <c r="C83" s="185" t="s">
+        <v>341</v>
+      </c>
+      <c r="D83" s="172">
         <f t="shared" si="17"/>
-        <v/>
+        <v>5.7</v>
       </c>
       <c r="P83" s="170">
         <v>0.0</v>
@@ -25613,10 +25669,12 @@
       </c>
     </row>
     <row r="84">
-      <c r="C84" s="185"/>
-      <c r="D84" s="172" t="str">
+      <c r="C84" s="185" t="s">
+        <v>342</v>
+      </c>
+      <c r="D84" s="172">
         <f t="shared" si="17"/>
-        <v/>
+        <v>3.14</v>
       </c>
       <c r="P84" s="170">
         <v>1.0</v>
@@ -25629,10 +25687,12 @@
       </c>
     </row>
     <row r="85">
-      <c r="C85" s="185"/>
-      <c r="D85" s="172" t="str">
+      <c r="C85" s="185" t="s">
+        <v>343</v>
+      </c>
+      <c r="D85" s="172">
         <f t="shared" si="17"/>
-        <v/>
+        <v>5.67</v>
       </c>
       <c r="P85" s="170">
         <v>0.0</v>
@@ -25645,10 +25705,12 @@
       </c>
     </row>
     <row r="86">
-      <c r="C86" s="185"/>
-      <c r="D86" s="172" t="str">
+      <c r="C86" s="185" t="s">
+        <v>344</v>
+      </c>
+      <c r="D86" s="172">
         <f t="shared" si="17"/>
-        <v/>
+        <v>3.55</v>
       </c>
       <c r="P86" s="170">
         <v>0.0</v>
@@ -25661,10 +25723,12 @@
       </c>
     </row>
     <row r="87">
-      <c r="C87" s="185"/>
-      <c r="D87" s="172" t="str">
+      <c r="C87" s="185" t="s">
+        <v>345</v>
+      </c>
+      <c r="D87" s="172">
         <f t="shared" si="17"/>
-        <v/>
+        <v>2.42</v>
       </c>
       <c r="P87" s="170">
         <v>1.0</v>
@@ -25677,10 +25741,12 @@
       </c>
     </row>
     <row r="88">
-      <c r="C88" s="185"/>
-      <c r="D88" s="172" t="str">
+      <c r="C88" s="185" t="s">
+        <v>346</v>
+      </c>
+      <c r="D88" s="172">
         <f t="shared" si="17"/>
-        <v/>
+        <v>2.64</v>
       </c>
       <c r="P88" s="170">
         <v>2.0</v>
@@ -25693,10 +25759,12 @@
       </c>
     </row>
     <row r="89">
-      <c r="C89" s="185"/>
-      <c r="D89" s="172" t="str">
+      <c r="C89" s="185" t="s">
+        <v>347</v>
+      </c>
+      <c r="D89" s="172">
         <f t="shared" si="17"/>
-        <v/>
+        <v>3.5</v>
       </c>
       <c r="P89" s="170">
         <v>2.0</v>
@@ -25709,10 +25777,12 @@
       </c>
     </row>
     <row r="90">
-      <c r="C90" s="185"/>
-      <c r="D90" s="172" t="str">
+      <c r="C90" s="185" t="s">
+        <v>257</v>
+      </c>
+      <c r="D90" s="172">
         <f t="shared" si="17"/>
-        <v/>
+        <v>3.63</v>
       </c>
       <c r="P90" s="170">
         <v>1.0</v>
@@ -25725,10 +25795,12 @@
       </c>
     </row>
     <row r="91">
-      <c r="C91" s="185"/>
-      <c r="D91" s="172" t="str">
+      <c r="C91" s="185" t="s">
+        <v>348</v>
+      </c>
+      <c r="D91" s="172">
         <f t="shared" si="17"/>
-        <v/>
+        <v>1.99</v>
       </c>
       <c r="P91" s="170">
         <v>1.0</v>
@@ -25741,10 +25813,12 @@
       </c>
     </row>
     <row r="92">
-      <c r="C92" s="185"/>
-      <c r="D92" s="172" t="str">
+      <c r="C92" s="185" t="s">
+        <v>349</v>
+      </c>
+      <c r="D92" s="172">
         <f t="shared" si="17"/>
-        <v/>
+        <v>2.27</v>
       </c>
       <c r="P92" s="170">
         <v>2.0</v>
@@ -25757,10 +25831,12 @@
       </c>
     </row>
     <row r="93">
-      <c r="C93" s="185"/>
-      <c r="D93" s="172" t="str">
+      <c r="C93" s="185" t="s">
+        <v>269</v>
+      </c>
+      <c r="D93" s="172">
         <f t="shared" si="17"/>
-        <v/>
+        <v>2.71</v>
       </c>
       <c r="P93" s="170">
         <v>0.0</v>
@@ -25773,10 +25849,12 @@
       </c>
     </row>
     <row r="94">
-      <c r="C94" s="185"/>
-      <c r="D94" s="172" t="str">
+      <c r="C94" s="185" t="s">
+        <v>350</v>
+      </c>
+      <c r="D94" s="172">
         <f t="shared" si="17"/>
-        <v/>
+        <v>2.55</v>
       </c>
       <c r="P94" s="170">
         <v>0.0</v>
@@ -25789,10 +25867,12 @@
       </c>
     </row>
     <row r="95">
-      <c r="C95" s="185"/>
-      <c r="D95" s="172" t="str">
+      <c r="C95" s="185" t="s">
+        <v>351</v>
+      </c>
+      <c r="D95" s="172">
         <f t="shared" si="17"/>
-        <v/>
+        <v>1.81</v>
       </c>
       <c r="P95" s="170">
         <v>1.0</v>
@@ -25805,10 +25885,12 @@
       </c>
     </row>
     <row r="96">
-      <c r="C96" s="185"/>
-      <c r="D96" s="172" t="str">
+      <c r="C96" s="185" t="s">
+        <v>352</v>
+      </c>
+      <c r="D96" s="172">
         <f t="shared" si="17"/>
-        <v/>
+        <v>2.16</v>
       </c>
       <c r="P96" s="170">
         <v>2.0</v>
@@ -48698,14 +48780,14 @@
     <row r="1">
       <c r="A1" s="197"/>
       <c r="B1" s="198" t="s">
-        <v>337</v>
+        <v>353</v>
       </c>
       <c r="C1" s="199"/>
       <c r="D1" s="199"/>
       <c r="E1" s="199"/>
       <c r="F1" s="199"/>
       <c r="G1" s="200" t="s">
-        <v>338</v>
+        <v>354</v>
       </c>
       <c r="H1" s="199"/>
       <c r="I1" s="199"/>
@@ -48739,19 +48821,19 @@
         <v>3</v>
       </c>
       <c r="B2" s="202" t="s">
-        <v>339</v>
+        <v>355</v>
       </c>
       <c r="C2" s="203" t="s">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="D2" s="203" t="s">
         <v>43</v>
       </c>
       <c r="E2" s="203" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="F2" s="204" t="s">
-        <v>342</v>
+        <v>358</v>
       </c>
       <c r="G2" s="202">
         <v>1.0</v>
@@ -48763,30 +48845,30 @@
         <v>2.0</v>
       </c>
       <c r="J2" s="203" t="s">
-        <v>343</v>
+        <v>359</v>
       </c>
       <c r="K2" s="205" t="s">
-        <v>344</v>
+        <v>360</v>
       </c>
       <c r="L2" s="203" t="s">
-        <v>345</v>
+        <v>361</v>
       </c>
       <c r="M2" s="206" t="s">
-        <v>346</v>
+        <v>362</v>
       </c>
       <c r="N2" s="187" t="s">
-        <v>347</v>
+        <v>363</v>
       </c>
       <c r="O2" s="187" t="s">
-        <v>348</v>
+        <v>364</v>
       </c>
       <c r="P2" s="187" t="s">
-        <v>349</v>
+        <v>365</v>
       </c>
       <c r="Q2" s="17"/>
       <c r="R2" s="17"/>
       <c r="S2" s="6" t="s">
-        <v>350</v>
+        <v>366</v>
       </c>
       <c r="T2" s="17"/>
       <c r="U2" s="17"/>
@@ -48876,7 +48958,7 @@
       <c r="Q4" s="17"/>
       <c r="R4" s="17"/>
       <c r="S4" s="212" t="s">
-        <v>351</v>
+        <v>367</v>
       </c>
       <c r="T4" s="213"/>
       <c r="Z4" s="90"/>
@@ -48912,7 +48994,7 @@
       <c r="P5" s="215"/>
       <c r="S5" s="213"/>
       <c r="T5" s="216" t="s">
-        <v>352</v>
+        <v>368</v>
       </c>
     </row>
     <row r="6">
@@ -48945,11 +49027,11 @@
       <c r="R6" s="17"/>
       <c r="S6" s="213"/>
       <c r="T6" s="216" t="s">
-        <v>353</v>
+        <v>369</v>
       </c>
       <c r="Z6" s="151"/>
       <c r="AD6" s="76" t="s">
-        <v>354</v>
+        <v>370</v>
       </c>
     </row>
     <row r="7">
@@ -48979,7 +49061,7 @@
       <c r="O7" s="143"/>
       <c r="P7" s="218"/>
       <c r="AD7" s="216" t="s">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="AE7" s="213"/>
       <c r="AF7" s="213"/>
@@ -49012,11 +49094,11 @@
       <c r="O8" s="143"/>
       <c r="P8" s="218"/>
       <c r="S8" s="216" t="s">
-        <v>356</v>
+        <v>372</v>
       </c>
       <c r="AA8" s="151"/>
       <c r="AD8" s="216" t="s">
-        <v>357</v>
+        <v>373</v>
       </c>
     </row>
     <row r="9">
@@ -49215,7 +49297,7 @@
       <c r="O15" s="143"/>
       <c r="P15" s="218"/>
       <c r="S15" s="76" t="s">
-        <v>358</v>
+        <v>374</v>
       </c>
     </row>
     <row r="16">
@@ -49328,7 +49410,7 @@
       <c r="Q19" s="17"/>
       <c r="R19" s="17"/>
       <c r="S19" s="76" t="s">
-        <v>359</v>
+        <v>375</v>
       </c>
     </row>
     <row r="20">
@@ -49612,7 +49694,7 @@
       <c r="E27" s="17"/>
       <c r="F27" s="17"/>
       <c r="G27" s="223" t="s">
-        <v>360</v>
+        <v>376</v>
       </c>
       <c r="H27" s="17"/>
       <c r="I27" s="17"/>
@@ -49697,7 +49779,7 @@
       <c r="B29" s="17"/>
       <c r="C29" s="17"/>
       <c r="D29" s="4" t="s">
-        <v>361</v>
+        <v>377</v>
       </c>
       <c r="E29" s="4">
         <f>J29</f>
@@ -49719,10 +49801,10 @@
       </c>
       <c r="K29" s="17"/>
       <c r="L29" s="6" t="s">
-        <v>362</v>
+        <v>378</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>363</v>
+        <v>379</v>
       </c>
       <c r="O29" s="4">
         <v>1.0</v>
@@ -49822,7 +49904,7 @@
       </c>
       <c r="R31" s="17"/>
       <c r="S31" s="6" t="s">
-        <v>364</v>
+        <v>380</v>
       </c>
       <c r="T31" s="17"/>
       <c r="U31" s="17"/>
@@ -49884,7 +49966,7 @@
       <c r="E33" s="17"/>
       <c r="F33" s="17"/>
       <c r="G33" s="168" t="s">
-        <v>365</v>
+        <v>381</v>
       </c>
       <c r="J33" s="17"/>
       <c r="K33" s="17"/>
@@ -49898,10 +49980,10 @@
       <c r="P33" s="17"/>
       <c r="R33" s="17"/>
       <c r="T33" s="93" t="s">
-        <v>366</v>
+        <v>382</v>
       </c>
       <c r="W33" s="76" t="s">
-        <v>367</v>
+        <v>383</v>
       </c>
       <c r="AA33" s="90"/>
       <c r="AD33" s="17"/>
@@ -49944,7 +50026,7 @@
         <v>1626.0</v>
       </c>
       <c r="U34" s="83" t="s">
-        <v>368</v>
+        <v>384</v>
       </c>
       <c r="W34" s="76">
         <v>5193.0</v>
@@ -49989,7 +50071,7 @@
         <v>4176.0</v>
       </c>
       <c r="U35" s="83" t="s">
-        <v>368</v>
+        <v>384</v>
       </c>
       <c r="W35" s="76">
         <v>4863.0</v>
@@ -50087,7 +50169,7 @@
       <c r="D38" s="17"/>
       <c r="E38" s="17"/>
       <c r="F38" s="4" t="s">
-        <v>369</v>
+        <v>385</v>
       </c>
       <c r="G38" s="226">
         <f t="shared" ref="G38:I38" si="8">G30-G35</f>
@@ -50289,7 +50371,7 @@
       <c r="Q45" s="17"/>
       <c r="R45" s="17"/>
       <c r="T45" s="216" t="s">
-        <v>370</v>
+        <v>386</v>
       </c>
       <c r="AD45" s="17"/>
       <c r="AE45" s="17"/>
@@ -50453,7 +50535,7 @@
         <v>156</v>
       </c>
       <c r="AG49" s="60" t="s">
-        <v>371</v>
+        <v>387</v>
       </c>
     </row>
     <row r="50">
@@ -50618,7 +50700,7 @@
         <v>13.03594852814783</v>
       </c>
       <c r="AG52" s="60" t="s">
-        <v>372</v>
+        <v>388</v>
       </c>
     </row>
     <row r="53">
@@ -50679,7 +50761,7 @@
         <v>6.291840048860032</v>
       </c>
       <c r="AG53" s="60" t="s">
-        <v>372</v>
+        <v>388</v>
       </c>
     </row>
     <row r="54">
@@ -50740,7 +50822,7 @@
         <v>2.7243520649411117</v>
       </c>
       <c r="AG54" s="60" t="s">
-        <v>372</v>
+        <v>388</v>
       </c>
     </row>
     <row r="55">
@@ -50801,7 +50883,7 @@
         <v>2.1429979739456915</v>
       </c>
       <c r="AG55" s="60" t="s">
-        <v>372</v>
+        <v>388</v>
       </c>
     </row>
     <row r="56">
@@ -50862,7 +50944,7 @@
         <v>3.98032040346951</v>
       </c>
       <c r="AG56" s="60" t="s">
-        <v>372</v>
+        <v>388</v>
       </c>
     </row>
     <row r="57">
@@ -51085,10 +51167,10 @@
       <c r="R62" s="17"/>
       <c r="S62" s="17"/>
       <c r="U62" s="76" t="s">
-        <v>373</v>
+        <v>389</v>
       </c>
       <c r="V62" s="76" t="s">
-        <v>374</v>
+        <v>390</v>
       </c>
       <c r="AC62" s="17"/>
       <c r="AD62" s="17"/>
@@ -51130,7 +51212,7 @@
         <v>2165.0</v>
       </c>
       <c r="W63" s="76" t="s">
-        <v>375</v>
+        <v>391</v>
       </c>
       <c r="AC63" s="17"/>
       <c r="AD63" s="17"/>
@@ -51764,7 +51846,7 @@
       <c r="R79" s="17"/>
       <c r="S79" s="17"/>
       <c r="T79" s="6" t="s">
-        <v>376</v>
+        <v>392</v>
       </c>
       <c r="U79" s="17"/>
       <c r="V79" s="17"/>
@@ -51805,7 +51887,7 @@
       <c r="R80" s="17"/>
       <c r="S80" s="17"/>
       <c r="T80" s="76" t="s">
-        <v>377</v>
+        <v>393</v>
       </c>
       <c r="U80" s="21"/>
       <c r="V80" s="21"/>

--- a/data/df_best_models.xlsx
+++ b/data/df_best_models.xlsx
@@ -132,8 +132,7 @@
 #10 roi, gran error y f1_score
 Distribucion aceptable (24%)"	
 :(
-Assess malo (0%) aunque mereció mas.
-</t>
+Assess malo (0%) aunque mereció mas.</t>
       </text>
     </comment>
     <comment authorId="0" ref="A1">
@@ -516,7 +515,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="886" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="463">
   <si>
     <t>id_country</t>
   </si>
@@ -586,6 +585,11 @@
     <t>Predice poco empate (-65%)</t>
   </si>
   <si>
+    <t>1071
+375
+771</t>
+  </si>
+  <si>
     <t>france</t>
   </si>
   <si>
@@ -622,11 +626,12 @@
     <t>spain</t>
   </si>
   <si>
-    <t>#2 roi con ea y #1 en f1_score
-Gran assess</t>
+    <t># Max roi con ea en empates
+Metrica buena
+Buen assess</t>
   </si>
   <si>
-    <t>Predice poco empate (-58%)</t>
+    <t>1066 / 1135 / 601</t>
   </si>
   <si>
     <t>ENG</t>
@@ -982,6 +987,9 @@
   </si>
   <si>
     <t xml:space="preserve">creo que por hoy, no estaria mal tomar empate en los dos... </t>
+  </si>
+  <si>
+    <t>Tras tener en cuenta cuotas de bet:</t>
   </si>
   <si>
     <t>deberia cambiar el modelo en: ENG y en SPA</t>
@@ -3576,7 +3584,7 @@
         <v>45739.0</v>
       </c>
       <c r="D4" s="14">
-        <v>458.0</v>
+        <v>1070.0</v>
       </c>
       <c r="E4" s="14" t="s">
         <v>17</v>
@@ -3603,8 +3611,8 @@
       <c r="L4" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="M4" s="4">
-        <v>1071.0</v>
+      <c r="M4" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="N4" s="28">
         <v>-0.959</v>
@@ -3622,7 +3630,7 @@
         <v>55.0</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" s="12">
         <v>45739.0</v>
@@ -3650,10 +3658,10 @@
         <v>11.0</v>
       </c>
       <c r="K5" s="26" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L5" s="27" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M5" s="4">
         <v>49.0</v>
@@ -3674,7 +3682,7 @@
         <v>59.0</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" s="12">
         <v>45739.0</v>
@@ -3702,10 +3710,10 @@
         <v>1.0</v>
       </c>
       <c r="K6" s="26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L6" s="27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M6" s="4">
         <v>385.0</v>
@@ -3726,7 +3734,7 @@
         <v>77.0</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C7" s="12">
         <v>45739.0</v>
@@ -3754,11 +3762,11 @@
         <v>2.0</v>
       </c>
       <c r="K7" s="26" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L7" s="31"/>
       <c r="M7" s="4">
-        <v>625.0</v>
+        <v>211.0</v>
       </c>
       <c r="N7" s="28">
         <v>-0.920368837543479</v>
@@ -3776,13 +3784,13 @@
         <v>148.0</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" s="12">
         <v>45740.0</v>
       </c>
       <c r="D8" s="14">
-        <v>112.0</v>
+        <v>546.0</v>
       </c>
       <c r="E8" s="14" t="s">
         <v>17</v>
@@ -3791,26 +3799,24 @@
         <v>5.0</v>
       </c>
       <c r="G8" s="24">
-        <v>10.79</v>
+        <v>15.0</v>
       </c>
       <c r="H8" s="24">
         <v>5.0</v>
       </c>
       <c r="I8" s="24">
         <f t="shared" si="1"/>
-        <v>6.93</v>
+        <v>8.333333333</v>
       </c>
       <c r="J8" s="25">
         <v>11.0</v>
       </c>
       <c r="K8" s="26" t="s">
-        <v>31</v>
-      </c>
-      <c r="L8" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="M8" s="4">
-        <v>261.0</v>
+      <c r="L8" s="27"/>
+      <c r="M8" s="4" t="s">
+        <v>33</v>
       </c>
       <c r="N8" s="28">
         <v>-1.0182155187786</v>
@@ -8850,146 +8856,146 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="76" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="2">
       <c r="B2" s="17"/>
       <c r="C2" s="5" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E2" s="235"/>
       <c r="F2" s="6" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="H2" s="235"/>
     </row>
     <row r="3">
       <c r="B3" s="186" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C3" s="236" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="D3" s="186" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E3" s="237" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="F3" s="186" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="G3" s="186" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="H3" s="186" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="238" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C4" s="239" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D4" s="187" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E4" s="240" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F4" s="241" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="G4" s="241" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="H4" s="187"/>
     </row>
     <row r="5">
       <c r="B5" s="238" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C5" s="242" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D5" s="197"/>
       <c r="E5" s="240" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F5" s="243" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="G5" s="244" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="H5" s="187"/>
     </row>
     <row r="6">
       <c r="B6" s="238" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C6" s="239" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D6" s="187" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E6" s="240" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F6" s="187" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="G6" s="187"/>
       <c r="H6" s="187"/>
     </row>
     <row r="7">
       <c r="B7" s="187" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C7" s="245" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D7" s="187"/>
       <c r="E7" s="246" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="F7" s="239" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="G7" s="187"/>
       <c r="H7" s="187" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="247" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C8" s="248" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D8" s="249"/>
       <c r="E8" s="247" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="F8" s="250" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="G8" s="251" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="H8" s="249"/>
     </row>
     <row r="9">
       <c r="B9" s="20" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C9" s="252" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D9" s="143"/>
       <c r="E9" s="143"/>
@@ -8999,27 +9005,27 @@
     </row>
     <row r="10">
       <c r="B10" s="20" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C10" s="217"/>
       <c r="D10" s="143"/>
       <c r="E10" s="143"/>
       <c r="F10" s="217"/>
       <c r="G10" s="241" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="H10" s="143"/>
     </row>
     <row r="11">
       <c r="B11" s="20" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C11" s="217"/>
       <c r="D11" s="143"/>
       <c r="E11" s="143"/>
       <c r="F11" s="217"/>
       <c r="G11" s="253" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="H11" s="20"/>
     </row>
@@ -9042,7 +9048,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="90" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="L1" s="32"/>
     </row>
@@ -9051,16 +9057,16 @@
     </row>
     <row r="3">
       <c r="A3" s="76" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L3" s="32"/>
     </row>
     <row r="4">
       <c r="B4" s="76" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="G4" s="76" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="L4" s="32"/>
     </row>
@@ -9086,7 +9092,7 @@
     </row>
     <row r="6">
       <c r="A6" s="23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B6" s="179">
         <v>0.664304152</v>
@@ -9106,7 +9112,7 @@
     </row>
     <row r="7">
       <c r="A7" s="20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B7" s="179">
         <v>0.67680879</v>
@@ -9126,7 +9132,7 @@
     </row>
     <row r="8">
       <c r="A8" s="20" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B8" s="179">
         <v>0.317632128</v>
@@ -9146,7 +9152,7 @@
     </row>
     <row r="9">
       <c r="A9" s="20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B9" s="179">
         <v>0.598124706</v>
@@ -9166,62 +9172,62 @@
     </row>
     <row r="11">
       <c r="A11" s="254" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="90" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="76" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="254" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="90" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="76" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="F19" s="151"/>
     </row>
     <row r="20">
       <c r="B20" s="90" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C20" s="105"/>
       <c r="D20" s="105"/>
       <c r="E20" s="105"/>
       <c r="F20" s="105"/>
       <c r="G20" s="90" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="H20" s="90" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I20" s="90" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J20" s="90" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K20" s="90" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="90" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="G21" s="107">
         <v>2.575</v>
@@ -9229,27 +9235,27 @@
     </row>
     <row r="23">
       <c r="K23" s="90" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="76" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="H24" s="76" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I24" s="76" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="K24" s="76" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="L24" s="76" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="M24" s="76" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="25">
@@ -9268,7 +9274,7 @@
         <v>#REF!</v>
       </c>
       <c r="K25" s="76" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="26">
@@ -9279,7 +9285,7 @@
         <v>1.19</v>
       </c>
       <c r="K26" s="76" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="27">
@@ -9290,7 +9296,7 @@
         <v>2.19</v>
       </c>
       <c r="K27" s="76" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="28">
@@ -9301,7 +9307,7 @@
         <v>0.05</v>
       </c>
       <c r="K28" s="76" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="29">
@@ -9320,7 +9326,7 @@
         <v>6.42</v>
       </c>
       <c r="K30" s="93" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="31">
@@ -9337,7 +9343,7 @@
         <v>3</v>
       </c>
       <c r="M31" s="76" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="32">
@@ -9365,7 +9371,7 @@
         <v>0.58</v>
       </c>
       <c r="K33" s="23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L33" s="14">
         <v>3960.0</v>
@@ -9382,7 +9388,7 @@
         <v>0.77</v>
       </c>
       <c r="K34" s="20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L34" s="14">
         <v>3032.0</v>
@@ -9399,7 +9405,7 @@
         <v>0.0</v>
       </c>
       <c r="K35" s="20" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L35" s="14">
         <v>2114.0</v>
@@ -9416,7 +9422,7 @@
         <v>2.53</v>
       </c>
       <c r="K36" s="20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L36" s="14">
         <v>2232.0</v>
@@ -9465,7 +9471,7 @@
         <v>0.61</v>
       </c>
       <c r="K41" s="90" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="42">
@@ -9476,13 +9482,13 @@
         <v>0.69</v>
       </c>
       <c r="K42" s="76" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="L42" s="76" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="M42" s="76" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="43">
@@ -9614,7 +9620,7 @@
         <v>0.0</v>
       </c>
       <c r="K51" s="76" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="52">
@@ -9642,20 +9648,20 @@
       </c>
       <c r="K54" s="143"/>
       <c r="L54" s="255" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="M54" s="256"/>
       <c r="N54" s="148" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="O54" s="148" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="P54" s="148" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="R54" s="79" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="S54" s="151">
         <v>0.15</v>
@@ -9669,7 +9675,7 @@
         <v>-0.12</v>
       </c>
       <c r="K55" s="20" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L55" s="257">
         <v>0.76</v>
@@ -9734,7 +9740,7 @@
         <v>5.86</v>
       </c>
       <c r="R57" s="76" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="S57" s="107">
         <f>SUM(P55:P74)</f>
@@ -9749,7 +9755,7 @@
         <v>0.0</v>
       </c>
       <c r="K58" s="20" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L58" s="257">
         <v>0.57</v>
@@ -9763,7 +9769,7 @@
         <v>0.855</v>
       </c>
       <c r="P58" s="20" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="59">
@@ -9810,7 +9816,7 @@
         <v>0.96</v>
       </c>
       <c r="P60" s="20" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="61">
@@ -9821,7 +9827,7 @@
         <v>0.02</v>
       </c>
       <c r="K61" s="20" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L61" s="20">
         <v>0.42</v>
@@ -9893,7 +9899,7 @@
         <v>0.0</v>
       </c>
       <c r="K64" s="20" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L64" s="20">
         <v>0.42</v>
@@ -10037,7 +10043,7 @@
         <v>0.0</v>
       </c>
       <c r="K70" s="20" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L70" s="20">
         <v>0.66</v>
@@ -10666,7 +10672,7 @@
     <row r="1">
       <c r="A1" s="33"/>
       <c r="B1" s="34" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C1" s="35"/>
       <c r="D1" s="33"/>
@@ -10682,7 +10688,7 @@
       <c r="N1" s="35"/>
       <c r="O1" s="35"/>
       <c r="P1" s="34" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q1" s="35"/>
       <c r="R1" s="35"/>
@@ -10693,7 +10699,7 @@
       <c r="W1" s="34"/>
       <c r="X1" s="36"/>
       <c r="Y1" s="36" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Z1" s="34"/>
       <c r="AA1" s="34"/>
@@ -10701,7 +10707,7 @@
       <c r="AC1" s="34"/>
       <c r="AD1" s="34"/>
       <c r="AE1" s="34" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AF1" s="35"/>
       <c r="AG1" s="35"/>
@@ -10718,7 +10724,7 @@
       <c r="AR1" s="35"/>
       <c r="AS1" s="35"/>
       <c r="AT1" s="34" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AU1" s="35"/>
       <c r="AV1" s="35"/>
@@ -10736,7 +10742,7 @@
       <c r="BH1" s="35"/>
       <c r="BI1" s="35"/>
       <c r="BJ1" s="34" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="BK1" s="35"/>
       <c r="BL1" s="33"/>
@@ -10759,19 +10765,19 @@
       <c r="CC1" s="33"/>
       <c r="CD1" s="33"/>
       <c r="CE1" s="38" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="CF1" s="39" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="CG1" s="39" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="CH1" s="39" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="CI1" s="39" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="CJ1" s="40"/>
       <c r="CK1" s="40"/>
@@ -10782,103 +10788,103 @@
     <row r="2">
       <c r="A2" s="41"/>
       <c r="B2" s="42" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E2" s="42"/>
       <c r="F2" s="43" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G2" s="43" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H2" s="43"/>
       <c r="I2" s="43" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J2" s="44" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N2" s="45" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O2" s="32"/>
       <c r="P2" s="42" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="S2" s="44" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="W2" s="46" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="X2" s="42"/>
       <c r="Y2" s="42" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z2" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="Z2" s="45" t="s">
-        <v>47</v>
-      </c>
       <c r="AA2" s="43" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AB2" s="43"/>
       <c r="AC2" s="43"/>
       <c r="AD2" s="43"/>
       <c r="AE2" s="42" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AH2" s="44" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AL2" s="45" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AM2" s="32"/>
       <c r="AN2" s="42"/>
       <c r="AO2" s="45" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AP2" s="43" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AQ2" s="32"/>
       <c r="AR2" s="32"/>
       <c r="AS2" s="32"/>
       <c r="AT2" s="42" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AW2" s="44" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="BB2" s="45" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="BC2" s="45"/>
       <c r="BD2" s="42"/>
       <c r="BE2" s="45" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="BF2" s="32"/>
       <c r="BG2" s="32"/>
       <c r="BH2" s="32"/>
       <c r="BI2" s="32"/>
       <c r="BJ2" s="42" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="BN2" s="44" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="BS2" s="47"/>
       <c r="BT2" s="45" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="BU2" s="45"/>
       <c r="BV2" s="42"/>
       <c r="BW2" s="45" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="BX2" s="43" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="BY2" s="47"/>
       <c r="BZ2" s="47"/>
@@ -10887,7 +10893,7 @@
       <c r="CC2" s="47"/>
       <c r="CD2" s="47"/>
       <c r="CE2" s="48" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="CF2" s="49">
         <v>-0.72106</v>
@@ -10910,220 +10916,220 @@
     <row r="3">
       <c r="A3" s="41"/>
       <c r="B3" s="43" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C3" s="43" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D3" s="47" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E3" s="51" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F3" s="51" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G3" s="51" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H3" s="52" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I3" s="53" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J3" s="45" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="K3" s="45" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L3" s="46" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M3" s="54" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N3" s="43" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="O3" s="32"/>
       <c r="P3" s="43" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q3" s="43" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="R3" s="47" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="S3" s="45" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="T3" s="45" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="U3" s="45" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="V3" s="55" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="W3" s="56" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="X3" s="57"/>
       <c r="Y3" s="51" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Z3" s="43" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AA3" s="51" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AB3" s="53" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AC3" s="45" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AD3" s="43"/>
       <c r="AE3" s="43" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AF3" s="43" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AG3" s="47" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AH3" s="46" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AI3" s="45" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ3" s="45" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK3" s="54" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AL3" s="43" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AM3" s="32"/>
       <c r="AN3" s="51" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AO3" s="43" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AP3" s="51" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AQ3" s="53" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AR3" s="45" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AS3" s="32"/>
       <c r="AT3" s="43" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AU3" s="43" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AV3" s="47" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AW3" s="46" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AX3" s="46" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AY3" s="45"/>
       <c r="AZ3" s="45" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="BA3" s="55" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="BB3" s="43" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="BC3" s="43"/>
       <c r="BD3" s="51" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="BE3" s="43" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="BF3" s="53" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="BG3" s="45" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="BH3" s="32"/>
       <c r="BI3" s="32"/>
       <c r="BJ3" s="43" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="BK3" s="43" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="BL3" s="58" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="BM3" s="47" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="BN3" s="45" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="BO3" s="45" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="BP3" s="45"/>
       <c r="BQ3" s="45" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="BR3" s="55" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="BS3" s="47" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="BT3" s="43" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="BU3" s="43"/>
       <c r="BV3" s="51" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="BW3" s="43" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="BX3" s="51" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="BY3" s="53" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="BZ3" s="45" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="CA3" s="47"/>
       <c r="CB3" s="47"/>
       <c r="CC3" s="47"/>
       <c r="CD3" s="47"/>
       <c r="CE3" s="48" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="CF3" s="59">
         <v>-0.2884</v>
@@ -11146,224 +11152,224 @@
     <row r="4">
       <c r="A4" s="41"/>
       <c r="B4" s="45" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C4" s="45" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D4" s="60" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E4" s="61" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F4" s="45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G4" s="45" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H4" s="45" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I4" s="60" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J4" s="62" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K4" s="62" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L4" s="63" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="M4" s="64" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="N4" s="45" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O4" s="32"/>
       <c r="P4" s="45" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q4" s="45" t="s">
+        <v>81</v>
+      </c>
+      <c r="R4" s="45" t="s">
+        <v>82</v>
+      </c>
+      <c r="S4" s="62" t="s">
+        <v>75</v>
+      </c>
+      <c r="T4" s="62" t="s">
+        <v>76</v>
+      </c>
+      <c r="U4" s="63" t="s">
+        <v>77</v>
+      </c>
+      <c r="V4" s="64" t="s">
+        <v>83</v>
+      </c>
+      <c r="W4" s="46" t="s">
         <v>79</v>
-      </c>
-      <c r="Q4" s="45" t="s">
-        <v>80</v>
-      </c>
-      <c r="R4" s="45" t="s">
-        <v>81</v>
-      </c>
-      <c r="S4" s="62" t="s">
-        <v>74</v>
-      </c>
-      <c r="T4" s="62" t="s">
-        <v>75</v>
-      </c>
-      <c r="U4" s="63" t="s">
-        <v>76</v>
-      </c>
-      <c r="V4" s="64" t="s">
-        <v>82</v>
-      </c>
-      <c r="W4" s="46" t="s">
-        <v>78</v>
       </c>
       <c r="X4" s="45"/>
       <c r="Y4" s="53" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Z4" s="45" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AA4" s="45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AB4" s="60" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC4" s="60" t="s">
         <v>73</v>
-      </c>
-      <c r="AC4" s="60" t="s">
-        <v>72</v>
       </c>
       <c r="AD4" s="45"/>
       <c r="AE4" s="45" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AF4" s="45" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AG4" s="45" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AH4" s="62" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AI4" s="62" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AJ4" s="63" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AK4" s="64" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AL4" s="45" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AM4" s="32"/>
       <c r="AN4" s="53" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AO4" s="45" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AP4" s="45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AQ4" s="60" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR4" s="60" t="s">
         <v>73</v>
-      </c>
-      <c r="AR4" s="60" t="s">
-        <v>72</v>
       </c>
       <c r="AS4" s="32"/>
       <c r="AT4" s="45" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AU4" s="45" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AV4" s="45" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AW4" s="65" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AX4" s="65" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AY4" s="60" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AZ4" s="63" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="BA4" s="64" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="BB4" s="45" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="BC4" s="45"/>
       <c r="BD4" s="53" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="BE4" s="45" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="BF4" s="60" t="s">
+        <v>74</v>
+      </c>
+      <c r="BG4" s="60" t="s">
         <v>73</v>
-      </c>
-      <c r="BG4" s="60" t="s">
-        <v>72</v>
       </c>
       <c r="BH4" s="32"/>
       <c r="BI4" s="32"/>
       <c r="BJ4" s="43" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="BK4" s="43" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="BL4" s="58" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="BM4" s="47" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="BN4" s="62" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="BO4" s="62" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BP4" s="60" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="BQ4" s="63" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="BR4" s="66" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="BS4" s="66" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="BT4" s="45" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="BU4" s="45"/>
       <c r="BV4" s="55" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="BW4" s="45" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="BX4" s="45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="BY4" s="60" t="s">
+        <v>74</v>
+      </c>
+      <c r="BZ4" s="60" t="s">
         <v>73</v>
-      </c>
-      <c r="BZ4" s="60" t="s">
-        <v>72</v>
       </c>
       <c r="CA4" s="60"/>
       <c r="CB4" s="60"/>
       <c r="CC4" s="60"/>
       <c r="CD4" s="60"/>
       <c r="CE4" s="38" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="CF4" s="67">
         <v>-0.456028563</v>
@@ -11385,7 +11391,7 @@
     </row>
     <row r="5">
       <c r="A5" s="68" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B5" s="69">
         <f t="shared" ref="B5:N5" si="1">AVERAGE(B7:B26)</f>
@@ -11672,7 +11678,7 @@
       <c r="CC5" s="69"/>
       <c r="CD5" s="69"/>
       <c r="CE5" s="73" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="CF5" s="74">
         <v>-0.57020319</v>
@@ -11694,7 +11700,7 @@
     </row>
     <row r="6">
       <c r="A6" s="68" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B6" s="69">
         <f t="shared" ref="B6:N6" si="11">STDEV(B7:B26)</f>
@@ -11981,7 +11987,7 @@
       <c r="CC6" s="69"/>
       <c r="CD6" s="69"/>
       <c r="CE6" s="73" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="CF6" s="74">
         <v>-0.221394985</v>
@@ -12219,7 +12225,7 @@
       <c r="CC7" s="15"/>
       <c r="CD7" s="15"/>
       <c r="CE7" s="80" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="CF7" s="81">
         <f t="shared" ref="CF7:CI7" si="21">AVERAGE(CF2:CF6)</f>
@@ -16582,13 +16588,13 @@
     <row r="29">
       <c r="A29" s="82"/>
       <c r="B29" s="15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C29" s="82"/>
       <c r="D29" s="82"/>
       <c r="E29" s="82"/>
       <c r="P29" s="15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="U29" s="15"/>
       <c r="V29" s="15"/>
@@ -16599,13 +16605,13 @@
       <c r="AC29" s="15"/>
       <c r="AD29" s="15"/>
       <c r="AE29" s="15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AT29" s="15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="BJ29" s="15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="30">
@@ -16614,12 +16620,12 @@
         <v>342.0</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D30" s="82"/>
       <c r="E30" s="82"/>
       <c r="F30" s="76" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P30" s="76">
         <v>912.0</v>
@@ -16631,13 +16637,13 @@
         <v>979.0</v>
       </c>
       <c r="AU30" s="76" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BJ30" s="77">
         <v>1117.0</v>
       </c>
       <c r="BK30" s="76" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="31">
@@ -16646,7 +16652,7 @@
         <v>1071.0</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D31" s="82"/>
       <c r="E31" s="82"/>
@@ -16657,19 +16663,19 @@
         <v>834.0</v>
       </c>
       <c r="Q31" s="76" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AE31" s="77">
         <v>899.0</v>
       </c>
       <c r="AF31" s="76" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="BJ31" s="76">
         <v>1093.0</v>
       </c>
       <c r="BK31" s="76" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="32">
@@ -16683,7 +16689,7 @@
         <v>1134.0</v>
       </c>
       <c r="Q32" s="76" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AE32" s="76">
         <v>372.0</v>
@@ -16692,13 +16698,13 @@
         <v>223.0</v>
       </c>
       <c r="AU32" s="76" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="BJ32" s="76">
         <v>261.0</v>
       </c>
       <c r="BK32" s="76" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="33">
@@ -16713,13 +16719,13 @@
         <v>1129.0</v>
       </c>
       <c r="Q33" s="76" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AE33" s="76">
         <v>544.0</v>
       </c>
       <c r="AF33" s="76" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="34">
@@ -16742,13 +16748,13 @@
     <row r="37">
       <c r="A37" s="82"/>
       <c r="C37" s="91" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="82"/>
       <c r="C38" s="92" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="BJ38" s="76"/>
     </row>
@@ -16764,7 +16770,7 @@
     <row r="42">
       <c r="A42" s="82"/>
       <c r="C42" s="93" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="43">
@@ -16778,7 +16784,7 @@
       <c r="A44" s="82"/>
       <c r="B44" s="82"/>
       <c r="C44" s="94" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D44" s="95"/>
       <c r="E44" s="95"/>
@@ -16875,7 +16881,7 @@
       <c r="B45" s="82"/>
       <c r="C45" s="82"/>
       <c r="D45" s="15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E45" s="15">
         <v>342.0</v>
@@ -16887,7 +16893,7 @@
       <c r="B46" s="82"/>
       <c r="C46" s="82"/>
       <c r="D46" s="15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E46" s="82"/>
       <c r="F46" s="82"/>
@@ -16897,7 +16903,7 @@
       <c r="B47" s="82"/>
       <c r="C47" s="82"/>
       <c r="D47" s="15" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E47" s="82"/>
       <c r="F47" s="82"/>
@@ -16907,7 +16913,7 @@
       <c r="B48" s="82"/>
       <c r="C48" s="82"/>
       <c r="D48" s="15" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E48" s="82"/>
       <c r="F48" s="82"/>
@@ -16917,7 +16923,7 @@
       <c r="B49" s="82"/>
       <c r="C49" s="82"/>
       <c r="D49" s="15" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E49" s="82"/>
       <c r="F49" s="82"/>
@@ -17034,70 +17040,70 @@
         <v>19</v>
       </c>
       <c r="G2" s="90" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3">
       <c r="C3" s="23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3" s="76">
         <v>800.0</v>
       </c>
       <c r="G3" s="76" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K3" s="97"/>
     </row>
     <row r="4">
       <c r="C4" s="20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G4" s="76" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K4" s="97"/>
     </row>
     <row r="5">
       <c r="C5" s="20" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G5" s="76" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K5" s="97"/>
     </row>
     <row r="6">
       <c r="C6" s="20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G6" s="76" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="7">
       <c r="G7" s="76" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12">
       <c r="D12" s="98" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F12" s="79"/>
     </row>
     <row r="13">
       <c r="C13" s="90" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D13" s="90" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F13" s="79"/>
     </row>
     <row r="14">
       <c r="C14" s="76" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D14" s="99">
         <v>1070.0</v>
@@ -17129,7 +17135,7 @@
     </row>
     <row r="15">
       <c r="C15" s="76" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D15" s="102">
         <v>800.0</v>
@@ -17143,7 +17149,7 @@
     </row>
     <row r="16">
       <c r="C16" s="76" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D16" s="76">
         <v>766.0</v>
@@ -17157,7 +17163,7 @@
     </row>
     <row r="17">
       <c r="C17" s="76" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D17" s="77">
         <v>184.0</v>
@@ -17169,7 +17175,7 @@
     </row>
     <row r="18">
       <c r="C18" s="76" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D18" s="99">
         <v>1135.0</v>
@@ -17186,13 +17192,13 @@
     </row>
     <row r="19">
       <c r="D19" s="76" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E19" s="76" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F19" s="76" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="20">
@@ -17205,9 +17211,78 @@
     </row>
     <row r="22">
       <c r="D22" s="76" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F22" s="21"/>
+    </row>
+    <row r="25">
+      <c r="D25" s="76" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="D26" s="76" t="s">
+        <v>50</v>
+      </c>
+      <c r="E26" s="77">
+        <v>375.0</v>
+      </c>
+      <c r="F26" s="76">
+        <v>1070.0</v>
+      </c>
+      <c r="G26" s="76">
+        <v>771.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="D27" s="76" t="s">
+        <v>66</v>
+      </c>
+      <c r="E27" s="77">
+        <v>1092.0</v>
+      </c>
+      <c r="F27" s="76">
+        <v>808.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="D28" s="76" t="s">
+        <v>105</v>
+      </c>
+      <c r="E28" s="77">
+        <v>900.0</v>
+      </c>
+      <c r="F28" s="76">
+        <v>457.0</v>
+      </c>
+      <c r="H28" s="76">
+        <v>424.0</v>
+      </c>
+      <c r="I28" s="76">
+        <v>899.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="D29" s="76" t="s">
+        <v>107</v>
+      </c>
+      <c r="E29" s="76">
+        <v>187.0</v>
+      </c>
+      <c r="F29" s="77">
+        <v>211.0</v>
+      </c>
+      <c r="G29" s="76">
+        <v>907.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="D30" s="76" t="s">
+        <v>109</v>
+      </c>
+      <c r="E30" s="77">
+        <v>546.0</v>
+      </c>
     </row>
   </sheetData>
   <drawing r:id="rId2"/>
@@ -17284,7 +17359,7 @@
         <v>55.0</v>
       </c>
       <c r="B3" s="107" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3" s="108">
         <v>45679.0</v>
@@ -17327,7 +17402,7 @@
         <v>59.0</v>
       </c>
       <c r="B4" s="76" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" s="108">
         <v>45680.0</v>
@@ -17370,7 +17445,7 @@
         <v>77.0</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C5" s="12">
         <v>45677.0</v>
@@ -17415,7 +17490,7 @@
         <v>148.0</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C6" s="12">
         <v>45677.0</v>
@@ -17491,32 +17566,32 @@
     </row>
     <row r="11">
       <c r="E11" s="116" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="L11" s="76" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="M11" s="110" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N11" s="77" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O11" s="114"/>
       <c r="P11" s="114"/>
     </row>
     <row r="12">
       <c r="E12" s="116" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="L12" s="76" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="M12" s="110" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N12" s="77" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O12" s="114"/>
       <c r="P12" s="114"/>
@@ -17600,7 +17675,7 @@
         <v>55.0</v>
       </c>
       <c r="B17" s="107" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C17" s="108">
         <v>45679.0</v>
@@ -17643,7 +17718,7 @@
         <v>59.0</v>
       </c>
       <c r="B18" s="76" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C18" s="108">
         <v>45680.0</v>
@@ -17684,7 +17759,7 @@
         <v>77.0</v>
       </c>
       <c r="B19" s="119" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C19" s="108">
         <v>45677.0</v>
@@ -17727,7 +17802,7 @@
         <v>148.0</v>
       </c>
       <c r="B20" s="76" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C20" s="108">
         <v>45677.0</v>
@@ -17772,49 +17847,49 @@
     </row>
     <row r="24">
       <c r="C24" s="90" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="25">
       <c r="C25" s="99" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26">
       <c r="C26" s="120" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="27">
       <c r="C27" s="121" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="28">
       <c r="C28" s="119" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="30">
       <c r="C30" s="93" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="31">
       <c r="C31" s="90" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="L31" s="90" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q31" s="90" t="s">
+        <v>35</v>
+      </c>
+      <c r="Z31" s="90" t="s">
         <v>37</v>
       </c>
-      <c r="Q31" s="90" t="s">
+      <c r="AH31" s="90" t="s">
         <v>34</v>
-      </c>
-      <c r="Z31" s="90" t="s">
-        <v>36</v>
-      </c>
-      <c r="AH31" s="90" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="32">
@@ -19794,7 +19869,7 @@
     </row>
     <row r="63">
       <c r="C63" s="90" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="65">
@@ -19814,25 +19889,25 @@
         <v>4</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="J65" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="K65" s="60" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="L65" s="4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="M65" s="131" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="N65" s="132" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="66">
@@ -19922,7 +19997,7 @@
         <v>55.0</v>
       </c>
       <c r="D69" s="23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E69" s="12">
         <v>45679.0</v>
@@ -19967,7 +20042,7 @@
         <v>59.0</v>
       </c>
       <c r="D70" s="20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E70" s="12">
         <v>45680.0</v>
@@ -20012,7 +20087,7 @@
         <v>77.0</v>
       </c>
       <c r="D71" s="20" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E71" s="12">
         <v>45677.0</v>
@@ -20056,7 +20131,7 @@
         <v>148.0</v>
       </c>
       <c r="D72" s="20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E72" s="12">
         <v>45677.0</v>
@@ -20097,7 +20172,7 @@
     </row>
     <row r="76">
       <c r="C76" s="90" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="77">
@@ -20117,16 +20192,16 @@
         <v>4</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="J77" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="K77" s="60" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="L77" s="4" t="s">
         <v>5</v>
@@ -20142,10 +20217,10 @@
         <v>8</v>
       </c>
       <c r="Q77" s="131" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="R77" s="132" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="78">
@@ -20254,7 +20329,7 @@
         <v>55.0</v>
       </c>
       <c r="D81" s="23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E81" s="12">
         <v>45679.0</v>
@@ -20309,7 +20384,7 @@
         <v>59.0</v>
       </c>
       <c r="D82" s="20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E82" s="12">
         <v>45680.0</v>
@@ -20364,7 +20439,7 @@
         <v>77.0</v>
       </c>
       <c r="D83" s="20" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E83" s="12">
         <v>45677.0</v>
@@ -20419,7 +20494,7 @@
         <v>148.0</v>
       </c>
       <c r="D84" s="20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E84" s="12">
         <v>45677.0</v>
@@ -20471,7 +20546,7 @@
     </row>
     <row r="94">
       <c r="C94" s="76" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="96">
@@ -20491,31 +20566,31 @@
         <v>4</v>
       </c>
       <c r="H96" s="4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="I96" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J96" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K96" s="60" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="L96" s="60" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="M96" s="60" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="N96" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O96" s="60" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="P96" s="131" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="Q96" s="4" t="s">
         <v>5</v>
@@ -20530,7 +20605,7 @@
         <v>8</v>
       </c>
       <c r="U96" s="132" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="97">
@@ -20651,7 +20726,7 @@
         <v>55.0</v>
       </c>
       <c r="D100" s="137" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E100" s="12">
         <v>45679.0</v>
@@ -20712,7 +20787,7 @@
         <v>59.0</v>
       </c>
       <c r="D101" s="136" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E101" s="12">
         <v>45680.0</v>
@@ -20773,7 +20848,7 @@
         <v>77.0</v>
       </c>
       <c r="D102" s="136" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E102" s="12">
         <v>45677.0</v>
@@ -20834,7 +20909,7 @@
         <v>148.0</v>
       </c>
       <c r="D103" s="136" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E103" s="12">
         <v>45677.0</v>
@@ -20945,7 +21020,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="138" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B1" s="139"/>
       <c r="C1" s="139"/>
@@ -20968,54 +21043,54 @@
     <row r="2">
       <c r="A2" s="143"/>
       <c r="B2" s="144" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C2" s="144" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D2" s="145" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E2" s="145" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F2" s="144" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G2" s="146" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H2" s="146" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I2" s="146" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="J2" s="144"/>
       <c r="K2" s="144" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L2" s="144" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="M2" s="147" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="N2" s="146" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="O2" s="146" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="P2" s="146" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="U2" s="105"/>
       <c r="V2" s="90"/>
     </row>
     <row r="3">
       <c r="A3" s="148" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B3" s="20">
         <v>343.0</v>
@@ -21063,7 +21138,7 @@
     </row>
     <row r="4">
       <c r="A4" s="148" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" s="20">
         <v>1127.0</v>
@@ -21114,7 +21189,7 @@
     </row>
     <row r="5">
       <c r="A5" s="148" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B5" s="149">
         <v>1051.0</v>
@@ -21165,7 +21240,7 @@
     </row>
     <row r="6">
       <c r="A6" s="148" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B6" s="20">
         <v>622.0</v>
@@ -21213,7 +21288,7 @@
     </row>
     <row r="7">
       <c r="A7" s="148" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B7" s="20">
         <v>1447.0</v>
@@ -21273,7 +21348,7 @@
     <row r="10">
       <c r="A10" s="115"/>
       <c r="E10" s="76" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="O10" s="109"/>
       <c r="P10" s="115"/>
@@ -21302,7 +21377,7 @@
     <row r="12">
       <c r="A12" s="151"/>
       <c r="E12" s="23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F12" s="14">
         <v>724.0</v>
@@ -21318,7 +21393,7 @@
     <row r="13">
       <c r="A13" s="151"/>
       <c r="E13" s="20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F13" s="14">
         <v>1051.0</v>
@@ -21334,7 +21409,7 @@
     <row r="14">
       <c r="A14" s="151"/>
       <c r="E14" s="20" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F14" s="14">
         <v>47.0</v>
@@ -21354,7 +21429,7 @@
       <c r="C15" s="151"/>
       <c r="D15" s="151"/>
       <c r="E15" s="20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F15" s="14">
         <v>1447.0</v>
@@ -21404,7 +21479,7 @@
     <row r="18">
       <c r="A18" s="109"/>
       <c r="E18" s="76" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="O18" s="109"/>
       <c r="P18" s="109"/>
@@ -21431,7 +21506,7 @@
     </row>
     <row r="20">
       <c r="E20" s="23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F20" s="14">
         <v>654.0</v>
@@ -21443,7 +21518,7 @@
     </row>
     <row r="21">
       <c r="E21" s="20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F21" s="14">
         <v>1051.0</v>
@@ -21454,7 +21529,7 @@
     </row>
     <row r="22">
       <c r="E22" s="20" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F22" s="14">
         <v>622.0</v>
@@ -21466,7 +21541,7 @@
     </row>
     <row r="23">
       <c r="E23" s="20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F23" s="14">
         <v>1545.0</v>
@@ -21509,7 +21584,7 @@
         <v>4</v>
       </c>
       <c r="H32" s="152" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="I32" s="4" t="s">
         <v>5</v>
@@ -21524,13 +21599,13 @@
         <v>8</v>
       </c>
       <c r="M32" s="153" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="N32" s="60" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="O32" s="154" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="33">
@@ -21641,7 +21716,7 @@
         <v>55.0</v>
       </c>
       <c r="D36" s="137" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E36" s="12">
         <v>45679.0</v>
@@ -21686,7 +21761,7 @@
         <v>59.0</v>
       </c>
       <c r="D37" s="136" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E37" s="12">
         <v>45680.0</v>
@@ -21731,7 +21806,7 @@
         <v>77.0</v>
       </c>
       <c r="D38" s="136" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E38" s="12">
         <v>45677.0</v>
@@ -21776,7 +21851,7 @@
         <v>148.0</v>
       </c>
       <c r="D39" s="136" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E39" s="12">
         <v>45677.0</v>
@@ -21984,13 +22059,13 @@
     </row>
     <row r="9">
       <c r="B9" s="76" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C9" s="76" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D9" s="76" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="10">
@@ -22008,7 +22083,7 @@
         <v>-0.1658536585</v>
       </c>
       <c r="F10" s="76" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
@@ -22026,7 +22101,7 @@
         <v>-0.15</v>
       </c>
       <c r="F11" s="76" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12">
@@ -22064,16 +22139,16 @@
     </row>
     <row r="16">
       <c r="H16" s="76" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="17">
       <c r="G17" s="164"/>
       <c r="H17" s="90" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="I17" s="90" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="18">
@@ -22087,13 +22162,13 @@
         <v>0.85</v>
       </c>
       <c r="G18" s="165" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H18" s="76">
         <v>332.0</v>
       </c>
       <c r="I18" s="83" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="19">
@@ -22107,13 +22182,13 @@
         <v>0.81</v>
       </c>
       <c r="G19" s="165" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H19" s="76" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I19" s="76" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="20">
@@ -22127,41 +22202,41 @@
         <v>0.89</v>
       </c>
       <c r="G20" s="165" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H20" s="76">
         <v>411.0</v>
       </c>
       <c r="I20" s="76" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="21">
       <c r="G21" s="165" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H21" s="76" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="I21" s="76" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="22">
       <c r="G22" s="165" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H22" s="76" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="I22" s="76" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="11"/>
       <c r="I24" s="76" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="25">
@@ -22169,7 +22244,7 @@
         <v>1</v>
       </c>
       <c r="I25" s="76" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="26">
@@ -22184,7 +22259,7 @@
     </row>
     <row r="27">
       <c r="B27" s="23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C27" s="76">
         <v>1288.0</v>
@@ -22194,7 +22269,7 @@
     </row>
     <row r="28">
       <c r="B28" s="20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C28" s="76">
         <v>411.0</v>
@@ -22204,7 +22279,7 @@
     </row>
     <row r="29">
       <c r="B29" s="20" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C29" s="76">
         <v>1015.0</v>
@@ -22214,34 +22289,34 @@
     </row>
     <row r="30">
       <c r="B30" s="20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C30" s="76">
         <v>530.0</v>
       </c>
       <c r="I30" s="90" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="M30" s="114"/>
       <c r="N30" s="114"/>
     </row>
     <row r="31">
       <c r="I31" s="90" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="M31" s="114"/>
       <c r="N31" s="114"/>
     </row>
     <row r="32">
       <c r="I32" s="76" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="M32" s="114"/>
       <c r="N32" s="114"/>
     </row>
     <row r="33">
       <c r="I33" s="76" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="M33" s="114"/>
       <c r="N33" s="114"/>
@@ -22252,7 +22327,7 @@
     </row>
     <row r="35">
       <c r="I35" s="76" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="M35" s="114"/>
       <c r="N35" s="114"/>
@@ -22271,28 +22346,28 @@
     </row>
     <row r="39">
       <c r="I39" s="90" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="M39" s="114"/>
       <c r="N39" s="114"/>
     </row>
     <row r="40">
       <c r="I40" s="76" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M40" s="114"/>
       <c r="N40" s="114"/>
     </row>
     <row r="41">
       <c r="I41" s="76" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="M41" s="114"/>
       <c r="N41" s="114"/>
     </row>
     <row r="42">
       <c r="I42" s="93" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="M42" s="114"/>
       <c r="N42" s="114"/>
@@ -22303,7 +22378,7 @@
     </row>
     <row r="44">
       <c r="I44" s="90" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
   </sheetData>
@@ -22321,34 +22396,34 @@
   <sheetData>
     <row r="1">
       <c r="B1" s="76" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="3">
       <c r="C3" s="76" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D3" s="76" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="H3" s="76" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="K3" s="114"/>
       <c r="L3" s="114"/>
     </row>
     <row r="4">
       <c r="B4" s="76" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C4" s="90" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D4" s="90" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="H4" s="76" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="I4" s="166"/>
       <c r="J4" s="166"/>
@@ -22357,7 +22432,7 @@
     </row>
     <row r="5">
       <c r="B5" s="90" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C5" s="105">
         <f t="shared" ref="C5:D5" si="1">SUM(C6:C18)</f>
@@ -22372,7 +22447,7 @@
         <v>0.4077999152</v>
       </c>
       <c r="F5" s="76" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="6">
@@ -22391,7 +22466,7 @@
         <v>3.06</v>
       </c>
       <c r="H7" s="76" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="8">
@@ -22410,7 +22485,7 @@
         <v>2.3</v>
       </c>
       <c r="H9" s="76" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="10">
@@ -22429,7 +22504,7 @@
         <v>4.18</v>
       </c>
       <c r="H11" s="76" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="12">
@@ -22448,7 +22523,7 @@
         <v>2.35</v>
       </c>
       <c r="H13" s="76" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="14">
@@ -22475,7 +22550,7 @@
         <v>1.37</v>
       </c>
       <c r="H16" s="76" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="17">
@@ -22496,18 +22571,18 @@
     </row>
     <row r="20">
       <c r="B20" s="90" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C20" s="90" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D20" s="90" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="90" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C21" s="105">
         <f t="shared" ref="C21:D21" si="2">sum(C22:C34)</f>
@@ -22522,7 +22597,7 @@
         <v>0.4012276786</v>
       </c>
       <c r="F21" s="76" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="22">
@@ -22631,18 +22706,18 @@
     </row>
     <row r="37">
       <c r="B37" s="90" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C37" s="90" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D37" s="90" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="90" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C38" s="105">
         <f t="shared" ref="C38:D38" si="3">sum(C39:C51)</f>
@@ -22657,7 +22732,7 @@
         <v>0.03155866056</v>
       </c>
       <c r="F38" s="76" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="39">
@@ -22780,20 +22855,20 @@
     </row>
     <row r="54">
       <c r="B54" s="90" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C54" s="90" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D54" s="90" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="K54" s="114"/>
       <c r="L54" s="114"/>
     </row>
     <row r="55">
       <c r="B55" s="90" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C55" s="105">
         <f>sum(C56:C69)</f>
@@ -22808,7 +22883,7 @@
         <v>0.005738332058</v>
       </c>
       <c r="F55" s="76" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K55" s="114"/>
       <c r="L55" s="114"/>
@@ -22959,20 +23034,20 @@
     </row>
     <row r="71">
       <c r="B71" s="90" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C71" s="90" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D71" s="90" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="K71" s="114"/>
       <c r="L71" s="114"/>
     </row>
     <row r="72">
       <c r="B72" s="90" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C72" s="105">
         <f>sum(C73:C86)</f>
@@ -22987,7 +23062,7 @@
         <v>0.3919949174</v>
       </c>
       <c r="F72" s="76" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="K72" s="114"/>
       <c r="L72" s="114"/>
@@ -23201,7 +23276,7 @@
     <row r="2">
       <c r="A2" s="79"/>
       <c r="B2" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C2" s="79">
         <v>0.1</v>
@@ -23211,7 +23286,7 @@
     <row r="3">
       <c r="A3" s="79"/>
       <c r="B3" s="6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C3" s="21" t="str">
         <f>AVERAGE(#REF!)</f>
@@ -23226,7 +23301,7 @@
       <c r="L4" s="34"/>
       <c r="P4" s="34"/>
       <c r="AE4" s="76" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AF4" s="167">
         <f>CORREL(AE6:AE10000,AF6:AF10000)</f>
@@ -23236,50 +23311,50 @@
     <row r="5">
       <c r="A5" s="79"/>
       <c r="B5" s="34" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L5" s="34" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="P5" s="34" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AE5" s="76" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AF5" s="76" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="79"/>
       <c r="B6" s="76" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F6" s="76" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="K6" s="90"/>
       <c r="L6" s="90" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="N6" s="90" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="P6" s="90" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="R6" s="90" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="V6" s="90" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AA6" s="76" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AB6" s="76" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AE6" s="76">
         <v>519.2</v>
@@ -23321,7 +23396,7 @@
         <v>0.5454545455</v>
       </c>
       <c r="AA7" s="76" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AB7" s="107">
         <f t="shared" ref="AB7:AB16" si="4">LEFT(REPLACE(AA7,1,1,""),FIND(",", AA7)-2)/1</f>
@@ -23337,14 +23412,14 @@
     <row r="8">
       <c r="A8" s="79"/>
       <c r="B8" s="171" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C8" s="172" t="str">
         <f t="shared" ref="C8:C17" si="5">REPLACE(B8,FIND(".",B8),1,",")*1</f>
         <v>#VALUE!</v>
       </c>
       <c r="F8" s="99" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="G8" s="172" t="str">
         <f t="shared" ref="G8:G27" si="6">REPLACE(F8,FIND(".",F8),1,",")*1</f>
@@ -23379,7 +23454,7 @@
         <v>0.5263157895</v>
       </c>
       <c r="AA8" s="76" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AB8" s="107">
         <f t="shared" si="4"/>
@@ -23395,14 +23470,14 @@
     <row r="9">
       <c r="A9" s="79"/>
       <c r="B9" s="171" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C9" s="172" t="str">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="F9" s="99" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="G9" s="172" t="str">
         <f t="shared" si="6"/>
@@ -23416,13 +23491,13 @@
       </c>
       <c r="K9" s="79"/>
       <c r="L9" s="168" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="M9" s="168" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="N9" s="90" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="P9" s="170">
         <v>1.0</v>
@@ -23446,7 +23521,7 @@
         <v>0.25</v>
       </c>
       <c r="AA9" s="76" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AB9" s="107">
         <f t="shared" si="4"/>
@@ -23462,14 +23537,14 @@
     <row r="10">
       <c r="A10" s="79"/>
       <c r="B10" s="173" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C10" s="172" t="str">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="F10" s="99" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="G10" s="172" t="str">
         <f t="shared" si="6"/>
@@ -23506,7 +23581,7 @@
         <v>76</v>
       </c>
       <c r="AA10" s="76" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AB10" s="107">
         <f t="shared" si="4"/>
@@ -23521,14 +23596,14 @@
     </row>
     <row r="11">
       <c r="B11" s="171" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C11" s="172" t="str">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="F11" s="99" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="G11" s="172" t="str">
         <f t="shared" si="6"/>
@@ -23557,7 +23632,7 @@
         <v>2.0</v>
       </c>
       <c r="AA11" s="76" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AB11" s="107">
         <f t="shared" si="4"/>
@@ -23572,14 +23647,14 @@
     </row>
     <row r="12">
       <c r="B12" s="173" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="C12" s="172" t="str">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="F12" s="99" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="G12" s="172" t="str">
         <f t="shared" si="6"/>
@@ -23608,7 +23683,7 @@
         <v>1.0</v>
       </c>
       <c r="AA12" s="76" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AB12" s="107">
         <f t="shared" si="4"/>
@@ -23623,14 +23698,14 @@
     </row>
     <row r="13">
       <c r="B13" s="171" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="C13" s="172" t="str">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="F13" s="99" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="G13" s="172" t="str">
         <f t="shared" si="6"/>
@@ -23660,16 +23735,16 @@
       <c r="Q13" s="105"/>
       <c r="R13" s="143"/>
       <c r="S13" s="148" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="T13" s="148" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="U13" s="148" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AA13" s="76" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AB13" s="107">
         <f t="shared" si="4"/>
@@ -23684,14 +23759,14 @@
     </row>
     <row r="14">
       <c r="B14" s="171" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C14" s="172" t="str">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="F14" s="99" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G14" s="172" t="str">
         <f t="shared" si="6"/>
@@ -23731,7 +23806,7 @@
         <v>11.0</v>
       </c>
       <c r="AA14" s="76" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AB14" s="107">
         <f t="shared" si="4"/>
@@ -23746,14 +23821,14 @@
     </row>
     <row r="15">
       <c r="B15" s="171" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C15" s="172" t="str">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="F15" s="99" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="G15" s="172" t="str">
         <f t="shared" si="6"/>
@@ -23793,7 +23868,7 @@
         <v>13.0</v>
       </c>
       <c r="AA15" s="76" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AB15" s="107">
         <f t="shared" si="4"/>
@@ -23808,14 +23883,14 @@
     </row>
     <row r="16">
       <c r="B16" s="171" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C16" s="172" t="str">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="F16" s="99" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="G16" s="172" t="str">
         <f t="shared" si="6"/>
@@ -23855,7 +23930,7 @@
         <v>12.0</v>
       </c>
       <c r="AA16" s="76" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AB16" s="107">
         <f t="shared" si="4"/>
@@ -23870,14 +23945,14 @@
     </row>
     <row r="17">
       <c r="B17" s="171" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C17" s="172" t="str">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="F17" s="99" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="G17" s="172" t="str">
         <f t="shared" si="6"/>
@@ -23905,7 +23980,7 @@
         <v>1.0</v>
       </c>
       <c r="R17" s="148" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="S17" s="175">
         <f t="shared" ref="S17:U17" si="10">SUM(S14:S16)</f>
@@ -23928,7 +24003,7 @@
     </row>
     <row r="18">
       <c r="F18" s="99" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="G18" s="172" t="str">
         <f t="shared" si="6"/>
@@ -23965,14 +24040,14 @@
     </row>
     <row r="19">
       <c r="B19" s="90" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C19" s="107" t="str">
         <f>AVERAGE(C8:C17)</f>
         <v>#VALUE!</v>
       </c>
       <c r="F19" s="99" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="G19" s="172" t="str">
         <f t="shared" si="6"/>
@@ -24000,7 +24075,7 @@
       <c r="T19" s="21"/>
       <c r="U19" s="21"/>
       <c r="AA19" s="76" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AB19" s="107">
         <f>AVERAGE(AB7:AB16)</f>
@@ -24015,7 +24090,7 @@
     </row>
     <row r="20">
       <c r="F20" s="99" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="G20" s="172" t="str">
         <f t="shared" si="6"/>
@@ -24040,7 +24115,7 @@
     </row>
     <row r="21">
       <c r="F21" s="99" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="G21" s="172" t="str">
         <f t="shared" si="6"/>
@@ -24054,13 +24129,13 @@
       </c>
       <c r="R21" s="143"/>
       <c r="S21" s="148" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="T21" s="148" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="U21" s="148" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AE21" s="76">
         <v>146.62</v>
@@ -24072,7 +24147,7 @@
     <row r="22">
       <c r="C22" s="172"/>
       <c r="F22" s="99" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="G22" s="172" t="str">
         <f t="shared" si="6"/>
@@ -24145,7 +24220,7 @@
     </row>
     <row r="24">
       <c r="F24" s="99" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="G24" s="172" t="str">
         <f t="shared" si="6"/>
@@ -24181,7 +24256,7 @@
     </row>
     <row r="25">
       <c r="F25" s="99" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="G25" s="172" t="str">
         <f t="shared" si="6"/>
@@ -24194,7 +24269,7 @@
         <v>1.0</v>
       </c>
       <c r="R25" s="148" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="S25" s="175">
         <f t="shared" ref="S25:U25" si="14">SUM(S22:S24)</f>
@@ -24217,7 +24292,7 @@
     </row>
     <row r="26">
       <c r="F26" s="99" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="G26" s="172" t="str">
         <f t="shared" si="6"/>
@@ -24262,13 +24337,13 @@
         <v>1.0</v>
       </c>
       <c r="AA28" s="76" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AB28" s="76" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AC28" s="76" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AE28" s="76">
         <v>106.73</v>
@@ -24279,7 +24354,7 @@
     </row>
     <row r="29">
       <c r="F29" s="90" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="G29" s="107" t="str">
         <f>AVERAGE(G8:G27)</f>
@@ -24370,7 +24445,7 @@
     </row>
     <row r="32">
       <c r="B32" s="119" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="G32" s="172"/>
       <c r="P32" s="170">
@@ -24399,7 +24474,7 @@
     </row>
     <row r="33">
       <c r="B33" s="178" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="G33" s="179"/>
       <c r="P33" s="170">
@@ -24453,7 +24528,7 @@
     </row>
     <row r="35">
       <c r="H35" s="90" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="P35" s="170">
         <v>1.0</v>
@@ -24481,7 +24556,7 @@
     </row>
     <row r="36">
       <c r="G36" s="90" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H36" s="180">
         <v>4.555000000000001</v>
@@ -24519,7 +24594,7 @@
         <v>3.140689655</v>
       </c>
       <c r="G37" s="90" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H37" s="180">
         <v>7.555294117647058</v>
@@ -24550,7 +24625,7 @@
     </row>
     <row r="38">
       <c r="G38" s="90" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H38" s="182">
         <v>2.21</v>
@@ -24581,14 +24656,14 @@
     </row>
     <row r="39">
       <c r="C39" s="183" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D39" s="184">
         <f t="shared" ref="D39:D221" si="17">IF(COUNTA(C39)=1,C39/1,"")</f>
         <v>1.39</v>
       </c>
       <c r="G39" s="90" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H39" s="180">
         <v>9.938235294117648</v>
@@ -24619,14 +24694,14 @@
     </row>
     <row r="40">
       <c r="C40" s="185" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D40" s="172">
         <f t="shared" si="17"/>
         <v>1.5</v>
       </c>
       <c r="G40" s="90" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H40" s="180">
         <v>3.3411111111111107</v>
@@ -24657,7 +24732,7 @@
     </row>
     <row r="41">
       <c r="C41" s="185" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D41" s="172">
         <f t="shared" si="17"/>
@@ -24689,7 +24764,7 @@
     </row>
     <row r="42">
       <c r="C42" s="185" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D42" s="172">
         <f t="shared" si="17"/>
@@ -24721,7 +24796,7 @@
     </row>
     <row r="43">
       <c r="C43" s="185" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="D43" s="172">
         <f t="shared" si="17"/>
@@ -24753,7 +24828,7 @@
     </row>
     <row r="44">
       <c r="C44" s="185" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D44" s="172">
         <f t="shared" si="17"/>
@@ -24783,7 +24858,7 @@
     </row>
     <row r="45">
       <c r="C45" s="185" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D45" s="172">
         <f t="shared" si="17"/>
@@ -24801,17 +24876,17 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="C46" s="185" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D46" s="172">
         <f t="shared" si="17"/>
         <v>1.91</v>
       </c>
       <c r="G46" s="186" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="H46" s="186" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="P46" s="170">
         <v>0.0</v>
@@ -24825,14 +24900,14 @@
     </row>
     <row r="47">
       <c r="C47" s="185" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D47" s="172">
         <f t="shared" si="17"/>
         <v>0.24</v>
       </c>
       <c r="G47" s="187" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H47" s="188">
         <v>0.376453591155815</v>
@@ -24844,7 +24919,7 @@
         <v>3</v>
       </c>
       <c r="AB47" s="76" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AE47" s="76">
         <v>67.98</v>
@@ -24855,20 +24930,20 @@
     </row>
     <row r="48">
       <c r="C48" s="185" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D48" s="172">
         <f t="shared" si="17"/>
         <v>0.54</v>
       </c>
       <c r="G48" s="187" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H48" s="188">
         <v>0.36678739680281</v>
       </c>
       <c r="J48" s="76" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="K48" s="163">
         <f>AVERAGE(H47:H51)</f>
@@ -24892,20 +24967,20 @@
     </row>
     <row r="49">
       <c r="C49" s="185" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D49" s="172">
         <f t="shared" si="17"/>
         <v>3.88</v>
       </c>
       <c r="G49" s="187" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H49" s="188">
         <v>0.142870351877935</v>
       </c>
       <c r="J49" s="76" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="K49" s="163">
         <f>MEDIAN(H47:H51)</f>
@@ -24929,20 +25004,20 @@
     </row>
     <row r="50">
       <c r="C50" s="185" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D50" s="172">
         <f t="shared" si="17"/>
         <v>4.22</v>
       </c>
       <c r="G50" s="187" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H50" s="188">
         <v>0.497437843674554</v>
       </c>
       <c r="J50" s="76" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="K50" s="163">
         <f>PERCENTILE(H47:H51,0.25)</f>
@@ -24966,20 +25041,20 @@
     </row>
     <row r="51">
       <c r="C51" s="185" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D51" s="172">
         <f t="shared" si="17"/>
         <v>4.62</v>
       </c>
       <c r="G51" s="187" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H51" s="188">
         <v>0.247446036291655</v>
       </c>
       <c r="J51" s="76" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="K51" s="163">
         <f>PERCENTILE(H47:H51,0.75)</f>
@@ -25003,7 +25078,7 @@
     </row>
     <row r="52">
       <c r="C52" s="185" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="D52" s="172">
         <f t="shared" si="17"/>
@@ -25027,7 +25102,7 @@
     </row>
     <row r="53">
       <c r="C53" s="185" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D53" s="172">
         <f t="shared" si="17"/>
@@ -25051,7 +25126,7 @@
     </row>
     <row r="54">
       <c r="C54" s="185" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D54" s="172">
         <f t="shared" si="17"/>
@@ -25075,7 +25150,7 @@
     </row>
     <row r="55">
       <c r="C55" s="185" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D55" s="172">
         <f t="shared" si="17"/>
@@ -25099,7 +25174,7 @@
     </row>
     <row r="56">
       <c r="C56" s="185" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D56" s="172">
         <f t="shared" si="17"/>
@@ -25123,7 +25198,7 @@
     </row>
     <row r="57">
       <c r="C57" s="185" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D57" s="172">
         <f t="shared" si="17"/>
@@ -25147,14 +25222,14 @@
     </row>
     <row r="58">
       <c r="C58" s="185" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D58" s="172">
         <f t="shared" si="17"/>
         <v>6.81</v>
       </c>
       <c r="G58" s="189" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="H58" s="190"/>
       <c r="P58" s="170">
@@ -25175,7 +25250,7 @@
     </row>
     <row r="59">
       <c r="C59" s="185" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="D59" s="172">
         <f t="shared" si="17"/>
@@ -25183,7 +25258,7 @@
       </c>
       <c r="G59" s="190"/>
       <c r="H59" s="191" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="P59" s="170">
         <v>0.0</v>
@@ -25203,7 +25278,7 @@
     </row>
     <row r="60">
       <c r="C60" s="185" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D60" s="172">
         <f t="shared" si="17"/>
@@ -25211,7 +25286,7 @@
       </c>
       <c r="G60" s="190"/>
       <c r="H60" s="191" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="P60" s="170">
         <v>2.0</v>
@@ -25231,7 +25306,7 @@
     </row>
     <row r="61">
       <c r="C61" s="185" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D61" s="172">
         <f t="shared" si="17"/>
@@ -25239,7 +25314,7 @@
       </c>
       <c r="G61" s="190"/>
       <c r="H61" s="191" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="P61" s="170">
         <v>2.0</v>
@@ -25259,7 +25334,7 @@
     </row>
     <row r="62">
       <c r="C62" s="185" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D62" s="172">
         <f t="shared" si="17"/>
@@ -25267,7 +25342,7 @@
       </c>
       <c r="G62" s="190"/>
       <c r="H62" s="191" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="P62" s="170">
         <v>1.0</v>
@@ -25287,7 +25362,7 @@
     </row>
     <row r="63">
       <c r="C63" s="185" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D63" s="172">
         <f t="shared" si="17"/>
@@ -25295,7 +25370,7 @@
       </c>
       <c r="G63" s="190"/>
       <c r="H63" s="191" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="P63" s="170">
         <v>0.0</v>
@@ -25309,7 +25384,7 @@
     </row>
     <row r="64">
       <c r="C64" s="185" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D64" s="172">
         <f t="shared" si="17"/>
@@ -25327,7 +25402,7 @@
     </row>
     <row r="65">
       <c r="C65" s="185" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D65" s="172">
         <f t="shared" si="17"/>
@@ -25345,7 +25420,7 @@
     </row>
     <row r="66">
       <c r="C66" s="185" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D66" s="172">
         <f t="shared" si="17"/>
@@ -25363,7 +25438,7 @@
     </row>
     <row r="67">
       <c r="C67" s="185" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D67" s="172">
         <f t="shared" si="17"/>
@@ -25381,7 +25456,7 @@
     </row>
     <row r="68">
       <c r="C68" s="185" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D68" s="172">
         <f t="shared" si="17"/>
@@ -25399,7 +25474,7 @@
     </row>
     <row r="69">
       <c r="C69" s="185" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D69" s="172">
         <f t="shared" si="17"/>
@@ -25417,7 +25492,7 @@
     </row>
     <row r="70">
       <c r="C70" s="185" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D70" s="172">
         <f t="shared" si="17"/>
@@ -25435,7 +25510,7 @@
     </row>
     <row r="71">
       <c r="C71" s="185" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D71" s="172">
         <f t="shared" si="17"/>
@@ -25454,7 +25529,7 @@
     </row>
     <row r="72">
       <c r="C72" s="185" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D72" s="172">
         <f t="shared" si="17"/>
@@ -25472,7 +25547,7 @@
     </row>
     <row r="73">
       <c r="C73" s="185" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D73" s="172">
         <f t="shared" si="17"/>
@@ -25490,7 +25565,7 @@
     </row>
     <row r="74">
       <c r="C74" s="185" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D74" s="172">
         <f t="shared" si="17"/>
@@ -25508,7 +25583,7 @@
     </row>
     <row r="75">
       <c r="C75" s="185" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D75" s="172">
         <f t="shared" si="17"/>
@@ -25526,7 +25601,7 @@
     </row>
     <row r="76">
       <c r="C76" s="185" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D76" s="172">
         <f t="shared" si="17"/>
@@ -25544,7 +25619,7 @@
     </row>
     <row r="77">
       <c r="C77" s="185" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D77" s="172">
         <f t="shared" si="17"/>
@@ -25562,7 +25637,7 @@
     </row>
     <row r="78">
       <c r="C78" s="185" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D78" s="172">
         <f t="shared" si="17"/>
@@ -25580,7 +25655,7 @@
     </row>
     <row r="79">
       <c r="C79" s="185" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D79" s="172">
         <f t="shared" si="17"/>
@@ -25598,7 +25673,7 @@
     </row>
     <row r="80">
       <c r="C80" s="185" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D80" s="172">
         <f t="shared" si="17"/>
@@ -25616,7 +25691,7 @@
     </row>
     <row r="81">
       <c r="C81" s="185" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D81" s="172">
         <f t="shared" si="17"/>
@@ -25634,7 +25709,7 @@
     </row>
     <row r="82">
       <c r="C82" s="185" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D82" s="172">
         <f t="shared" si="17"/>
@@ -25652,7 +25727,7 @@
     </row>
     <row r="83">
       <c r="C83" s="185" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D83" s="172">
         <f t="shared" si="17"/>
@@ -25670,7 +25745,7 @@
     </row>
     <row r="84">
       <c r="C84" s="185" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D84" s="172">
         <f t="shared" si="17"/>
@@ -25688,7 +25763,7 @@
     </row>
     <row r="85">
       <c r="C85" s="185" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D85" s="172">
         <f t="shared" si="17"/>
@@ -25706,7 +25781,7 @@
     </row>
     <row r="86">
       <c r="C86" s="185" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="D86" s="172">
         <f t="shared" si="17"/>
@@ -25724,7 +25799,7 @@
     </row>
     <row r="87">
       <c r="C87" s="185" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D87" s="172">
         <f t="shared" si="17"/>
@@ -25742,7 +25817,7 @@
     </row>
     <row r="88">
       <c r="C88" s="185" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D88" s="172">
         <f t="shared" si="17"/>
@@ -25760,7 +25835,7 @@
     </row>
     <row r="89">
       <c r="C89" s="185" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D89" s="172">
         <f t="shared" si="17"/>
@@ -25778,7 +25853,7 @@
     </row>
     <row r="90">
       <c r="C90" s="185" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D90" s="172">
         <f t="shared" si="17"/>
@@ -25796,7 +25871,7 @@
     </row>
     <row r="91">
       <c r="C91" s="185" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D91" s="172">
         <f t="shared" si="17"/>
@@ -25814,7 +25889,7 @@
     </row>
     <row r="92">
       <c r="C92" s="185" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D92" s="172">
         <f t="shared" si="17"/>
@@ -25832,7 +25907,7 @@
     </row>
     <row r="93">
       <c r="C93" s="185" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D93" s="172">
         <f t="shared" si="17"/>
@@ -25850,7 +25925,7 @@
     </row>
     <row r="94">
       <c r="C94" s="185" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D94" s="172">
         <f t="shared" si="17"/>
@@ -25868,7 +25943,7 @@
     </row>
     <row r="95">
       <c r="C95" s="185" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D95" s="172">
         <f t="shared" si="17"/>
@@ -25886,7 +25961,7 @@
     </row>
     <row r="96">
       <c r="C96" s="185" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D96" s="172">
         <f t="shared" si="17"/>
@@ -48780,14 +48855,14 @@
     <row r="1">
       <c r="A1" s="197"/>
       <c r="B1" s="198" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C1" s="199"/>
       <c r="D1" s="199"/>
       <c r="E1" s="199"/>
       <c r="F1" s="199"/>
       <c r="G1" s="200" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="H1" s="199"/>
       <c r="I1" s="199"/>
@@ -48821,54 +48896,54 @@
         <v>3</v>
       </c>
       <c r="B2" s="202" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C2" s="203" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D2" s="203" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E2" s="203" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F2" s="204" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="G2" s="202">
         <v>1.0</v>
       </c>
       <c r="H2" s="203" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="I2" s="203">
         <v>2.0</v>
       </c>
       <c r="J2" s="203" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="K2" s="205" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="L2" s="203" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="M2" s="206" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="N2" s="187" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="O2" s="187" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="P2" s="187" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Q2" s="17"/>
       <c r="R2" s="17"/>
       <c r="S2" s="6" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="T2" s="17"/>
       <c r="U2" s="17"/>
@@ -48958,7 +49033,7 @@
       <c r="Q4" s="17"/>
       <c r="R4" s="17"/>
       <c r="S4" s="212" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="T4" s="213"/>
       <c r="Z4" s="90"/>
@@ -48994,7 +49069,7 @@
       <c r="P5" s="215"/>
       <c r="S5" s="213"/>
       <c r="T5" s="216" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="6">
@@ -49027,11 +49102,11 @@
       <c r="R6" s="17"/>
       <c r="S6" s="213"/>
       <c r="T6" s="216" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="Z6" s="151"/>
       <c r="AD6" s="76" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="7">
@@ -49061,7 +49136,7 @@
       <c r="O7" s="143"/>
       <c r="P7" s="218"/>
       <c r="AD7" s="216" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AE7" s="213"/>
       <c r="AF7" s="213"/>
@@ -49094,11 +49169,11 @@
       <c r="O8" s="143"/>
       <c r="P8" s="218"/>
       <c r="S8" s="216" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AA8" s="151"/>
       <c r="AD8" s="216" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9">
@@ -49297,7 +49372,7 @@
       <c r="O15" s="143"/>
       <c r="P15" s="218"/>
       <c r="S15" s="76" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="16">
@@ -49410,7 +49485,7 @@
       <c r="Q19" s="17"/>
       <c r="R19" s="17"/>
       <c r="S19" s="76" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="20">
@@ -49548,7 +49623,7 @@
     </row>
     <row r="24">
       <c r="A24" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B24" s="222" t="str">
         <f t="shared" ref="B24:F24" si="4">IFERROR(AVERAGE(B3:B22),"")</f>
@@ -49624,7 +49699,7 @@
       <c r="Q25" s="17"/>
       <c r="R25" s="17"/>
       <c r="S25" s="23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T25" s="76">
         <v>1172.0</v>
@@ -49665,7 +49740,7 @@
       <c r="Q26" s="17"/>
       <c r="R26" s="17"/>
       <c r="S26" s="20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="T26" s="76">
         <v>411.0</v>
@@ -49694,7 +49769,7 @@
       <c r="E27" s="17"/>
       <c r="F27" s="17"/>
       <c r="G27" s="223" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="H27" s="17"/>
       <c r="I27" s="17"/>
@@ -49707,7 +49782,7 @@
       <c r="Q27" s="17"/>
       <c r="R27" s="17"/>
       <c r="S27" s="20" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="T27" s="76">
         <v>1267.0</v>
@@ -49739,7 +49814,7 @@
         <v>1.0</v>
       </c>
       <c r="H28" s="224" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="I28" s="224">
         <v>2.0</v>
@@ -49753,7 +49828,7 @@
       <c r="Q28" s="17"/>
       <c r="R28" s="17"/>
       <c r="S28" s="20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="T28" s="76">
         <v>770.0</v>
@@ -49779,7 +49854,7 @@
       <c r="B29" s="17"/>
       <c r="C29" s="17"/>
       <c r="D29" s="4" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E29" s="4">
         <f>J29</f>
@@ -49801,10 +49876,10 @@
       </c>
       <c r="K29" s="17"/>
       <c r="L29" s="6" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="O29" s="4">
         <v>1.0</v>
@@ -49904,7 +49979,7 @@
       </c>
       <c r="R31" s="17"/>
       <c r="S31" s="6" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="T31" s="17"/>
       <c r="U31" s="17"/>
@@ -49966,7 +50041,7 @@
       <c r="E33" s="17"/>
       <c r="F33" s="17"/>
       <c r="G33" s="168" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="J33" s="17"/>
       <c r="K33" s="17"/>
@@ -49980,10 +50055,10 @@
       <c r="P33" s="17"/>
       <c r="R33" s="17"/>
       <c r="T33" s="93" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="W33" s="76" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AA33" s="90"/>
       <c r="AD33" s="17"/>
@@ -50002,7 +50077,7 @@
         <v>1.0</v>
       </c>
       <c r="H34" s="227" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="I34" s="227">
         <v>2.0</v>
@@ -50026,7 +50101,7 @@
         <v>1626.0</v>
       </c>
       <c r="U34" s="83" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="W34" s="76">
         <v>5193.0</v>
@@ -50065,13 +50140,13 @@
       <c r="P35" s="17"/>
       <c r="R35" s="17"/>
       <c r="S35" s="107" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T35" s="83">
         <v>4176.0</v>
       </c>
       <c r="U35" s="83" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="W35" s="76">
         <v>4863.0</v>
@@ -50113,7 +50188,7 @@
       <c r="P36" s="17"/>
       <c r="R36" s="17"/>
       <c r="S36" s="76" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="T36" s="83">
         <v>5130.0</v>
@@ -50148,7 +50223,7 @@
       <c r="Q37" s="17"/>
       <c r="R37" s="17"/>
       <c r="S37" s="76" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="T37" s="83">
         <v>2114.0</v>
@@ -50169,7 +50244,7 @@
       <c r="D38" s="17"/>
       <c r="E38" s="17"/>
       <c r="F38" s="4" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="G38" s="226">
         <f t="shared" ref="G38:I38" si="8">G30-G35</f>
@@ -50197,7 +50272,7 @@
       <c r="Q38" s="17"/>
       <c r="R38" s="17"/>
       <c r="S38" s="76" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="T38" s="230"/>
       <c r="U38" s="230"/>
@@ -50371,7 +50446,7 @@
       <c r="Q45" s="17"/>
       <c r="R45" s="17"/>
       <c r="T45" s="216" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AD45" s="17"/>
       <c r="AE45" s="17"/>
@@ -50508,10 +50583,10 @@
         <v>4</v>
       </c>
       <c r="X49" s="4" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="Y49" s="4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Z49" s="4" t="s">
         <v>5</v>
@@ -50526,16 +50601,16 @@
         <v>8</v>
       </c>
       <c r="AD49" s="4" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AE49" s="60" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AF49" s="60" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AG49" s="60" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="50">
@@ -50700,7 +50775,7 @@
         <v>13.03594852814783</v>
       </c>
       <c r="AG52" s="60" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="53">
@@ -50730,7 +50805,7 @@
         <v>55.0</v>
       </c>
       <c r="T53" s="17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U53" s="232">
         <v>45719.0</v>
@@ -50761,7 +50836,7 @@
         <v>6.291840048860032</v>
       </c>
       <c r="AG53" s="60" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="54">
@@ -50791,7 +50866,7 @@
         <v>59.0</v>
       </c>
       <c r="T54" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U54" s="232">
         <v>45720.0</v>
@@ -50822,7 +50897,7 @@
         <v>2.7243520649411117</v>
       </c>
       <c r="AG54" s="60" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="55">
@@ -50852,7 +50927,7 @@
         <v>77.0</v>
       </c>
       <c r="T55" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="U55" s="232">
         <v>45720.0</v>
@@ -50883,7 +50958,7 @@
         <v>2.1429979739456915</v>
       </c>
       <c r="AG55" s="60" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="56">
@@ -50913,7 +50988,7 @@
         <v>148.0</v>
       </c>
       <c r="T56" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="U56" s="232">
         <v>45720.0</v>
@@ -50944,7 +51019,7 @@
         <v>3.98032040346951</v>
       </c>
       <c r="AG56" s="60" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="57">
@@ -51167,10 +51242,10 @@
       <c r="R62" s="17"/>
       <c r="S62" s="17"/>
       <c r="U62" s="76" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="V62" s="76" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AC62" s="17"/>
       <c r="AD62" s="17"/>
@@ -51212,7 +51287,7 @@
         <v>2165.0</v>
       </c>
       <c r="W63" s="76" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AC63" s="17"/>
       <c r="AD63" s="17"/>
@@ -51245,7 +51320,7 @@
       <c r="R64" s="17"/>
       <c r="S64" s="17"/>
       <c r="T64" s="23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U64" s="76">
         <v>4863.0</v>
@@ -51284,7 +51359,7 @@
       <c r="R65" s="17"/>
       <c r="S65" s="17"/>
       <c r="T65" s="20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U65" s="76">
         <v>4954.0</v>
@@ -51323,7 +51398,7 @@
       <c r="R66" s="17"/>
       <c r="S66" s="17"/>
       <c r="T66" s="20" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="U66" s="76">
         <v>5132.0</v>
@@ -51362,7 +51437,7 @@
       <c r="R67" s="17"/>
       <c r="S67" s="17"/>
       <c r="T67" s="20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="U67" s="76">
         <v>3490.0</v>
@@ -51518,7 +51593,7 @@
       <c r="S71" s="17"/>
       <c r="T71" s="17"/>
       <c r="U71" s="23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="V71" s="77">
         <v>4522.0</v>
@@ -51559,7 +51634,7 @@
       <c r="S72" s="17"/>
       <c r="T72" s="17"/>
       <c r="U72" s="20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="V72" s="99">
         <v>5130.0</v>
@@ -51603,7 +51678,7 @@
       <c r="S73" s="17"/>
       <c r="T73" s="17"/>
       <c r="U73" s="20" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="V73" s="77">
         <v>2516.0</v>
@@ -51647,7 +51722,7 @@
       <c r="S74" s="17"/>
       <c r="T74" s="17"/>
       <c r="U74" s="20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="V74" s="83">
         <v>5142.0</v>
@@ -51846,7 +51921,7 @@
       <c r="R79" s="17"/>
       <c r="S79" s="17"/>
       <c r="T79" s="6" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="U79" s="17"/>
       <c r="V79" s="17"/>
@@ -51887,7 +51962,7 @@
       <c r="R80" s="17"/>
       <c r="S80" s="17"/>
       <c r="T80" s="76" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="U80" s="21"/>
       <c r="V80" s="21"/>
@@ -51984,7 +52059,7 @@
         <v>3960.0</v>
       </c>
       <c r="V82" s="23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W82" s="76">
         <v>80.0</v>
@@ -52038,7 +52113,7 @@
         <v>3032.0</v>
       </c>
       <c r="V83" s="20" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="W83" s="76">
         <v>80.0</v>
@@ -52092,7 +52167,7 @@
         <v>2114.0</v>
       </c>
       <c r="V84" s="20" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="W84" s="76">
         <v>120.0</v>
@@ -52146,7 +52221,7 @@
         <v>870.0</v>
       </c>
       <c r="V85" s="20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="W85" s="76">
         <v>130.0</v>

--- a/data/df_best_models.xlsx
+++ b/data/df_best_models.xlsx
@@ -44,9 +44,9 @@
         <t xml:space="preserve">Alarma si llega a 20%. En ese caso, podria ser conveniente reentrenar modellos</t>
       </text>
     </comment>
-    <comment authorId="0" ref="D4">
+    <comment authorId="0" ref="G4">
       <text>
-        <t xml:space="preserve">al menos por hoy, para no tener que decidir cual empata</t>
+        <t xml:space="preserve">Leccion aprendida: los empates de ENG siempre se deberian haber dado pero nunca se dan. Ir mas por 2. Las GP por rdo te lo indican.</t>
       </text>
     </comment>
     <comment authorId="0" ref="L4">
@@ -310,6 +310,11 @@
 mal error.</t>
       </text>
     </comment>
+    <comment authorId="0" ref="L28">
+      <text>
+        <t xml:space="preserve">Dice 1 y bet 2, no le pretendo ganar en eso. No deja pasar un local.</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -515,7 +520,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="893" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="464">
   <si>
     <t>id_country</t>
   </si>
@@ -1542,28 +1547,28 @@
     <t>Stake promedio</t>
   </si>
   <si>
-    <t>1.39</t>
+    <t>0.30</t>
   </si>
   <si>
-    <t>1.50</t>
+    <t>0.77</t>
   </si>
   <si>
-    <t>0.46</t>
+    <t>2.44</t>
   </si>
   <si>
-    <t>0.84</t>
+    <t>2.20</t>
   </si>
   <si>
-    <t>2.83</t>
+    <t>1.16</t>
   </si>
   <si>
-    <t>1.52</t>
+    <t>1.88</t>
   </si>
   <si>
-    <t>1.94</t>
+    <t>0.61</t>
   </si>
   <si>
-    <t>1.91</t>
+    <t>2.60</t>
   </si>
   <si>
     <t>Country</t>
@@ -1572,88 +1577,79 @@
     <t>Correl ROI y Expected ROI</t>
   </si>
   <si>
-    <t>0.24</t>
+    <t>4.31</t>
   </si>
   <si>
-    <t>0.54</t>
+    <t>4.62</t>
   </si>
   <si>
     <t>mean</t>
   </si>
   <si>
-    <t>3.88</t>
+    <t>6.06</t>
   </si>
   <si>
     <t>median</t>
   </si>
   <si>
-    <t>4.22</t>
+    <t>4.16</t>
   </si>
   <si>
     <t>p25</t>
   </si>
   <si>
-    <t>4.62</t>
+    <t>4.83</t>
   </si>
   <si>
     <t>p75</t>
   </si>
   <si>
-    <t>5.77</t>
+    <t>6.12</t>
   </si>
   <si>
-    <t>3.56</t>
+    <t>4.02</t>
   </si>
   <si>
-    <t>3.78</t>
+    <t>7.42</t>
   </si>
   <si>
-    <t>5.26</t>
+    <t>1.17</t>
   </si>
   <si>
-    <t>5.86</t>
+    <t>0.79</t>
   </si>
   <si>
-    <t>4.45</t>
-  </si>
-  <si>
-    <t>6.81</t>
+    <t>0.86</t>
   </si>
   <si>
     <t>Gracias a las nuevas métricas de G/P sin bank en test, me di cuenta de que:</t>
   </si>
   <si>
-    <t>1.35</t>
+    <t>1.32</t>
   </si>
   <si>
     <t>La rentabilidad en ITA está en el visitante y no en el empate como creía.</t>
   </si>
   <si>
-    <t>1.69</t>
+    <t>2.47</t>
   </si>
   <si>
     <t>La rentabilidad en ENG y GER está en el empate tal como creía.</t>
   </si>
   <si>
-    <t>0.86</t>
+    <t>0.97</t>
   </si>
   <si>
     <t>En SPA esta repartido aunque Empate saca una ventaja.</t>
   </si>
   <si>
-    <t>1.24</t>
+    <t>1.73</t>
   </si>
   <si>
     <t>En FRA, depende el modelo. A veces local, a veces, empate.</t>
   </si>
   <si>
-    <t>2.38</t>
-  </si>
-  <si>
     <t>Si en FRA empate no rinde, no tiene sentido exigirle una buena distrib en empate… → Tiene sentido pero al parecer si importa el empate puesto que el modelo que gana se basa en empate.</t>
-  </si>
-  <si>
-    <t>1.73</t>
   </si>
   <si>
     <t>3.92</t>
@@ -1663,6 +1659,9 @@
   </si>
   <si>
     <t>1.96</t>
+  </si>
+  <si>
+    <t>3.78</t>
   </si>
   <si>
     <t>2.94</t>
@@ -1686,13 +1685,16 @@
     <t>9.13</t>
   </si>
   <si>
+    <t>5.79</t>
+  </si>
+  <si>
     <t>3.00</t>
   </si>
   <si>
     <t>1.90</t>
   </si>
   <si>
-    <t>0.39</t>
+    <t>0.40</t>
   </si>
   <si>
     <t>5.85</t>
@@ -1701,7 +1703,7 @@
     <t>5.70</t>
   </si>
   <si>
-    <t>3.14</t>
+    <t>3.17</t>
   </si>
   <si>
     <t>5.67</t>
@@ -1710,28 +1712,34 @@
     <t>3.55</t>
   </si>
   <si>
-    <t>2.42</t>
+    <t>5.76</t>
   </si>
   <si>
-    <t>2.64</t>
-  </si>
-  <si>
-    <t>3.50</t>
-  </si>
-  <si>
-    <t>1.99</t>
+    <t>2.02</t>
   </si>
   <si>
     <t>2.27</t>
   </si>
   <si>
-    <t>2.55</t>
+    <t>3.12</t>
   </si>
   <si>
-    <t>1.81</t>
+    <t>1.97</t>
   </si>
   <si>
-    <t>2.16</t>
+    <t>3.41</t>
+  </si>
+  <si>
+    <t>5.59</t>
+  </si>
+  <si>
+    <t>5.41</t>
+  </si>
+  <si>
+    <t>2.31</t>
+  </si>
+  <si>
+    <t>2.34</t>
   </si>
   <si>
     <t>RENTABILIDAD</t>
@@ -3593,14 +3601,14 @@
         <v>5.0</v>
       </c>
       <c r="G4" s="24">
-        <v>12.8</v>
+        <v>6.58</v>
       </c>
       <c r="H4" s="24">
-        <v>10.79</v>
+        <v>11.42</v>
       </c>
       <c r="I4" s="24">
         <f t="shared" ref="I4:I8" si="1">AVERAGE(F4:H4)</f>
-        <v>9.53</v>
+        <v>7.666666667</v>
       </c>
       <c r="J4" s="25">
         <v>5.0</v>
@@ -3688,7 +3696,7 @@
         <v>45739.0</v>
       </c>
       <c r="D6" s="14">
-        <v>900.0</v>
+        <v>563.0</v>
       </c>
       <c r="E6" s="14" t="s">
         <v>17</v>
@@ -3697,14 +3705,14 @@
         <v>5.0</v>
       </c>
       <c r="G6" s="24">
-        <v>8.16</v>
+        <v>7.11</v>
       </c>
       <c r="H6" s="24">
-        <v>13.42</v>
+        <v>8.68</v>
       </c>
       <c r="I6" s="24">
         <f t="shared" si="1"/>
-        <v>8.86</v>
+        <v>6.93</v>
       </c>
       <c r="J6" s="25">
         <v>1.0</v>
@@ -8856,146 +8864,146 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="76" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="2">
       <c r="B2" s="17"/>
       <c r="C2" s="5" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E2" s="235"/>
       <c r="F2" s="6" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H2" s="235"/>
     </row>
     <row r="3">
       <c r="B3" s="186" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C3" s="236" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D3" s="186" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E3" s="237" t="s">
         <v>214</v>
       </c>
       <c r="F3" s="186" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="G3" s="186" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H3" s="186" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="238" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C4" s="239" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D4" s="187" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E4" s="240" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F4" s="241" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="G4" s="241" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H4" s="187"/>
     </row>
     <row r="5">
       <c r="B5" s="238" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C5" s="242" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D5" s="197"/>
       <c r="E5" s="240" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F5" s="243" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="G5" s="244" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H5" s="187"/>
     </row>
     <row r="6">
       <c r="B6" s="238" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C6" s="239" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D6" s="187" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E6" s="240" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F6" s="187" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="G6" s="187"/>
       <c r="H6" s="187"/>
     </row>
     <row r="7">
       <c r="B7" s="187" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C7" s="245" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D7" s="187"/>
       <c r="E7" s="246" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F7" s="239" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="G7" s="187"/>
       <c r="H7" s="187" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="247" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C8" s="248" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D8" s="249"/>
       <c r="E8" s="247" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F8" s="250" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="G8" s="251" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H8" s="249"/>
     </row>
     <row r="9">
       <c r="B9" s="20" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C9" s="252" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D9" s="143"/>
       <c r="E9" s="143"/>
@@ -9005,27 +9013,27 @@
     </row>
     <row r="10">
       <c r="B10" s="20" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C10" s="217"/>
       <c r="D10" s="143"/>
       <c r="E10" s="143"/>
       <c r="F10" s="217"/>
       <c r="G10" s="241" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H10" s="143"/>
     </row>
     <row r="11">
       <c r="B11" s="20" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C11" s="217"/>
       <c r="D11" s="143"/>
       <c r="E11" s="143"/>
       <c r="F11" s="217"/>
       <c r="G11" s="253" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H11" s="20"/>
     </row>
@@ -9048,7 +9056,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="90" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="L1" s="32"/>
     </row>
@@ -9057,16 +9065,16 @@
     </row>
     <row r="3">
       <c r="A3" s="76" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L3" s="32"/>
     </row>
     <row r="4">
       <c r="B4" s="76" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="G4" s="76" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="L4" s="32"/>
     </row>
@@ -9172,45 +9180,45 @@
     </row>
     <row r="11">
       <c r="A11" s="254" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="90" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="76" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="254" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="90" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="76" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F19" s="151"/>
     </row>
     <row r="20">
       <c r="B20" s="90" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C20" s="105"/>
       <c r="D20" s="105"/>
       <c r="E20" s="105"/>
       <c r="F20" s="105"/>
       <c r="G20" s="90" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H20" s="90" t="s">
         <v>66</v>
@@ -9227,7 +9235,7 @@
     </row>
     <row r="21">
       <c r="B21" s="90" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G21" s="107">
         <v>2.575</v>
@@ -9235,27 +9243,27 @@
     </row>
     <row r="23">
       <c r="K23" s="90" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="76" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H24" s="76" t="s">
         <v>44</v>
       </c>
       <c r="I24" s="76" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="K24" s="76" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L24" s="76" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M24" s="76" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="25">
@@ -9274,7 +9282,7 @@
         <v>#REF!</v>
       </c>
       <c r="K25" s="76" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="26">
@@ -9285,7 +9293,7 @@
         <v>1.19</v>
       </c>
       <c r="K26" s="76" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="27">
@@ -9296,7 +9304,7 @@
         <v>2.19</v>
       </c>
       <c r="K27" s="76" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="28">
@@ -9307,7 +9315,7 @@
         <v>0.05</v>
       </c>
       <c r="K28" s="76" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="29">
@@ -9326,7 +9334,7 @@
         <v>6.42</v>
       </c>
       <c r="K30" s="93" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="31">
@@ -9471,7 +9479,7 @@
         <v>0.61</v>
       </c>
       <c r="K41" s="90" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="42">
@@ -9482,13 +9490,13 @@
         <v>0.69</v>
       </c>
       <c r="K42" s="76" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L42" s="76" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="M42" s="76" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="43">
@@ -9620,7 +9628,7 @@
         <v>0.0</v>
       </c>
       <c r="K51" s="76" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="52">
@@ -9648,17 +9656,17 @@
       </c>
       <c r="K54" s="143"/>
       <c r="L54" s="255" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M54" s="256"/>
       <c r="N54" s="148" t="s">
         <v>157</v>
       </c>
       <c r="O54" s="148" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="P54" s="148" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="R54" s="79" t="s">
         <v>224</v>
@@ -9740,7 +9748,7 @@
         <v>5.86</v>
       </c>
       <c r="R57" s="76" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="S57" s="107">
         <f>SUM(P55:P74)</f>
@@ -9769,7 +9777,7 @@
         <v>0.855</v>
       </c>
       <c r="P58" s="20" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="59">
@@ -9816,7 +9824,7 @@
         <v>0.96</v>
       </c>
       <c r="P60" s="20" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="61">
@@ -17249,17 +17257,26 @@
       <c r="D28" s="76" t="s">
         <v>105</v>
       </c>
-      <c r="E28" s="77">
+      <c r="E28" s="76">
+        <v>563.0</v>
+      </c>
+      <c r="F28" s="76">
+        <v>766.0</v>
+      </c>
+      <c r="H28" s="76">
+        <v>385.0</v>
+      </c>
+      <c r="L28" s="76">
         <v>900.0</v>
       </c>
-      <c r="F28" s="76">
+      <c r="M28" s="76">
         <v>457.0</v>
       </c>
-      <c r="H28" s="76">
+      <c r="N28" s="76">
+        <v>899.0</v>
+      </c>
+      <c r="O28" s="76">
         <v>424.0</v>
-      </c>
-      <c r="I28" s="76">
-        <v>899.0</v>
       </c>
     </row>
     <row r="29">
@@ -24591,7 +24608,7 @@
       <c r="C37" s="105"/>
       <c r="D37" s="181">
         <f>AVERAGE(D39:D1775)</f>
-        <v>3.140689655</v>
+        <v>3.399830508</v>
       </c>
       <c r="G37" s="90" t="s">
         <v>35</v>
@@ -24660,7 +24677,7 @@
       </c>
       <c r="D39" s="184">
         <f t="shared" ref="D39:D221" si="17">IF(COUNTA(C39)=1,C39/1,"")</f>
-        <v>1.39</v>
+        <v>0.3</v>
       </c>
       <c r="G39" s="90" t="s">
         <v>38</v>
@@ -24698,7 +24715,7 @@
       </c>
       <c r="D40" s="172">
         <f t="shared" si="17"/>
-        <v>1.5</v>
+        <v>0.77</v>
       </c>
       <c r="G40" s="90" t="s">
         <v>39</v>
@@ -24736,7 +24753,7 @@
       </c>
       <c r="D41" s="172">
         <f t="shared" si="17"/>
-        <v>0.46</v>
+        <v>2.44</v>
       </c>
       <c r="P41" s="170">
         <v>0.0</v>
@@ -24768,7 +24785,7 @@
       </c>
       <c r="D42" s="172">
         <f t="shared" si="17"/>
-        <v>0.84</v>
+        <v>2.2</v>
       </c>
       <c r="P42" s="170">
         <v>2.0</v>
@@ -24800,7 +24817,7 @@
       </c>
       <c r="D43" s="172">
         <f t="shared" si="17"/>
-        <v>2.83</v>
+        <v>1.16</v>
       </c>
       <c r="P43" s="170">
         <v>1.0</v>
@@ -24832,7 +24849,7 @@
       </c>
       <c r="D44" s="172">
         <f t="shared" si="17"/>
-        <v>1.52</v>
+        <v>1.88</v>
       </c>
       <c r="P44" s="170">
         <v>2.0</v>
@@ -24862,7 +24879,7 @@
       </c>
       <c r="D45" s="172">
         <f t="shared" si="17"/>
-        <v>1.94</v>
+        <v>0.61</v>
       </c>
       <c r="P45" s="170">
         <v>1.0</v>
@@ -24880,7 +24897,7 @@
       </c>
       <c r="D46" s="172">
         <f t="shared" si="17"/>
-        <v>1.91</v>
+        <v>2.6</v>
       </c>
       <c r="G46" s="186" t="s">
         <v>299</v>
@@ -24904,7 +24921,7 @@
       </c>
       <c r="D47" s="172">
         <f t="shared" si="17"/>
-        <v>0.24</v>
+        <v>4.31</v>
       </c>
       <c r="G47" s="187" t="s">
         <v>34</v>
@@ -24934,7 +24951,7 @@
       </c>
       <c r="D48" s="172">
         <f t="shared" si="17"/>
-        <v>0.54</v>
+        <v>4.62</v>
       </c>
       <c r="G48" s="187" t="s">
         <v>35</v>
@@ -24971,7 +24988,7 @@
       </c>
       <c r="D49" s="172">
         <f t="shared" si="17"/>
-        <v>3.88</v>
+        <v>6.06</v>
       </c>
       <c r="G49" s="187" t="s">
         <v>37</v>
@@ -25008,7 +25025,7 @@
       </c>
       <c r="D50" s="172">
         <f t="shared" si="17"/>
-        <v>4.22</v>
+        <v>4.16</v>
       </c>
       <c r="G50" s="187" t="s">
         <v>38</v>
@@ -25045,7 +25062,7 @@
       </c>
       <c r="D51" s="172">
         <f t="shared" si="17"/>
-        <v>4.62</v>
+        <v>4.83</v>
       </c>
       <c r="G51" s="187" t="s">
         <v>39</v>
@@ -25082,7 +25099,7 @@
       </c>
       <c r="D52" s="172">
         <f t="shared" si="17"/>
-        <v>5.77</v>
+        <v>6.12</v>
       </c>
       <c r="P52" s="170">
         <v>0.0</v>
@@ -25102,11 +25119,11 @@
     </row>
     <row r="53">
       <c r="C53" s="185" t="s">
-        <v>311</v>
+        <v>258</v>
       </c>
       <c r="D53" s="172">
         <f t="shared" si="17"/>
-        <v>3.56</v>
+        <v>5.94</v>
       </c>
       <c r="P53" s="170">
         <v>0.0</v>
@@ -25126,11 +25143,11 @@
     </row>
     <row r="54">
       <c r="C54" s="185" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D54" s="172">
         <f t="shared" si="17"/>
-        <v>3.78</v>
+        <v>4.02</v>
       </c>
       <c r="P54" s="170">
         <v>2.0</v>
@@ -25150,11 +25167,11 @@
     </row>
     <row r="55">
       <c r="C55" s="185" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D55" s="172">
         <f t="shared" si="17"/>
-        <v>5.26</v>
+        <v>7.42</v>
       </c>
       <c r="P55" s="170">
         <v>0.0</v>
@@ -25174,11 +25191,11 @@
     </row>
     <row r="56">
       <c r="C56" s="185" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D56" s="172">
         <f t="shared" si="17"/>
-        <v>5.86</v>
+        <v>1.17</v>
       </c>
       <c r="P56" s="170">
         <v>0.0</v>
@@ -25198,11 +25215,11 @@
     </row>
     <row r="57">
       <c r="C57" s="185" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D57" s="172">
         <f t="shared" si="17"/>
-        <v>4.45</v>
+        <v>0.79</v>
       </c>
       <c r="P57" s="170">
         <v>2.0</v>
@@ -25222,14 +25239,14 @@
     </row>
     <row r="58">
       <c r="C58" s="185" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D58" s="172">
         <f t="shared" si="17"/>
-        <v>6.81</v>
+        <v>0.86</v>
       </c>
       <c r="G58" s="189" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H58" s="190"/>
       <c r="P58" s="170">
@@ -25250,15 +25267,15 @@
     </row>
     <row r="59">
       <c r="C59" s="185" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D59" s="172">
         <f t="shared" si="17"/>
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="G59" s="190"/>
       <c r="H59" s="191" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="P59" s="170">
         <v>0.0</v>
@@ -25278,15 +25295,15 @@
     </row>
     <row r="60">
       <c r="C60" s="185" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D60" s="172">
         <f t="shared" si="17"/>
-        <v>1.69</v>
+        <v>2.47</v>
       </c>
       <c r="G60" s="190"/>
       <c r="H60" s="191" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="P60" s="170">
         <v>2.0</v>
@@ -25306,15 +25323,15 @@
     </row>
     <row r="61">
       <c r="C61" s="185" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D61" s="172">
         <f t="shared" si="17"/>
-        <v>0.86</v>
+        <v>0.97</v>
       </c>
       <c r="G61" s="190"/>
       <c r="H61" s="191" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="P61" s="170">
         <v>2.0</v>
@@ -25334,15 +25351,15 @@
     </row>
     <row r="62">
       <c r="C62" s="185" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D62" s="172">
         <f t="shared" si="17"/>
-        <v>1.24</v>
+        <v>1.73</v>
       </c>
       <c r="G62" s="190"/>
       <c r="H62" s="191" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="P62" s="170">
         <v>1.0</v>
@@ -25362,15 +25379,15 @@
     </row>
     <row r="63">
       <c r="C63" s="185" t="s">
-        <v>326</v>
+        <v>255</v>
       </c>
       <c r="D63" s="172">
         <f t="shared" si="17"/>
-        <v>2.38</v>
+        <v>3.83</v>
       </c>
       <c r="G63" s="190"/>
       <c r="H63" s="191" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="P63" s="170">
         <v>0.0</v>
@@ -25384,11 +25401,11 @@
     </row>
     <row r="64">
       <c r="C64" s="185" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D64" s="172">
         <f t="shared" si="17"/>
-        <v>1.73</v>
+        <v>3.92</v>
       </c>
       <c r="P64" s="170">
         <v>1.0</v>
@@ -25402,11 +25419,11 @@
     </row>
     <row r="65">
       <c r="C65" s="185" t="s">
-        <v>255</v>
+        <v>327</v>
       </c>
       <c r="D65" s="172">
         <f t="shared" si="17"/>
-        <v>3.83</v>
+        <v>4.91</v>
       </c>
       <c r="P65" s="170">
         <v>2.0</v>
@@ -25420,11 +25437,11 @@
     </row>
     <row r="66">
       <c r="C66" s="185" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D66" s="172">
         <f t="shared" si="17"/>
-        <v>3.92</v>
+        <v>1.96</v>
       </c>
       <c r="P66" s="170">
         <v>0.0</v>
@@ -25438,11 +25455,11 @@
     </row>
     <row r="67">
       <c r="C67" s="185" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D67" s="172">
         <f t="shared" si="17"/>
-        <v>4.91</v>
+        <v>3.78</v>
       </c>
       <c r="P67" s="170">
         <v>0.0</v>
@@ -25456,11 +25473,11 @@
     </row>
     <row r="68">
       <c r="C68" s="185" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D68" s="172">
         <f t="shared" si="17"/>
-        <v>1.96</v>
+        <v>2.94</v>
       </c>
       <c r="P68" s="170">
         <v>1.0</v>
@@ -25474,11 +25491,11 @@
     </row>
     <row r="69">
       <c r="C69" s="185" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
       <c r="D69" s="172">
         <f t="shared" si="17"/>
-        <v>3.78</v>
+        <v>2.59</v>
       </c>
       <c r="P69" s="170">
         <v>2.0</v>
@@ -25496,7 +25513,7 @@
       </c>
       <c r="D70" s="172">
         <f t="shared" si="17"/>
-        <v>2.94</v>
+        <v>2.18</v>
       </c>
       <c r="P70" s="170">
         <v>1.0</v>
@@ -25514,7 +25531,7 @@
       </c>
       <c r="D71" s="172">
         <f t="shared" si="17"/>
-        <v>2.59</v>
+        <v>2.03</v>
       </c>
       <c r="F71" s="192"/>
       <c r="P71" s="170">
@@ -25533,7 +25550,7 @@
       </c>
       <c r="D72" s="172">
         <f t="shared" si="17"/>
-        <v>2.18</v>
+        <v>3.85</v>
       </c>
       <c r="P72" s="170">
         <v>0.0</v>
@@ -25551,7 +25568,7 @@
       </c>
       <c r="D73" s="172">
         <f t="shared" si="17"/>
-        <v>2.03</v>
+        <v>7.02</v>
       </c>
       <c r="P73" s="170">
         <v>1.0</v>
@@ -25569,7 +25586,7 @@
       </c>
       <c r="D74" s="172">
         <f t="shared" si="17"/>
-        <v>3.85</v>
+        <v>9.13</v>
       </c>
       <c r="P74" s="170">
         <v>0.0</v>
@@ -25587,7 +25604,7 @@
       </c>
       <c r="D75" s="172">
         <f t="shared" si="17"/>
-        <v>7.02</v>
+        <v>5.79</v>
       </c>
       <c r="P75" s="170">
         <v>1.0</v>
@@ -25605,7 +25622,7 @@
       </c>
       <c r="D76" s="172">
         <f t="shared" si="17"/>
-        <v>9.13</v>
+        <v>3</v>
       </c>
       <c r="P76" s="170">
         <v>0.0</v>
@@ -25619,11 +25636,11 @@
     </row>
     <row r="77">
       <c r="C77" s="185" t="s">
-        <v>339</v>
+        <v>271</v>
       </c>
       <c r="D77" s="172">
         <f t="shared" si="17"/>
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="P77" s="170">
         <v>0.0</v>
@@ -25637,11 +25654,11 @@
     </row>
     <row r="78">
       <c r="C78" s="185" t="s">
-        <v>271</v>
+        <v>339</v>
       </c>
       <c r="D78" s="172">
         <f t="shared" si="17"/>
-        <v>2.71</v>
+        <v>1.9</v>
       </c>
       <c r="P78" s="170">
         <v>1.0</v>
@@ -25659,7 +25676,7 @@
       </c>
       <c r="D79" s="172">
         <f t="shared" si="17"/>
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="P79" s="170">
         <v>2.0</v>
@@ -25673,11 +25690,11 @@
     </row>
     <row r="80">
       <c r="C80" s="185" t="s">
-        <v>341</v>
+        <v>243</v>
       </c>
       <c r="D80" s="172">
         <f t="shared" si="17"/>
-        <v>0.39</v>
+        <v>5.8</v>
       </c>
       <c r="P80" s="170">
         <v>1.0</v>
@@ -25691,11 +25708,11 @@
     </row>
     <row r="81">
       <c r="C81" s="185" t="s">
-        <v>243</v>
+        <v>341</v>
       </c>
       <c r="D81" s="172">
         <f t="shared" si="17"/>
-        <v>5.8</v>
+        <v>5.85</v>
       </c>
       <c r="P81" s="170">
         <v>2.0</v>
@@ -25713,7 +25730,7 @@
       </c>
       <c r="D82" s="172">
         <f t="shared" si="17"/>
-        <v>5.85</v>
+        <v>5.7</v>
       </c>
       <c r="P82" s="170">
         <v>1.0</v>
@@ -25731,7 +25748,7 @@
       </c>
       <c r="D83" s="172">
         <f t="shared" si="17"/>
-        <v>5.7</v>
+        <v>3.17</v>
       </c>
       <c r="P83" s="170">
         <v>0.0</v>
@@ -25749,7 +25766,7 @@
       </c>
       <c r="D84" s="172">
         <f t="shared" si="17"/>
-        <v>3.14</v>
+        <v>5.67</v>
       </c>
       <c r="P84" s="170">
         <v>1.0</v>
@@ -25767,7 +25784,7 @@
       </c>
       <c r="D85" s="172">
         <f t="shared" si="17"/>
-        <v>5.67</v>
+        <v>3.55</v>
       </c>
       <c r="P85" s="170">
         <v>0.0</v>
@@ -25785,7 +25802,7 @@
       </c>
       <c r="D86" s="172">
         <f t="shared" si="17"/>
-        <v>3.55</v>
+        <v>5.76</v>
       </c>
       <c r="P86" s="170">
         <v>0.0</v>
@@ -25803,7 +25820,7 @@
       </c>
       <c r="D87" s="172">
         <f t="shared" si="17"/>
-        <v>2.42</v>
+        <v>2.02</v>
       </c>
       <c r="P87" s="170">
         <v>1.0</v>
@@ -25821,7 +25838,7 @@
       </c>
       <c r="D88" s="172">
         <f t="shared" si="17"/>
-        <v>2.64</v>
+        <v>2.27</v>
       </c>
       <c r="P88" s="170">
         <v>2.0</v>
@@ -25839,7 +25856,7 @@
       </c>
       <c r="D89" s="172">
         <f t="shared" si="17"/>
-        <v>3.5</v>
+        <v>3.12</v>
       </c>
       <c r="P89" s="170">
         <v>2.0</v>
@@ -25853,11 +25870,11 @@
     </row>
     <row r="90">
       <c r="C90" s="185" t="s">
-        <v>259</v>
+        <v>350</v>
       </c>
       <c r="D90" s="172">
         <f t="shared" si="17"/>
-        <v>3.63</v>
+        <v>1.97</v>
       </c>
       <c r="P90" s="170">
         <v>1.0</v>
@@ -25871,11 +25888,11 @@
     </row>
     <row r="91">
       <c r="C91" s="185" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D91" s="172">
         <f t="shared" si="17"/>
-        <v>1.99</v>
+        <v>3.41</v>
       </c>
       <c r="P91" s="170">
         <v>1.0</v>
@@ -25889,11 +25906,11 @@
     </row>
     <row r="92">
       <c r="C92" s="185" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="D92" s="172">
         <f t="shared" si="17"/>
-        <v>2.27</v>
+        <v>5.59</v>
       </c>
       <c r="P92" s="170">
         <v>2.0</v>
@@ -25907,11 +25924,11 @@
     </row>
     <row r="93">
       <c r="C93" s="185" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="D93" s="172">
         <f t="shared" si="17"/>
-        <v>2.71</v>
+        <v>5.56</v>
       </c>
       <c r="P93" s="170">
         <v>0.0</v>
@@ -25925,11 +25942,11 @@
     </row>
     <row r="94">
       <c r="C94" s="185" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D94" s="172">
         <f t="shared" si="17"/>
-        <v>2.55</v>
+        <v>5.41</v>
       </c>
       <c r="P94" s="170">
         <v>0.0</v>
@@ -25943,11 +25960,11 @@
     </row>
     <row r="95">
       <c r="C95" s="185" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D95" s="172">
         <f t="shared" si="17"/>
-        <v>1.81</v>
+        <v>2.31</v>
       </c>
       <c r="P95" s="170">
         <v>1.0</v>
@@ -25961,11 +25978,11 @@
     </row>
     <row r="96">
       <c r="C96" s="185" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D96" s="172">
         <f t="shared" si="17"/>
-        <v>2.16</v>
+        <v>2.34</v>
       </c>
       <c r="P96" s="170">
         <v>2.0</v>
@@ -25978,10 +25995,12 @@
       </c>
     </row>
     <row r="97">
-      <c r="C97" s="185"/>
-      <c r="D97" s="172" t="str">
+      <c r="C97" s="185" t="s">
+        <v>340</v>
+      </c>
+      <c r="D97" s="172">
         <f t="shared" si="17"/>
-        <v/>
+        <v>0.4</v>
       </c>
       <c r="P97" s="170">
         <v>0.0</v>
@@ -48855,14 +48874,14 @@
     <row r="1">
       <c r="A1" s="197"/>
       <c r="B1" s="198" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C1" s="199"/>
       <c r="D1" s="199"/>
       <c r="E1" s="199"/>
       <c r="F1" s="199"/>
       <c r="G1" s="200" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H1" s="199"/>
       <c r="I1" s="199"/>
@@ -48896,19 +48915,19 @@
         <v>3</v>
       </c>
       <c r="B2" s="202" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C2" s="203" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D2" s="203" t="s">
         <v>44</v>
       </c>
       <c r="E2" s="203" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F2" s="204" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="G2" s="202">
         <v>1.0</v>
@@ -48920,30 +48939,30 @@
         <v>2.0</v>
       </c>
       <c r="J2" s="203" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="K2" s="205" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="L2" s="203" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="M2" s="206" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="N2" s="187" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O2" s="187" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P2" s="187" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q2" s="17"/>
       <c r="R2" s="17"/>
       <c r="S2" s="6" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="T2" s="17"/>
       <c r="U2" s="17"/>
@@ -49033,7 +49052,7 @@
       <c r="Q4" s="17"/>
       <c r="R4" s="17"/>
       <c r="S4" s="212" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="T4" s="213"/>
       <c r="Z4" s="90"/>
@@ -49069,7 +49088,7 @@
       <c r="P5" s="215"/>
       <c r="S5" s="213"/>
       <c r="T5" s="216" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="6">
@@ -49102,11 +49121,11 @@
       <c r="R6" s="17"/>
       <c r="S6" s="213"/>
       <c r="T6" s="216" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Z6" s="151"/>
       <c r="AD6" s="76" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="7">
@@ -49136,7 +49155,7 @@
       <c r="O7" s="143"/>
       <c r="P7" s="218"/>
       <c r="AD7" s="216" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AE7" s="213"/>
       <c r="AF7" s="213"/>
@@ -49169,11 +49188,11 @@
       <c r="O8" s="143"/>
       <c r="P8" s="218"/>
       <c r="S8" s="216" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AA8" s="151"/>
       <c r="AD8" s="216" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9">
@@ -49372,7 +49391,7 @@
       <c r="O15" s="143"/>
       <c r="P15" s="218"/>
       <c r="S15" s="76" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="16">
@@ -49485,7 +49504,7 @@
       <c r="Q19" s="17"/>
       <c r="R19" s="17"/>
       <c r="S19" s="76" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="20">
@@ -49769,7 +49788,7 @@
       <c r="E27" s="17"/>
       <c r="F27" s="17"/>
       <c r="G27" s="223" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H27" s="17"/>
       <c r="I27" s="17"/>
@@ -49854,7 +49873,7 @@
       <c r="B29" s="17"/>
       <c r="C29" s="17"/>
       <c r="D29" s="4" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E29" s="4">
         <f>J29</f>
@@ -49876,10 +49895,10 @@
       </c>
       <c r="K29" s="17"/>
       <c r="L29" s="6" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="O29" s="4">
         <v>1.0</v>
@@ -49979,7 +49998,7 @@
       </c>
       <c r="R31" s="17"/>
       <c r="S31" s="6" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="T31" s="17"/>
       <c r="U31" s="17"/>
@@ -50041,7 +50060,7 @@
       <c r="E33" s="17"/>
       <c r="F33" s="17"/>
       <c r="G33" s="168" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J33" s="17"/>
       <c r="K33" s="17"/>
@@ -50055,10 +50074,10 @@
       <c r="P33" s="17"/>
       <c r="R33" s="17"/>
       <c r="T33" s="93" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="W33" s="76" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AA33" s="90"/>
       <c r="AD33" s="17"/>
@@ -50101,7 +50120,7 @@
         <v>1626.0</v>
       </c>
       <c r="U34" s="83" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="W34" s="76">
         <v>5193.0</v>
@@ -50146,7 +50165,7 @@
         <v>4176.0</v>
       </c>
       <c r="U35" s="83" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="W35" s="76">
         <v>4863.0</v>
@@ -50244,7 +50263,7 @@
       <c r="D38" s="17"/>
       <c r="E38" s="17"/>
       <c r="F38" s="4" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G38" s="226">
         <f t="shared" ref="G38:I38" si="8">G30-G35</f>
@@ -50446,7 +50465,7 @@
       <c r="Q45" s="17"/>
       <c r="R45" s="17"/>
       <c r="T45" s="216" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AD45" s="17"/>
       <c r="AE45" s="17"/>
@@ -50610,7 +50629,7 @@
         <v>158</v>
       </c>
       <c r="AG49" s="60" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="50">
@@ -50775,7 +50794,7 @@
         <v>13.03594852814783</v>
       </c>
       <c r="AG52" s="60" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="53">
@@ -50836,7 +50855,7 @@
         <v>6.291840048860032</v>
       </c>
       <c r="AG53" s="60" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="54">
@@ -50897,7 +50916,7 @@
         <v>2.7243520649411117</v>
       </c>
       <c r="AG54" s="60" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="55">
@@ -50958,7 +50977,7 @@
         <v>2.1429979739456915</v>
       </c>
       <c r="AG55" s="60" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="56">
@@ -51019,7 +51038,7 @@
         <v>3.98032040346951</v>
       </c>
       <c r="AG56" s="60" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="57">
@@ -51242,10 +51261,10 @@
       <c r="R62" s="17"/>
       <c r="S62" s="17"/>
       <c r="U62" s="76" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="V62" s="76" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AC62" s="17"/>
       <c r="AD62" s="17"/>
@@ -51287,7 +51306,7 @@
         <v>2165.0</v>
       </c>
       <c r="W63" s="76" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AC63" s="17"/>
       <c r="AD63" s="17"/>
@@ -51921,7 +51940,7 @@
       <c r="R79" s="17"/>
       <c r="S79" s="17"/>
       <c r="T79" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="U79" s="17"/>
       <c r="V79" s="17"/>
@@ -51962,7 +51981,7 @@
       <c r="R80" s="17"/>
       <c r="S80" s="17"/>
       <c r="T80" s="76" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="U80" s="21"/>
       <c r="V80" s="21"/>

--- a/data/df_best_models.xlsx
+++ b/data/df_best_models.xlsx
@@ -65,6 +65,11 @@
 :(
 Assess promedio
 Deja pasar empates (-50% de dif_draw)"</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="G5">
+      <text>
+        <t xml:space="preserve">se lo bajo pues solo predijo 2 empates x eso el m es alto</t>
       </text>
     </comment>
     <comment authorId="0" ref="M5">
@@ -315,6 +320,118 @@
         <t xml:space="preserve">Dice 1 y bet 2, no le pretendo ganar en eso. No deja pasar un local.</t>
       </text>
     </comment>
+    <comment authorId="0" ref="G35">
+      <text>
+        <t xml:space="preserve">me guie demasiado por el assess.
+</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="F43">
+      <text>
+        <t xml:space="preserve">Fecha de entrenamiento de modelos</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="R43">
+      <text>
+        <t xml:space="preserve">ultima actualizacion: Sabado semana 33</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="S43">
+      <text>
+        <t xml:space="preserve">Alarma si llega a 20%. En ese caso, podria ser conveniente reentrenar modellos</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="J46">
+      <text>
+        <t xml:space="preserve">Leccion aprendida: los empates de ENG siempre se deberian haber dado pero nunca se dan. Ir mas por 2. Las GP por rdo te lo indican.</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="O46">
+      <text>
+        <t xml:space="preserve">el 1071 un poco mas pero predicen lo mismo en prox partidos</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="P46">
+      <text>
+        <t xml:space="preserve">no lo use solo porque la bs lo lleva a usar stakes bajos.
+Ademas, el roi es mas bajo.
+1071:
+:)
+"2º en metrica (gran expected_error, error y gp_draw)
+#8 de 1152 en roi + #5 de 1152 en f1_score"
+:(
+Assess promedio
+Deja pasar empates (-50% de dif_draw)"</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="P47">
+      <text>
+        <t xml:space="preserve">el 1134 tambien pero ojo la distrib de probas no me gusta
+1083
+918
+</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="P48">
+      <text>
+        <t xml:space="preserve">900:
+:) 
+#1 en metrica (gp_away, error)
+Buenas metricas en cv (top 100)
+# buenos roi y f1 score y error
+:( 
+mas expected_error y mas G/P en away que en draw
+No me gusta su distrib. Poca visita?
+el 899: le fue bien en asses y tiene buenas metricas de cv y roi PERO 1) mala distribucion de bets (41%). No me gusta su distrib predice mucho 0 y poco 2.
+2) en 2 es bastante malo justo donde mas apostamos con ea. 
+3) Error alto
+Ventajas del 882: assess + distribucion excelente (4%)
+Desventajas del 882: error alto, f1_score mas bajo
+457:
+:) 
+"# 3 roi, prioriza gp_draw
+Gran f1_score
+Minimiza expected_error"	
+:(
+"Distribucion promedio (19%) aunque promedio.
+Metricas de cv"
+</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="P49">
+      <text>
+        <t xml:space="preserve">1117: 
+:) distribucion (13%), f1_score alto
+:( error promedio y gp_home alto? y assess malo
+349:
+Tiene menos roi, G/P en draw y away
+211:
+:) 
+#4 en metrica (gp_home, error)
+Buen assess
+#23 en f1_score
+expected_roi aceptable"	
+:( 
+Distribucion mala (31%) aunque mejor que la media (mas empates)
+Mala estrategia de apuesta con poco empate y mucho local</t>
+      </text>
+    </comment>
+    <comment authorId="0" ref="P50">
+      <text>
+        <t xml:space="preserve">546:
+:( 
+Metricas de cv (error alto y f1_score bajo)
+Distribucion mala (39%) aunque creo que todos son asi.
+ROI &lt; 0 en test"
+601:
+:)
+"#6 en metrica (expected_error, gp_draw)
+#10 roi, gran error y f1_score
+Distribucion aceptable (24%)"	
+:(
+Assess malo (0%) aunque mereció mas.</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -520,7 +637,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="894" uniqueCount="464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="939" uniqueCount="469">
   <si>
     <t>id_country</t>
   </si>
@@ -995,6 +1112,9 @@
   </si>
   <si>
     <t>Tras tener en cuenta cuotas de bet:</t>
+  </si>
+  <si>
+    <t>Maximizando n_res y acc_res del rdo mas rentable de cada pais + buen roi en test (y assess promedio)</t>
   </si>
   <si>
     <t>deberia cambiar el modelo en: ENG y en SPA</t>
@@ -1547,28 +1667,28 @@
     <t>Stake promedio</t>
   </si>
   <si>
-    <t>0.30</t>
+    <t>0.33</t>
   </si>
   <si>
-    <t>0.77</t>
+    <t>0.85</t>
   </si>
   <si>
-    <t>2.44</t>
+    <t>2.68</t>
   </si>
   <si>
-    <t>2.20</t>
+    <t>2.42</t>
   </si>
   <si>
-    <t>1.16</t>
+    <t>1.28</t>
   </si>
   <si>
-    <t>1.88</t>
+    <t>2.07</t>
   </si>
   <si>
-    <t>0.61</t>
+    <t>0.67</t>
   </si>
   <si>
-    <t>2.60</t>
+    <t>2.86</t>
   </si>
   <si>
     <t>Country</t>
@@ -1577,169 +1697,181 @@
     <t>Correl ROI y Expected ROI</t>
   </si>
   <si>
-    <t>4.31</t>
+    <t>4.74</t>
   </si>
   <si>
-    <t>4.62</t>
+    <t>5.08</t>
   </si>
   <si>
     <t>mean</t>
   </si>
   <si>
-    <t>6.06</t>
+    <t>6.67</t>
   </si>
   <si>
     <t>median</t>
   </si>
   <si>
-    <t>4.16</t>
+    <t>4.57</t>
   </si>
   <si>
     <t>p25</t>
   </si>
   <si>
-    <t>4.83</t>
+    <t>5.31</t>
   </si>
   <si>
     <t>p75</t>
   </si>
   <si>
-    <t>6.12</t>
+    <t>6.73</t>
   </si>
   <si>
-    <t>4.02</t>
+    <t>6.53</t>
   </si>
   <si>
-    <t>7.42</t>
+    <t>4.42</t>
   </si>
   <si>
-    <t>1.17</t>
+    <t>8.16</t>
   </si>
   <si>
-    <t>0.79</t>
+    <t>1.29</t>
   </si>
   <si>
     <t>0.86</t>
   </si>
   <si>
+    <t>0.95</t>
+  </si>
+  <si>
     <t>Gracias a las nuevas métricas de G/P sin bank en test, me di cuenta de que:</t>
   </si>
   <si>
-    <t>1.32</t>
+    <t>1.45</t>
   </si>
   <si>
     <t>La rentabilidad en ITA está en el visitante y no en el empate como creía.</t>
   </si>
   <si>
-    <t>2.47</t>
-  </si>
-  <si>
     <t>La rentabilidad en ENG y GER está en el empate tal como creía.</t>
   </si>
   <si>
-    <t>0.97</t>
+    <t>1.06</t>
   </si>
   <si>
     <t>En SPA esta repartido aunque Empate saca una ventaja.</t>
   </si>
   <si>
-    <t>1.73</t>
+    <t>1.90</t>
   </si>
   <si>
     <t>En FRA, depende el modelo. A veces local, a veces, empate.</t>
   </si>
   <si>
+    <t>4.21</t>
+  </si>
+  <si>
     <t>Si en FRA empate no rinde, no tiene sentido exigirle una buena distrib en empate… → Tiene sentido pero al parecer si importa el empate puesto que el modelo que gana se basa en empate.</t>
   </si>
   <si>
-    <t>3.92</t>
+    <t>4.32</t>
   </si>
   <si>
-    <t>4.91</t>
+    <t>5.40</t>
   </si>
   <si>
-    <t>1.96</t>
+    <t>0.96</t>
   </si>
   <si>
-    <t>3.78</t>
+    <t>0.94</t>
   </si>
   <si>
-    <t>2.94</t>
+    <t>6.68</t>
   </si>
   <si>
-    <t>2.59</t>
+    <t>4.79</t>
   </si>
   <si>
-    <t>2.18</t>
+    <t>5.93</t>
   </si>
   <si>
-    <t>2.03</t>
+    <t>7.29</t>
   </si>
   <si>
-    <t>3.85</t>
+    <t>4.04</t>
   </si>
   <si>
-    <t>7.02</t>
+    <t>4.10</t>
   </si>
   <si>
-    <t>9.13</t>
+    <t>4.01</t>
   </si>
   <si>
-    <t>5.79</t>
+    <t>5.14</t>
   </si>
   <si>
-    <t>3.00</t>
+    <t>3.30</t>
   </si>
   <si>
-    <t>1.90</t>
+    <t>2.98</t>
   </si>
   <si>
-    <t>0.40</t>
+    <t>2.09</t>
   </si>
   <si>
-    <t>5.85</t>
+    <t>0.44</t>
   </si>
   <si>
-    <t>5.70</t>
+    <t>6.38</t>
   </si>
   <si>
-    <t>3.17</t>
+    <t>6.44</t>
   </si>
   <si>
-    <t>5.67</t>
+    <t>6.26</t>
   </si>
   <si>
-    <t>3.55</t>
+    <t>3.49</t>
   </si>
   <si>
-    <t>5.76</t>
+    <t>6.24</t>
   </si>
   <si>
-    <t>2.02</t>
+    <t>3.91</t>
   </si>
   <si>
-    <t>2.27</t>
+    <t>6.33</t>
   </si>
   <si>
-    <t>3.12</t>
+    <t>2.22</t>
   </si>
   <si>
-    <t>1.97</t>
+    <t>2.50</t>
   </si>
   <si>
-    <t>3.41</t>
+    <t>3.43</t>
   </si>
   <si>
-    <t>5.59</t>
+    <t>2.16</t>
   </si>
   <si>
-    <t>5.41</t>
+    <t>3.75</t>
   </si>
   <si>
-    <t>2.31</t>
+    <t>6.15</t>
   </si>
   <si>
-    <t>2.34</t>
+    <t>6.12</t>
+  </si>
+  <si>
+    <t>5.96</t>
+  </si>
+  <si>
+    <t>2.54</t>
+  </si>
+  <si>
+    <t>2.57</t>
   </si>
   <si>
     <t>RENTABILIDAD</t>
@@ -2811,6 +2943,9 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="1" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -2840,9 +2975,6 @@
     </xf>
     <xf borderId="0" fillId="5" fontId="3" numFmtId="3" xfId="0" applyFont="1" applyNumberFormat="1"/>
     <xf borderId="0" fillId="5" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
     <xf borderId="0" fillId="16" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -3592,7 +3724,7 @@
         <v>45739.0</v>
       </c>
       <c r="D4" s="14">
-        <v>1070.0</v>
+        <v>506.0</v>
       </c>
       <c r="E4" s="14" t="s">
         <v>17</v>
@@ -3601,14 +3733,14 @@
         <v>5.0</v>
       </c>
       <c r="G4" s="24">
-        <v>6.58</v>
+        <v>5.0</v>
       </c>
       <c r="H4" s="24">
-        <v>11.42</v>
+        <v>12.89</v>
       </c>
       <c r="I4" s="24">
         <f t="shared" ref="I4:I8" si="1">AVERAGE(F4:H4)</f>
-        <v>7.666666667</v>
+        <v>7.63</v>
       </c>
       <c r="J4" s="25">
         <v>5.0</v>
@@ -3650,17 +3782,17 @@
         <v>17</v>
       </c>
       <c r="F5" s="24">
-        <v>7.11</v>
+        <v>5.79</v>
       </c>
       <c r="G5" s="24">
         <v>5.0</v>
       </c>
       <c r="H5" s="24">
-        <v>9.74</v>
+        <v>10.53</v>
       </c>
       <c r="I5" s="24">
         <f t="shared" si="1"/>
-        <v>7.283333333</v>
+        <v>7.106666667</v>
       </c>
       <c r="J5" s="25">
         <v>11.0</v>
@@ -3696,7 +3828,7 @@
         <v>45739.0</v>
       </c>
       <c r="D6" s="14">
-        <v>563.0</v>
+        <v>900.0</v>
       </c>
       <c r="E6" s="14" t="s">
         <v>17</v>
@@ -3705,14 +3837,14 @@
         <v>5.0</v>
       </c>
       <c r="G6" s="24">
-        <v>7.11</v>
+        <v>7.37</v>
       </c>
       <c r="H6" s="24">
-        <v>8.68</v>
+        <v>14.47</v>
       </c>
       <c r="I6" s="24">
         <f t="shared" si="1"/>
-        <v>6.93</v>
+        <v>8.946666667</v>
       </c>
       <c r="J6" s="25">
         <v>1.0</v>
@@ -3754,17 +3886,17 @@
         <v>17</v>
       </c>
       <c r="F7" s="24">
-        <v>6.05</v>
+        <v>6.58</v>
       </c>
       <c r="G7" s="24">
         <v>12.89</v>
       </c>
       <c r="H7" s="24">
-        <v>8.68</v>
+        <v>8.16</v>
       </c>
       <c r="I7" s="24">
         <f t="shared" si="1"/>
-        <v>9.206666667</v>
+        <v>9.21</v>
       </c>
       <c r="J7" s="25">
         <v>2.0</v>
@@ -3798,7 +3930,7 @@
         <v>45740.0</v>
       </c>
       <c r="D8" s="14">
-        <v>546.0</v>
+        <v>1135.0</v>
       </c>
       <c r="E8" s="14" t="s">
         <v>17</v>
@@ -3807,14 +3939,14 @@
         <v>5.0</v>
       </c>
       <c r="G8" s="24">
-        <v>15.0</v>
+        <v>12.89</v>
       </c>
       <c r="H8" s="24">
         <v>5.0</v>
       </c>
       <c r="I8" s="24">
         <f t="shared" si="1"/>
-        <v>8.333333333</v>
+        <v>7.63</v>
       </c>
       <c r="J8" s="25">
         <v>11.0</v>
@@ -8838,6 +8970,16 @@
         <cfvo type="formula" val="0.2"/>
         <color rgb="FFFFFFFF"/>
         <color rgb="FFE67C73"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I4:I8">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FFFFD666"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
@@ -8864,146 +9006,146 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="76" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
     </row>
     <row r="2">
       <c r="B2" s="17"/>
       <c r="C2" s="5" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="E2" s="235"/>
       <c r="F2" s="6" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="H2" s="235"/>
     </row>
     <row r="3">
       <c r="B3" s="186" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="C3" s="236" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="D3" s="186" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="E3" s="237" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F3" s="186" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="G3" s="186" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="H3" s="186" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="238" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="C4" s="239" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="D4" s="187" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="E4" s="240" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="F4" s="241" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="G4" s="241" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="H4" s="187"/>
     </row>
     <row r="5">
       <c r="B5" s="238" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="C5" s="242" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="D5" s="197"/>
       <c r="E5" s="240" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="F5" s="243" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="G5" s="244" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="H5" s="187"/>
     </row>
     <row r="6">
       <c r="B6" s="238" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="C6" s="239" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="D6" s="187" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="E6" s="240" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="F6" s="187" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="G6" s="187"/>
       <c r="H6" s="187"/>
     </row>
     <row r="7">
       <c r="B7" s="187" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="C7" s="245" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="D7" s="187"/>
       <c r="E7" s="246" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="F7" s="239" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="G7" s="187"/>
       <c r="H7" s="187" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="247" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="C8" s="248" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="D8" s="249"/>
       <c r="E8" s="247" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="F8" s="250" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="G8" s="251" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="H8" s="249"/>
     </row>
     <row r="9">
       <c r="B9" s="20" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="C9" s="252" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="D9" s="143"/>
       <c r="E9" s="143"/>
@@ -9013,27 +9155,27 @@
     </row>
     <row r="10">
       <c r="B10" s="20" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="C10" s="217"/>
       <c r="D10" s="143"/>
       <c r="E10" s="143"/>
       <c r="F10" s="217"/>
       <c r="G10" s="241" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="H10" s="143"/>
     </row>
     <row r="11">
       <c r="B11" s="20" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="C11" s="217"/>
       <c r="D11" s="143"/>
       <c r="E11" s="143"/>
       <c r="F11" s="217"/>
       <c r="G11" s="253" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="H11" s="20"/>
     </row>
@@ -9056,7 +9198,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="90" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="L1" s="32"/>
     </row>
@@ -9065,16 +9207,16 @@
     </row>
     <row r="3">
       <c r="A3" s="76" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="L3" s="32"/>
     </row>
     <row r="4">
       <c r="B4" s="76" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="G4" s="76" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="L4" s="32"/>
     </row>
@@ -9180,45 +9322,45 @@
     </row>
     <row r="11">
       <c r="A11" s="254" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="90" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="76" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="254" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="90" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="76" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="F19" s="151"/>
     </row>
     <row r="20">
       <c r="B20" s="90" t="s">
-        <v>442</v>
-      </c>
-      <c r="C20" s="105"/>
-      <c r="D20" s="105"/>
-      <c r="E20" s="105"/>
-      <c r="F20" s="105"/>
+        <v>447</v>
+      </c>
+      <c r="C20" s="106"/>
+      <c r="D20" s="106"/>
+      <c r="E20" s="106"/>
+      <c r="F20" s="106"/>
       <c r="G20" s="90" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="H20" s="90" t="s">
         <v>66</v>
@@ -9235,35 +9377,35 @@
     </row>
     <row r="21">
       <c r="B21" s="90" t="s">
-        <v>444</v>
-      </c>
-      <c r="G21" s="107">
+        <v>449</v>
+      </c>
+      <c r="G21" s="108">
         <v>2.575</v>
       </c>
     </row>
     <row r="23">
       <c r="K23" s="90" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="76" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="H24" s="76" t="s">
         <v>44</v>
       </c>
       <c r="I24" s="76" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="K24" s="76" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="L24" s="76" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="M24" s="76" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
     </row>
     <row r="25">
@@ -9273,16 +9415,16 @@
       <c r="B25" s="76">
         <v>0.0</v>
       </c>
-      <c r="H25" s="107" t="str">
+      <c r="H25" s="108" t="str">
         <f t="shared" ref="H25:I25" si="2">AVERAGE(#REF!)</f>
         <v>#REF!</v>
       </c>
-      <c r="I25" s="107" t="str">
+      <c r="I25" s="108" t="str">
         <f t="shared" si="2"/>
         <v>#REF!</v>
       </c>
       <c r="K25" s="76" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="26">
@@ -9293,7 +9435,7 @@
         <v>1.19</v>
       </c>
       <c r="K26" s="76" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
     </row>
     <row r="27">
@@ -9304,7 +9446,7 @@
         <v>2.19</v>
       </c>
       <c r="K27" s="76" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
     </row>
     <row r="28">
@@ -9315,7 +9457,7 @@
         <v>0.05</v>
       </c>
       <c r="K28" s="76" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
     </row>
     <row r="29">
@@ -9334,7 +9476,7 @@
         <v>6.42</v>
       </c>
       <c r="K30" s="93" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
     </row>
     <row r="31">
@@ -9351,7 +9493,7 @@
         <v>3</v>
       </c>
       <c r="M31" s="76" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="32">
@@ -9367,7 +9509,7 @@
       <c r="L32" s="14">
         <v>6293.0</v>
       </c>
-      <c r="M32" s="109">
+      <c r="M32" s="110">
         <v>20.0</v>
       </c>
     </row>
@@ -9384,7 +9526,7 @@
       <c r="L33" s="14">
         <v>3960.0</v>
       </c>
-      <c r="M33" s="109">
+      <c r="M33" s="110">
         <v>60.0</v>
       </c>
     </row>
@@ -9401,7 +9543,7 @@
       <c r="L34" s="14">
         <v>3032.0</v>
       </c>
-      <c r="M34" s="109">
+      <c r="M34" s="110">
         <v>10.0</v>
       </c>
     </row>
@@ -9418,7 +9560,7 @@
       <c r="L35" s="14">
         <v>2114.0</v>
       </c>
-      <c r="M35" s="109">
+      <c r="M35" s="110">
         <v>40.0</v>
       </c>
     </row>
@@ -9435,7 +9577,7 @@
       <c r="L36" s="14">
         <v>2232.0</v>
       </c>
-      <c r="M36" s="109">
+      <c r="M36" s="110">
         <v>10.0</v>
       </c>
     </row>
@@ -9479,7 +9621,7 @@
         <v>0.61</v>
       </c>
       <c r="K41" s="90" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
     </row>
     <row r="42">
@@ -9490,13 +9632,13 @@
         <v>0.69</v>
       </c>
       <c r="K42" s="76" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="L42" s="76" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="M42" s="76" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
     </row>
     <row r="43">
@@ -9509,10 +9651,10 @@
       <c r="K43" s="76">
         <v>0.8</v>
       </c>
-      <c r="L43" s="107">
+      <c r="L43" s="108">
         <v>5.276900000000001</v>
       </c>
-      <c r="M43" s="107">
+      <c r="M43" s="108">
         <v>-3.314500000000001</v>
       </c>
     </row>
@@ -9537,10 +9679,10 @@
       <c r="K45" s="76">
         <v>0.5</v>
       </c>
-      <c r="L45" s="107">
+      <c r="L45" s="108">
         <v>4.023500000000001</v>
       </c>
-      <c r="M45" s="107">
+      <c r="M45" s="108">
         <v>-0.9597</v>
       </c>
     </row>
@@ -9554,10 +9696,10 @@
       <c r="K46" s="76">
         <v>0.4</v>
       </c>
-      <c r="L46" s="107">
+      <c r="L46" s="108">
         <v>3.2705</v>
       </c>
-      <c r="M46" s="107">
+      <c r="M46" s="108">
         <v>0.5869999999999999</v>
       </c>
     </row>
@@ -9571,10 +9713,10 @@
       <c r="K47" s="76">
         <v>0.3</v>
       </c>
-      <c r="L47" s="107">
+      <c r="L47" s="108">
         <v>2.568899999999999</v>
       </c>
-      <c r="M47" s="107">
+      <c r="M47" s="108">
         <v>1.3571999999999995</v>
       </c>
     </row>
@@ -9588,10 +9730,10 @@
       <c r="K48" s="76">
         <v>0.2</v>
       </c>
-      <c r="L48" s="107">
+      <c r="L48" s="108">
         <v>2.434199999999999</v>
       </c>
-      <c r="M48" s="107">
+      <c r="M48" s="108">
         <v>1.5152999999999996</v>
       </c>
     </row>
@@ -9605,10 +9747,10 @@
       <c r="K49" s="76">
         <v>0.1</v>
       </c>
-      <c r="L49" s="107">
+      <c r="L49" s="108">
         <v>2.067100000000001</v>
       </c>
-      <c r="M49" s="107">
+      <c r="M49" s="108">
         <v>1.6288</v>
       </c>
     </row>
@@ -9628,7 +9770,7 @@
         <v>0.0</v>
       </c>
       <c r="K51" s="76" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
     </row>
     <row r="52">
@@ -9656,20 +9798,20 @@
       </c>
       <c r="K54" s="143"/>
       <c r="L54" s="255" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="M54" s="256"/>
       <c r="N54" s="148" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O54" s="148" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="P54" s="148" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="R54" s="79" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="S54" s="151">
         <v>0.15</v>
@@ -9699,7 +9841,7 @@
       <c r="P55" s="20">
         <v>-0.25</v>
       </c>
-      <c r="S55" s="115"/>
+      <c r="S55" s="116"/>
     </row>
     <row r="56">
       <c r="A56" s="76">
@@ -9748,9 +9890,9 @@
         <v>5.86</v>
       </c>
       <c r="R57" s="76" t="s">
-        <v>461</v>
-      </c>
-      <c r="S57" s="107">
+        <v>466</v>
+      </c>
+      <c r="S57" s="108">
         <f>SUM(P55:P74)</f>
         <v>9.42</v>
       </c>
@@ -9777,7 +9919,7 @@
         <v>0.855</v>
       </c>
       <c r="P58" s="20" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
     </row>
     <row r="59">
@@ -9824,7 +9966,7 @@
         <v>0.96</v>
       </c>
       <c r="P60" s="20" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
     </row>
     <row r="61">
@@ -10304,9 +10446,9 @@
         <v>4.19</v>
       </c>
       <c r="G97" s="79"/>
-      <c r="H97" s="114"/>
-      <c r="I97" s="114"/>
-      <c r="J97" s="114"/>
+      <c r="H97" s="115"/>
+      <c r="I97" s="115"/>
+      <c r="J97" s="115"/>
     </row>
     <row r="98">
       <c r="A98" s="76">
@@ -10316,9 +10458,9 @@
         <v>3.15</v>
       </c>
       <c r="G98" s="79"/>
-      <c r="H98" s="114"/>
-      <c r="I98" s="114"/>
-      <c r="J98" s="114"/>
+      <c r="H98" s="115"/>
+      <c r="I98" s="115"/>
+      <c r="J98" s="115"/>
     </row>
     <row r="99">
       <c r="A99" s="76">
@@ -10328,9 +10470,9 @@
         <v>0.21</v>
       </c>
       <c r="G99" s="79"/>
-      <c r="H99" s="114"/>
-      <c r="I99" s="114"/>
-      <c r="J99" s="114"/>
+      <c r="H99" s="115"/>
+      <c r="I99" s="115"/>
+      <c r="J99" s="115"/>
     </row>
     <row r="100">
       <c r="A100" s="76">
@@ -10340,9 +10482,9 @@
         <v>17.28</v>
       </c>
       <c r="G100" s="79"/>
-      <c r="H100" s="114"/>
-      <c r="I100" s="114"/>
-      <c r="J100" s="114"/>
+      <c r="H100" s="115"/>
+      <c r="I100" s="115"/>
+      <c r="J100" s="115"/>
     </row>
     <row r="101">
       <c r="A101" s="76">
@@ -10352,9 +10494,9 @@
         <v>0.33</v>
       </c>
       <c r="G101" s="79"/>
-      <c r="H101" s="114"/>
-      <c r="I101" s="114"/>
-      <c r="J101" s="114"/>
+      <c r="H101" s="115"/>
+      <c r="I101" s="115"/>
+      <c r="J101" s="115"/>
     </row>
     <row r="102">
       <c r="A102" s="76">
@@ -10364,9 +10506,9 @@
         <v>4.08</v>
       </c>
       <c r="G102" s="79"/>
-      <c r="H102" s="114"/>
-      <c r="I102" s="114"/>
-      <c r="J102" s="114"/>
+      <c r="H102" s="115"/>
+      <c r="I102" s="115"/>
+      <c r="J102" s="115"/>
     </row>
     <row r="103">
       <c r="A103" s="76">
@@ -10376,9 +10518,9 @@
         <v>2.93</v>
       </c>
       <c r="G103" s="79"/>
-      <c r="H103" s="114"/>
-      <c r="I103" s="114"/>
-      <c r="J103" s="114"/>
+      <c r="H103" s="115"/>
+      <c r="I103" s="115"/>
+      <c r="J103" s="115"/>
     </row>
     <row r="104">
       <c r="A104" s="76">
@@ -10388,9 +10530,9 @@
         <v>2.09</v>
       </c>
       <c r="G104" s="79"/>
-      <c r="H104" s="114"/>
-      <c r="I104" s="114"/>
-      <c r="J104" s="114"/>
+      <c r="H104" s="115"/>
+      <c r="I104" s="115"/>
+      <c r="J104" s="115"/>
     </row>
     <row r="105">
       <c r="A105" s="76">
@@ -10400,9 +10542,9 @@
         <v>2.32</v>
       </c>
       <c r="G105" s="79"/>
-      <c r="H105" s="114"/>
-      <c r="I105" s="114"/>
-      <c r="J105" s="114"/>
+      <c r="H105" s="115"/>
+      <c r="I105" s="115"/>
+      <c r="J105" s="115"/>
     </row>
     <row r="106">
       <c r="A106" s="76">
@@ -10412,9 +10554,9 @@
         <v>9.35</v>
       </c>
       <c r="G106" s="79"/>
-      <c r="H106" s="114"/>
-      <c r="I106" s="114"/>
-      <c r="J106" s="114"/>
+      <c r="H106" s="115"/>
+      <c r="I106" s="115"/>
+      <c r="J106" s="115"/>
     </row>
     <row r="107">
       <c r="A107" s="76">
@@ -10424,9 +10566,9 @@
         <v>0.03</v>
       </c>
       <c r="G107" s="79"/>
-      <c r="H107" s="114"/>
-      <c r="I107" s="114"/>
-      <c r="J107" s="114"/>
+      <c r="H107" s="115"/>
+      <c r="I107" s="115"/>
+      <c r="J107" s="115"/>
     </row>
     <row r="108">
       <c r="A108" s="76">
@@ -10436,9 +10578,9 @@
         <v>2.81</v>
       </c>
       <c r="G108" s="79"/>
-      <c r="H108" s="114"/>
-      <c r="I108" s="114"/>
-      <c r="J108" s="114"/>
+      <c r="H108" s="115"/>
+      <c r="I108" s="115"/>
+      <c r="J108" s="115"/>
     </row>
     <row r="109">
       <c r="A109" s="76">
@@ -10448,9 +10590,9 @@
         <v>7.09</v>
       </c>
       <c r="G109" s="79"/>
-      <c r="H109" s="114"/>
-      <c r="I109" s="114"/>
-      <c r="J109" s="114"/>
+      <c r="H109" s="115"/>
+      <c r="I109" s="115"/>
+      <c r="J109" s="115"/>
     </row>
     <row r="110">
       <c r="A110" s="76">
@@ -10460,9 +10602,9 @@
         <v>0.91</v>
       </c>
       <c r="G110" s="79"/>
-      <c r="H110" s="114"/>
-      <c r="I110" s="114"/>
-      <c r="J110" s="114"/>
+      <c r="H110" s="115"/>
+      <c r="I110" s="115"/>
+      <c r="J110" s="115"/>
     </row>
     <row r="111">
       <c r="A111" s="76">
@@ -10472,9 +10614,9 @@
         <v>0.03</v>
       </c>
       <c r="G111" s="79"/>
-      <c r="H111" s="114"/>
-      <c r="I111" s="114"/>
-      <c r="J111" s="114"/>
+      <c r="H111" s="115"/>
+      <c r="I111" s="115"/>
+      <c r="J111" s="115"/>
     </row>
     <row r="112">
       <c r="A112" s="76">
@@ -10484,9 +10626,9 @@
         <v>1.07</v>
       </c>
       <c r="G112" s="79"/>
-      <c r="H112" s="114"/>
-      <c r="I112" s="114"/>
-      <c r="J112" s="114"/>
+      <c r="H112" s="115"/>
+      <c r="I112" s="115"/>
+      <c r="J112" s="115"/>
     </row>
     <row r="113">
       <c r="A113" s="76">
@@ -10496,9 +10638,9 @@
         <v>0.93</v>
       </c>
       <c r="G113" s="79"/>
-      <c r="H113" s="114"/>
-      <c r="I113" s="114"/>
-      <c r="J113" s="114"/>
+      <c r="H113" s="115"/>
+      <c r="I113" s="115"/>
+      <c r="J113" s="115"/>
     </row>
     <row r="114">
       <c r="A114" s="76">
@@ -10508,9 +10650,9 @@
         <v>0.26</v>
       </c>
       <c r="G114" s="79"/>
-      <c r="H114" s="114"/>
-      <c r="I114" s="114"/>
-      <c r="J114" s="114"/>
+      <c r="H114" s="115"/>
+      <c r="I114" s="115"/>
+      <c r="J114" s="115"/>
     </row>
     <row r="115">
       <c r="A115" s="76">
@@ -10520,9 +10662,9 @@
         <v>-0.11</v>
       </c>
       <c r="G115" s="79"/>
-      <c r="H115" s="114"/>
-      <c r="I115" s="114"/>
-      <c r="J115" s="114"/>
+      <c r="H115" s="115"/>
+      <c r="I115" s="115"/>
+      <c r="J115" s="115"/>
     </row>
     <row r="116">
       <c r="A116" s="76">
@@ -10532,9 +10674,9 @@
         <v>0.06</v>
       </c>
       <c r="G116" s="79"/>
-      <c r="H116" s="114"/>
-      <c r="I116" s="114"/>
-      <c r="J116" s="114"/>
+      <c r="H116" s="115"/>
+      <c r="I116" s="115"/>
+      <c r="J116" s="115"/>
     </row>
     <row r="117">
       <c r="A117" s="76">
@@ -10544,9 +10686,9 @@
         <v>0.19</v>
       </c>
       <c r="G117" s="79"/>
-      <c r="H117" s="114"/>
-      <c r="I117" s="114"/>
-      <c r="J117" s="114"/>
+      <c r="H117" s="115"/>
+      <c r="I117" s="115"/>
+      <c r="J117" s="115"/>
     </row>
     <row r="118">
       <c r="A118" s="76">
@@ -10556,9 +10698,9 @@
         <v>0.11</v>
       </c>
       <c r="G118" s="79"/>
-      <c r="H118" s="114"/>
-      <c r="I118" s="114"/>
-      <c r="J118" s="114"/>
+      <c r="H118" s="115"/>
+      <c r="I118" s="115"/>
+      <c r="J118" s="115"/>
     </row>
     <row r="119">
       <c r="A119" s="76">
@@ -10568,9 +10710,9 @@
         <v>-0.01</v>
       </c>
       <c r="G119" s="79"/>
-      <c r="H119" s="114"/>
-      <c r="I119" s="114"/>
-      <c r="J119" s="114"/>
+      <c r="H119" s="115"/>
+      <c r="I119" s="115"/>
+      <c r="J119" s="115"/>
     </row>
     <row r="120">
       <c r="A120" s="76">
@@ -10580,9 +10722,9 @@
         <v>0.03</v>
       </c>
       <c r="G120" s="79"/>
-      <c r="H120" s="114"/>
-      <c r="I120" s="114"/>
-      <c r="J120" s="114"/>
+      <c r="H120" s="115"/>
+      <c r="I120" s="115"/>
+      <c r="J120" s="115"/>
     </row>
     <row r="121">
       <c r="A121" s="76">
@@ -10592,9 +10734,9 @@
         <v>0.01</v>
       </c>
       <c r="G121" s="79"/>
-      <c r="H121" s="114"/>
-      <c r="I121" s="114"/>
-      <c r="J121" s="114"/>
+      <c r="H121" s="115"/>
+      <c r="I121" s="115"/>
+      <c r="J121" s="115"/>
     </row>
     <row r="122">
       <c r="A122" s="76">
@@ -10604,9 +10746,9 @@
         <v>0.34</v>
       </c>
       <c r="G122" s="79"/>
-      <c r="H122" s="114"/>
-      <c r="I122" s="114"/>
-      <c r="J122" s="114"/>
+      <c r="H122" s="115"/>
+      <c r="I122" s="115"/>
+      <c r="J122" s="115"/>
     </row>
     <row r="123">
       <c r="A123" s="76">
@@ -10616,9 +10758,9 @@
         <v>0.22</v>
       </c>
       <c r="G123" s="79"/>
-      <c r="H123" s="114"/>
-      <c r="I123" s="114"/>
-      <c r="J123" s="114"/>
+      <c r="H123" s="115"/>
+      <c r="I123" s="115"/>
+      <c r="J123" s="115"/>
     </row>
     <row r="124">
       <c r="A124" s="76">
@@ -10628,34 +10770,34 @@
         <v>0.72</v>
       </c>
       <c r="G124" s="79"/>
-      <c r="H124" s="114"/>
-      <c r="I124" s="114"/>
-      <c r="J124" s="114"/>
+      <c r="H124" s="115"/>
+      <c r="I124" s="115"/>
+      <c r="J124" s="115"/>
     </row>
     <row r="125">
-      <c r="H125" s="114"/>
-      <c r="I125" s="114"/>
-      <c r="J125" s="114"/>
+      <c r="H125" s="115"/>
+      <c r="I125" s="115"/>
+      <c r="J125" s="115"/>
     </row>
     <row r="126">
-      <c r="H126" s="114"/>
-      <c r="I126" s="114"/>
-      <c r="J126" s="114"/>
+      <c r="H126" s="115"/>
+      <c r="I126" s="115"/>
+      <c r="J126" s="115"/>
     </row>
     <row r="127">
-      <c r="H127" s="114"/>
-      <c r="I127" s="114"/>
-      <c r="J127" s="114"/>
+      <c r="H127" s="115"/>
+      <c r="I127" s="115"/>
+      <c r="J127" s="115"/>
     </row>
     <row r="128">
-      <c r="H128" s="114"/>
-      <c r="I128" s="114"/>
-      <c r="J128" s="114"/>
+      <c r="H128" s="115"/>
+      <c r="I128" s="115"/>
+      <c r="J128" s="115"/>
     </row>
     <row r="129">
-      <c r="H129" s="114"/>
-      <c r="I129" s="114"/>
-      <c r="J129" s="114"/>
+      <c r="H129" s="115"/>
+      <c r="I129" s="115"/>
+      <c r="J129" s="115"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -17301,7 +17443,458 @@
         <v>546.0</v>
       </c>
     </row>
+    <row r="34">
+      <c r="D34" s="76" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="D35" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="E35" s="104">
+        <v>506.0</v>
+      </c>
+      <c r="G35" s="77">
+        <v>893.0</v>
+      </c>
+      <c r="H35" s="76">
+        <v>1097.0</v>
+      </c>
+      <c r="I35" s="76">
+        <v>436.0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="D36" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E36" s="104">
+        <v>1083.0</v>
+      </c>
+      <c r="H36" s="77">
+        <v>1140.0</v>
+      </c>
+      <c r="I36" s="76">
+        <v>1092.0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="D37" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="E37" s="104">
+        <v>766.0</v>
+      </c>
+      <c r="G37" s="77">
+        <v>563.0</v>
+      </c>
+      <c r="H37" s="77">
+        <v>751.0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="D38" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="G38" s="77">
+        <v>112.0</v>
+      </c>
+      <c r="H38" s="76">
+        <v>160.0</v>
+      </c>
+      <c r="I38" s="104">
+        <v>184.0</v>
+      </c>
+      <c r="J38" s="104">
+        <v>907.0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="D39" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="G39" s="77">
+        <v>1066.0</v>
+      </c>
+      <c r="H39" s="76">
+        <v>872.0</v>
+      </c>
+      <c r="I39" s="76">
+        <v>1135.0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="D43" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I43" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="J43" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K43" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L43" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="M43" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="N43" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="O43" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="P43" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q43" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="R43" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="S43" s="9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="D44" s="10">
+        <v>6.0</v>
+      </c>
+      <c r="E44" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="F44" s="12">
+        <v>45685.0</v>
+      </c>
+      <c r="G44" s="13">
+        <v>616.0</v>
+      </c>
+      <c r="H44" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="I44" s="15"/>
+      <c r="J44" s="15"/>
+      <c r="K44" s="15"/>
+      <c r="L44" s="15"/>
+      <c r="M44" s="16"/>
+      <c r="P44" s="17"/>
+      <c r="Q44" s="18"/>
+      <c r="S44" s="19"/>
+    </row>
+    <row r="45">
+      <c r="D45" s="20">
+        <v>167.0</v>
+      </c>
+      <c r="E45" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="F45" s="12"/>
+      <c r="G45" s="12"/>
+      <c r="H45" s="12"/>
+      <c r="I45" s="21"/>
+      <c r="J45" s="21"/>
+      <c r="K45" s="21"/>
+      <c r="L45" s="21"/>
+      <c r="M45" s="16"/>
+      <c r="P45" s="17"/>
+      <c r="Q45" s="18"/>
+      <c r="S45" s="19"/>
+    </row>
+    <row r="46">
+      <c r="D46" s="22">
+        <v>48.0</v>
+      </c>
+      <c r="E46" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="F46" s="12">
+        <v>45739.0</v>
+      </c>
+      <c r="G46" s="14">
+        <v>1070.0</v>
+      </c>
+      <c r="H46" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="I46" s="24">
+        <v>5.0</v>
+      </c>
+      <c r="J46" s="24">
+        <v>6.58</v>
+      </c>
+      <c r="K46" s="24">
+        <v>11.42</v>
+      </c>
+      <c r="L46" s="24">
+        <f t="shared" ref="L46:L50" si="1">AVERAGE(I46:K46)</f>
+        <v>7.666666667</v>
+      </c>
+      <c r="M46" s="25">
+        <v>5.0</v>
+      </c>
+      <c r="N46" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="O46" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="P46" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q46" s="28">
+        <v>-0.959</v>
+      </c>
+      <c r="R46" s="29">
+        <v>-0.941356160637481</v>
+      </c>
+      <c r="S46" s="30">
+        <f t="shared" ref="S46:S50" si="2">(R46-Q46)/Q46</f>
+        <v>-0.01839816409</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="D47" s="20">
+        <v>55.0</v>
+      </c>
+      <c r="E47" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="F47" s="12">
+        <v>45739.0</v>
+      </c>
+      <c r="G47" s="14">
+        <v>1092.0</v>
+      </c>
+      <c r="H47" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="I47" s="24">
+        <v>7.11</v>
+      </c>
+      <c r="J47" s="24">
+        <v>5.0</v>
+      </c>
+      <c r="K47" s="24">
+        <v>9.74</v>
+      </c>
+      <c r="L47" s="24">
+        <f t="shared" si="1"/>
+        <v>7.283333333</v>
+      </c>
+      <c r="M47" s="25">
+        <v>11.0</v>
+      </c>
+      <c r="N47" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="O47" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="P47" s="4">
+        <v>49.0</v>
+      </c>
+      <c r="Q47" s="28">
+        <v>-0.983461055390758</v>
+      </c>
+      <c r="R47" s="29">
+        <v>-1.03568863905778</v>
+      </c>
+      <c r="S47" s="30">
+        <f t="shared" si="2"/>
+        <v>0.05310589919</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="D48" s="20">
+        <v>59.0</v>
+      </c>
+      <c r="E48" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F48" s="12">
+        <v>45739.0</v>
+      </c>
+      <c r="G48" s="14">
+        <v>563.0</v>
+      </c>
+      <c r="H48" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="I48" s="24">
+        <v>5.0</v>
+      </c>
+      <c r="J48" s="24">
+        <v>7.11</v>
+      </c>
+      <c r="K48" s="24">
+        <v>8.68</v>
+      </c>
+      <c r="L48" s="24">
+        <f t="shared" si="1"/>
+        <v>6.93</v>
+      </c>
+      <c r="M48" s="25">
+        <v>1.0</v>
+      </c>
+      <c r="N48" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="O48" s="27" t="s">
+        <v>28</v>
+      </c>
+      <c r="P48" s="4">
+        <v>385.0</v>
+      </c>
+      <c r="Q48" s="28">
+        <v>-1.0062289543877</v>
+      </c>
+      <c r="R48" s="29">
+        <v>-0.97031500407769</v>
+      </c>
+      <c r="S48" s="30">
+        <f t="shared" si="2"/>
+        <v>-0.03569162878</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="D49" s="20">
+        <v>77.0</v>
+      </c>
+      <c r="E49" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="F49" s="12">
+        <v>45739.0</v>
+      </c>
+      <c r="G49" s="14">
+        <v>184.0</v>
+      </c>
+      <c r="H49" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="I49" s="24">
+        <v>6.05</v>
+      </c>
+      <c r="J49" s="24">
+        <v>12.89</v>
+      </c>
+      <c r="K49" s="24">
+        <v>8.68</v>
+      </c>
+      <c r="L49" s="24">
+        <f t="shared" si="1"/>
+        <v>9.206666667</v>
+      </c>
+      <c r="M49" s="25">
+        <v>2.0</v>
+      </c>
+      <c r="N49" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="O49" s="31"/>
+      <c r="P49" s="4">
+        <v>211.0</v>
+      </c>
+      <c r="Q49" s="28">
+        <v>-0.920368837543479</v>
+      </c>
+      <c r="R49" s="29">
+        <v>-1.00954296359786</v>
+      </c>
+      <c r="S49" s="30">
+        <f t="shared" si="2"/>
+        <v>0.09688955386</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="D50" s="20">
+        <v>148.0</v>
+      </c>
+      <c r="E50" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="F50" s="12">
+        <v>45740.0</v>
+      </c>
+      <c r="G50" s="14">
+        <v>546.0</v>
+      </c>
+      <c r="H50" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="I50" s="24">
+        <v>5.0</v>
+      </c>
+      <c r="J50" s="24">
+        <v>15.0</v>
+      </c>
+      <c r="K50" s="24">
+        <v>5.0</v>
+      </c>
+      <c r="L50" s="24">
+        <f t="shared" si="1"/>
+        <v>8.333333333</v>
+      </c>
+      <c r="M50" s="25">
+        <v>11.0</v>
+      </c>
+      <c r="N50" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="O50" s="27"/>
+      <c r="P50" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q50" s="28">
+        <v>-1.0182155187786</v>
+      </c>
+      <c r="R50" s="29">
+        <v>-0.866421412348542</v>
+      </c>
+      <c r="S50" s="30">
+        <f t="shared" si="2"/>
+        <v>-0.1490785631</v>
+      </c>
+    </row>
   </sheetData>
+  <conditionalFormatting sqref="I46:K50">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FF57BB8A"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S46:S50">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="formula" val="0.2"/>
+        <color rgb="FFFFFFFF"/>
+        <color rgb="FFE67C73"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
 </worksheet>
@@ -17322,20 +17915,20 @@
       <c r="J1" s="90"/>
       <c r="K1" s="90"/>
       <c r="L1" s="90"/>
-      <c r="M1" s="104"/>
+      <c r="M1" s="105"/>
       <c r="N1" s="90"/>
-      <c r="O1" s="104"/>
-      <c r="P1" s="104"/>
-      <c r="Q1" s="105"/>
+      <c r="O1" s="105"/>
+      <c r="P1" s="105"/>
+      <c r="Q1" s="106"/>
     </row>
     <row r="2">
-      <c r="A2" s="106">
+      <c r="A2" s="107">
         <v>48.0</v>
       </c>
-      <c r="B2" s="107" t="s">
+      <c r="B2" s="108" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="108">
+      <c r="C2" s="109">
         <v>45679.0</v>
       </c>
       <c r="D2" s="76">
@@ -17347,27 +17940,27 @@
       <c r="F2" s="76">
         <v>57.9999999999999</v>
       </c>
-      <c r="G2" s="109"/>
-      <c r="H2" s="109"/>
-      <c r="I2" s="109"/>
-      <c r="J2" s="109"/>
-      <c r="K2" s="109">
+      <c r="G2" s="110"/>
+      <c r="H2" s="110"/>
+      <c r="I2" s="110"/>
+      <c r="J2" s="110"/>
+      <c r="K2" s="110">
         <v>2.0</v>
       </c>
-      <c r="L2" s="109">
+      <c r="L2" s="110">
         <v>153.7</v>
       </c>
-      <c r="M2" s="110">
+      <c r="M2" s="111">
         <v>3507.81</v>
       </c>
       <c r="N2" s="76">
         <v>30.0</v>
       </c>
-      <c r="O2" s="109"/>
-      <c r="P2" s="109">
+      <c r="O2" s="110"/>
+      <c r="P2" s="110">
         <v>22.82244632400781</v>
       </c>
-      <c r="Q2" s="107">
+      <c r="Q2" s="108">
         <v>9.0</v>
       </c>
     </row>
@@ -17375,10 +17968,10 @@
       <c r="A3" s="76">
         <v>55.0</v>
       </c>
-      <c r="B3" s="107" t="s">
+      <c r="B3" s="108" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="108">
+      <c r="C3" s="109">
         <v>45679.0</v>
       </c>
       <c r="D3" s="76">
@@ -17387,30 +17980,30 @@
       <c r="E3" s="76" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="109">
+      <c r="F3" s="110">
         <v>61.0</v>
       </c>
-      <c r="G3" s="109"/>
-      <c r="H3" s="109"/>
-      <c r="I3" s="109"/>
-      <c r="J3" s="109"/>
-      <c r="K3" s="109">
+      <c r="G3" s="110"/>
+      <c r="H3" s="110"/>
+      <c r="I3" s="110"/>
+      <c r="J3" s="110"/>
+      <c r="K3" s="110">
         <v>7.0</v>
       </c>
-      <c r="L3" s="109">
+      <c r="L3" s="110">
         <v>174.21</v>
       </c>
-      <c r="M3" s="109">
+      <c r="M3" s="110">
         <v>1825.8099999999997</v>
       </c>
-      <c r="N3" s="109">
+      <c r="N3" s="110">
         <v>30.0</v>
       </c>
-      <c r="O3" s="109"/>
-      <c r="P3" s="109">
+      <c r="O3" s="110"/>
+      <c r="P3" s="110">
         <v>10.480512025716088</v>
       </c>
-      <c r="Q3" s="107">
+      <c r="Q3" s="108">
         <v>9.0</v>
       </c>
     </row>
@@ -17421,7 +18014,7 @@
       <c r="B4" s="76" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="108">
+      <c r="C4" s="109">
         <v>45680.0</v>
       </c>
       <c r="D4" s="76">
@@ -17430,30 +18023,30 @@
       <c r="E4" s="76" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="109">
+      <c r="F4" s="110">
         <v>62.0</v>
       </c>
-      <c r="G4" s="109"/>
-      <c r="H4" s="109"/>
-      <c r="I4" s="109"/>
-      <c r="J4" s="109"/>
-      <c r="K4" s="109">
+      <c r="G4" s="110"/>
+      <c r="H4" s="110"/>
+      <c r="I4" s="110"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="110">
         <v>3.0</v>
       </c>
-      <c r="L4" s="109">
+      <c r="L4" s="110">
         <v>171.72</v>
       </c>
-      <c r="M4" s="111">
+      <c r="M4" s="112">
         <v>5053.5599999999995</v>
       </c>
-      <c r="N4" s="109">
+      <c r="N4" s="110">
         <v>25.0</v>
       </c>
-      <c r="O4" s="109"/>
-      <c r="P4" s="109">
+      <c r="O4" s="110"/>
+      <c r="P4" s="110">
         <v>29.429070580013974</v>
       </c>
-      <c r="Q4" s="107">
+      <c r="Q4" s="108">
         <v>7.5</v>
       </c>
     </row>
@@ -17486,7 +18079,7 @@
       <c r="L5" s="76">
         <v>190.1</v>
       </c>
-      <c r="M5" s="112">
+      <c r="M5" s="113">
         <f>2.59+
 1339.47+
 236.53
@@ -17496,8 +18089,8 @@
       <c r="N5" s="76">
         <v>40.0</v>
       </c>
-      <c r="O5" s="109"/>
-      <c r="P5" s="109">
+      <c r="O5" s="110"/>
+      <c r="P5" s="110">
         <f t="shared" ref="P5:P6" si="1">M5/L5</f>
         <v>8.303997896</v>
       </c>
@@ -17521,7 +18114,7 @@
       <c r="L6" s="99">
         <v>127.26</v>
       </c>
-      <c r="M6" s="113">
+      <c r="M6" s="114">
         <f>1920.79+
 729.18+
 -17.44
@@ -17531,130 +18124,130 @@
       <c r="N6" s="76">
         <v>40.0</v>
       </c>
-      <c r="O6" s="109"/>
-      <c r="P6" s="109">
+      <c r="O6" s="110"/>
+      <c r="P6" s="110">
         <f t="shared" si="1"/>
         <v>20.68623291</v>
       </c>
     </row>
     <row r="7">
-      <c r="M7" s="114"/>
-      <c r="O7" s="114"/>
-      <c r="P7" s="114"/>
+      <c r="M7" s="115"/>
+      <c r="O7" s="115"/>
+      <c r="P7" s="115"/>
     </row>
     <row r="8">
-      <c r="F8" s="115"/>
-      <c r="G8" s="115"/>
-      <c r="H8" s="115"/>
-      <c r="I8" s="115"/>
-      <c r="J8" s="115"/>
-      <c r="K8" s="115"/>
-      <c r="L8" s="115"/>
-      <c r="M8" s="109"/>
-      <c r="N8" s="115"/>
-      <c r="O8" s="109"/>
-      <c r="P8" s="109"/>
+      <c r="F8" s="116"/>
+      <c r="G8" s="116"/>
+      <c r="H8" s="116"/>
+      <c r="I8" s="116"/>
+      <c r="J8" s="116"/>
+      <c r="K8" s="116"/>
+      <c r="L8" s="116"/>
+      <c r="M8" s="110"/>
+      <c r="N8" s="116"/>
+      <c r="O8" s="110"/>
+      <c r="P8" s="110"/>
     </row>
     <row r="9">
-      <c r="F9" s="115"/>
-      <c r="G9" s="115"/>
-      <c r="H9" s="115"/>
-      <c r="I9" s="115"/>
-      <c r="J9" s="115"/>
-      <c r="K9" s="115"/>
-      <c r="L9" s="115"/>
-      <c r="M9" s="109"/>
-      <c r="N9" s="115"/>
-      <c r="O9" s="109"/>
-      <c r="P9" s="109"/>
+      <c r="F9" s="116"/>
+      <c r="G9" s="116"/>
+      <c r="H9" s="116"/>
+      <c r="I9" s="116"/>
+      <c r="J9" s="116"/>
+      <c r="K9" s="116"/>
+      <c r="L9" s="116"/>
+      <c r="M9" s="110"/>
+      <c r="N9" s="116"/>
+      <c r="O9" s="110"/>
+      <c r="P9" s="110"/>
     </row>
     <row r="10">
-      <c r="F10" s="115"/>
-      <c r="G10" s="115"/>
-      <c r="H10" s="115"/>
-      <c r="I10" s="115"/>
-      <c r="J10" s="115"/>
-      <c r="K10" s="115"/>
-      <c r="L10" s="115"/>
-      <c r="M10" s="109"/>
-      <c r="N10" s="115"/>
-      <c r="O10" s="109"/>
-      <c r="P10" s="109"/>
+      <c r="F10" s="116"/>
+      <c r="G10" s="116"/>
+      <c r="H10" s="116"/>
+      <c r="I10" s="116"/>
+      <c r="J10" s="116"/>
+      <c r="K10" s="116"/>
+      <c r="L10" s="116"/>
+      <c r="M10" s="110"/>
+      <c r="N10" s="116"/>
+      <c r="O10" s="110"/>
+      <c r="P10" s="110"/>
     </row>
     <row r="11">
-      <c r="E11" s="116" t="s">
-        <v>143</v>
+      <c r="E11" s="117" t="s">
+        <v>144</v>
       </c>
       <c r="L11" s="76" t="s">
-        <v>144</v>
-      </c>
-      <c r="M11" s="110" t="s">
+        <v>145</v>
+      </c>
+      <c r="M11" s="111" t="s">
         <v>50</v>
       </c>
       <c r="N11" s="77" t="s">
         <v>39</v>
       </c>
-      <c r="O11" s="114"/>
-      <c r="P11" s="114"/>
+      <c r="O11" s="115"/>
+      <c r="P11" s="115"/>
     </row>
     <row r="12">
-      <c r="E12" s="116" t="s">
-        <v>145</v>
+      <c r="E12" s="117" t="s">
+        <v>146</v>
       </c>
       <c r="L12" s="76" t="s">
-        <v>146</v>
-      </c>
-      <c r="M12" s="110" t="s">
+        <v>147</v>
+      </c>
+      <c r="M12" s="111" t="s">
         <v>37</v>
       </c>
       <c r="N12" s="77" t="s">
         <v>38</v>
       </c>
-      <c r="O12" s="114"/>
-      <c r="P12" s="114"/>
+      <c r="O12" s="115"/>
+      <c r="P12" s="115"/>
     </row>
     <row r="13">
-      <c r="M13" s="114"/>
-      <c r="O13" s="114"/>
-      <c r="P13" s="114"/>
+      <c r="M13" s="115"/>
+      <c r="O13" s="115"/>
+      <c r="P13" s="115"/>
     </row>
     <row r="14">
-      <c r="F14" s="115"/>
-      <c r="G14" s="115"/>
-      <c r="H14" s="115"/>
-      <c r="I14" s="115"/>
-      <c r="J14" s="115"/>
-      <c r="K14" s="115"/>
-      <c r="L14" s="115"/>
-      <c r="M14" s="109"/>
-      <c r="N14" s="115"/>
-      <c r="O14" s="109"/>
-      <c r="P14" s="109"/>
+      <c r="F14" s="116"/>
+      <c r="G14" s="116"/>
+      <c r="H14" s="116"/>
+      <c r="I14" s="116"/>
+      <c r="J14" s="116"/>
+      <c r="K14" s="116"/>
+      <c r="L14" s="116"/>
+      <c r="M14" s="110"/>
+      <c r="N14" s="116"/>
+      <c r="O14" s="110"/>
+      <c r="P14" s="110"/>
     </row>
     <row r="15">
-      <c r="F15" s="115"/>
-      <c r="G15" s="115"/>
-      <c r="H15" s="115"/>
-      <c r="I15" s="115"/>
-      <c r="J15" s="115"/>
-      <c r="K15" s="115"/>
-      <c r="L15" s="115"/>
-      <c r="M15" s="109"/>
-      <c r="N15" s="115"/>
-      <c r="O15" s="109"/>
-      <c r="P15" s="109"/>
+      <c r="F15" s="116"/>
+      <c r="G15" s="116"/>
+      <c r="H15" s="116"/>
+      <c r="I15" s="116"/>
+      <c r="J15" s="116"/>
+      <c r="K15" s="116"/>
+      <c r="L15" s="116"/>
+      <c r="M15" s="110"/>
+      <c r="N15" s="116"/>
+      <c r="O15" s="110"/>
+      <c r="P15" s="110"/>
     </row>
     <row r="16">
-      <c r="A16" s="117">
+      <c r="A16" s="118">
         <v>48.0</v>
       </c>
-      <c r="B16" s="118" t="s">
+      <c r="B16" s="119" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="108">
+      <c r="C16" s="109">
         <v>45679.0</v>
       </c>
-      <c r="D16" s="119">
+      <c r="D16" s="104">
         <v>1363.0</v>
       </c>
       <c r="E16" s="76" t="s">
@@ -17663,27 +18256,27 @@
       <c r="F16" s="76">
         <v>57.5213675213675</v>
       </c>
-      <c r="G16" s="109"/>
-      <c r="H16" s="109"/>
-      <c r="I16" s="109"/>
-      <c r="J16" s="109"/>
-      <c r="K16" s="109">
+      <c r="G16" s="110"/>
+      <c r="H16" s="110"/>
+      <c r="I16" s="110"/>
+      <c r="J16" s="110"/>
+      <c r="K16" s="110">
         <v>5.99999999999999</v>
       </c>
-      <c r="L16" s="109">
+      <c r="L16" s="110">
         <v>127.72</v>
       </c>
-      <c r="M16" s="109">
+      <c r="M16" s="110">
         <v>958.71</v>
       </c>
       <c r="N16" s="76">
         <v>40.0</v>
       </c>
-      <c r="O16" s="109"/>
-      <c r="P16" s="109">
+      <c r="O16" s="110"/>
+      <c r="P16" s="110">
         <v>7.50634199812089</v>
       </c>
-      <c r="Q16" s="107">
+      <c r="Q16" s="108">
         <v>12.0</v>
       </c>
     </row>
@@ -17691,10 +18284,10 @@
       <c r="A17" s="76">
         <v>55.0</v>
       </c>
-      <c r="B17" s="107" t="s">
+      <c r="B17" s="108" t="s">
         <v>23</v>
       </c>
-      <c r="C17" s="108">
+      <c r="C17" s="109">
         <v>45679.0</v>
       </c>
       <c r="D17" s="76">
@@ -17703,30 +18296,30 @@
       <c r="E17" s="76" t="s">
         <v>17</v>
       </c>
-      <c r="F17" s="109">
+      <c r="F17" s="110">
         <v>57.7626974489822</v>
       </c>
-      <c r="G17" s="109"/>
-      <c r="H17" s="109"/>
-      <c r="I17" s="109"/>
-      <c r="J17" s="109"/>
-      <c r="K17" s="109">
+      <c r="G17" s="110"/>
+      <c r="H17" s="110"/>
+      <c r="I17" s="110"/>
+      <c r="J17" s="110"/>
+      <c r="K17" s="110">
         <v>7.0</v>
       </c>
-      <c r="L17" s="109">
+      <c r="L17" s="110">
         <v>174.21</v>
       </c>
-      <c r="M17" s="109">
+      <c r="M17" s="110">
         <v>1825.8099999999997</v>
       </c>
-      <c r="N17" s="109">
+      <c r="N17" s="110">
         <v>30.0</v>
       </c>
-      <c r="O17" s="109"/>
-      <c r="P17" s="109">
+      <c r="O17" s="110"/>
+      <c r="P17" s="110">
         <v>10.480512025716088</v>
       </c>
-      <c r="Q17" s="107">
+      <c r="Q17" s="108">
         <v>9.0</v>
       </c>
     </row>
@@ -17737,7 +18330,7 @@
       <c r="B18" s="76" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="108">
+      <c r="C18" s="109">
         <v>45680.0</v>
       </c>
       <c r="D18" s="76">
@@ -17746,71 +18339,71 @@
       <c r="E18" s="76" t="s">
         <v>17</v>
       </c>
-      <c r="F18" s="109">
+      <c r="F18" s="110">
         <v>61.8147668934429</v>
       </c>
-      <c r="G18" s="109"/>
-      <c r="H18" s="109"/>
-      <c r="I18" s="109"/>
-      <c r="J18" s="109"/>
-      <c r="K18" s="109">
+      <c r="G18" s="110"/>
+      <c r="H18" s="110"/>
+      <c r="I18" s="110"/>
+      <c r="J18" s="110"/>
+      <c r="K18" s="110">
         <v>5.0</v>
       </c>
-      <c r="L18" s="109">
+      <c r="L18" s="110">
         <v>149.66</v>
       </c>
-      <c r="M18" s="109">
+      <c r="M18" s="110">
         <v>8422.4</v>
       </c>
-      <c r="N18" s="109"/>
-      <c r="O18" s="109"/>
-      <c r="P18" s="109">
+      <c r="N18" s="110"/>
+      <c r="O18" s="110"/>
+      <c r="P18" s="110">
         <v>56.27689429373246</v>
       </c>
-      <c r="Q18" s="107">
+      <c r="Q18" s="108">
         <v>0.0</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="119">
+      <c r="A19" s="104">
         <v>77.0</v>
       </c>
-      <c r="B19" s="119" t="s">
+      <c r="B19" s="104" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="108">
+      <c r="C19" s="109">
         <v>45677.0</v>
       </c>
-      <c r="D19" s="119">
+      <c r="D19" s="104">
         <v>47.0</v>
       </c>
       <c r="E19" s="76" t="s">
         <v>17</v>
       </c>
-      <c r="F19" s="109">
+      <c r="F19" s="110">
         <v>60.7563651137594</v>
       </c>
-      <c r="G19" s="109"/>
-      <c r="H19" s="109"/>
-      <c r="I19" s="109"/>
-      <c r="J19" s="109"/>
-      <c r="K19" s="109">
+      <c r="G19" s="110"/>
+      <c r="H19" s="110"/>
+      <c r="I19" s="110"/>
+      <c r="J19" s="110"/>
+      <c r="K19" s="110">
         <v>12.0</v>
       </c>
-      <c r="L19" s="109">
+      <c r="L19" s="110">
         <v>152.96</v>
       </c>
-      <c r="M19" s="109">
+      <c r="M19" s="110">
         <v>2356.64</v>
       </c>
       <c r="N19" s="76">
         <v>60.0</v>
       </c>
-      <c r="O19" s="109"/>
-      <c r="P19" s="109">
+      <c r="O19" s="110"/>
+      <c r="P19" s="110">
         <v>15.406903765690375</v>
       </c>
-      <c r="Q19" s="107">
+      <c r="Q19" s="108">
         <v>18.0</v>
       </c>
     </row>
@@ -17821,7 +18414,7 @@
       <c r="B20" s="76" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="108">
+      <c r="C20" s="109">
         <v>45677.0</v>
       </c>
       <c r="D20" s="76">
@@ -17830,41 +18423,41 @@
       <c r="E20" s="76" t="s">
         <v>17</v>
       </c>
-      <c r="F20" s="109">
+      <c r="F20" s="110">
         <v>56.4173196363555</v>
       </c>
-      <c r="G20" s="109"/>
-      <c r="H20" s="109"/>
-      <c r="I20" s="109"/>
-      <c r="J20" s="109"/>
-      <c r="K20" s="109">
+      <c r="G20" s="110"/>
+      <c r="H20" s="110"/>
+      <c r="I20" s="110"/>
+      <c r="J20" s="110"/>
+      <c r="K20" s="110">
         <v>6.99999999999999</v>
       </c>
-      <c r="L20" s="109">
+      <c r="L20" s="110">
         <v>101.46</v>
       </c>
-      <c r="M20" s="109">
+      <c r="M20" s="110">
         <v>795.72</v>
       </c>
       <c r="N20" s="76">
         <v>30.0</v>
       </c>
-      <c r="O20" s="109"/>
-      <c r="P20" s="109">
+      <c r="O20" s="110"/>
+      <c r="P20" s="110">
         <v>7.842696629213484</v>
       </c>
-      <c r="Q20" s="107">
+      <c r="Q20" s="108">
         <v>9.0</v>
       </c>
     </row>
     <row r="21">
-      <c r="M21" s="114"/>
-      <c r="O21" s="114"/>
-      <c r="P21" s="114"/>
+      <c r="M21" s="115"/>
+      <c r="O21" s="115"/>
+      <c r="P21" s="115"/>
     </row>
     <row r="24">
       <c r="C24" s="90" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="25">
@@ -17874,27 +18467,27 @@
     </row>
     <row r="26">
       <c r="C26" s="120" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="27">
       <c r="C27" s="121" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="28">
-      <c r="C28" s="119" t="s">
-        <v>150</v>
+      <c r="C28" s="104" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="30">
       <c r="C30" s="93" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="31">
       <c r="C31" s="90" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L31" s="90" t="s">
         <v>38</v>
@@ -17967,7 +18560,7 @@
       <c r="W32" s="76">
         <v>1375.0</v>
       </c>
-      <c r="X32" s="119">
+      <c r="X32" s="104">
         <v>808.0</v>
       </c>
       <c r="Z32" s="99">
@@ -18015,7 +18608,7 @@
       <c r="AO32" s="76">
         <v>44.0</v>
       </c>
-      <c r="AP32" s="119">
+      <c r="AP32" s="104">
         <v>194.0</v>
       </c>
     </row>
@@ -18024,31 +18617,31 @@
         <f t="shared" ref="C33:J33" si="2">SUM(C34:C47)</f>
         <v>2.25</v>
       </c>
-      <c r="D33" s="107">
+      <c r="D33" s="108">
         <f t="shared" si="2"/>
         <v>-12.37</v>
       </c>
-      <c r="E33" s="107">
+      <c r="E33" s="108">
         <f t="shared" si="2"/>
         <v>-24.21</v>
       </c>
-      <c r="F33" s="107">
+      <c r="F33" s="108">
         <f t="shared" si="2"/>
         <v>11.79</v>
       </c>
-      <c r="G33" s="107">
+      <c r="G33" s="108">
         <f t="shared" si="2"/>
         <v>-15.52</v>
       </c>
-      <c r="H33" s="107">
+      <c r="H33" s="108">
         <f t="shared" si="2"/>
         <v>-8.53</v>
       </c>
-      <c r="I33" s="107">
+      <c r="I33" s="108">
         <f t="shared" si="2"/>
         <v>-4.23</v>
       </c>
-      <c r="J33" s="107">
+      <c r="J33" s="108">
         <f t="shared" si="2"/>
         <v>-24.21</v>
       </c>
@@ -18056,15 +18649,15 @@
         <f>SUM(L34:L51)</f>
         <v>-1.5</v>
       </c>
-      <c r="M33" s="107">
+      <c r="M33" s="108">
         <f t="shared" ref="M33:O33" si="3">SUM(M34:M47)</f>
         <v>24.31</v>
       </c>
-      <c r="N33" s="107">
+      <c r="N33" s="108">
         <f t="shared" si="3"/>
         <v>31.5</v>
       </c>
-      <c r="O33" s="107">
+      <c r="O33" s="108">
         <f t="shared" si="3"/>
         <v>-5.84</v>
       </c>
@@ -18072,7 +18665,7 @@
         <f>SUM(Q34:Q51)</f>
         <v>-7.31</v>
       </c>
-      <c r="R33" s="107">
+      <c r="R33" s="108">
         <f t="shared" ref="R33:W33" si="4">SUM(R34:R47)</f>
         <v>-20.51</v>
       </c>
@@ -18080,32 +18673,32 @@
         <f t="shared" si="4"/>
         <v>-10.26</v>
       </c>
-      <c r="T33" s="107">
+      <c r="T33" s="108">
         <f t="shared" si="4"/>
         <v>7.35</v>
       </c>
-      <c r="U33" s="107">
+      <c r="U33" s="108">
         <f t="shared" si="4"/>
         <v>17.63</v>
       </c>
-      <c r="V33" s="107">
+      <c r="V33" s="108">
         <f t="shared" si="4"/>
         <v>4.01</v>
       </c>
-      <c r="W33" s="107">
+      <c r="W33" s="108">
         <f t="shared" si="4"/>
         <v>-18.07</v>
       </c>
-      <c r="X33" s="118"/>
-      <c r="Z33" s="107">
+      <c r="X33" s="119"/>
+      <c r="Z33" s="108">
         <f t="shared" ref="Z33:AF33" si="5">SUM(Z34:Z101)</f>
         <v>-14.05</v>
       </c>
-      <c r="AA33" s="107">
+      <c r="AA33" s="108">
         <f t="shared" si="5"/>
         <v>18.35</v>
       </c>
-      <c r="AB33" s="107">
+      <c r="AB33" s="108">
         <f t="shared" si="5"/>
         <v>17.99</v>
       </c>
@@ -18113,11 +18706,11 @@
         <f t="shared" si="5"/>
         <v>13.54</v>
       </c>
-      <c r="AD33" s="107">
+      <c r="AD33" s="108">
         <f t="shared" si="5"/>
         <v>-12.75</v>
       </c>
-      <c r="AE33" s="107">
+      <c r="AE33" s="108">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
@@ -18129,19 +18722,19 @@
         <f t="shared" ref="AH33:AO33" si="6">SUM(AH34:AH49)</f>
         <v>4</v>
       </c>
-      <c r="AI33" s="107">
+      <c r="AI33" s="108">
         <f t="shared" si="6"/>
         <v>-23.73</v>
       </c>
-      <c r="AJ33" s="107">
+      <c r="AJ33" s="108">
         <f t="shared" si="6"/>
         <v>-49.24</v>
       </c>
-      <c r="AK33" s="107">
+      <c r="AK33" s="108">
         <f t="shared" si="6"/>
         <v>-59.85</v>
       </c>
-      <c r="AL33" s="107">
+      <c r="AL33" s="108">
         <f t="shared" si="6"/>
         <v>16.48</v>
       </c>
@@ -18149,7 +18742,7 @@
         <f t="shared" si="6"/>
         <v>1.43</v>
       </c>
-      <c r="AN33" s="107">
+      <c r="AN33" s="108">
         <f t="shared" si="6"/>
         <v>-17.53</v>
       </c>
@@ -18213,7 +18806,7 @@
       <c r="W34" s="76">
         <v>-4.94</v>
       </c>
-      <c r="X34" s="118"/>
+      <c r="X34" s="119"/>
       <c r="Z34" s="99">
         <v>1.43</v>
       </c>
@@ -18315,7 +18908,7 @@
       <c r="W35" s="76">
         <v>-4.28</v>
       </c>
-      <c r="X35" s="118"/>
+      <c r="X35" s="119"/>
       <c r="Z35" s="99">
         <v>-4.37</v>
       </c>
@@ -18417,7 +19010,7 @@
       <c r="W36" s="76">
         <v>5.81</v>
       </c>
-      <c r="X36" s="118"/>
+      <c r="X36" s="119"/>
       <c r="Z36" s="99">
         <v>5.91</v>
       </c>
@@ -18519,7 +19112,7 @@
       <c r="W37" s="76">
         <v>3.67</v>
       </c>
-      <c r="X37" s="118"/>
+      <c r="X37" s="119"/>
       <c r="Z37" s="99">
         <v>-4.19</v>
       </c>
@@ -18621,7 +19214,7 @@
       <c r="W38" s="76">
         <v>-4.06</v>
       </c>
-      <c r="X38" s="118"/>
+      <c r="X38" s="119"/>
       <c r="Z38" s="99">
         <v>-5.4</v>
       </c>
@@ -18723,7 +19316,7 @@
       <c r="W39" s="76">
         <v>0.72</v>
       </c>
-      <c r="X39" s="118"/>
+      <c r="X39" s="119"/>
       <c r="Z39" s="99">
         <v>0.88</v>
       </c>
@@ -18820,7 +19413,7 @@
       <c r="W40" s="76">
         <v>-5.09</v>
       </c>
-      <c r="X40" s="118"/>
+      <c r="X40" s="119"/>
       <c r="Z40" s="99">
         <v>-5.16</v>
       </c>
@@ -18917,7 +19510,7 @@
       <c r="W41" s="76">
         <v>10.73</v>
       </c>
-      <c r="X41" s="118"/>
+      <c r="X41" s="119"/>
       <c r="Z41" s="99">
         <v>-4.28</v>
       </c>
@@ -19014,7 +19607,7 @@
       <c r="W42" s="76">
         <v>3.08</v>
       </c>
-      <c r="X42" s="118"/>
+      <c r="X42" s="119"/>
       <c r="Z42" s="99">
         <v>-4.84</v>
       </c>
@@ -19111,7 +19704,7 @@
       <c r="W43" s="76">
         <v>-4.69</v>
       </c>
-      <c r="X43" s="118"/>
+      <c r="X43" s="119"/>
       <c r="Z43" s="99">
         <v>0.67</v>
       </c>
@@ -19208,7 +19801,7 @@
       <c r="W44" s="76">
         <v>-4.41</v>
       </c>
-      <c r="X44" s="118"/>
+      <c r="X44" s="119"/>
       <c r="Z44" s="99">
         <v>-4.35</v>
       </c>
@@ -19305,7 +19898,7 @@
       <c r="W45" s="76">
         <v>-4.24</v>
       </c>
-      <c r="X45" s="118"/>
+      <c r="X45" s="119"/>
       <c r="Z45" s="99">
         <v>5.55</v>
       </c>
@@ -19402,7 +19995,7 @@
       <c r="W46" s="76">
         <v>-6.0</v>
       </c>
-      <c r="X46" s="118"/>
+      <c r="X46" s="119"/>
       <c r="Z46" s="99">
         <v>2.51</v>
       </c>
@@ -19499,7 +20092,7 @@
       <c r="W47" s="76">
         <v>-4.37</v>
       </c>
-      <c r="X47" s="118"/>
+      <c r="X47" s="119"/>
       <c r="Z47" s="99">
         <v>-5.06</v>
       </c>
@@ -19554,7 +20147,7 @@
         <v>-5.39</v>
       </c>
       <c r="Q48" s="128"/>
-      <c r="X48" s="118"/>
+      <c r="X48" s="119"/>
       <c r="Z48" s="99">
         <v>3.18</v>
       </c>
@@ -19594,7 +20187,7 @@
       <c r="AM48" s="127"/>
     </row>
     <row r="49">
-      <c r="C49" s="118"/>
+      <c r="C49" s="119"/>
       <c r="L49" s="99">
         <v>-6.86</v>
       </c>
@@ -19765,7 +20358,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="L54" s="118"/>
+      <c r="L54" s="119"/>
       <c r="Z54" s="76">
         <v>6.48</v>
       </c>
@@ -19882,11 +20475,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="AC59" s="118"/>
+      <c r="AC59" s="119"/>
     </row>
     <row r="63">
       <c r="C63" s="90" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="65">
@@ -19909,22 +20502,22 @@
         <v>43</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J65" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K65" s="60" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L65" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M65" s="131" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N65" s="132" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="66">
@@ -20189,7 +20782,7 @@
     </row>
     <row r="76">
       <c r="C76" s="90" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="77">
@@ -20212,13 +20805,13 @@
         <v>43</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J77" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K77" s="60" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L77" s="4" t="s">
         <v>5</v>
@@ -20234,10 +20827,10 @@
         <v>8</v>
       </c>
       <c r="Q77" s="131" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="R77" s="132" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="78">
@@ -20563,7 +21156,7 @@
     </row>
     <row r="94">
       <c r="C94" s="76" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="96">
@@ -20583,7 +21176,7 @@
         <v>4</v>
       </c>
       <c r="H96" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I96" s="4" t="s">
         <v>42</v>
@@ -20592,22 +21185,22 @@
         <v>43</v>
       </c>
       <c r="K96" s="60" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L96" s="60" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M96" s="60" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N96" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O96" s="60" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P96" s="131" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q96" s="4" t="s">
         <v>5</v>
@@ -20622,7 +21215,7 @@
         <v>8</v>
       </c>
       <c r="U96" s="132" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="97">
@@ -21037,7 +21630,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="138" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B1" s="139"/>
       <c r="C1" s="139"/>
@@ -21054,55 +21647,55 @@
       <c r="N1" s="141"/>
       <c r="O1" s="141"/>
       <c r="P1" s="141"/>
-      <c r="U1" s="105"/>
+      <c r="U1" s="106"/>
       <c r="V1" s="90"/>
     </row>
     <row r="2">
       <c r="A2" s="143"/>
       <c r="B2" s="144" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C2" s="144" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D2" s="145" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E2" s="145" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F2" s="144" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G2" s="146" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H2" s="146" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I2" s="146" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J2" s="144"/>
       <c r="K2" s="144" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L2" s="144" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M2" s="147" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N2" s="146" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O2" s="146" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P2" s="146" t="s">
-        <v>179</v>
-      </c>
-      <c r="U2" s="105"/>
+        <v>180</v>
+      </c>
+      <c r="U2" s="106"/>
       <c r="V2" s="90"/>
     </row>
     <row r="3">
@@ -21200,9 +21793,9 @@
       <c r="P4" s="149">
         <v>724.0</v>
       </c>
-      <c r="Q4" s="109"/>
-      <c r="R4" s="109"/>
-      <c r="S4" s="109"/>
+      <c r="Q4" s="110"/>
+      <c r="R4" s="110"/>
+      <c r="S4" s="110"/>
     </row>
     <row r="5">
       <c r="A5" s="148" t="s">
@@ -21251,9 +21844,9 @@
       <c r="P5" s="149">
         <v>1051.0</v>
       </c>
-      <c r="Q5" s="109"/>
-      <c r="R5" s="109"/>
-      <c r="S5" s="109"/>
+      <c r="Q5" s="110"/>
+      <c r="R5" s="110"/>
+      <c r="S5" s="110"/>
     </row>
     <row r="6">
       <c r="A6" s="148" t="s">
@@ -21352,44 +21945,44 @@
       </c>
     </row>
     <row r="8">
-      <c r="O8" s="114"/>
+      <c r="O8" s="115"/>
     </row>
     <row r="9">
-      <c r="O9" s="109"/>
-      <c r="P9" s="115"/>
-      <c r="Q9" s="115"/>
-      <c r="R9" s="115"/>
-      <c r="S9" s="115"/>
-      <c r="V9" s="115"/>
+      <c r="O9" s="110"/>
+      <c r="P9" s="116"/>
+      <c r="Q9" s="116"/>
+      <c r="R9" s="116"/>
+      <c r="S9" s="116"/>
+      <c r="V9" s="116"/>
     </row>
     <row r="10">
-      <c r="A10" s="115"/>
+      <c r="A10" s="116"/>
       <c r="E10" s="76" t="s">
-        <v>180</v>
-      </c>
-      <c r="O10" s="109"/>
-      <c r="P10" s="115"/>
-      <c r="Q10" s="115"/>
-      <c r="R10" s="115"/>
+        <v>181</v>
+      </c>
+      <c r="O10" s="110"/>
+      <c r="P10" s="116"/>
+      <c r="Q10" s="116"/>
+      <c r="R10" s="116"/>
       <c r="S10" s="45"/>
       <c r="T10" s="32"/>
     </row>
     <row r="11">
-      <c r="A11" s="105"/>
+      <c r="A11" s="106"/>
       <c r="E11" s="23" t="s">
         <v>19</v>
       </c>
       <c r="F11" s="14">
         <v>343.0</v>
       </c>
-      <c r="O11" s="109"/>
-      <c r="P11" s="105"/>
-      <c r="Q11" s="105"/>
-      <c r="R11" s="105"/>
-      <c r="S11" s="105"/>
-      <c r="T11" s="105"/>
-      <c r="V11" s="105"/>
-      <c r="W11" s="105"/>
+      <c r="O11" s="110"/>
+      <c r="P11" s="106"/>
+      <c r="Q11" s="106"/>
+      <c r="R11" s="106"/>
+      <c r="S11" s="106"/>
+      <c r="T11" s="106"/>
+      <c r="V11" s="106"/>
+      <c r="W11" s="106"/>
     </row>
     <row r="12">
       <c r="A12" s="151"/>
@@ -21399,7 +21992,7 @@
       <c r="F12" s="14">
         <v>724.0</v>
       </c>
-      <c r="O12" s="114"/>
+      <c r="O12" s="115"/>
       <c r="P12" s="151"/>
       <c r="Q12" s="151"/>
       <c r="S12" s="151"/>
@@ -21415,7 +22008,7 @@
       <c r="F13" s="14">
         <v>1051.0</v>
       </c>
-      <c r="O13" s="114"/>
+      <c r="O13" s="115"/>
       <c r="P13" s="151"/>
       <c r="Q13" s="151"/>
       <c r="S13" s="151"/>
@@ -21431,8 +22024,8 @@
       <c r="F14" s="14">
         <v>47.0</v>
       </c>
-      <c r="N14" s="114"/>
-      <c r="O14" s="114"/>
+      <c r="N14" s="115"/>
+      <c r="O14" s="115"/>
       <c r="P14" s="151"/>
       <c r="Q14" s="151"/>
       <c r="S14" s="151"/>
@@ -21441,7 +22034,7 @@
       <c r="W14" s="151"/>
     </row>
     <row r="15">
-      <c r="A15" s="115"/>
+      <c r="A15" s="116"/>
       <c r="B15" s="151"/>
       <c r="C15" s="151"/>
       <c r="D15" s="151"/>
@@ -21457,17 +22050,17 @@
       <c r="J15" s="151"/>
       <c r="K15" s="151"/>
       <c r="N15" s="151"/>
-      <c r="O15" s="109"/>
-      <c r="P15" s="115"/>
-      <c r="Q15" s="115"/>
-      <c r="R15" s="115"/>
+      <c r="O15" s="110"/>
+      <c r="P15" s="116"/>
+      <c r="Q15" s="116"/>
+      <c r="R15" s="116"/>
       <c r="S15" s="151"/>
       <c r="T15" s="151"/>
       <c r="V15" s="151"/>
       <c r="W15" s="151"/>
     </row>
     <row r="16">
-      <c r="A16" s="115"/>
+      <c r="A16" s="116"/>
       <c r="B16" s="151"/>
       <c r="C16" s="151"/>
       <c r="D16" s="151"/>
@@ -21478,46 +22071,46 @@
       <c r="I16" s="151"/>
       <c r="J16" s="151"/>
       <c r="K16" s="151"/>
-      <c r="O16" s="109"/>
-      <c r="P16" s="115"/>
-      <c r="Q16" s="115"/>
-      <c r="R16" s="115"/>
+      <c r="O16" s="110"/>
+      <c r="P16" s="116"/>
+      <c r="Q16" s="116"/>
+      <c r="R16" s="116"/>
       <c r="S16" s="151"/>
       <c r="T16" s="151"/>
       <c r="V16" s="151"/>
     </row>
     <row r="17">
-      <c r="O17" s="109"/>
+      <c r="O17" s="110"/>
       <c r="P17" s="151"/>
       <c r="Q17" s="151"/>
       <c r="S17" s="151"/>
       <c r="T17" s="151"/>
     </row>
     <row r="18">
-      <c r="A18" s="109"/>
+      <c r="A18" s="110"/>
       <c r="E18" s="76" t="s">
-        <v>181</v>
-      </c>
-      <c r="O18" s="109"/>
-      <c r="P18" s="109"/>
-      <c r="Q18" s="109"/>
-      <c r="R18" s="109"/>
+        <v>182</v>
+      </c>
+      <c r="O18" s="110"/>
+      <c r="P18" s="110"/>
+      <c r="Q18" s="110"/>
+      <c r="R18" s="110"/>
       <c r="S18" s="151"/>
       <c r="T18" s="151"/>
       <c r="W18" s="151"/>
     </row>
     <row r="19">
-      <c r="A19" s="109"/>
+      <c r="A19" s="110"/>
       <c r="E19" s="23" t="s">
         <v>19</v>
       </c>
       <c r="F19" s="14">
         <v>663.0</v>
       </c>
-      <c r="O19" s="109"/>
-      <c r="P19" s="109"/>
-      <c r="Q19" s="109"/>
-      <c r="R19" s="109"/>
+      <c r="O19" s="110"/>
+      <c r="P19" s="110"/>
+      <c r="Q19" s="110"/>
+      <c r="R19" s="110"/>
       <c r="S19" s="151"/>
       <c r="T19" s="151"/>
     </row>
@@ -21528,7 +22121,7 @@
       <c r="F20" s="14">
         <v>654.0</v>
       </c>
-      <c r="O20" s="109"/>
+      <c r="O20" s="110"/>
       <c r="Q20" s="151"/>
       <c r="S20" s="151"/>
       <c r="T20" s="151"/>
@@ -21540,7 +22133,7 @@
       <c r="F21" s="14">
         <v>1051.0</v>
       </c>
-      <c r="O21" s="109"/>
+      <c r="O21" s="110"/>
       <c r="P21" s="151"/>
       <c r="T21" s="151"/>
     </row>
@@ -21551,8 +22144,8 @@
       <c r="F22" s="14">
         <v>622.0</v>
       </c>
-      <c r="M22" s="115"/>
-      <c r="O22" s="114"/>
+      <c r="M22" s="116"/>
+      <c r="O22" s="115"/>
       <c r="P22" s="151"/>
       <c r="T22" s="151"/>
     </row>
@@ -21563,26 +22156,26 @@
       <c r="F23" s="14">
         <v>1545.0</v>
       </c>
-      <c r="M23" s="115"/>
-      <c r="O23" s="114"/>
+      <c r="M23" s="116"/>
+      <c r="O23" s="115"/>
       <c r="T23" s="151"/>
     </row>
     <row r="24">
-      <c r="M24" s="115"/>
-      <c r="O24" s="114"/>
+      <c r="M24" s="116"/>
+      <c r="O24" s="115"/>
       <c r="Q24" s="151"/>
       <c r="T24" s="151"/>
     </row>
     <row r="25">
-      <c r="O25" s="114"/>
+      <c r="O25" s="115"/>
     </row>
     <row r="26">
-      <c r="O26" s="114"/>
+      <c r="O26" s="115"/>
       <c r="T26" s="151"/>
     </row>
     <row r="27">
-      <c r="N27" s="114"/>
-      <c r="O27" s="114"/>
+      <c r="N27" s="115"/>
+      <c r="O27" s="115"/>
     </row>
     <row r="32">
       <c r="C32" s="1" t="s">
@@ -21601,7 +22194,7 @@
         <v>4</v>
       </c>
       <c r="H32" s="152" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I32" s="4" t="s">
         <v>5</v>
@@ -21616,13 +22209,13 @@
         <v>8</v>
       </c>
       <c r="M32" s="153" t="s">
+        <v>160</v>
+      </c>
+      <c r="N32" s="60" t="s">
+        <v>174</v>
+      </c>
+      <c r="O32" s="154" t="s">
         <v>159</v>
-      </c>
-      <c r="N32" s="60" t="s">
-        <v>173</v>
-      </c>
-      <c r="O32" s="154" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="33">
@@ -22062,27 +22655,27 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="108"/>
-      <c r="B7" s="108"/>
-      <c r="C7" s="108"/>
-      <c r="D7" s="108"/>
-      <c r="E7" s="108"/>
-      <c r="F7" s="108"/>
-      <c r="G7" s="108"/>
-      <c r="H7" s="108"/>
-      <c r="I7" s="108"/>
-      <c r="J7" s="108"/>
-      <c r="K7" s="108"/>
+      <c r="A7" s="109"/>
+      <c r="B7" s="109"/>
+      <c r="C7" s="109"/>
+      <c r="D7" s="109"/>
+      <c r="E7" s="109"/>
+      <c r="F7" s="109"/>
+      <c r="G7" s="109"/>
+      <c r="H7" s="109"/>
+      <c r="I7" s="109"/>
+      <c r="J7" s="109"/>
+      <c r="K7" s="109"/>
     </row>
     <row r="9">
       <c r="B9" s="76" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C9" s="76" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D9" s="76" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="10">
@@ -22100,7 +22693,7 @@
         <v>-0.1658536585</v>
       </c>
       <c r="F10" s="76" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11">
@@ -22118,7 +22711,7 @@
         <v>-0.15</v>
       </c>
       <c r="F11" s="76" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12">
@@ -22156,16 +22749,16 @@
     </row>
     <row r="16">
       <c r="H16" s="76" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="17">
       <c r="G17" s="164"/>
       <c r="H17" s="90" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="I17" s="90" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="18">
@@ -22185,7 +22778,7 @@
         <v>332.0</v>
       </c>
       <c r="I18" s="83" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="19">
@@ -22202,10 +22795,10 @@
         <v>35</v>
       </c>
       <c r="H19" s="76" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I19" s="76" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="20">
@@ -22225,7 +22818,7 @@
         <v>411.0</v>
       </c>
       <c r="I20" s="76" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="21">
@@ -22233,10 +22826,10 @@
         <v>38</v>
       </c>
       <c r="H21" s="76" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I21" s="76" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="22">
@@ -22244,16 +22837,16 @@
         <v>39</v>
       </c>
       <c r="H22" s="76" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I22" s="76" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="11"/>
       <c r="I24" s="76" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="25">
@@ -22261,7 +22854,7 @@
         <v>1</v>
       </c>
       <c r="I25" s="76" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="26">
@@ -22271,8 +22864,8 @@
       <c r="C26" s="76">
         <v>332.0</v>
       </c>
-      <c r="M26" s="114"/>
-      <c r="N26" s="114"/>
+      <c r="M26" s="115"/>
+      <c r="N26" s="115"/>
     </row>
     <row r="27">
       <c r="B27" s="23" t="s">
@@ -22281,8 +22874,8 @@
       <c r="C27" s="76">
         <v>1288.0</v>
       </c>
-      <c r="M27" s="114"/>
-      <c r="N27" s="114"/>
+      <c r="M27" s="115"/>
+      <c r="N27" s="115"/>
     </row>
     <row r="28">
       <c r="B28" s="20" t="s">
@@ -22291,8 +22884,8 @@
       <c r="C28" s="76">
         <v>411.0</v>
       </c>
-      <c r="M28" s="114"/>
-      <c r="N28" s="114"/>
+      <c r="M28" s="115"/>
+      <c r="N28" s="115"/>
     </row>
     <row r="29">
       <c r="B29" s="20" t="s">
@@ -22301,8 +22894,8 @@
       <c r="C29" s="76">
         <v>1015.0</v>
       </c>
-      <c r="M29" s="114"/>
-      <c r="N29" s="114"/>
+      <c r="M29" s="115"/>
+      <c r="N29" s="115"/>
     </row>
     <row r="30">
       <c r="B30" s="20" t="s">
@@ -22312,90 +22905,90 @@
         <v>530.0</v>
       </c>
       <c r="I30" s="90" t="s">
-        <v>200</v>
-      </c>
-      <c r="M30" s="114"/>
-      <c r="N30" s="114"/>
+        <v>201</v>
+      </c>
+      <c r="M30" s="115"/>
+      <c r="N30" s="115"/>
     </row>
     <row r="31">
       <c r="I31" s="90" t="s">
-        <v>201</v>
-      </c>
-      <c r="M31" s="114"/>
-      <c r="N31" s="114"/>
+        <v>202</v>
+      </c>
+      <c r="M31" s="115"/>
+      <c r="N31" s="115"/>
     </row>
     <row r="32">
       <c r="I32" s="76" t="s">
-        <v>202</v>
-      </c>
-      <c r="M32" s="114"/>
-      <c r="N32" s="114"/>
+        <v>203</v>
+      </c>
+      <c r="M32" s="115"/>
+      <c r="N32" s="115"/>
     </row>
     <row r="33">
       <c r="I33" s="76" t="s">
-        <v>203</v>
-      </c>
-      <c r="M33" s="114"/>
-      <c r="N33" s="114"/>
+        <v>204</v>
+      </c>
+      <c r="M33" s="115"/>
+      <c r="N33" s="115"/>
     </row>
     <row r="34">
-      <c r="M34" s="114"/>
-      <c r="N34" s="114"/>
+      <c r="M34" s="115"/>
+      <c r="N34" s="115"/>
     </row>
     <row r="35">
       <c r="I35" s="76" t="s">
-        <v>204</v>
-      </c>
-      <c r="M35" s="114"/>
-      <c r="N35" s="114"/>
+        <v>205</v>
+      </c>
+      <c r="M35" s="115"/>
+      <c r="N35" s="115"/>
     </row>
     <row r="36">
-      <c r="M36" s="114"/>
-      <c r="N36" s="114"/>
+      <c r="M36" s="115"/>
+      <c r="N36" s="115"/>
     </row>
     <row r="37">
-      <c r="M37" s="114"/>
-      <c r="N37" s="114"/>
+      <c r="M37" s="115"/>
+      <c r="N37" s="115"/>
     </row>
     <row r="38">
-      <c r="M38" s="114"/>
-      <c r="N38" s="114"/>
+      <c r="M38" s="115"/>
+      <c r="N38" s="115"/>
     </row>
     <row r="39">
       <c r="I39" s="90" t="s">
-        <v>205</v>
-      </c>
-      <c r="M39" s="114"/>
-      <c r="N39" s="114"/>
+        <v>206</v>
+      </c>
+      <c r="M39" s="115"/>
+      <c r="N39" s="115"/>
     </row>
     <row r="40">
       <c r="I40" s="76" t="s">
-        <v>206</v>
-      </c>
-      <c r="M40" s="114"/>
-      <c r="N40" s="114"/>
+        <v>207</v>
+      </c>
+      <c r="M40" s="115"/>
+      <c r="N40" s="115"/>
     </row>
     <row r="41">
       <c r="I41" s="76" t="s">
-        <v>207</v>
-      </c>
-      <c r="M41" s="114"/>
-      <c r="N41" s="114"/>
+        <v>208</v>
+      </c>
+      <c r="M41" s="115"/>
+      <c r="N41" s="115"/>
     </row>
     <row r="42">
       <c r="I42" s="93" t="s">
-        <v>208</v>
-      </c>
-      <c r="M42" s="114"/>
-      <c r="N42" s="114"/>
+        <v>209</v>
+      </c>
+      <c r="M42" s="115"/>
+      <c r="N42" s="115"/>
     </row>
     <row r="43">
-      <c r="M43" s="114"/>
-      <c r="N43" s="114"/>
+      <c r="M43" s="115"/>
+      <c r="N43" s="115"/>
     </row>
     <row r="44">
       <c r="I44" s="90" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -22413,49 +23006,49 @@
   <sheetData>
     <row r="1">
       <c r="B1" s="76" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3">
       <c r="C3" s="76" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D3" s="76" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H3" s="76" t="s">
-        <v>213</v>
-      </c>
-      <c r="K3" s="114"/>
-      <c r="L3" s="114"/>
+        <v>214</v>
+      </c>
+      <c r="K3" s="115"/>
+      <c r="L3" s="115"/>
     </row>
     <row r="4">
       <c r="B4" s="76" t="s">
         <v>34</v>
       </c>
       <c r="C4" s="90" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D4" s="90" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H4" s="76" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I4" s="166"/>
       <c r="J4" s="166"/>
-      <c r="K4" s="114"/>
-      <c r="L4" s="114"/>
+      <c r="K4" s="115"/>
+      <c r="L4" s="115"/>
     </row>
     <row r="5">
       <c r="B5" s="90" t="s">
-        <v>216</v>
-      </c>
-      <c r="C5" s="105">
+        <v>217</v>
+      </c>
+      <c r="C5" s="106">
         <f t="shared" ref="C5:D5" si="1">SUM(C6:C18)</f>
         <v>23.59</v>
       </c>
-      <c r="D5" s="105">
+      <c r="D5" s="106">
         <f t="shared" si="1"/>
         <v>33.21</v>
       </c>
@@ -22464,7 +23057,7 @@
         <v>0.4077999152</v>
       </c>
       <c r="F5" s="76" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="6">
@@ -22483,7 +23076,7 @@
         <v>3.06</v>
       </c>
       <c r="H7" s="76" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="8">
@@ -22502,7 +23095,7 @@
         <v>2.3</v>
       </c>
       <c r="H9" s="76" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="10">
@@ -22521,7 +23114,7 @@
         <v>4.18</v>
       </c>
       <c r="H11" s="76" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="12">
@@ -22540,7 +23133,7 @@
         <v>2.35</v>
       </c>
       <c r="H13" s="76" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="14">
@@ -22567,7 +23160,7 @@
         <v>1.37</v>
       </c>
       <c r="H16" s="76" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="17">
@@ -22591,21 +23184,21 @@
         <v>35</v>
       </c>
       <c r="C20" s="90" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D20" s="90" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="90" t="s">
-        <v>216</v>
-      </c>
-      <c r="C21" s="105">
+        <v>217</v>
+      </c>
+      <c r="C21" s="106">
         <f t="shared" ref="C21:D21" si="2">sum(C22:C34)</f>
         <v>17.92</v>
       </c>
-      <c r="D21" s="105">
+      <c r="D21" s="106">
         <f t="shared" si="2"/>
         <v>25.11</v>
       </c>
@@ -22614,7 +23207,7 @@
         <v>0.4012276786</v>
       </c>
       <c r="F21" s="76" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="22">
@@ -22726,21 +23319,21 @@
         <v>37</v>
       </c>
       <c r="C37" s="90" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D37" s="90" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="90" t="s">
-        <v>216</v>
-      </c>
-      <c r="C38" s="105">
+        <v>217</v>
+      </c>
+      <c r="C38" s="106">
         <f t="shared" ref="C38:D38" si="3">sum(C39:C51)</f>
         <v>41.51</v>
       </c>
-      <c r="D38" s="105">
+      <c r="D38" s="106">
         <f t="shared" si="3"/>
         <v>42.82</v>
       </c>
@@ -22749,7 +23342,7 @@
         <v>0.03155866056</v>
       </c>
       <c r="F38" s="76" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="39">
@@ -22839,8 +23432,8 @@
       <c r="D49" s="76">
         <v>2.07</v>
       </c>
-      <c r="K49" s="114"/>
-      <c r="L49" s="114"/>
+      <c r="K49" s="115"/>
+      <c r="L49" s="115"/>
     </row>
     <row r="50">
       <c r="C50" s="76">
@@ -22849,8 +23442,8 @@
       <c r="D50" s="76">
         <v>3.14</v>
       </c>
-      <c r="K50" s="114"/>
-      <c r="L50" s="114"/>
+      <c r="K50" s="115"/>
+      <c r="L50" s="115"/>
     </row>
     <row r="51">
       <c r="C51" s="76">
@@ -22859,39 +23452,39 @@
       <c r="D51" s="76">
         <v>3.43</v>
       </c>
-      <c r="K51" s="114"/>
-      <c r="L51" s="114"/>
+      <c r="K51" s="115"/>
+      <c r="L51" s="115"/>
     </row>
     <row r="52">
-      <c r="K52" s="114"/>
-      <c r="L52" s="114"/>
+      <c r="K52" s="115"/>
+      <c r="L52" s="115"/>
     </row>
     <row r="53">
-      <c r="K53" s="114"/>
-      <c r="L53" s="114"/>
+      <c r="K53" s="115"/>
+      <c r="L53" s="115"/>
     </row>
     <row r="54">
       <c r="B54" s="90" t="s">
         <v>38</v>
       </c>
       <c r="C54" s="90" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D54" s="90" t="s">
-        <v>212</v>
-      </c>
-      <c r="K54" s="114"/>
-      <c r="L54" s="114"/>
+        <v>213</v>
+      </c>
+      <c r="K54" s="115"/>
+      <c r="L54" s="115"/>
     </row>
     <row r="55">
       <c r="B55" s="90" t="s">
-        <v>216</v>
-      </c>
-      <c r="C55" s="105">
+        <v>217</v>
+      </c>
+      <c r="C55" s="106">
         <f>sum(C56:C69)</f>
         <v>26.14</v>
       </c>
-      <c r="D55" s="105">
+      <c r="D55" s="106">
         <f>sum(D56:D68)</f>
         <v>26.29</v>
       </c>
@@ -22900,10 +23493,10 @@
         <v>0.005738332058</v>
       </c>
       <c r="F55" s="76" t="s">
-        <v>223</v>
-      </c>
-      <c r="K55" s="114"/>
-      <c r="L55" s="114"/>
+        <v>224</v>
+      </c>
+      <c r="K55" s="115"/>
+      <c r="L55" s="115"/>
     </row>
     <row r="56">
       <c r="C56" s="76">
@@ -22912,8 +23505,8 @@
       <c r="D56" s="76">
         <v>4.62</v>
       </c>
-      <c r="K56" s="114"/>
-      <c r="L56" s="114"/>
+      <c r="K56" s="115"/>
+      <c r="L56" s="115"/>
     </row>
     <row r="57">
       <c r="C57" s="76">
@@ -22922,8 +23515,8 @@
       <c r="D57" s="76">
         <v>1.75</v>
       </c>
-      <c r="K57" s="114"/>
-      <c r="L57" s="114"/>
+      <c r="K57" s="115"/>
+      <c r="L57" s="115"/>
     </row>
     <row r="58">
       <c r="C58" s="76">
@@ -22932,8 +23525,8 @@
       <c r="D58" s="76">
         <v>2.53</v>
       </c>
-      <c r="K58" s="114"/>
-      <c r="L58" s="114"/>
+      <c r="K58" s="115"/>
+      <c r="L58" s="115"/>
     </row>
     <row r="59">
       <c r="C59" s="76">
@@ -22942,8 +23535,8 @@
       <c r="D59" s="76">
         <v>2.5</v>
       </c>
-      <c r="K59" s="114"/>
-      <c r="L59" s="114"/>
+      <c r="K59" s="115"/>
+      <c r="L59" s="115"/>
     </row>
     <row r="60">
       <c r="C60" s="76">
@@ -22952,8 +23545,8 @@
       <c r="D60" s="76">
         <v>1.85</v>
       </c>
-      <c r="K60" s="114"/>
-      <c r="L60" s="114"/>
+      <c r="K60" s="115"/>
+      <c r="L60" s="115"/>
     </row>
     <row r="61">
       <c r="C61" s="76">
@@ -22962,8 +23555,8 @@
       <c r="D61" s="76">
         <v>1.51</v>
       </c>
-      <c r="K61" s="114"/>
-      <c r="L61" s="114"/>
+      <c r="K61" s="115"/>
+      <c r="L61" s="115"/>
     </row>
     <row r="62">
       <c r="C62" s="76">
@@ -22972,8 +23565,8 @@
       <c r="D62" s="76">
         <v>1.09</v>
       </c>
-      <c r="K62" s="114"/>
-      <c r="L62" s="114"/>
+      <c r="K62" s="115"/>
+      <c r="L62" s="115"/>
     </row>
     <row r="63">
       <c r="C63" s="76">
@@ -22982,8 +23575,8 @@
       <c r="D63" s="76">
         <v>1.39</v>
       </c>
-      <c r="K63" s="114"/>
-      <c r="L63" s="114"/>
+      <c r="K63" s="115"/>
+      <c r="L63" s="115"/>
     </row>
     <row r="64">
       <c r="C64" s="76">
@@ -22992,8 +23585,8 @@
       <c r="D64" s="76">
         <v>1.17</v>
       </c>
-      <c r="K64" s="114"/>
-      <c r="L64" s="114"/>
+      <c r="K64" s="115"/>
+      <c r="L64" s="115"/>
     </row>
     <row r="65">
       <c r="C65" s="76">
@@ -23002,8 +23595,8 @@
       <c r="D65" s="76">
         <v>1.9</v>
       </c>
-      <c r="K65" s="114"/>
-      <c r="L65" s="114"/>
+      <c r="K65" s="115"/>
+      <c r="L65" s="115"/>
     </row>
     <row r="66">
       <c r="C66" s="76">
@@ -23012,8 +23605,8 @@
       <c r="D66" s="76">
         <v>1.02</v>
       </c>
-      <c r="K66" s="114"/>
-      <c r="L66" s="114"/>
+      <c r="K66" s="115"/>
+      <c r="L66" s="115"/>
     </row>
     <row r="67">
       <c r="C67" s="76">
@@ -23022,8 +23615,8 @@
       <c r="D67" s="76">
         <v>2.42</v>
       </c>
-      <c r="K67" s="114"/>
-      <c r="L67" s="114"/>
+      <c r="K67" s="115"/>
+      <c r="L67" s="115"/>
     </row>
     <row r="68">
       <c r="C68" s="76">
@@ -23032,8 +23625,8 @@
       <c r="D68" s="76">
         <v>2.54</v>
       </c>
-      <c r="K68" s="114"/>
-      <c r="L68" s="114"/>
+      <c r="K68" s="115"/>
+      <c r="L68" s="115"/>
     </row>
     <row r="69">
       <c r="C69" s="76">
@@ -23042,35 +23635,35 @@
       <c r="D69" s="76">
         <v>1.46</v>
       </c>
-      <c r="K69" s="114"/>
-      <c r="L69" s="114"/>
+      <c r="K69" s="115"/>
+      <c r="L69" s="115"/>
     </row>
     <row r="70">
-      <c r="K70" s="114"/>
-      <c r="L70" s="114"/>
+      <c r="K70" s="115"/>
+      <c r="L70" s="115"/>
     </row>
     <row r="71">
       <c r="B71" s="90" t="s">
         <v>39</v>
       </c>
       <c r="C71" s="90" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D71" s="90" t="s">
-        <v>212</v>
-      </c>
-      <c r="K71" s="114"/>
-      <c r="L71" s="114"/>
+        <v>213</v>
+      </c>
+      <c r="K71" s="115"/>
+      <c r="L71" s="115"/>
     </row>
     <row r="72">
       <c r="B72" s="90" t="s">
-        <v>216</v>
-      </c>
-      <c r="C72" s="105">
+        <v>217</v>
+      </c>
+      <c r="C72" s="106">
         <f>sum(C73:C86)</f>
         <v>15.74</v>
       </c>
-      <c r="D72" s="105">
+      <c r="D72" s="106">
         <f>sum(D73:D85)</f>
         <v>21.91</v>
       </c>
@@ -23079,10 +23672,10 @@
         <v>0.3919949174</v>
       </c>
       <c r="F72" s="76" t="s">
-        <v>217</v>
-      </c>
-      <c r="K72" s="114"/>
-      <c r="L72" s="114"/>
+        <v>218</v>
+      </c>
+      <c r="K72" s="115"/>
+      <c r="L72" s="115"/>
     </row>
     <row r="73">
       <c r="C73" s="76">
@@ -23091,8 +23684,8 @@
       <c r="D73" s="76">
         <v>2.51</v>
       </c>
-      <c r="K73" s="114"/>
-      <c r="L73" s="114"/>
+      <c r="K73" s="115"/>
+      <c r="L73" s="115"/>
     </row>
     <row r="74">
       <c r="C74" s="76">
@@ -23101,8 +23694,8 @@
       <c r="D74" s="76">
         <v>1.39</v>
       </c>
-      <c r="K74" s="114"/>
-      <c r="L74" s="114"/>
+      <c r="K74" s="115"/>
+      <c r="L74" s="115"/>
     </row>
     <row r="75">
       <c r="C75" s="76">
@@ -23111,8 +23704,8 @@
       <c r="D75" s="76">
         <v>1.4</v>
       </c>
-      <c r="K75" s="114"/>
-      <c r="L75" s="114"/>
+      <c r="K75" s="115"/>
+      <c r="L75" s="115"/>
     </row>
     <row r="76">
       <c r="C76" s="76">
@@ -23121,8 +23714,8 @@
       <c r="D76" s="76">
         <v>3.85</v>
       </c>
-      <c r="K76" s="114"/>
-      <c r="L76" s="114"/>
+      <c r="K76" s="115"/>
+      <c r="L76" s="115"/>
     </row>
     <row r="77">
       <c r="C77" s="76">
@@ -23131,8 +23724,8 @@
       <c r="D77" s="76">
         <v>0.74</v>
       </c>
-      <c r="K77" s="114"/>
-      <c r="L77" s="114"/>
+      <c r="K77" s="115"/>
+      <c r="L77" s="115"/>
     </row>
     <row r="78">
       <c r="C78" s="76">
@@ -23141,8 +23734,8 @@
       <c r="D78" s="76">
         <v>0.99</v>
       </c>
-      <c r="K78" s="114"/>
-      <c r="L78" s="114"/>
+      <c r="K78" s="115"/>
+      <c r="L78" s="115"/>
     </row>
     <row r="79">
       <c r="C79" s="76">
@@ -23151,8 +23744,8 @@
       <c r="D79" s="76">
         <v>3.84</v>
       </c>
-      <c r="K79" s="114"/>
-      <c r="L79" s="114"/>
+      <c r="K79" s="115"/>
+      <c r="L79" s="115"/>
     </row>
     <row r="80">
       <c r="C80" s="76">
@@ -23161,8 +23754,8 @@
       <c r="D80" s="76">
         <v>1.58</v>
       </c>
-      <c r="K80" s="114"/>
-      <c r="L80" s="114"/>
+      <c r="K80" s="115"/>
+      <c r="L80" s="115"/>
     </row>
     <row r="81">
       <c r="C81" s="76">
@@ -23171,8 +23764,8 @@
       <c r="D81" s="76">
         <v>2.37</v>
       </c>
-      <c r="K81" s="114"/>
-      <c r="L81" s="114"/>
+      <c r="K81" s="115"/>
+      <c r="L81" s="115"/>
     </row>
     <row r="82">
       <c r="C82" s="76">
@@ -23181,8 +23774,8 @@
       <c r="D82" s="76">
         <v>0.56</v>
       </c>
-      <c r="K82" s="114"/>
-      <c r="L82" s="114"/>
+      <c r="K82" s="115"/>
+      <c r="L82" s="115"/>
     </row>
     <row r="83">
       <c r="C83" s="76">
@@ -23191,8 +23784,8 @@
       <c r="D83" s="76">
         <v>0.61</v>
       </c>
-      <c r="K83" s="114"/>
-      <c r="L83" s="114"/>
+      <c r="K83" s="115"/>
+      <c r="L83" s="115"/>
     </row>
     <row r="84">
       <c r="C84" s="76">
@@ -23201,8 +23794,8 @@
       <c r="D84" s="76">
         <v>1.22</v>
       </c>
-      <c r="K84" s="114"/>
-      <c r="L84" s="114"/>
+      <c r="K84" s="115"/>
+      <c r="L84" s="115"/>
     </row>
     <row r="85">
       <c r="C85" s="76">
@@ -23211,58 +23804,58 @@
       <c r="D85" s="76">
         <v>0.85</v>
       </c>
-      <c r="K85" s="114"/>
-      <c r="L85" s="114"/>
+      <c r="K85" s="115"/>
+      <c r="L85" s="115"/>
     </row>
     <row r="86">
-      <c r="K86" s="114"/>
-      <c r="L86" s="114"/>
+      <c r="K86" s="115"/>
+      <c r="L86" s="115"/>
     </row>
     <row r="87">
-      <c r="K87" s="114"/>
-      <c r="L87" s="114"/>
+      <c r="K87" s="115"/>
+      <c r="L87" s="115"/>
     </row>
     <row r="88">
-      <c r="K88" s="114"/>
-      <c r="L88" s="114"/>
+      <c r="K88" s="115"/>
+      <c r="L88" s="115"/>
     </row>
     <row r="89">
-      <c r="K89" s="114"/>
-      <c r="L89" s="114"/>
+      <c r="K89" s="115"/>
+      <c r="L89" s="115"/>
     </row>
     <row r="90">
-      <c r="K90" s="114"/>
-      <c r="L90" s="114"/>
+      <c r="K90" s="115"/>
+      <c r="L90" s="115"/>
     </row>
     <row r="91">
-      <c r="K91" s="114"/>
-      <c r="L91" s="114"/>
+      <c r="K91" s="115"/>
+      <c r="L91" s="115"/>
     </row>
     <row r="92">
-      <c r="K92" s="114"/>
-      <c r="L92" s="114"/>
+      <c r="K92" s="115"/>
+      <c r="L92" s="115"/>
     </row>
     <row r="93">
-      <c r="K93" s="114"/>
-      <c r="L93" s="114"/>
+      <c r="K93" s="115"/>
+      <c r="L93" s="115"/>
     </row>
     <row r="94">
-      <c r="K94" s="114"/>
-      <c r="L94" s="114"/>
+      <c r="K94" s="115"/>
+      <c r="L94" s="115"/>
     </row>
     <row r="95">
-      <c r="K95" s="114"/>
-      <c r="L95" s="114"/>
+      <c r="K95" s="115"/>
+      <c r="L95" s="115"/>
     </row>
     <row r="96">
       <c r="J96" s="79"/>
-      <c r="K96" s="114"/>
-      <c r="L96" s="114"/>
+      <c r="K96" s="115"/>
+      <c r="L96" s="115"/>
     </row>
     <row r="97">
       <c r="J97" s="79"/>
-      <c r="K97" s="114"/>
-      <c r="L97" s="114"/>
+      <c r="K97" s="115"/>
+      <c r="L97" s="115"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -23293,7 +23886,7 @@
     <row r="2">
       <c r="A2" s="79"/>
       <c r="B2" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C2" s="79">
         <v>0.1</v>
@@ -23303,7 +23896,7 @@
     <row r="3">
       <c r="A3" s="79"/>
       <c r="B3" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C3" s="21" t="str">
         <f>AVERAGE(#REF!)</f>
@@ -23318,7 +23911,7 @@
       <c r="L4" s="34"/>
       <c r="P4" s="34"/>
       <c r="AE4" s="76" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AF4" s="167">
         <f>CORREL(AE6:AE10000,AF6:AF10000)</f>
@@ -23328,50 +23921,50 @@
     <row r="5">
       <c r="A5" s="79"/>
       <c r="B5" s="34" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L5" s="34" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P5" s="34" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AE5" s="76" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AF5" s="76" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="79"/>
       <c r="B6" s="76" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F6" s="76" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K6" s="90"/>
       <c r="L6" s="90" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="N6" s="90" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P6" s="90" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="R6" s="90" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="V6" s="90" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AA6" s="76" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AB6" s="76" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AE6" s="76">
         <v>519.2</v>
@@ -23387,7 +23980,7 @@
         <f>AVERAGE(L10:L19)</f>
         <v>#VALUE!</v>
       </c>
-      <c r="N7" s="107" t="str">
+      <c r="N7" s="108" t="str">
         <f>SUM(N10:N29)/SUM(M10:M19)</f>
         <v>#VALUE!</v>
       </c>
@@ -23397,7 +23990,7 @@
       <c r="R7" s="76">
         <v>1.0</v>
       </c>
-      <c r="S7" s="107">
+      <c r="S7" s="108">
         <f t="shared" ref="S7:S9" si="1">COUNTIF($P$7:$P1775,R7)</f>
         <v>51</v>
       </c>
@@ -23405,7 +23998,7 @@
         <f t="shared" ref="T7:T9" si="2">S7/$S$10</f>
         <v>0.4636363636</v>
       </c>
-      <c r="V7" s="107">
+      <c r="V7" s="108">
         <v>33.0</v>
       </c>
       <c r="W7" s="163">
@@ -23413,9 +24006,9 @@
         <v>0.5454545455</v>
       </c>
       <c r="AA7" s="76" t="s">
-        <v>241</v>
-      </c>
-      <c r="AB7" s="107">
+        <v>242</v>
+      </c>
+      <c r="AB7" s="108">
         <f t="shared" ref="AB7:AB16" si="4">LEFT(REPLACE(AA7,1,1,""),FIND(",", AA7)-2)/1</f>
         <v>81</v>
       </c>
@@ -23429,14 +24022,14 @@
     <row r="8">
       <c r="A8" s="79"/>
       <c r="B8" s="171" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C8" s="172" t="str">
         <f t="shared" ref="C8:C17" si="5">REPLACE(B8,FIND(".",B8),1,",")*1</f>
         <v>#VALUE!</v>
       </c>
       <c r="F8" s="99" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G8" s="172" t="str">
         <f t="shared" ref="G8:G27" si="6">REPLACE(F8,FIND(".",F8),1,",")*1</f>
@@ -23455,7 +24048,7 @@
       <c r="R8" s="76">
         <v>0.0</v>
       </c>
-      <c r="S8" s="107">
+      <c r="S8" s="108">
         <f t="shared" si="1"/>
         <v>29</v>
       </c>
@@ -23463,7 +24056,7 @@
         <f t="shared" si="2"/>
         <v>0.2636363636</v>
       </c>
-      <c r="V8" s="107">
+      <c r="V8" s="108">
         <v>19.0</v>
       </c>
       <c r="W8" s="163">
@@ -23471,9 +24064,9 @@
         <v>0.5263157895</v>
       </c>
       <c r="AA8" s="76" t="s">
-        <v>244</v>
-      </c>
-      <c r="AB8" s="107">
+        <v>245</v>
+      </c>
+      <c r="AB8" s="108">
         <f t="shared" si="4"/>
         <v>54</v>
       </c>
@@ -23487,14 +24080,14 @@
     <row r="9">
       <c r="A9" s="79"/>
       <c r="B9" s="171" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C9" s="172" t="str">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="F9" s="99" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G9" s="172" t="str">
         <f t="shared" si="6"/>
@@ -23508,13 +24101,13 @@
       </c>
       <c r="K9" s="79"/>
       <c r="L9" s="168" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M9" s="168" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="N9" s="90" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P9" s="170">
         <v>1.0</v>
@@ -23522,7 +24115,7 @@
       <c r="R9" s="76">
         <v>2.0</v>
       </c>
-      <c r="S9" s="107">
+      <c r="S9" s="108">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
@@ -23530,7 +24123,7 @@
         <f t="shared" si="2"/>
         <v>0.2727272727</v>
       </c>
-      <c r="V9" s="107">
+      <c r="V9" s="108">
         <v>24.0</v>
       </c>
       <c r="W9" s="163">
@@ -23538,9 +24131,9 @@
         <v>0.25</v>
       </c>
       <c r="AA9" s="76" t="s">
-        <v>250</v>
-      </c>
-      <c r="AB9" s="107">
+        <v>251</v>
+      </c>
+      <c r="AB9" s="108">
         <f t="shared" si="4"/>
         <v>81</v>
       </c>
@@ -23554,14 +24147,14 @@
     <row r="10">
       <c r="A10" s="79"/>
       <c r="B10" s="173" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C10" s="172" t="str">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="F10" s="99" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G10" s="172" t="str">
         <f t="shared" si="6"/>
@@ -23582,25 +24175,25 @@
         <f t="shared" ref="M10:M18" si="8">M11*2</f>
         <v>512</v>
       </c>
-      <c r="N10" s="107" t="str">
+      <c r="N10" s="108" t="str">
         <f t="shared" ref="N10:N19" si="9">M10*L10</f>
         <v>#VALUE!</v>
       </c>
       <c r="P10" s="170">
         <v>0.0</v>
       </c>
-      <c r="S10" s="107">
+      <c r="S10" s="108">
         <f>SUM(S7:S9)</f>
         <v>110</v>
       </c>
-      <c r="V10" s="107">
+      <c r="V10" s="108">
         <f>SUM(V7:V9)</f>
         <v>76</v>
       </c>
       <c r="AA10" s="76" t="s">
-        <v>253</v>
-      </c>
-      <c r="AB10" s="107">
+        <v>254</v>
+      </c>
+      <c r="AB10" s="108">
         <f t="shared" si="4"/>
         <v>54</v>
       </c>
@@ -23613,14 +24206,14 @@
     </row>
     <row r="11">
       <c r="B11" s="171" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C11" s="172" t="str">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="F11" s="99" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="G11" s="172" t="str">
         <f t="shared" si="6"/>
@@ -23641,7 +24234,7 @@
         <f t="shared" si="8"/>
         <v>256</v>
       </c>
-      <c r="N11" s="107" t="str">
+      <c r="N11" s="108" t="str">
         <f t="shared" si="9"/>
         <v>#VALUE!</v>
       </c>
@@ -23649,9 +24242,9 @@
         <v>2.0</v>
       </c>
       <c r="AA11" s="76" t="s">
-        <v>256</v>
-      </c>
-      <c r="AB11" s="107">
+        <v>257</v>
+      </c>
+      <c r="AB11" s="108">
         <f t="shared" si="4"/>
         <v>54</v>
       </c>
@@ -23664,14 +24257,14 @@
     </row>
     <row r="12">
       <c r="B12" s="173" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C12" s="172" t="str">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="F12" s="99" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G12" s="172" t="str">
         <f t="shared" si="6"/>
@@ -23692,7 +24285,7 @@
         <f t="shared" si="8"/>
         <v>128</v>
       </c>
-      <c r="N12" s="107" t="str">
+      <c r="N12" s="108" t="str">
         <f t="shared" si="9"/>
         <v>#VALUE!</v>
       </c>
@@ -23700,9 +24293,9 @@
         <v>1.0</v>
       </c>
       <c r="AA12" s="76" t="s">
-        <v>253</v>
-      </c>
-      <c r="AB12" s="107">
+        <v>254</v>
+      </c>
+      <c r="AB12" s="108">
         <f t="shared" si="4"/>
         <v>54</v>
       </c>
@@ -23715,14 +24308,14 @@
     </row>
     <row r="13">
       <c r="B13" s="171" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C13" s="172" t="str">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="F13" s="99" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G13" s="172" t="str">
         <f t="shared" si="6"/>
@@ -23742,28 +24335,28 @@
         <f t="shared" si="8"/>
         <v>64</v>
       </c>
-      <c r="N13" s="107" t="str">
+      <c r="N13" s="108" t="str">
         <f t="shared" si="9"/>
         <v>#VALUE!</v>
       </c>
       <c r="P13" s="170">
         <v>1.0</v>
       </c>
-      <c r="Q13" s="105"/>
+      <c r="Q13" s="106"/>
       <c r="R13" s="143"/>
       <c r="S13" s="148" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="T13" s="148" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="U13" s="148" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AA13" s="76" t="s">
-        <v>264</v>
-      </c>
-      <c r="AB13" s="107">
+        <v>265</v>
+      </c>
+      <c r="AB13" s="108">
         <f t="shared" si="4"/>
         <v>81</v>
       </c>
@@ -23776,14 +24369,14 @@
     </row>
     <row r="14">
       <c r="B14" s="171" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C14" s="172" t="str">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="F14" s="99" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="G14" s="172" t="str">
         <f t="shared" si="6"/>
@@ -23803,7 +24396,7 @@
         <f t="shared" si="8"/>
         <v>32</v>
       </c>
-      <c r="N14" s="107" t="str">
+      <c r="N14" s="108" t="str">
         <f t="shared" si="9"/>
         <v>#VALUE!</v>
       </c>
@@ -23823,9 +24416,9 @@
         <v>11.0</v>
       </c>
       <c r="AA14" s="76" t="s">
-        <v>267</v>
-      </c>
-      <c r="AB14" s="107">
+        <v>268</v>
+      </c>
+      <c r="AB14" s="108">
         <f t="shared" si="4"/>
         <v>81</v>
       </c>
@@ -23838,14 +24431,14 @@
     </row>
     <row r="15">
       <c r="B15" s="171" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C15" s="172" t="str">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="F15" s="99" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G15" s="172" t="str">
         <f t="shared" si="6"/>
@@ -23865,7 +24458,7 @@
         <f t="shared" si="8"/>
         <v>16</v>
       </c>
-      <c r="N15" s="107" t="str">
+      <c r="N15" s="108" t="str">
         <f t="shared" si="9"/>
         <v>#VALUE!</v>
       </c>
@@ -23885,9 +24478,9 @@
         <v>13.0</v>
       </c>
       <c r="AA15" s="76" t="s">
-        <v>270</v>
-      </c>
-      <c r="AB15" s="107">
+        <v>271</v>
+      </c>
+      <c r="AB15" s="108">
         <f t="shared" si="4"/>
         <v>54</v>
       </c>
@@ -23900,14 +24493,14 @@
     </row>
     <row r="16">
       <c r="B16" s="171" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C16" s="172" t="str">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="F16" s="99" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G16" s="172" t="str">
         <f t="shared" si="6"/>
@@ -23927,7 +24520,7 @@
         <f t="shared" si="8"/>
         <v>8</v>
       </c>
-      <c r="N16" s="107" t="str">
+      <c r="N16" s="108" t="str">
         <f t="shared" si="9"/>
         <v>#VALUE!</v>
       </c>
@@ -23947,9 +24540,9 @@
         <v>12.0</v>
       </c>
       <c r="AA16" s="76" t="s">
-        <v>273</v>
-      </c>
-      <c r="AB16" s="107">
+        <v>274</v>
+      </c>
+      <c r="AB16" s="108">
         <f t="shared" si="4"/>
         <v>81</v>
       </c>
@@ -23962,14 +24555,14 @@
     </row>
     <row r="17">
       <c r="B17" s="171" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C17" s="172" t="str">
         <f t="shared" si="5"/>
         <v>#VALUE!</v>
       </c>
       <c r="F17" s="99" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G17" s="172" t="str">
         <f t="shared" si="6"/>
@@ -23989,7 +24582,7 @@
         <f t="shared" si="8"/>
         <v>4</v>
       </c>
-      <c r="N17" s="107" t="str">
+      <c r="N17" s="108" t="str">
         <f t="shared" si="9"/>
         <v>#VALUE!</v>
       </c>
@@ -23997,7 +24590,7 @@
         <v>1.0</v>
       </c>
       <c r="R17" s="148" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="S17" s="175">
         <f t="shared" ref="S17:U17" si="10">SUM(S14:S16)</f>
@@ -24020,7 +24613,7 @@
     </row>
     <row r="18">
       <c r="F18" s="99" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G18" s="172" t="str">
         <f t="shared" si="6"/>
@@ -24037,7 +24630,7 @@
         <f t="shared" si="8"/>
         <v>2</v>
       </c>
-      <c r="N18" s="107" t="str">
+      <c r="N18" s="108" t="str">
         <f t="shared" si="9"/>
         <v>#VALUE!</v>
       </c>
@@ -24057,14 +24650,14 @@
     </row>
     <row r="19">
       <c r="B19" s="90" t="s">
-        <v>278</v>
-      </c>
-      <c r="C19" s="107" t="str">
+        <v>279</v>
+      </c>
+      <c r="C19" s="108" t="str">
         <f>AVERAGE(C8:C17)</f>
         <v>#VALUE!</v>
       </c>
       <c r="F19" s="99" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G19" s="172" t="str">
         <f t="shared" si="6"/>
@@ -24080,7 +24673,7 @@
       <c r="M19" s="79">
         <v>1.0</v>
       </c>
-      <c r="N19" s="107" t="str">
+      <c r="N19" s="108" t="str">
         <f t="shared" si="9"/>
         <v>#VALUE!</v>
       </c>
@@ -24092,9 +24685,9 @@
       <c r="T19" s="21"/>
       <c r="U19" s="21"/>
       <c r="AA19" s="76" t="s">
-        <v>280</v>
-      </c>
-      <c r="AB19" s="107">
+        <v>281</v>
+      </c>
+      <c r="AB19" s="108">
         <f>AVERAGE(AB7:AB16)</f>
         <v>67.5</v>
       </c>
@@ -24107,7 +24700,7 @@
     </row>
     <row r="20">
       <c r="F20" s="99" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G20" s="172" t="str">
         <f t="shared" si="6"/>
@@ -24132,7 +24725,7 @@
     </row>
     <row r="21">
       <c r="F21" s="99" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="G21" s="172" t="str">
         <f t="shared" si="6"/>
@@ -24146,13 +24739,13 @@
       </c>
       <c r="R21" s="143"/>
       <c r="S21" s="148" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="T21" s="148" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="U21" s="148" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AE21" s="76">
         <v>146.62</v>
@@ -24164,7 +24757,7 @@
     <row r="22">
       <c r="C22" s="172"/>
       <c r="F22" s="99" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G22" s="172" t="str">
         <f t="shared" si="6"/>
@@ -24237,7 +24830,7 @@
     </row>
     <row r="24">
       <c r="F24" s="99" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="G24" s="172" t="str">
         <f t="shared" si="6"/>
@@ -24273,7 +24866,7 @@
     </row>
     <row r="25">
       <c r="F25" s="99" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G25" s="172" t="str">
         <f t="shared" si="6"/>
@@ -24286,7 +24879,7 @@
         <v>1.0</v>
       </c>
       <c r="R25" s="148" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="S25" s="175">
         <f t="shared" ref="S25:U25" si="14">SUM(S22:S24)</f>
@@ -24309,7 +24902,7 @@
     </row>
     <row r="26">
       <c r="F26" s="99" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G26" s="172" t="str">
         <f t="shared" si="6"/>
@@ -24354,7 +24947,7 @@
         <v>1.0</v>
       </c>
       <c r="AA28" s="76" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AB28" s="76" t="s">
         <v>44</v>
@@ -24371,9 +24964,9 @@
     </row>
     <row r="29">
       <c r="F29" s="90" t="s">
-        <v>278</v>
-      </c>
-      <c r="G29" s="107" t="str">
+        <v>279</v>
+      </c>
+      <c r="G29" s="108" t="str">
         <f>AVERAGE(G8:G27)</f>
         <v>#VALUE!</v>
       </c>
@@ -24389,13 +24982,13 @@
       <c r="P29" s="170">
         <v>0.0</v>
       </c>
-      <c r="AA29" s="115">
+      <c r="AA29" s="116">
         <v>1051.0</v>
       </c>
       <c r="AB29" s="76">
         <v>207.56</v>
       </c>
-      <c r="AC29" s="107">
+      <c r="AC29" s="108">
         <f t="shared" ref="AC29:AC43" si="15">VLOOKUP(AA29,$AA$48:$AB$62,2,0)</f>
         <v>263.81</v>
       </c>
@@ -24420,7 +25013,7 @@
       <c r="AB30" s="76">
         <v>185.35</v>
       </c>
-      <c r="AC30" s="107">
+      <c r="AC30" s="108">
         <f t="shared" si="15"/>
         <v>130.76</v>
       </c>
@@ -24445,7 +25038,7 @@
       <c r="AB31" s="76">
         <v>121.6</v>
       </c>
-      <c r="AC31" s="107">
+      <c r="AC31" s="108">
         <f t="shared" si="15"/>
         <v>78.68</v>
       </c>
@@ -24461,20 +25054,20 @@
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="119" t="s">
-        <v>288</v>
+      <c r="B32" s="104" t="s">
+        <v>289</v>
       </c>
       <c r="G32" s="172"/>
       <c r="P32" s="170">
         <v>0.0</v>
       </c>
-      <c r="AA32" s="115">
+      <c r="AA32" s="116">
         <v>1475.0</v>
       </c>
       <c r="AB32" s="76">
         <v>120.82</v>
       </c>
-      <c r="AC32" s="107">
+      <c r="AC32" s="108">
         <f t="shared" si="15"/>
         <v>83.5</v>
       </c>
@@ -24491,19 +25084,19 @@
     </row>
     <row r="33">
       <c r="B33" s="178" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G33" s="179"/>
       <c r="P33" s="170">
         <v>1.0</v>
       </c>
-      <c r="AA33" s="115">
+      <c r="AA33" s="116">
         <v>1545.0</v>
       </c>
       <c r="AB33" s="76">
         <v>111.42</v>
       </c>
-      <c r="AC33" s="107">
+      <c r="AC33" s="108">
         <f t="shared" si="15"/>
         <v>101.16</v>
       </c>
@@ -24528,7 +25121,7 @@
       <c r="AB34" s="76">
         <v>104.32</v>
       </c>
-      <c r="AC34" s="107">
+      <c r="AC34" s="108">
         <f t="shared" si="15"/>
         <v>60.31</v>
       </c>
@@ -24545,18 +25138,18 @@
     </row>
     <row r="35">
       <c r="H35" s="90" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P35" s="170">
         <v>1.0</v>
       </c>
-      <c r="AA35" s="115">
+      <c r="AA35" s="116">
         <v>1426.0</v>
       </c>
       <c r="AB35" s="76">
         <v>101.23</v>
       </c>
-      <c r="AC35" s="107">
+      <c r="AC35" s="108">
         <f t="shared" si="15"/>
         <v>68.02</v>
       </c>
@@ -24581,13 +25174,13 @@
       <c r="P36" s="170">
         <v>1.0</v>
       </c>
-      <c r="AA36" s="115">
+      <c r="AA36" s="116">
         <v>1447.0</v>
       </c>
       <c r="AB36" s="76">
         <v>97.89</v>
       </c>
-      <c r="AC36" s="107">
+      <c r="AC36" s="108">
         <f t="shared" si="15"/>
         <v>138.76</v>
       </c>
@@ -24603,12 +25196,12 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="105"/>
-      <c r="B37" s="105"/>
-      <c r="C37" s="105"/>
+      <c r="A37" s="106"/>
+      <c r="B37" s="106"/>
+      <c r="C37" s="106"/>
       <c r="D37" s="181">
         <f>AVERAGE(D39:D1775)</f>
-        <v>3.399830508</v>
+        <v>3.713559322</v>
       </c>
       <c r="G37" s="90" t="s">
         <v>35</v>
@@ -24625,7 +25218,7 @@
       <c r="AB37" s="76">
         <v>87.93</v>
       </c>
-      <c r="AC37" s="107">
+      <c r="AC37" s="108">
         <f t="shared" si="15"/>
         <v>58.8</v>
       </c>
@@ -24650,13 +25243,13 @@
       <c r="P38" s="170">
         <v>2.0</v>
       </c>
-      <c r="AA38" s="115">
+      <c r="AA38" s="116">
         <v>1526.0</v>
       </c>
       <c r="AB38" s="76">
         <v>85.82</v>
       </c>
-      <c r="AC38" s="107">
+      <c r="AC38" s="108">
         <f t="shared" si="15"/>
         <v>53.3</v>
       </c>
@@ -24673,11 +25266,11 @@
     </row>
     <row r="39">
       <c r="C39" s="183" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D39" s="184">
         <f t="shared" ref="D39:D221" si="17">IF(COUNTA(C39)=1,C39/1,"")</f>
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="G39" s="90" t="s">
         <v>38</v>
@@ -24694,7 +25287,7 @@
       <c r="AB39" s="76">
         <v>78.09</v>
       </c>
-      <c r="AC39" s="107">
+      <c r="AC39" s="108">
         <f t="shared" si="15"/>
         <v>73.76</v>
       </c>
@@ -24711,11 +25304,11 @@
     </row>
     <row r="40">
       <c r="C40" s="185" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D40" s="172">
         <f t="shared" si="17"/>
-        <v>0.77</v>
+        <v>0.85</v>
       </c>
       <c r="G40" s="90" t="s">
         <v>39</v>
@@ -24726,13 +25319,13 @@
       <c r="P40" s="170">
         <v>2.0</v>
       </c>
-      <c r="AA40" s="115">
+      <c r="AA40" s="116">
         <v>1606.0</v>
       </c>
       <c r="AB40" s="76">
         <v>77.21</v>
       </c>
-      <c r="AC40" s="107">
+      <c r="AC40" s="108">
         <f t="shared" si="15"/>
         <v>75.05</v>
       </c>
@@ -24749,22 +25342,22 @@
     </row>
     <row r="41">
       <c r="C41" s="185" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D41" s="172">
         <f t="shared" si="17"/>
-        <v>2.44</v>
+        <v>2.68</v>
       </c>
       <c r="P41" s="170">
         <v>0.0</v>
       </c>
-      <c r="AA41" s="115">
+      <c r="AA41" s="116">
         <v>1164.0</v>
       </c>
       <c r="AB41" s="76">
         <v>76.05</v>
       </c>
-      <c r="AC41" s="107">
+      <c r="AC41" s="108">
         <f t="shared" si="15"/>
         <v>26.27</v>
       </c>
@@ -24781,22 +25374,22 @@
     </row>
     <row r="42">
       <c r="C42" s="185" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D42" s="172">
         <f t="shared" si="17"/>
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="P42" s="170">
         <v>2.0</v>
       </c>
-      <c r="AA42" s="115">
+      <c r="AA42" s="116">
         <v>1448.0</v>
       </c>
       <c r="AB42" s="76">
         <v>71.77</v>
       </c>
-      <c r="AC42" s="107">
+      <c r="AC42" s="108">
         <f t="shared" si="15"/>
         <v>39.69</v>
       </c>
@@ -24813,22 +25406,22 @@
     </row>
     <row r="43">
       <c r="C43" s="185" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D43" s="172">
         <f t="shared" si="17"/>
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="P43" s="170">
         <v>1.0</v>
       </c>
-      <c r="AA43" s="115">
+      <c r="AA43" s="116">
         <v>1614.0</v>
       </c>
       <c r="AB43" s="76">
         <v>68.01</v>
       </c>
-      <c r="AC43" s="107">
+      <c r="AC43" s="108">
         <f t="shared" si="15"/>
         <v>67.42</v>
       </c>
@@ -24845,20 +25438,20 @@
     </row>
     <row r="44">
       <c r="C44" s="185" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D44" s="172">
         <f t="shared" si="17"/>
-        <v>1.88</v>
+        <v>2.07</v>
       </c>
       <c r="P44" s="170">
         <v>2.0</v>
       </c>
-      <c r="AB44" s="107">
+      <c r="AB44" s="108">
         <f t="shared" ref="AB44:AD44" si="18">AVERAGE(AB29:AB43)</f>
         <v>106.338</v>
       </c>
-      <c r="AC44" s="107">
+      <c r="AC44" s="108">
         <f t="shared" si="18"/>
         <v>87.95266667</v>
       </c>
@@ -24875,11 +25468,11 @@
     </row>
     <row r="45">
       <c r="C45" s="185" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D45" s="172">
         <f t="shared" si="17"/>
-        <v>0.61</v>
+        <v>0.67</v>
       </c>
       <c r="P45" s="170">
         <v>1.0</v>
@@ -24893,17 +25486,17 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="C46" s="185" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D46" s="172">
         <f t="shared" si="17"/>
-        <v>2.6</v>
+        <v>2.86</v>
       </c>
       <c r="G46" s="186" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H46" s="186" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P46" s="170">
         <v>0.0</v>
@@ -24917,11 +25510,11 @@
     </row>
     <row r="47">
       <c r="C47" s="185" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D47" s="172">
         <f t="shared" si="17"/>
-        <v>4.31</v>
+        <v>4.74</v>
       </c>
       <c r="G47" s="187" t="s">
         <v>34</v>
@@ -24947,11 +25540,11 @@
     </row>
     <row r="48">
       <c r="C48" s="185" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D48" s="172">
         <f t="shared" si="17"/>
-        <v>4.62</v>
+        <v>5.08</v>
       </c>
       <c r="G48" s="187" t="s">
         <v>35</v>
@@ -24960,7 +25553,7 @@
         <v>0.36678739680281</v>
       </c>
       <c r="J48" s="76" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K48" s="163">
         <f>AVERAGE(H47:H51)</f>
@@ -24984,11 +25577,11 @@
     </row>
     <row r="49">
       <c r="C49" s="185" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D49" s="172">
         <f t="shared" si="17"/>
-        <v>6.06</v>
+        <v>6.67</v>
       </c>
       <c r="G49" s="187" t="s">
         <v>37</v>
@@ -24997,7 +25590,7 @@
         <v>0.142870351877935</v>
       </c>
       <c r="J49" s="76" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K49" s="163">
         <f>MEDIAN(H47:H51)</f>
@@ -25006,7 +25599,7 @@
       <c r="P49" s="170">
         <v>1.0</v>
       </c>
-      <c r="AA49" s="115">
+      <c r="AA49" s="116">
         <v>1051.0</v>
       </c>
       <c r="AB49" s="76">
@@ -25021,11 +25614,11 @@
     </row>
     <row r="50">
       <c r="C50" s="185" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D50" s="172">
         <f t="shared" si="17"/>
-        <v>4.16</v>
+        <v>4.57</v>
       </c>
       <c r="G50" s="187" t="s">
         <v>38</v>
@@ -25034,7 +25627,7 @@
         <v>0.497437843674554</v>
       </c>
       <c r="J50" s="76" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K50" s="163">
         <f>PERCENTILE(H47:H51,0.25)</f>
@@ -25058,11 +25651,11 @@
     </row>
     <row r="51">
       <c r="C51" s="185" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D51" s="172">
         <f t="shared" si="17"/>
-        <v>4.83</v>
+        <v>5.31</v>
       </c>
       <c r="G51" s="187" t="s">
         <v>39</v>
@@ -25071,7 +25664,7 @@
         <v>0.247446036291655</v>
       </c>
       <c r="J51" s="76" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K51" s="163">
         <f>PERCENTILE(H47:H51,0.75)</f>
@@ -25080,7 +25673,7 @@
       <c r="P51" s="170">
         <v>2.0</v>
       </c>
-      <c r="AA51" s="115">
+      <c r="AA51" s="116">
         <v>1545.0</v>
       </c>
       <c r="AB51" s="76">
@@ -25095,16 +25688,16 @@
     </row>
     <row r="52">
       <c r="C52" s="185" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D52" s="172">
         <f t="shared" si="17"/>
-        <v>6.12</v>
+        <v>6.73</v>
       </c>
       <c r="P52" s="170">
         <v>0.0</v>
       </c>
-      <c r="AA52" s="115">
+      <c r="AA52" s="116">
         <v>1447.0</v>
       </c>
       <c r="AB52" s="76">
@@ -25119,16 +25712,16 @@
     </row>
     <row r="53">
       <c r="C53" s="185" t="s">
-        <v>258</v>
+        <v>312</v>
       </c>
       <c r="D53" s="172">
         <f t="shared" si="17"/>
-        <v>5.94</v>
+        <v>6.53</v>
       </c>
       <c r="P53" s="170">
         <v>0.0</v>
       </c>
-      <c r="AA53" s="115">
+      <c r="AA53" s="116">
         <v>1426.0</v>
       </c>
       <c r="AB53" s="76">
@@ -25143,16 +25736,16 @@
     </row>
     <row r="54">
       <c r="C54" s="185" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D54" s="172">
         <f t="shared" si="17"/>
-        <v>4.02</v>
+        <v>4.42</v>
       </c>
       <c r="P54" s="170">
         <v>2.0</v>
       </c>
-      <c r="AA54" s="115">
+      <c r="AA54" s="116">
         <v>1475.0</v>
       </c>
       <c r="AB54" s="76">
@@ -25167,16 +25760,16 @@
     </row>
     <row r="55">
       <c r="C55" s="185" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="D55" s="172">
         <f t="shared" si="17"/>
-        <v>7.42</v>
+        <v>8.16</v>
       </c>
       <c r="P55" s="170">
         <v>0.0</v>
       </c>
-      <c r="AA55" s="115">
+      <c r="AA55" s="116">
         <v>1606.0</v>
       </c>
       <c r="AB55" s="76">
@@ -25191,16 +25784,16 @@
     </row>
     <row r="56">
       <c r="C56" s="185" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D56" s="172">
         <f t="shared" si="17"/>
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="P56" s="170">
         <v>0.0</v>
       </c>
-      <c r="AA56" s="115">
+      <c r="AA56" s="116">
         <v>1614.0</v>
       </c>
       <c r="AB56" s="76">
@@ -25215,11 +25808,11 @@
     </row>
     <row r="57">
       <c r="C57" s="185" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D57" s="172">
         <f t="shared" si="17"/>
-        <v>0.79</v>
+        <v>0.86</v>
       </c>
       <c r="P57" s="170">
         <v>2.0</v>
@@ -25239,14 +25832,14 @@
     </row>
     <row r="58">
       <c r="C58" s="185" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D58" s="172">
         <f t="shared" si="17"/>
-        <v>0.86</v>
+        <v>0.95</v>
       </c>
       <c r="G58" s="189" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="H58" s="190"/>
       <c r="P58" s="170">
@@ -25267,15 +25860,15 @@
     </row>
     <row r="59">
       <c r="C59" s="185" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D59" s="172">
         <f t="shared" si="17"/>
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="G59" s="190"/>
       <c r="H59" s="191" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="P59" s="170">
         <v>0.0</v>
@@ -25295,20 +25888,20 @@
     </row>
     <row r="60">
       <c r="C60" s="185" t="s">
-        <v>319</v>
+        <v>272</v>
       </c>
       <c r="D60" s="172">
         <f t="shared" si="17"/>
-        <v>2.47</v>
+        <v>2.71</v>
       </c>
       <c r="G60" s="190"/>
       <c r="H60" s="191" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P60" s="170">
         <v>2.0</v>
       </c>
-      <c r="AA60" s="115">
+      <c r="AA60" s="116">
         <v>1526.0</v>
       </c>
       <c r="AB60" s="76">
@@ -25323,20 +25916,20 @@
     </row>
     <row r="61">
       <c r="C61" s="185" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D61" s="172">
         <f t="shared" si="17"/>
-        <v>0.97</v>
+        <v>1.06</v>
       </c>
       <c r="G61" s="190"/>
       <c r="H61" s="191" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="P61" s="170">
         <v>2.0</v>
       </c>
-      <c r="AA61" s="115">
+      <c r="AA61" s="116">
         <v>1448.0</v>
       </c>
       <c r="AB61" s="76">
@@ -25351,20 +25944,20 @@
     </row>
     <row r="62">
       <c r="C62" s="185" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D62" s="172">
         <f t="shared" si="17"/>
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="G62" s="190"/>
       <c r="H62" s="191" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P62" s="170">
         <v>1.0</v>
       </c>
-      <c r="AA62" s="115">
+      <c r="AA62" s="116">
         <v>1164.0</v>
       </c>
       <c r="AB62" s="76">
@@ -25379,15 +25972,15 @@
     </row>
     <row r="63">
       <c r="C63" s="185" t="s">
-        <v>255</v>
+        <v>326</v>
       </c>
       <c r="D63" s="172">
         <f t="shared" si="17"/>
-        <v>3.83</v>
+        <v>4.21</v>
       </c>
       <c r="G63" s="190"/>
       <c r="H63" s="191" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="P63" s="170">
         <v>0.0</v>
@@ -25401,11 +25994,11 @@
     </row>
     <row r="64">
       <c r="C64" s="185" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D64" s="172">
         <f t="shared" si="17"/>
-        <v>3.92</v>
+        <v>4.32</v>
       </c>
       <c r="P64" s="170">
         <v>1.0</v>
@@ -25419,11 +26012,11 @@
     </row>
     <row r="65">
       <c r="C65" s="185" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D65" s="172">
         <f t="shared" si="17"/>
-        <v>4.91</v>
+        <v>5.4</v>
       </c>
       <c r="P65" s="170">
         <v>2.0</v>
@@ -25437,11 +26030,11 @@
     </row>
     <row r="66">
       <c r="C66" s="185" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D66" s="172">
         <f t="shared" si="17"/>
-        <v>1.96</v>
+        <v>0.96</v>
       </c>
       <c r="P66" s="170">
         <v>0.0</v>
@@ -25455,11 +26048,11 @@
     </row>
     <row r="67">
       <c r="C67" s="185" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D67" s="172">
         <f t="shared" si="17"/>
-        <v>3.78</v>
+        <v>0.94</v>
       </c>
       <c r="P67" s="170">
         <v>0.0</v>
@@ -25473,11 +26066,11 @@
     </row>
     <row r="68">
       <c r="C68" s="185" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D68" s="172">
         <f t="shared" si="17"/>
-        <v>2.94</v>
+        <v>6.68</v>
       </c>
       <c r="P68" s="170">
         <v>1.0</v>
@@ -25491,11 +26084,11 @@
     </row>
     <row r="69">
       <c r="C69" s="185" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D69" s="172">
         <f t="shared" si="17"/>
-        <v>2.59</v>
+        <v>4.79</v>
       </c>
       <c r="P69" s="170">
         <v>2.0</v>
@@ -25509,11 +26102,11 @@
     </row>
     <row r="70">
       <c r="C70" s="185" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D70" s="172">
         <f t="shared" si="17"/>
-        <v>2.18</v>
+        <v>5.93</v>
       </c>
       <c r="P70" s="170">
         <v>1.0</v>
@@ -25527,11 +26120,11 @@
     </row>
     <row r="71">
       <c r="C71" s="185" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D71" s="172">
         <f t="shared" si="17"/>
-        <v>2.03</v>
+        <v>7.29</v>
       </c>
       <c r="F71" s="192"/>
       <c r="P71" s="170">
@@ -25546,11 +26139,11 @@
     </row>
     <row r="72">
       <c r="C72" s="185" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D72" s="172">
         <f t="shared" si="17"/>
-        <v>3.85</v>
+        <v>4.04</v>
       </c>
       <c r="P72" s="170">
         <v>0.0</v>
@@ -25564,11 +26157,11 @@
     </row>
     <row r="73">
       <c r="C73" s="185" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="D73" s="172">
         <f t="shared" si="17"/>
-        <v>7.02</v>
+        <v>4.1</v>
       </c>
       <c r="P73" s="170">
         <v>1.0</v>
@@ -25582,11 +26175,11 @@
     </row>
     <row r="74">
       <c r="C74" s="185" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D74" s="172">
         <f t="shared" si="17"/>
-        <v>9.13</v>
+        <v>4.01</v>
       </c>
       <c r="P74" s="170">
         <v>0.0</v>
@@ -25600,11 +26193,11 @@
     </row>
     <row r="75">
       <c r="C75" s="185" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D75" s="172">
         <f t="shared" si="17"/>
-        <v>5.79</v>
+        <v>5.14</v>
       </c>
       <c r="P75" s="170">
         <v>1.0</v>
@@ -25618,11 +26211,11 @@
     </row>
     <row r="76">
       <c r="C76" s="185" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="D76" s="172">
         <f t="shared" si="17"/>
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="P76" s="170">
         <v>0.0</v>
@@ -25636,11 +26229,11 @@
     </row>
     <row r="77">
       <c r="C77" s="185" t="s">
-        <v>271</v>
+        <v>341</v>
       </c>
       <c r="D77" s="172">
         <f t="shared" si="17"/>
-        <v>2.71</v>
+        <v>2.98</v>
       </c>
       <c r="P77" s="170">
         <v>0.0</v>
@@ -25654,11 +26247,11 @@
     </row>
     <row r="78">
       <c r="C78" s="185" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="D78" s="172">
         <f t="shared" si="17"/>
-        <v>1.9</v>
+        <v>2.09</v>
       </c>
       <c r="P78" s="170">
         <v>1.0</v>
@@ -25672,11 +26265,11 @@
     </row>
     <row r="79">
       <c r="C79" s="185" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="D79" s="172">
         <f t="shared" si="17"/>
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="P79" s="170">
         <v>2.0</v>
@@ -25690,11 +26283,11 @@
     </row>
     <row r="80">
       <c r="C80" s="185" t="s">
-        <v>243</v>
+        <v>344</v>
       </c>
       <c r="D80" s="172">
         <f t="shared" si="17"/>
-        <v>5.8</v>
+        <v>6.38</v>
       </c>
       <c r="P80" s="170">
         <v>1.0</v>
@@ -25708,11 +26301,11 @@
     </row>
     <row r="81">
       <c r="C81" s="185" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="D81" s="172">
         <f t="shared" si="17"/>
-        <v>5.85</v>
+        <v>6.44</v>
       </c>
       <c r="P81" s="170">
         <v>2.0</v>
@@ -25726,11 +26319,11 @@
     </row>
     <row r="82">
       <c r="C82" s="185" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="D82" s="172">
         <f t="shared" si="17"/>
-        <v>5.7</v>
+        <v>6.26</v>
       </c>
       <c r="P82" s="170">
         <v>1.0</v>
@@ -25744,11 +26337,11 @@
     </row>
     <row r="83">
       <c r="C83" s="185" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="D83" s="172">
         <f t="shared" si="17"/>
-        <v>3.17</v>
+        <v>3.49</v>
       </c>
       <c r="P83" s="170">
         <v>0.0</v>
@@ -25762,11 +26355,11 @@
     </row>
     <row r="84">
       <c r="C84" s="185" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="D84" s="172">
         <f t="shared" si="17"/>
-        <v>5.67</v>
+        <v>6.24</v>
       </c>
       <c r="P84" s="170">
         <v>1.0</v>
@@ -25780,11 +26373,11 @@
     </row>
     <row r="85">
       <c r="C85" s="185" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="D85" s="172">
         <f t="shared" si="17"/>
-        <v>3.55</v>
+        <v>3.91</v>
       </c>
       <c r="P85" s="170">
         <v>0.0</v>
@@ -25798,11 +26391,11 @@
     </row>
     <row r="86">
       <c r="C86" s="185" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D86" s="172">
         <f t="shared" si="17"/>
-        <v>5.76</v>
+        <v>6.33</v>
       </c>
       <c r="P86" s="170">
         <v>0.0</v>
@@ -25816,11 +26409,11 @@
     </row>
     <row r="87">
       <c r="C87" s="185" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="D87" s="172">
         <f t="shared" si="17"/>
-        <v>2.02</v>
+        <v>2.22</v>
       </c>
       <c r="P87" s="170">
         <v>1.0</v>
@@ -25834,11 +26427,11 @@
     </row>
     <row r="88">
       <c r="C88" s="185" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="D88" s="172">
         <f t="shared" si="17"/>
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="P88" s="170">
         <v>2.0</v>
@@ -25852,11 +26445,11 @@
     </row>
     <row r="89">
       <c r="C89" s="185" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="D89" s="172">
         <f t="shared" si="17"/>
-        <v>3.12</v>
+        <v>3.43</v>
       </c>
       <c r="P89" s="170">
         <v>2.0</v>
@@ -25870,11 +26463,11 @@
     </row>
     <row r="90">
       <c r="C90" s="185" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D90" s="172">
         <f t="shared" si="17"/>
-        <v>1.97</v>
+        <v>2.16</v>
       </c>
       <c r="P90" s="170">
         <v>1.0</v>
@@ -25888,11 +26481,11 @@
     </row>
     <row r="91">
       <c r="C91" s="185" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="D91" s="172">
         <f t="shared" si="17"/>
-        <v>3.41</v>
+        <v>3.75</v>
       </c>
       <c r="P91" s="170">
         <v>1.0</v>
@@ -25906,11 +26499,11 @@
     </row>
     <row r="92">
       <c r="C92" s="185" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="D92" s="172">
         <f t="shared" si="17"/>
-        <v>5.59</v>
+        <v>6.15</v>
       </c>
       <c r="P92" s="170">
         <v>2.0</v>
@@ -25924,11 +26517,11 @@
     </row>
     <row r="93">
       <c r="C93" s="185" t="s">
-        <v>283</v>
+        <v>357</v>
       </c>
       <c r="D93" s="172">
         <f t="shared" si="17"/>
-        <v>5.56</v>
+        <v>6.12</v>
       </c>
       <c r="P93" s="170">
         <v>0.0</v>
@@ -25942,11 +26535,11 @@
     </row>
     <row r="94">
       <c r="C94" s="185" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="D94" s="172">
         <f t="shared" si="17"/>
-        <v>5.41</v>
+        <v>5.96</v>
       </c>
       <c r="P94" s="170">
         <v>0.0</v>
@@ -25960,11 +26553,11 @@
     </row>
     <row r="95">
       <c r="C95" s="185" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="D95" s="172">
         <f t="shared" si="17"/>
-        <v>2.31</v>
+        <v>2.54</v>
       </c>
       <c r="P95" s="170">
         <v>1.0</v>
@@ -25978,11 +26571,11 @@
     </row>
     <row r="96">
       <c r="C96" s="185" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="D96" s="172">
         <f t="shared" si="17"/>
-        <v>2.34</v>
+        <v>2.57</v>
       </c>
       <c r="P96" s="170">
         <v>2.0</v>
@@ -25996,11 +26589,11 @@
     </row>
     <row r="97">
       <c r="C97" s="185" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="D97" s="172">
         <f t="shared" si="17"/>
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="P97" s="170">
         <v>0.0</v>
@@ -48874,14 +49467,14 @@
     <row r="1">
       <c r="A1" s="197"/>
       <c r="B1" s="198" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="C1" s="199"/>
       <c r="D1" s="199"/>
       <c r="E1" s="199"/>
       <c r="F1" s="199"/>
       <c r="G1" s="200" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="H1" s="199"/>
       <c r="I1" s="199"/>
@@ -48915,54 +49508,54 @@
         <v>3</v>
       </c>
       <c r="B2" s="202" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="C2" s="203" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="D2" s="203" t="s">
         <v>44</v>
       </c>
       <c r="E2" s="203" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="F2" s="204" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="G2" s="202">
         <v>1.0</v>
       </c>
       <c r="H2" s="203" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I2" s="203">
         <v>2.0</v>
       </c>
       <c r="J2" s="203" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="K2" s="205" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="L2" s="203" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="M2" s="206" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="N2" s="187" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="O2" s="187" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="P2" s="187" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="Q2" s="17"/>
       <c r="R2" s="17"/>
       <c r="S2" s="6" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="T2" s="17"/>
       <c r="U2" s="17"/>
@@ -49052,7 +49645,7 @@
       <c r="Q4" s="17"/>
       <c r="R4" s="17"/>
       <c r="S4" s="212" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="T4" s="213"/>
       <c r="Z4" s="90"/>
@@ -49088,7 +49681,7 @@
       <c r="P5" s="215"/>
       <c r="S5" s="213"/>
       <c r="T5" s="216" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
     </row>
     <row r="6">
@@ -49121,11 +49714,11 @@
       <c r="R6" s="17"/>
       <c r="S6" s="213"/>
       <c r="T6" s="216" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="Z6" s="151"/>
       <c r="AD6" s="76" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
     </row>
     <row r="7">
@@ -49155,7 +49748,7 @@
       <c r="O7" s="143"/>
       <c r="P7" s="218"/>
       <c r="AD7" s="216" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="AE7" s="213"/>
       <c r="AF7" s="213"/>
@@ -49188,11 +49781,11 @@
       <c r="O8" s="143"/>
       <c r="P8" s="218"/>
       <c r="S8" s="216" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="AA8" s="151"/>
       <c r="AD8" s="216" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
     </row>
     <row r="9">
@@ -49391,7 +49984,7 @@
       <c r="O15" s="143"/>
       <c r="P15" s="218"/>
       <c r="S15" s="76" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
     </row>
     <row r="16">
@@ -49504,7 +50097,7 @@
       <c r="Q19" s="17"/>
       <c r="R19" s="17"/>
       <c r="S19" s="76" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="20">
@@ -49642,7 +50235,7 @@
     </row>
     <row r="24">
       <c r="A24" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B24" s="222" t="str">
         <f t="shared" ref="B24:F24" si="4">IFERROR(AVERAGE(B3:B22),"")</f>
@@ -49788,7 +50381,7 @@
       <c r="E27" s="17"/>
       <c r="F27" s="17"/>
       <c r="G27" s="223" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="H27" s="17"/>
       <c r="I27" s="17"/>
@@ -49833,7 +50426,7 @@
         <v>1.0</v>
       </c>
       <c r="H28" s="224" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I28" s="224">
         <v>2.0</v>
@@ -49873,7 +50466,7 @@
       <c r="B29" s="17"/>
       <c r="C29" s="17"/>
       <c r="D29" s="4" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="E29" s="4">
         <f>J29</f>
@@ -49895,10 +50488,10 @@
       </c>
       <c r="K29" s="17"/>
       <c r="L29" s="6" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="O29" s="4">
         <v>1.0</v>
@@ -49998,7 +50591,7 @@
       </c>
       <c r="R31" s="17"/>
       <c r="S31" s="6" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="T31" s="17"/>
       <c r="U31" s="17"/>
@@ -50060,7 +50653,7 @@
       <c r="E33" s="17"/>
       <c r="F33" s="17"/>
       <c r="G33" s="168" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="J33" s="17"/>
       <c r="K33" s="17"/>
@@ -50074,10 +50667,10 @@
       <c r="P33" s="17"/>
       <c r="R33" s="17"/>
       <c r="T33" s="93" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="W33" s="76" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="AA33" s="90"/>
       <c r="AD33" s="17"/>
@@ -50096,7 +50689,7 @@
         <v>1.0</v>
       </c>
       <c r="H34" s="227" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I34" s="227">
         <v>2.0</v>
@@ -50113,14 +50706,14 @@
       <c r="O34" s="17"/>
       <c r="P34" s="17"/>
       <c r="R34" s="17"/>
-      <c r="S34" s="107" t="s">
+      <c r="S34" s="108" t="s">
         <v>19</v>
       </c>
       <c r="T34" s="83">
         <v>1626.0</v>
       </c>
       <c r="U34" s="83" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="W34" s="76">
         <v>5193.0</v>
@@ -50158,14 +50751,14 @@
       <c r="O35" s="17"/>
       <c r="P35" s="17"/>
       <c r="R35" s="17"/>
-      <c r="S35" s="107" t="s">
+      <c r="S35" s="108" t="s">
         <v>23</v>
       </c>
       <c r="T35" s="83">
         <v>4176.0</v>
       </c>
       <c r="U35" s="83" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="W35" s="76">
         <v>4863.0</v>
@@ -50263,7 +50856,7 @@
       <c r="D38" s="17"/>
       <c r="E38" s="17"/>
       <c r="F38" s="4" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="G38" s="226">
         <f t="shared" ref="G38:I38" si="8">G30-G35</f>
@@ -50465,7 +51058,7 @@
       <c r="Q45" s="17"/>
       <c r="R45" s="17"/>
       <c r="T45" s="216" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="AD45" s="17"/>
       <c r="AE45" s="17"/>
@@ -50602,10 +51195,10 @@
         <v>4</v>
       </c>
       <c r="X49" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Y49" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Z49" s="4" t="s">
         <v>5</v>
@@ -50620,16 +51213,16 @@
         <v>8</v>
       </c>
       <c r="AD49" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="AE49" s="60" t="s">
+        <v>174</v>
+      </c>
+      <c r="AF49" s="60" t="s">
         <v>159</v>
       </c>
-      <c r="AE49" s="60" t="s">
-        <v>173</v>
-      </c>
-      <c r="AF49" s="60" t="s">
-        <v>158</v>
-      </c>
       <c r="AG49" s="60" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="50">
@@ -50794,7 +51387,7 @@
         <v>13.03594852814783</v>
       </c>
       <c r="AG52" s="60" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="53">
@@ -50855,7 +51448,7 @@
         <v>6.291840048860032</v>
       </c>
       <c r="AG53" s="60" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="54">
@@ -50916,7 +51509,7 @@
         <v>2.7243520649411117</v>
       </c>
       <c r="AG54" s="60" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="55">
@@ -50977,7 +51570,7 @@
         <v>2.1429979739456915</v>
       </c>
       <c r="AG55" s="60" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="56">
@@ -51038,7 +51631,7 @@
         <v>3.98032040346951</v>
       </c>
       <c r="AG56" s="60" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="57">
@@ -51261,10 +51854,10 @@
       <c r="R62" s="17"/>
       <c r="S62" s="17"/>
       <c r="U62" s="76" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="V62" s="76" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="AC62" s="17"/>
       <c r="AD62" s="17"/>
@@ -51306,7 +51899,7 @@
         <v>2165.0</v>
       </c>
       <c r="W63" s="76" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="AC63" s="17"/>
       <c r="AD63" s="17"/>
@@ -51940,7 +52533,7 @@
       <c r="R79" s="17"/>
       <c r="S79" s="17"/>
       <c r="T79" s="6" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="U79" s="17"/>
       <c r="V79" s="17"/>
@@ -51981,7 +52574,7 @@
       <c r="R80" s="17"/>
       <c r="S80" s="17"/>
       <c r="T80" s="76" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="U80" s="21"/>
       <c r="V80" s="21"/>

--- a/data/df_best_models.xlsx
+++ b/data/df_best_models.xlsx
@@ -611,7 +611,7 @@
         <v>45883</v>
       </c>
       <c r="D3" s="14">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E3" s="11" t="s">
         <v>8</v>

--- a/data/df_best_models.xlsx
+++ b/data/df_best_models.xlsx
@@ -490,10 +490,10 @@
         </is>
       </c>
       <c r="C3" s="2" t="n">
-        <v>45889</v>
+        <v>45895</v>
       </c>
       <c r="D3" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -511,14 +511,14 @@
         </is>
       </c>
       <c r="C4" s="2" t="n">
-        <v>45889</v>
+        <v>45895</v>
       </c>
       <c r="D4" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>SVC</t>
+          <t>RandomForestClassifier</t>
         </is>
       </c>
     </row>
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="C5" s="2" t="n">
-        <v>45889</v>
+        <v>45895</v>
       </c>
       <c r="D5" t="n">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SVC</t>
+          <t>XGBClassifier</t>
         </is>
       </c>
     </row>
@@ -553,14 +553,14 @@
         </is>
       </c>
       <c r="C6" s="2" t="n">
-        <v>45889</v>
+        <v>45895</v>
       </c>
       <c r="D6" t="n">
-        <v>29</v>
+        <v>94</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>XGBClassifier</t>
         </is>
       </c>
     </row>
@@ -574,10 +574,10 @@
         </is>
       </c>
       <c r="C7" s="2" t="n">
-        <v>45889</v>
+        <v>45895</v>
       </c>
       <c r="D7" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>

--- a/data/df_best_models.xlsx
+++ b/data/df_best_models.xlsx
@@ -493,11 +493,11 @@
         <v>45895</v>
       </c>
       <c r="D3" t="n">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>RandomForestClassifier</t>
         </is>
       </c>
     </row>
@@ -514,11 +514,11 @@
         <v>45895</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RandomForestClassifier</t>
+          <t>XGBClassifier</t>
         </is>
       </c>
     </row>
@@ -535,11 +535,11 @@
         <v>45895</v>
       </c>
       <c r="D5" t="n">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>XGBClassifier</t>
+          <t>RandomForestClassifier</t>
         </is>
       </c>
     </row>
@@ -556,11 +556,11 @@
         <v>45895</v>
       </c>
       <c r="D6" t="n">
-        <v>94</v>
+        <v>3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>XGBClassifier</t>
+          <t>RandomForestClassifier</t>
         </is>
       </c>
     </row>
@@ -577,11 +577,11 @@
         <v>45895</v>
       </c>
       <c r="D7" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>RandomForestClassifier</t>
         </is>
       </c>
     </row>

--- a/data/df_best_models.xlsx
+++ b/data/df_best_models.xlsx
@@ -40,16 +40,16 @@
     <t>england</t>
   </si>
   <si>
+    <t>france</t>
+  </si>
+  <si>
+    <t>XGBClassifier</t>
+  </si>
+  <si>
+    <t>germany</t>
+  </si>
+  <si>
     <t>RandomForestClassifier</t>
-  </si>
-  <si>
-    <t>france</t>
-  </si>
-  <si>
-    <t>germany</t>
-  </si>
-  <si>
-    <t>XGBClassifier</t>
   </si>
   <si>
     <t>italy</t>
@@ -71,7 +71,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd hh:mm:ss"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -81,7 +81,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -139,13 +145,13 @@
     <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -466,10 +472,10 @@
     <col min="2" max="2" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="4" max="4" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="8" width="17.14785714285714" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="20.25">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -486,7 +492,7 @@
         <v>4</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="17.25">
       <c r="A2" s="4">
         <v>6</v>
       </c>
@@ -503,7 +509,7 @@
         <v>6</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="17.25">
       <c r="A3" s="4">
         <v>48</v>
       </c>
@@ -514,30 +520,30 @@
         <v>45895</v>
       </c>
       <c r="D3" s="4">
-        <v>79</v>
+        <v>23</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
+        <v>6</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="17.25">
       <c r="A4" s="4">
         <v>55</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" s="6">
         <v>45895</v>
       </c>
       <c r="D4" s="4">
-        <v>84</v>
+        <v>12</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
+        <v>9</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="17.25">
       <c r="A5" s="4">
         <v>59</v>
       </c>
@@ -548,13 +554,13 @@
         <v>45895</v>
       </c>
       <c r="D5" s="4">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="17.25">
       <c r="A6" s="4">
         <v>77</v>
       </c>
@@ -565,13 +571,13 @@
         <v>45895</v>
       </c>
       <c r="D6" s="4">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
+        <v>6</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="17.25">
       <c r="A7" s="4">
         <v>148</v>
       </c>
@@ -582,13 +588,13 @@
         <v>45895</v>
       </c>
       <c r="D7" s="4">
-        <v>120</v>
+        <v>54</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
+        <v>6</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="17.25">
       <c r="A8" s="4">
         <v>167</v>
       </c>

--- a/data/df_best_models.xlsx
+++ b/data/df_best_models.xlsx
@@ -40,16 +40,16 @@
     <t>england</t>
   </si>
   <si>
+    <t>RandomForestClassifier</t>
+  </si>
+  <si>
     <t>france</t>
   </si>
   <si>
+    <t>germany</t>
+  </si>
+  <si>
     <t>XGBClassifier</t>
-  </si>
-  <si>
-    <t>germany</t>
-  </si>
-  <si>
-    <t>RandomForestClassifier</t>
   </si>
   <si>
     <t>italy</t>
@@ -472,7 +472,7 @@
     <col min="2" max="2" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="4" max="4" style="7" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="8" width="17.14785714285714" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="8" width="12.43357142857143" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
@@ -520,10 +520,10 @@
         <v>45895</v>
       </c>
       <c r="D3" s="4">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="17.25">
@@ -531,16 +531,16 @@
         <v>55</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" s="6">
         <v>45895</v>
       </c>
       <c r="D4" s="4">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="17.25">
@@ -554,7 +554,7 @@
         <v>45895</v>
       </c>
       <c r="D5" s="4">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>11</v>
@@ -571,10 +571,10 @@
         <v>45895</v>
       </c>
       <c r="D6" s="4">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="17.25">
@@ -588,10 +588,10 @@
         <v>45895</v>
       </c>
       <c r="D7" s="4">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="17.25">

--- a/data/df_best_models.xlsx
+++ b/data/df_best_models.xlsx
@@ -1,40 +1,97 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nachomondino/Documents/GitHub/predictor-apuestas/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFAC367B-B2F2-C240-9F62-D826E8E22E11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="20740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="15">
+  <si>
+    <t>id_country</t>
+  </si>
+  <si>
+    <t>country</t>
+  </si>
+  <si>
+    <t>iteration_date</t>
+  </si>
+  <si>
+    <t>n_model</t>
+  </si>
+  <si>
+    <t>model_name</t>
+  </si>
+  <si>
+    <t>argentina</t>
+  </si>
+  <si>
+    <t>LogisticRegression</t>
+  </si>
+  <si>
+    <t>england</t>
+  </si>
+  <si>
+    <t>RandomForestClassifier</t>
+  </si>
+  <si>
+    <t>france</t>
+  </si>
+  <si>
+    <t>germany</t>
+  </si>
+  <si>
+    <t>italy</t>
+  </si>
+  <si>
+    <t>spain</t>
+  </si>
+  <si>
+    <t>usa</t>
+  </si>
+  <si>
+    <t>SVC</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -49,94 +106,44 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -424,186 +431,147 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="17.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>id_country</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>country</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>iteration_date</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>n_model</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>model_name</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2">
         <v>6</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>argentina</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>45895</v>
-      </c>
-      <c r="D2" t="n">
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2">
+        <v>45895</v>
+      </c>
+      <c r="D2">
         <v>1</v>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>LogisticRegression</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3">
         <v>48</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>england</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="n">
-        <v>45895</v>
-      </c>
-      <c r="D3" t="n">
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2">
+        <v>45895</v>
+      </c>
+      <c r="D3">
+        <v>3</v>
+      </c>
+      <c r="E3" t="s">
         <v>6</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>RandomForestClassifier</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4">
         <v>55</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>france</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="n">
-        <v>45895</v>
-      </c>
-      <c r="D4" t="n">
-        <v>49</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>LogisticRegression</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2">
+        <v>45895</v>
+      </c>
+      <c r="D4">
+        <v>37</v>
+      </c>
+      <c r="E4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5">
         <v>59</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="n">
-        <v>45895</v>
-      </c>
-      <c r="D5" t="n">
-        <v>128</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>RandomForestClassifier</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="2">
+        <v>45895</v>
+      </c>
+      <c r="D5">
+        <v>31</v>
+      </c>
+      <c r="E5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6">
         <v>77</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>45895</v>
-      </c>
-      <c r="D6" t="n">
-        <v>18</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>LogisticRegression</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="2">
+        <v>45895</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="E6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7">
         <v>148</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>spain</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="n">
-        <v>45895</v>
-      </c>
-      <c r="D7" t="n">
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="2">
+        <v>45895</v>
+      </c>
+      <c r="D7">
         <v>54</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>LogisticRegression</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
+      <c r="E7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8">
         <v>167</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>usa</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="n">
-        <v>45895</v>
-      </c>
-      <c r="D8" t="n">
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="2">
+        <v>45895</v>
+      </c>
+      <c r="D8">
         <v>1</v>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>SVC</t>
-        </is>
+      <c r="E8" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/data/df_best_models.xlsx
+++ b/data/df_best_models.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nachomondino/Documents/GitHub/predictor-apuestas/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFAC367B-B2F2-C240-9F62-D826E8E22E11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90FE5CFF-D282-4B40-A18D-3E2234B14952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="20740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
   <si>
     <t>id_country</t>
   </si>
@@ -40,19 +40,22 @@
     <t>argentina</t>
   </si>
   <si>
+    <t>RandomForestClassifier</t>
+  </si>
+  <si>
+    <t>england</t>
+  </si>
+  <si>
     <t>LogisticRegression</t>
   </si>
   <si>
-    <t>england</t>
-  </si>
-  <si>
-    <t>RandomForestClassifier</t>
-  </si>
-  <si>
     <t>france</t>
   </si>
   <si>
     <t>germany</t>
+  </si>
+  <si>
+    <t>XGBClassifier</t>
   </si>
   <si>
     <t>italy</t>
@@ -72,7 +75,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -129,7 +132,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -434,9 +437,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="3" max="3" width="17.6640625" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
@@ -469,7 +469,7 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
@@ -483,10 +483,10 @@
         <v>45895</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
@@ -500,10 +500,10 @@
         <v>45895</v>
       </c>
       <c r="D4">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -517,10 +517,10 @@
         <v>45895</v>
       </c>
       <c r="D5">
-        <v>31</v>
+        <v>124</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
@@ -528,16 +528,16 @@
         <v>77</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" s="2">
         <v>45895</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -545,16 +545,16 @@
         <v>148</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" s="2">
         <v>45895</v>
       </c>
       <c r="D7">
-        <v>54</v>
+        <v>118</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -562,7 +562,7 @@
         <v>167</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" s="2">
         <v>45895</v>
@@ -571,7 +571,7 @@
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/data/df_best_models.xlsx
+++ b/data/df_best_models.xlsx
@@ -1,100 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nachomondino/Documents/GitHub/predictor-apuestas/data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90FE5CFF-D282-4B40-A18D-3E2234B14952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="20740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
-  <si>
-    <t>id_country</t>
-  </si>
-  <si>
-    <t>country</t>
-  </si>
-  <si>
-    <t>iteration_date</t>
-  </si>
-  <si>
-    <t>n_model</t>
-  </si>
-  <si>
-    <t>model_name</t>
-  </si>
-  <si>
-    <t>argentina</t>
-  </si>
-  <si>
-    <t>RandomForestClassifier</t>
-  </si>
-  <si>
-    <t>england</t>
-  </si>
-  <si>
-    <t>LogisticRegression</t>
-  </si>
-  <si>
-    <t>france</t>
-  </si>
-  <si>
-    <t>germany</t>
-  </si>
-  <si>
-    <t>XGBClassifier</t>
-  </si>
-  <si>
-    <t>italy</t>
-  </si>
-  <si>
-    <t>spain</t>
-  </si>
-  <si>
-    <t>usa</t>
-  </si>
-  <si>
-    <t>SVC</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -109,44 +49,94 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -434,144 +424,186 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>id_country</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>iteration_date</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>n_model</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>model_name</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>argentina</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>45895</v>
+      </c>
+      <c r="D2" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="2">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>RandomForestClassifier</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>48</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>england</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
         <v>45895</v>
       </c>
-      <c r="D2">
+      <c r="D3" t="n">
+        <v>23</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>55</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>france</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>45895</v>
+      </c>
+      <c r="D4" t="n">
+        <v>12</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>59</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>45895</v>
+      </c>
+      <c r="D5" t="n">
+        <v>128</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>77</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>45895</v>
+      </c>
+      <c r="D6" t="n">
+        <v>94</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>148</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>spain</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>45895</v>
+      </c>
+      <c r="D7" t="n">
+        <v>30</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>LogisticRegression</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>167</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>45895</v>
+      </c>
+      <c r="D8" t="n">
         <v>1</v>
       </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3">
-        <v>48</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="2">
-        <v>45895</v>
-      </c>
-      <c r="D3">
-        <v>49</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4">
-        <v>55</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="2">
-        <v>45895</v>
-      </c>
-      <c r="D4">
-        <v>71</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5">
-        <v>59</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="2">
-        <v>45895</v>
-      </c>
-      <c r="D5">
-        <v>124</v>
-      </c>
-      <c r="E5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>77</v>
-      </c>
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="2">
-        <v>45895</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>148</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="2">
-        <v>45895</v>
-      </c>
-      <c r="D7">
-        <v>118</v>
-      </c>
-      <c r="E7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>167</v>
-      </c>
-      <c r="B8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="2">
-        <v>45895</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8" t="s">
-        <v>15</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>SVC</t>
+        </is>
       </c>
     </row>
   </sheetData>
